--- a/阵营/大小攻防团队监控.xlsx
+++ b/阵营/大小攻防团队监控.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JX3\Game\JX3\bin\zhcn_hd\interface\MY#DATA\!all-users@zhcn_hd\userdata\team_mon\remote\打包\阵营\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{3506E3FC-C330-49C4-A10D-27C7AC32B185}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{61038297-F7D4-4ADA-9AEE-01964B446BE1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据总控" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">角色喊话!$A$1:$AV$183</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">系统角色!$A$1:$X$404</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">系统频道!$A$1:$BG$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">系统频道!$A$1:$BG$149</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">有利气劲!$A$1:$AS$46</definedName>
     <definedName name="JunSun1" localSheetId="6">DATE(交互物件!日历年份,6,1)-WEEKDAY(DATE(交互物件!日历年份,6,1))</definedName>
     <definedName name="JunSun1" localSheetId="4">DATE(武学招式!日历年份,6,1)-WEEKDAY(DATE(武学招式!日历年份,6,1))</definedName>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="5658" uniqueCount="2734">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="5683" uniqueCount="2734">
   <si>
     <t>标识</t>
   </si>
@@ -10743,7 +10743,7 @@
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="21" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1769517860930,</v>
+        <v>nTimeStamp = 1772372969870,</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>34</v>
@@ -42220,7 +42220,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F872A71-AE2F-48FF-A98F-0D6E9F4CDE78}">
-  <dimension ref="A1:BT147"/>
+  <dimension ref="A1:BT153"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="88" customWidth="1"/>
@@ -42334,7 +42334,7 @@
         <v>1</v>
       </c>
       <c r="T3" s="36" t="str">
-        <f t="shared" ref="T3:T66" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(L3),ISBLANK(M3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(L2)=FALSE,ISBLANK(M2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(K3&lt;&gt;"","col={"&amp;K3&amp;"},","")&amp;IF(L3&gt;0,"bSearch=true,","")&amp;IF(M3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N3&gt;0,"szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bTeamChannel=true,","")&amp;IF(P3&gt;0,"bWhisperChannel=true,","")&amp;IF(Q3&gt;0,"bCenterAlarm=true,","")&amp;IF(R3&gt;0,"bScreenHead=true,","")&amp;IF(S3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U3:AAF3)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="T3:T72" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(L3),ISBLANK(M3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(L2)=FALSE,ISBLANK(M2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(K3&lt;&gt;"","col={"&amp;K3&amp;"},","")&amp;IF(L3&gt;0,"bSearch=true,","")&amp;IF(M3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N3&gt;0,"szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bTeamChannel=true,","")&amp;IF(P3&gt;0,"bWhisperChannel=true,","")&amp;IF(Q3&gt;0,"bCenterAlarm=true,","")&amp;IF(R3&gt;0,"bScreenHead=true,","")&amp;IF(S3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U3:AAF3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="[团队监控]数据加载成功",szNote="关闭刷马等计时条",bSearch=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},},},</v>
       </c>
       <c r="U3" s="40" t="s">
@@ -43463,1205 +43463,1171 @@
     </row>
     <row r="38" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C38" s="36" t="s">
+        <v>1936</v>
+      </c>
+      <c r="D38" s="36" t="s">
+        <v>1938</v>
+      </c>
+      <c r="K38" s="36" t="s">
+        <v>1438</v>
+      </c>
+      <c r="T38" s="36" t="str">
+        <f t="shared" ref="T38:T40" si="1">IF(ISBLANK(B38)=FALSE,IF(ISBLANK(B37),"},["&amp;B38&amp;"]={","["&amp;B38&amp;"]={"),IF(AND(ISBLANK(B38),ISBLANK(C38),ISBLANK(L38),ISBLANK(M38),OR(ISBLANK(B37)=FALSE,ISBLANK(C37)=FALSE,ISBLANK(L37)=FALSE,ISBLANK(M37)=FALSE)),"},},}",IF(ISBLANK(C38),"","{szContent="""&amp;C38&amp;""","&amp;IF(D38&lt;&gt;"","szNote="""&amp;D38&amp;""",","")&amp;IF(K38&lt;&gt;"","col={"&amp;K38&amp;"},","")&amp;IF(L38&gt;0,"bSearch=true,","")&amp;IF(M38&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N38&gt;0,"szVoice="""&amp;N38&amp;""",","")&amp;IF(O38&gt;0,"bTeamChannel=true,","")&amp;IF(P38&gt;0,"bWhisperChannel=true,","")&amp;IF(Q38&gt;0,"bCenterAlarm=true,","")&amp;IF(R38&gt;0,"bScreenHead=true,","")&amp;IF(S38&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U38&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U38:AAF38)&amp;"},","")&amp;"},")))</f>
+        <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
+      </c>
+      <c r="U38" s="36" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C39" s="36" t="s">
+        <v>1935</v>
+      </c>
+      <c r="D39" s="36" t="s">
+        <v>1937</v>
+      </c>
+      <c r="K39" s="36" t="s">
+        <v>1565</v>
+      </c>
+      <c r="T39" s="36" t="str">
+        <f t="shared" si="1"/>
+        <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
+      </c>
+      <c r="U39" s="36" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C40" s="36" t="s">
+        <v>1932</v>
+      </c>
+      <c r="D40" s="36" t="s">
+        <v>2131</v>
+      </c>
+      <c r="K40" s="36" t="s">
+        <v>1432</v>
+      </c>
+      <c r="Q40" s="36">
+        <v>1</v>
+      </c>
+      <c r="T40" s="36" t="str">
+        <f t="shared" si="1"/>
+        <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
+      </c>
+      <c r="U40" s="36" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C41" s="36" t="s">
         <v>2202</v>
       </c>
-      <c r="D38" s="36" t="s">
+      <c r="D41" s="36" t="s">
         <v>2203</v>
       </c>
-      <c r="K38" s="36" t="s">
+      <c r="K41" s="36" t="s">
         <v>1432</v>
       </c>
-      <c r="T38" s="36" t="str">
+      <c r="T41" s="36" t="str">
+        <f>IF(ISBLANK(B41)=FALSE,IF(ISBLANK(B37),"},["&amp;B41&amp;"]={","["&amp;B41&amp;"]={"),IF(AND(ISBLANK(B41),ISBLANK(C41),ISBLANK(L41),ISBLANK(M41),OR(ISBLANK(B37)=FALSE,ISBLANK(C37)=FALSE,ISBLANK(L37)=FALSE,ISBLANK(M37)=FALSE)),"},},}",IF(ISBLANK(C41),"","{szContent="""&amp;C41&amp;""","&amp;IF(D41&lt;&gt;"","szNote="""&amp;D41&amp;""",","")&amp;IF(K41&lt;&gt;"","col={"&amp;K41&amp;"},","")&amp;IF(L41&gt;0,"bSearch=true,","")&amp;IF(M41&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N41&gt;0,"szVoice="""&amp;N41&amp;""",","")&amp;IF(O41&gt;0,"bTeamChannel=true,","")&amp;IF(P41&gt;0,"bWhisperChannel=true,","")&amp;IF(Q41&gt;0,"bCenterAlarm=true,","")&amp;IF(R41&gt;0,"bScreenHead=true,","")&amp;IF(S41&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U41&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U41:AAF41)&amp;"},","")&amp;"},")))</f>
+        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
+      </c>
+      <c r="U41" s="36" t="s">
+        <v>2299</v>
+      </c>
+      <c r="V41" s="39"/>
+    </row>
+    <row r="42" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C42" s="36" t="s">
+        <v>2196</v>
+      </c>
+      <c r="D42" s="36" t="s">
+        <v>2197</v>
+      </c>
+      <c r="K42" s="36" t="s">
+        <v>1432</v>
+      </c>
+      <c r="T42" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
+      </c>
+      <c r="U42" s="36" t="s">
+        <v>2298</v>
+      </c>
+      <c r="V42" s="39"/>
+    </row>
+    <row r="43" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C43" s="36" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D43" s="36" t="s">
+        <v>2117</v>
+      </c>
+      <c r="K43" s="36" t="s">
+        <v>1432</v>
+      </c>
+      <c r="T43" s="36" t="str">
+        <f t="shared" ref="T43" si="2">IF(ISBLANK(B43)=FALSE,IF(ISBLANK(B42),"},["&amp;B43&amp;"]={","["&amp;B43&amp;"]={"),IF(AND(ISBLANK(B43),ISBLANK(C43),ISBLANK(L43),ISBLANK(M43),OR(ISBLANK(B42)=FALSE,ISBLANK(C42)=FALSE,ISBLANK(L42)=FALSE,ISBLANK(M42)=FALSE)),"},},}",IF(ISBLANK(C43),"","{szContent="""&amp;C43&amp;""","&amp;IF(D43&lt;&gt;"","szNote="""&amp;D43&amp;""",","")&amp;IF(K43&lt;&gt;"","col={"&amp;K43&amp;"},","")&amp;IF(L43&gt;0,"bSearch=true,","")&amp;IF(M43&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N43&gt;0,"szVoice="""&amp;N43&amp;""",","")&amp;IF(O43&gt;0,"bTeamChannel=true,","")&amp;IF(P43&gt;0,"bWhisperChannel=true,","")&amp;IF(Q43&gt;0,"bCenterAlarm=true,","")&amp;IF(R43&gt;0,"bScreenHead=true,","")&amp;IF(S43&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U43&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U43:AAF43)&amp;"},","")&amp;"},")))</f>
+        <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
+      </c>
+      <c r="U43" s="36" t="s">
+        <v>1790</v>
+      </c>
+      <c r="V43" s="41" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C44" s="36" t="s">
+        <v>1574</v>
+      </c>
+      <c r="K44" s="36" t="s">
+        <v>1432</v>
+      </c>
+      <c r="T44" s="36" t="str">
+        <f>IF(ISBLANK(B44)=FALSE,IF(ISBLANK(B42),"},["&amp;B44&amp;"]={","["&amp;B44&amp;"]={"),IF(AND(ISBLANK(B44),ISBLANK(C44),ISBLANK(L44),ISBLANK(M44),OR(ISBLANK(B42)=FALSE,ISBLANK(C42)=FALSE,ISBLANK(L42)=FALSE,ISBLANK(M42)=FALSE)),"},},}",IF(ISBLANK(C44),"","{szContent="""&amp;C44&amp;""","&amp;IF(D44&lt;&gt;"","szNote="""&amp;D44&amp;""",","")&amp;IF(K44&lt;&gt;"","col={"&amp;K44&amp;"},","")&amp;IF(L44&gt;0,"bSearch=true,","")&amp;IF(M44&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N44&gt;0,"szVoice="""&amp;N44&amp;""",","")&amp;IF(O44&gt;0,"bTeamChannel=true,","")&amp;IF(P44&gt;0,"bWhisperChannel=true,","")&amp;IF(Q44&gt;0,"bCenterAlarm=true,","")&amp;IF(R44&gt;0,"bScreenHead=true,","")&amp;IF(S44&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U44&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U44:AAF44)&amp;"},","")&amp;"},")))</f>
+        <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
+      </c>
+      <c r="U44" s="36" t="s">
+        <v>2381</v>
+      </c>
+      <c r="V44" s="36" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C45" s="36" t="s">
+        <v>1572</v>
+      </c>
+      <c r="K45" s="36" t="s">
+        <v>1432</v>
+      </c>
+      <c r="T45" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
+      </c>
+      <c r="U45" s="36" t="s">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C46" s="36" t="s">
+        <v>1573</v>
+      </c>
+      <c r="K46" s="36" t="s">
+        <v>1432</v>
+      </c>
+      <c r="T46" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
+      </c>
+      <c r="U46" s="36" t="s">
+        <v>2381</v>
+      </c>
+      <c r="V46" s="36" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C47" s="36" t="s">
+        <v>1575</v>
+      </c>
+      <c r="K47" s="36" t="s">
+        <v>1432</v>
+      </c>
+      <c r="T47" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·分线·开启",nTime=30,nRefresh=10,key="分流活动",},},},</v>
+      </c>
+      <c r="U47" s="36" t="s">
+        <v>2379</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A48" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B48">
+        <v>-2</v>
+      </c>
+      <c r="T48" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v>},[-2]={</v>
+      </c>
+    </row>
+    <row r="49" spans="1:38" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C49" s="36" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D49" s="36" t="s">
+        <v>2132</v>
+      </c>
+      <c r="K49" s="36" t="s">
+        <v>1432</v>
+      </c>
+      <c r="M49" s="36">
+        <v>1</v>
+      </c>
+      <c r="T49" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
+      </c>
+      <c r="U49" s="36" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="50" spans="1:38" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C50" s="36" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D50" s="36" t="s">
+        <v>1492</v>
+      </c>
+      <c r="K50" s="36" t="s">
+        <v>1432</v>
+      </c>
+      <c r="M50" s="36">
+        <v>1</v>
+      </c>
+      <c r="T50" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
+      </c>
+      <c r="U50" s="36" t="s">
+        <v>2419</v>
+      </c>
+      <c r="V50" s="36" t="s">
+        <v>2420</v>
+      </c>
+      <c r="W50" s="36" t="s">
+        <v>2421</v>
+      </c>
+      <c r="X50" s="36" t="s">
+        <v>2293</v>
+      </c>
+      <c r="Y50" s="36" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="51" spans="1:38" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C51" s="36" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D51" s="36" t="s">
+        <v>1493</v>
+      </c>
+      <c r="K51" s="36" t="s">
+        <v>1432</v>
+      </c>
+      <c r="M51" s="36">
+        <v>1</v>
+      </c>
+      <c r="T51" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
+      </c>
+      <c r="U51" s="36" t="s">
+        <v>1861</v>
+      </c>
+      <c r="V51" s="36" t="s">
+        <v>2423</v>
+      </c>
+      <c r="W51" s="36" t="s">
+        <v>2425</v>
+      </c>
+      <c r="X51" s="36" t="s">
+        <v>2426</v>
+      </c>
+      <c r="Y51" s="36" t="s">
+        <v>2200</v>
+      </c>
+      <c r="Z51" s="36" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="52" spans="1:38" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C52" s="36" t="s">
+        <v>1936</v>
+      </c>
+      <c r="D52" s="36" t="s">
+        <v>1938</v>
+      </c>
+      <c r="K52" s="36" t="s">
+        <v>1438</v>
+      </c>
+      <c r="T52" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
+      </c>
+      <c r="U52" s="36" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="53" spans="1:38" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C53" s="36" t="s">
+        <v>1935</v>
+      </c>
+      <c r="D53" s="36" t="s">
+        <v>1937</v>
+      </c>
+      <c r="K53" s="36" t="s">
+        <v>1565</v>
+      </c>
+      <c r="T53" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
+      </c>
+      <c r="U53" s="36" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="54" spans="1:38" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C54" s="36" t="s">
+        <v>1932</v>
+      </c>
+      <c r="D54" s="36" t="s">
+        <v>2131</v>
+      </c>
+      <c r="K54" s="36" t="s">
+        <v>1432</v>
+      </c>
+      <c r="Q54" s="36">
+        <v>1</v>
+      </c>
+      <c r="T54" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
+      </c>
+      <c r="U54" s="36" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="55" spans="1:38" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C55" s="36" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D55" s="36" t="s">
+        <v>2203</v>
+      </c>
+      <c r="K55" s="36" t="s">
+        <v>1432</v>
+      </c>
+      <c r="T55" s="36" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
-      <c r="U38" s="36" t="s">
+      <c r="U55" s="36" t="s">
         <v>2299</v>
       </c>
-      <c r="V38" s="39"/>
-    </row>
-    <row r="39" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C39" s="36" t="s">
+      <c r="V55" s="39"/>
+    </row>
+    <row r="56" spans="1:38" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C56" s="36" t="s">
         <v>2196</v>
       </c>
-      <c r="D39" s="36" t="s">
+      <c r="D56" s="36" t="s">
         <v>2197</v>
       </c>
-      <c r="K39" s="36" t="s">
+      <c r="K56" s="36" t="s">
         <v>1432</v>
       </c>
-      <c r="T39" s="36" t="str">
+      <c r="T56" s="36" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
-      <c r="U39" s="36" t="s">
+      <c r="U56" s="36" t="s">
         <v>2298</v>
       </c>
-      <c r="V39" s="39"/>
-    </row>
-    <row r="40" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C40" s="36" t="s">
+      <c r="V56" s="39"/>
+    </row>
+    <row r="57" spans="1:38" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C57" s="36" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D57" s="36" t="s">
+        <v>2117</v>
+      </c>
+      <c r="K57" s="36" t="s">
+        <v>1432</v>
+      </c>
+      <c r="T57" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
+      </c>
+      <c r="U57" s="36" t="s">
+        <v>1790</v>
+      </c>
+      <c r="V57" s="41" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="58" spans="1:38" x14ac:dyDescent="0.15">
+      <c r="C58" t="s">
         <v>1574</v>
       </c>
-      <c r="K40" s="36" t="s">
+      <c r="K58" t="s">
         <v>1432</v>
       </c>
-      <c r="T40" s="36" t="str">
+      <c r="T58" s="36" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
-      <c r="U40" s="36" t="s">
+      <c r="U58" s="36" t="s">
         <v>2381</v>
       </c>
-      <c r="V40" s="36" t="s">
+      <c r="V58" t="s">
         <v>2382</v>
       </c>
     </row>
-    <row r="41" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C41" s="36" t="s">
+    <row r="59" spans="1:38" x14ac:dyDescent="0.15">
+      <c r="C59" t="s">
         <v>1572</v>
       </c>
-      <c r="K41" s="36" t="s">
+      <c r="K59" t="s">
         <v>1432</v>
       </c>
-      <c r="T41" s="36" t="str">
+      <c r="T59" s="36" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
-      <c r="U41" s="36" t="s">
+      <c r="U59" t="s">
         <v>2378</v>
       </c>
     </row>
-    <row r="42" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C42" s="36" t="s">
+    <row r="60" spans="1:38" x14ac:dyDescent="0.15">
+      <c r="C60" t="s">
         <v>1573</v>
       </c>
-      <c r="K42" s="36" t="s">
+      <c r="K60" t="s">
         <v>1432</v>
       </c>
-      <c r="T42" s="36" t="str">
+      <c r="T60" s="36" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
-      <c r="U42" s="36" t="s">
+      <c r="U60" s="36" t="s">
         <v>2381</v>
       </c>
-      <c r="V42" s="36" t="s">
+      <c r="V60" t="s">
         <v>2383</v>
       </c>
     </row>
-    <row r="43" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C43" s="36" t="s">
+    <row r="61" spans="1:38" x14ac:dyDescent="0.15">
+      <c r="C61" t="s">
         <v>1575</v>
       </c>
-      <c r="K43" s="36" t="s">
+      <c r="K61" t="s">
         <v>1432</v>
       </c>
-      <c r="T43" s="36" t="str">
+      <c r="T61" s="36" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·分线·开启",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
-      <c r="U43" s="36" t="s">
+      <c r="U61" t="s">
         <v>2379</v>
       </c>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.15">
-      <c r="A44" t="s">
-        <v>1923</v>
-      </c>
-      <c r="B44">
-        <v>-2</v>
-      </c>
-      <c r="T44" s="36" t="str">
+    <row r="62" spans="1:38" s="42" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="42" t="s">
+        <v>963</v>
+      </c>
+      <c r="B62" s="42">
+        <v>-7</v>
+      </c>
+      <c r="T62" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>},[-2]={</v>
-      </c>
-    </row>
-    <row r="45" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C45" s="36" t="s">
+        <v>},[-7]={</v>
+      </c>
+    </row>
+    <row r="63" spans="1:38" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C63" s="36" t="s">
         <v>1948</v>
       </c>
-      <c r="D45" s="36" t="s">
+      <c r="D63" s="36" t="s">
         <v>2132</v>
       </c>
-      <c r="K45" s="36" t="s">
+      <c r="K63" s="36" t="s">
         <v>1432</v>
       </c>
-      <c r="M45" s="36">
-        <v>1</v>
-      </c>
-      <c r="T45" s="36" t="str">
+      <c r="M63" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="36">
+        <v>1</v>
+      </c>
+      <c r="T63" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
-      </c>
-      <c r="U45" s="36" t="s">
+        <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
+      </c>
+      <c r="U63" s="36" t="s">
         <v>1977</v>
       </c>
     </row>
-    <row r="46" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C46" s="36" t="s">
+    <row r="64" spans="1:38" x14ac:dyDescent="0.15">
+      <c r="C64" t="s">
         <v>1491</v>
       </c>
-      <c r="D46" s="36" t="s">
+      <c r="D64" t="s">
         <v>1492</v>
       </c>
-      <c r="K46" s="36" t="s">
+      <c r="K64" t="s">
         <v>1432</v>
       </c>
-      <c r="M46" s="36">
-        <v>1</v>
-      </c>
-      <c r="T46" s="36" t="str">
+      <c r="M64">
+        <v>1</v>
+      </c>
+      <c r="T64" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
-      </c>
-      <c r="U46" s="36" t="s">
-        <v>2419</v>
-      </c>
-      <c r="V46" s="36" t="s">
-        <v>2420</v>
-      </c>
-      <c r="W46" s="36" t="s">
-        <v>2421</v>
-      </c>
-      <c r="X46" s="36" t="s">
-        <v>2293</v>
-      </c>
-      <c r="Y46" s="36" t="s">
-        <v>2294</v>
-      </c>
-    </row>
-    <row r="47" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C47" s="36" t="s">
+        <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,key="{$3}·恶人大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气占领",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人占领",},{nClass=20,nIcon=13,szName="{$3}·{$1}占领",nTime=-1,key="{$3}·{$1}占领",},},},</v>
+      </c>
+      <c r="U64" s="36" t="s">
+        <v>2291</v>
+      </c>
+      <c r="V64" s="36" t="s">
+        <v>2292</v>
+      </c>
+      <c r="W64" s="36" t="s">
+        <v>2295</v>
+      </c>
+      <c r="X64" s="36" t="s">
+        <v>2296</v>
+      </c>
+      <c r="Y64" s="36" t="s">
+        <v>2297</v>
+      </c>
+      <c r="Z64" s="36"/>
+      <c r="AA64" s="36"/>
+      <c r="AB64" s="36"/>
+      <c r="AE64" s="36"/>
+      <c r="AF64" s="36"/>
+      <c r="AG64" s="36"/>
+      <c r="AH64" s="36"/>
+      <c r="AI64" s="36"/>
+      <c r="AJ64" s="36"/>
+      <c r="AK64" s="36"/>
+      <c r="AL64" s="36"/>
+    </row>
+    <row r="65" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C65" s="36" t="s">
         <v>1798</v>
       </c>
-      <c r="D47" s="36" t="s">
+      <c r="D65" s="36" t="s">
         <v>1493</v>
       </c>
-      <c r="K47" s="36" t="s">
+      <c r="K65" s="36" t="s">
         <v>1432</v>
       </c>
-      <c r="M47" s="36">
-        <v>1</v>
-      </c>
-      <c r="T47" s="36" t="str">
+      <c r="M65" s="36">
+        <v>1</v>
+      </c>
+      <c r="T65" s="36" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
-      <c r="U47" s="36" t="s">
+      <c r="U65" s="36" t="s">
         <v>1861</v>
       </c>
-      <c r="V47" s="36" t="s">
+      <c r="V65" s="36" t="s">
         <v>2423</v>
       </c>
-      <c r="W47" s="36" t="s">
+      <c r="W65" s="36" t="s">
         <v>2425</v>
       </c>
-      <c r="X47" s="36" t="s">
+      <c r="X65" s="36" t="s">
         <v>2426</v>
       </c>
-      <c r="Y47" s="36" t="s">
+      <c r="Y65" s="36" t="s">
         <v>2200</v>
       </c>
-      <c r="Z47" s="36" t="s">
+      <c r="Z65" s="36" t="s">
         <v>2201</v>
       </c>
     </row>
-    <row r="48" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C48" s="36" t="s">
+    <row r="66" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C66" s="36" t="s">
         <v>1936</v>
       </c>
-      <c r="D48" s="36" t="s">
+      <c r="D66" s="36" t="s">
         <v>1938</v>
       </c>
-      <c r="K48" s="36" t="s">
+      <c r="K66" s="36" t="s">
         <v>1438</v>
       </c>
-      <c r="T48" s="36" t="str">
+      <c r="T66" s="36" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
-      <c r="U48" s="36" t="s">
+      <c r="U66" s="36" t="s">
         <v>2024</v>
       </c>
     </row>
-    <row r="49" spans="1:38" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C49" s="36" t="s">
+    <row r="67" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C67" s="36" t="s">
         <v>1935</v>
       </c>
-      <c r="D49" s="36" t="s">
+      <c r="D67" s="36" t="s">
         <v>1937</v>
       </c>
-      <c r="K49" s="36" t="s">
+      <c r="K67" s="36" t="s">
         <v>1565</v>
       </c>
-      <c r="T49" s="36" t="str">
+      <c r="T67" s="36" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
-      <c r="U49" s="36" t="s">
+      <c r="U67" s="36" t="s">
         <v>2025</v>
       </c>
     </row>
-    <row r="50" spans="1:38" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C50" s="36" t="s">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="C68" t="s">
+        <v>1577</v>
+      </c>
+      <c r="K68" t="s">
+        <v>1432</v>
+      </c>
+      <c r="T68" s="36" t="str">
+        <f>IF(ISBLANK(B68)=FALSE,IF(ISBLANK(B65),"},["&amp;B68&amp;"]={","["&amp;B68&amp;"]={"),IF(AND(ISBLANK(B68),ISBLANK(C68),ISBLANK(L68),ISBLANK(M68),OR(ISBLANK(B65)=FALSE,ISBLANK(C65)=FALSE,ISBLANK(L65)=FALSE,ISBLANK(M65)=FALSE)),"},},}",IF(ISBLANK(C68),"","{szContent="""&amp;C68&amp;""","&amp;IF(D68&lt;&gt;"","szNote="""&amp;D68&amp;""",","")&amp;IF(K68&lt;&gt;"","col={"&amp;K68&amp;"},","")&amp;IF(L68&gt;0,"bSearch=true,","")&amp;IF(M68&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N68&gt;0,"szVoice="""&amp;N68&amp;""",","")&amp;IF(O68&gt;0,"bTeamChannel=true,","")&amp;IF(P68&gt;0,"bWhisperChannel=true,","")&amp;IF(Q68&gt;0,"bCenterAlarm=true,","")&amp;IF(R68&gt;0,"bScreenHead=true,","")&amp;IF(S68&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U68&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U68:AAF68)&amp;"},","")&amp;"},")))</f>
+        <v>{szContent="本场贡献值进入前1200名，额外获得3000威名，可通过邮件领取\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=6,szName="攻防进入前1200名",nTime=10,key="阵营活动",},},},</v>
+      </c>
+      <c r="U68" t="s">
+        <v>1789</v>
+      </c>
+    </row>
+    <row r="69" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C69" s="36" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D69" s="36" t="s">
+        <v>2203</v>
+      </c>
+      <c r="K69" s="36" t="s">
+        <v>1432</v>
+      </c>
+      <c r="T69" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=20,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=20,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=20,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=20,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=20,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=20,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=20,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=20,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=20,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
+      </c>
+      <c r="U69" s="36" t="s">
+        <v>2299</v>
+      </c>
+      <c r="V69" s="38" t="s">
+        <v>2574</v>
+      </c>
+      <c r="W69" s="38" t="s">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="70" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C70" s="36" t="s">
         <v>1932</v>
       </c>
-      <c r="D50" s="36" t="s">
+      <c r="D70" s="36" t="s">
         <v>2131</v>
       </c>
-      <c r="K50" s="36" t="s">
+      <c r="K70" s="36" t="s">
         <v>1432</v>
       </c>
-      <c r="Q50" s="36">
-        <v>1</v>
-      </c>
-      <c r="T50" s="36" t="str">
+      <c r="Q70" s="36">
+        <v>1</v>
+      </c>
+      <c r="T70" s="36" t="str">
+        <f>IF(ISBLANK(B70)=FALSE,IF(ISBLANK(B69),"},["&amp;B70&amp;"]={","["&amp;B70&amp;"]={"),IF(AND(ISBLANK(B70),ISBLANK(C70),ISBLANK(L70),ISBLANK(M70),OR(ISBLANK(B69)=FALSE,ISBLANK(C69)=FALSE,ISBLANK(L69)=FALSE,ISBLANK(M69)=FALSE)),"},},}",IF(ISBLANK(C70),"","{szContent="""&amp;C70&amp;""","&amp;IF(D70&lt;&gt;"","szNote="""&amp;D70&amp;""",","")&amp;IF(K70&lt;&gt;"","col={"&amp;K70&amp;"},","")&amp;IF(L70&gt;0,"bSearch=true,","")&amp;IF(M70&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N70&gt;0,"szVoice="""&amp;N70&amp;""",","")&amp;IF(O70&gt;0,"bTeamChannel=true,","")&amp;IF(P70&gt;0,"bWhisperChannel=true,","")&amp;IF(Q70&gt;0,"bCenterAlarm=true,","")&amp;IF(R70&gt;0,"bScreenHead=true,","")&amp;IF(S70&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U70&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U70:AAF70)&amp;"},","")&amp;"},")))</f>
+        <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
+      </c>
+      <c r="U70" s="36" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="71" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="C71" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D71" t="s">
+        <v>2117</v>
+      </c>
+      <c r="K71" t="s">
+        <v>1432</v>
+      </c>
+      <c r="T71" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
-      </c>
-      <c r="U50" s="36" t="s">
-        <v>1934</v>
-      </c>
-    </row>
-    <row r="51" spans="1:38" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C51" s="36" t="s">
-        <v>2202</v>
-      </c>
-      <c r="D51" s="36" t="s">
-        <v>2203</v>
-      </c>
-      <c r="K51" s="36" t="s">
+        <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=13,szName="狼牙先锋首领",nTime=0,key="狼牙先锋首领",},{nClass=20,nIcon=13,szName="离开据点·大旗重置",nTime=0,key="离开据点·大旗重置",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
+      </c>
+      <c r="U71" t="s">
+        <v>2380</v>
+      </c>
+      <c r="V71" t="s">
+        <v>2128</v>
+      </c>
+      <c r="W71" s="36" t="s">
+        <v>2129</v>
+      </c>
+      <c r="X71" s="41" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="72" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="C72" t="s">
+        <v>1574</v>
+      </c>
+      <c r="K72" t="s">
         <v>1432</v>
       </c>
-      <c r="T51" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
-      </c>
-      <c r="U51" s="36" t="s">
-        <v>2299</v>
-      </c>
-      <c r="V51" s="39"/>
-    </row>
-    <row r="52" spans="1:38" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C52" s="36" t="s">
-        <v>2196</v>
-      </c>
-      <c r="D52" s="36" t="s">
-        <v>2197</v>
-      </c>
-      <c r="K52" s="36" t="s">
-        <v>1432</v>
-      </c>
-      <c r="T52" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
-      </c>
-      <c r="U52" s="36" t="s">
-        <v>2298</v>
-      </c>
-      <c r="V52" s="39"/>
-    </row>
-    <row r="53" spans="1:38" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C53" s="36" t="s">
-        <v>1933</v>
-      </c>
-      <c r="D53" s="36" t="s">
-        <v>2117</v>
-      </c>
-      <c r="K53" s="36" t="s">
-        <v>1432</v>
-      </c>
-      <c r="T53" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
-      </c>
-      <c r="U53" s="36" t="s">
-        <v>1790</v>
-      </c>
-      <c r="V53" s="41" t="s">
-        <v>2290</v>
-      </c>
-    </row>
-    <row r="54" spans="1:38" x14ac:dyDescent="0.15">
-      <c r="C54" t="s">
-        <v>1574</v>
-      </c>
-      <c r="K54" t="s">
-        <v>1432</v>
-      </c>
-      <c r="T54" s="36" t="str">
+      <c r="T72" s="36" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
-      <c r="U54" s="36" t="s">
+      <c r="U72" s="36" t="s">
         <v>2381</v>
       </c>
-      <c r="V54" t="s">
+      <c r="V72" s="36" t="s">
         <v>2382</v>
       </c>
     </row>
-    <row r="55" spans="1:38" x14ac:dyDescent="0.15">
-      <c r="C55" t="s">
-        <v>1572</v>
-      </c>
-      <c r="K55" t="s">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="C73" t="s">
+        <v>1573</v>
+      </c>
+      <c r="D73" t="s">
+        <v>2693</v>
+      </c>
+      <c r="K73" t="s">
         <v>1432</v>
       </c>
-      <c r="T55" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
-      </c>
-      <c r="U55" t="s">
-        <v>2378</v>
-      </c>
-    </row>
-    <row r="56" spans="1:38" x14ac:dyDescent="0.15">
-      <c r="C56" t="s">
-        <v>1573</v>
-      </c>
-      <c r="K56" t="s">
+      <c r="T73" s="36" t="str">
+        <f t="shared" ref="T73:T136" si="3">IF(ISBLANK(B73)=FALSE,IF(ISBLANK(B72),"},["&amp;B73&amp;"]={","["&amp;B73&amp;"]={"),IF(AND(ISBLANK(B73),ISBLANK(C73),ISBLANK(L73),ISBLANK(M73),OR(ISBLANK(B72)=FALSE,ISBLANK(C72)=FALSE,ISBLANK(L72)=FALSE,ISBLANK(M72)=FALSE)),"},},}",IF(ISBLANK(C73),"","{szContent="""&amp;C73&amp;""","&amp;IF(D73&lt;&gt;"","szNote="""&amp;D73&amp;""",","")&amp;IF(K73&lt;&gt;"","col={"&amp;K73&amp;"},","")&amp;IF(L73&gt;0,"bSearch=true,","")&amp;IF(M73&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N73&gt;0,"szVoice="""&amp;N73&amp;""",","")&amp;IF(O73&gt;0,"bTeamChannel=true,","")&amp;IF(P73&gt;0,"bWhisperChannel=true,","")&amp;IF(Q73&gt;0,"bCenterAlarm=true,","")&amp;IF(R73&gt;0,"bScreenHead=true,","")&amp;IF(S73&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U73&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U73:AAF73)&amp;"},","")&amp;"},")))</f>
+        <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·5分钟·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
+      </c>
+      <c r="U73" s="36" t="s">
+        <v>2381</v>
+      </c>
+      <c r="V73" s="36" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="74" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="C74" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D74" t="s">
+        <v>2369</v>
+      </c>
+      <c r="K74" t="s">
         <v>1432</v>
       </c>
-      <c r="T56" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
-      </c>
-      <c r="U56" s="36" t="s">
-        <v>2381</v>
-      </c>
-      <c r="V56" t="s">
-        <v>2383</v>
-      </c>
-    </row>
-    <row r="57" spans="1:38" x14ac:dyDescent="0.15">
-      <c r="C57" t="s">
+      <c r="T74" s="36" t="str">
+        <f t="shared" si="3"/>
+        <v>{szContent="前线据点之争已经打响，争夺正式开始，沙盘地图（CTRL + M）绘有详细战略意图，谁将称霸中原，我们拭目以待！\n",szNote="据点攻防·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime=10,key="阵营活动",},},},</v>
+      </c>
+      <c r="U74" t="s">
+        <v>2628</v>
+      </c>
+    </row>
+    <row r="75" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="C75" t="s">
         <v>1575</v>
       </c>
-      <c r="K57" t="s">
+      <c r="K75" t="s">
         <v>1432</v>
       </c>
-      <c r="T57" s="36" t="str">
-        <f t="shared" si="0"/>
+      <c r="T75" s="36" t="str">
+        <f t="shared" si="3"/>
         <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·分线·开启",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
-      <c r="U57" t="s">
+      <c r="U75" t="s">
         <v>2379</v>
       </c>
     </row>
-    <row r="58" spans="1:38" s="42" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="42" t="s">
-        <v>963</v>
-      </c>
-      <c r="B58" s="42">
-        <v>-7</v>
-      </c>
-      <c r="T58" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>},[-7]={</v>
-      </c>
-    </row>
-    <row r="59" spans="1:38" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C59" s="36" t="s">
-        <v>1948</v>
-      </c>
-      <c r="D59" s="36" t="s">
-        <v>2132</v>
-      </c>
-      <c r="K59" s="36" t="s">
-        <v>1432</v>
-      </c>
-      <c r="M59" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q59" s="36">
-        <v>1</v>
-      </c>
-      <c r="T59" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
-      </c>
-      <c r="U59" s="36" t="s">
-        <v>1977</v>
-      </c>
-    </row>
-    <row r="60" spans="1:38" x14ac:dyDescent="0.15">
-      <c r="C60" t="s">
-        <v>1491</v>
-      </c>
-      <c r="D60" t="s">
-        <v>1492</v>
-      </c>
-      <c r="K60" t="s">
-        <v>1432</v>
-      </c>
-      <c r="M60">
-        <v>1</v>
-      </c>
-      <c r="T60" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,key="{$3}·恶人大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气占领",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人占领",},{nClass=20,nIcon=13,szName="{$3}·{$1}占领",nTime=-1,key="{$3}·{$1}占领",},},},</v>
-      </c>
-      <c r="U60" s="36" t="s">
-        <v>2291</v>
-      </c>
-      <c r="V60" s="36" t="s">
-        <v>2292</v>
-      </c>
-      <c r="W60" s="36" t="s">
-        <v>2295</v>
-      </c>
-      <c r="X60" s="36" t="s">
-        <v>2296</v>
-      </c>
-      <c r="Y60" s="36" t="s">
-        <v>2297</v>
-      </c>
-      <c r="Z60" s="36"/>
-      <c r="AA60" s="36"/>
-      <c r="AB60" s="36"/>
-      <c r="AE60" s="36"/>
-      <c r="AF60" s="36"/>
-      <c r="AG60" s="36"/>
-      <c r="AH60" s="36"/>
-      <c r="AI60" s="36"/>
-      <c r="AJ60" s="36"/>
-      <c r="AK60" s="36"/>
-      <c r="AL60" s="36"/>
-    </row>
-    <row r="61" spans="1:38" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C61" s="36" t="s">
-        <v>1798</v>
-      </c>
-      <c r="D61" s="36" t="s">
-        <v>1493</v>
-      </c>
-      <c r="K61" s="36" t="s">
-        <v>1432</v>
-      </c>
-      <c r="M61" s="36">
-        <v>1</v>
-      </c>
-      <c r="T61" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
-      </c>
-      <c r="U61" s="36" t="s">
-        <v>1861</v>
-      </c>
-      <c r="V61" s="36" t="s">
-        <v>2423</v>
-      </c>
-      <c r="W61" s="36" t="s">
-        <v>2425</v>
-      </c>
-      <c r="X61" s="36" t="s">
-        <v>2426</v>
-      </c>
-      <c r="Y61" s="36" t="s">
-        <v>2200</v>
-      </c>
-      <c r="Z61" s="36" t="s">
-        <v>2201</v>
-      </c>
-    </row>
-    <row r="62" spans="1:38" x14ac:dyDescent="0.15">
-      <c r="C62" t="s">
-        <v>1577</v>
-      </c>
-      <c r="K62" t="s">
-        <v>1432</v>
-      </c>
-      <c r="T62" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="本场贡献值进入前1200名，额外获得3000威名，可通过邮件领取\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=6,szName="攻防进入前1200名",nTime=10,key="阵营活动",},},},</v>
-      </c>
-      <c r="U62" t="s">
-        <v>1789</v>
-      </c>
-    </row>
-    <row r="63" spans="1:38" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C63" s="36" t="s">
-        <v>2202</v>
-      </c>
-      <c r="D63" s="36" t="s">
-        <v>2203</v>
-      </c>
-      <c r="K63" s="36" t="s">
-        <v>1432</v>
-      </c>
-      <c r="T63" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=20,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=20,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=20,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=20,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=20,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=20,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=20,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=20,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=20,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
-      </c>
-      <c r="U63" s="36" t="s">
-        <v>2299</v>
-      </c>
-      <c r="V63" s="38" t="s">
-        <v>2574</v>
-      </c>
-      <c r="W63" s="38" t="s">
-        <v>2571</v>
-      </c>
-    </row>
-    <row r="64" spans="1:38" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C64" s="36" t="s">
-        <v>1932</v>
-      </c>
-      <c r="D64" s="36" t="s">
-        <v>2131</v>
-      </c>
-      <c r="K64" s="36" t="s">
-        <v>1432</v>
-      </c>
-      <c r="Q64" s="36">
-        <v>1</v>
-      </c>
-      <c r="T64" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
-      </c>
-      <c r="U64" s="36" t="s">
-        <v>1934</v>
-      </c>
-    </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="C65" t="s">
-        <v>1933</v>
-      </c>
-      <c r="D65" t="s">
-        <v>2117</v>
-      </c>
-      <c r="K65" t="s">
-        <v>1432</v>
-      </c>
-      <c r="T65" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=13,szName="狼牙先锋首领",nTime=0,key="狼牙先锋首领",},{nClass=20,nIcon=13,szName="离开据点·大旗重置",nTime=0,key="离开据点·大旗重置",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
-      </c>
-      <c r="U65" t="s">
-        <v>2380</v>
-      </c>
-      <c r="V65" t="s">
-        <v>2128</v>
-      </c>
-      <c r="W65" s="36" t="s">
-        <v>2129</v>
-      </c>
-      <c r="X65" s="41" t="s">
-        <v>2290</v>
-      </c>
-    </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="C66" t="s">
-        <v>1574</v>
-      </c>
-      <c r="K66" t="s">
-        <v>1432</v>
-      </c>
-      <c r="T66" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
-      </c>
-      <c r="U66" s="36" t="s">
-        <v>2381</v>
-      </c>
-      <c r="V66" s="36" t="s">
-        <v>2382</v>
-      </c>
-    </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="C67" t="s">
-        <v>1573</v>
-      </c>
-      <c r="D67" t="s">
-        <v>2693</v>
-      </c>
-      <c r="K67" t="s">
-        <v>1432</v>
-      </c>
-      <c r="T67" s="36" t="str">
-        <f t="shared" ref="T67:T130" si="1">IF(ISBLANK(B67)=FALSE,IF(ISBLANK(B66),"},["&amp;B67&amp;"]={","["&amp;B67&amp;"]={"),IF(AND(ISBLANK(B67),ISBLANK(C67),ISBLANK(L67),ISBLANK(M67),OR(ISBLANK(B66)=FALSE,ISBLANK(C66)=FALSE,ISBLANK(L66)=FALSE,ISBLANK(M66)=FALSE)),"},},}",IF(ISBLANK(C67),"","{szContent="""&amp;C67&amp;""","&amp;IF(D67&lt;&gt;"","szNote="""&amp;D67&amp;""",","")&amp;IF(K67&lt;&gt;"","col={"&amp;K67&amp;"},","")&amp;IF(L67&gt;0,"bSearch=true,","")&amp;IF(M67&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N67&gt;0,"szVoice="""&amp;N67&amp;""",","")&amp;IF(O67&gt;0,"bTeamChannel=true,","")&amp;IF(P67&gt;0,"bWhisperChannel=true,","")&amp;IF(Q67&gt;0,"bCenterAlarm=true,","")&amp;IF(R67&gt;0,"bScreenHead=true,","")&amp;IF(S67&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U67&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U67:AAF67)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·5分钟·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
-      </c>
-      <c r="U67" s="36" t="s">
-        <v>2381</v>
-      </c>
-      <c r="V67" s="36" t="s">
-        <v>2383</v>
-      </c>
-    </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="C68" t="s">
-        <v>1576</v>
-      </c>
-      <c r="D68" t="s">
-        <v>2369</v>
-      </c>
-      <c r="K68" t="s">
-        <v>1432</v>
-      </c>
-      <c r="T68" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="前线据点之争已经打响，争夺正式开始，沙盘地图（CTRL + M）绘有详细战略意图，谁将称霸中原，我们拭目以待！\n",szNote="据点攻防·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime=10,key="阵营活动",},},},</v>
-      </c>
-      <c r="U68" t="s">
-        <v>2628</v>
-      </c>
-    </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="C69" t="s">
-        <v>1575</v>
-      </c>
-      <c r="K69" t="s">
-        <v>1432</v>
-      </c>
-      <c r="T69" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·分线·开启",nTime=30,nRefresh=10,key="分流活动",},},},</v>
-      </c>
-      <c r="U69" t="s">
-        <v>2379</v>
-      </c>
-    </row>
-    <row r="70" spans="1:25" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="36" t="s">
+    <row r="76" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A76" s="36" t="s">
         <v>2692</v>
       </c>
-      <c r="B70" s="36">
+      <c r="B76" s="36">
         <v>-20</v>
       </c>
-      <c r="T70" s="36" t="str">
-        <f t="shared" si="1"/>
+      <c r="T76" s="36" t="str">
+        <f t="shared" si="3"/>
         <v>},[-20]={</v>
       </c>
     </row>
-    <row r="71" spans="1:25" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C71" s="36" t="s">
+    <row r="77" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C77" s="36" t="s">
         <v>1803</v>
       </c>
-      <c r="D71" s="36" t="s">
+      <c r="D77" s="36" t="s">
         <v>1494</v>
-      </c>
-      <c r="K71" s="36" t="s">
-        <v>1432</v>
-      </c>
-      <c r="M71" s="36">
-        <v>1</v>
-      </c>
-      <c r="T71" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
-      </c>
-      <c r="U71" s="36" t="s">
-        <v>2427</v>
-      </c>
-      <c r="V71" s="36" t="s">
-        <v>2428</v>
-      </c>
-      <c r="W71" s="36" t="s">
-        <v>2429</v>
-      </c>
-      <c r="X71" s="36" t="s">
-        <v>1771</v>
-      </c>
-      <c r="Y71" s="36" t="s">
-        <v>1772</v>
-      </c>
-    </row>
-    <row r="72" spans="1:25" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A72" s="36" t="s">
-        <v>2161</v>
-      </c>
-      <c r="B72" s="36">
-        <v>-3</v>
-      </c>
-      <c r="T72" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>},[-3]={</v>
-      </c>
-    </row>
-    <row r="73" spans="1:25" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C73" s="36" t="s">
-        <v>1794</v>
-      </c>
-      <c r="K73" s="36" t="s">
-        <v>1438</v>
-      </c>
-      <c r="T73" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往恶人谷地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=3,szName="主战场·恶人谷",nTime="1,阵营攻防·开始排队·恶人谷;10,阵营攻防·开始排队·恶人谷",key="大攻防·主战场",},},},</v>
-      </c>
-      <c r="U73" s="36" t="s">
-        <v>2164</v>
-      </c>
-    </row>
-    <row r="74" spans="1:25" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C74" s="36" t="s">
-        <v>1793</v>
-      </c>
-      <c r="K74" s="36" t="s">
-        <v>1565</v>
-      </c>
-      <c r="T74" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往浩气盟地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=7,szName="主战场·浩气盟",nTime="1,阵营攻防·开始排队·浩气盟;10,阵营攻防·开始排队·浩气盟",key="大攻防·主战场",},},},</v>
-      </c>
-      <c r="U74" s="36" t="s">
-        <v>2163</v>
-      </c>
-    </row>
-    <row r="75" spans="1:25" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A75" s="36" t="s">
-        <v>2093</v>
-      </c>
-      <c r="B75" s="36">
-        <v>74</v>
-      </c>
-      <c r="T75" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>},[74]={</v>
-      </c>
-    </row>
-    <row r="76" spans="1:25" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C76" s="36" t="s">
-        <v>1488</v>
-      </c>
-      <c r="D76" s="36" t="s">
-        <v>1489</v>
-      </c>
-      <c r="K76" s="36" t="s">
-        <v>1432</v>
-      </c>
-      <c r="T76" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="本场攻防“奇袭场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="奇袭场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2402,nFrame=4,szName="奇袭场·平手",nTime=57,nRefresh=5,key="大攻防·奇袭场",},},},</v>
-      </c>
-      <c r="U76" s="36" t="s">
-        <v>2403</v>
-      </c>
-    </row>
-    <row r="77" spans="1:25" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C77" s="36" t="s">
-        <v>2096</v>
-      </c>
-      <c r="D77" s="36" t="s">
-        <v>1490</v>
       </c>
       <c r="K77" s="36" t="s">
         <v>1432</v>
       </c>
+      <c r="M77" s="36">
+        <v>1</v>
+      </c>
       <c r="T77" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="本场攻防“主战场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="主战场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="主战场·平手",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U77" s="36" t="s">
-        <v>2402</v>
-      </c>
-    </row>
-    <row r="78" spans="1:25" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C78" s="36" t="s">
-        <v>1487</v>
-      </c>
-      <c r="D78" s="36" t="s">
-        <v>1931</v>
-      </c>
-      <c r="K78" s="36" t="s">
-        <v>1432</v>
-      </c>
-      <c r="M78" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q78" s="36">
-        <v>1</v>
+        <v>2427</v>
+      </c>
+      <c r="V77" s="36" t="s">
+        <v>2428</v>
+      </c>
+      <c r="W77" s="36" t="s">
+        <v>2429</v>
+      </c>
+      <c r="X77" s="36" t="s">
+        <v>1771</v>
+      </c>
+      <c r="Y77" s="36" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="78" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A78" s="36" t="s">
+        <v>2161</v>
+      </c>
+      <c r="B78" s="36">
+        <v>-3</v>
       </c>
       <c r="T78" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="^本场攻防“([主战奇袭场]+)”已结束，([浩气盟恶人谷]+)[侠士们众志成城和，]-([大完险胜]+)([浩气盟恶人谷]+)[！，]+",szNote="{$1}·{$2}·{$3}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,szName="大攻防·奇袭场",nTime=-2,nRefresh=10,key="大攻防·奇袭场",},{nClass=20,nIcon=13,szName="大攻防·主战场",nTime=-2,nRefresh=10,key="大攻防·主战场",},{nClass=20,nIcon=13,szName="大攻防·{$1}",nTime=-2,key="大攻防·{$1}",},{nClass=20,nIcon=2402,nFrame=4,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
-      </c>
-      <c r="U78" s="36" t="s">
-        <v>2512</v>
-      </c>
-      <c r="V78" s="36" t="s">
-        <v>2513</v>
-      </c>
-      <c r="W78" s="36" t="s">
-        <v>2187</v>
-      </c>
-      <c r="X78" s="36" t="s">
-        <v>2399</v>
-      </c>
-      <c r="Y78" s="36" t="s">
-        <v>2398</v>
-      </c>
-    </row>
-    <row r="79" spans="1:25" s="36" customFormat="1" x14ac:dyDescent="0.15">
+        <f t="shared" si="3"/>
+        <v>},[-3]={</v>
+      </c>
+    </row>
+    <row r="79" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C79" s="36" t="s">
-        <v>1948</v>
-      </c>
-      <c r="D79" s="36" t="s">
-        <v>2132</v>
+        <v>1794</v>
       </c>
       <c r="K79" s="36" t="s">
-        <v>1432</v>
-      </c>
-      <c r="M79" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q79" s="36">
-        <v>1</v>
+        <v>1438</v>
       </c>
       <c r="T79" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往恶人谷地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=3,szName="主战场·恶人谷",nTime="1,阵营攻防·开始排队·恶人谷;10,阵营攻防·开始排队·恶人谷",key="大攻防·主战场",},},},</v>
       </c>
       <c r="U79" s="36" t="s">
-        <v>1977</v>
-      </c>
-    </row>
-    <row r="80" spans="1:25" s="36" customFormat="1" x14ac:dyDescent="0.15">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="80" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C80" s="36" t="s">
-        <v>1491</v>
-      </c>
-      <c r="D80" s="36" t="s">
-        <v>1492</v>
+        <v>1793</v>
       </c>
       <c r="K80" s="36" t="s">
-        <v>1432</v>
-      </c>
-      <c r="M80" s="36">
-        <v>1</v>
+        <v>1565</v>
       </c>
       <c r="T80" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往浩气盟地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=7,szName="主战场·浩气盟",nTime="1,阵营攻防·开始排队·浩气盟;10,阵营攻防·开始排队·浩气盟",key="大攻防·主战场",},},},</v>
       </c>
       <c r="U80" s="36" t="s">
-        <v>2419</v>
-      </c>
-      <c r="V80" s="36" t="s">
-        <v>2420</v>
-      </c>
-      <c r="W80" s="36" t="s">
-        <v>2421</v>
-      </c>
-      <c r="X80" s="36" t="s">
-        <v>2293</v>
-      </c>
-      <c r="Y80" s="36" t="s">
-        <v>2294</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="81" spans="1:30" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C81" s="36" t="s">
-        <v>1798</v>
-      </c>
-      <c r="D81" s="36" t="s">
-        <v>1493</v>
-      </c>
-      <c r="K81" s="36" t="s">
-        <v>1432</v>
-      </c>
-      <c r="M81" s="36">
-        <v>1</v>
+      <c r="A81" s="36" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B81" s="36">
+        <v>74</v>
       </c>
       <c r="T81" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
-      </c>
-      <c r="U81" s="36" t="s">
-        <v>1861</v>
-      </c>
-      <c r="V81" s="36" t="s">
-        <v>2423</v>
-      </c>
-      <c r="W81" s="36" t="s">
-        <v>2425</v>
-      </c>
-      <c r="X81" s="36" t="s">
-        <v>2426</v>
-      </c>
-      <c r="Y81" s="36" t="s">
-        <v>2200</v>
-      </c>
-      <c r="Z81" s="36" t="s">
-        <v>2201</v>
+        <f t="shared" si="3"/>
+        <v>},[74]={</v>
       </c>
     </row>
     <row r="82" spans="1:30" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C82" s="36" t="s">
-        <v>1936</v>
+        <v>1488</v>
       </c>
       <c r="D82" s="36" t="s">
-        <v>1938</v>
+        <v>1489</v>
       </c>
       <c r="K82" s="36" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="T82" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="本场攻防“奇袭场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="奇袭场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2402,nFrame=4,szName="奇袭场·平手",nTime=57,nRefresh=5,key="大攻防·奇袭场",},},},</v>
       </c>
       <c r="U82" s="36" t="s">
-        <v>2024</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="83" spans="1:30" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C83" s="36" t="s">
-        <v>1935</v>
+        <v>2096</v>
       </c>
       <c r="D83" s="36" t="s">
-        <v>1937</v>
+        <v>1490</v>
       </c>
       <c r="K83" s="36" t="s">
-        <v>1565</v>
+        <v>1432</v>
       </c>
       <c r="T83" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="本场攻防“主战场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="主战场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="主战场·平手",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U83" s="36" t="s">
-        <v>2025</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="84" spans="1:30" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C84" s="36" t="s">
-        <v>1932</v>
+        <v>1487</v>
       </c>
       <c r="D84" s="36" t="s">
-        <v>2131</v>
+        <v>1931</v>
       </c>
       <c r="K84" s="36" t="s">
         <v>1432</v>
       </c>
+      <c r="M84" s="36">
+        <v>1</v>
+      </c>
       <c r="Q84" s="36">
         <v>1</v>
       </c>
       <c r="T84" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="^本场攻防“([主战奇袭场]+)”已结束，([浩气盟恶人谷]+)[侠士们众志成城和，]-([大完险胜]+)([浩气盟恶人谷]+)[！，]+",szNote="{$1}·{$2}·{$3}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,szName="大攻防·奇袭场",nTime=-2,nRefresh=10,key="大攻防·奇袭场",},{nClass=20,nIcon=13,szName="大攻防·主战场",nTime=-2,nRefresh=10,key="大攻防·主战场",},{nClass=20,nIcon=13,szName="大攻防·{$1}",nTime=-2,key="大攻防·{$1}",},{nClass=20,nIcon=2402,nFrame=4,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U84" s="36" t="s">
-        <v>1934</v>
+        <v>2512</v>
+      </c>
+      <c r="V84" s="36" t="s">
+        <v>2513</v>
+      </c>
+      <c r="W84" s="36" t="s">
+        <v>2187</v>
+      </c>
+      <c r="X84" s="36" t="s">
+        <v>2399</v>
+      </c>
+      <c r="Y84" s="36" t="s">
+        <v>2398</v>
       </c>
     </row>
     <row r="85" spans="1:30" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C85" s="36" t="s">
-        <v>1933</v>
+        <v>1948</v>
       </c>
       <c r="D85" s="36" t="s">
-        <v>2117</v>
+        <v>2132</v>
       </c>
       <c r="K85" s="36" t="s">
         <v>1432</v>
       </c>
+      <c r="M85" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q85" s="36">
+        <v>1</v>
+      </c>
       <c r="T85" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U85" s="36" t="s">
-        <v>1790</v>
-      </c>
-      <c r="V85" s="41" t="s">
-        <v>2290</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="86" spans="1:30" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C86" s="36" t="s">
-        <v>2202</v>
+        <v>1491</v>
       </c>
       <c r="D86" s="36" t="s">
-        <v>2203</v>
+        <v>1492</v>
       </c>
       <c r="K86" s="36" t="s">
         <v>1432</v>
       </c>
+      <c r="M86" s="36">
+        <v>1</v>
+      </c>
       <c r="T86" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U86" s="36" t="s">
-        <v>2299</v>
-      </c>
-      <c r="V86" s="39"/>
+        <v>2419</v>
+      </c>
+      <c r="V86" s="36" t="s">
+        <v>2420</v>
+      </c>
+      <c r="W86" s="36" t="s">
+        <v>2421</v>
+      </c>
+      <c r="X86" s="36" t="s">
+        <v>2293</v>
+      </c>
+      <c r="Y86" s="36" t="s">
+        <v>2294</v>
+      </c>
     </row>
     <row r="87" spans="1:30" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C87" s="36" t="s">
-        <v>2196</v>
+        <v>1798</v>
       </c>
       <c r="D87" s="36" t="s">
-        <v>2197</v>
+        <v>1493</v>
       </c>
       <c r="K87" s="36" t="s">
         <v>1432</v>
       </c>
+      <c r="M87" s="36">
+        <v>1</v>
+      </c>
       <c r="T87" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U87" s="36" t="s">
-        <v>2298</v>
-      </c>
-      <c r="V87" s="39"/>
+        <v>1861</v>
+      </c>
+      <c r="V87" s="36" t="s">
+        <v>2423</v>
+      </c>
+      <c r="W87" s="36" t="s">
+        <v>2425</v>
+      </c>
+      <c r="X87" s="36" t="s">
+        <v>2426</v>
+      </c>
+      <c r="Y87" s="36" t="s">
+        <v>2200</v>
+      </c>
+      <c r="Z87" s="36" t="s">
+        <v>2201</v>
+      </c>
     </row>
     <row r="88" spans="1:30" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="36" t="s">
-        <v>1805</v>
-      </c>
-      <c r="B88" s="36">
-        <v>22</v>
+      <c r="C88" s="36" t="s">
+        <v>1936</v>
+      </c>
+      <c r="D88" s="36" t="s">
+        <v>1938</v>
+      </c>
+      <c r="K88" s="36" t="s">
+        <v>1438</v>
       </c>
       <c r="T88" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>},[22]={</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
+      </c>
+      <c r="U88" s="36" t="s">
+        <v>2024</v>
       </c>
     </row>
     <row r="89" spans="1:30" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C89" s="36" t="s">
-        <v>1798</v>
+        <v>1935</v>
       </c>
       <c r="D89" s="36" t="s">
-        <v>1493</v>
-      </c>
-      <c r="G89" s="36" t="s">
-        <v>2204</v>
+        <v>1937</v>
       </c>
       <c r="K89" s="36" t="s">
-        <v>1432</v>
-      </c>
-      <c r="M89" s="36">
-        <v>1</v>
+        <v>1565</v>
       </c>
       <c r="T89" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【武王城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="武王城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【武王城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="武王城·恶人大旗",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U89" s="36" t="s">
-        <v>1861</v>
-      </c>
-      <c r="V89" s="36" t="str">
-        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G89&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·浩气大旗",},</v>
-      </c>
-      <c r="W89" s="36" t="str">
-        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G89&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·恶人大旗",},</v>
-      </c>
-      <c r="X89" s="36" t="s">
-        <v>2423</v>
-      </c>
-      <c r="Y89" s="36" t="s">
-        <v>2425</v>
-      </c>
-      <c r="Z89" s="36" t="s">
-        <v>2433</v>
-      </c>
-      <c r="AA89" s="36" t="s">
-        <v>2232</v>
-      </c>
-      <c r="AB89" s="36" t="s">
-        <v>2233</v>
-      </c>
-      <c r="AC89" s="36" t="str">
-        <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G89&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G89&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【武王城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="武王城·浩气大旗",},</v>
-      </c>
-      <c r="AD89" s="36" t="str">
-        <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G89&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G89&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【武王城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="武王城·恶人大旗",},</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="90" spans="1:30" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C90" s="36" t="s">
-        <v>2435</v>
+        <v>1932</v>
       </c>
       <c r="D90" s="36" t="s">
-        <v>1820</v>
+        <v>2131</v>
       </c>
       <c r="K90" s="36" t="s">
         <v>1432</v>
       </c>
-      <c r="M90" s="36">
+      <c r="Q90" s="36">
         <v>1</v>
       </c>
       <c r="T90" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="武王城·大旗重置",nTime=-2,nRefresh=7200,key="武王城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【武王城】大旗重置",nTime=180,nRefresh=7200,key="武王城·大旗重置",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U90" s="36" t="s">
-        <v>2451</v>
-      </c>
-      <c r="V90" s="36" t="s">
-        <v>2431</v>
-      </c>
-      <c r="W90" s="36" t="s">
-        <v>1898</v>
-      </c>
-      <c r="X90" s="36" t="s">
-        <v>2452</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="91" spans="1:30" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C91" s="36" t="s">
-        <v>1611</v>
+        <v>1933</v>
+      </c>
+      <c r="D91" s="36" t="s">
+        <v>2117</v>
       </c>
       <c r="K91" s="36" t="s">
         <v>1432</v>
       </c>
       <c r="T91" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="本场浩气盟攻防即将结束，南屏山物资运送暂且休整，等待下一场攻防开启！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="粮草先行·活动结束",nTime=5,key="粮草先行·浩气盟",},{nClass=20,nIcon=13,szName="粮草先行·恶人谷",nTime=0,key="粮草先行·恶人谷",},{nClass=20,nIcon=589,nFrame=7,szName="赵新宇",nTime="60,赵新宇·刷新剩余;62,赵新宇·即将刷新",nRefresh=0,key="赵新宇",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U91" s="36" t="s">
-        <v>2319</v>
-      </c>
-      <c r="V91" s="36" t="s">
-        <v>2322</v>
-      </c>
-      <c r="W91" s="36" t="s">
-        <v>2323</v>
+        <v>1790</v>
+      </c>
+      <c r="V91" s="41" t="s">
+        <v>2290</v>
       </c>
     </row>
     <row r="92" spans="1:30" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C92" s="36" t="s">
-        <v>1571</v>
+        <v>2202</v>
+      </c>
+      <c r="D92" s="36" t="s">
+        <v>2203</v>
       </c>
       <c r="K92" s="36" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="T92" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="南屏山恶人谷伴江村援军已到，营地夺回，交通恢复！\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=10,nRefresh=600,key="赵新宇",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U92" s="36" t="s">
-        <v>1658</v>
-      </c>
+        <v>2299</v>
+      </c>
+      <c r="V92" s="39"/>
     </row>
     <row r="93" spans="1:30" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C93" s="36" t="s">
-        <v>1570</v>
+        <v>2196</v>
+      </c>
+      <c r="D93" s="36" t="s">
+        <v>2197</v>
       </c>
       <c r="K93" s="36" t="s">
-        <v>1565</v>
+        <v>1432</v>
       </c>
       <c r="T93" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="南屏山浩气盟望北村援军已到，营地夺回，交通恢复！\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=10,nRefresh=600,key="方超",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U93" s="36" t="s">
-        <v>1657</v>
-      </c>
-    </row>
-    <row r="94" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="A94" t="s">
-        <v>1806</v>
-      </c>
-      <c r="B94">
-        <v>30</v>
+        <v>2298</v>
+      </c>
+      <c r="V93" s="39"/>
+    </row>
+    <row r="94" spans="1:30" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A94" s="36" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B94" s="36">
+        <v>22</v>
       </c>
       <c r="T94" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>},[30]={</v>
+        <f t="shared" si="3"/>
+        <v>},[22]={</v>
       </c>
     </row>
     <row r="95" spans="1:30" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -44672,7 +44638,7 @@
         <v>1493</v>
       </c>
       <c r="G95" s="36" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="K95" s="36" t="s">
         <v>1432</v>
@@ -44681,19 +44647,19 @@
         <v>1</v>
       </c>
       <c r="T95" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凛风堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凛风堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·恶人大旗",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【武王城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="武王城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【武王城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="武王城·恶人大旗",},},},</v>
       </c>
       <c r="U95" s="36" t="s">
         <v>1861</v>
       </c>
       <c r="V95" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G95&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·浩气大旗",},</v>
       </c>
       <c r="W95" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G95&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·恶人大旗",},</v>
       </c>
       <c r="X95" s="36" t="s">
         <v>2423</v>
@@ -44712,32 +44678,32 @@
       </c>
       <c r="AC95" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G95&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G95&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【凛风堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【武王城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="武王城·浩气大旗",},</v>
       </c>
       <c r="AD95" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G95&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G95&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【凛风堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·恶人大旗",},</v>
-      </c>
-    </row>
-    <row r="96" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="C96" t="s">
-        <v>1925</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【武王城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="武王城·恶人大旗",},</v>
+      </c>
+    </row>
+    <row r="96" spans="1:30" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C96" s="36" t="s">
+        <v>2435</v>
       </c>
       <c r="D96" s="36" t="s">
         <v>1820</v>
       </c>
-      <c r="K96" t="s">
+      <c r="K96" s="36" t="s">
         <v>1432</v>
       </c>
-      <c r="M96">
+      <c r="M96" s="36">
         <v>1</v>
       </c>
       <c r="T96" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凛风堡·大旗重置",nTime=-2,nRefresh=7200,key="凛风堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凛风堡】大旗重置",nTime=180,nRefresh=7200,key="凛风堡·大旗重置",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="武王城·大旗重置",nTime=-2,nRefresh=7200,key="武王城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【武王城】大旗重置",nTime=180,nRefresh=7200,key="武王城·大旗重置",},},},</v>
       </c>
       <c r="U96" s="36" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="V96" s="36" t="s">
         <v>2431</v>
@@ -44746,73 +44712,70 @@
         <v>1898</v>
       </c>
       <c r="X96" s="36" t="s">
-        <v>1864</v>
-      </c>
-    </row>
-    <row r="97" spans="1:34" x14ac:dyDescent="0.15">
-      <c r="C97" t="s">
-        <v>1567</v>
-      </c>
-      <c r="K97" t="s">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="97" spans="1:34" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C97" s="36" t="s">
+        <v>1611</v>
+      </c>
+      <c r="K97" s="36" t="s">
         <v>1432</v>
       </c>
       <c r="T97" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="本场恶人谷攻防即将结束，昆仑物资运送暂且休整，等待下一场攻防开启！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="粮草先行·活动结束",nTime=5,key="粮草先行·恶人谷",},{nClass=20,nIcon=13,szName="粮草先行·浩气盟",nTime=0,key="粮草先行·浩气盟",},{nClass=20,nIcon=2864,nFrame=7,szName="霸图",nTime="60,霸图·刷新剩余;62,霸图·即将刷新",nRefresh=0,key="霸图",},{nClass=20,nIcon=845,nFrame=3,szName="孙永恒",nTime="60,孙永恒·刷新剩余;62,孙永恒·即将刷新",nRefresh=0,key="孙永恒",},},},</v>
-      </c>
-      <c r="U97" t="s">
-        <v>2320</v>
-      </c>
-      <c r="V97" t="s">
-        <v>2321</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="本场浩气盟攻防即将结束，南屏山物资运送暂且休整，等待下一场攻防开启！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="粮草先行·活动结束",nTime=5,key="粮草先行·浩气盟",},{nClass=20,nIcon=13,szName="粮草先行·恶人谷",nTime=0,key="粮草先行·恶人谷",},{nClass=20,nIcon=589,nFrame=7,szName="赵新宇",nTime="60,赵新宇·刷新剩余;62,赵新宇·即将刷新",nRefresh=0,key="赵新宇",},},},</v>
+      </c>
+      <c r="U97" s="36" t="s">
+        <v>2319</v>
+      </c>
+      <c r="V97" s="36" t="s">
+        <v>2322</v>
       </c>
       <c r="W97" s="36" t="s">
-        <v>2324</v>
-      </c>
-      <c r="X97" s="36" t="s">
-        <v>2325</v>
-      </c>
-    </row>
-    <row r="98" spans="1:34" x14ac:dyDescent="0.15">
-      <c r="C98" t="s">
-        <v>1569</v>
-      </c>
-      <c r="K98" t="s">
+        <v>2323</v>
+      </c>
+    </row>
+    <row r="98" spans="1:34" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C98" s="36" t="s">
+        <v>1571</v>
+      </c>
+      <c r="K98" s="36" t="s">
         <v>1438</v>
       </c>
       <c r="T98" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="昆仑山恶人谷西昆仑高地援军已到，营地夺回，交通恢复！\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=10,nRefresh=600,key="霸图",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="南屏山恶人谷伴江村援军已到，营地夺回，交通恢复！\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=10,nRefresh=600,key="赵新宇",},},},</v>
       </c>
       <c r="U98" s="36" t="s">
-        <v>1660</v>
-      </c>
-    </row>
-    <row r="99" spans="1:34" x14ac:dyDescent="0.15">
-      <c r="C99" t="s">
-        <v>1568</v>
-      </c>
-      <c r="K99" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="99" spans="1:34" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C99" s="36" t="s">
+        <v>1570</v>
+      </c>
+      <c r="K99" s="36" t="s">
         <v>1565</v>
       </c>
       <c r="T99" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="昆仑山浩气盟东昆仑高地援军已到，营地夺回，交通恢复！\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=10,nRefresh=600,key="孙永恒",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="南屏山浩气盟望北村援军已到，营地夺回，交通恢复！\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=10,nRefresh=600,key="方超",},},},</v>
       </c>
       <c r="U99" s="36" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="100" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A100" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="B100">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="T100" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>},[21]={</v>
+        <f t="shared" si="3"/>
+        <v>},[30]={</v>
       </c>
     </row>
     <row r="101" spans="1:34" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -44823,10 +44786,7 @@
         <v>1493</v>
       </c>
       <c r="G101" s="36" t="s">
-        <v>2206</v>
-      </c>
-      <c r="H101" s="36" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
       <c r="K101" s="36" t="s">
         <v>1432</v>
@@ -44835,58 +44795,42 @@
         <v>1</v>
       </c>
       <c r="T101" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【盘龙坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【逐鹿坪】恶人·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【盘龙坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【逐鹿坪】浩气·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·恶人大旗",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凛风堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凛风堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·恶人大旗",},},},</v>
       </c>
       <c r="U101" s="36" t="s">
         <v>1861</v>
       </c>
       <c r="V101" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G101&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·浩气大旗",},</v>
       </c>
       <c r="W101" s="36" t="str">
-        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H101&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·浩气大旗",},</v>
-      </c>
-      <c r="X101" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G101&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·恶人大旗",},</v>
-      </c>
-      <c r="Y101" s="36" t="str">
-        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H101&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·恶人大旗",},</v>
+      </c>
+      <c r="X101" s="36" t="s">
+        <v>2423</v>
+      </c>
+      <c r="Y101" s="36" t="s">
+        <v>2425</v>
       </c>
       <c r="Z101" s="36" t="s">
-        <v>2422</v>
+        <v>2433</v>
       </c>
       <c r="AA101" s="36" t="s">
-        <v>2424</v>
+        <v>2232</v>
       </c>
       <c r="AB101" s="36" t="s">
-        <v>2432</v>
-      </c>
-      <c r="AC101" s="36" t="s">
-        <v>2232</v>
-      </c>
-      <c r="AD101" s="36" t="s">
         <v>2233</v>
       </c>
-      <c r="AE101" s="36" t="str">
+      <c r="AC101" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G101&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G101&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【盘龙坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·浩气大旗",},</v>
-      </c>
-      <c r="AF101" s="36" t="str">
-        <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H101&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H101&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【逐鹿坪】恶人·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·浩气大旗",},</v>
-      </c>
-      <c r="AG101" s="36" t="str">
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【凛风堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·浩气大旗",},</v>
+      </c>
+      <c r="AD101" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G101&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G101&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【盘龙坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·恶人大旗",},</v>
-      </c>
-      <c r="AH101" s="36" t="str">
-        <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H101&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H101&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【逐鹿坪】浩气·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【凛风堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·恶人大旗",},</v>
       </c>
     </row>
     <row r="102" spans="1:34" x14ac:dyDescent="0.15">
@@ -44903,167 +44847,87 @@
         <v>1</v>
       </c>
       <c r="T102" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="盘龙坞·大旗重置",nTime=-2,nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=1465,szName="逐鹿坪·大旗重置",nTime=-2,nRefresh=7200,key="逐鹿坪·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【盘龙坞】大旗重置",nTime=180,nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【逐鹿坪】大旗重置",nTime=180,nRefresh=7200,key="逐鹿坪·大旗重置",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凛风堡·大旗重置",nTime=-2,nRefresh=7200,key="凛风堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凛风堡】大旗重置",nTime=180,nRefresh=7200,key="凛风堡·大旗重置",},},},</v>
       </c>
       <c r="U102" s="36" t="s">
-        <v>2465</v>
+        <v>2450</v>
       </c>
       <c r="V102" s="36" t="s">
-        <v>2478</v>
+        <v>2431</v>
       </c>
       <c r="W102" s="36" t="s">
-        <v>2430</v>
+        <v>1898</v>
       </c>
       <c r="X102" s="36" t="s">
-        <v>1897</v>
-      </c>
-      <c r="Y102" s="36" t="s">
-        <v>1870</v>
-      </c>
-      <c r="Z102" s="36" t="s">
-        <v>2453</v>
-      </c>
-      <c r="AA102" s="36"/>
+        <v>1864</v>
+      </c>
     </row>
     <row r="103" spans="1:34" x14ac:dyDescent="0.15">
-      <c r="A103" t="s">
-        <v>1808</v>
-      </c>
-      <c r="B103">
-        <v>23</v>
+      <c r="C103" t="s">
+        <v>1567</v>
+      </c>
+      <c r="K103" t="s">
+        <v>1432</v>
       </c>
       <c r="T103" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>},[23]={</v>
-      </c>
-      <c r="Z103" s="36"/>
-      <c r="AA103" s="36"/>
-    </row>
-    <row r="104" spans="1:34" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C104" s="36" t="s">
-        <v>1798</v>
-      </c>
-      <c r="D104" s="36" t="s">
-        <v>1493</v>
-      </c>
-      <c r="G104" s="36" t="s">
-        <v>2208</v>
-      </c>
-      <c r="H104" s="36" t="s">
-        <v>2209</v>
-      </c>
-      <c r="K104" s="36" t="s">
-        <v>1432</v>
-      </c>
-      <c r="M104" s="36">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="本场恶人谷攻防即将结束，昆仑物资运送暂且休整，等待下一场攻防开启！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="粮草先行·活动结束",nTime=5,key="粮草先行·恶人谷",},{nClass=20,nIcon=13,szName="粮草先行·浩气盟",nTime=0,key="粮草先行·浩气盟",},{nClass=20,nIcon=2864,nFrame=7,szName="霸图",nTime="60,霸图·刷新剩余;62,霸图·即将刷新",nRefresh=0,key="霸图",},{nClass=20,nIcon=845,nFrame=3,szName="孙永恒",nTime="60,孙永恒·刷新剩余;62,孙永恒·即将刷新",nRefresh=0,key="孙永恒",},},},</v>
+      </c>
+      <c r="U103" t="s">
+        <v>2320</v>
+      </c>
+      <c r="V103" t="s">
+        <v>2321</v>
+      </c>
+      <c r="W103" s="36" t="s">
+        <v>2324</v>
+      </c>
+      <c r="X103" s="36" t="s">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="104" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="C104" t="s">
+        <v>1569</v>
+      </c>
+      <c r="K104" t="s">
+        <v>1438</v>
       </c>
       <c r="T104" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【龙门镇】恶人·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【飞沙关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【龙门镇】浩气·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【飞沙关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·恶人大旗",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="昆仑山恶人谷西昆仑高地援军已到，营地夺回，交通恢复！\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=10,nRefresh=600,key="霸图",},},},</v>
       </c>
       <c r="U104" s="36" t="s">
-        <v>1861</v>
-      </c>
-      <c r="V104" s="36" t="str">
-        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G104&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·浩气大旗",},</v>
-      </c>
-      <c r="W104" s="36" t="str">
-        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H104&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·浩气大旗",},</v>
-      </c>
-      <c r="X104" s="36" t="str">
-        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G104&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·恶人大旗",},</v>
-      </c>
-      <c r="Y104" s="36" t="str">
-        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H104&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·恶人大旗",},</v>
-      </c>
-      <c r="Z104" s="36" t="s">
-        <v>2422</v>
-      </c>
-      <c r="AA104" s="36" t="s">
-        <v>2424</v>
-      </c>
-      <c r="AB104" s="36" t="s">
-        <v>2432</v>
-      </c>
-      <c r="AC104" s="36" t="s">
-        <v>2232</v>
-      </c>
-      <c r="AD104" s="36" t="s">
-        <v>2233</v>
-      </c>
-      <c r="AE104" s="36" t="str">
-        <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G104&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G104&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【龙门镇】恶人·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·浩气大旗",},</v>
-      </c>
-      <c r="AF104" s="36" t="str">
-        <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H104&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H104&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【飞沙关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·浩气大旗",},</v>
-      </c>
-      <c r="AG104" s="36" t="str">
-        <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G104&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G104&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【龙门镇】浩气·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·恶人大旗",},</v>
-      </c>
-      <c r="AH104" s="36" t="str">
-        <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H104&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H104&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【飞沙关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·恶人大旗",},</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="105" spans="1:34" x14ac:dyDescent="0.15">
       <c r="C105" t="s">
-        <v>1925</v>
-      </c>
-      <c r="D105" s="36" t="s">
-        <v>1820</v>
+        <v>1568</v>
       </c>
       <c r="K105" t="s">
-        <v>1432</v>
-      </c>
-      <c r="M105">
-        <v>1</v>
+        <v>1565</v>
       </c>
       <c r="T105" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="龙门镇·大旗重置",nTime=-2,nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=1465,szName="飞沙关·大旗重置",nTime=-2,nRefresh=7200,key="飞沙关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【龙门镇】大旗重置",nTime=180,nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【飞沙关】大旗重置",nTime=180,nRefresh=7200,key="飞沙关·大旗重置",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="昆仑山浩气盟东昆仑高地援军已到，营地夺回，交通恢复！\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=10,nRefresh=600,key="孙永恒",},},},</v>
       </c>
       <c r="U105" s="36" t="s">
-        <v>2466</v>
-      </c>
-      <c r="V105" s="36" t="s">
-        <v>2479</v>
-      </c>
-      <c r="W105" s="36" t="s">
-        <v>2430</v>
-      </c>
-      <c r="X105" s="36" t="s">
-        <v>1897</v>
-      </c>
-      <c r="Y105" s="36" t="s">
-        <v>1879</v>
-      </c>
-      <c r="Z105" s="36" t="s">
-        <v>2454</v>
-      </c>
-      <c r="AA105" s="36"/>
+        <v>1659</v>
+      </c>
     </row>
     <row r="106" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A106" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="B106">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="T106" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>},[9]={</v>
-      </c>
-      <c r="Z106" s="36"/>
-      <c r="AA106" s="36"/>
+        <f t="shared" si="3"/>
+        <v>},[21]={</v>
+      </c>
     </row>
     <row r="107" spans="1:34" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C107" s="36" t="s">
@@ -45073,10 +44937,10 @@
         <v>1493</v>
       </c>
       <c r="G107" s="36" t="s">
-        <v>2210</v>
+        <v>2206</v>
       </c>
       <c r="H107" s="36" t="s">
-        <v>2211</v>
+        <v>2207</v>
       </c>
       <c r="K107" s="36" t="s">
         <v>1432</v>
@@ -45085,27 +44949,27 @@
         <v>1</v>
       </c>
       <c r="T107" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【红莲岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【秋雨堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【红莲岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【秋雨堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·恶人大旗",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【盘龙坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【逐鹿坪】恶人·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【盘龙坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【逐鹿坪】浩气·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·恶人大旗",},},},</v>
       </c>
       <c r="U107" s="36" t="s">
         <v>1861</v>
       </c>
       <c r="V107" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G107&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·浩气大旗",},</v>
       </c>
       <c r="W107" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H107&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·浩气大旗",},</v>
       </c>
       <c r="X107" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G107&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·恶人大旗",},</v>
       </c>
       <c r="Y107" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H107&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·恶人大旗",},</v>
       </c>
       <c r="Z107" s="36" t="s">
         <v>2422</v>
@@ -45124,19 +44988,19 @@
       </c>
       <c r="AE107" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G107&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G107&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【红莲岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【盘龙坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·浩气大旗",},</v>
       </c>
       <c r="AF107" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H107&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H107&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【秋雨堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【逐鹿坪】恶人·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·浩气大旗",},</v>
       </c>
       <c r="AG107" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G107&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G107&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【红莲岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【盘龙坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·恶人大旗",},</v>
       </c>
       <c r="AH107" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H107&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H107&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【秋雨堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【逐鹿坪】浩气·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·恶人大旗",},</v>
       </c>
     </row>
     <row r="108" spans="1:34" x14ac:dyDescent="0.15">
@@ -45153,14 +45017,14 @@
         <v>1</v>
       </c>
       <c r="T108" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="红莲岗·大旗重置",nTime=-2,nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=1465,szName="秋雨堡·大旗重置",nTime=-2,nRefresh=7200,key="秋雨堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【红莲岗】大旗重置",nTime=180,nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【秋雨堡】大旗重置",nTime=180,nRefresh=7200,key="秋雨堡·大旗重置",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="盘龙坞·大旗重置",nTime=-2,nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=1465,szName="逐鹿坪·大旗重置",nTime=-2,nRefresh=7200,key="逐鹿坪·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【盘龙坞】大旗重置",nTime=180,nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【逐鹿坪】大旗重置",nTime=180,nRefresh=7200,key="逐鹿坪·大旗重置",},},},</v>
       </c>
       <c r="U108" s="36" t="s">
-        <v>2467</v>
+        <v>2465</v>
       </c>
       <c r="V108" s="36" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
       <c r="W108" s="36" t="s">
         <v>2430</v>
@@ -45169,23 +45033,23 @@
         <v>1897</v>
       </c>
       <c r="Y108" s="36" t="s">
-        <v>1881</v>
+        <v>1870</v>
       </c>
       <c r="Z108" s="36" t="s">
-        <v>2455</v>
+        <v>2453</v>
       </c>
       <c r="AA108" s="36"/>
     </row>
     <row r="109" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A109" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="B109">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="T109" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>},[13]={</v>
+        <f t="shared" si="3"/>
+        <v>},[23]={</v>
       </c>
       <c r="Z109" s="36"/>
       <c r="AA109" s="36"/>
@@ -45198,10 +45062,10 @@
         <v>1493</v>
       </c>
       <c r="G110" s="36" t="s">
-        <v>2212</v>
+        <v>2208</v>
       </c>
       <c r="H110" s="36" t="s">
-        <v>2213</v>
+        <v>2209</v>
       </c>
       <c r="K110" s="36" t="s">
         <v>1432</v>
@@ -45210,27 +45074,27 @@
         <v>1</v>
       </c>
       <c r="T110" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【金门关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="金门关·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【青云坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【金门关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="金门关·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【青云坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·恶人大旗",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【龙门镇】恶人·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【飞沙关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【龙门镇】浩气·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【飞沙关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·恶人大旗",},},},</v>
       </c>
       <c r="U110" s="36" t="s">
         <v>1861</v>
       </c>
       <c r="V110" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G110&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·浩气大旗",},</v>
       </c>
       <c r="W110" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H110&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·浩气大旗",},</v>
       </c>
       <c r="X110" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G110&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·恶人大旗",},</v>
       </c>
       <c r="Y110" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H110&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·恶人大旗",},</v>
       </c>
       <c r="Z110" s="36" t="s">
         <v>2422</v>
@@ -45249,19 +45113,19 @@
       </c>
       <c r="AE110" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G110&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G110&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【金门关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="金门关·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【龙门镇】恶人·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·浩气大旗",},</v>
       </c>
       <c r="AF110" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H110&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H110&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【青云坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【飞沙关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·浩气大旗",},</v>
       </c>
       <c r="AG110" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G110&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G110&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【金门关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="金门关·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【龙门镇】浩气·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·恶人大旗",},</v>
       </c>
       <c r="AH110" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H110&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H110&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【青云坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【飞沙关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·恶人大旗",},</v>
       </c>
     </row>
     <row r="111" spans="1:34" x14ac:dyDescent="0.15">
@@ -45278,14 +45142,14 @@
         <v>1</v>
       </c>
       <c r="T111" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="金门关·大旗重置",nTime=-2,nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=1465,szName="青云坞·大旗重置",nTime=-2,nRefresh=7200,key="青云坞·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【金门关】大旗重置",nTime=180,nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【青云坞】大旗重置",nTime=180,nRefresh=7200,key="青云坞·大旗重置",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="龙门镇·大旗重置",nTime=-2,nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=1465,szName="飞沙关·大旗重置",nTime=-2,nRefresh=7200,key="飞沙关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【龙门镇】大旗重置",nTime=180,nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【飞沙关】大旗重置",nTime=180,nRefresh=7200,key="飞沙关·大旗重置",},},},</v>
       </c>
       <c r="U111" s="36" t="s">
-        <v>2468</v>
+        <v>2466</v>
       </c>
       <c r="V111" s="36" t="s">
-        <v>2481</v>
+        <v>2479</v>
       </c>
       <c r="W111" s="36" t="s">
         <v>2430</v>
@@ -45294,23 +45158,23 @@
         <v>1897</v>
       </c>
       <c r="Y111" s="36" t="s">
-        <v>1882</v>
+        <v>1879</v>
       </c>
       <c r="Z111" s="36" t="s">
-        <v>2456</v>
+        <v>2454</v>
       </c>
       <c r="AA111" s="36"/>
     </row>
     <row r="112" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A112" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="B112">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="T112" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>},[35]={</v>
+        <f t="shared" si="3"/>
+        <v>},[9]={</v>
       </c>
       <c r="Z112" s="36"/>
       <c r="AA112" s="36"/>
@@ -45323,10 +45187,10 @@
         <v>1493</v>
       </c>
       <c r="G113" s="36" t="s">
-        <v>2214</v>
+        <v>2210</v>
       </c>
       <c r="H113" s="36" t="s">
-        <v>2215</v>
+        <v>2211</v>
       </c>
       <c r="K113" s="36" t="s">
         <v>1432</v>
@@ -45335,27 +45199,27 @@
         <v>1</v>
       </c>
       <c r="T113" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【激流坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【不空关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="不空关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【激流坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【不空关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="不空关·恶人大旗",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【红莲岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【秋雨堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【红莲岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【秋雨堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·恶人大旗",},},},</v>
       </c>
       <c r="U113" s="36" t="s">
         <v>1861</v>
       </c>
       <c r="V113" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G113&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·浩气大旗",},</v>
       </c>
       <c r="W113" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H113&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·浩气大旗",},</v>
       </c>
       <c r="X113" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G113&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·恶人大旗",},</v>
       </c>
       <c r="Y113" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H113&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},</v>
       </c>
       <c r="Z113" s="36" t="s">
         <v>2422</v>
@@ -45374,19 +45238,19 @@
       </c>
       <c r="AE113" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G113&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G113&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【激流坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【红莲岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·浩气大旗",},</v>
       </c>
       <c r="AF113" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H113&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H113&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【不空关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="不空关·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【秋雨堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·浩气大旗",},</v>
       </c>
       <c r="AG113" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G113&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G113&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【激流坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【红莲岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·恶人大旗",},</v>
       </c>
       <c r="AH113" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H113&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H113&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【不空关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="不空关·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【秋雨堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·恶人大旗",},</v>
       </c>
     </row>
     <row r="114" spans="1:34" x14ac:dyDescent="0.15">
@@ -45403,14 +45267,14 @@
         <v>1</v>
       </c>
       <c r="T114" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="激流坞·大旗重置",nTime=-2,nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=1465,szName="不空关·大旗重置",nTime=-2,nRefresh=7200,key="不空关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【激流坞】大旗重置",nTime=180,nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【不空关】大旗重置",nTime=180,nRefresh=7200,key="不空关·大旗重置",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="红莲岗·大旗重置",nTime=-2,nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=1465,szName="秋雨堡·大旗重置",nTime=-2,nRefresh=7200,key="秋雨堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【红莲岗】大旗重置",nTime=180,nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【秋雨堡】大旗重置",nTime=180,nRefresh=7200,key="秋雨堡·大旗重置",},},},</v>
       </c>
       <c r="U114" s="36" t="s">
-        <v>2469</v>
+        <v>2467</v>
       </c>
       <c r="V114" s="36" t="s">
-        <v>2482</v>
+        <v>2480</v>
       </c>
       <c r="W114" s="36" t="s">
         <v>2430</v>
@@ -45419,23 +45283,23 @@
         <v>1897</v>
       </c>
       <c r="Y114" s="36" t="s">
-        <v>1884</v>
+        <v>1881</v>
       </c>
       <c r="Z114" s="36" t="s">
-        <v>2457</v>
+        <v>2455</v>
       </c>
       <c r="AA114" s="36"/>
     </row>
     <row r="115" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A115" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="B115">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="T115" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>},[100]={</v>
+        <f t="shared" si="3"/>
+        <v>},[13]={</v>
       </c>
       <c r="Z115" s="36"/>
       <c r="AA115" s="36"/>
@@ -45448,10 +45312,10 @@
         <v>1493</v>
       </c>
       <c r="G116" s="36" t="s">
-        <v>2216</v>
+        <v>2212</v>
       </c>
       <c r="H116" s="36" t="s">
-        <v>2217</v>
+        <v>2213</v>
       </c>
       <c r="K116" s="36" t="s">
         <v>1432</v>
@@ -45460,27 +45324,27 @@
         <v>1</v>
       </c>
       <c r="T116" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【日月崖】恶人·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【卧龙坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【日月崖】浩气·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【卧龙坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·恶人大旗",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【金门关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="金门关·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【青云坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【金门关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="金门关·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【青云坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·恶人大旗",},},},</v>
       </c>
       <c r="U116" s="36" t="s">
         <v>1861</v>
       </c>
       <c r="V116" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G116&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·浩气大旗",},</v>
       </c>
       <c r="W116" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H116&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·浩气大旗",},</v>
       </c>
       <c r="X116" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G116&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·恶人大旗",},</v>
       </c>
       <c r="Y116" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H116&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·恶人大旗",},</v>
       </c>
       <c r="Z116" s="36" t="s">
         <v>2422</v>
@@ -45499,19 +45363,19 @@
       </c>
       <c r="AE116" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G116&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G116&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【日月崖】恶人·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【金门关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="金门关·浩气大旗",},</v>
       </c>
       <c r="AF116" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H116&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H116&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【卧龙坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【青云坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·浩气大旗",},</v>
       </c>
       <c r="AG116" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G116&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G116&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【日月崖】浩气·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【金门关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="金门关·恶人大旗",},</v>
       </c>
       <c r="AH116" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H116&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H116&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【卧龙坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【青云坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·恶人大旗",},</v>
       </c>
     </row>
     <row r="117" spans="1:34" x14ac:dyDescent="0.15">
@@ -45528,14 +45392,14 @@
         <v>1</v>
       </c>
       <c r="T117" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="日月崖·大旗重置",nTime=-2,nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=1465,szName="卧龙坡·大旗重置",nTime=-2,nRefresh=7200,key="卧龙坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【日月崖】大旗重置",nTime=180,nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【卧龙坡】大旗重置",nTime=180,nRefresh=7200,key="卧龙坡·大旗重置",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="金门关·大旗重置",nTime=-2,nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=1465,szName="青云坞·大旗重置",nTime=-2,nRefresh=7200,key="青云坞·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【金门关】大旗重置",nTime=180,nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【青云坞】大旗重置",nTime=180,nRefresh=7200,key="青云坞·大旗重置",},},},</v>
       </c>
       <c r="U117" s="36" t="s">
-        <v>2470</v>
+        <v>2468</v>
       </c>
       <c r="V117" s="36" t="s">
-        <v>2483</v>
+        <v>2481</v>
       </c>
       <c r="W117" s="36" t="s">
         <v>2430</v>
@@ -45544,23 +45408,23 @@
         <v>1897</v>
       </c>
       <c r="Y117" s="36" t="s">
-        <v>1886</v>
+        <v>1882</v>
       </c>
       <c r="Z117" s="36" t="s">
-        <v>2458</v>
+        <v>2456</v>
       </c>
       <c r="AA117" s="36"/>
     </row>
     <row r="118" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A118" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="B118">
-        <v>101</v>
+        <v>35</v>
       </c>
       <c r="T118" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>},[101]={</v>
+        <f t="shared" si="3"/>
+        <v>},[35]={</v>
       </c>
       <c r="Z118" s="36"/>
       <c r="AA118" s="36"/>
@@ -45573,10 +45437,10 @@
         <v>1493</v>
       </c>
       <c r="G119" s="36" t="s">
-        <v>2218</v>
+        <v>2214</v>
       </c>
       <c r="H119" s="36" t="s">
-        <v>2219</v>
+        <v>2215</v>
       </c>
       <c r="K119" s="36" t="s">
         <v>1432</v>
@@ -45585,27 +45449,27 @@
         <v>1</v>
       </c>
       <c r="T119" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【霜戈堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【澜沧城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【霜戈堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【澜沧城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·恶人大旗",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【激流坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【不空关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="不空关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【激流坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【不空关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="不空关·恶人大旗",},},},</v>
       </c>
       <c r="U119" s="36" t="s">
         <v>1861</v>
       </c>
       <c r="V119" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G119&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·浩气大旗",},</v>
       </c>
       <c r="W119" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H119&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·浩气大旗",},</v>
       </c>
       <c r="X119" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G119&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·恶人大旗",},</v>
       </c>
       <c r="Y119" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H119&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·恶人大旗",},</v>
       </c>
       <c r="Z119" s="36" t="s">
         <v>2422</v>
@@ -45624,19 +45488,19 @@
       </c>
       <c r="AE119" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G119&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G119&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【霜戈堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【激流坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·浩气大旗",},</v>
       </c>
       <c r="AF119" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H119&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H119&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【澜沧城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【不空关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="不空关·浩气大旗",},</v>
       </c>
       <c r="AG119" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G119&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G119&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【霜戈堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【激流坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·恶人大旗",},</v>
       </c>
       <c r="AH119" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H119&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H119&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【澜沧城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【不空关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="不空关·恶人大旗",},</v>
       </c>
     </row>
     <row r="120" spans="1:34" x14ac:dyDescent="0.15">
@@ -45653,14 +45517,14 @@
         <v>1</v>
       </c>
       <c r="T120" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="霜戈堡·大旗重置",nTime=-2,nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=1465,szName="澜沧城·大旗重置",nTime=-2,nRefresh=7200,key="澜沧城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【霜戈堡】大旗重置",nTime=180,nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【澜沧城】大旗重置",nTime=180,nRefresh=7200,key="澜沧城·大旗重置",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="激流坞·大旗重置",nTime=-2,nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=1465,szName="不空关·大旗重置",nTime=-2,nRefresh=7200,key="不空关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【激流坞】大旗重置",nTime=180,nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【不空关】大旗重置",nTime=180,nRefresh=7200,key="不空关·大旗重置",},},},</v>
       </c>
       <c r="U120" s="36" t="s">
-        <v>2471</v>
+        <v>2469</v>
       </c>
       <c r="V120" s="36" t="s">
-        <v>2484</v>
+        <v>2482</v>
       </c>
       <c r="W120" s="36" t="s">
         <v>2430</v>
@@ -45669,23 +45533,23 @@
         <v>1897</v>
       </c>
       <c r="Y120" s="36" t="s">
-        <v>1888</v>
+        <v>1884</v>
       </c>
       <c r="Z120" s="36" t="s">
-        <v>2459</v>
+        <v>2457</v>
       </c>
       <c r="AA120" s="36"/>
     </row>
     <row r="121" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A121" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="B121">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="T121" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>},[103]={</v>
+        <f t="shared" si="3"/>
+        <v>},[100]={</v>
       </c>
       <c r="Z121" s="36"/>
       <c r="AA121" s="36"/>
@@ -45698,10 +45562,10 @@
         <v>1493</v>
       </c>
       <c r="G122" s="36" t="s">
-        <v>2220</v>
+        <v>2216</v>
       </c>
       <c r="H122" s="36" t="s">
-        <v>2221</v>
+        <v>2217</v>
       </c>
       <c r="K122" s="36" t="s">
         <v>1432</v>
@@ -45710,27 +45574,27 @@
         <v>1</v>
       </c>
       <c r="T122" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【神池岭】恶人·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【烈日岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【神池岭】浩气·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【烈日岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·恶人大旗",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【日月崖】恶人·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【卧龙坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【日月崖】浩气·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【卧龙坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·恶人大旗",},},},</v>
       </c>
       <c r="U122" s="36" t="s">
         <v>1861</v>
       </c>
       <c r="V122" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G122&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·浩气大旗",},</v>
       </c>
       <c r="W122" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H122&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·浩气大旗",},</v>
       </c>
       <c r="X122" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G122&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·恶人大旗",},</v>
       </c>
       <c r="Y122" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H122&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·恶人大旗",},</v>
       </c>
       <c r="Z122" s="36" t="s">
         <v>2422</v>
@@ -45749,19 +45613,19 @@
       </c>
       <c r="AE122" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G122&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G122&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【神池岭】恶人·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【日月崖】恶人·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·浩气大旗",},</v>
       </c>
       <c r="AF122" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H122&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H122&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【烈日岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【卧龙坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·浩气大旗",},</v>
       </c>
       <c r="AG122" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G122&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G122&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【神池岭】浩气·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【日月崖】浩气·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·恶人大旗",},</v>
       </c>
       <c r="AH122" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H122&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H122&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【烈日岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【卧龙坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·恶人大旗",},</v>
       </c>
     </row>
     <row r="123" spans="1:34" x14ac:dyDescent="0.15">
@@ -45778,14 +45642,14 @@
         <v>1</v>
       </c>
       <c r="T123" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="神池岭·大旗重置",nTime=-2,nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=1465,szName="烈日岗·大旗重置",nTime=-2,nRefresh=7200,key="烈日岗·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【神池岭】大旗重置",nTime=180,nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【烈日岗】大旗重置",nTime=180,nRefresh=7200,key="烈日岗·大旗重置",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="日月崖·大旗重置",nTime=-2,nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=1465,szName="卧龙坡·大旗重置",nTime=-2,nRefresh=7200,key="卧龙坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【日月崖】大旗重置",nTime=180,nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【卧龙坡】大旗重置",nTime=180,nRefresh=7200,key="卧龙坡·大旗重置",},},},</v>
       </c>
       <c r="U123" s="36" t="s">
-        <v>2472</v>
+        <v>2470</v>
       </c>
       <c r="V123" s="36" t="s">
-        <v>2485</v>
+        <v>2483</v>
       </c>
       <c r="W123" s="36" t="s">
         <v>2430</v>
@@ -45794,23 +45658,23 @@
         <v>1897</v>
       </c>
       <c r="Y123" s="36" t="s">
-        <v>1890</v>
+        <v>1886</v>
       </c>
       <c r="Z123" s="36" t="s">
-        <v>2460</v>
+        <v>2458</v>
       </c>
       <c r="AA123" s="36"/>
     </row>
     <row r="124" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A124" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="B124">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="T124" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>},[104]={</v>
+        <f t="shared" si="3"/>
+        <v>},[101]={</v>
       </c>
       <c r="Z124" s="36"/>
       <c r="AA124" s="36"/>
@@ -45823,10 +45687,10 @@
         <v>1493</v>
       </c>
       <c r="G125" s="36" t="s">
-        <v>2222</v>
+        <v>2218</v>
       </c>
       <c r="H125" s="36" t="s">
-        <v>2223</v>
+        <v>2219</v>
       </c>
       <c r="K125" s="36" t="s">
         <v>1432</v>
@@ -45835,27 +45699,27 @@
         <v>1</v>
       </c>
       <c r="T125" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凤鸣堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【惊虬谷】恶人·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凤鸣堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【惊虬谷】浩气·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·恶人大旗",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【霜戈堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【澜沧城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【霜戈堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【澜沧城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·恶人大旗",},},},</v>
       </c>
       <c r="U125" s="36" t="s">
         <v>1861</v>
       </c>
       <c r="V125" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G125&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·浩气大旗",},</v>
       </c>
       <c r="W125" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H125&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·浩气大旗",},</v>
       </c>
       <c r="X125" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G125&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·恶人大旗",},</v>
       </c>
       <c r="Y125" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H125&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·恶人大旗",},</v>
       </c>
       <c r="Z125" s="36" t="s">
         <v>2422</v>
@@ -45874,19 +45738,19 @@
       </c>
       <c r="AE125" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G125&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G125&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【凤鸣堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【霜戈堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·浩气大旗",},</v>
       </c>
       <c r="AF125" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H125&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H125&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【惊虬谷】恶人·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【澜沧城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·浩气大旗",},</v>
       </c>
       <c r="AG125" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G125&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G125&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【凤鸣堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【霜戈堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·恶人大旗",},</v>
       </c>
       <c r="AH125" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H125&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H125&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【惊虬谷】浩气·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【澜沧城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·恶人大旗",},</v>
       </c>
     </row>
     <row r="126" spans="1:34" x14ac:dyDescent="0.15">
@@ -45903,14 +45767,14 @@
         <v>1</v>
       </c>
       <c r="T126" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凤鸣堡·大旗重置",nTime=-2,nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=1465,szName="惊虬谷·大旗重置",nTime=-2,nRefresh=7200,key="惊虬谷·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凤鸣堡】大旗重置",nTime=180,nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【惊虬谷】大旗重置",nTime=180,nRefresh=7200,key="惊虬谷·大旗重置",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="霜戈堡·大旗重置",nTime=-2,nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=1465,szName="澜沧城·大旗重置",nTime=-2,nRefresh=7200,key="澜沧城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【霜戈堡】大旗重置",nTime=180,nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【澜沧城】大旗重置",nTime=180,nRefresh=7200,key="澜沧城·大旗重置",},},},</v>
       </c>
       <c r="U126" s="36" t="s">
-        <v>2473</v>
+        <v>2471</v>
       </c>
       <c r="V126" s="36" t="s">
-        <v>2486</v>
+        <v>2484</v>
       </c>
       <c r="W126" s="36" t="s">
         <v>2430</v>
@@ -45919,23 +45783,23 @@
         <v>1897</v>
       </c>
       <c r="Y126" s="36" t="s">
-        <v>1892</v>
+        <v>1888</v>
       </c>
       <c r="Z126" s="36" t="s">
-        <v>2461</v>
+        <v>2459</v>
       </c>
       <c r="AA126" s="36"/>
     </row>
     <row r="127" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A127" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="B127">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="T127" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>},[105]={</v>
+        <f t="shared" si="3"/>
+        <v>},[103]={</v>
       </c>
       <c r="Z127" s="36"/>
       <c r="AA127" s="36"/>
@@ -45948,10 +45812,10 @@
         <v>1493</v>
       </c>
       <c r="G128" s="36" t="s">
-        <v>2224</v>
+        <v>2220</v>
       </c>
       <c r="H128" s="36" t="s">
-        <v>2225</v>
+        <v>2221</v>
       </c>
       <c r="K128" s="36" t="s">
         <v>1432</v>
@@ -45960,27 +45824,27 @@
         <v>1</v>
       </c>
       <c r="T128" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【大理山城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【千岩关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【大理山城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【千岩关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·恶人大旗",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【神池岭】恶人·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【烈日岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【神池岭】浩气·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【烈日岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·恶人大旗",},},},</v>
       </c>
       <c r="U128" s="36" t="s">
         <v>1861</v>
       </c>
       <c r="V128" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G128&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·浩气大旗",},</v>
       </c>
       <c r="W128" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H128&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·浩气大旗",},</v>
       </c>
       <c r="X128" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G128&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·恶人大旗",},</v>
       </c>
       <c r="Y128" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H128&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·恶人大旗",},</v>
       </c>
       <c r="Z128" s="36" t="s">
         <v>2422</v>
@@ -45999,22 +45863,22 @@
       </c>
       <c r="AE128" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G128&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G128&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【大理山城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【神池岭】恶人·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·浩气大旗",},</v>
       </c>
       <c r="AF128" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H128&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H128&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【千岩关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【烈日岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·浩气大旗",},</v>
       </c>
       <c r="AG128" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G128&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G128&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【大理山城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【神池岭】浩气·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·恶人大旗",},</v>
       </c>
       <c r="AH128" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H128&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H128&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【千岩关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·恶人大旗",},</v>
-      </c>
-    </row>
-    <row r="129" spans="1:45" x14ac:dyDescent="0.15">
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【烈日岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·恶人大旗",},</v>
+      </c>
+    </row>
+    <row r="129" spans="1:36" x14ac:dyDescent="0.15">
       <c r="C129" t="s">
         <v>1925</v>
       </c>
@@ -46028,14 +45892,14 @@
         <v>1</v>
       </c>
       <c r="T129" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="大理山城·大旗重置",nTime=-2,nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=1465,szName="千岩关·大旗重置",nTime=-2,nRefresh=7200,key="千岩关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【大理山城】大旗重置",nTime=180,nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【千岩关】大旗重置",nTime=180,nRefresh=7200,key="千岩关·大旗重置",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="神池岭·大旗重置",nTime=-2,nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=1465,szName="烈日岗·大旗重置",nTime=-2,nRefresh=7200,key="烈日岗·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【神池岭】大旗重置",nTime=180,nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【烈日岗】大旗重置",nTime=180,nRefresh=7200,key="烈日岗·大旗重置",},},},</v>
       </c>
       <c r="U129" s="36" t="s">
-        <v>2474</v>
+        <v>2472</v>
       </c>
       <c r="V129" s="36" t="s">
-        <v>2487</v>
+        <v>2485</v>
       </c>
       <c r="W129" s="36" t="s">
         <v>2430</v>
@@ -46044,28 +45908,28 @@
         <v>1897</v>
       </c>
       <c r="Y129" s="36" t="s">
-        <v>1894</v>
+        <v>1890</v>
       </c>
       <c r="Z129" s="36" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="AA129" s="36"/>
     </row>
-    <row r="130" spans="1:45" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:36" x14ac:dyDescent="0.15">
       <c r="A130" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="B130">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="T130" s="36" t="str">
-        <f t="shared" si="1"/>
-        <v>},[139]={</v>
+        <f t="shared" si="3"/>
+        <v>},[104]={</v>
       </c>
       <c r="Z130" s="36"/>
       <c r="AA130" s="36"/>
     </row>
-    <row r="131" spans="1:45" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:36" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C131" s="36" t="s">
         <v>1798</v>
       </c>
@@ -46073,10 +45937,10 @@
         <v>1493</v>
       </c>
       <c r="G131" s="36" t="s">
-        <v>2226</v>
+        <v>2222</v>
       </c>
       <c r="H131" s="36" t="s">
-        <v>2227</v>
+        <v>2223</v>
       </c>
       <c r="K131" s="36" t="s">
         <v>1432</v>
@@ -46085,27 +45949,27 @@
         <v>1</v>
       </c>
       <c r="T131" s="36" t="str">
-        <f t="shared" ref="T131:T143" si="2">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(C131),ISBLANK(L131),ISBLANK(M131),OR(ISBLANK(B130)=FALSE,ISBLANK(C130)=FALSE,ISBLANK(L130)=FALSE,ISBLANK(M130)=FALSE)),"},},}",IF(ISBLANK(C131),"","{szContent="""&amp;C131&amp;""","&amp;IF(D131&lt;&gt;"","szNote="""&amp;D131&amp;""",","")&amp;IF(K131&lt;&gt;"","col={"&amp;K131&amp;"},","")&amp;IF(L131&gt;0,"bSearch=true,","")&amp;IF(M131&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N131&gt;0,"szVoice="""&amp;N131&amp;""",","")&amp;IF(O131&gt;0,"bTeamChannel=true,","")&amp;IF(P131&gt;0,"bWhisperChannel=true,","")&amp;IF(Q131&gt;0,"bCenterAlarm=true,","")&amp;IF(R131&gt;0,"bScreenHead=true,","")&amp;IF(S131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U131:AAF131)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【枫湖寨】恶人·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【啖杏林】恶人·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【枫湖寨】浩气·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【啖杏林】浩气·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·恶人大旗",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凤鸣堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【惊虬谷】恶人·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凤鸣堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【惊虬谷】浩气·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·恶人大旗",},},},</v>
       </c>
       <c r="U131" s="36" t="s">
         <v>1861</v>
       </c>
       <c r="V131" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G131&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·浩气大旗",},</v>
       </c>
       <c r="W131" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H131&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·浩气大旗",},</v>
       </c>
       <c r="X131" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G131&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·恶人大旗",},</v>
       </c>
       <c r="Y131" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H131&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},</v>
       </c>
       <c r="Z131" s="36" t="s">
         <v>2422</v>
@@ -46124,22 +45988,22 @@
       </c>
       <c r="AE131" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G131&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G131&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【枫湖寨】恶人·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【凤鸣堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·浩气大旗",},</v>
       </c>
       <c r="AF131" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H131&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H131&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【啖杏林】恶人·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【惊虬谷】恶人·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·浩气大旗",},</v>
       </c>
       <c r="AG131" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G131&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G131&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【枫湖寨】浩气·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【凤鸣堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·恶人大旗",},</v>
       </c>
       <c r="AH131" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H131&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H131&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【啖杏林】浩气·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·恶人大旗",},</v>
-      </c>
-    </row>
-    <row r="132" spans="1:45" x14ac:dyDescent="0.15">
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【惊虬谷】浩气·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·恶人大旗",},</v>
+      </c>
+    </row>
+    <row r="132" spans="1:36" x14ac:dyDescent="0.15">
       <c r="C132" t="s">
         <v>1925</v>
       </c>
@@ -46153,14 +46017,14 @@
         <v>1</v>
       </c>
       <c r="T132" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="枫湖寨·大旗重置",nTime=-2,nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=1465,szName="啖杏林·大旗重置",nTime=-2,nRefresh=7200,key="啖杏林·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【枫湖寨】大旗重置",nTime=180,nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【啖杏林】大旗重置",nTime=180,nRefresh=7200,key="啖杏林·大旗重置",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凤鸣堡·大旗重置",nTime=-2,nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=1465,szName="惊虬谷·大旗重置",nTime=-2,nRefresh=7200,key="惊虬谷·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凤鸣堡】大旗重置",nTime=180,nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【惊虬谷】大旗重置",nTime=180,nRefresh=7200,key="惊虬谷·大旗重置",},},},</v>
       </c>
       <c r="U132" s="36" t="s">
-        <v>2475</v>
+        <v>2473</v>
       </c>
       <c r="V132" s="36" t="s">
-        <v>2488</v>
+        <v>2486</v>
       </c>
       <c r="W132" s="36" t="s">
         <v>2430</v>
@@ -46169,28 +46033,28 @@
         <v>1897</v>
       </c>
       <c r="Y132" s="36" t="s">
-        <v>1896</v>
+        <v>1892</v>
       </c>
       <c r="Z132" s="36" t="s">
-        <v>2463</v>
+        <v>2461</v>
       </c>
       <c r="AA132" s="36"/>
     </row>
-    <row r="133" spans="1:45" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:36" x14ac:dyDescent="0.15">
       <c r="A133" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="B133">
-        <v>153</v>
+        <v>105</v>
       </c>
       <c r="T133" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>},[153]={</v>
+        <f t="shared" si="3"/>
+        <v>},[105]={</v>
       </c>
       <c r="Z133" s="36"/>
       <c r="AA133" s="36"/>
     </row>
-    <row r="134" spans="1:45" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:36" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C134" s="36" t="s">
         <v>1798</v>
       </c>
@@ -46198,10 +46062,10 @@
         <v>1493</v>
       </c>
       <c r="G134" s="36" t="s">
-        <v>2228</v>
+        <v>2224</v>
       </c>
       <c r="H134" s="36" t="s">
-        <v>2229</v>
+        <v>2225</v>
       </c>
       <c r="K134" s="36" t="s">
         <v>1432</v>
@@ -46210,27 +46074,27 @@
         <v>1</v>
       </c>
       <c r="T134" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【扶风郡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【世外坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【扶风郡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【世外坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·恶人大旗",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【大理山城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【千岩关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【大理山城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【千岩关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·恶人大旗",},},},</v>
       </c>
       <c r="U134" s="36" t="s">
         <v>1861</v>
       </c>
       <c r="V134" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G134&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·浩气大旗",},</v>
       </c>
       <c r="W134" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H134&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·浩气大旗",},</v>
       </c>
       <c r="X134" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G134&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·恶人大旗",},</v>
       </c>
       <c r="Y134" s="36" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H134&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·恶人大旗",},</v>
       </c>
       <c r="Z134" s="36" t="s">
         <v>2422</v>
@@ -46249,22 +46113,22 @@
       </c>
       <c r="AE134" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G134&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G134&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【扶风郡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【大理山城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·浩气大旗",},</v>
       </c>
       <c r="AF134" s="36" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H134&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H134&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【世外坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【千岩关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·浩气大旗",},</v>
       </c>
       <c r="AG134" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G134&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G134&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【扶风郡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【大理山城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·恶人大旗",},</v>
       </c>
       <c r="AH134" s="36" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H134&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H134&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【世外坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·恶人大旗",},</v>
-      </c>
-    </row>
-    <row r="135" spans="1:45" x14ac:dyDescent="0.15">
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【千岩关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·恶人大旗",},</v>
+      </c>
+    </row>
+    <row r="135" spans="1:36" x14ac:dyDescent="0.15">
       <c r="C135" t="s">
         <v>1925</v>
       </c>
@@ -46278,94 +46142,118 @@
         <v>1</v>
       </c>
       <c r="T135" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="扶风郡·大旗重置",nTime=-2,nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=1465,szName="世外坡·大旗重置",nTime=-2,nRefresh=7200,key="世外坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【扶风郡】大旗重置",nTime=180,nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【世外坡】大旗重置",nTime=180,nRefresh=7200,key="世外坡·大旗重置",},},},</v>
+        <f t="shared" si="3"/>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="大理山城·大旗重置",nTime=-2,nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=1465,szName="千岩关·大旗重置",nTime=-2,nRefresh=7200,key="千岩关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【大理山城】大旗重置",nTime=180,nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【千岩关】大旗重置",nTime=180,nRefresh=7200,key="千岩关·大旗重置",},},},</v>
       </c>
       <c r="U135" s="36" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="V135" s="36" t="s">
-        <v>2489</v>
+        <v>2487</v>
       </c>
       <c r="W135" s="36" t="s">
         <v>2430</v>
       </c>
       <c r="X135" s="36" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="Y135" s="36" t="s">
-        <v>1868</v>
+        <v>1894</v>
       </c>
       <c r="Z135" s="36" t="s">
-        <v>2464</v>
+        <v>2462</v>
       </c>
       <c r="AA135" s="36"/>
     </row>
-    <row r="136" spans="1:45" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:36" x14ac:dyDescent="0.15">
       <c r="A136" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="B136">
-        <v>216</v>
+        <v>139</v>
       </c>
       <c r="T136" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>},[216]={</v>
+        <f t="shared" si="3"/>
+        <v>},[139]={</v>
       </c>
       <c r="Z136" s="36"/>
       <c r="AA136" s="36"/>
     </row>
-    <row r="137" spans="1:45" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:36" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C137" s="36" t="s">
-        <v>1799</v>
-      </c>
-      <c r="D137" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D137" s="36" t="s">
         <v>1493</v>
       </c>
-      <c r="G137" t="s">
-        <v>2230</v>
-      </c>
-      <c r="H137" t="s">
-        <v>2231</v>
-      </c>
-      <c r="K137" t="s">
+      <c r="G137" s="36" t="s">
+        <v>2226</v>
+      </c>
+      <c r="H137" s="36" t="s">
+        <v>2227</v>
+      </c>
+      <c r="K137" s="36" t="s">
         <v>1432</v>
       </c>
-      <c r="M137">
+      <c r="M137" s="36">
         <v>1</v>
       </c>
       <c r="T137" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
+        <f t="shared" ref="T137:T149" si="4">IF(ISBLANK(B137)=FALSE,IF(ISBLANK(B136),"},["&amp;B137&amp;"]={","["&amp;B137&amp;"]={"),IF(AND(ISBLANK(B137),ISBLANK(C137),ISBLANK(L137),ISBLANK(M137),OR(ISBLANK(B136)=FALSE,ISBLANK(C136)=FALSE,ISBLANK(L136)=FALSE,ISBLANK(M136)=FALSE)),"},},}",IF(ISBLANK(C137),"","{szContent="""&amp;C137&amp;""","&amp;IF(D137&lt;&gt;"","szNote="""&amp;D137&amp;""",","")&amp;IF(K137&lt;&gt;"","col={"&amp;K137&amp;"},","")&amp;IF(L137&gt;0,"bSearch=true,","")&amp;IF(M137&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N137&gt;0,"szVoice="""&amp;N137&amp;""",","")&amp;IF(O137&gt;0,"bTeamChannel=true,","")&amp;IF(P137&gt;0,"bWhisperChannel=true,","")&amp;IF(Q137&gt;0,"bCenterAlarm=true,","")&amp;IF(R137&gt;0,"bScreenHead=true,","")&amp;IF(S137&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U137&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U137:AAF137)&amp;"},","")&amp;"},")))</f>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【枫湖寨】恶人·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【啖杏林】恶人·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【枫湖寨】浩气·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【啖杏林】浩气·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·恶人大旗",},},},</v>
       </c>
       <c r="U137" s="36" t="s">
         <v>1861</v>
       </c>
-      <c r="V137" s="36" t="s">
+      <c r="V137" s="36" t="str">
+        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G137&amp;"·浩气大旗"&amp;""",},"</f>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·浩气大旗",},</v>
+      </c>
+      <c r="W137" s="36" t="str">
+        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H137&amp;"·浩气大旗"&amp;""",},"</f>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·浩气大旗",},</v>
+      </c>
+      <c r="X137" s="36" t="str">
+        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G137&amp;"·恶人大旗"&amp;""",},"</f>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·恶人大旗",},</v>
+      </c>
+      <c r="Y137" s="36" t="str">
+        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H137&amp;"·恶人大旗"&amp;""",},"</f>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·恶人大旗",},</v>
+      </c>
+      <c r="Z137" s="36" t="s">
         <v>2422</v>
       </c>
-      <c r="W137" s="36" t="s">
+      <c r="AA137" s="36" t="s">
         <v>2424</v>
       </c>
-      <c r="X137" s="36" t="s">
-        <v>2434</v>
-      </c>
-      <c r="Y137" s="36" t="s">
-        <v>2200</v>
-      </c>
-      <c r="Z137" s="36" t="s">
-        <v>2201</v>
-      </c>
-      <c r="AC137" s="36"/>
-      <c r="AD137" s="36"/>
-      <c r="AE137" s="36"/>
-      <c r="AF137" s="36"/>
-      <c r="AG137" s="36"/>
-      <c r="AH137" s="36"/>
-      <c r="AI137" s="36"/>
-      <c r="AJ137" s="36"/>
-    </row>
-    <row r="138" spans="1:45" x14ac:dyDescent="0.15">
+      <c r="AB137" s="36" t="s">
+        <v>2432</v>
+      </c>
+      <c r="AC137" s="36" t="s">
+        <v>2232</v>
+      </c>
+      <c r="AD137" s="36" t="s">
+        <v>2233</v>
+      </c>
+      <c r="AE137" s="36" t="str">
+        <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G137&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G137&amp;"·浩气大旗"""&amp;",},"</f>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【枫湖寨】恶人·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·浩气大旗",},</v>
+      </c>
+      <c r="AF137" s="36" t="str">
+        <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H137&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H137&amp;"·浩气大旗"""&amp;",},"</f>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【啖杏林】恶人·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·浩气大旗",},</v>
+      </c>
+      <c r="AG137" s="36" t="str">
+        <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G137&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G137&amp;"·恶人大旗"""&amp;",},"</f>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【枫湖寨】浩气·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·恶人大旗",},</v>
+      </c>
+      <c r="AH137" s="36" t="str">
+        <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H137&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H137&amp;"·恶人大旗"""&amp;",},"</f>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【啖杏林】浩气·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·恶人大旗",},</v>
+      </c>
+    </row>
+    <row r="138" spans="1:36" x14ac:dyDescent="0.15">
       <c r="C138" t="s">
         <v>1925</v>
       </c>
@@ -46379,14 +46267,14 @@
         <v>1</v>
       </c>
       <c r="T138" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime=180,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime=180,nRefresh=7200,key="高阳营·大旗重置",},},},</v>
+        <f t="shared" si="4"/>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="枫湖寨·大旗重置",nTime=-2,nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=1465,szName="啖杏林·大旗重置",nTime=-2,nRefresh=7200,key="啖杏林·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【枫湖寨】大旗重置",nTime=180,nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【啖杏林】大旗重置",nTime=180,nRefresh=7200,key="啖杏林·大旗重置",},},},</v>
       </c>
       <c r="U138" s="36" t="s">
-        <v>2477</v>
+        <v>2475</v>
       </c>
       <c r="V138" s="36" t="s">
-        <v>2490</v>
+        <v>2488</v>
       </c>
       <c r="W138" s="36" t="s">
         <v>2430</v>
@@ -46395,70 +46283,107 @@
         <v>1897</v>
       </c>
       <c r="Y138" s="36" t="s">
-        <v>1919</v>
+        <v>1896</v>
       </c>
       <c r="Z138" s="36" t="s">
-        <v>1920</v>
+        <v>2463</v>
       </c>
       <c r="AA138" s="36"/>
     </row>
-    <row r="139" spans="1:45" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C139" s="36" t="s">
-        <v>1803</v>
-      </c>
-      <c r="D139" s="36" t="s">
-        <v>1494</v>
-      </c>
-      <c r="K139" s="36" t="s">
+    <row r="139" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="A139" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B139">
+        <v>153</v>
+      </c>
+      <c r="T139" s="36" t="str">
+        <f t="shared" si="4"/>
+        <v>},[153]={</v>
+      </c>
+      <c r="Z139" s="36"/>
+      <c r="AA139" s="36"/>
+    </row>
+    <row r="140" spans="1:36" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C140" s="36" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D140" s="36" t="s">
+        <v>1493</v>
+      </c>
+      <c r="G140" s="36" t="s">
+        <v>2228</v>
+      </c>
+      <c r="H140" s="36" t="s">
+        <v>2229</v>
+      </c>
+      <c r="K140" s="36" t="s">
         <v>1432</v>
       </c>
-      <c r="M139" s="36">
-        <v>1</v>
-      </c>
-      <c r="T139" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
-      </c>
-      <c r="U139" s="36" t="s">
-        <v>2427</v>
-      </c>
-      <c r="V139" s="36" t="s">
-        <v>2428</v>
-      </c>
-      <c r="W139" s="36" t="s">
-        <v>2429</v>
-      </c>
-      <c r="X139" s="36" t="s">
-        <v>1771</v>
-      </c>
-      <c r="Y139" s="36" t="s">
-        <v>1772</v>
-      </c>
-    </row>
-    <row r="140" spans="1:45" x14ac:dyDescent="0.15">
-      <c r="A140" t="s">
-        <v>613</v>
-      </c>
-      <c r="B140">
-        <v>656</v>
+      <c r="M140" s="36">
+        <v>1</v>
       </c>
       <c r="T140" s="36" t="str">
-        <f t="shared" si="2"/>
-        <v>},[656]={</v>
-      </c>
-    </row>
-    <row r="141" spans="1:45" x14ac:dyDescent="0.15">
-      <c r="C141" s="36" t="s">
-        <v>1799</v>
-      </c>
-      <c r="D141" t="s">
-        <v>1493</v>
-      </c>
-      <c r="G141" s="36" t="s">
-        <v>2230</v>
-      </c>
-      <c r="H141" s="36" t="s">
-        <v>2231</v>
+        <f t="shared" si="4"/>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【扶风郡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【世外坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【扶风郡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【世外坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·恶人大旗",},},},</v>
+      </c>
+      <c r="U140" s="36" t="s">
+        <v>1861</v>
+      </c>
+      <c r="V140" s="36" t="str">
+        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G140&amp;"·浩气大旗"&amp;""",},"</f>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·浩气大旗",},</v>
+      </c>
+      <c r="W140" s="36" t="str">
+        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H140&amp;"·浩气大旗"&amp;""",},"</f>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·浩气大旗",},</v>
+      </c>
+      <c r="X140" s="36" t="str">
+        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G140&amp;"·恶人大旗"&amp;""",},"</f>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·恶人大旗",},</v>
+      </c>
+      <c r="Y140" s="36" t="str">
+        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H140&amp;"·恶人大旗"&amp;""",},"</f>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·恶人大旗",},</v>
+      </c>
+      <c r="Z140" s="36" t="s">
+        <v>2422</v>
+      </c>
+      <c r="AA140" s="36" t="s">
+        <v>2424</v>
+      </c>
+      <c r="AB140" s="36" t="s">
+        <v>2432</v>
+      </c>
+      <c r="AC140" s="36" t="s">
+        <v>2232</v>
+      </c>
+      <c r="AD140" s="36" t="s">
+        <v>2233</v>
+      </c>
+      <c r="AE140" s="36" t="str">
+        <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G140&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G140&amp;"·浩气大旗"""&amp;",},"</f>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【扶风郡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·浩气大旗",},</v>
+      </c>
+      <c r="AF140" s="36" t="str">
+        <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H140&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H140&amp;"·浩气大旗"""&amp;",},"</f>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【世外坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·浩气大旗",},</v>
+      </c>
+      <c r="AG140" s="36" t="str">
+        <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G140&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G140&amp;"·恶人大旗"""&amp;",},"</f>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【扶风郡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·恶人大旗",},</v>
+      </c>
+      <c r="AH140" s="36" t="str">
+        <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H140&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H140&amp;"·恶人大旗"""&amp;",},"</f>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【世外坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·恶人大旗",},</v>
+      </c>
+    </row>
+    <row r="141" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="C141" t="s">
+        <v>1925</v>
+      </c>
+      <c r="D141" s="36" t="s">
+        <v>1820</v>
       </c>
       <c r="K141" t="s">
         <v>1432</v>
@@ -46467,133 +46392,322 @@
         <v>1</v>
       </c>
       <c r="T141" s="36" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="扶风郡·大旗重置",nTime=-2,nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=1465,szName="世外坡·大旗重置",nTime=-2,nRefresh=7200,key="世外坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【扶风郡】大旗重置",nTime=180,nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【世外坡】大旗重置",nTime=180,nRefresh=7200,key="世外坡·大旗重置",},},},</v>
+      </c>
+      <c r="U141" s="36" t="s">
+        <v>2476</v>
+      </c>
+      <c r="V141" s="36" t="s">
+        <v>2489</v>
+      </c>
+      <c r="W141" s="36" t="s">
+        <v>2430</v>
+      </c>
+      <c r="X141" s="36" t="s">
+        <v>1898</v>
+      </c>
+      <c r="Y141" s="36" t="s">
+        <v>1868</v>
+      </c>
+      <c r="Z141" s="36" t="s">
+        <v>2464</v>
+      </c>
+      <c r="AA141" s="36"/>
+    </row>
+    <row r="142" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="A142" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B142">
+        <v>216</v>
+      </c>
+      <c r="T142" s="36" t="str">
+        <f t="shared" si="4"/>
+        <v>},[216]={</v>
+      </c>
+      <c r="Z142" s="36"/>
+      <c r="AA142" s="36"/>
+    </row>
+    <row r="143" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="C143" s="36" t="s">
+        <v>1799</v>
+      </c>
+      <c r="D143" t="s">
+        <v>1493</v>
+      </c>
+      <c r="G143" t="s">
+        <v>2230</v>
+      </c>
+      <c r="H143" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K143" t="s">
+        <v>1432</v>
+      </c>
+      <c r="M143">
+        <v>1</v>
+      </c>
+      <c r="T143" s="36" t="str">
+        <f t="shared" si="4"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
-      <c r="U141" s="36" t="s">
+      <c r="U143" s="36" t="s">
         <v>1861</v>
       </c>
-      <c r="V141" t="s">
+      <c r="V143" s="36" t="s">
         <v>2422</v>
       </c>
-      <c r="W141" t="s">
+      <c r="W143" s="36" t="s">
         <v>2424</v>
       </c>
-      <c r="X141" s="36" t="s">
+      <c r="X143" s="36" t="s">
         <v>2434</v>
       </c>
-      <c r="Y141" s="36" t="s">
+      <c r="Y143" s="36" t="s">
         <v>2200</v>
       </c>
-      <c r="Z141" s="36" t="s">
+      <c r="Z143" s="36" t="s">
         <v>2201</v>
       </c>
-      <c r="AC141" s="36"/>
-      <c r="AD141" s="36"/>
-      <c r="AE141" s="36"/>
-    </row>
-    <row r="142" spans="1:45" x14ac:dyDescent="0.15">
-      <c r="C142" t="s">
+      <c r="AC143" s="36"/>
+      <c r="AD143" s="36"/>
+      <c r="AE143" s="36"/>
+      <c r="AF143" s="36"/>
+      <c r="AG143" s="36"/>
+      <c r="AH143" s="36"/>
+      <c r="AI143" s="36"/>
+      <c r="AJ143" s="36"/>
+    </row>
+    <row r="144" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="C144" t="s">
         <v>1925</v>
       </c>
-      <c r="D142" s="36" t="s">
+      <c r="D144" s="36" t="s">
         <v>1820</v>
       </c>
-      <c r="K142" t="s">
+      <c r="K144" t="s">
         <v>1432</v>
       </c>
-      <c r="M142">
-        <v>1</v>
-      </c>
-      <c r="T142" s="36" t="str">
-        <f t="shared" si="2"/>
+      <c r="M144">
+        <v>1</v>
+      </c>
+      <c r="T144" s="36" t="str">
+        <f t="shared" si="4"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime=180,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime=180,nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
-      <c r="U142" s="36" t="s">
+      <c r="U144" s="36" t="s">
         <v>2477</v>
       </c>
-      <c r="V142" s="36" t="s">
+      <c r="V144" s="36" t="s">
         <v>2490</v>
       </c>
-      <c r="W142" s="36" t="s">
+      <c r="W144" s="36" t="s">
         <v>2430</v>
       </c>
-      <c r="X142" s="36" t="s">
+      <c r="X144" s="36" t="s">
         <v>1897</v>
       </c>
-      <c r="Y142" s="36" t="s">
+      <c r="Y144" s="36" t="s">
         <v>1919</v>
       </c>
-      <c r="Z142" s="36" t="s">
+      <c r="Z144" s="36" t="s">
         <v>1920</v>
       </c>
-      <c r="AA142" s="36"/>
-      <c r="AB142" s="36"/>
-      <c r="AC142" s="36"/>
-      <c r="AD142" s="36"/>
-      <c r="AE142" s="36"/>
-      <c r="AF142" s="36"/>
-      <c r="AG142" s="36"/>
-      <c r="AH142" s="36"/>
-      <c r="AI142" s="36"/>
-      <c r="AJ142" s="36"/>
-      <c r="AK142" s="36"/>
-      <c r="AL142" s="36"/>
-      <c r="AM142" s="36"/>
-      <c r="AN142" s="36"/>
-      <c r="AO142" s="36"/>
-      <c r="AP142" s="36"/>
-      <c r="AQ142" s="36"/>
-      <c r="AR142" s="36"/>
-      <c r="AS142" s="36"/>
-    </row>
-    <row r="143" spans="1:45" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C143" s="36" t="s">
+      <c r="AA144" s="36"/>
+    </row>
+    <row r="145" spans="1:45" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C145" s="36" t="s">
         <v>1803</v>
       </c>
-      <c r="D143" s="36" t="s">
+      <c r="D145" s="36" t="s">
         <v>1494</v>
       </c>
-      <c r="K143" s="36" t="s">
+      <c r="K145" s="36" t="s">
         <v>1432</v>
       </c>
-      <c r="M143" s="36">
-        <v>1</v>
-      </c>
-      <c r="T143" s="36" t="str">
-        <f t="shared" si="2"/>
+      <c r="M145" s="36">
+        <v>1</v>
+      </c>
+      <c r="T145" s="36" t="str">
+        <f t="shared" si="4"/>
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
-      <c r="U143" s="36" t="s">
+      <c r="U145" s="36" t="s">
         <v>2427</v>
       </c>
-      <c r="V143" s="36" t="s">
+      <c r="V145" s="36" t="s">
         <v>2428</v>
       </c>
-      <c r="W143" s="36" t="s">
+      <c r="W145" s="36" t="s">
         <v>2429</v>
       </c>
-      <c r="X143" s="36" t="s">
+      <c r="X145" s="36" t="s">
         <v>1771</v>
       </c>
-      <c r="Y143" s="36" t="s">
+      <c r="Y145" s="36" t="s">
         <v>1772</v>
       </c>
     </row>
-    <row r="144" spans="1:45" x14ac:dyDescent="0.15">
-      <c r="T144" s="36"/>
-    </row>
-    <row r="145" spans="20:20" x14ac:dyDescent="0.15">
-      <c r="T145" s="36"/>
-    </row>
-    <row r="146" spans="20:20" x14ac:dyDescent="0.15">
-      <c r="T146" s="36"/>
-    </row>
-    <row r="147" spans="20:20" x14ac:dyDescent="0.15">
-      <c r="T147" s="36"/>
+    <row r="146" spans="1:45" x14ac:dyDescent="0.15">
+      <c r="A146" t="s">
+        <v>613</v>
+      </c>
+      <c r="B146">
+        <v>656</v>
+      </c>
+      <c r="T146" s="36" t="str">
+        <f t="shared" si="4"/>
+        <v>},[656]={</v>
+      </c>
+    </row>
+    <row r="147" spans="1:45" x14ac:dyDescent="0.15">
+      <c r="C147" s="36" t="s">
+        <v>1799</v>
+      </c>
+      <c r="D147" t="s">
+        <v>1493</v>
+      </c>
+      <c r="G147" s="36" t="s">
+        <v>2230</v>
+      </c>
+      <c r="H147" s="36" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K147" t="s">
+        <v>1432</v>
+      </c>
+      <c r="M147">
+        <v>1</v>
+      </c>
+      <c r="T147" s="36" t="str">
+        <f t="shared" si="4"/>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
+      </c>
+      <c r="U147" s="36" t="s">
+        <v>1861</v>
+      </c>
+      <c r="V147" t="s">
+        <v>2422</v>
+      </c>
+      <c r="W147" t="s">
+        <v>2424</v>
+      </c>
+      <c r="X147" s="36" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Y147" s="36" t="s">
+        <v>2200</v>
+      </c>
+      <c r="Z147" s="36" t="s">
+        <v>2201</v>
+      </c>
+      <c r="AC147" s="36"/>
+      <c r="AD147" s="36"/>
+      <c r="AE147" s="36"/>
+    </row>
+    <row r="148" spans="1:45" x14ac:dyDescent="0.15">
+      <c r="C148" t="s">
+        <v>1925</v>
+      </c>
+      <c r="D148" s="36" t="s">
+        <v>1820</v>
+      </c>
+      <c r="K148" t="s">
+        <v>1432</v>
+      </c>
+      <c r="M148">
+        <v>1</v>
+      </c>
+      <c r="T148" s="36" t="str">
+        <f t="shared" si="4"/>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime=180,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime=180,nRefresh=7200,key="高阳营·大旗重置",},},},</v>
+      </c>
+      <c r="U148" s="36" t="s">
+        <v>2477</v>
+      </c>
+      <c r="V148" s="36" t="s">
+        <v>2490</v>
+      </c>
+      <c r="W148" s="36" t="s">
+        <v>2430</v>
+      </c>
+      <c r="X148" s="36" t="s">
+        <v>1897</v>
+      </c>
+      <c r="Y148" s="36" t="s">
+        <v>1919</v>
+      </c>
+      <c r="Z148" s="36" t="s">
+        <v>1920</v>
+      </c>
+      <c r="AA148" s="36"/>
+      <c r="AB148" s="36"/>
+      <c r="AC148" s="36"/>
+      <c r="AD148" s="36"/>
+      <c r="AE148" s="36"/>
+      <c r="AF148" s="36"/>
+      <c r="AG148" s="36"/>
+      <c r="AH148" s="36"/>
+      <c r="AI148" s="36"/>
+      <c r="AJ148" s="36"/>
+      <c r="AK148" s="36"/>
+      <c r="AL148" s="36"/>
+      <c r="AM148" s="36"/>
+      <c r="AN148" s="36"/>
+      <c r="AO148" s="36"/>
+      <c r="AP148" s="36"/>
+      <c r="AQ148" s="36"/>
+      <c r="AR148" s="36"/>
+      <c r="AS148" s="36"/>
+    </row>
+    <row r="149" spans="1:45" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C149" s="36" t="s">
+        <v>1803</v>
+      </c>
+      <c r="D149" s="36" t="s">
+        <v>1494</v>
+      </c>
+      <c r="K149" s="36" t="s">
+        <v>1432</v>
+      </c>
+      <c r="M149" s="36">
+        <v>1</v>
+      </c>
+      <c r="T149" s="36" t="str">
+        <f t="shared" si="4"/>
+        <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
+      </c>
+      <c r="U149" s="36" t="s">
+        <v>2427</v>
+      </c>
+      <c r="V149" s="36" t="s">
+        <v>2428</v>
+      </c>
+      <c r="W149" s="36" t="s">
+        <v>2429</v>
+      </c>
+      <c r="X149" s="36" t="s">
+        <v>1771</v>
+      </c>
+      <c r="Y149" s="36" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="150" spans="1:45" x14ac:dyDescent="0.15">
+      <c r="T150" s="36"/>
+    </row>
+    <row r="151" spans="1:45" x14ac:dyDescent="0.15">
+      <c r="T151" s="36"/>
+    </row>
+    <row r="152" spans="1:45" x14ac:dyDescent="0.15">
+      <c r="T152" s="36"/>
+    </row>
+    <row r="153" spans="1:45" x14ac:dyDescent="0.15">
+      <c r="T153" s="36"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BG143" xr:uid="{CA93DE1B-A3F3-4B99-8EB6-90DC2B8497E1}"/>
+  <autoFilter ref="A1:BG149" xr:uid="{CA93DE1B-A3F3-4B99-8EB6-90DC2B8497E1}"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/阵营/大小攻防团队监控.xlsx
+++ b/阵营/大小攻防团队监控.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JX3\Game\JX3\bin\zhcn_hd\interface\MY#DATA\!all-users@zhcn_hd\userdata\team_mon\remote\打包\阵营\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{61038297-F7D4-4ADA-9AEE-01964B446BE1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CA092919-726B-4258-909A-51F73D21A766}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据总控" sheetId="2" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="5683" uniqueCount="2734">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="5683" uniqueCount="2735">
   <si>
     <t>标识</t>
   </si>
@@ -8805,22 +8805,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>{nClass=0,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=2,nRefresh=600,key="赵新宇",},</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{nClass=0,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=2,nRefresh=600,key="方超",},</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{nClass=0,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=2,nRefresh=600,key="霸图",},</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{nClass=0,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=2,nRefresh=600,key="孙永恒",},</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>捡</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -8861,10 +8845,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>{nClass=1,nIcon=1272,nFrame=2,szName="离开据点·大旗重置",nTime=-1,key="离开据点·大旗重置",},</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>您因消极怠战,扰乱阵营秩序，被阵营督查官请离当前地图，但同时给予250点贡献积分！</t>
   </si>
   <si>
@@ -9300,10 +9280,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>{nClass=14,nIcon=592,nFrame=8,szName="【{$me}】·拾取大旗",nTime=30,key="拾取大旗·{$me}",},</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=0,key="大旗赛点·CD",},</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -9373,6 +9349,34 @@
   </si>
   <si>
     <t>{nClass=2,nIcon=22928,nFrame=2,szName="【{$receiver}】·可以捡旗",nTime=5,key="经脉逆行·{$receiver}",},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="据点大旗·旗手提示",},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=592,nFrame=8,szName="【{$me}】·拾取大旗",nTime=30,key="据点大旗·旗手提示",},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{nClass=1,nIcon=1272,nFrame=2,szName="据点大旗·旗手提示",nTime=-1,key="据点大旗·旗手提示",},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{nClass=-1,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=2,nRefresh=600,key="霸图",},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{nClass=-1,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=2,nRefresh=600,key="孙永恒",},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{nClass=-1,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=2,nRefresh=600,key="赵新宇",},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{nClass=-1,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=2,nRefresh=600,key="方超",},</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -10743,7 +10747,7 @@
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="21" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1772372969870,</v>
+        <v>nTimeStamp = 1774718023190,</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>34</v>
@@ -14339,7 +14343,7 @@
         <v>95</v>
       </c>
       <c r="K39" s="44" t="s">
-        <v>2643</v>
+        <v>2638</v>
       </c>
       <c r="M39" s="3" t="s">
         <v>1123</v>
@@ -14359,7 +14363,7 @@
         <v>99</v>
       </c>
       <c r="K40" s="45" t="s">
-        <v>2644</v>
+        <v>2639</v>
       </c>
       <c r="M40" s="3" t="s">
         <v>1125</v>
@@ -14379,7 +14383,7 @@
         <v>104</v>
       </c>
       <c r="K41" s="46" t="s">
-        <v>2645</v>
+        <v>2640</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>1128</v>
@@ -14399,7 +14403,7 @@
         <v>107</v>
       </c>
       <c r="K42" s="47" t="s">
-        <v>2646</v>
+        <v>2641</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>1131</v>
@@ -14419,7 +14423,7 @@
         <v>111</v>
       </c>
       <c r="K43" s="49" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>1133</v>
@@ -14439,7 +14443,7 @@
         <v>115</v>
       </c>
       <c r="K44" s="48" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>1136</v>
@@ -20685,13 +20689,13 @@
         <v>1</v>
       </c>
       <c r="G6" s="36" t="s">
-        <v>2687</v>
+        <v>2682</v>
       </c>
       <c r="I6" s="36">
         <v>2</v>
       </c>
       <c r="K6" s="36" t="s">
-        <v>2686</v>
+        <v>2681</v>
       </c>
       <c r="T6" s="36">
         <v>1</v>
@@ -20718,7 +20722,7 @@
         <v>1801</v>
       </c>
       <c r="L7" s="36" t="s">
-        <v>2639</v>
+        <v>2634</v>
       </c>
       <c r="T7" s="36">
         <v>1</v>
@@ -20834,7 +20838,7 @@
       <c r="E10" s="35"/>
       <c r="F10" s="35"/>
       <c r="G10" s="35" t="s">
-        <v>2688</v>
+        <v>2683</v>
       </c>
       <c r="H10" s="35"/>
       <c r="I10" s="35">
@@ -20947,7 +20951,7 @@
     </row>
     <row r="12" spans="1:45" x14ac:dyDescent="0.15">
       <c r="A12" s="31" t="s">
-        <v>2692</v>
+        <v>2687</v>
       </c>
       <c r="B12" s="31">
         <v>-20</v>
@@ -21010,7 +21014,7 @@
       <c r="E13" s="31"/>
       <c r="F13" s="31"/>
       <c r="G13" s="31" t="s">
-        <v>2640</v>
+        <v>2635</v>
       </c>
       <c r="H13" s="31"/>
       <c r="I13" s="31"/>
@@ -21093,7 +21097,7 @@
       <c r="E14" s="31"/>
       <c r="F14" s="31"/>
       <c r="G14" s="31" t="s">
-        <v>2641</v>
+        <v>2636</v>
       </c>
       <c r="H14" s="31"/>
       <c r="I14" s="31"/>
@@ -21265,7 +21269,7 @@
         <v>1</v>
       </c>
       <c r="G19" s="36" t="s">
-        <v>2640</v>
+        <v>2635</v>
       </c>
       <c r="K19" s="36" t="s">
         <v>1653</v>
@@ -21322,7 +21326,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="36" t="s">
-        <v>2641</v>
+        <v>2636</v>
       </c>
       <c r="K20" s="36" t="s">
         <v>1652</v>
@@ -21472,7 +21476,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="36" t="s">
-        <v>2640</v>
+        <v>2635</v>
       </c>
       <c r="K25" s="36" t="s">
         <v>1653</v>
@@ -21529,7 +21533,7 @@
         <v>1</v>
       </c>
       <c r="G26" s="36" t="s">
-        <v>2641</v>
+        <v>2636</v>
       </c>
       <c r="K26" s="36" t="s">
         <v>1652</v>
@@ -21712,7 +21716,7 @@
         <v>1</v>
       </c>
       <c r="G32" s="36" t="s">
-        <v>2688</v>
+        <v>2683</v>
       </c>
       <c r="I32" s="36">
         <v>1</v>
@@ -22659,7 +22663,7 @@
         <v>3</v>
       </c>
       <c r="AG13" s="36" t="s">
-        <v>2642</v>
+        <v>2637</v>
       </c>
       <c r="AI13" s="36">
         <v>0</v>
@@ -22825,10 +22829,10 @@
         <v>1943</v>
       </c>
       <c r="AS17" s="36" t="s">
-        <v>2630</v>
+        <v>2625</v>
       </c>
       <c r="AT17" s="52" t="s">
-        <v>2657</v>
+        <v>2652</v>
       </c>
       <c r="AU17" s="36"/>
       <c r="AV17" s="36"/>
@@ -22922,7 +22926,7 @@
         <v>2408</v>
       </c>
       <c r="AQ18" s="36" t="s">
-        <v>2631</v>
+        <v>2626</v>
       </c>
       <c r="AR18" s="36"/>
       <c r="AS18" s="36"/>
@@ -23337,7 +23341,7 @@
     </row>
     <row r="30" spans="1:77" x14ac:dyDescent="0.15">
       <c r="A30" s="36" t="s">
-        <v>2692</v>
+        <v>2687</v>
       </c>
       <c r="B30" s="36">
         <v>-20</v>
@@ -23493,13 +23497,13 @@
         <v>16834</v>
       </c>
       <c r="G34" s="36" t="s">
-        <v>2709</v>
+        <v>2704</v>
       </c>
       <c r="K34" s="36" t="s">
-        <v>2704</v>
+        <v>2699</v>
       </c>
       <c r="L34" s="36" t="s">
-        <v>2706</v>
+        <v>2701</v>
       </c>
       <c r="T34" s="36">
         <v>1</v>
@@ -23508,16 +23512,16 @@
         <v>1</v>
       </c>
       <c r="AE34" s="36" t="s">
-        <v>2705</v>
+        <v>2700</v>
       </c>
       <c r="AF34" s="36">
         <v>37</v>
       </c>
       <c r="AG34" s="36" t="s">
-        <v>2707</v>
+        <v>2702</v>
       </c>
       <c r="AH34" s="36" t="s">
-        <v>2708</v>
+        <v>2703</v>
       </c>
       <c r="AI34" s="36">
         <v>255</v>
@@ -23527,7 +23531,7 @@
         <v>{dwID=32813,nLevel=1,nIcon=16834,szName="旗易伤",szNote="旗帜受损",col={255,153,204,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="损",nPriority=37,col="#FF99CCFF",colScreenHead="#FF99CC",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=1,key="大旗赛点·CD",},},},</v>
       </c>
       <c r="AO34" s="36" t="s">
-        <v>2713</v>
+        <v>2708</v>
       </c>
     </row>
     <row r="35" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -23541,13 +23545,13 @@
         <v>3451</v>
       </c>
       <c r="G35" s="36" t="s">
-        <v>2710</v>
+        <v>2705</v>
       </c>
       <c r="K35" s="36" t="s">
-        <v>2711</v>
+        <v>2706</v>
       </c>
       <c r="L35" s="36" t="s">
-        <v>2712</v>
+        <v>2707</v>
       </c>
       <c r="T35" s="36">
         <v>1</v>
@@ -23557,7 +23561,7 @@
         <v>{dwID=32812,nLevel=1,nIcon=3451,szName="损CD",szNote="据点大旗赛点CD",col={255,50,50,},[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=0,key="大旗赛点·CD",},},},</v>
       </c>
       <c r="AO35" s="36" t="s">
-        <v>2716</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="36" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -23583,7 +23587,7 @@
         <v>1</v>
       </c>
       <c r="AE36" s="36" t="s">
-        <v>2583</v>
+        <v>2579</v>
       </c>
       <c r="AF36" s="36">
         <v>11</v>
@@ -23605,10 +23609,10 @@
         <v>{dwID=31381,nLevel=1,szName="禁捡旗",szNote="无法拾取大旗",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="捡",nPriority=11,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=22928,nFrame=2,szName="【{$receiver}】·禁止捡旗",nTime="30,【{$receiver}】·禁止捡旗;32,【{$receiver}】·可以捡旗",nRefresh=1,key="经脉逆行·{$receiver}",},{nClass=2,nIcon=22928,nFrame=2,szName="【{$receiver}】·可以捡旗",nTime=5,key="经脉逆行·{$receiver}",},},},</v>
       </c>
       <c r="AO36" s="36" t="s">
-        <v>2732</v>
+        <v>2726</v>
       </c>
       <c r="AP36" s="36" t="s">
-        <v>2733</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="37" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -23790,7 +23794,7 @@
         <v>3</v>
       </c>
       <c r="AG40" s="36" t="s">
-        <v>2642</v>
+        <v>2637</v>
       </c>
       <c r="AI40" s="36">
         <v>0</v>
@@ -24030,23 +24034,23 @@
         <v>1</v>
       </c>
       <c r="G46" s="36" t="s">
-        <v>2590</v>
+        <v>2586</v>
       </c>
       <c r="I46" s="36">
         <v>1</v>
       </c>
       <c r="K46" s="36" t="s">
-        <v>2592</v>
+        <v>2588</v>
       </c>
       <c r="L46" s="36" t="s">
-        <v>2591</v>
+        <v>2587</v>
       </c>
       <c r="AN46" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=11561,nLevel=1,szName="据点内",nScrutinyType=1,szNote="判断是否在大旗附近",col={80,231,236,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=1272,nFrame=2,szName="离开据点·大旗重置",nTime=-1,key="离开据点·大旗重置",},},},</v>
+        <v>{dwID=11561,nLevel=1,szName="据点内",nScrutinyType=1,szNote="判断是否在大旗附近",col={80,231,236,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=1272,nFrame=2,szName="据点大旗·旗手提示",nTime=-1,key="据点大旗·旗手提示",},},},</v>
       </c>
       <c r="AO46" s="36" t="s">
-        <v>2593</v>
+        <v>2730</v>
       </c>
       <c r="AP46" s="39"/>
       <c r="AQ46" s="39"/>
@@ -24259,7 +24263,7 @@
         <v>1</v>
       </c>
       <c r="AE52" s="36" t="s">
-        <v>2583</v>
+        <v>2579</v>
       </c>
       <c r="AF52" s="36">
         <v>11</v>
@@ -24281,7 +24285,7 @@
         <v>{dwID=31381,nLevel=1,szName="禁捡旗",szNote="无法拾取大旗",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="捡",nPriority=11,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=2,szName="【{$receiver}】·禁止捡旗",nTime="30,【{$receiver}】·禁止捡旗;32,【{$receiver}】·可以捡旗",nRefresh=1,key="经脉逆行·{$receiver}",},{nClass=2,nIcon=13,nFrame=2,szName="【{$receiver}】·可以捡旗",nTime=5,key="经脉逆行·{$receiver}",},},},</v>
       </c>
       <c r="AO52" s="36" t="s">
-        <v>2695</v>
+        <v>2690</v>
       </c>
       <c r="AP52" s="36" t="s">
         <v>2391</v>
@@ -24466,7 +24470,7 @@
         <v>3</v>
       </c>
       <c r="AG56" s="36" t="s">
-        <v>2642</v>
+        <v>2637</v>
       </c>
       <c r="AI56" s="36">
         <v>0</v>
@@ -24736,23 +24740,23 @@
         <v>1</v>
       </c>
       <c r="G63" s="36" t="s">
-        <v>2590</v>
+        <v>2586</v>
       </c>
       <c r="I63" s="36">
         <v>1</v>
       </c>
       <c r="K63" s="36" t="s">
-        <v>2592</v>
+        <v>2588</v>
       </c>
       <c r="L63" s="36" t="s">
-        <v>2591</v>
+        <v>2587</v>
       </c>
       <c r="AN63" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=11561,nLevel=1,szName="据点内",nScrutinyType=1,szNote="判断是否在大旗附近",col={80,231,236,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=1272,nFrame=2,szName="离开据点·大旗重置",nTime=-1,key="离开据点·大旗重置",},},},</v>
+        <v>{dwID=11561,nLevel=1,szName="据点内",nScrutinyType=1,szNote="判断是否在大旗附近",col={80,231,236,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=1272,nFrame=2,szName="据点大旗·旗手提示",nTime=-1,key="据点大旗·旗手提示",},},},</v>
       </c>
       <c r="AO63" s="36" t="s">
-        <v>2593</v>
+        <v>2730</v>
       </c>
       <c r="AP63" s="39"/>
       <c r="AQ63" s="39"/>
@@ -24964,7 +24968,7 @@
         <v>1</v>
       </c>
       <c r="AE69" s="36" t="s">
-        <v>2583</v>
+        <v>2579</v>
       </c>
       <c r="AF69" s="36">
         <v>11</v>
@@ -24986,7 +24990,7 @@
         <v>{dwID=31381,nLevel=1,szName="禁捡旗",szNote="无法拾取大旗",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="捡",nPriority=11,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=2,szName="【{$receiver}】·禁止捡旗",nTime="30,【{$receiver}】·禁止捡旗;32,【{$receiver}】·可以捡旗",nRefresh=1,key="经脉逆行·{$receiver}",},{nClass=2,nIcon=13,nFrame=2,szName="【{$receiver}】·可以捡旗",nTime=5,key="经脉逆行·{$receiver}",},},},</v>
       </c>
       <c r="AO69" s="36" t="s">
-        <v>2695</v>
+        <v>2690</v>
       </c>
       <c r="AP69" s="36" t="s">
         <v>2391</v>
@@ -25171,7 +25175,7 @@
         <v>3</v>
       </c>
       <c r="AG73" s="36" t="s">
-        <v>2642</v>
+        <v>2637</v>
       </c>
       <c r="AI73" s="36">
         <v>0</v>
@@ -25441,23 +25445,23 @@
         <v>1</v>
       </c>
       <c r="G80" s="36" t="s">
-        <v>2590</v>
+        <v>2586</v>
       </c>
       <c r="I80" s="36">
         <v>1</v>
       </c>
       <c r="K80" s="36" t="s">
-        <v>2592</v>
+        <v>2588</v>
       </c>
       <c r="L80" s="36" t="s">
-        <v>2591</v>
+        <v>2587</v>
       </c>
       <c r="AN80" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=11561,nLevel=1,szName="据点内",nScrutinyType=1,szNote="判断是否在大旗附近",col={80,231,236,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=1272,nFrame=2,szName="离开据点·大旗重置",nTime=-1,key="离开据点·大旗重置",},},},</v>
+        <v>{dwID=11561,nLevel=1,szName="据点内",nScrutinyType=1,szNote="判断是否在大旗附近",col={80,231,236,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=1272,nFrame=2,szName="据点大旗·旗手提示",nTime=-1,key="据点大旗·旗手提示",},},},</v>
       </c>
       <c r="AO80" s="36" t="s">
-        <v>2593</v>
+        <v>2730</v>
       </c>
       <c r="AP80" s="39"/>
       <c r="AQ80" s="39"/>
@@ -25976,10 +25980,10 @@
         <v>{dwID=7242,nLevel=1,szNote="屹立不倒",[9]={},[8]={bScreenHead=true,},tCountdown={{nClass=8,nIcon=1537,nFrame=0,nTime="1,屹立不倒·{$sender}·释放剩余;9.5,屹立不倒·{$sender}·50减伤;34,屹立不倒·{$sender}·释放剩余;40.5,屹立不倒·{$sender}·释放延迟",szName="屹立不倒",nRefresh=0,key="屹立不倒",},{nClass=9,nIcon=1537,nFrame=0,nTime="9,屹立不倒·{$sender}·50减伤;33.5,屹立不倒·{$sender}·释放剩余;40,屹立不倒·{$sender}·释放延迟",szName="屹立不倒",nRefresh=1,key="屹立不倒",},},},</v>
       </c>
       <c r="Y4" s="36" t="s">
-        <v>2728</v>
+        <v>2722</v>
       </c>
       <c r="Z4" s="36" t="s">
-        <v>2727</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.15">
@@ -26138,7 +26142,7 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>2692</v>
+        <v>2687</v>
       </c>
       <c r="B5">
         <v>-20</v>
@@ -26159,7 +26163,7 @@
         <v>2146</v>
       </c>
       <c r="U6" t="s">
-        <v>2690</v>
+        <v>2685</v>
       </c>
       <c r="V6" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26177,7 +26181,7 @@
         <v>2146</v>
       </c>
       <c r="U7" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V7" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26195,7 +26199,7 @@
         <v>2146</v>
       </c>
       <c r="U8" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V8" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26213,7 +26217,7 @@
         <v>2146</v>
       </c>
       <c r="U9" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V9" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26231,7 +26235,7 @@
         <v>2146</v>
       </c>
       <c r="U10" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V10" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26249,7 +26253,7 @@
         <v>2146</v>
       </c>
       <c r="U11" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V11" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26267,7 +26271,7 @@
         <v>2148</v>
       </c>
       <c r="U12" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V12" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26285,7 +26289,7 @@
         <v>2148</v>
       </c>
       <c r="U13" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V13" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26303,7 +26307,7 @@
         <v>2148</v>
       </c>
       <c r="U14" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V14" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26321,7 +26325,7 @@
         <v>2148</v>
       </c>
       <c r="U15" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V15" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26339,7 +26343,7 @@
         <v>2148</v>
       </c>
       <c r="U16" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V16" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26357,7 +26361,7 @@
         <v>2148</v>
       </c>
       <c r="U17" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V17" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26375,7 +26379,7 @@
         <v>2148</v>
       </c>
       <c r="U18" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V18" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26393,7 +26397,7 @@
         <v>2148</v>
       </c>
       <c r="U19" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V19" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26411,7 +26415,7 @@
         <v>2140</v>
       </c>
       <c r="U20" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V20" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26429,7 +26433,7 @@
         <v>2140</v>
       </c>
       <c r="U21" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V21" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26447,7 +26451,7 @@
         <v>2140</v>
       </c>
       <c r="U22" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V22" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26465,7 +26469,7 @@
         <v>2140</v>
       </c>
       <c r="U23" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V23" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26483,7 +26487,7 @@
         <v>2140</v>
       </c>
       <c r="U24" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V24" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26501,7 +26505,7 @@
         <v>2140</v>
       </c>
       <c r="U25" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V25" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26519,7 +26523,7 @@
         <v>2140</v>
       </c>
       <c r="U26" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V26" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26537,7 +26541,7 @@
         <v>2140</v>
       </c>
       <c r="U27" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V27" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26555,7 +26559,7 @@
         <v>2140</v>
       </c>
       <c r="U28" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V28" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26573,7 +26577,7 @@
         <v>2140</v>
       </c>
       <c r="U29" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V29" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26591,7 +26595,7 @@
         <v>2140</v>
       </c>
       <c r="U30" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V30" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26609,7 +26613,7 @@
         <v>2140</v>
       </c>
       <c r="U31" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V31" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26627,7 +26631,7 @@
         <v>2140</v>
       </c>
       <c r="U32" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V32" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26645,7 +26649,7 @@
         <v>2140</v>
       </c>
       <c r="U33" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V33" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26663,7 +26667,7 @@
         <v>2140</v>
       </c>
       <c r="U34" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V34" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26681,7 +26685,7 @@
         <v>2140</v>
       </c>
       <c r="U35" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V35" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26699,7 +26703,7 @@
         <v>2140</v>
       </c>
       <c r="U36" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V36" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26849,7 +26853,7 @@
         <v>2071</v>
       </c>
       <c r="J43" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="O43" s="36">
         <v>1</v>
@@ -26882,7 +26886,7 @@
         <v>2070</v>
       </c>
       <c r="J44" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="O44" s="36">
         <v>1</v>
@@ -26969,7 +26973,7 @@
         <v>2072</v>
       </c>
       <c r="J47" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="P47" s="36">
         <v>1</v>
@@ -26993,7 +26997,7 @@
         <v>2073</v>
       </c>
       <c r="J48" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="P48" s="36">
         <v>1</v>
@@ -27017,7 +27021,7 @@
         <v>2065</v>
       </c>
       <c r="J49" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="P49" s="36">
         <v>1</v>
@@ -27041,7 +27045,7 @@
         <v>2066</v>
       </c>
       <c r="J50" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="P50" s="36">
         <v>1</v>
@@ -27107,13 +27111,13 @@
         <v>57</v>
       </c>
       <c r="I53" s="36" t="s">
-        <v>2696</v>
+        <v>2691</v>
       </c>
       <c r="P53" s="36">
         <v>1</v>
       </c>
       <c r="U53" s="36" t="s">
-        <v>2697</v>
+        <v>2692</v>
       </c>
       <c r="V53" s="36" t="str">
         <f t="shared" si="0"/>
@@ -27179,7 +27183,7 @@
         <v>1747</v>
       </c>
       <c r="J56" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="P56" s="36">
         <v>1</v>
@@ -27200,7 +27204,7 @@
         <v>1746</v>
       </c>
       <c r="J57" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="P57" s="36">
         <v>1</v>
@@ -27296,7 +27300,7 @@
         <v>2033</v>
       </c>
       <c r="J62" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="O62" s="36">
         <v>1</v>
@@ -27329,7 +27333,7 @@
         <v>2032</v>
       </c>
       <c r="J63" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="O63" s="36">
         <v>1</v>
@@ -27413,7 +27417,7 @@
         <v>52</v>
       </c>
       <c r="I66" s="36" t="s">
-        <v>2649</v>
+        <v>2644</v>
       </c>
       <c r="P66" s="36">
         <v>1</v>
@@ -27434,7 +27438,7 @@
         <v>1600</v>
       </c>
       <c r="J67" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="P67">
         <v>1</v>
@@ -27458,7 +27462,7 @@
         <v>1601</v>
       </c>
       <c r="J68" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="P68">
         <v>1</v>
@@ -27590,7 +27594,7 @@
         <v>1599</v>
       </c>
       <c r="J74" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="P74">
         <v>1</v>
@@ -27614,7 +27618,7 @@
         <v>1599</v>
       </c>
       <c r="J75" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="P75">
         <v>1</v>
@@ -27635,7 +27639,7 @@
         <v>47</v>
       </c>
       <c r="I76" s="36" t="s">
-        <v>2623</v>
+        <v>2618</v>
       </c>
       <c r="J76" s="36" t="s">
         <v>1667</v>
@@ -27735,7 +27739,7 @@
         <v>47</v>
       </c>
       <c r="I80" s="36" t="s">
-        <v>2622</v>
+        <v>2617</v>
       </c>
       <c r="J80" s="36" t="s">
         <v>1667</v>
@@ -27935,7 +27939,7 @@
         <v>47</v>
       </c>
       <c r="I88" t="s">
-        <v>2610</v>
+        <v>2605</v>
       </c>
       <c r="J88" s="36" t="s">
         <v>1667</v>
@@ -28109,7 +28113,7 @@
         <v>47</v>
       </c>
       <c r="I95" s="36" t="s">
-        <v>2612</v>
+        <v>2607</v>
       </c>
       <c r="J95" s="36" t="s">
         <v>1667</v>
@@ -28298,7 +28302,7 @@
         <v>47</v>
       </c>
       <c r="I102" s="36" t="s">
-        <v>2627</v>
+        <v>2622</v>
       </c>
       <c r="J102" s="36" t="s">
         <v>1667</v>
@@ -28325,7 +28329,7 @@
         <v>47</v>
       </c>
       <c r="I103" s="36" t="s">
-        <v>2626</v>
+        <v>2621</v>
       </c>
       <c r="J103" s="36" t="s">
         <v>1667</v>
@@ -28737,7 +28741,7 @@
         <v>1603</v>
       </c>
       <c r="J118" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="P118">
         <v>1</v>
@@ -28761,7 +28765,7 @@
         <v>1598</v>
       </c>
       <c r="J119" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="P119">
         <v>1</v>
@@ -28782,7 +28786,7 @@
         <v>47</v>
       </c>
       <c r="I120" t="s">
-        <v>2623</v>
+        <v>2618</v>
       </c>
       <c r="J120" s="36" t="s">
         <v>1667</v>
@@ -28807,7 +28811,7 @@
         <v>47</v>
       </c>
       <c r="I121" t="s">
-        <v>2625</v>
+        <v>2620</v>
       </c>
       <c r="J121" s="36" t="s">
         <v>1667</v>
@@ -28882,7 +28886,7 @@
         <v>47</v>
       </c>
       <c r="I124" s="36" t="s">
-        <v>2622</v>
+        <v>2617</v>
       </c>
       <c r="J124" s="36" t="s">
         <v>1667</v>
@@ -29082,7 +29086,7 @@
         <v>47</v>
       </c>
       <c r="I132" t="s">
-        <v>2624</v>
+        <v>2619</v>
       </c>
       <c r="J132" s="36" t="s">
         <v>1667</v>
@@ -29256,7 +29260,7 @@
         <v>47</v>
       </c>
       <c r="I139" t="s">
-        <v>2611</v>
+        <v>2606</v>
       </c>
       <c r="J139" s="36" t="s">
         <v>1667</v>
@@ -29843,7 +29847,7 @@
         <v>1692</v>
       </c>
       <c r="J160" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="P160">
         <v>1</v>
@@ -29867,7 +29871,7 @@
         <v>1690</v>
       </c>
       <c r="J161" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="P161">
         <v>1</v>
@@ -30065,7 +30069,7 @@
         <v>2316</v>
       </c>
       <c r="J170" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="P170" s="36">
         <v>1</v>
@@ -30125,7 +30129,7 @@
         <v>1692</v>
       </c>
       <c r="J173" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="P173">
         <v>1</v>
@@ -30149,7 +30153,7 @@
         <v>1690</v>
       </c>
       <c r="J174" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="P174">
         <v>1</v>
@@ -30395,7 +30399,7 @@
         <v>2315</v>
       </c>
       <c r="J185" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="P185" s="36">
         <v>1</v>
@@ -30464,7 +30468,7 @@
         <v>2142</v>
       </c>
       <c r="U188" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V188" s="36" t="str">
         <f t="shared" si="2"/>
@@ -30482,7 +30486,7 @@
         <v>2142</v>
       </c>
       <c r="U189" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V189" s="36" t="str">
         <f t="shared" si="2"/>
@@ -30500,7 +30504,7 @@
         <v>2142</v>
       </c>
       <c r="U190" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V190" s="36" t="str">
         <f t="shared" si="2"/>
@@ -30518,7 +30522,7 @@
         <v>2142</v>
       </c>
       <c r="U191" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V191" s="36" t="str">
         <f t="shared" si="2"/>
@@ -30536,7 +30540,7 @@
         <v>2158</v>
       </c>
       <c r="U192" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V192" s="36" t="str">
         <f t="shared" si="2"/>
@@ -30554,7 +30558,7 @@
         <v>2158</v>
       </c>
       <c r="U193" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V193" s="36" t="str">
         <f t="shared" si="2"/>
@@ -30572,7 +30576,7 @@
         <v>2158</v>
       </c>
       <c r="U194" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V194" s="36" t="str">
         <f t="shared" ref="V194:V257" si="3">IF(ISBLANK(B194)=FALSE,IF(ISBLANK(B193),"},["&amp;B194&amp;"]={","["&amp;B194&amp;"]={"),IF(AND(ISBLANK(B194),ISBLANK(D194),ISBLANK(C194),OR(ISBLANK(B193)=FALSE,ISBLANK(D193)=FALSE,ISBLANK(C193)=FALSE)),"},},}",IF(ISBLANK(C194),"","{dwID="&amp;C194&amp;","&amp;"nFrame="&amp;D194&amp;","&amp;IF(E194&gt;0,"nCount="&amp;E194&amp;",","")&amp;IF(F194&gt;0,"bAllLeave=true,","")&amp;IF(G194&lt;&gt;"","szName="""&amp;G194&amp;""",","")&amp;IF(H194&lt;&gt;"","tKungFu={"&amp;H194&amp;"},","")&amp;IF(I194&lt;&gt;"","szNote="""&amp;I194&amp;""",","")&amp;IF(J194&lt;&gt;"","col={"&amp;J194&amp;"},","")&amp;"[3]={"&amp;IF(K194&lt;&gt;"","tMark={"&amp;K194&amp;"},","")&amp;IF(L194&lt;&gt;"","szVoice="""&amp;L194&amp;""",","")&amp;IF(M194&gt;0,"bTeamChannel=true,","")&amp;IF(N194&gt;0,"bWhisperChannel=true,","")&amp;IF(O194&gt;0,"bCenterAlarm=true,","")&amp;IF(P194&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q194&lt;&gt;"","szVoice="""&amp;Q194&amp;""",","")&amp;IF(R194&gt;0,"bTeamChannel=true,","")&amp;IF(S194&gt;0,"bWhisperChannel=true,","")&amp;IF(T194&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U194&lt;&gt;"","aFocus={"&amp;U194&amp;"},","")&amp;IF(W194&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W194:ZZ194)&amp;"},","")&amp;"},")))</f>
@@ -30590,7 +30594,7 @@
         <v>2158</v>
       </c>
       <c r="U195" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V195" s="36" t="str">
         <f t="shared" si="3"/>
@@ -30608,7 +30612,7 @@
         <v>2158</v>
       </c>
       <c r="U196" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V196" s="36" t="str">
         <f t="shared" si="3"/>
@@ -30626,7 +30630,7 @@
         <v>2158</v>
       </c>
       <c r="U197" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V197" s="36" t="str">
         <f t="shared" si="3"/>
@@ -30656,7 +30660,7 @@
         <v>2316</v>
       </c>
       <c r="J199" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="P199" s="36">
         <v>1</v>
@@ -30881,7 +30885,7 @@
         <v>2315</v>
       </c>
       <c r="J209" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="P209" s="36">
         <v>1</v>
@@ -31226,7 +31230,7 @@
         <v>2147</v>
       </c>
       <c r="U224" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V224" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31244,7 +31248,7 @@
         <v>2147</v>
       </c>
       <c r="U225" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V225" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31262,7 +31266,7 @@
         <v>2147</v>
       </c>
       <c r="U226" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V226" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31280,7 +31284,7 @@
         <v>2147</v>
       </c>
       <c r="U227" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V227" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31298,7 +31302,7 @@
         <v>2149</v>
       </c>
       <c r="U228" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V228" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31316,7 +31320,7 @@
         <v>2149</v>
       </c>
       <c r="U229" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V229" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31334,7 +31338,7 @@
         <v>2149</v>
       </c>
       <c r="U230" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V230" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31352,7 +31356,7 @@
         <v>2141</v>
       </c>
       <c r="U231" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V231" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31370,7 +31374,7 @@
         <v>2141</v>
       </c>
       <c r="U232" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V232" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31388,7 +31392,7 @@
         <v>2141</v>
       </c>
       <c r="U233" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V233" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31406,7 +31410,7 @@
         <v>2141</v>
       </c>
       <c r="U234" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V234" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31424,7 +31428,7 @@
         <v>2141</v>
       </c>
       <c r="U235" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V235" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31442,7 +31446,7 @@
         <v>2141</v>
       </c>
       <c r="U236" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V236" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31460,7 +31464,7 @@
         <v>2141</v>
       </c>
       <c r="U237" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V237" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31478,7 +31482,7 @@
         <v>2141</v>
       </c>
       <c r="U238" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V238" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31496,7 +31500,7 @@
         <v>2141</v>
       </c>
       <c r="U239" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V239" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31514,7 +31518,7 @@
         <v>2141</v>
       </c>
       <c r="U240" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V240" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31532,7 +31536,7 @@
         <v>2159</v>
       </c>
       <c r="U241" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V241" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31550,7 +31554,7 @@
         <v>2141</v>
       </c>
       <c r="U242" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V242" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31580,7 +31584,7 @@
         <v>2316</v>
       </c>
       <c r="J244" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="P244" s="36">
         <v>1</v>
@@ -31787,7 +31791,7 @@
         <v>2157</v>
       </c>
       <c r="U253" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V253" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31805,7 +31809,7 @@
         <v>2143</v>
       </c>
       <c r="U254" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V254" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31823,7 +31827,7 @@
         <v>2143</v>
       </c>
       <c r="U255" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V255" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31841,7 +31845,7 @@
         <v>2143</v>
       </c>
       <c r="U256" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V256" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31859,7 +31863,7 @@
         <v>2143</v>
       </c>
       <c r="U257" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V257" s="36" t="str">
         <f t="shared" si="3"/>
@@ -32072,7 +32076,7 @@
         <v>2144</v>
       </c>
       <c r="U267" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V267" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32102,7 +32106,7 @@
         <v>2315</v>
       </c>
       <c r="J269" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="P269" s="36">
         <v>1</v>
@@ -32255,7 +32259,7 @@
         <v>2316</v>
       </c>
       <c r="J276" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="P276" s="36">
         <v>1</v>
@@ -32435,7 +32439,7 @@
         <v>2151</v>
       </c>
       <c r="U284" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V284" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32453,7 +32457,7 @@
         <v>2151</v>
       </c>
       <c r="U285" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V285" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32471,7 +32475,7 @@
         <v>2150</v>
       </c>
       <c r="U286" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V286" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32489,7 +32493,7 @@
         <v>2150</v>
       </c>
       <c r="U287" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V287" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32507,7 +32511,7 @@
         <v>2158</v>
       </c>
       <c r="U288" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V288" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32525,7 +32529,7 @@
         <v>2158</v>
       </c>
       <c r="U289" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V289" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32543,7 +32547,7 @@
         <v>2158</v>
       </c>
       <c r="U290" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V290" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32561,7 +32565,7 @@
         <v>2158</v>
       </c>
       <c r="U291" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V291" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32579,7 +32583,7 @@
         <v>2158</v>
       </c>
       <c r="U292" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V292" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32597,7 +32601,7 @@
         <v>2158</v>
       </c>
       <c r="U293" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V293" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32615,7 +32619,7 @@
         <v>2145</v>
       </c>
       <c r="U294" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V294" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32633,7 +32637,7 @@
         <v>2145</v>
       </c>
       <c r="U295" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V295" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32651,7 +32655,7 @@
         <v>2145</v>
       </c>
       <c r="U296" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V296" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32669,7 +32673,7 @@
         <v>2145</v>
       </c>
       <c r="U297" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V297" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32687,7 +32691,7 @@
         <v>2145</v>
       </c>
       <c r="U298" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V298" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32705,7 +32709,7 @@
         <v>2145</v>
       </c>
       <c r="U299" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V299" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32723,7 +32727,7 @@
         <v>2145</v>
       </c>
       <c r="U300" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V300" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32741,7 +32745,7 @@
         <v>2145</v>
       </c>
       <c r="U301" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V301" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32825,7 +32829,7 @@
         <v>2157</v>
       </c>
       <c r="U305" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V305" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32855,7 +32859,7 @@
         <v>2315</v>
       </c>
       <c r="J307" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="P307" s="36">
         <v>1</v>
@@ -32993,7 +32997,7 @@
         <v>2152</v>
       </c>
       <c r="U313" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V313" s="36" t="str">
         <f t="shared" si="4"/>
@@ -33011,7 +33015,7 @@
         <v>2159</v>
       </c>
       <c r="U314" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V314" s="36" t="str">
         <f t="shared" si="4"/>
@@ -33140,7 +33144,7 @@
         <v>1707</v>
       </c>
       <c r="J321" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="P321">
         <v>1</v>
@@ -33164,7 +33168,7 @@
         <v>1708</v>
       </c>
       <c r="J322" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="P322">
         <v>1</v>
@@ -33188,7 +33192,7 @@
         <v>2313</v>
       </c>
       <c r="J323" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="P323">
         <v>1</v>
@@ -33212,7 +33216,7 @@
         <v>2314</v>
       </c>
       <c r="J324" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="P324">
         <v>1</v>
@@ -33341,7 +33345,7 @@
         <v>1707</v>
       </c>
       <c r="J329" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="P329">
         <v>1</v>
@@ -33365,7 +33369,7 @@
         <v>1708</v>
       </c>
       <c r="J330" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="P330">
         <v>1</v>
@@ -33650,7 +33654,7 @@
         <v>1752</v>
       </c>
       <c r="U343" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V343" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33668,7 +33672,7 @@
         <v>1752</v>
       </c>
       <c r="U344" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V344" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33686,7 +33690,7 @@
         <v>1752</v>
       </c>
       <c r="U345" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V345" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33704,7 +33708,7 @@
         <v>1752</v>
       </c>
       <c r="U346" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V346" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33722,7 +33726,7 @@
         <v>1753</v>
       </c>
       <c r="U347" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V347" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33740,7 +33744,7 @@
         <v>1753</v>
       </c>
       <c r="U348" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V348" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33758,7 +33762,7 @@
         <v>1753</v>
       </c>
       <c r="U349" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V349" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33776,7 +33780,7 @@
         <v>1753</v>
       </c>
       <c r="U350" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V350" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33794,7 +33798,7 @@
         <v>1757</v>
       </c>
       <c r="U351" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V351" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33812,7 +33816,7 @@
         <v>1757</v>
       </c>
       <c r="U352" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V352" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33830,7 +33834,7 @@
         <v>1757</v>
       </c>
       <c r="U353" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V353" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33848,7 +33852,7 @@
         <v>1757</v>
       </c>
       <c r="U354" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V354" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33866,7 +33870,7 @@
         <v>1757</v>
       </c>
       <c r="U355" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V355" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33884,7 +33888,7 @@
         <v>1757</v>
       </c>
       <c r="U356" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V356" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33902,7 +33906,7 @@
         <v>1757</v>
       </c>
       <c r="U357" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V357" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33920,7 +33924,7 @@
         <v>1757</v>
       </c>
       <c r="U358" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V358" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33938,7 +33942,7 @@
         <v>1757</v>
       </c>
       <c r="U359" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V359" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33956,7 +33960,7 @@
         <v>1757</v>
       </c>
       <c r="U360" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V360" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33974,7 +33978,7 @@
         <v>1757</v>
       </c>
       <c r="U361" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V361" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33992,7 +33996,7 @@
         <v>1757</v>
       </c>
       <c r="U362" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V362" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34010,7 +34014,7 @@
         <v>1757</v>
       </c>
       <c r="U363" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V363" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34028,7 +34032,7 @@
         <v>1757</v>
       </c>
       <c r="U364" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V364" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34046,7 +34050,7 @@
         <v>1757</v>
       </c>
       <c r="U365" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V365" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34064,7 +34068,7 @@
         <v>1757</v>
       </c>
       <c r="U366" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V366" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34316,7 +34320,7 @@
         <v>1754</v>
       </c>
       <c r="U378" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V378" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34334,7 +34338,7 @@
         <v>1754</v>
       </c>
       <c r="U379" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V379" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34352,7 +34356,7 @@
         <v>1754</v>
       </c>
       <c r="U380" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V380" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34370,7 +34374,7 @@
         <v>1754</v>
       </c>
       <c r="U381" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V381" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34388,7 +34392,7 @@
         <v>1755</v>
       </c>
       <c r="U382" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V382" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34406,7 +34410,7 @@
         <v>1755</v>
       </c>
       <c r="U383" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V383" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34424,7 +34428,7 @@
         <v>1755</v>
       </c>
       <c r="U384" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V384" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34442,7 +34446,7 @@
         <v>1755</v>
       </c>
       <c r="U385" s="36" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="V385" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34460,7 +34464,7 @@
         <v>1756</v>
       </c>
       <c r="U386" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V386" s="36" t="str">
         <f t="shared" ref="V386:V404" si="6">IF(ISBLANK(B386)=FALSE,IF(ISBLANK(B385),"},["&amp;B386&amp;"]={","["&amp;B386&amp;"]={"),IF(AND(ISBLANK(B386),ISBLANK(D386),ISBLANK(C386),OR(ISBLANK(B385)=FALSE,ISBLANK(D385)=FALSE,ISBLANK(C385)=FALSE)),"},},}",IF(ISBLANK(C386),"","{dwID="&amp;C386&amp;","&amp;"nFrame="&amp;D386&amp;","&amp;IF(E386&gt;0,"nCount="&amp;E386&amp;",","")&amp;IF(F386&gt;0,"bAllLeave=true,","")&amp;IF(G386&lt;&gt;"","szName="""&amp;G386&amp;""",","")&amp;IF(H386&lt;&gt;"","tKungFu={"&amp;H386&amp;"},","")&amp;IF(I386&lt;&gt;"","szNote="""&amp;I386&amp;""",","")&amp;IF(J386&lt;&gt;"","col={"&amp;J386&amp;"},","")&amp;"[3]={"&amp;IF(K386&lt;&gt;"","tMark={"&amp;K386&amp;"},","")&amp;IF(L386&lt;&gt;"","szVoice="""&amp;L386&amp;""",","")&amp;IF(M386&gt;0,"bTeamChannel=true,","")&amp;IF(N386&gt;0,"bWhisperChannel=true,","")&amp;IF(O386&gt;0,"bCenterAlarm=true,","")&amp;IF(P386&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q386&lt;&gt;"","szVoice="""&amp;Q386&amp;""",","")&amp;IF(R386&gt;0,"bTeamChannel=true,","")&amp;IF(S386&gt;0,"bWhisperChannel=true,","")&amp;IF(T386&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U386&lt;&gt;"","aFocus={"&amp;U386&amp;"},","")&amp;IF(W386&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W386:ZZ386)&amp;"},","")&amp;"},")))</f>
@@ -34478,7 +34482,7 @@
         <v>1756</v>
       </c>
       <c r="U387" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V387" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34496,7 +34500,7 @@
         <v>1756</v>
       </c>
       <c r="U388" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V388" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34514,7 +34518,7 @@
         <v>1756</v>
       </c>
       <c r="U389" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V389" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34532,7 +34536,7 @@
         <v>1756</v>
       </c>
       <c r="U390" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V390" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34550,7 +34554,7 @@
         <v>1756</v>
       </c>
       <c r="U391" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V391" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34568,7 +34572,7 @@
         <v>1756</v>
       </c>
       <c r="U392" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V392" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34586,7 +34590,7 @@
         <v>1756</v>
       </c>
       <c r="U393" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V393" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34604,7 +34608,7 @@
         <v>1756</v>
       </c>
       <c r="U394" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V394" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34622,7 +34626,7 @@
         <v>1756</v>
       </c>
       <c r="U395" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V395" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34640,7 +34644,7 @@
         <v>1756</v>
       </c>
       <c r="U396" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V396" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34658,7 +34662,7 @@
         <v>1756</v>
       </c>
       <c r="U397" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V397" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34676,7 +34680,7 @@
         <v>1756</v>
       </c>
       <c r="U398" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V398" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34694,7 +34698,7 @@
         <v>1756</v>
       </c>
       <c r="U399" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V399" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34712,7 +34716,7 @@
         <v>1756</v>
       </c>
       <c r="U400" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V400" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34730,7 +34734,7 @@
         <v>1756</v>
       </c>
       <c r="U401" s="36" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="V401" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34842,40 +34846,40 @@
         <v>1421</v>
       </c>
       <c r="J1" s="36" t="s">
+        <v>2653</v>
+      </c>
+      <c r="K1" s="36" t="s">
+        <v>2654</v>
+      </c>
+      <c r="L1" s="36" t="s">
+        <v>2655</v>
+      </c>
+      <c r="M1" s="36" t="s">
+        <v>2656</v>
+      </c>
+      <c r="N1" s="36" t="s">
+        <v>2657</v>
+      </c>
+      <c r="O1" s="36" t="s">
         <v>2658</v>
       </c>
-      <c r="K1" s="36" t="s">
+      <c r="P1" s="36" t="s">
         <v>2659</v>
       </c>
-      <c r="L1" s="36" t="s">
+      <c r="Q1" s="36" t="s">
         <v>2660</v>
       </c>
-      <c r="M1" s="36" t="s">
+      <c r="R1" s="36" t="s">
         <v>2661</v>
       </c>
-      <c r="N1" s="36" t="s">
+      <c r="S1" s="36" t="s">
         <v>2662</v>
-      </c>
-      <c r="O1" s="36" t="s">
-        <v>2663</v>
-      </c>
-      <c r="P1" s="36" t="s">
-        <v>2664</v>
-      </c>
-      <c r="Q1" s="36" t="s">
-        <v>2665</v>
-      </c>
-      <c r="R1" s="36" t="s">
-        <v>2666</v>
-      </c>
-      <c r="S1" s="36" t="s">
-        <v>2667</v>
       </c>
       <c r="T1" s="36" t="s">
         <v>1526</v>
       </c>
       <c r="U1" s="36" t="s">
-        <v>2668</v>
+        <v>2663</v>
       </c>
       <c r="V1" s="36" t="s">
         <v>1422</v>
@@ -34883,7 +34887,7 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A2" s="36" t="s">
-        <v>2669</v>
+        <v>2664</v>
       </c>
       <c r="B2" s="36">
         <v>-19</v>
@@ -34901,13 +34905,13 @@
         <v>1561</v>
       </c>
       <c r="I3" s="36" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="N3" s="36">
         <v>1</v>
       </c>
       <c r="T3" s="36" t="s">
-        <v>2671</v>
+        <v>2666</v>
       </c>
       <c r="U3" s="36" t="str">
         <f t="shared" si="0"/>
@@ -34922,7 +34926,7 @@
         <v>1562</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="N4" s="36">
         <v>1</v>
@@ -34940,10 +34944,10 @@
         <v>7518</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>2672</v>
+        <v>2667</v>
       </c>
       <c r="I5" s="36" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="M5" s="36">
         <v>1</v>
@@ -34952,7 +34956,7 @@
         <v>1</v>
       </c>
       <c r="T5" s="36" t="s">
-        <v>2673</v>
+        <v>2668</v>
       </c>
       <c r="U5" s="36" t="str">
         <f t="shared" si="0"/>
@@ -34964,19 +34968,19 @@
         <v>5626</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>2674</v>
+        <v>2669</v>
       </c>
       <c r="I6" s="36" t="s">
+        <v>2665</v>
+      </c>
+      <c r="M6" s="36">
+        <v>1</v>
+      </c>
+      <c r="N6" s="36">
+        <v>1</v>
+      </c>
+      <c r="T6" s="36" t="s">
         <v>2670</v>
-      </c>
-      <c r="M6" s="36">
-        <v>1</v>
-      </c>
-      <c r="N6" s="36">
-        <v>1</v>
-      </c>
-      <c r="T6" s="36" t="s">
-        <v>2675</v>
       </c>
       <c r="U6" s="36" t="str">
         <f t="shared" si="0"/>
@@ -34985,7 +34989,7 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A7" s="36" t="s">
-        <v>2692</v>
+        <v>2687</v>
       </c>
       <c r="B7" s="36">
         <v>-20</v>
@@ -35003,13 +35007,13 @@
         <v>1978</v>
       </c>
       <c r="I8" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="N8" s="36">
         <v>1</v>
       </c>
       <c r="T8" s="36" t="s">
-        <v>2676</v>
+        <v>2671</v>
       </c>
       <c r="U8" s="36" t="str">
         <f t="shared" si="0"/>
@@ -35024,13 +35028,13 @@
         <v>1979</v>
       </c>
       <c r="I9" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="N9" s="36">
         <v>1</v>
       </c>
       <c r="T9" s="36" t="s">
-        <v>2676</v>
+        <v>2671</v>
       </c>
       <c r="U9" s="36" t="str">
         <f t="shared" si="0"/>
@@ -35045,7 +35049,7 @@
         <v>1550</v>
       </c>
       <c r="I10" s="36" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="M10" s="36">
         <v>1</v>
@@ -35069,7 +35073,7 @@
         <v>1552</v>
       </c>
       <c r="I11" s="36" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="M11" s="36">
         <v>1</v>
@@ -35105,7 +35109,7 @@
         <v>1550</v>
       </c>
       <c r="I13" s="36" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="M13" s="36">
         <v>1</v>
@@ -35129,7 +35133,7 @@
         <v>1552</v>
       </c>
       <c r="I14" s="36" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="M14" s="36">
         <v>1</v>
@@ -35165,7 +35169,7 @@
         <v>1550</v>
       </c>
       <c r="I16" s="36" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="M16" s="36">
         <v>1</v>
@@ -35189,7 +35193,7 @@
         <v>1552</v>
       </c>
       <c r="I17" s="36" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="M17" s="36">
         <v>1</v>
@@ -35222,10 +35226,10 @@
         <v>3444</v>
       </c>
       <c r="H19" s="36" t="s">
-        <v>2677</v>
+        <v>2672</v>
       </c>
       <c r="I19" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="M19" s="36">
         <v>1</v>
@@ -35246,10 +35250,10 @@
         <v>3443</v>
       </c>
       <c r="H20" s="36" t="s">
-        <v>2678</v>
+        <v>2673</v>
       </c>
       <c r="I20" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="M20" s="36">
         <v>1</v>
@@ -35270,10 +35274,10 @@
         <v>843</v>
       </c>
       <c r="H21" s="36" t="s">
-        <v>2679</v>
+        <v>2674</v>
       </c>
       <c r="I21" s="36" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="N21" s="36">
         <v>1</v>
@@ -35303,10 +35307,10 @@
         <v>843</v>
       </c>
       <c r="H23" s="36" t="s">
-        <v>2679</v>
+        <v>2674</v>
       </c>
       <c r="I23" s="36" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="N23" s="36">
         <v>1</v>
@@ -35324,10 +35328,10 @@
         <v>7662</v>
       </c>
       <c r="H24" s="36" t="s">
-        <v>2680</v>
+        <v>2675</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="M24" s="36">
         <v>1</v>
@@ -35348,10 +35352,10 @@
         <v>7663</v>
       </c>
       <c r="H25" s="36" t="s">
-        <v>2681</v>
+        <v>2676</v>
       </c>
       <c r="I25" s="36" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="M25" s="36">
         <v>1</v>
@@ -35372,10 +35376,10 @@
         <v>3444</v>
       </c>
       <c r="H26" s="36" t="s">
-        <v>2677</v>
+        <v>2672</v>
       </c>
       <c r="I26" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="M26" s="36">
         <v>1</v>
@@ -35396,10 +35400,10 @@
         <v>3443</v>
       </c>
       <c r="H27" s="36" t="s">
-        <v>2678</v>
+        <v>2673</v>
       </c>
       <c r="I27" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="M27" s="36">
         <v>1</v>
@@ -35435,10 +35439,10 @@
         <v>3445</v>
       </c>
       <c r="H29" s="36" t="s">
-        <v>2682</v>
+        <v>2677</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="M29" s="36">
         <v>1</v>
@@ -35459,10 +35463,10 @@
         <v>3442</v>
       </c>
       <c r="H30" s="36" t="s">
-        <v>2683</v>
+        <v>2678</v>
       </c>
       <c r="I30" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="M30" s="36">
         <v>1</v>
@@ -35483,10 +35487,10 @@
         <v>6474</v>
       </c>
       <c r="H31" s="36" t="s">
-        <v>2684</v>
+        <v>2679</v>
       </c>
       <c r="I31" s="36" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="T31" s="36" t="s">
         <v>1560</v>
@@ -35513,10 +35517,10 @@
         <v>1519</v>
       </c>
       <c r="H33" s="36" t="s">
-        <v>2685</v>
+        <v>2680</v>
       </c>
       <c r="I33" s="36" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="N33" s="36">
         <v>1</v>
@@ -35534,10 +35538,10 @@
         <v>7662</v>
       </c>
       <c r="H34" s="36" t="s">
-        <v>2680</v>
+        <v>2675</v>
       </c>
       <c r="I34" s="36" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="M34" s="36">
         <v>1</v>
@@ -35558,10 +35562,10 @@
         <v>7663</v>
       </c>
       <c r="H35" s="36" t="s">
-        <v>2681</v>
+        <v>2676</v>
       </c>
       <c r="I35" s="36" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="M35" s="36">
         <v>1</v>
@@ -35582,10 +35586,10 @@
         <v>3445</v>
       </c>
       <c r="H36" s="36" t="s">
-        <v>2682</v>
+        <v>2677</v>
       </c>
       <c r="I36" s="51" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="M36" s="36">
         <v>1</v>
@@ -35606,10 +35610,10 @@
         <v>3442</v>
       </c>
       <c r="H37" s="36" t="s">
-        <v>2683</v>
+        <v>2678</v>
       </c>
       <c r="I37" s="50" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="M37" s="36">
         <v>1</v>
@@ -35800,10 +35804,10 @@
         <v>2188</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>2718</v>
+        <v>2712</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>2723</v>
+        <v>2717</v>
       </c>
       <c r="M5" s="36" t="s">
         <v>1432</v>
@@ -35819,22 +35823,22 @@
         <v>{szContent="^本场攻防“(.-)”“(.-)·(.-)”已结束，(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分；(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分。请再接再厉！",szTarget="%",szNote="{$2}·{$3}·[{$4}·{$6}]:[{$7}·{$9}]",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2401,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=14,nIcon=2397,nFrame=-1,nTime=-1,szName="破阵点将·一",nRefresh=2,key="破阵点将·一",},{nClass=14,nIcon=2398,nFrame=-1,nTime=-1,szName="破阵点将·二",nRefresh=2,key="破阵点将·二",},{nClass=14,nIcon=2396,nFrame=-1,nTime=-2,szName="{$2}·{$3}",key="{$2}·{$3}",},{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}·{$6}分·{$7}·{$9}分;840,阶段·物资车2·出发剩余;850,阶段·物资车2·正在出发;900,阶段·首领出战·助战剩余;905,阶段·首领出战·助战结束;2700,阶段·破阵点将2·结算剩余;2702,阶段·破阵点将2·正在结算;2710,阶段·物资车3·正在出发;4500,阶段·本场攻防·结束剩余;4505,阶段·本场攻防·已经结束",szName="{$4}·{$6}分·{$7}·{$9}分",nRefresh=1,key="破阵点将·一",},{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}·{$6}分·{$7}·{$9}分;1800,阶段·本场攻防·结束剩余;1805,阶段·本场攻防·已经结束",szName="{$4}·{$6}分·{$7}·{$9}分",nRefresh=1,key="破阵点将·二",},},},</v>
       </c>
       <c r="W5" s="36" t="s">
-        <v>2719</v>
+        <v>2713</v>
       </c>
       <c r="X5" s="36" t="s">
-        <v>2722</v>
+        <v>2716</v>
       </c>
       <c r="Y5" s="36" t="s">
-        <v>2720</v>
+        <v>2714</v>
       </c>
       <c r="Z5" s="36" t="s">
-        <v>2721</v>
+        <v>2715</v>
       </c>
       <c r="AA5" s="36" t="s">
-        <v>2730</v>
+        <v>2724</v>
       </c>
       <c r="AB5" s="36" t="s">
-        <v>2731</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="6" spans="1:65" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -35842,10 +35846,10 @@
         <v>1431</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>2585</v>
+        <v>2581</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>2586</v>
+        <v>2582</v>
       </c>
       <c r="M6" s="36" t="s">
         <v>1432</v>
@@ -35866,10 +35870,10 @@
         <v>1431</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>2588</v>
+        <v>2584</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>2589</v>
+        <v>2585</v>
       </c>
       <c r="M7" s="36" t="s">
         <v>1432</v>
@@ -35903,7 +35907,7 @@
         <v>{szContent="([浩气恶人]-)前线战况焦灼，(.-)，有劳你速速前往支援！",szTarget="%",szNote="{$1}·{$2}·即将到达",col={255,255,100,},bReg=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="谢渊·月弄痕·减伤",nTime=-2,key="谢渊·月弄痕·减伤",},{nClass=14,nIcon=13,szName="谢渊·游驹·减伤",nTime=-2,key="谢渊·游驹·减伤",},{nClass=14,nIcon=13,szName="谢渊·穆玄英·减伤",nTime=-2,key="谢渊·穆玄英·减伤",},{nClass=14,nIcon=13,szName="谢渊·张桎辕·减伤",nTime=-2,key="谢渊·张桎辕·减伤",},{nClass=14,nIcon=13,szName="谢渊·司空仲平·减伤",nTime=-2,key="谢渊·司空仲平·减伤",},{nClass=14,nIcon=13,szName="王遗风·万兽王·减伤",nTime=-2,key="王遗风·万兽王·减伤",},{nClass=14,nIcon=13,szName="王遗风·莫雨·减伤",nTime=-2,key="王遗风·莫雨·减伤",},{nClass=14,nIcon=13,szName="王遗风·米丽古丽·减伤",nTime=-2,key="王遗风·米丽古丽·减伤",},{nClass=14,nIcon=13,szName="王遗风·陶寒亭·减伤",nTime=-2,key="王遗风·陶寒亭·减伤",},{nClass=14,nIcon=13,szName="王遗风·肖药儿·减伤",nTime=-2,key="王遗风·肖药儿·减伤",},},},</v>
       </c>
       <c r="W8" s="52" t="s">
-        <v>2655</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="9" spans="1:65" x14ac:dyDescent="0.15">
@@ -35973,7 +35977,7 @@
         <v>2552</v>
       </c>
       <c r="Y10" s="36" t="s">
-        <v>2699</v>
+        <v>2694</v>
       </c>
       <c r="Z10" s="36"/>
       <c r="AA10" s="36"/>
@@ -36009,7 +36013,7 @@
         <v>2555</v>
       </c>
       <c r="Y11" s="36" t="s">
-        <v>2700</v>
+        <v>2695</v>
       </c>
       <c r="Z11" s="36"/>
       <c r="AA11" s="36"/>
@@ -36041,7 +36045,7 @@
         <v>2555</v>
       </c>
       <c r="Y12" s="36" t="s">
-        <v>2701</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="13" spans="1:65" x14ac:dyDescent="0.15">
@@ -36081,10 +36085,10 @@
         <v>1508</v>
       </c>
       <c r="Z13" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="AA13" t="s">
-        <v>2703</v>
+        <v>2698</v>
       </c>
       <c r="AB13" s="36"/>
       <c r="AZ13" s="36"/>
@@ -36126,7 +36130,7 @@
         <v>2517</v>
       </c>
       <c r="Y14" s="36" t="s">
-        <v>2633</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="15" spans="1:65" x14ac:dyDescent="0.15">
@@ -36154,10 +36158,10 @@
         <v>{szContent="罢了，青山不改，绿水长流，后会有期！",szTarget="%",szNote="{$sender}·败退",col={255,255,100,},bSearch=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,szName="谢渊·{$sender}·减伤",nTime=-2,key="谢渊·{$sender}·减伤",},{nClass=14,nIcon=13,szName="王遗风·{$sender}·减伤",nTime=-2,key="王遗风·{$sender}·减伤",},},},</v>
       </c>
       <c r="W15" t="s">
-        <v>2637</v>
+        <v>2632</v>
       </c>
       <c r="X15" t="s">
-        <v>2638</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="16" spans="1:65" s="39" customFormat="1" x14ac:dyDescent="0.15">
@@ -36554,7 +36558,7 @@
         <v>1609</v>
       </c>
       <c r="L22" s="39" t="s">
-        <v>2613</v>
+        <v>2608</v>
       </c>
       <c r="M22" s="39" t="s">
         <v>1454</v>
@@ -36914,7 +36918,7 @@
         <v>1609</v>
       </c>
       <c r="J28" s="39" t="s">
-        <v>2613</v>
+        <v>2608</v>
       </c>
       <c r="K28" s="39" t="s">
         <v>1607</v>
@@ -37081,10 +37085,10 @@
         <v>1444</v>
       </c>
       <c r="D31" s="39" t="s">
-        <v>2616</v>
+        <v>2611</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>2617</v>
+        <v>2612</v>
       </c>
       <c r="F31" s="36" t="s">
         <v>1444</v>
@@ -37102,7 +37106,7 @@
         <v>1607</v>
       </c>
       <c r="L31" s="36" t="s">
-        <v>2618</v>
+        <v>2613</v>
       </c>
       <c r="M31" s="36" t="s">
         <v>1486</v>
@@ -37205,10 +37209,10 @@
         <v>1444</v>
       </c>
       <c r="D33" s="39" t="s">
-        <v>2621</v>
+        <v>2616</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>2620</v>
+        <v>2615</v>
       </c>
       <c r="F33" s="36" t="s">
         <v>1444</v>
@@ -37226,7 +37230,7 @@
         <v>1607</v>
       </c>
       <c r="L33" s="36" t="s">
-        <v>2619</v>
+        <v>2614</v>
       </c>
       <c r="M33" s="36" t="s">
         <v>1486</v>
@@ -37329,10 +37333,10 @@
         <v>1446</v>
       </c>
       <c r="D35" s="39" t="s">
-        <v>2614</v>
+        <v>2609</v>
       </c>
       <c r="E35" s="36" t="s">
-        <v>2615</v>
+        <v>2610</v>
       </c>
       <c r="F35" s="36" t="s">
         <v>1446</v>
@@ -37406,7 +37410,7 @@
         <v>1607</v>
       </c>
       <c r="J36" s="36" t="s">
-        <v>2618</v>
+        <v>2613</v>
       </c>
       <c r="K36" s="36" t="s">
         <v>1609</v>
@@ -37530,7 +37534,7 @@
         <v>1607</v>
       </c>
       <c r="J38" s="36" t="s">
-        <v>2619</v>
+        <v>2614</v>
       </c>
       <c r="K38" s="36" t="s">
         <v>1609</v>
@@ -37687,7 +37691,7 @@
         <v>2188</v>
       </c>
       <c r="D42" s="43" t="s">
-        <v>2584</v>
+        <v>2580</v>
       </c>
       <c r="E42" s="36" t="s">
         <v>2134</v>
@@ -37709,7 +37713,7 @@
         <v>2188</v>
       </c>
       <c r="D43" s="43" t="s">
-        <v>2587</v>
+        <v>2583</v>
       </c>
       <c r="E43" s="36" t="s">
         <v>2133</v>
@@ -37795,7 +37799,7 @@
         <v>{szContent="你获得了100点威名、100点战阶。",szNote="堆堆·助战首领",[14]={},tCountdown={{nClass=14,nIcon=13564,nFrame=1,szName="拾取间隔",nTime="300,助战堆·拾取物资·间隔剩余;310,助战堆·可以拾取物资了",nRefresh=1,key="首领拾取间隔",},},},</v>
       </c>
       <c r="W47" s="36" t="s">
-        <v>2651</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="48" spans="3:28" x14ac:dyDescent="0.15">
@@ -38981,7 +38985,7 @@
         <v>2525</v>
       </c>
       <c r="X68" s="36" t="s">
-        <v>2650</v>
+        <v>2645</v>
       </c>
       <c r="AA68" s="39"/>
     </row>
@@ -40180,7 +40184,7 @@
         <v>2525</v>
       </c>
       <c r="X89" s="36" t="s">
-        <v>2650</v>
+        <v>2645</v>
       </c>
       <c r="AA89" s="39"/>
     </row>
@@ -40230,7 +40234,7 @@
     </row>
     <row r="92" spans="1:38" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A92" s="36" t="s">
-        <v>2698</v>
+        <v>2693</v>
       </c>
       <c r="B92" s="36">
         <v>-21</v>
@@ -40357,7 +40361,7 @@
     </row>
     <row r="101" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A101" s="36" t="s">
-        <v>2692</v>
+        <v>2687</v>
       </c>
       <c r="B101" s="36">
         <v>-20</v>
@@ -40369,10 +40373,10 @@
     </row>
     <row r="102" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="D102" s="36" t="s">
-        <v>2597</v>
+        <v>2592</v>
       </c>
       <c r="E102" s="36" t="s">
-        <v>2598</v>
+        <v>2593</v>
       </c>
       <c r="M102" s="36" t="s">
         <v>2504</v>
@@ -40385,7 +40389,7 @@
         <v>{szContent="因侠士近来行为异常，逐鹿中原期间，禁止参与，你即将被传送到百溪！",szNote="据点攻防·禁止参与",col={255,50,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,bHold=true,nTime=30,szName="据点攻防·禁止参与本场",key="挂机检测",},},},</v>
       </c>
       <c r="W102" s="36" t="s">
-        <v>2599</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="103" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -40430,18 +40434,18 @@
       </c>
       <c r="V104" s="36" t="str">
         <f t="shared" si="23"/>
-        <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="离开据点·大旗重置",},},},</v>
+        <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="据点大旗·旗手提示",},},},</v>
       </c>
       <c r="W104" s="36" t="s">
-        <v>1909</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="105" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="D105" s="36" t="s">
-        <v>2714</v>
+        <v>2709</v>
       </c>
       <c r="E105" s="36" t="s">
-        <v>2717</v>
+        <v>2711</v>
       </c>
       <c r="M105" s="36" t="s">
         <v>1432</v>
@@ -40454,10 +40458,10 @@
       </c>
       <c r="V105" s="36" t="str">
         <f t="shared" si="23"/>
-        <v>{szContent="身负据点大旗，当心被夺！",szNote="[{$me}]·扛起大旗",col={255,255,100,},[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=8,szName="【{$me}】·拾取大旗",nTime=30,key="拾取大旗·{$me}",},},},</v>
+        <v>{szContent="身负据点大旗，当心被夺！",szNote="[{$me}]·扛起大旗",col={255,255,100,},[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=8,szName="【{$me}】·拾取大旗",nTime=30,key="据点大旗·旗手提示",},},},</v>
       </c>
       <c r="W105" s="36" t="s">
-        <v>2715</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="106" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -40465,10 +40469,10 @@
         <v>1431</v>
       </c>
       <c r="D106" s="36" t="s">
-        <v>2603</v>
+        <v>2598</v>
       </c>
       <c r="E106" s="36" t="s">
-        <v>2604</v>
+        <v>2599</v>
       </c>
       <c r="M106" s="36" t="s">
         <v>1432</v>
@@ -40484,19 +40488,19 @@
         <v>{szContent="^%[逐鹿中原%]%[(.-)%]：正在(.-)城门！",szTarget="%",szNote="[{$1}]·{$2}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,nFrame=5,nTime=-2,szName="打开·城门",nRefresh=10,key="打开·城门",},{nClass=14,nIcon=1465,nFrame=5,nTime=-2,szName="关闭·城门",nRefresh=10,key="关闭·城门",},{nClass=14,nIcon=13,nFrame=5,nTime=-2,szName="{$2}·城门",key="{$2}·城门",},{nClass=14,nIcon=2310,nFrame=1,nTime=10,szName="城门·打开·[{$1}]",nRefresh=10,key="打开·城门",},{nClass=14,nIcon=4839,nFrame=1,nTime=10,szName="城门·关闭·[{$1}]",nRefresh=10,key="关闭·城门",},},},</v>
       </c>
       <c r="W106" s="36" t="s">
-        <v>2605</v>
+        <v>2600</v>
       </c>
       <c r="X106" s="36" t="s">
-        <v>2606</v>
+        <v>2601</v>
       </c>
       <c r="Y106" s="36" t="s">
-        <v>2607</v>
+        <v>2602</v>
       </c>
       <c r="Z106" s="36" t="s">
-        <v>2608</v>
+        <v>2603</v>
       </c>
       <c r="AA106" s="36" t="s">
-        <v>2609</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="107" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -40588,10 +40592,10 @@
         <v>1431</v>
       </c>
       <c r="D110" s="36" t="s">
-        <v>2594</v>
+        <v>2589</v>
       </c>
       <c r="E110" s="36" t="s">
-        <v>2595</v>
+        <v>2590</v>
       </c>
       <c r="M110" s="36" t="s">
         <v>2504</v>
@@ -40607,7 +40611,7 @@
         <v>{szContent="您因消极怠战,扰乱阵营秩序，被阵营督查官请离当前地图，但同时给予250点贡献积分！",szTarget="%",szNote="阵营督查官·请离据点攻防",col={255,50,255,},[14]={bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,bHold=true,nTime=30,szName="阵营督查·请离据点攻防",key="挂机检测",},},},</v>
       </c>
       <c r="W110" s="36" t="s">
-        <v>2596</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="111" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -40631,7 +40635,7 @@
         <v>2436</v>
       </c>
       <c r="X111" s="36" t="s">
-        <v>2653</v>
+        <v>2648</v>
       </c>
     </row>
     <row r="112" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -40655,7 +40659,7 @@
         <v>2436</v>
       </c>
       <c r="X112" s="36" t="s">
-        <v>2654</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="113" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -40712,7 +40716,7 @@
         <v>{szContent="尔等鼠辈！谁敢与我一战！",szTarget="%",szNote="据点攻防·正式开始",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime="2,据点攻防·正式开始;10,建议关闭·江湖身份",nRefresh=2,key="阵营活动",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W114" s="36" t="s">
-        <v>2629</v>
+        <v>2624</v>
       </c>
       <c r="X114" s="40" t="s">
         <v>2412</v>
@@ -40797,7 +40801,7 @@
         <v>1582</v>
       </c>
       <c r="E118" t="s">
-        <v>2694</v>
+        <v>2689</v>
       </c>
       <c r="T118" s="36"/>
       <c r="V118" s="36" t="str">
@@ -40805,7 +40809,7 @@
         <v>{szContent="我竟然败给你们这群小辈！",szTarget="狼牙先锋首领",szNote="防冲突禁用·击退·狼牙先锋首领",[14]={},tCountdown={{nClass=-1,nIcon=3556,nFrame=1,szName="狼牙先锋首领·拾取掉落",nTime="10,狼牙先锋首领·已击退;300,狼牙先锋首领·拾取剩余;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=2,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W118" t="s">
-        <v>2652</v>
+        <v>2647</v>
       </c>
       <c r="X118" s="40" t="s">
         <v>2412</v>
@@ -40906,10 +40910,10 @@
       <c r="T123" s="36"/>
       <c r="V123" s="36" t="str">
         <f t="shared" si="23"/>
-        <v>{szContent="恶人谷老友们可在我这里传送到恶人谷！",szTarget="赵新宇",col={255,100,100,},[14]={},tCountdown={{nClass=0,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=2,nRefresh=600,key="赵新宇",},},},</v>
+        <v>{szContent="恶人谷老友们可在我这里传送到恶人谷！",szTarget="赵新宇",col={255,100,100,},[14]={},tCountdown={{nClass=-1,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=2,nRefresh=600,key="赵新宇",},},},</v>
       </c>
       <c r="W123" t="s">
-        <v>2579</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="124" spans="1:27" x14ac:dyDescent="0.15">
@@ -40925,10 +40929,10 @@
       <c r="T124" s="36"/>
       <c r="V124" s="36" t="str">
         <f t="shared" si="23"/>
-        <v>{szContent="浩气盟侠士们可在我这里传送到浩气盟！",szTarget="方超",col={100,100,255,},[14]={},tCountdown={{nClass=0,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=2,nRefresh=600,key="方超",},},},</v>
+        <v>{szContent="浩气盟侠士们可在我这里传送到浩气盟！",szTarget="方超",col={100,100,255,},[14]={},tCountdown={{nClass=-1,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=2,nRefresh=600,key="方超",},},},</v>
       </c>
       <c r="W124" t="s">
-        <v>2580</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="125" spans="1:27" x14ac:dyDescent="0.15">
@@ -41205,10 +41209,10 @@
       </c>
       <c r="V137" s="36" t="str">
         <f t="shared" si="27"/>
-        <v>{szContent="恶人谷老友们可在我这里传送到恶人谷！",szTarget="霸图",col={255,100,100,},[14]={},tCountdown={{nClass=0,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=2,nRefresh=600,key="霸图",},},},</v>
+        <v>{szContent="恶人谷老友们可在我这里传送到恶人谷！",szTarget="霸图",col={255,100,100,},[14]={},tCountdown={{nClass=-1,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=2,nRefresh=600,key="霸图",},},},</v>
       </c>
       <c r="W137" t="s">
-        <v>2581</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="138" spans="1:24" x14ac:dyDescent="0.15">
@@ -41223,10 +41227,10 @@
       </c>
       <c r="V138" s="36" t="str">
         <f t="shared" si="27"/>
-        <v>{szContent="浩气盟侠士们可在我这里传送到浩气盟！",szTarget="孙永恒",col={100,100,255,},[14]={},tCountdown={{nClass=0,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=2,nRefresh=600,key="孙永恒",},},},</v>
+        <v>{szContent="浩气盟侠士们可在我这里传送到浩气盟！",szTarget="孙永恒",col={100,100,255,},[14]={},tCountdown={{nClass=-1,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=2,nRefresh=600,key="孙永恒",},},},</v>
       </c>
       <c r="W138" t="s">
-        <v>2582</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="139" spans="1:24" x14ac:dyDescent="0.15">
@@ -41475,10 +41479,10 @@
       </c>
       <c r="V150" s="36" t="str">
         <f t="shared" si="27"/>
-        <v>{szContent="恶人谷老友们可在我这里传送到恶人谷！",szTarget="赵新宇",col={255,100,100,},[14]={},tCountdown={{nClass=0,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=2,nRefresh=600,key="赵新宇",},},},</v>
+        <v>{szContent="恶人谷老友们可在我这里传送到恶人谷！",szTarget="赵新宇",col={255,100,100,},[14]={},tCountdown={{nClass=-1,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=2,nRefresh=600,key="赵新宇",},},},</v>
       </c>
       <c r="W150" s="36" t="s">
-        <v>2579</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="151" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -41493,10 +41497,10 @@
       </c>
       <c r="V151" s="36" t="str">
         <f t="shared" si="27"/>
-        <v>{szContent="浩气盟侠士们可在我这里传送到浩气盟！",szTarget="方超",col={100,100,255,},[14]={},tCountdown={{nClass=0,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=2,nRefresh=600,key="方超",},},},</v>
+        <v>{szContent="浩气盟侠士们可在我这里传送到浩气盟！",szTarget="方超",col={100,100,255,},[14]={},tCountdown={{nClass=-1,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=2,nRefresh=600,key="方超",},},},</v>
       </c>
       <c r="W151" s="36" t="s">
-        <v>2580</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="152" spans="1:27" x14ac:dyDescent="0.15">
@@ -41625,10 +41629,10 @@
       </c>
       <c r="V157" s="36" t="str">
         <f t="shared" si="27"/>
-        <v>{szContent="恶人谷老友们可在我这里传送到恶人谷！",szTarget="霸图",col={255,100,100,},[14]={},tCountdown={{nClass=0,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=2,nRefresh=600,key="霸图",},},},</v>
+        <v>{szContent="恶人谷老友们可在我这里传送到恶人谷！",szTarget="霸图",col={255,100,100,},[14]={},tCountdown={{nClass=-1,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=2,nRefresh=600,key="霸图",},},},</v>
       </c>
       <c r="W157" s="36" t="s">
-        <v>2581</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="158" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -41643,10 +41647,10 @@
       </c>
       <c r="V158" s="36" t="str">
         <f t="shared" si="27"/>
-        <v>{szContent="浩气盟侠士们可在我这里传送到浩气盟！",szTarget="孙永恒",col={100,100,255,},[14]={},tCountdown={{nClass=0,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=2,nRefresh=600,key="孙永恒",},},},</v>
+        <v>{szContent="浩气盟侠士们可在我这里传送到浩气盟！",szTarget="孙永恒",col={100,100,255,},[14]={},tCountdown={{nClass=-1,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=2,nRefresh=600,key="孙永恒",},},},</v>
       </c>
       <c r="W158" s="36" t="s">
-        <v>2582</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="159" spans="1:27" x14ac:dyDescent="0.15">
@@ -42334,7 +42338,7 @@
         <v>1</v>
       </c>
       <c r="T3" s="36" t="str">
-        <f t="shared" ref="T3:T72" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(L3),ISBLANK(M3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(L2)=FALSE,ISBLANK(M2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(K3&lt;&gt;"","col={"&amp;K3&amp;"},","")&amp;IF(L3&gt;0,"bSearch=true,","")&amp;IF(M3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N3&gt;0,"szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bTeamChannel=true,","")&amp;IF(P3&gt;0,"bWhisperChannel=true,","")&amp;IF(Q3&gt;0,"bCenterAlarm=true,","")&amp;IF(R3&gt;0,"bScreenHead=true,","")&amp;IF(S3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U3:AAF3)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="T3:T66" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(L3),ISBLANK(M3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(L2)=FALSE,ISBLANK(M2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(K3&lt;&gt;"","col={"&amp;K3&amp;"},","")&amp;IF(L3&gt;0,"bSearch=true,","")&amp;IF(M3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N3&gt;0,"szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bTeamChannel=true,","")&amp;IF(P3&gt;0,"bWhisperChannel=true,","")&amp;IF(Q3&gt;0,"bCenterAlarm=true,","")&amp;IF(R3&gt;0,"bScreenHead=true,","")&amp;IF(S3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U3:AAF3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="[团队监控]数据加载成功",szNote="关闭刷马等计时条",bSearch=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},},},</v>
       </c>
       <c r="U3" s="40" t="s">
@@ -42346,10 +42350,10 @@
     </row>
     <row r="4" spans="1:72" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C4" s="36" t="s">
-        <v>2634</v>
+        <v>2629</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>2635</v>
+        <v>2630</v>
       </c>
       <c r="K4" s="36" t="s">
         <v>1748</v>
@@ -42359,7 +42363,7 @@
         <v>{szContent="驿马快报！本周浩气盟和恶人谷最终战为平手，未分胜负！\n",szNote="阵营事件·本周战平",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13354,nFrame=4,szName="阵营事件·本周战平",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U4" s="36" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="5" spans="1:72" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -42416,13 +42420,13 @@
         <v>2401</v>
       </c>
       <c r="V7" s="36" t="s">
-        <v>2726</v>
+        <v>2720</v>
       </c>
       <c r="W7" s="36" t="s">
-        <v>2724</v>
+        <v>2718</v>
       </c>
       <c r="X7" s="36" t="s">
-        <v>2725</v>
+        <v>2719</v>
       </c>
       <c r="Y7" s="36" t="s">
         <v>2113</v>
@@ -42437,7 +42441,7 @@
         <v>1941</v>
       </c>
       <c r="AC7" s="52" t="s">
-        <v>2656</v>
+        <v>2651</v>
       </c>
       <c r="AD7" s="36"/>
       <c r="AE7" s="36"/>
@@ -42497,13 +42501,13 @@
         <v>2400</v>
       </c>
       <c r="V8" s="36" t="s">
-        <v>2726</v>
+        <v>2720</v>
       </c>
       <c r="W8" s="36" t="s">
-        <v>2724</v>
+        <v>2718</v>
       </c>
       <c r="X8" s="36" t="s">
-        <v>2725</v>
+        <v>2719</v>
       </c>
       <c r="Y8" s="36" t="s">
         <v>2113</v>
@@ -42518,7 +42522,7 @@
         <v>1941</v>
       </c>
       <c r="AC8" s="52" t="s">
-        <v>2656</v>
+        <v>2651</v>
       </c>
       <c r="AD8" s="36"/>
       <c r="AE8" s="36"/>
@@ -42596,13 +42600,13 @@
         <v>2398</v>
       </c>
       <c r="Z9" s="36" t="s">
-        <v>2726</v>
+        <v>2720</v>
       </c>
       <c r="AA9" s="36" t="s">
-        <v>2724</v>
+        <v>2718</v>
       </c>
       <c r="AB9" s="36" t="s">
-        <v>2725</v>
+        <v>2719</v>
       </c>
       <c r="AC9" s="36" t="s">
         <v>2113</v>
@@ -42617,7 +42621,7 @@
         <v>1941</v>
       </c>
       <c r="AG9" s="40" t="s">
-        <v>2656</v>
+        <v>2651</v>
       </c>
       <c r="AH9" s="36"/>
       <c r="AI9" s="36"/>
@@ -42936,7 +42940,7 @@
         <v>2414</v>
       </c>
       <c r="X18" s="36" t="s">
-        <v>2632</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="19" spans="1:72" x14ac:dyDescent="0.15">
@@ -42957,7 +42961,7 @@
         <v>{szContent="王遗风已率恶人谷众首领抵达浩气盟，请各位恶人谷侠士速到浩气盟支援。浩气盟侠士也请速回浩气盟防御！\n",szNote="主场攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2702,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5402,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=30,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="速战速决",nTime=-2,key="速战速决",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U19" s="36" t="s">
-        <v>2729</v>
+        <v>2723</v>
       </c>
       <c r="V19" s="36" t="s">
         <v>2418</v>
@@ -42969,7 +42973,7 @@
         <v>2414</v>
       </c>
       <c r="Y19" s="36" t="s">
-        <v>2632</v>
+        <v>2627</v>
       </c>
       <c r="Z19" s="36"/>
       <c r="AA19" s="36"/>
@@ -43125,7 +43129,7 @@
         <v>2414</v>
       </c>
       <c r="X22" s="36" t="s">
-        <v>2632</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="23" spans="1:72" x14ac:dyDescent="0.15">
@@ -43146,7 +43150,7 @@
         <v>{szContent="谢渊已率浩气盟众首领抵达恶人谷，请各位浩气盟侠士速到恶人谷支援。恶人谷侠士也请速回恶人谷防御！\n",szNote="主场攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2702,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5402,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=30,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="速战速决",nTime=-2,key="速战速决",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U23" s="36" t="s">
-        <v>2729</v>
+        <v>2723</v>
       </c>
       <c r="V23" s="36" t="s">
         <v>2418</v>
@@ -43158,7 +43162,7 @@
         <v>2414</v>
       </c>
       <c r="Y23" s="36" t="s">
-        <v>2632</v>
+        <v>2627</v>
       </c>
       <c r="Z23" s="36"/>
       <c r="AA23" s="36"/>
@@ -43208,10 +43212,10 @@
     </row>
     <row r="25" spans="1:72" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C25" s="36" t="s">
-        <v>2600</v>
+        <v>2595</v>
       </c>
       <c r="D25" s="36" t="s">
-        <v>2601</v>
+        <v>2596</v>
       </c>
       <c r="K25" s="36" t="s">
         <v>1432</v>
@@ -43224,7 +43228,7 @@
         <v>{szContent="(.-)【(.-)】帮会的(.-)大侠成功护送祭祀物资到达(.-)据点，该据点将士备受鼓舞，战意高昂，战时必将固若金汤！",szNote="祭天·{$1}·[{$2}]·{$4}",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=8838,nFrame=1,szName="{$1}祭天·[{$2}]·{$4}",nTime=30,key="通用事件",},},},</v>
       </c>
       <c r="U25" s="36" t="s">
-        <v>2602</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="26" spans="1:72" x14ac:dyDescent="0.15">
@@ -43361,7 +43365,7 @@
     </row>
     <row r="34" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A34" s="36" t="s">
-        <v>2698</v>
+        <v>2693</v>
       </c>
       <c r="B34" s="36">
         <v>-21</v>
@@ -43472,7 +43476,7 @@
         <v>1438</v>
       </c>
       <c r="T38" s="36" t="str">
-        <f t="shared" ref="T38:T40" si="1">IF(ISBLANK(B38)=FALSE,IF(ISBLANK(B37),"},["&amp;B38&amp;"]={","["&amp;B38&amp;"]={"),IF(AND(ISBLANK(B38),ISBLANK(C38),ISBLANK(L38),ISBLANK(M38),OR(ISBLANK(B37)=FALSE,ISBLANK(C37)=FALSE,ISBLANK(L37)=FALSE,ISBLANK(M37)=FALSE)),"},},}",IF(ISBLANK(C38),"","{szContent="""&amp;C38&amp;""","&amp;IF(D38&lt;&gt;"","szNote="""&amp;D38&amp;""",","")&amp;IF(K38&lt;&gt;"","col={"&amp;K38&amp;"},","")&amp;IF(L38&gt;0,"bSearch=true,","")&amp;IF(M38&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N38&gt;0,"szVoice="""&amp;N38&amp;""",","")&amp;IF(O38&gt;0,"bTeamChannel=true,","")&amp;IF(P38&gt;0,"bWhisperChannel=true,","")&amp;IF(Q38&gt;0,"bCenterAlarm=true,","")&amp;IF(R38&gt;0,"bScreenHead=true,","")&amp;IF(S38&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U38&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U38:AAF38)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="0"/>
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U38" s="36" t="s">
@@ -43490,7 +43494,7 @@
         <v>1565</v>
       </c>
       <c r="T39" s="36" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U39" s="36" t="s">
@@ -43511,7 +43515,7 @@
         <v>1</v>
       </c>
       <c r="T40" s="36" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U40" s="36" t="s">
@@ -43529,7 +43533,7 @@
         <v>1432</v>
       </c>
       <c r="T41" s="36" t="str">
-        <f>IF(ISBLANK(B41)=FALSE,IF(ISBLANK(B37),"},["&amp;B41&amp;"]={","["&amp;B41&amp;"]={"),IF(AND(ISBLANK(B41),ISBLANK(C41),ISBLANK(L41),ISBLANK(M41),OR(ISBLANK(B37)=FALSE,ISBLANK(C37)=FALSE,ISBLANK(L37)=FALSE,ISBLANK(M37)=FALSE)),"},},}",IF(ISBLANK(C41),"","{szContent="""&amp;C41&amp;""","&amp;IF(D41&lt;&gt;"","szNote="""&amp;D41&amp;""",","")&amp;IF(K41&lt;&gt;"","col={"&amp;K41&amp;"},","")&amp;IF(L41&gt;0,"bSearch=true,","")&amp;IF(M41&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N41&gt;0,"szVoice="""&amp;N41&amp;""",","")&amp;IF(O41&gt;0,"bTeamChannel=true,","")&amp;IF(P41&gt;0,"bWhisperChannel=true,","")&amp;IF(Q41&gt;0,"bCenterAlarm=true,","")&amp;IF(R41&gt;0,"bScreenHead=true,","")&amp;IF(S41&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U41&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U41:AAF41)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="0"/>
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U41" s="36" t="s">
@@ -43567,7 +43571,7 @@
         <v>1432</v>
       </c>
       <c r="T43" s="36" t="str">
-        <f t="shared" ref="T43" si="2">IF(ISBLANK(B43)=FALSE,IF(ISBLANK(B42),"},["&amp;B43&amp;"]={","["&amp;B43&amp;"]={"),IF(AND(ISBLANK(B43),ISBLANK(C43),ISBLANK(L43),ISBLANK(M43),OR(ISBLANK(B42)=FALSE,ISBLANK(C42)=FALSE,ISBLANK(L42)=FALSE,ISBLANK(M42)=FALSE)),"},},}",IF(ISBLANK(C43),"","{szContent="""&amp;C43&amp;""","&amp;IF(D43&lt;&gt;"","szNote="""&amp;D43&amp;""",","")&amp;IF(K43&lt;&gt;"","col={"&amp;K43&amp;"},","")&amp;IF(L43&gt;0,"bSearch=true,","")&amp;IF(M43&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N43&gt;0,"szVoice="""&amp;N43&amp;""",","")&amp;IF(O43&gt;0,"bTeamChannel=true,","")&amp;IF(P43&gt;0,"bWhisperChannel=true,","")&amp;IF(Q43&gt;0,"bCenterAlarm=true,","")&amp;IF(R43&gt;0,"bScreenHead=true,","")&amp;IF(S43&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U43&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U43:AAF43)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="0"/>
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U43" s="36" t="s">
@@ -43585,7 +43589,7 @@
         <v>1432</v>
       </c>
       <c r="T44" s="36" t="str">
-        <f>IF(ISBLANK(B44)=FALSE,IF(ISBLANK(B42),"},["&amp;B44&amp;"]={","["&amp;B44&amp;"]={"),IF(AND(ISBLANK(B44),ISBLANK(C44),ISBLANK(L44),ISBLANK(M44),OR(ISBLANK(B42)=FALSE,ISBLANK(C42)=FALSE,ISBLANK(L42)=FALSE,ISBLANK(M42)=FALSE)),"},},}",IF(ISBLANK(C44),"","{szContent="""&amp;C44&amp;""","&amp;IF(D44&lt;&gt;"","szNote="""&amp;D44&amp;""",","")&amp;IF(K44&lt;&gt;"","col={"&amp;K44&amp;"},","")&amp;IF(L44&gt;0,"bSearch=true,","")&amp;IF(M44&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N44&gt;0,"szVoice="""&amp;N44&amp;""",","")&amp;IF(O44&gt;0,"bTeamChannel=true,","")&amp;IF(P44&gt;0,"bWhisperChannel=true,","")&amp;IF(Q44&gt;0,"bCenterAlarm=true,","")&amp;IF(R44&gt;0,"bScreenHead=true,","")&amp;IF(S44&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U44&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U44:AAF44)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="0"/>
         <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U44" s="36" t="s">
@@ -44072,7 +44076,7 @@
         <v>1565</v>
       </c>
       <c r="T67" s="36" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="T67:T130" si="1">IF(ISBLANK(B67)=FALSE,IF(ISBLANK(B66),"},["&amp;B67&amp;"]={","["&amp;B67&amp;"]={"),IF(AND(ISBLANK(B67),ISBLANK(C67),ISBLANK(L67),ISBLANK(M67),OR(ISBLANK(B66)=FALSE,ISBLANK(C66)=FALSE,ISBLANK(L66)=FALSE,ISBLANK(M66)=FALSE)),"},},}",IF(ISBLANK(C67),"","{szContent="""&amp;C67&amp;""","&amp;IF(D67&lt;&gt;"","szNote="""&amp;D67&amp;""",","")&amp;IF(K67&lt;&gt;"","col={"&amp;K67&amp;"},","")&amp;IF(L67&gt;0,"bSearch=true,","")&amp;IF(M67&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N67&gt;0,"szVoice="""&amp;N67&amp;""",","")&amp;IF(O67&gt;0,"bTeamChannel=true,","")&amp;IF(P67&gt;0,"bWhisperChannel=true,","")&amp;IF(Q67&gt;0,"bCenterAlarm=true,","")&amp;IF(R67&gt;0,"bScreenHead=true,","")&amp;IF(S67&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U67&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U67:AAF67)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U67" s="36" t="s">
@@ -44087,7 +44091,7 @@
         <v>1432</v>
       </c>
       <c r="T68" s="36" t="str">
-        <f>IF(ISBLANK(B68)=FALSE,IF(ISBLANK(B65),"},["&amp;B68&amp;"]={","["&amp;B68&amp;"]={"),IF(AND(ISBLANK(B68),ISBLANK(C68),ISBLANK(L68),ISBLANK(M68),OR(ISBLANK(B65)=FALSE,ISBLANK(C65)=FALSE,ISBLANK(L65)=FALSE,ISBLANK(M65)=FALSE)),"},},}",IF(ISBLANK(C68),"","{szContent="""&amp;C68&amp;""","&amp;IF(D68&lt;&gt;"","szNote="""&amp;D68&amp;""",","")&amp;IF(K68&lt;&gt;"","col={"&amp;K68&amp;"},","")&amp;IF(L68&gt;0,"bSearch=true,","")&amp;IF(M68&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N68&gt;0,"szVoice="""&amp;N68&amp;""",","")&amp;IF(O68&gt;0,"bTeamChannel=true,","")&amp;IF(P68&gt;0,"bWhisperChannel=true,","")&amp;IF(Q68&gt;0,"bCenterAlarm=true,","")&amp;IF(R68&gt;0,"bScreenHead=true,","")&amp;IF(S68&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U68&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U68:AAF68)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="1"/>
         <v>{szContent="本场贡献值进入前1200名，额外获得3000威名，可通过邮件领取\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=6,szName="攻防进入前1200名",nTime=10,key="阵营活动",},},},</v>
       </c>
       <c r="U68" t="s">
@@ -44105,7 +44109,7 @@
         <v>1432</v>
       </c>
       <c r="T69" s="36" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=20,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=20,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=20,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=20,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=20,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=20,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=20,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=20,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=20,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="U69" s="36" t="s">
@@ -44132,7 +44136,7 @@
         <v>1</v>
       </c>
       <c r="T70" s="36" t="str">
-        <f>IF(ISBLANK(B70)=FALSE,IF(ISBLANK(B69),"},["&amp;B70&amp;"]={","["&amp;B70&amp;"]={"),IF(AND(ISBLANK(B70),ISBLANK(C70),ISBLANK(L70),ISBLANK(M70),OR(ISBLANK(B69)=FALSE,ISBLANK(C69)=FALSE,ISBLANK(L69)=FALSE,ISBLANK(M69)=FALSE)),"},},}",IF(ISBLANK(C70),"","{szContent="""&amp;C70&amp;""","&amp;IF(D70&lt;&gt;"","szNote="""&amp;D70&amp;""",","")&amp;IF(K70&lt;&gt;"","col={"&amp;K70&amp;"},","")&amp;IF(L70&gt;0,"bSearch=true,","")&amp;IF(M70&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N70&gt;0,"szVoice="""&amp;N70&amp;""",","")&amp;IF(O70&gt;0,"bTeamChannel=true,","")&amp;IF(P70&gt;0,"bWhisperChannel=true,","")&amp;IF(Q70&gt;0,"bCenterAlarm=true,","")&amp;IF(R70&gt;0,"bScreenHead=true,","")&amp;IF(S70&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U70&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U70:AAF70)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="1"/>
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U70" s="36" t="s">
@@ -44150,7 +44154,7 @@
         <v>1432</v>
       </c>
       <c r="T71" s="36" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=13,szName="狼牙先锋首领",nTime=0,key="狼牙先锋首领",},{nClass=20,nIcon=13,szName="离开据点·大旗重置",nTime=0,key="离开据点·大旗重置",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U71" t="s">
@@ -44174,7 +44178,7 @@
         <v>1432</v>
       </c>
       <c r="T72" s="36" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U72" s="36" t="s">
@@ -44189,13 +44193,13 @@
         <v>1573</v>
       </c>
       <c r="D73" t="s">
-        <v>2693</v>
+        <v>2688</v>
       </c>
       <c r="K73" t="s">
         <v>1432</v>
       </c>
       <c r="T73" s="36" t="str">
-        <f t="shared" ref="T73:T136" si="3">IF(ISBLANK(B73)=FALSE,IF(ISBLANK(B72),"},["&amp;B73&amp;"]={","["&amp;B73&amp;"]={"),IF(AND(ISBLANK(B73),ISBLANK(C73),ISBLANK(L73),ISBLANK(M73),OR(ISBLANK(B72)=FALSE,ISBLANK(C72)=FALSE,ISBLANK(L72)=FALSE,ISBLANK(M72)=FALSE)),"},},}",IF(ISBLANK(C73),"","{szContent="""&amp;C73&amp;""","&amp;IF(D73&lt;&gt;"","szNote="""&amp;D73&amp;""",","")&amp;IF(K73&lt;&gt;"","col={"&amp;K73&amp;"},","")&amp;IF(L73&gt;0,"bSearch=true,","")&amp;IF(M73&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N73&gt;0,"szVoice="""&amp;N73&amp;""",","")&amp;IF(O73&gt;0,"bTeamChannel=true,","")&amp;IF(P73&gt;0,"bWhisperChannel=true,","")&amp;IF(Q73&gt;0,"bCenterAlarm=true,","")&amp;IF(R73&gt;0,"bScreenHead=true,","")&amp;IF(S73&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U73&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U73:AAF73)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="1"/>
         <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·5分钟·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U73" s="36" t="s">
@@ -44216,11 +44220,11 @@
         <v>1432</v>
       </c>
       <c r="T74" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="前线据点之争已经打响，争夺正式开始，沙盘地图（CTRL + M）绘有详细战略意图，谁将称霸中原，我们拭目以待！\n",szNote="据点攻防·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime=10,key="阵营活动",},},},</v>
       </c>
       <c r="U74" t="s">
-        <v>2628</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="75" spans="1:26" x14ac:dyDescent="0.15">
@@ -44231,7 +44235,7 @@
         <v>1432</v>
       </c>
       <c r="T75" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·分线·开启",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
       <c r="U75" t="s">
@@ -44240,13 +44244,13 @@
     </row>
     <row r="76" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A76" s="36" t="s">
-        <v>2692</v>
+        <v>2687</v>
       </c>
       <c r="B76" s="36">
         <v>-20</v>
       </c>
       <c r="T76" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>},[-20]={</v>
       </c>
     </row>
@@ -44264,7 +44268,7 @@
         <v>1</v>
       </c>
       <c r="T77" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U77" s="36" t="s">
@@ -44291,7 +44295,7 @@
         <v>-3</v>
       </c>
       <c r="T78" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>},[-3]={</v>
       </c>
     </row>
@@ -44303,7 +44307,7 @@
         <v>1438</v>
       </c>
       <c r="T79" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往恶人谷地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=3,szName="主战场·恶人谷",nTime="1,阵营攻防·开始排队·恶人谷;10,阵营攻防·开始排队·恶人谷",key="大攻防·主战场",},},},</v>
       </c>
       <c r="U79" s="36" t="s">
@@ -44318,7 +44322,7 @@
         <v>1565</v>
       </c>
       <c r="T80" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往浩气盟地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=7,szName="主战场·浩气盟",nTime="1,阵营攻防·开始排队·浩气盟;10,阵营攻防·开始排队·浩气盟",key="大攻防·主战场",},},},</v>
       </c>
       <c r="U80" s="36" t="s">
@@ -44333,7 +44337,7 @@
         <v>74</v>
       </c>
       <c r="T81" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>},[74]={</v>
       </c>
     </row>
@@ -44348,7 +44352,7 @@
         <v>1432</v>
       </c>
       <c r="T82" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="本场攻防“奇袭场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="奇袭场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2402,nFrame=4,szName="奇袭场·平手",nTime=57,nRefresh=5,key="大攻防·奇袭场",},},},</v>
       </c>
       <c r="U82" s="36" t="s">
@@ -44366,7 +44370,7 @@
         <v>1432</v>
       </c>
       <c r="T83" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="本场攻防“主战场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="主战场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="主战场·平手",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U83" s="36" t="s">
@@ -44390,7 +44394,7 @@
         <v>1</v>
       </c>
       <c r="T84" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="^本场攻防“([主战奇袭场]+)”已结束，([浩气盟恶人谷]+)[侠士们众志成城和，]-([大完险胜]+)([浩气盟恶人谷]+)[！，]+",szNote="{$1}·{$2}·{$3}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,szName="大攻防·奇袭场",nTime=-2,nRefresh=10,key="大攻防·奇袭场",},{nClass=20,nIcon=13,szName="大攻防·主战场",nTime=-2,nRefresh=10,key="大攻防·主战场",},{nClass=20,nIcon=13,szName="大攻防·{$1}",nTime=-2,key="大攻防·{$1}",},{nClass=20,nIcon=2402,nFrame=4,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U84" s="36" t="s">
@@ -44426,7 +44430,7 @@
         <v>1</v>
       </c>
       <c r="T85" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U85" s="36" t="s">
@@ -44447,7 +44451,7 @@
         <v>1</v>
       </c>
       <c r="T86" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U86" s="36" t="s">
@@ -44480,7 +44484,7 @@
         <v>1</v>
       </c>
       <c r="T87" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U87" s="36" t="s">
@@ -44513,7 +44517,7 @@
         <v>1438</v>
       </c>
       <c r="T88" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U88" s="36" t="s">
@@ -44531,7 +44535,7 @@
         <v>1565</v>
       </c>
       <c r="T89" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U89" s="36" t="s">
@@ -44552,7 +44556,7 @@
         <v>1</v>
       </c>
       <c r="T90" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U90" s="36" t="s">
@@ -44570,7 +44574,7 @@
         <v>1432</v>
       </c>
       <c r="T91" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U91" s="36" t="s">
@@ -44591,7 +44595,7 @@
         <v>1432</v>
       </c>
       <c r="T92" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U92" s="36" t="s">
@@ -44610,7 +44614,7 @@
         <v>1432</v>
       </c>
       <c r="T93" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U93" s="36" t="s">
@@ -44626,7 +44630,7 @@
         <v>22</v>
       </c>
       <c r="T94" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>},[22]={</v>
       </c>
     </row>
@@ -44647,7 +44651,7 @@
         <v>1</v>
       </c>
       <c r="T95" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【武王城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="武王城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【武王城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="武王城·恶人大旗",},},},</v>
       </c>
       <c r="U95" s="36" t="s">
@@ -44699,7 +44703,7 @@
         <v>1</v>
       </c>
       <c r="T96" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="武王城·大旗重置",nTime=-2,nRefresh=7200,key="武王城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【武王城】大旗重置",nTime=180,nRefresh=7200,key="武王城·大旗重置",},},},</v>
       </c>
       <c r="U96" s="36" t="s">
@@ -44723,7 +44727,7 @@
         <v>1432</v>
       </c>
       <c r="T97" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="本场浩气盟攻防即将结束，南屏山物资运送暂且休整，等待下一场攻防开启！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="粮草先行·活动结束",nTime=5,key="粮草先行·浩气盟",},{nClass=20,nIcon=13,szName="粮草先行·恶人谷",nTime=0,key="粮草先行·恶人谷",},{nClass=20,nIcon=589,nFrame=7,szName="赵新宇",nTime="60,赵新宇·刷新剩余;62,赵新宇·即将刷新",nRefresh=0,key="赵新宇",},},},</v>
       </c>
       <c r="U97" s="36" t="s">
@@ -44744,7 +44748,7 @@
         <v>1438</v>
       </c>
       <c r="T98" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="南屏山恶人谷伴江村援军已到，营地夺回，交通恢复！\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=10,nRefresh=600,key="赵新宇",},},},</v>
       </c>
       <c r="U98" s="36" t="s">
@@ -44759,7 +44763,7 @@
         <v>1565</v>
       </c>
       <c r="T99" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="南屏山浩气盟望北村援军已到，营地夺回，交通恢复！\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=10,nRefresh=600,key="方超",},},},</v>
       </c>
       <c r="U99" s="36" t="s">
@@ -44774,7 +44778,7 @@
         <v>30</v>
       </c>
       <c r="T100" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>},[30]={</v>
       </c>
     </row>
@@ -44795,7 +44799,7 @@
         <v>1</v>
       </c>
       <c r="T101" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凛风堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凛风堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·恶人大旗",},},},</v>
       </c>
       <c r="U101" s="36" t="s">
@@ -44847,7 +44851,7 @@
         <v>1</v>
       </c>
       <c r="T102" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凛风堡·大旗重置",nTime=-2,nRefresh=7200,key="凛风堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凛风堡】大旗重置",nTime=180,nRefresh=7200,key="凛风堡·大旗重置",},},},</v>
       </c>
       <c r="U102" s="36" t="s">
@@ -44871,7 +44875,7 @@
         <v>1432</v>
       </c>
       <c r="T103" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="本场恶人谷攻防即将结束，昆仑物资运送暂且休整，等待下一场攻防开启！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="粮草先行·活动结束",nTime=5,key="粮草先行·恶人谷",},{nClass=20,nIcon=13,szName="粮草先行·浩气盟",nTime=0,key="粮草先行·浩气盟",},{nClass=20,nIcon=2864,nFrame=7,szName="霸图",nTime="60,霸图·刷新剩余;62,霸图·即将刷新",nRefresh=0,key="霸图",},{nClass=20,nIcon=845,nFrame=3,szName="孙永恒",nTime="60,孙永恒·刷新剩余;62,孙永恒·即将刷新",nRefresh=0,key="孙永恒",},},},</v>
       </c>
       <c r="U103" t="s">
@@ -44895,7 +44899,7 @@
         <v>1438</v>
       </c>
       <c r="T104" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="昆仑山恶人谷西昆仑高地援军已到，营地夺回，交通恢复！\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=10,nRefresh=600,key="霸图",},},},</v>
       </c>
       <c r="U104" s="36" t="s">
@@ -44910,7 +44914,7 @@
         <v>1565</v>
       </c>
       <c r="T105" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="昆仑山浩气盟东昆仑高地援军已到，营地夺回，交通恢复！\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=10,nRefresh=600,key="孙永恒",},},},</v>
       </c>
       <c r="U105" s="36" t="s">
@@ -44925,7 +44929,7 @@
         <v>21</v>
       </c>
       <c r="T106" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>},[21]={</v>
       </c>
     </row>
@@ -44949,7 +44953,7 @@
         <v>1</v>
       </c>
       <c r="T107" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【盘龙坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【逐鹿坪】恶人·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【盘龙坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【逐鹿坪】浩气·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·恶人大旗",},},},</v>
       </c>
       <c r="U107" s="36" t="s">
@@ -45017,7 +45021,7 @@
         <v>1</v>
       </c>
       <c r="T108" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="盘龙坞·大旗重置",nTime=-2,nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=1465,szName="逐鹿坪·大旗重置",nTime=-2,nRefresh=7200,key="逐鹿坪·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【盘龙坞】大旗重置",nTime=180,nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【逐鹿坪】大旗重置",nTime=180,nRefresh=7200,key="逐鹿坪·大旗重置",},},},</v>
       </c>
       <c r="U108" s="36" t="s">
@@ -45048,7 +45052,7 @@
         <v>23</v>
       </c>
       <c r="T109" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>},[23]={</v>
       </c>
       <c r="Z109" s="36"/>
@@ -45074,7 +45078,7 @@
         <v>1</v>
       </c>
       <c r="T110" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【龙门镇】恶人·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【飞沙关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【龙门镇】浩气·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【飞沙关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·恶人大旗",},},},</v>
       </c>
       <c r="U110" s="36" t="s">
@@ -45142,7 +45146,7 @@
         <v>1</v>
       </c>
       <c r="T111" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="龙门镇·大旗重置",nTime=-2,nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=1465,szName="飞沙关·大旗重置",nTime=-2,nRefresh=7200,key="飞沙关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【龙门镇】大旗重置",nTime=180,nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【飞沙关】大旗重置",nTime=180,nRefresh=7200,key="飞沙关·大旗重置",},},},</v>
       </c>
       <c r="U111" s="36" t="s">
@@ -45173,7 +45177,7 @@
         <v>9</v>
       </c>
       <c r="T112" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>},[9]={</v>
       </c>
       <c r="Z112" s="36"/>
@@ -45199,7 +45203,7 @@
         <v>1</v>
       </c>
       <c r="T113" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【红莲岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【秋雨堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【红莲岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【秋雨堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·恶人大旗",},},},</v>
       </c>
       <c r="U113" s="36" t="s">
@@ -45267,7 +45271,7 @@
         <v>1</v>
       </c>
       <c r="T114" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="红莲岗·大旗重置",nTime=-2,nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=1465,szName="秋雨堡·大旗重置",nTime=-2,nRefresh=7200,key="秋雨堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【红莲岗】大旗重置",nTime=180,nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【秋雨堡】大旗重置",nTime=180,nRefresh=7200,key="秋雨堡·大旗重置",},},},</v>
       </c>
       <c r="U114" s="36" t="s">
@@ -45298,7 +45302,7 @@
         <v>13</v>
       </c>
       <c r="T115" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>},[13]={</v>
       </c>
       <c r="Z115" s="36"/>
@@ -45324,7 +45328,7 @@
         <v>1</v>
       </c>
       <c r="T116" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【金门关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="金门关·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【青云坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【金门关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="金门关·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【青云坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·恶人大旗",},},},</v>
       </c>
       <c r="U116" s="36" t="s">
@@ -45392,7 +45396,7 @@
         <v>1</v>
       </c>
       <c r="T117" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="金门关·大旗重置",nTime=-2,nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=1465,szName="青云坞·大旗重置",nTime=-2,nRefresh=7200,key="青云坞·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【金门关】大旗重置",nTime=180,nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【青云坞】大旗重置",nTime=180,nRefresh=7200,key="青云坞·大旗重置",},},},</v>
       </c>
       <c r="U117" s="36" t="s">
@@ -45423,7 +45427,7 @@
         <v>35</v>
       </c>
       <c r="T118" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>},[35]={</v>
       </c>
       <c r="Z118" s="36"/>
@@ -45449,7 +45453,7 @@
         <v>1</v>
       </c>
       <c r="T119" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【激流坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【不空关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="不空关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【激流坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【不空关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="不空关·恶人大旗",},},},</v>
       </c>
       <c r="U119" s="36" t="s">
@@ -45517,7 +45521,7 @@
         <v>1</v>
       </c>
       <c r="T120" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="激流坞·大旗重置",nTime=-2,nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=1465,szName="不空关·大旗重置",nTime=-2,nRefresh=7200,key="不空关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【激流坞】大旗重置",nTime=180,nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【不空关】大旗重置",nTime=180,nRefresh=7200,key="不空关·大旗重置",},},},</v>
       </c>
       <c r="U120" s="36" t="s">
@@ -45548,7 +45552,7 @@
         <v>100</v>
       </c>
       <c r="T121" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>},[100]={</v>
       </c>
       <c r="Z121" s="36"/>
@@ -45574,7 +45578,7 @@
         <v>1</v>
       </c>
       <c r="T122" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【日月崖】恶人·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【卧龙坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【日月崖】浩气·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【卧龙坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·恶人大旗",},},},</v>
       </c>
       <c r="U122" s="36" t="s">
@@ -45642,7 +45646,7 @@
         <v>1</v>
       </c>
       <c r="T123" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="日月崖·大旗重置",nTime=-2,nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=1465,szName="卧龙坡·大旗重置",nTime=-2,nRefresh=7200,key="卧龙坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【日月崖】大旗重置",nTime=180,nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【卧龙坡】大旗重置",nTime=180,nRefresh=7200,key="卧龙坡·大旗重置",},},},</v>
       </c>
       <c r="U123" s="36" t="s">
@@ -45673,7 +45677,7 @@
         <v>101</v>
       </c>
       <c r="T124" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>},[101]={</v>
       </c>
       <c r="Z124" s="36"/>
@@ -45699,7 +45703,7 @@
         <v>1</v>
       </c>
       <c r="T125" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【霜戈堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【澜沧城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【霜戈堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【澜沧城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·恶人大旗",},},},</v>
       </c>
       <c r="U125" s="36" t="s">
@@ -45767,7 +45771,7 @@
         <v>1</v>
       </c>
       <c r="T126" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="霜戈堡·大旗重置",nTime=-2,nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=1465,szName="澜沧城·大旗重置",nTime=-2,nRefresh=7200,key="澜沧城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【霜戈堡】大旗重置",nTime=180,nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【澜沧城】大旗重置",nTime=180,nRefresh=7200,key="澜沧城·大旗重置",},},},</v>
       </c>
       <c r="U126" s="36" t="s">
@@ -45798,7 +45802,7 @@
         <v>103</v>
       </c>
       <c r="T127" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>},[103]={</v>
       </c>
       <c r="Z127" s="36"/>
@@ -45824,7 +45828,7 @@
         <v>1</v>
       </c>
       <c r="T128" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【神池岭】恶人·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【烈日岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【神池岭】浩气·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【烈日岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·恶人大旗",},},},</v>
       </c>
       <c r="U128" s="36" t="s">
@@ -45892,7 +45896,7 @@
         <v>1</v>
       </c>
       <c r="T129" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="神池岭·大旗重置",nTime=-2,nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=1465,szName="烈日岗·大旗重置",nTime=-2,nRefresh=7200,key="烈日岗·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【神池岭】大旗重置",nTime=180,nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【烈日岗】大旗重置",nTime=180,nRefresh=7200,key="烈日岗·大旗重置",},},},</v>
       </c>
       <c r="U129" s="36" t="s">
@@ -45923,7 +45927,7 @@
         <v>104</v>
       </c>
       <c r="T130" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>},[104]={</v>
       </c>
       <c r="Z130" s="36"/>
@@ -45949,7 +45953,7 @@
         <v>1</v>
       </c>
       <c r="T131" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="T131:T149" si="2">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(C131),ISBLANK(L131),ISBLANK(M131),OR(ISBLANK(B130)=FALSE,ISBLANK(C130)=FALSE,ISBLANK(L130)=FALSE,ISBLANK(M130)=FALSE)),"},},}",IF(ISBLANK(C131),"","{szContent="""&amp;C131&amp;""","&amp;IF(D131&lt;&gt;"","szNote="""&amp;D131&amp;""",","")&amp;IF(K131&lt;&gt;"","col={"&amp;K131&amp;"},","")&amp;IF(L131&gt;0,"bSearch=true,","")&amp;IF(M131&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N131&gt;0,"szVoice="""&amp;N131&amp;""",","")&amp;IF(O131&gt;0,"bTeamChannel=true,","")&amp;IF(P131&gt;0,"bWhisperChannel=true,","")&amp;IF(Q131&gt;0,"bCenterAlarm=true,","")&amp;IF(R131&gt;0,"bScreenHead=true,","")&amp;IF(S131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U131:AAF131)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凤鸣堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【惊虬谷】恶人·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凤鸣堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【惊虬谷】浩气·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·恶人大旗",},},},</v>
       </c>
       <c r="U131" s="36" t="s">
@@ -46017,7 +46021,7 @@
         <v>1</v>
       </c>
       <c r="T132" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凤鸣堡·大旗重置",nTime=-2,nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=1465,szName="惊虬谷·大旗重置",nTime=-2,nRefresh=7200,key="惊虬谷·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凤鸣堡】大旗重置",nTime=180,nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【惊虬谷】大旗重置",nTime=180,nRefresh=7200,key="惊虬谷·大旗重置",},},},</v>
       </c>
       <c r="U132" s="36" t="s">
@@ -46048,7 +46052,7 @@
         <v>105</v>
       </c>
       <c r="T133" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>},[105]={</v>
       </c>
       <c r="Z133" s="36"/>
@@ -46074,7 +46078,7 @@
         <v>1</v>
       </c>
       <c r="T134" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【大理山城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【千岩关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【大理山城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【千岩关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·恶人大旗",},},},</v>
       </c>
       <c r="U134" s="36" t="s">
@@ -46142,7 +46146,7 @@
         <v>1</v>
       </c>
       <c r="T135" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="大理山城·大旗重置",nTime=-2,nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=1465,szName="千岩关·大旗重置",nTime=-2,nRefresh=7200,key="千岩关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【大理山城】大旗重置",nTime=180,nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【千岩关】大旗重置",nTime=180,nRefresh=7200,key="千岩关·大旗重置",},},},</v>
       </c>
       <c r="U135" s="36" t="s">
@@ -46173,7 +46177,7 @@
         <v>139</v>
       </c>
       <c r="T136" s="36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>},[139]={</v>
       </c>
       <c r="Z136" s="36"/>
@@ -46199,7 +46203,7 @@
         <v>1</v>
       </c>
       <c r="T137" s="36" t="str">
-        <f t="shared" ref="T137:T149" si="4">IF(ISBLANK(B137)=FALSE,IF(ISBLANK(B136),"},["&amp;B137&amp;"]={","["&amp;B137&amp;"]={"),IF(AND(ISBLANK(B137),ISBLANK(C137),ISBLANK(L137),ISBLANK(M137),OR(ISBLANK(B136)=FALSE,ISBLANK(C136)=FALSE,ISBLANK(L136)=FALSE,ISBLANK(M136)=FALSE)),"},},}",IF(ISBLANK(C137),"","{szContent="""&amp;C137&amp;""","&amp;IF(D137&lt;&gt;"","szNote="""&amp;D137&amp;""",","")&amp;IF(K137&lt;&gt;"","col={"&amp;K137&amp;"},","")&amp;IF(L137&gt;0,"bSearch=true,","")&amp;IF(M137&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N137&gt;0,"szVoice="""&amp;N137&amp;""",","")&amp;IF(O137&gt;0,"bTeamChannel=true,","")&amp;IF(P137&gt;0,"bWhisperChannel=true,","")&amp;IF(Q137&gt;0,"bCenterAlarm=true,","")&amp;IF(R137&gt;0,"bScreenHead=true,","")&amp;IF(S137&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U137&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U137:AAF137)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="2"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【枫湖寨】恶人·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【啖杏林】恶人·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【枫湖寨】浩气·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【啖杏林】浩气·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·恶人大旗",},},},</v>
       </c>
       <c r="U137" s="36" t="s">
@@ -46267,7 +46271,7 @@
         <v>1</v>
       </c>
       <c r="T138" s="36" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="枫湖寨·大旗重置",nTime=-2,nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=1465,szName="啖杏林·大旗重置",nTime=-2,nRefresh=7200,key="啖杏林·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【枫湖寨】大旗重置",nTime=180,nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【啖杏林】大旗重置",nTime=180,nRefresh=7200,key="啖杏林·大旗重置",},},},</v>
       </c>
       <c r="U138" s="36" t="s">
@@ -46298,7 +46302,7 @@
         <v>153</v>
       </c>
       <c r="T139" s="36" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>},[153]={</v>
       </c>
       <c r="Z139" s="36"/>
@@ -46324,7 +46328,7 @@
         <v>1</v>
       </c>
       <c r="T140" s="36" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【扶风郡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【世外坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【扶风郡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【世外坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U140" s="36" t="s">
@@ -46392,7 +46396,7 @@
         <v>1</v>
       </c>
       <c r="T141" s="36" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="扶风郡·大旗重置",nTime=-2,nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=1465,szName="世外坡·大旗重置",nTime=-2,nRefresh=7200,key="世外坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【扶风郡】大旗重置",nTime=180,nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【世外坡】大旗重置",nTime=180,nRefresh=7200,key="世外坡·大旗重置",},},},</v>
       </c>
       <c r="U141" s="36" t="s">
@@ -46423,7 +46427,7 @@
         <v>216</v>
       </c>
       <c r="T142" s="36" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>},[216]={</v>
       </c>
       <c r="Z142" s="36"/>
@@ -46449,7 +46453,7 @@
         <v>1</v>
       </c>
       <c r="T143" s="36" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U143" s="36" t="s">
@@ -46493,7 +46497,7 @@
         <v>1</v>
       </c>
       <c r="T144" s="36" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime=180,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime=180,nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U144" s="36" t="s">
@@ -46530,7 +46534,7 @@
         <v>1</v>
       </c>
       <c r="T145" s="36" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U145" s="36" t="s">
@@ -46557,7 +46561,7 @@
         <v>656</v>
       </c>
       <c r="T146" s="36" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>},[656]={</v>
       </c>
     </row>
@@ -46581,7 +46585,7 @@
         <v>1</v>
       </c>
       <c r="T147" s="36" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U147" s="36" t="s">
@@ -46620,7 +46624,7 @@
         <v>1</v>
       </c>
       <c r="T148" s="36" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime=180,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime=180,nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U148" s="36" t="s">
@@ -46675,7 +46679,7 @@
         <v>1</v>
       </c>
       <c r="T149" s="36" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U149" s="36" t="s">

--- a/阵营/大小攻防团队监控.xlsx
+++ b/阵营/大小攻防团队监控.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JX3\Game\JX3\bin\zhcn_hd\interface\MY#DATA\!all-users@zhcn_hd\userdata\team_mon\remote\打包\阵营\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CA092919-726B-4258-909A-51F73D21A766}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{FEDEFBB9-91DA-492A-8D8F-082508D3EDCF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据总控" sheetId="2" r:id="rId1"/>
@@ -24,10 +24,10 @@
     <sheet name="系统频道" sheetId="11" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">角色喊话!$A$1:$AV$183</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">系统角色!$A$1:$X$404</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">角色喊话!$A$1:$AV$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">系统角色!$A$1:$X$409</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">系统频道!$A$1:$BG$149</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">有利气劲!$A$1:$AS$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">有利气劲!$A$1:$AS$45</definedName>
     <definedName name="JunSun1" localSheetId="6">DATE(交互物件!日历年份,6,1)-WEEKDAY(DATE(交互物件!日历年份,6,1))</definedName>
     <definedName name="JunSun1" localSheetId="4">DATE(武学招式!日历年份,6,1)-WEEKDAY(DATE(武学招式!日历年份,6,1))</definedName>
     <definedName name="JunSun1" localSheetId="5">DATE(系统角色!日历年份,6,1)-WEEKDAY(DATE(系统角色!日历年份,6,1))</definedName>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="5683" uniqueCount="2735">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="5787" uniqueCount="2735">
   <si>
     <t>标识</t>
   </si>
@@ -10747,7 +10747,7 @@
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="21" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1774718023190,</v>
+        <v>nTimeStamp = 1774974165490,</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>34</v>
@@ -20378,7 +20378,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D081BAC9-EDC6-4C51-AA88-6C0F8A94F7D5}">
-  <dimension ref="A1:AS47"/>
+  <dimension ref="A1:AS46"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="11" max="11" width="15.375" customWidth="1"/>
@@ -20599,7 +20599,7 @@
         <v>1</v>
       </c>
       <c r="AN3" s="36" t="str">
-        <f t="shared" ref="AN3:AN46" si="0">IF(B3&lt;&gt;"",IF(IFERROR(VALUE(C2),0)&lt;=0,"["&amp;B3&amp;"]={","},["&amp;B3&amp;"]={"),IF(C3&gt;0,"{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"nIcon="&amp;F3&amp;",","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&gt;0,"bCheckLevel=true,","")&amp;IF(I3&gt;0,"nScrutinyType="&amp;I3&amp;",","")&amp;IF(J3&lt;&gt;"","tKungFu={"&amp;J3&amp;"},","")&amp;IF(K3&lt;&gt;"","szNote="""&amp;K3&amp;""",","")&amp;IF(L3&lt;&gt;"","col={"&amp;L3&amp;"},","")&amp;"[1]={"&amp;IF(M3&lt;&gt;"","tMark={"&amp;M3&amp;"},","")&amp;IF(N3&lt;&gt;"","szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bTeamChannel=true,","")&amp;IF(P3&gt;0,"bWhisperChannel=true,","")&amp;IF(Q3&gt;0,"bCenterAlarm=true,","")&amp;IF(R3&gt;0,"bScreenHead=true,","")&amp;IF(S3&gt;0,"bPartyBuffList=true,","")&amp;IF(T3&gt;0,"bBuffList=true,","")&amp;IF(U3&gt;0,"bFullScreen=true,","")&amp;IF(V3&gt;0,"bTeamPanel=true,","")&amp;IF(W3&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(X3&gt;0,"bTeamChannel=true,","")&amp;IF(Y3&gt;0,"bWhisperChannel=true,","")&amp;IF(Z3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AA3&gt;0,AE3&lt;&gt;"",AF3&gt;0,AG3&lt;&gt;"",AH3&lt;&gt;"",AI3&gt;0,AJ3&gt;0,AK3&gt;0,AL3&gt;0),"aCataclysmBuff={{"&amp;IF(AA3&gt;0,"nStackNum="&amp;AA3&amp;",","")&amp;IF(AB3&lt;&gt;"","szStackOp="""&amp;AB3&amp;""",","")&amp;IF(AC3&gt;0,"bOnlyMine=true,","")&amp;IF(AD3&gt;0,"bOnlyMe=true,","")&amp;IF(AE3&lt;&gt;"","szReminder="""&amp;AE3&amp;""",","")&amp;IF(AF3&gt;0,"nPriority="&amp;AF3&amp;",","")&amp;IF(AG3&lt;&gt;"","col="""&amp;AG3&amp;""",","")&amp;IF(AH3&lt;&gt;"","colScreenHead="""&amp;AH3&amp;""",","")&amp;IF(AI3&gt;0,"nColAlpha="&amp;AI3&amp;",","")&amp;IF(AJ3&gt;0,"bAttention=true,","")&amp;IF(AK3&gt;0,"bCaution=true,","")&amp;IF(AL3&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AM3&amp;"},","")&amp;IF(AO3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AO3:ZZ3)&amp;"},","")&amp;"},",IF(C2&gt;0,"},","")&amp;IF(AND(B3="",C3="",OR(B2&lt;&gt;"",C2&lt;&gt;"")),"},}","")))</f>
+        <f t="shared" ref="AN3:AN45" si="0">IF(B3&lt;&gt;"",IF(IFERROR(VALUE(C2),0)&lt;=0,"["&amp;B3&amp;"]={","},["&amp;B3&amp;"]={"),IF(C3&gt;0,"{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"nIcon="&amp;F3&amp;",","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&gt;0,"bCheckLevel=true,","")&amp;IF(I3&gt;0,"nScrutinyType="&amp;I3&amp;",","")&amp;IF(J3&lt;&gt;"","tKungFu={"&amp;J3&amp;"},","")&amp;IF(K3&lt;&gt;"","szNote="""&amp;K3&amp;""",","")&amp;IF(L3&lt;&gt;"","col={"&amp;L3&amp;"},","")&amp;"[1]={"&amp;IF(M3&lt;&gt;"","tMark={"&amp;M3&amp;"},","")&amp;IF(N3&lt;&gt;"","szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bTeamChannel=true,","")&amp;IF(P3&gt;0,"bWhisperChannel=true,","")&amp;IF(Q3&gt;0,"bCenterAlarm=true,","")&amp;IF(R3&gt;0,"bScreenHead=true,","")&amp;IF(S3&gt;0,"bPartyBuffList=true,","")&amp;IF(T3&gt;0,"bBuffList=true,","")&amp;IF(U3&gt;0,"bFullScreen=true,","")&amp;IF(V3&gt;0,"bTeamPanel=true,","")&amp;IF(W3&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(X3&gt;0,"bTeamChannel=true,","")&amp;IF(Y3&gt;0,"bWhisperChannel=true,","")&amp;IF(Z3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AA3&gt;0,AE3&lt;&gt;"",AF3&gt;0,AG3&lt;&gt;"",AH3&lt;&gt;"",AI3&gt;0,AJ3&gt;0,AK3&gt;0,AL3&gt;0),"aCataclysmBuff={{"&amp;IF(AA3&gt;0,"nStackNum="&amp;AA3&amp;",","")&amp;IF(AB3&lt;&gt;"","szStackOp="""&amp;AB3&amp;""",","")&amp;IF(AC3&gt;0,"bOnlyMine=true,","")&amp;IF(AD3&gt;0,"bOnlyMe=true,","")&amp;IF(AE3&lt;&gt;"","szReminder="""&amp;AE3&amp;""",","")&amp;IF(AF3&gt;0,"nPriority="&amp;AF3&amp;",","")&amp;IF(AG3&lt;&gt;"","col="""&amp;AG3&amp;""",","")&amp;IF(AH3&lt;&gt;"","colScreenHead="""&amp;AH3&amp;""",","")&amp;IF(AI3&gt;0,"nColAlpha="&amp;AI3&amp;",","")&amp;IF(AJ3&gt;0,"bAttention=true,","")&amp;IF(AK3&gt;0,"bCaution=true,","")&amp;IF(AL3&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AM3&amp;"},","")&amp;IF(AO3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AO3:ZZ3)&amp;"},","")&amp;"},",IF(C2&gt;0,"},","")&amp;IF(AND(B3="",C3="",OR(B2&lt;&gt;"",C2&lt;&gt;"")),"},}","")))</f>
         <v>{dwID=3921,nLevel=1,nIcon=134,szName="弩CD",nScrutinyType=1,szNote="伟龙debuff",[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
@@ -21251,795 +21251,783 @@
     </row>
     <row r="18" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A18" s="36" t="s">
-        <v>1819</v>
+        <v>2165</v>
       </c>
       <c r="B18" s="36">
-        <v>216</v>
+        <v>50</v>
       </c>
       <c r="AN18" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>},[216]={</v>
+        <v>},[50]={</v>
       </c>
     </row>
     <row r="19" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C19" s="36">
-        <v>7561</v>
+        <v>8477</v>
       </c>
       <c r="D19" s="36">
         <v>1</v>
       </c>
+      <c r="F19" s="36">
+        <v>6491</v>
+      </c>
       <c r="G19" s="36" t="s">
-        <v>2635</v>
+        <v>1647</v>
+      </c>
+      <c r="I19" s="36">
+        <v>1</v>
       </c>
       <c r="K19" s="36" t="s">
-        <v>1653</v>
-      </c>
-      <c r="L19" s="36" t="s">
-        <v>2115</v>
-      </c>
-      <c r="R19" s="36">
-        <v>1</v>
-      </c>
-      <c r="S19" s="36">
-        <v>1</v>
+        <v>1650</v>
       </c>
       <c r="T19" s="36">
-        <v>1</v>
-      </c>
-      <c r="V19" s="36">
-        <v>1</v>
-      </c>
-      <c r="AE19" s="36" t="s">
-        <v>2023</v>
-      </c>
-      <c r="AF19" s="36">
-        <v>2</v>
-      </c>
-      <c r="AG19" s="36" t="s">
-        <v>2177</v>
-      </c>
-      <c r="AH19" s="36" t="s">
-        <v>2178</v>
-      </c>
-      <c r="AI19" s="36">
-        <v>255</v>
-      </c>
-      <c r="AL19" s="36">
         <v>1</v>
       </c>
       <c r="AN19" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7561,nLevel=1,szName="守据点",szNote="守卫据点",col={0,255,255,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="旗",nPriority=2,col="#00FFFFFF",colScreenHead="#00FFFF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nTime=30,szName="【{$receiver}】·拾取大旗",nFrame=8,nIcon=592,key="拾取大旗·{$receiver}",},{nClass=2,nTime=-1,szName="拾取大旗",nIcon=592,key="拾取大旗·{$receiver}",},},},</v>
+        <v>{dwID=8477,nLevel=1,nIcon=6491,szName="劲足",nScrutinyType=1,szNote="速度·劲足",[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=6491,nFrame=6,szName="骑御·劲足",nTime=0.5,nRefresh=300,key="骑御·调息",},{nClass=2,nIcon=6491,nFrame=1,szName="劲足·已消失",nTime=3,nRefresh=5,key="骑御·劲足",},},},</v>
       </c>
       <c r="AO19" s="36" t="s">
-        <v>2578</v>
+        <v>1782</v>
       </c>
       <c r="AP19" s="36" t="s">
-        <v>2577</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="20" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C20" s="36">
-        <v>7525</v>
+        <v>8607</v>
       </c>
       <c r="D20" s="36">
         <v>1</v>
       </c>
       <c r="G20" s="36" t="s">
-        <v>2636</v>
+        <v>2683</v>
+      </c>
+      <c r="I20" s="36">
+        <v>1</v>
       </c>
       <c r="K20" s="36" t="s">
-        <v>1652</v>
-      </c>
-      <c r="L20" s="36" t="s">
-        <v>2115</v>
-      </c>
-      <c r="R20" s="36">
-        <v>1</v>
-      </c>
-      <c r="S20" s="36">
-        <v>1</v>
+        <v>1649</v>
       </c>
       <c r="T20" s="36">
-        <v>1</v>
-      </c>
-      <c r="V20" s="36">
-        <v>1</v>
-      </c>
-      <c r="AE20" s="36" t="s">
-        <v>2023</v>
-      </c>
-      <c r="AF20" s="36">
-        <v>2</v>
-      </c>
-      <c r="AG20" s="36" t="s">
-        <v>2177</v>
-      </c>
-      <c r="AH20" s="36" t="s">
-        <v>2178</v>
-      </c>
-      <c r="AI20" s="36">
-        <v>255</v>
-      </c>
-      <c r="AL20" s="36">
         <v>1</v>
       </c>
       <c r="AN20" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7525,nLevel=1,szName="占据点",szNote="据点大旗",col={0,255,255,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="旗",nPriority=2,col="#00FFFFFF",colScreenHead="#00FFFF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nTime=30,szName="【{$receiver}】·拾取大旗",nFrame=8,nIcon=592,key="拾取大旗·{$receiver}",},{nClass=2,nTime=-1,szName="拾取大旗",nIcon=592,key="拾取大旗·{$receiver}",},},},</v>
+        <v>{dwID=8607,nLevel=1,szName="气力",nScrutinyType=1,szNote="气力·调息",[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=6678,nFrame=6,szName="骑御·调息",nTime=0,key="骑御·调息",},},},</v>
       </c>
       <c r="AO20" s="36" t="s">
-        <v>2578</v>
-      </c>
-      <c r="AP20" s="36" t="s">
-        <v>2577</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="21" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C21" s="36">
-        <v>7373</v>
+        <v>244</v>
       </c>
       <c r="D21" s="36">
         <v>1</v>
       </c>
-      <c r="F21" s="36">
-        <v>134</v>
-      </c>
-      <c r="G21" s="36" t="s">
-        <v>2390</v>
+      <c r="H21" s="36">
+        <v>1</v>
       </c>
       <c r="I21" s="36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K21" s="36" t="s">
-        <v>2389</v>
-      </c>
-      <c r="L21" s="36" t="s">
-        <v>1964</v>
-      </c>
-      <c r="R21" s="36">
-        <v>1</v>
+        <v>1651</v>
       </c>
       <c r="AN21" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7373,nLevel=1,nIcon=134,szName="箭弩车",nScrutinyType=3,szNote="箭弩车记录ID",col={255,50,255,},[1]={bScreenHead=true,},[2]={},},</v>
+        <v>{dwID=244,nLevel=1,bCheckLevel=true,nScrutinyType=1,szNote="骑御",[1]={},[2]={},tCountdown={{nClass=2,nIcon=6678,nFrame=6,szName="骑御·调息",nTime=-1,key="骑御·调息",},{nClass=1,nIcon=6678,nFrame=6,szName="骑御·调息",nTime="18.8,调息·7级·触发剩余;22.8,调息·5级·触发剩余",nRefresh=0,key="骑御·调息",},},},</v>
+      </c>
+      <c r="AO21" s="36" t="s">
+        <v>1646</v>
+      </c>
+      <c r="AP21" s="36" t="s">
+        <v>1821</v>
       </c>
     </row>
     <row r="22" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C22" s="36">
-        <v>7492</v>
-      </c>
-      <c r="D22" s="36">
-        <v>1</v>
-      </c>
-      <c r="G22" s="36" t="s">
-        <v>1785</v>
-      </c>
-      <c r="I22" s="36">
-        <v>2</v>
-      </c>
-      <c r="K22" s="36" t="s">
-        <v>1784</v>
-      </c>
-      <c r="L22" s="36" t="s">
-        <v>1527</v>
-      </c>
-      <c r="T22" s="36">
-        <v>1</v>
+      <c r="A22" s="36" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B22" s="36">
+        <v>74</v>
       </c>
       <c r="AN22" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7492,nLevel=1,szName="御城矛",nScrutinyType=2,szNote="御城·矛",col={0,255,0,},[1]={bBuffList=true,},[2]={},},</v>
+        <v>},[74]={</v>
       </c>
     </row>
     <row r="23" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C23" s="36">
-        <v>8606</v>
+        <v>8477</v>
       </c>
       <c r="D23" s="36">
         <v>1</v>
       </c>
+      <c r="F23" s="36">
+        <v>6491</v>
+      </c>
       <c r="G23" s="36" t="s">
-        <v>1915</v>
+        <v>1647</v>
       </c>
       <c r="I23" s="36">
         <v>1</v>
       </c>
       <c r="K23" s="36" t="s">
-        <v>1914</v>
+        <v>1650</v>
       </c>
       <c r="T23" s="36">
         <v>1</v>
       </c>
       <c r="AN23" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=8606,nLevel=1,szName="抗摔",nScrutinyType=1,szNote="抗摔·强健",[1]={bBuffList=true,},[2]={},},</v>
+        <v>{dwID=8477,nLevel=1,nIcon=6491,szName="劲足",nScrutinyType=1,szNote="速度·劲足",[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=6491,nFrame=6,szName="骑御·劲足",nTime=0.5,nRefresh=300,key="骑御·调息",},{nClass=2,nIcon=6491,nFrame=1,szName="劲足·已消失",nTime=3,nRefresh=5,key="骑御·劲足",},},},</v>
+      </c>
+      <c r="AO23" s="36" t="s">
+        <v>1782</v>
+      </c>
+      <c r="AP23" s="36" t="s">
+        <v>2168</v>
       </c>
     </row>
     <row r="24" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="36" t="s">
-        <v>613</v>
-      </c>
-      <c r="B24" s="36">
-        <v>656</v>
+      <c r="C24" s="36">
+        <v>8607</v>
+      </c>
+      <c r="D24" s="36">
+        <v>1</v>
+      </c>
+      <c r="I24" s="36">
+        <v>1</v>
+      </c>
+      <c r="K24" s="36" t="s">
+        <v>1649</v>
+      </c>
+      <c r="T24" s="36">
+        <v>1</v>
       </c>
       <c r="AN24" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>},[656]={</v>
+        <v>{dwID=8607,nLevel=1,nScrutinyType=1,szNote="气力·调息",[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=6678,nFrame=6,szName="骑御·调息",nTime=0,key="骑御·调息",},},},</v>
+      </c>
+      <c r="AO24" s="36" t="s">
+        <v>1648</v>
       </c>
     </row>
     <row r="25" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C25" s="36">
-        <v>7561</v>
+        <v>244</v>
       </c>
       <c r="D25" s="36">
         <v>1</v>
       </c>
-      <c r="G25" s="36" t="s">
-        <v>2635</v>
+      <c r="H25" s="36">
+        <v>1</v>
+      </c>
+      <c r="I25" s="36">
+        <v>1</v>
       </c>
       <c r="K25" s="36" t="s">
-        <v>1653</v>
-      </c>
-      <c r="L25" s="36" t="s">
-        <v>2115</v>
-      </c>
-      <c r="R25" s="36">
-        <v>1</v>
-      </c>
-      <c r="S25" s="36">
-        <v>1</v>
-      </c>
-      <c r="T25" s="36">
-        <v>1</v>
-      </c>
-      <c r="V25" s="36">
-        <v>1</v>
-      </c>
-      <c r="AE25" s="36" t="s">
-        <v>2023</v>
-      </c>
-      <c r="AF25" s="36">
-        <v>2</v>
-      </c>
-      <c r="AG25" s="36" t="s">
-        <v>2177</v>
-      </c>
-      <c r="AH25" s="36" t="s">
-        <v>2178</v>
-      </c>
-      <c r="AI25" s="36">
-        <v>255</v>
-      </c>
-      <c r="AL25" s="36">
-        <v>1</v>
+        <v>1651</v>
       </c>
       <c r="AN25" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7561,nLevel=1,szName="守据点",szNote="守卫据点",col={0,255,255,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="旗",nPriority=2,col="#00FFFFFF",colScreenHead="#00FFFF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nTime=30,szName="【{$receiver}】·拾取大旗",nFrame=8,nIcon=592,key="拾取大旗·{$receiver}",},{nClass=2,nTime=-1,szName="拾取大旗",nIcon=592,key="拾取大旗·{$receiver}",},},},</v>
+        <v>{dwID=244,nLevel=1,bCheckLevel=true,nScrutinyType=1,szNote="骑御",[1]={},[2]={},tCountdown={{nClass=2,nIcon=6678,nFrame=6,szName="骑御·调息",nTime=-1,key="骑御·调息",},{nClass=1,nIcon=6678,nFrame=6,szName="骑御·调息",nTime="18.8,调息·7级·触发剩余;22.8,调息·5级·触发剩余",nRefresh=0,key="骑御·调息",},},},</v>
       </c>
       <c r="AO25" s="36" t="s">
-        <v>2578</v>
+        <v>1646</v>
       </c>
       <c r="AP25" s="36" t="s">
-        <v>2577</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="26" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C26" s="36">
-        <v>7525</v>
-      </c>
-      <c r="D26" s="36">
-        <v>1</v>
-      </c>
-      <c r="G26" s="36" t="s">
-        <v>2636</v>
-      </c>
-      <c r="K26" s="36" t="s">
-        <v>1652</v>
-      </c>
-      <c r="L26" s="36" t="s">
-        <v>2115</v>
-      </c>
-      <c r="R26" s="36">
-        <v>1</v>
-      </c>
-      <c r="S26" s="36">
-        <v>1</v>
-      </c>
-      <c r="T26" s="36">
-        <v>1</v>
-      </c>
-      <c r="V26" s="36">
-        <v>1</v>
-      </c>
-      <c r="AE26" s="36" t="s">
-        <v>2023</v>
-      </c>
-      <c r="AF26" s="36">
-        <v>2</v>
-      </c>
-      <c r="AG26" s="36" t="s">
-        <v>2177</v>
-      </c>
-      <c r="AH26" s="36" t="s">
-        <v>2178</v>
-      </c>
-      <c r="AI26" s="36">
-        <v>255</v>
-      </c>
-      <c r="AL26" s="36">
-        <v>1</v>
+      <c r="A26" s="36" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B26" s="36">
+        <v>214</v>
       </c>
       <c r="AN26" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7525,nLevel=1,szName="占据点",szNote="据点大旗",col={0,255,255,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="旗",nPriority=2,col="#00FFFFFF",colScreenHead="#00FFFF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nTime=30,szName="【{$receiver}】·拾取大旗",nFrame=8,nIcon=592,key="拾取大旗·{$receiver}",},{nClass=2,nTime=-1,szName="拾取大旗",nIcon=592,key="拾取大旗·{$receiver}",},},},</v>
-      </c>
-      <c r="AO26" s="36" t="s">
-        <v>2578</v>
-      </c>
-      <c r="AP26" s="36" t="s">
-        <v>2577</v>
+        <v>},[214]={</v>
       </c>
     </row>
     <row r="27" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C27" s="36">
-        <v>7373</v>
+        <v>10067</v>
       </c>
       <c r="D27" s="36">
         <v>1</v>
       </c>
-      <c r="F27" s="36">
-        <v>134</v>
-      </c>
       <c r="G27" s="36" t="s">
-        <v>2390</v>
+        <v>2310</v>
       </c>
       <c r="I27" s="36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K27" s="36" t="s">
-        <v>2389</v>
+        <v>2309</v>
       </c>
       <c r="L27" s="36" t="s">
-        <v>1964</v>
-      </c>
-      <c r="R27" s="36">
+        <v>2311</v>
+      </c>
+      <c r="T27" s="36">
         <v>1</v>
       </c>
       <c r="AN27" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7373,nLevel=1,nIcon=134,szName="箭弩车",nScrutinyType=3,szNote="箭弩车记录ID",col={255,50,255,},[1]={bScreenHead=true,},[2]={},},</v>
+        <v>{dwID=10067,nLevel=1,szName="补货点",nScrutinyType=1,szNote="阴山商路贸易区",col={255,150,0,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="28" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C28" s="36">
-        <v>7492</v>
+        <v>7508</v>
       </c>
       <c r="D28" s="36">
         <v>1</v>
       </c>
-      <c r="G28" s="36" t="s">
-        <v>1785</v>
-      </c>
       <c r="I28" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K28" s="36" t="s">
-        <v>1784</v>
+        <v>2308</v>
       </c>
       <c r="L28" s="36" t="s">
-        <v>1527</v>
+        <v>2307</v>
+      </c>
+      <c r="R28" s="36">
+        <v>1</v>
       </c>
       <c r="T28" s="36">
         <v>1</v>
       </c>
       <c r="AN28" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7492,nLevel=1,szName="御城矛",nScrutinyType=2,szNote="御城·矛",col={0,255,0,},[1]={bBuffList=true,},[2]={},},</v>
+        <v>{dwID=7508,nLevel=1,nScrutinyType=1,szNote="哑运",col={179,238,58,},[1]={bScreenHead=true,bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="29" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C29" s="36">
-        <v>8606</v>
-      </c>
-      <c r="D29" s="36">
-        <v>1</v>
-      </c>
-      <c r="G29" s="36" t="s">
-        <v>1915</v>
-      </c>
-      <c r="I29" s="36">
-        <v>1</v>
-      </c>
-      <c r="K29" s="36" t="s">
-        <v>1914</v>
-      </c>
-      <c r="T29" s="36">
-        <v>1</v>
+      <c r="A29" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" s="36">
+        <v>217</v>
       </c>
       <c r="AN29" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=8606,nLevel=1,szName="抗摔",nScrutinyType=1,szNote="抗摔·强健",[1]={bBuffList=true,},[2]={},},</v>
+        <v>},[217]={</v>
       </c>
     </row>
     <row r="30" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="36" t="s">
-        <v>2165</v>
-      </c>
-      <c r="B30" s="36">
-        <v>50</v>
+      <c r="C30" s="36">
+        <v>7508</v>
+      </c>
+      <c r="D30" s="36">
+        <v>1</v>
+      </c>
+      <c r="I30" s="36">
+        <v>1</v>
+      </c>
+      <c r="K30" s="36" t="s">
+        <v>2308</v>
+      </c>
+      <c r="L30" s="36" t="s">
+        <v>2307</v>
+      </c>
+      <c r="R30" s="36">
+        <v>1</v>
+      </c>
+      <c r="T30" s="36">
+        <v>1</v>
       </c>
       <c r="AN30" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>},[50]={</v>
+        <v>{dwID=7508,nLevel=1,nScrutinyType=1,szNote="哑运",col={179,238,58,},[1]={bScreenHead=true,bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="31" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C31" s="36">
-        <v>8477</v>
-      </c>
-      <c r="D31" s="36">
-        <v>1</v>
-      </c>
-      <c r="F31" s="36">
-        <v>6491</v>
-      </c>
-      <c r="G31" s="36" t="s">
-        <v>1647</v>
-      </c>
-      <c r="I31" s="36">
-        <v>1</v>
-      </c>
-      <c r="K31" s="36" t="s">
-        <v>1650</v>
-      </c>
-      <c r="T31" s="36">
-        <v>1</v>
+      <c r="A31" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" s="36">
+        <v>216</v>
       </c>
       <c r="AN31" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=8477,nLevel=1,nIcon=6491,szName="劲足",nScrutinyType=1,szNote="速度·劲足",[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=6491,nFrame=6,szName="骑御·劲足",nTime=0.5,nRefresh=300,key="骑御·调息",},{nClass=2,nIcon=6491,nFrame=1,szName="劲足·已消失",nTime=3,nRefresh=5,key="骑御·劲足",},},},</v>
-      </c>
-      <c r="AO31" s="36" t="s">
-        <v>1782</v>
-      </c>
-      <c r="AP31" s="36" t="s">
-        <v>2168</v>
+        <v>},[216]={</v>
       </c>
     </row>
     <row r="32" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C32" s="36">
-        <v>8607</v>
+        <v>10067</v>
       </c>
       <c r="D32" s="36">
         <v>1</v>
       </c>
       <c r="G32" s="36" t="s">
-        <v>2683</v>
+        <v>2310</v>
       </c>
       <c r="I32" s="36">
         <v>1</v>
       </c>
       <c r="K32" s="36" t="s">
-        <v>1649</v>
+        <v>2309</v>
+      </c>
+      <c r="L32" s="36" t="s">
+        <v>2311</v>
       </c>
       <c r="T32" s="36">
         <v>1</v>
       </c>
       <c r="AN32" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=8607,nLevel=1,szName="气力",nScrutinyType=1,szNote="气力·调息",[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=6678,nFrame=6,szName="骑御·调息",nTime=0,key="骑御·调息",},},},</v>
-      </c>
-      <c r="AO32" s="36" t="s">
-        <v>1648</v>
+        <v>{dwID=10067,nLevel=1,szName="补货点",nScrutinyType=1,szNote="阴山商路贸易区",col={255,150,0,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="33" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C33" s="36">
-        <v>244</v>
+        <v>7508</v>
       </c>
       <c r="D33" s="36">
         <v>1</v>
       </c>
-      <c r="H33" s="36">
-        <v>1</v>
-      </c>
       <c r="I33" s="36">
         <v>1</v>
       </c>
       <c r="K33" s="36" t="s">
-        <v>1651</v>
+        <v>2308</v>
+      </c>
+      <c r="L33" s="36" t="s">
+        <v>2307</v>
+      </c>
+      <c r="R33" s="36">
+        <v>1</v>
+      </c>
+      <c r="T33" s="36">
+        <v>1</v>
       </c>
       <c r="AN33" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=244,nLevel=1,bCheckLevel=true,nScrutinyType=1,szNote="骑御",[1]={},[2]={},tCountdown={{nClass=2,nIcon=6678,nFrame=6,szName="骑御·调息",nTime=-1,key="骑御·调息",},{nClass=1,nIcon=6678,nFrame=6,szName="骑御·调息",nTime="18.8,调息·7级·触发剩余;22.8,调息·5级·触发剩余",nRefresh=0,key="骑御·调息",},},},</v>
-      </c>
-      <c r="AO33" s="36" t="s">
-        <v>1646</v>
-      </c>
-      <c r="AP33" s="36" t="s">
-        <v>1821</v>
+        <v>{dwID=7508,nLevel=1,nScrutinyType=1,szNote="哑运",col={179,238,58,},[1]={bScreenHead=true,bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="34" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="36" t="s">
-        <v>2093</v>
-      </c>
-      <c r="B34" s="36">
-        <v>74</v>
+      <c r="C34" s="40">
+        <v>7561</v>
+      </c>
+      <c r="D34" s="36">
+        <v>1</v>
+      </c>
+      <c r="G34" s="36" t="s">
+        <v>2635</v>
+      </c>
+      <c r="K34" s="36" t="s">
+        <v>1653</v>
+      </c>
+      <c r="L34" s="36" t="s">
+        <v>2115</v>
+      </c>
+      <c r="R34" s="36">
+        <v>1</v>
+      </c>
+      <c r="S34" s="36">
+        <v>1</v>
+      </c>
+      <c r="T34" s="36">
+        <v>1</v>
+      </c>
+      <c r="V34" s="36">
+        <v>1</v>
+      </c>
+      <c r="AE34" s="36" t="s">
+        <v>2023</v>
+      </c>
+      <c r="AF34" s="36">
+        <v>2</v>
+      </c>
+      <c r="AG34" s="36" t="s">
+        <v>2177</v>
+      </c>
+      <c r="AH34" s="36" t="s">
+        <v>2178</v>
+      </c>
+      <c r="AI34" s="36">
+        <v>255</v>
+      </c>
+      <c r="AL34" s="36">
+        <v>1</v>
       </c>
       <c r="AN34" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>},[74]={</v>
+        <v>{dwID=7561,nLevel=1,szName="守据点",szNote="守卫据点",col={0,255,255,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="旗",nPriority=2,col="#00FFFFFF",colScreenHead="#00FFFF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nTime=30,szName="【{$receiver}】·拾取大旗",nFrame=8,nIcon=592,key="拾取大旗·{$receiver}",},{nClass=2,nTime=-1,szName="拾取大旗",nIcon=592,key="拾取大旗·{$receiver}",},},},</v>
+      </c>
+      <c r="AO34" s="36" t="s">
+        <v>2578</v>
+      </c>
+      <c r="AP34" s="36" t="s">
+        <v>2577</v>
       </c>
     </row>
     <row r="35" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C35" s="36">
-        <v>8477</v>
+      <c r="C35" s="40">
+        <v>7525</v>
       </c>
       <c r="D35" s="36">
         <v>1</v>
       </c>
-      <c r="F35" s="36">
-        <v>6491</v>
-      </c>
       <c r="G35" s="36" t="s">
-        <v>1647</v>
-      </c>
-      <c r="I35" s="36">
-        <v>1</v>
+        <v>2636</v>
       </c>
       <c r="K35" s="36" t="s">
-        <v>1650</v>
+        <v>1652</v>
+      </c>
+      <c r="L35" s="36" t="s">
+        <v>2115</v>
+      </c>
+      <c r="R35" s="36">
+        <v>1</v>
+      </c>
+      <c r="S35" s="36">
+        <v>1</v>
       </c>
       <c r="T35" s="36">
+        <v>1</v>
+      </c>
+      <c r="V35" s="36">
+        <v>1</v>
+      </c>
+      <c r="AE35" s="36" t="s">
+        <v>2023</v>
+      </c>
+      <c r="AF35" s="36">
+        <v>2</v>
+      </c>
+      <c r="AG35" s="36" t="s">
+        <v>2177</v>
+      </c>
+      <c r="AH35" s="36" t="s">
+        <v>2178</v>
+      </c>
+      <c r="AI35" s="36">
+        <v>255</v>
+      </c>
+      <c r="AL35" s="36">
         <v>1</v>
       </c>
       <c r="AN35" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=8477,nLevel=1,nIcon=6491,szName="劲足",nScrutinyType=1,szNote="速度·劲足",[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=6491,nFrame=6,szName="骑御·劲足",nTime=0.5,nRefresh=300,key="骑御·调息",},{nClass=2,nIcon=6491,nFrame=1,szName="劲足·已消失",nTime=3,nRefresh=5,key="骑御·劲足",},},},</v>
+        <v>{dwID=7525,nLevel=1,szName="占据点",szNote="据点大旗",col={0,255,255,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="旗",nPriority=2,col="#00FFFFFF",colScreenHead="#00FFFF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nTime=30,szName="【{$receiver}】·拾取大旗",nFrame=8,nIcon=592,key="拾取大旗·{$receiver}",},{nClass=2,nTime=-1,szName="拾取大旗",nIcon=592,key="拾取大旗·{$receiver}",},},},</v>
       </c>
       <c r="AO35" s="36" t="s">
-        <v>1782</v>
+        <v>2578</v>
       </c>
       <c r="AP35" s="36" t="s">
-        <v>2168</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="36" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C36" s="36">
-        <v>8607</v>
+      <c r="C36" s="40">
+        <v>7373</v>
       </c>
       <c r="D36" s="36">
         <v>1</v>
       </c>
+      <c r="F36" s="36">
+        <v>134</v>
+      </c>
+      <c r="G36" s="36" t="s">
+        <v>2390</v>
+      </c>
       <c r="I36" s="36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K36" s="36" t="s">
-        <v>1649</v>
-      </c>
-      <c r="T36" s="36">
+        <v>2389</v>
+      </c>
+      <c r="L36" s="36" t="s">
+        <v>1964</v>
+      </c>
+      <c r="R36" s="36">
         <v>1</v>
       </c>
       <c r="AN36" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=8607,nLevel=1,nScrutinyType=1,szNote="气力·调息",[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=6678,nFrame=6,szName="骑御·调息",nTime=0,key="骑御·调息",},},},</v>
-      </c>
-      <c r="AO36" s="36" t="s">
-        <v>1648</v>
+        <v>{dwID=7373,nLevel=1,nIcon=134,szName="箭弩车",nScrutinyType=3,szNote="箭弩车记录ID",col={255,50,255,},[1]={bScreenHead=true,},[2]={},},</v>
       </c>
     </row>
     <row r="37" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C37" s="36">
-        <v>244</v>
+      <c r="C37" s="40">
+        <v>7492</v>
       </c>
       <c r="D37" s="36">
         <v>1</v>
       </c>
-      <c r="H37" s="36">
-        <v>1</v>
+      <c r="G37" s="36" t="s">
+        <v>1785</v>
       </c>
       <c r="I37" s="36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K37" s="36" t="s">
-        <v>1651</v>
+        <v>1784</v>
+      </c>
+      <c r="L37" s="36" t="s">
+        <v>1527</v>
+      </c>
+      <c r="T37" s="36">
+        <v>1</v>
       </c>
       <c r="AN37" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=244,nLevel=1,bCheckLevel=true,nScrutinyType=1,szNote="骑御",[1]={},[2]={},tCountdown={{nClass=2,nIcon=6678,nFrame=6,szName="骑御·调息",nTime=-1,key="骑御·调息",},{nClass=1,nIcon=6678,nFrame=6,szName="骑御·调息",nTime="18.8,调息·7级·触发剩余;22.8,调息·5级·触发剩余",nRefresh=0,key="骑御·调息",},},},</v>
-      </c>
-      <c r="AO37" s="36" t="s">
-        <v>1646</v>
-      </c>
-      <c r="AP37" s="36" t="s">
-        <v>1821</v>
+        <v>{dwID=7492,nLevel=1,szName="御城矛",nScrutinyType=2,szNote="御城·矛",col={0,255,0,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="38" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="36" t="s">
-        <v>1767</v>
-      </c>
-      <c r="B38" s="36">
-        <v>214</v>
+      <c r="C38" s="40">
+        <v>8606</v>
+      </c>
+      <c r="D38" s="36">
+        <v>1</v>
+      </c>
+      <c r="G38" s="36" t="s">
+        <v>1915</v>
+      </c>
+      <c r="I38" s="36">
+        <v>1</v>
+      </c>
+      <c r="K38" s="36" t="s">
+        <v>1914</v>
+      </c>
+      <c r="T38" s="36">
+        <v>1</v>
       </c>
       <c r="AN38" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>},[214]={</v>
+        <v>{dwID=8606,nLevel=1,szName="抗摔",nScrutinyType=1,szNote="抗摔·强健",[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="39" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C39" s="36">
-        <v>10067</v>
-      </c>
-      <c r="D39" s="36">
-        <v>1</v>
-      </c>
-      <c r="G39" s="36" t="s">
-        <v>2310</v>
-      </c>
-      <c r="I39" s="36">
-        <v>1</v>
-      </c>
-      <c r="K39" s="36" t="s">
-        <v>2309</v>
-      </c>
-      <c r="L39" s="36" t="s">
-        <v>2311</v>
-      </c>
-      <c r="T39" s="36">
-        <v>1</v>
+      <c r="A39" s="36" t="s">
+        <v>613</v>
+      </c>
+      <c r="B39" s="36">
+        <v>656</v>
       </c>
       <c r="AN39" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=10067,nLevel=1,szName="补货点",nScrutinyType=1,szNote="阴山商路贸易区",col={255,150,0,},[1]={bBuffList=true,},[2]={},},</v>
+        <v>},[656]={</v>
       </c>
     </row>
     <row r="40" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C40" s="36">
-        <v>7508</v>
+      <c r="C40" s="40">
+        <v>7561</v>
       </c>
       <c r="D40" s="36">
         <v>1</v>
       </c>
-      <c r="I40" s="36">
-        <v>1</v>
+      <c r="G40" s="36" t="s">
+        <v>2635</v>
       </c>
       <c r="K40" s="36" t="s">
-        <v>2308</v>
+        <v>1653</v>
       </c>
       <c r="L40" s="36" t="s">
-        <v>2307</v>
+        <v>2115</v>
       </c>
       <c r="R40" s="36">
         <v>1</v>
       </c>
+      <c r="S40" s="36">
+        <v>1</v>
+      </c>
       <c r="T40" s="36">
+        <v>1</v>
+      </c>
+      <c r="V40" s="36">
+        <v>1</v>
+      </c>
+      <c r="AE40" s="36" t="s">
+        <v>2023</v>
+      </c>
+      <c r="AF40" s="36">
+        <v>2</v>
+      </c>
+      <c r="AG40" s="36" t="s">
+        <v>2177</v>
+      </c>
+      <c r="AH40" s="36" t="s">
+        <v>2178</v>
+      </c>
+      <c r="AI40" s="36">
+        <v>255</v>
+      </c>
+      <c r="AL40" s="36">
         <v>1</v>
       </c>
       <c r="AN40" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7508,nLevel=1,nScrutinyType=1,szNote="哑运",col={179,238,58,},[1]={bScreenHead=true,bBuffList=true,},[2]={},},</v>
+        <v>{dwID=7561,nLevel=1,szName="守据点",szNote="守卫据点",col={0,255,255,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="旗",nPriority=2,col="#00FFFFFF",colScreenHead="#00FFFF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nTime=30,szName="【{$receiver}】·拾取大旗",nFrame=8,nIcon=592,key="拾取大旗·{$receiver}",},{nClass=2,nTime=-1,szName="拾取大旗",nIcon=592,key="拾取大旗·{$receiver}",},},},</v>
+      </c>
+      <c r="AO40" s="36" t="s">
+        <v>2578</v>
+      </c>
+      <c r="AP40" s="36" t="s">
+        <v>2577</v>
       </c>
     </row>
     <row r="41" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="B41" s="36">
-        <v>217</v>
+      <c r="C41" s="40">
+        <v>7525</v>
+      </c>
+      <c r="D41" s="36">
+        <v>1</v>
+      </c>
+      <c r="G41" s="36" t="s">
+        <v>2636</v>
+      </c>
+      <c r="K41" s="36" t="s">
+        <v>1652</v>
+      </c>
+      <c r="L41" s="36" t="s">
+        <v>2115</v>
+      </c>
+      <c r="R41" s="36">
+        <v>1</v>
+      </c>
+      <c r="S41" s="36">
+        <v>1</v>
+      </c>
+      <c r="T41" s="36">
+        <v>1</v>
+      </c>
+      <c r="V41" s="36">
+        <v>1</v>
+      </c>
+      <c r="AE41" s="36" t="s">
+        <v>2023</v>
+      </c>
+      <c r="AF41" s="36">
+        <v>2</v>
+      </c>
+      <c r="AG41" s="36" t="s">
+        <v>2177</v>
+      </c>
+      <c r="AH41" s="36" t="s">
+        <v>2178</v>
+      </c>
+      <c r="AI41" s="36">
+        <v>255</v>
+      </c>
+      <c r="AL41" s="36">
+        <v>1</v>
       </c>
       <c r="AN41" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>},[217]={</v>
+        <v>{dwID=7525,nLevel=1,szName="占据点",szNote="据点大旗",col={0,255,255,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="旗",nPriority=2,col="#00FFFFFF",colScreenHead="#00FFFF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nTime=30,szName="【{$receiver}】·拾取大旗",nFrame=8,nIcon=592,key="拾取大旗·{$receiver}",},{nClass=2,nTime=-1,szName="拾取大旗",nIcon=592,key="拾取大旗·{$receiver}",},},},</v>
+      </c>
+      <c r="AO41" s="36" t="s">
+        <v>2578</v>
+      </c>
+      <c r="AP41" s="36" t="s">
+        <v>2577</v>
       </c>
     </row>
     <row r="42" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C42" s="36">
-        <v>7508</v>
+      <c r="C42" s="40">
+        <v>7373</v>
       </c>
       <c r="D42" s="36">
         <v>1</v>
       </c>
+      <c r="F42" s="36">
+        <v>134</v>
+      </c>
+      <c r="G42" s="36" t="s">
+        <v>2390</v>
+      </c>
       <c r="I42" s="36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K42" s="36" t="s">
-        <v>2308</v>
+        <v>2389</v>
       </c>
       <c r="L42" s="36" t="s">
-        <v>2307</v>
+        <v>1964</v>
       </c>
       <c r="R42" s="36">
-        <v>1</v>
-      </c>
-      <c r="T42" s="36">
         <v>1</v>
       </c>
       <c r="AN42" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7508,nLevel=1,nScrutinyType=1,szNote="哑运",col={179,238,58,},[1]={bScreenHead=true,bBuffList=true,},[2]={},},</v>
+        <v>{dwID=7373,nLevel=1,nIcon=134,szName="箭弩车",nScrutinyType=3,szNote="箭弩车记录ID",col={255,50,255,},[1]={bScreenHead=true,},[2]={},},</v>
       </c>
     </row>
     <row r="43" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="B43" s="36">
-        <v>216</v>
+      <c r="C43" s="40">
+        <v>7492</v>
+      </c>
+      <c r="D43" s="36">
+        <v>1</v>
+      </c>
+      <c r="G43" s="36" t="s">
+        <v>1785</v>
+      </c>
+      <c r="I43" s="36">
+        <v>2</v>
+      </c>
+      <c r="K43" s="36" t="s">
+        <v>1784</v>
+      </c>
+      <c r="L43" s="36" t="s">
+        <v>1527</v>
+      </c>
+      <c r="T43" s="36">
+        <v>1</v>
       </c>
       <c r="AN43" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>},[216]={</v>
+        <v>{dwID=7492,nLevel=1,szName="御城矛",nScrutinyType=2,szNote="御城·矛",col={0,255,0,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="44" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C44" s="36">
-        <v>10067</v>
+      <c r="C44" s="40">
+        <v>8606</v>
       </c>
       <c r="D44" s="36">
         <v>1</v>
       </c>
       <c r="G44" s="36" t="s">
-        <v>2310</v>
+        <v>1915</v>
       </c>
       <c r="I44" s="36">
         <v>1</v>
       </c>
       <c r="K44" s="36" t="s">
-        <v>2309</v>
-      </c>
-      <c r="L44" s="36" t="s">
-        <v>2311</v>
+        <v>1914</v>
       </c>
       <c r="T44" s="36">
         <v>1</v>
       </c>
       <c r="AN44" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=10067,nLevel=1,szName="补货点",nScrutinyType=1,szNote="阴山商路贸易区",col={255,150,0,},[1]={bBuffList=true,},[2]={},},</v>
-      </c>
-    </row>
-    <row r="45" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C45" s="36">
-        <v>7508</v>
-      </c>
-      <c r="D45" s="36">
-        <v>1</v>
-      </c>
-      <c r="I45" s="36">
-        <v>1</v>
-      </c>
-      <c r="K45" s="36" t="s">
-        <v>2308</v>
-      </c>
-      <c r="L45" s="36" t="s">
-        <v>2307</v>
-      </c>
-      <c r="R45" s="36">
-        <v>1</v>
-      </c>
-      <c r="T45" s="36">
-        <v>1</v>
-      </c>
+        <v>{dwID=8606,nLevel=1,szName="抗摔",nScrutinyType=1,szNote="抗摔·强健",[1]={bBuffList=true,},[2]={},},</v>
+      </c>
+    </row>
+    <row r="45" spans="1:42" x14ac:dyDescent="0.15">
       <c r="AN45" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7508,nLevel=1,nScrutinyType=1,szNote="哑运",col={179,238,58,},[1]={bScreenHead=true,bBuffList=true,},[2]={},},</v>
+        <v>},},}</v>
       </c>
     </row>
     <row r="46" spans="1:42" x14ac:dyDescent="0.15">
-      <c r="AN46" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>},},}</v>
-      </c>
-    </row>
-    <row r="47" spans="1:42" x14ac:dyDescent="0.15">
-      <c r="AN47" s="36"/>
+      <c r="AN46" s="36"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS46" xr:uid="{BE5AC9BD-489D-458A-B659-EC571E65401A}"/>
+  <autoFilter ref="A1:AS45" xr:uid="{BE5AC9BD-489D-458A-B659-EC571E65401A}"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -22048,7 +22036,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA35C877-1799-48AF-987C-71E994537D5C}">
-  <dimension ref="A1:BY95"/>
+  <dimension ref="A1:BY96"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="11" max="11" width="18.5" customWidth="1"/>
@@ -22246,7 +22234,7 @@
       <c r="AL2" s="36"/>
       <c r="AM2" s="36"/>
       <c r="AN2" s="36" t="str">
-        <f t="shared" ref="AN2:AN95" si="0">IF(B2&lt;&gt;"",IF(IFERROR(VALUE(C1),0)&lt;=0,"["&amp;B2&amp;"]={","},["&amp;B2&amp;"]={"),IF(C2&gt;0,"{dwID="&amp;C2&amp;","&amp;"nLevel="&amp;D2&amp;","&amp;IF(E2&gt;0,"nCount="&amp;E2&amp;",","")&amp;IF(F2&gt;0,"nIcon="&amp;F2&amp;",","")&amp;IF(G2&lt;&gt;"","szName="""&amp;G2&amp;""",","")&amp;IF(H2&gt;0,"bCheckLevel=true,","")&amp;IF(I2&gt;0,"nScrutinyType="&amp;I2&amp;",","")&amp;IF(J2&lt;&gt;"","tKungFu={"&amp;J2&amp;"},","")&amp;IF(K2&lt;&gt;"","szNote="""&amp;K2&amp;""",","")&amp;IF(L2&lt;&gt;"","col={"&amp;L2&amp;"},","")&amp;"[1]={"&amp;IF(M2&lt;&gt;"","tMark={"&amp;M2&amp;"},","")&amp;IF(N2&lt;&gt;"","szVoice="""&amp;N2&amp;""",","")&amp;IF(O2&gt;0,"bTeamChannel=true,","")&amp;IF(P2&gt;0,"bWhisperChannel=true,","")&amp;IF(Q2&gt;0,"bCenterAlarm=true,","")&amp;IF(R2&gt;0,"bScreenHead=true,","")&amp;IF(S2&gt;0,"bPartyBuffList=true,","")&amp;IF(T2&gt;0,"bBuffList=true,","")&amp;IF(U2&gt;0,"bFullScreen=true,","")&amp;IF(V2&gt;0,"bTeamPanel=true,","")&amp;IF(W2&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(X2&gt;0,"bTeamChannel=true,","")&amp;IF(Y2&gt;0,"bWhisperChannel=true,","")&amp;IF(Z2&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AA2&gt;0,AE2&lt;&gt;"",AF2&gt;0,AG2&lt;&gt;"",AH2&lt;&gt;"",AI2&gt;0,AJ2&gt;0,AK2&gt;0,AL2&gt;0),"aCataclysmBuff={{"&amp;IF(AA2&gt;0,"nStackNum="&amp;AA2&amp;",","")&amp;IF(AB2&lt;&gt;"","szStackOp="""&amp;AB2&amp;""",","")&amp;IF(AC2&gt;0,"bOnlyMine=true,","")&amp;IF(AD2&gt;0,"bOnlyMe=true,","")&amp;IF(AE2&lt;&gt;"","szReminder="""&amp;AE2&amp;""",","")&amp;IF(AF2&gt;0,"nPriority="&amp;AF2&amp;",","")&amp;IF(AG2&lt;&gt;"","col="""&amp;AG2&amp;""",","")&amp;IF(AH2&lt;&gt;"","colScreenHead="""&amp;AH2&amp;""",","")&amp;IF(AI2&gt;0,"nColAlpha="&amp;AI2&amp;",","")&amp;IF(AJ2&gt;0,"bAttention=true,","")&amp;IF(AK2&gt;0,"bCaution=true,","")&amp;IF(AL2&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AM2&amp;"},","")&amp;IF(AO2&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AO2:ZZ2)&amp;"},","")&amp;"},",IF(C1&gt;0,"},","")&amp;IF(AND(B2="",C2="",OR(B1&lt;&gt;"",C1&lt;&gt;"")),"},}","")))</f>
+        <f t="shared" ref="AN2:AN65" si="0">IF(B2&lt;&gt;"",IF(IFERROR(VALUE(C1),0)&lt;=0,"["&amp;B2&amp;"]={","},["&amp;B2&amp;"]={"),IF(C2&gt;0,"{dwID="&amp;C2&amp;","&amp;"nLevel="&amp;D2&amp;","&amp;IF(E2&gt;0,"nCount="&amp;E2&amp;",","")&amp;IF(F2&gt;0,"nIcon="&amp;F2&amp;",","")&amp;IF(G2&lt;&gt;"","szName="""&amp;G2&amp;""",","")&amp;IF(H2&gt;0,"bCheckLevel=true,","")&amp;IF(I2&gt;0,"nScrutinyType="&amp;I2&amp;",","")&amp;IF(J2&lt;&gt;"","tKungFu={"&amp;J2&amp;"},","")&amp;IF(K2&lt;&gt;"","szNote="""&amp;K2&amp;""",","")&amp;IF(L2&lt;&gt;"","col={"&amp;L2&amp;"},","")&amp;"[1]={"&amp;IF(M2&lt;&gt;"","tMark={"&amp;M2&amp;"},","")&amp;IF(N2&lt;&gt;"","szVoice="""&amp;N2&amp;""",","")&amp;IF(O2&gt;0,"bTeamChannel=true,","")&amp;IF(P2&gt;0,"bWhisperChannel=true,","")&amp;IF(Q2&gt;0,"bCenterAlarm=true,","")&amp;IF(R2&gt;0,"bScreenHead=true,","")&amp;IF(S2&gt;0,"bPartyBuffList=true,","")&amp;IF(T2&gt;0,"bBuffList=true,","")&amp;IF(U2&gt;0,"bFullScreen=true,","")&amp;IF(V2&gt;0,"bTeamPanel=true,","")&amp;IF(W2&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(X2&gt;0,"bTeamChannel=true,","")&amp;IF(Y2&gt;0,"bWhisperChannel=true,","")&amp;IF(Z2&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AA2&gt;0,AE2&lt;&gt;"",AF2&gt;0,AG2&lt;&gt;"",AH2&lt;&gt;"",AI2&gt;0,AJ2&gt;0,AK2&gt;0,AL2&gt;0),"aCataclysmBuff={{"&amp;IF(AA2&gt;0,"nStackNum="&amp;AA2&amp;",","")&amp;IF(AB2&lt;&gt;"","szStackOp="""&amp;AB2&amp;""",","")&amp;IF(AC2&gt;0,"bOnlyMine=true,","")&amp;IF(AD2&gt;0,"bOnlyMe=true,","")&amp;IF(AE2&lt;&gt;"","szReminder="""&amp;AE2&amp;""",","")&amp;IF(AF2&gt;0,"nPriority="&amp;AF2&amp;",","")&amp;IF(AG2&lt;&gt;"","col="""&amp;AG2&amp;""",","")&amp;IF(AH2&lt;&gt;"","colScreenHead="""&amp;AH2&amp;""",","")&amp;IF(AI2&gt;0,"nColAlpha="&amp;AI2&amp;",","")&amp;IF(AJ2&gt;0,"bAttention=true,","")&amp;IF(AK2&gt;0,"bCaution=true,","")&amp;IF(AL2&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AM2&amp;"},","")&amp;IF(AO2&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AO2:ZZ2)&amp;"},","")&amp;"},",IF(C1&gt;0,"},","")&amp;IF(AND(B2="",C2="",OR(B1&lt;&gt;"",C1&lt;&gt;"")),"},}","")))</f>
         <v>[-19]={</v>
       </c>
       <c r="AO2" s="36"/>
@@ -23459,7 +23447,7 @@
         <v>2084</v>
       </c>
     </row>
-    <row r="33" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C33" s="36">
         <v>11565</v>
       </c>
@@ -23486,7 +23474,7 @@
         <v>{dwID=11565,nLevel=1,nIcon=592,szName="大旗手",szNote="大旗手检测",col={0,255,255,},[1]={bScreenHead=true,},[2]={},},</v>
       </c>
     </row>
-    <row r="34" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C34" s="36">
         <v>32813</v>
       </c>
@@ -23534,7 +23522,7 @@
         <v>2708</v>
       </c>
     </row>
-    <row r="35" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C35" s="36">
         <v>32812</v>
       </c>
@@ -23564,7 +23552,7 @@
         <v>2710</v>
       </c>
     </row>
-    <row r="36" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C36" s="36">
         <v>31381</v>
       </c>
@@ -23615,7 +23603,7 @@
         <v>2727</v>
       </c>
     </row>
-    <row r="37" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C37" s="36">
         <v>8807</v>
       </c>
@@ -23675,7 +23663,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="38" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C38" s="36">
         <v>7913</v>
       </c>
@@ -23720,7 +23708,7 @@
         <v>{dwID=7913,nLevel=1,nScrutinyType=2,szNote="意涌系统通用抗百分比回血",col={255,204,0,},[1]={bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="涌",nPriority=5,col="#FFCC00FF",colScreenHead="#FFCC00",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
       </c>
     </row>
-    <row r="39" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C39" s="36">
         <v>7911</v>
       </c>
@@ -23768,7 +23756,7 @@
         <v>{dwID=7911,nLevel=1,nScrutinyType=2,szNote="繁忙",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="忙",nPriority=4,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
       </c>
     </row>
-    <row r="40" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C40" s="36">
         <v>7756</v>
       </c>
@@ -23810,7 +23798,7 @@
         <v>2080</v>
       </c>
     </row>
-    <row r="41" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C41" s="36">
         <v>7497</v>
       </c>
@@ -23858,7 +23846,7 @@
         <v>{dwID=7497,nLevel=1,szName="眩晕·抛掷",nScrutinyType=2,szNote="御城·抛掷",col={255,255,0,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="晕",nPriority=13,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
       </c>
     </row>
-    <row r="42" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C42" s="36">
         <v>7504</v>
       </c>
@@ -23906,7 +23894,7 @@
         <v>{dwID=7504,nLevel=1,szName="眩晕·御城",nScrutinyType=2,szNote="御城·精准",col={255,255,0,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="晕",nPriority=13,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
       </c>
     </row>
-    <row r="43" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C43" s="36">
         <v>7503</v>
       </c>
@@ -23948,7 +23936,7 @@
         <v>{dwID=7503,nLevel=1,szName="减速·御城",nScrutinyType=1,szNote="御城·断股",col={31,63,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=37,col="#1F3FFFAA",colScreenHead="#1F3FFF",nColAlpha=170,},},},</v>
       </c>
     </row>
-    <row r="44" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C44" s="36">
         <v>4038</v>
       </c>
@@ -23993,7 +23981,7 @@
         <v>{dwID=4038,nLevel=1,nScrutinyType=1,szNote="锁足·首领",col={31,63,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="锁",nPriority=15,col="#1F3FFFFF",colScreenHead="#1F3FFF",nColAlpha=255,bScreenHead=true,},},},</v>
       </c>
     </row>
-    <row r="45" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C45" s="36">
         <v>29007</v>
       </c>
@@ -24026,7 +24014,7 @@
         <v>2576</v>
       </c>
     </row>
-    <row r="46" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C46" s="36">
         <v>11561</v>
       </c>
@@ -24056,7 +24044,7 @@
       <c r="AQ46" s="39"/>
       <c r="AR46" s="39"/>
     </row>
-    <row r="47" spans="1:44" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:74" x14ac:dyDescent="0.15">
       <c r="C47">
         <v>7723</v>
       </c>
@@ -24093,267 +24081,163 @@
         <v>{dwID=7723,nLevel=1,nScrutinyType=2,szNote="神机雷",col={255,255,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=1,col="#FFFFFFAA",nColAlpha=170,},},},</v>
       </c>
     </row>
-    <row r="48" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:74" x14ac:dyDescent="0.15">
       <c r="A48" s="36" t="s">
-        <v>1819</v>
+        <v>1767</v>
       </c>
       <c r="B48" s="36">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AN48" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>},[216]={</v>
-      </c>
-    </row>
-    <row r="49" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+        <v>},[214]={</v>
+      </c>
+      <c r="BM48" s="36"/>
+      <c r="BN48" s="36"/>
+      <c r="BO48" s="36"/>
+      <c r="BP48" s="36"/>
+      <c r="BQ48" s="36"/>
+      <c r="BR48" s="36"/>
+      <c r="BS48" s="36"/>
+      <c r="BT48" s="36"/>
+      <c r="BU48" s="36"/>
+      <c r="BV48" s="36"/>
+    </row>
+    <row r="49" spans="1:41" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C49" s="36">
-        <v>11567</v>
+        <v>9992</v>
       </c>
       <c r="D49" s="36">
         <v>1</v>
       </c>
       <c r="F49" s="36">
-        <v>1245</v>
+        <v>8004</v>
       </c>
       <c r="G49" s="36" t="s">
-        <v>2091</v>
+        <v>2303</v>
       </c>
       <c r="I49" s="36">
         <v>1</v>
       </c>
       <c r="K49" s="36" t="s">
-        <v>1953</v>
+        <v>2304</v>
       </c>
       <c r="L49" s="36" t="s">
         <v>1781</v>
       </c>
+      <c r="T49" s="36">
+        <v>1</v>
+      </c>
       <c r="AN49" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=11567,nLevel=1,nIcon=1245,szName="答对",nScrutinyType=1,szNote="回答奖励",col={255,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,nFrame=1,szName="答题验证·回答正确",nTime=5,key="挂机检测",},},},</v>
-      </c>
-      <c r="AO49" s="36" t="s">
-        <v>2083</v>
-      </c>
-    </row>
-    <row r="50" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+        <v>{dwID=9992,nLevel=1,nIcon=8004,szName="大跑商",nScrutinyType=1,szNote="场景标记",col={255,255,0,},[1]={bBuffList=true,},[2]={},},</v>
+      </c>
+    </row>
+    <row r="50" spans="1:41" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C50" s="36">
-        <v>11559</v>
+        <v>9982</v>
       </c>
       <c r="D50" s="36">
         <v>1</v>
       </c>
-      <c r="F50" s="36">
-        <v>1244</v>
-      </c>
-      <c r="G50" s="36" t="s">
-        <v>1957</v>
-      </c>
       <c r="I50" s="36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K50" s="36" t="s">
-        <v>1954</v>
+        <v>2305</v>
       </c>
       <c r="L50" s="36" t="s">
-        <v>1964</v>
-      </c>
-      <c r="N50" s="36" t="s">
-        <v>1787</v>
-      </c>
-      <c r="O50" s="36">
-        <v>1</v>
-      </c>
-      <c r="P50" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q50" s="36">
-        <v>1</v>
-      </c>
-      <c r="R50" s="36">
-        <v>1</v>
-      </c>
-      <c r="T50" s="36">
-        <v>1</v>
-      </c>
-      <c r="U50" s="36">
-        <v>1</v>
-      </c>
-      <c r="V50" s="36">
-        <v>1</v>
+        <v>1667</v>
       </c>
       <c r="AE50" s="36" t="s">
-        <v>1973</v>
+        <v>2306</v>
       </c>
       <c r="AF50" s="36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG50" s="36" t="s">
-        <v>1955</v>
+        <v>1970</v>
       </c>
       <c r="AH50" s="36" t="s">
-        <v>1956</v>
+        <v>1970</v>
       </c>
       <c r="AI50" s="36">
         <v>255</v>
       </c>
-      <c r="AJ50" s="36">
-        <v>1</v>
-      </c>
-      <c r="AK50" s="36">
-        <v>1</v>
-      </c>
-      <c r="AL50" s="36">
-        <v>1</v>
-      </c>
       <c r="AN50" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=11559,nLevel=1,nIcon=1244,szName="答题",nScrutinyType=1,szNote="验证码答案",col={255,50,255,},[1]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bScreenHead=true,bBuffList=true,bFullScreen=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="题",nPriority=3,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bAttention=true,bCaution=true,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=1,szName="答题验证·剩余时间",nTime=30,key="挂机检测",},},},</v>
-      </c>
-      <c r="AO50" s="36" t="s">
-        <v>2084</v>
-      </c>
-    </row>
-    <row r="51" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+        <v>{dwID=9982,nLevel=1,nScrutinyType=2,szNote="运货首领",col={255,255,255,},[1]={},[2]={},aCataclysmBuff={{szReminder="镖",nPriority=2,col="#FFFFFFFF",colScreenHead="#FFFFFFFF",nColAlpha=255,},},},</v>
+      </c>
+    </row>
+    <row r="51" spans="1:41" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C51" s="36">
-        <v>11565</v>
+        <v>7851</v>
       </c>
       <c r="D51" s="36">
         <v>1</v>
       </c>
-      <c r="F51" s="36">
-        <v>592</v>
-      </c>
-      <c r="G51" s="36" t="s">
-        <v>2387</v>
+      <c r="I51" s="36">
+        <v>1</v>
       </c>
       <c r="K51" s="36" t="s">
-        <v>2388</v>
+        <v>2564</v>
       </c>
       <c r="L51" s="36" t="s">
-        <v>2115</v>
-      </c>
-      <c r="R51" s="36">
+        <v>2312</v>
+      </c>
+      <c r="T51" s="36">
         <v>1</v>
       </c>
       <c r="AN51" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=11565,nLevel=1,nIcon=592,szName="大旗手",szNote="大旗手检测",col={0,255,255,},[1]={bScreenHead=true,},[2]={},},</v>
-      </c>
-    </row>
-    <row r="52" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C52" s="36">
-        <v>31381</v>
-      </c>
-      <c r="D52" s="36">
-        <v>1</v>
-      </c>
-      <c r="G52" s="36" t="s">
-        <v>2563</v>
-      </c>
-      <c r="K52" s="36" t="s">
-        <v>2385</v>
-      </c>
-      <c r="L52" s="36" t="s">
-        <v>1964</v>
-      </c>
-      <c r="R52" s="36">
-        <v>1</v>
-      </c>
-      <c r="T52" s="36">
-        <v>1</v>
-      </c>
-      <c r="AE52" s="36" t="s">
-        <v>2579</v>
-      </c>
-      <c r="AF52" s="36">
-        <v>11</v>
-      </c>
-      <c r="AG52" s="36" t="s">
-        <v>1955</v>
-      </c>
-      <c r="AH52" s="36" t="s">
-        <v>1956</v>
-      </c>
-      <c r="AI52" s="36">
-        <v>255</v>
-      </c>
-      <c r="AL52" s="36">
-        <v>1</v>
+        <v>{dwID=7851,nLevel=1,nScrutinyType=1,szNote="追踪·减速50%",col={31,63,255,},[1]={bBuffList=true,},[2]={},},</v>
+      </c>
+    </row>
+    <row r="52" spans="1:41" x14ac:dyDescent="0.15">
+      <c r="A52" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B52" s="36">
+        <v>217</v>
       </c>
       <c r="AN52" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=31381,nLevel=1,szName="禁捡旗",szNote="无法拾取大旗",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="捡",nPriority=11,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=2,szName="【{$receiver}】·禁止捡旗",nTime="30,【{$receiver}】·禁止捡旗;32,【{$receiver}】·可以捡旗",nRefresh=1,key="经脉逆行·{$receiver}",},{nClass=2,nIcon=13,nFrame=2,szName="【{$receiver}】·可以捡旗",nTime=5,key="经脉逆行·{$receiver}",},},},</v>
-      </c>
-      <c r="AO52" s="36" t="s">
-        <v>2690</v>
-      </c>
-      <c r="AP52" s="36" t="s">
-        <v>2391</v>
-      </c>
-    </row>
-    <row r="53" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+        <v>},[217]={</v>
+      </c>
+    </row>
+    <row r="53" spans="1:41" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C53" s="36">
-        <v>8807</v>
+        <v>9992</v>
       </c>
       <c r="D53" s="36">
         <v>1</v>
       </c>
+      <c r="F53" s="36">
+        <v>8004</v>
+      </c>
       <c r="G53" s="36" t="s">
-        <v>1966</v>
+        <v>2303</v>
       </c>
       <c r="I53" s="36">
         <v>1</v>
       </c>
       <c r="K53" s="36" t="s">
-        <v>1967</v>
+        <v>2304</v>
       </c>
       <c r="L53" s="36" t="s">
-        <v>1964</v>
-      </c>
-      <c r="N53" s="36" t="s">
-        <v>1787</v>
-      </c>
-      <c r="O53" s="36">
-        <v>1</v>
-      </c>
-      <c r="P53" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q53" s="36">
-        <v>1</v>
+        <v>1781</v>
       </c>
       <c r="T53" s="36">
-        <v>1</v>
-      </c>
-      <c r="U53" s="36">
-        <v>1</v>
-      </c>
-      <c r="AE53" s="36" t="s">
-        <v>1972</v>
-      </c>
-      <c r="AF53" s="36">
-        <v>2</v>
-      </c>
-      <c r="AG53" s="36" t="s">
-        <v>1955</v>
-      </c>
-      <c r="AI53" s="36">
-        <v>255</v>
-      </c>
-      <c r="AJ53" s="36">
         <v>1</v>
       </c>
       <c r="AN53" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=8807,nLevel=1,szName="注视",nScrutinyType=1,szNote="据点挂机",col={255,50,255,},[1]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bBuffList=true,bFullScreen=true,},[2]={},aCataclysmBuff={{szReminder="视",nPriority=2,col="#FF32FFFF",nColAlpha=255,bAttention=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=2,szName="挂机检测·首领注视",nTime=30,key="挂机检测",},},},</v>
-      </c>
-      <c r="AO53" s="36" t="s">
-        <v>2082</v>
-      </c>
-    </row>
-    <row r="54" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+        <v>{dwID=9992,nLevel=1,nIcon=8004,szName="大跑商",nScrutinyType=1,szNote="场景标记",col={255,255,0,},[1]={bBuffList=true,},[2]={},},</v>
+      </c>
+    </row>
+    <row r="54" spans="1:41" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C54" s="36">
-        <v>7913</v>
+        <v>9982</v>
       </c>
       <c r="D54" s="36">
         <v>1</v>
@@ -24362,541 +24246,511 @@
         <v>2</v>
       </c>
       <c r="K54" s="36" t="s">
-        <v>1833</v>
+        <v>2305</v>
       </c>
       <c r="L54" s="36" t="s">
-        <v>1830</v>
-      </c>
-      <c r="T54" s="36">
-        <v>1</v>
+        <v>1667</v>
       </c>
       <c r="AE54" s="36" t="s">
-        <v>2374</v>
+        <v>2306</v>
       </c>
       <c r="AF54" s="36">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG54" s="36" t="s">
-        <v>1832</v>
+        <v>1970</v>
       </c>
       <c r="AH54" s="36" t="s">
-        <v>1831</v>
+        <v>1970</v>
       </c>
       <c r="AI54" s="36">
         <v>255</v>
       </c>
-      <c r="AJ54" s="36">
-        <v>1</v>
-      </c>
-      <c r="AL54" s="36">
-        <v>1</v>
-      </c>
       <c r="AN54" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7913,nLevel=1,nScrutinyType=2,szNote="意涌系统通用抗百分比回血",col={255,204,0,},[1]={bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="涌",nPriority=5,col="#FFCC00FF",colScreenHead="#FFCC00",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
-      </c>
-    </row>
-    <row r="55" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+        <v>{dwID=9982,nLevel=1,nScrutinyType=2,szNote="运货首领",col={255,255,255,},[1]={},[2]={},aCataclysmBuff={{szReminder="镖",nPriority=2,col="#FFFFFFFF",colScreenHead="#FFFFFFFF",nColAlpha=255,},},},</v>
+      </c>
+    </row>
+    <row r="55" spans="1:41" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C55" s="36">
-        <v>7911</v>
+        <v>7851</v>
       </c>
       <c r="D55" s="36">
         <v>1</v>
       </c>
       <c r="I55" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K55" s="36" t="s">
-        <v>1947</v>
+        <v>2564</v>
       </c>
       <c r="L55" s="36" t="s">
-        <v>1964</v>
-      </c>
-      <c r="R55" s="36">
-        <v>1</v>
+        <v>2312</v>
       </c>
       <c r="T55" s="36">
-        <v>1</v>
-      </c>
-      <c r="AE55" s="36" t="s">
-        <v>1974</v>
-      </c>
-      <c r="AF55" s="36">
-        <v>4</v>
-      </c>
-      <c r="AG55" s="36" t="s">
-        <v>1955</v>
-      </c>
-      <c r="AH55" s="36" t="s">
-        <v>1956</v>
-      </c>
-      <c r="AI55" s="36">
-        <v>255</v>
-      </c>
-      <c r="AJ55" s="36">
-        <v>1</v>
-      </c>
-      <c r="AL55" s="36">
         <v>1</v>
       </c>
       <c r="AN55" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7911,nLevel=1,nScrutinyType=2,szNote="繁忙",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="忙",nPriority=4,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
-      </c>
-    </row>
-    <row r="56" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C56" s="36">
-        <v>7756</v>
-      </c>
-      <c r="D56" s="36">
-        <v>1</v>
-      </c>
-      <c r="I56" s="36">
-        <v>1</v>
-      </c>
-      <c r="K56" s="36" t="s">
-        <v>2038</v>
-      </c>
-      <c r="L56" s="36" t="s">
-        <v>1781</v>
-      </c>
-      <c r="T56" s="36">
-        <v>1</v>
-      </c>
-      <c r="AE56" s="36" t="s">
-        <v>2039</v>
-      </c>
-      <c r="AF56" s="36">
-        <v>3</v>
-      </c>
-      <c r="AG56" s="36" t="s">
-        <v>2637</v>
-      </c>
-      <c r="AI56" s="36">
-        <v>0</v>
+        <v>{dwID=7851,nLevel=1,nScrutinyType=1,szNote="追踪·减速50%",col={31,63,255,},[1]={bBuffList=true,},[2]={},},</v>
+      </c>
+    </row>
+    <row r="56" spans="1:41" x14ac:dyDescent="0.15">
+      <c r="A56" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B56" s="36">
+        <v>216</v>
       </c>
       <c r="AN56" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7756,nLevel=1,nScrutinyType=1,szNote="燃火20s",col={255,255,0,},[1]={bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="火",nPriority=3,col="#00FFFF00",},},tCountdown={{nClass=1,nIcon=5399,nFrame=0,szName="增益·燃火·持续剩余",nTime=20,key="燃火",},{nClass=2,nIcon=13,szName="燃火",nTime=-1,key="燃火",},},},</v>
-      </c>
-      <c r="AO56" s="36" t="s">
-        <v>2079</v>
-      </c>
-      <c r="AP56" s="36" t="s">
-        <v>2080</v>
-      </c>
-    </row>
-    <row r="57" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+        <v>},[216]={</v>
+      </c>
+    </row>
+    <row r="57" spans="1:41" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C57" s="36">
-        <v>7497</v>
+        <v>9992</v>
       </c>
       <c r="D57" s="36">
         <v>1</v>
       </c>
+      <c r="F57" s="36">
+        <v>8004</v>
+      </c>
       <c r="G57" s="36" t="s">
-        <v>2041</v>
+        <v>2303</v>
       </c>
       <c r="I57" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K57" s="36" t="s">
-        <v>2040</v>
+        <v>2304</v>
       </c>
       <c r="L57" s="36" t="s">
         <v>1781</v>
       </c>
-      <c r="R57" s="36">
-        <v>1</v>
-      </c>
       <c r="T57" s="36">
-        <v>1</v>
-      </c>
-      <c r="AE57" s="36" t="s">
-        <v>2042</v>
-      </c>
-      <c r="AF57" s="36">
-        <v>13</v>
-      </c>
-      <c r="AG57" s="36" t="s">
-        <v>2043</v>
-      </c>
-      <c r="AH57" s="36" t="s">
-        <v>2044</v>
-      </c>
-      <c r="AI57" s="36">
-        <v>255</v>
-      </c>
-      <c r="AL57" s="36">
         <v>1</v>
       </c>
       <c r="AN57" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7497,nLevel=1,szName="眩晕·抛掷",nScrutinyType=2,szNote="御城·抛掷",col={255,255,0,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="晕",nPriority=13,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
-      </c>
-    </row>
-    <row r="58" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+        <v>{dwID=9992,nLevel=1,nIcon=8004,szName="大跑商",nScrutinyType=1,szNote="场景标记",col={255,255,0,},[1]={bBuffList=true,},[2]={},},</v>
+      </c>
+    </row>
+    <row r="58" spans="1:41" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C58" s="36">
-        <v>7504</v>
+        <v>9982</v>
       </c>
       <c r="D58" s="36">
         <v>1</v>
-      </c>
-      <c r="G58" s="36" t="s">
-        <v>2167</v>
       </c>
       <c r="I58" s="36">
         <v>2</v>
       </c>
       <c r="K58" s="36" t="s">
-        <v>2166</v>
+        <v>2305</v>
       </c>
       <c r="L58" s="36" t="s">
-        <v>1781</v>
-      </c>
-      <c r="R58" s="36">
-        <v>1</v>
-      </c>
-      <c r="T58" s="36">
-        <v>1</v>
+        <v>1667</v>
       </c>
       <c r="AE58" s="36" t="s">
-        <v>2042</v>
+        <v>2306</v>
       </c>
       <c r="AF58" s="36">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AG58" s="36" t="s">
-        <v>2043</v>
+        <v>1970</v>
       </c>
       <c r="AH58" s="36" t="s">
-        <v>2044</v>
+        <v>1970</v>
       </c>
       <c r="AI58" s="36">
         <v>255</v>
       </c>
-      <c r="AL58" s="36">
-        <v>1</v>
-      </c>
       <c r="AN58" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7504,nLevel=1,szName="眩晕·御城",nScrutinyType=2,szNote="御城·精准",col={255,255,0,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="晕",nPriority=13,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
-      </c>
-    </row>
-    <row r="59" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+        <v>{dwID=9982,nLevel=1,nScrutinyType=2,szNote="运货首领",col={255,255,255,},[1]={},[2]={},aCataclysmBuff={{szReminder="镖",nPriority=2,col="#FFFFFFFF",colScreenHead="#FFFFFFFF",nColAlpha=255,},},},</v>
+      </c>
+    </row>
+    <row r="59" spans="1:41" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C59" s="36">
-        <v>7503</v>
+        <v>7851</v>
       </c>
       <c r="D59" s="36">
         <v>1</v>
       </c>
-      <c r="G59" s="36" t="s">
-        <v>2509</v>
-      </c>
       <c r="I59" s="36">
         <v>1</v>
       </c>
       <c r="K59" s="36" t="s">
-        <v>2510</v>
+        <v>2564</v>
       </c>
       <c r="L59" s="36" t="s">
-        <v>2361</v>
+        <v>2312</v>
       </c>
       <c r="T59" s="36">
         <v>1</v>
-      </c>
-      <c r="V59" s="36">
-        <v>1</v>
-      </c>
-      <c r="AF59" s="36">
-        <v>37</v>
-      </c>
-      <c r="AG59" s="36" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AH59" s="36" t="s">
-        <v>2364</v>
-      </c>
-      <c r="AI59" s="36">
-        <v>170</v>
       </c>
       <c r="AN59" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7503,nLevel=1,szName="减速·御城",nScrutinyType=1,szNote="御城·断股",col={31,63,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=37,col="#1F3FFFAA",colScreenHead="#1F3FFF",nColAlpha=170,},},},</v>
-      </c>
-    </row>
-    <row r="60" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C60" s="36">
-        <v>4038</v>
+        <v>{dwID=7851,nLevel=1,nScrutinyType=1,szNote="追踪·减速50%",col={31,63,255,},[1]={bBuffList=true,},[2]={},},</v>
+      </c>
+    </row>
+    <row r="60" spans="1:41" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C60" s="40">
+        <v>11567</v>
       </c>
       <c r="D60" s="36">
         <v>1</v>
       </c>
+      <c r="F60" s="36">
+        <v>1245</v>
+      </c>
+      <c r="G60" s="36" t="s">
+        <v>2091</v>
+      </c>
       <c r="I60" s="36">
         <v>1</v>
       </c>
       <c r="K60" s="36" t="s">
-        <v>2365</v>
+        <v>1953</v>
       </c>
       <c r="L60" s="36" t="s">
-        <v>2361</v>
-      </c>
-      <c r="R60" s="36">
-        <v>1</v>
-      </c>
-      <c r="T60" s="36">
-        <v>1</v>
-      </c>
-      <c r="AE60" s="36" t="s">
-        <v>2362</v>
-      </c>
-      <c r="AF60" s="36">
-        <v>15</v>
-      </c>
-      <c r="AG60" s="36" t="s">
-        <v>2363</v>
-      </c>
-      <c r="AH60" s="36" t="s">
-        <v>2364</v>
-      </c>
-      <c r="AI60" s="36">
-        <v>255</v>
-      </c>
-      <c r="AL60" s="36">
-        <v>1</v>
+        <v>1781</v>
       </c>
       <c r="AN60" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=4038,nLevel=1,nScrutinyType=1,szNote="锁足·首领",col={31,63,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="锁",nPriority=15,col="#1F3FFFFF",colScreenHead="#1F3FFF",nColAlpha=255,bScreenHead=true,},},},</v>
-      </c>
-    </row>
-    <row r="61" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C61" s="36">
-        <v>1499</v>
+        <v>{dwID=11567,nLevel=1,nIcon=1245,szName="答对",nScrutinyType=1,szNote="回答奖励",col={255,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,nFrame=1,szName="答题验证·回答正确",nTime=5,key="挂机检测",},},},</v>
+      </c>
+      <c r="AO60" s="36" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="61" spans="1:41" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C61" s="40">
+        <v>11559</v>
       </c>
       <c r="D61" s="36">
         <v>1</v>
       </c>
+      <c r="F61" s="36">
+        <v>1244</v>
+      </c>
       <c r="G61" s="36" t="s">
-        <v>2375</v>
+        <v>1957</v>
       </c>
       <c r="I61" s="36">
         <v>1</v>
       </c>
       <c r="K61" s="36" t="s">
-        <v>2365</v>
+        <v>1954</v>
       </c>
       <c r="L61" s="36" t="s">
-        <v>2361</v>
+        <v>1964</v>
+      </c>
+      <c r="N61" s="36" t="s">
+        <v>1787</v>
+      </c>
+      <c r="O61" s="36">
+        <v>1</v>
+      </c>
+      <c r="P61" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q61" s="36">
+        <v>1</v>
       </c>
       <c r="R61" s="36">
         <v>1</v>
       </c>
       <c r="T61" s="36">
+        <v>1</v>
+      </c>
+      <c r="U61" s="36">
+        <v>1</v>
+      </c>
+      <c r="V61" s="36">
+        <v>1</v>
+      </c>
+      <c r="AE61" s="36" t="s">
+        <v>1973</v>
+      </c>
+      <c r="AF61" s="36">
+        <v>3</v>
+      </c>
+      <c r="AG61" s="36" t="s">
+        <v>1955</v>
+      </c>
+      <c r="AH61" s="36" t="s">
+        <v>1956</v>
+      </c>
+      <c r="AI61" s="36">
+        <v>255</v>
+      </c>
+      <c r="AJ61" s="36">
+        <v>1</v>
+      </c>
+      <c r="AK61" s="36">
+        <v>1</v>
+      </c>
+      <c r="AL61" s="36">
         <v>1</v>
       </c>
       <c r="AN61" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=1499,nLevel=1,szName="锁足·呔",nScrutinyType=1,szNote="锁足·首领",col={31,63,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},},</v>
-      </c>
-    </row>
-    <row r="62" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C62" s="36">
-        <v>29007</v>
+        <v>{dwID=11559,nLevel=1,nIcon=1244,szName="答题",nScrutinyType=1,szNote="验证码答案",col={255,50,255,},[1]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bScreenHead=true,bBuffList=true,bFullScreen=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="题",nPriority=3,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bAttention=true,bCaution=true,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=1,szName="答题验证·剩余时间",nTime=30,key="挂机检测",},},},</v>
+      </c>
+      <c r="AO61" s="36" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="62" spans="1:41" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C62" s="40">
+        <v>11565</v>
       </c>
       <c r="D62" s="36">
         <v>1</v>
       </c>
-      <c r="I62" s="36">
-        <v>1</v>
+      <c r="F62" s="36">
+        <v>592</v>
+      </c>
+      <c r="G62" s="36" t="s">
+        <v>2387</v>
       </c>
       <c r="K62" s="36" t="s">
-        <v>2160</v>
+        <v>2388</v>
       </c>
       <c r="L62" s="36" t="s">
-        <v>2386</v>
+        <v>2115</v>
+      </c>
+      <c r="R62" s="36">
+        <v>1</v>
       </c>
       <c r="AN62" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29007,nLevel=1,nScrutinyType=1,szNote="九素化生·伤害距离",col={128,238,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=1,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=1,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=1,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=1,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=1,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=1,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=1,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=1,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=1,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=1,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=1,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=1,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},{nClass=2,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=2,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=2,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=2,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=2,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=2,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=2,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=2,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=2,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=2,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=2,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=2,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=2,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
-      </c>
-      <c r="AO62" s="40" t="s">
-        <v>2409</v>
-      </c>
-      <c r="AP62" s="40" t="s">
-        <v>2408</v>
-      </c>
-      <c r="AQ62" s="38" t="s">
-        <v>2575</v>
-      </c>
-      <c r="AR62" s="38" t="s">
-        <v>2576</v>
-      </c>
-    </row>
-    <row r="63" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C63" s="36">
-        <v>11561</v>
+        <v>{dwID=11565,nLevel=1,nIcon=592,szName="大旗手",szNote="大旗手检测",col={0,255,255,},[1]={bScreenHead=true,},[2]={},},</v>
+      </c>
+    </row>
+    <row r="63" spans="1:41" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C63" s="40">
+        <v>32813</v>
       </c>
       <c r="D63" s="36">
         <v>1</v>
       </c>
+      <c r="F63" s="36">
+        <v>16834</v>
+      </c>
       <c r="G63" s="36" t="s">
-        <v>2586</v>
-      </c>
-      <c r="I63" s="36">
-        <v>1</v>
+        <v>2704</v>
       </c>
       <c r="K63" s="36" t="s">
-        <v>2588</v>
+        <v>2699</v>
       </c>
       <c r="L63" s="36" t="s">
-        <v>2587</v>
+        <v>2701</v>
+      </c>
+      <c r="T63" s="36">
+        <v>1</v>
+      </c>
+      <c r="V63" s="36">
+        <v>1</v>
+      </c>
+      <c r="AE63" s="36" t="s">
+        <v>2700</v>
+      </c>
+      <c r="AF63" s="36">
+        <v>37</v>
+      </c>
+      <c r="AG63" s="36" t="s">
+        <v>2702</v>
+      </c>
+      <c r="AH63" s="36" t="s">
+        <v>2703</v>
+      </c>
+      <c r="AI63" s="36">
+        <v>255</v>
       </c>
       <c r="AN63" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=11561,nLevel=1,szName="据点内",nScrutinyType=1,szNote="判断是否在大旗附近",col={80,231,236,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=1272,nFrame=2,szName="据点大旗·旗手提示",nTime=-1,key="据点大旗·旗手提示",},},},</v>
+        <v>{dwID=32813,nLevel=1,nIcon=16834,szName="旗易伤",szNote="旗帜受损",col={255,153,204,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="损",nPriority=37,col="#FF99CCFF",colScreenHead="#FF99CC",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=1,key="大旗赛点·CD",},},},</v>
       </c>
       <c r="AO63" s="36" t="s">
-        <v>2730</v>
-      </c>
-      <c r="AP63" s="39"/>
-      <c r="AQ63" s="39"/>
-      <c r="AR63" s="39"/>
-    </row>
-    <row r="64" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C64" s="36">
-        <v>7723</v>
+        <v>2708</v>
+      </c>
+    </row>
+    <row r="64" spans="1:41" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C64" s="40">
+        <v>32812</v>
       </c>
       <c r="D64" s="36">
         <v>1</v>
       </c>
-      <c r="I64" s="36">
-        <v>2</v>
+      <c r="F64" s="36">
+        <v>3451</v>
+      </c>
+      <c r="G64" s="36" t="s">
+        <v>2705</v>
       </c>
       <c r="K64" s="36" t="s">
-        <v>1797</v>
+        <v>2706</v>
       </c>
       <c r="L64" s="36" t="s">
-        <v>1667</v>
+        <v>2707</v>
       </c>
       <c r="T64" s="36">
         <v>1</v>
-      </c>
-      <c r="V64" s="36">
-        <v>1</v>
-      </c>
-      <c r="AF64" s="36">
-        <v>1</v>
-      </c>
-      <c r="AG64" s="36" t="s">
-        <v>2491</v>
-      </c>
-      <c r="AI64" s="36">
-        <v>170</v>
       </c>
       <c r="AN64" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7723,nLevel=1,nScrutinyType=2,szNote="神机雷",col={255,255,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=1,col="#FFFFFFAA",nColAlpha=170,},},},</v>
+        <v>{dwID=32812,nLevel=1,nIcon=3451,szName="损CD",szNote="据点大旗赛点CD",col={255,50,50,},[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=0,key="大旗赛点·CD",},},},</v>
+      </c>
+      <c r="AO64" s="36" t="s">
+        <v>2710</v>
       </c>
     </row>
     <row r="65" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A65" s="36" t="s">
-        <v>613</v>
-      </c>
-      <c r="B65" s="36">
-        <v>656</v>
+      <c r="C65" s="40">
+        <v>31381</v>
+      </c>
+      <c r="D65" s="36">
+        <v>1</v>
+      </c>
+      <c r="G65" s="36" t="s">
+        <v>2563</v>
+      </c>
+      <c r="K65" s="36" t="s">
+        <v>2385</v>
+      </c>
+      <c r="L65" s="36" t="s">
+        <v>1964</v>
+      </c>
+      <c r="R65" s="36">
+        <v>1</v>
+      </c>
+      <c r="T65" s="36">
+        <v>1</v>
+      </c>
+      <c r="AE65" s="36" t="s">
+        <v>2579</v>
+      </c>
+      <c r="AF65" s="36">
+        <v>11</v>
+      </c>
+      <c r="AG65" s="36" t="s">
+        <v>1955</v>
+      </c>
+      <c r="AH65" s="36" t="s">
+        <v>1956</v>
+      </c>
+      <c r="AI65" s="36">
+        <v>255</v>
+      </c>
+      <c r="AL65" s="36">
+        <v>1</v>
       </c>
       <c r="AN65" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>},[656]={</v>
+        <v>{dwID=31381,nLevel=1,szName="禁捡旗",szNote="无法拾取大旗",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="捡",nPriority=11,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=2,szName="【{$receiver}】·禁止捡旗",nTime="30,【{$receiver}】·禁止捡旗;32,【{$receiver}】·可以捡旗",nRefresh=1,key="经脉逆行·{$receiver}",},{nClass=2,nIcon=13,nFrame=2,szName="【{$receiver}】·可以捡旗",nTime=5,key="经脉逆行·{$receiver}",},},},</v>
+      </c>
+      <c r="AO65" s="36" t="s">
+        <v>2690</v>
+      </c>
+      <c r="AP65" s="36" t="s">
+        <v>2391</v>
       </c>
     </row>
     <row r="66" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C66" s="36">
-        <v>11567</v>
+      <c r="C66" s="40">
+        <v>8807</v>
       </c>
       <c r="D66" s="36">
         <v>1</v>
       </c>
-      <c r="F66" s="36">
-        <v>1245</v>
-      </c>
       <c r="G66" s="36" t="s">
-        <v>2091</v>
+        <v>1966</v>
       </c>
       <c r="I66" s="36">
         <v>1</v>
       </c>
       <c r="K66" s="36" t="s">
-        <v>1953</v>
+        <v>1967</v>
       </c>
       <c r="L66" s="36" t="s">
-        <v>1781</v>
+        <v>1964</v>
+      </c>
+      <c r="N66" s="36" t="s">
+        <v>1787</v>
+      </c>
+      <c r="O66" s="36">
+        <v>1</v>
+      </c>
+      <c r="P66" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q66" s="36">
+        <v>1</v>
+      </c>
+      <c r="T66" s="36">
+        <v>1</v>
+      </c>
+      <c r="U66" s="36">
+        <v>1</v>
+      </c>
+      <c r="AE66" s="36" t="s">
+        <v>1972</v>
+      </c>
+      <c r="AF66" s="36">
+        <v>2</v>
+      </c>
+      <c r="AG66" s="36" t="s">
+        <v>1955</v>
+      </c>
+      <c r="AI66" s="36">
+        <v>255</v>
+      </c>
+      <c r="AJ66" s="36">
+        <v>1</v>
       </c>
       <c r="AN66" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=11567,nLevel=1,nIcon=1245,szName="答对",nScrutinyType=1,szNote="回答奖励",col={255,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,nFrame=1,szName="答题验证·回答正确",nTime=5,key="挂机检测",},},},</v>
+        <f t="shared" ref="AN66:AN95" si="1">IF(B66&lt;&gt;"",IF(IFERROR(VALUE(C65),0)&lt;=0,"["&amp;B66&amp;"]={","},["&amp;B66&amp;"]={"),IF(C66&gt;0,"{dwID="&amp;C66&amp;","&amp;"nLevel="&amp;D66&amp;","&amp;IF(E66&gt;0,"nCount="&amp;E66&amp;",","")&amp;IF(F66&gt;0,"nIcon="&amp;F66&amp;",","")&amp;IF(G66&lt;&gt;"","szName="""&amp;G66&amp;""",","")&amp;IF(H66&gt;0,"bCheckLevel=true,","")&amp;IF(I66&gt;0,"nScrutinyType="&amp;I66&amp;",","")&amp;IF(J66&lt;&gt;"","tKungFu={"&amp;J66&amp;"},","")&amp;IF(K66&lt;&gt;"","szNote="""&amp;K66&amp;""",","")&amp;IF(L66&lt;&gt;"","col={"&amp;L66&amp;"},","")&amp;"[1]={"&amp;IF(M66&lt;&gt;"","tMark={"&amp;M66&amp;"},","")&amp;IF(N66&lt;&gt;"","szVoice="""&amp;N66&amp;""",","")&amp;IF(O66&gt;0,"bTeamChannel=true,","")&amp;IF(P66&gt;0,"bWhisperChannel=true,","")&amp;IF(Q66&gt;0,"bCenterAlarm=true,","")&amp;IF(R66&gt;0,"bScreenHead=true,","")&amp;IF(S66&gt;0,"bPartyBuffList=true,","")&amp;IF(T66&gt;0,"bBuffList=true,","")&amp;IF(U66&gt;0,"bFullScreen=true,","")&amp;IF(V66&gt;0,"bTeamPanel=true,","")&amp;IF(W66&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(X66&gt;0,"bTeamChannel=true,","")&amp;IF(Y66&gt;0,"bWhisperChannel=true,","")&amp;IF(Z66&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AA66&gt;0,AE66&lt;&gt;"",AF66&gt;0,AG66&lt;&gt;"",AH66&lt;&gt;"",AI66&gt;0,AJ66&gt;0,AK66&gt;0,AL66&gt;0),"aCataclysmBuff={{"&amp;IF(AA66&gt;0,"nStackNum="&amp;AA66&amp;",","")&amp;IF(AB66&lt;&gt;"","szStackOp="""&amp;AB66&amp;""",","")&amp;IF(AC66&gt;0,"bOnlyMine=true,","")&amp;IF(AD66&gt;0,"bOnlyMe=true,","")&amp;IF(AE66&lt;&gt;"","szReminder="""&amp;AE66&amp;""",","")&amp;IF(AF66&gt;0,"nPriority="&amp;AF66&amp;",","")&amp;IF(AG66&lt;&gt;"","col="""&amp;AG66&amp;""",","")&amp;IF(AH66&lt;&gt;"","colScreenHead="""&amp;AH66&amp;""",","")&amp;IF(AI66&gt;0,"nColAlpha="&amp;AI66&amp;",","")&amp;IF(AJ66&gt;0,"bAttention=true,","")&amp;IF(AK66&gt;0,"bCaution=true,","")&amp;IF(AL66&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AM66&amp;"},","")&amp;IF(AO66&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AO66:ZZ66)&amp;"},","")&amp;"},",IF(C65&gt;0,"},","")&amp;IF(AND(B66="",C66="",OR(B65&lt;&gt;"",C65&lt;&gt;"")),"},}","")))</f>
+        <v>{dwID=8807,nLevel=1,szName="注视",nScrutinyType=1,szNote="据点挂机",col={255,50,255,},[1]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bBuffList=true,bFullScreen=true,},[2]={},aCataclysmBuff={{szReminder="视",nPriority=2,col="#FF32FFFF",nColAlpha=255,bAttention=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=2,szName="挂机检测·首领注视",nTime=30,key="挂机检测",},},},</v>
       </c>
       <c r="AO66" s="36" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="67" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C67" s="36">
-        <v>11559</v>
+      <c r="C67" s="40">
+        <v>7913</v>
       </c>
       <c r="D67" s="36">
         <v>1</v>
       </c>
-      <c r="F67" s="36">
-        <v>1244</v>
-      </c>
-      <c r="G67" s="36" t="s">
-        <v>1957</v>
-      </c>
       <c r="I67" s="36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K67" s="36" t="s">
-        <v>1954</v>
+        <v>1833</v>
       </c>
       <c r="L67" s="36" t="s">
-        <v>1964</v>
-      </c>
-      <c r="N67" s="36" t="s">
-        <v>1787</v>
-      </c>
-      <c r="O67" s="36">
-        <v>1</v>
-      </c>
-      <c r="P67" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q67" s="36">
-        <v>1</v>
-      </c>
-      <c r="R67" s="36">
-        <v>1</v>
+        <v>1830</v>
       </c>
       <c r="T67" s="36">
         <v>1</v>
       </c>
-      <c r="U67" s="36">
-        <v>1</v>
-      </c>
-      <c r="V67" s="36">
-        <v>1</v>
-      </c>
       <c r="AE67" s="36" t="s">
-        <v>1973</v>
+        <v>2374</v>
       </c>
       <c r="AF67" s="36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG67" s="36" t="s">
-        <v>1955</v>
+        <v>1832</v>
       </c>
       <c r="AH67" s="36" t="s">
-        <v>1956</v>
+        <v>1831</v>
       </c>
       <c r="AI67" s="36">
         <v>255</v>
@@ -24904,407 +24758,365 @@
       <c r="AJ67" s="36">
         <v>1</v>
       </c>
-      <c r="AK67" s="36">
-        <v>1</v>
-      </c>
       <c r="AL67" s="36">
         <v>1</v>
       </c>
       <c r="AN67" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=11559,nLevel=1,nIcon=1244,szName="答题",nScrutinyType=1,szNote="验证码答案",col={255,50,255,},[1]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bScreenHead=true,bBuffList=true,bFullScreen=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="题",nPriority=3,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bAttention=true,bCaution=true,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=1,szName="答题验证·剩余时间",nTime=30,key="挂机检测",},},},</v>
-      </c>
-      <c r="AO67" s="36" t="s">
-        <v>2084</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=7913,nLevel=1,nScrutinyType=2,szNote="意涌系统通用抗百分比回血",col={255,204,0,},[1]={bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="涌",nPriority=5,col="#FFCC00FF",colScreenHead="#FFCC00",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="68" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C68" s="36">
-        <v>11565</v>
+      <c r="C68" s="40">
+        <v>7911</v>
       </c>
       <c r="D68" s="36">
         <v>1</v>
       </c>
-      <c r="F68" s="36">
-        <v>592</v>
-      </c>
-      <c r="G68" s="36" t="s">
-        <v>2387</v>
+      <c r="I68" s="36">
+        <v>2</v>
       </c>
       <c r="K68" s="36" t="s">
-        <v>2388</v>
+        <v>1947</v>
       </c>
       <c r="L68" s="36" t="s">
-        <v>2115</v>
+        <v>1964</v>
       </c>
       <c r="R68" s="36">
         <v>1</v>
       </c>
+      <c r="T68" s="36">
+        <v>1</v>
+      </c>
+      <c r="AE68" s="36" t="s">
+        <v>1974</v>
+      </c>
+      <c r="AF68" s="36">
+        <v>4</v>
+      </c>
+      <c r="AG68" s="36" t="s">
+        <v>1955</v>
+      </c>
+      <c r="AH68" s="36" t="s">
+        <v>1956</v>
+      </c>
+      <c r="AI68" s="36">
+        <v>255</v>
+      </c>
+      <c r="AJ68" s="36">
+        <v>1</v>
+      </c>
+      <c r="AL68" s="36">
+        <v>1</v>
+      </c>
       <c r="AN68" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=11565,nLevel=1,nIcon=592,szName="大旗手",szNote="大旗手检测",col={0,255,255,},[1]={bScreenHead=true,},[2]={},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=7911,nLevel=1,nScrutinyType=2,szNote="繁忙",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="忙",nPriority=4,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="69" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C69" s="36">
-        <v>31381</v>
+      <c r="C69" s="40">
+        <v>7756</v>
       </c>
       <c r="D69" s="36">
         <v>1</v>
       </c>
-      <c r="G69" s="36" t="s">
-        <v>2563</v>
+      <c r="I69" s="36">
+        <v>1</v>
       </c>
       <c r="K69" s="36" t="s">
-        <v>2385</v>
+        <v>2038</v>
       </c>
       <c r="L69" s="36" t="s">
-        <v>1964</v>
-      </c>
-      <c r="R69" s="36">
-        <v>1</v>
+        <v>1781</v>
       </c>
       <c r="T69" s="36">
         <v>1</v>
       </c>
       <c r="AE69" s="36" t="s">
-        <v>2579</v>
+        <v>2039</v>
       </c>
       <c r="AF69" s="36">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AG69" s="36" t="s">
-        <v>1955</v>
-      </c>
-      <c r="AH69" s="36" t="s">
-        <v>1956</v>
+        <v>2637</v>
       </c>
       <c r="AI69" s="36">
-        <v>255</v>
-      </c>
-      <c r="AL69" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN69" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=31381,nLevel=1,szName="禁捡旗",szNote="无法拾取大旗",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="捡",nPriority=11,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=2,szName="【{$receiver}】·禁止捡旗",nTime="30,【{$receiver}】·禁止捡旗;32,【{$receiver}】·可以捡旗",nRefresh=1,key="经脉逆行·{$receiver}",},{nClass=2,nIcon=13,nFrame=2,szName="【{$receiver}】·可以捡旗",nTime=5,key="经脉逆行·{$receiver}",},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=7756,nLevel=1,nScrutinyType=1,szNote="燃火20s",col={255,255,0,},[1]={bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="火",nPriority=3,col="#00FFFF00",},},tCountdown={{nClass=1,nIcon=5399,nFrame=0,szName="增益·燃火·持续剩余",nTime=20,key="燃火",},{nClass=2,nIcon=13,szName="燃火",nTime=-1,key="燃火",},},},</v>
       </c>
       <c r="AO69" s="36" t="s">
-        <v>2690</v>
+        <v>2079</v>
       </c>
       <c r="AP69" s="36" t="s">
-        <v>2391</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="70" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C70" s="36">
-        <v>8807</v>
+      <c r="C70" s="40">
+        <v>7497</v>
       </c>
       <c r="D70" s="36">
         <v>1</v>
       </c>
       <c r="G70" s="36" t="s">
-        <v>1966</v>
+        <v>2041</v>
       </c>
       <c r="I70" s="36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K70" s="36" t="s">
-        <v>1967</v>
+        <v>2040</v>
       </c>
       <c r="L70" s="36" t="s">
-        <v>1964</v>
-      </c>
-      <c r="N70" s="36" t="s">
-        <v>1787</v>
-      </c>
-      <c r="O70" s="36">
-        <v>1</v>
-      </c>
-      <c r="P70" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q70" s="36">
+        <v>1781</v>
+      </c>
+      <c r="R70" s="36">
         <v>1</v>
       </c>
       <c r="T70" s="36">
         <v>1</v>
       </c>
-      <c r="U70" s="36">
-        <v>1</v>
-      </c>
       <c r="AE70" s="36" t="s">
-        <v>1972</v>
+        <v>2042</v>
       </c>
       <c r="AF70" s="36">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="AG70" s="36" t="s">
-        <v>1955</v>
+        <v>2043</v>
+      </c>
+      <c r="AH70" s="36" t="s">
+        <v>2044</v>
       </c>
       <c r="AI70" s="36">
         <v>255</v>
       </c>
-      <c r="AJ70" s="36">
+      <c r="AL70" s="36">
         <v>1</v>
       </c>
       <c r="AN70" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=8807,nLevel=1,szName="注视",nScrutinyType=1,szNote="据点挂机",col={255,50,255,},[1]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bBuffList=true,bFullScreen=true,},[2]={},aCataclysmBuff={{szReminder="视",nPriority=2,col="#FF32FFFF",nColAlpha=255,bAttention=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=2,szName="挂机检测·首领注视",nTime=30,key="挂机检测",},},},</v>
-      </c>
-      <c r="AO70" s="36" t="s">
-        <v>2082</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=7497,nLevel=1,szName="眩晕·抛掷",nScrutinyType=2,szNote="御城·抛掷",col={255,255,0,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="晕",nPriority=13,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="71" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C71" s="36">
-        <v>7913</v>
+      <c r="C71" s="40">
+        <v>7504</v>
       </c>
       <c r="D71" s="36">
         <v>1</v>
+      </c>
+      <c r="G71" s="36" t="s">
+        <v>2167</v>
       </c>
       <c r="I71" s="36">
         <v>2</v>
       </c>
       <c r="K71" s="36" t="s">
-        <v>1833</v>
+        <v>2166</v>
       </c>
       <c r="L71" s="36" t="s">
-        <v>1830</v>
+        <v>1781</v>
+      </c>
+      <c r="R71" s="36">
+        <v>1</v>
       </c>
       <c r="T71" s="36">
         <v>1</v>
       </c>
       <c r="AE71" s="36" t="s">
-        <v>2374</v>
+        <v>2042</v>
       </c>
       <c r="AF71" s="36">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AG71" s="36" t="s">
-        <v>1832</v>
+        <v>2043</v>
       </c>
       <c r="AH71" s="36" t="s">
-        <v>1831</v>
+        <v>2044</v>
       </c>
       <c r="AI71" s="36">
         <v>255</v>
       </c>
-      <c r="AJ71" s="36">
-        <v>1</v>
-      </c>
       <c r="AL71" s="36">
         <v>1</v>
       </c>
       <c r="AN71" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=7913,nLevel=1,nScrutinyType=2,szNote="意涌系统通用抗百分比回血",col={255,204,0,},[1]={bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="涌",nPriority=5,col="#FFCC00FF",colScreenHead="#FFCC00",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=7504,nLevel=1,szName="眩晕·御城",nScrutinyType=2,szNote="御城·精准",col={255,255,0,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="晕",nPriority=13,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="72" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C72" s="36">
-        <v>7911</v>
+      <c r="C72" s="40">
+        <v>7503</v>
       </c>
       <c r="D72" s="36">
         <v>1</v>
       </c>
+      <c r="G72" s="36" t="s">
+        <v>2509</v>
+      </c>
       <c r="I72" s="36">
+        <v>1</v>
+      </c>
+      <c r="K72" s="36" t="s">
+        <v>2510</v>
+      </c>
+      <c r="L72" s="36" t="s">
+        <v>2361</v>
+      </c>
+      <c r="T72" s="36">
+        <v>1</v>
+      </c>
+      <c r="V72" s="36">
+        <v>1</v>
+      </c>
+      <c r="AF72" s="36">
+        <v>37</v>
+      </c>
+      <c r="AG72" s="36" t="s">
+        <v>2511</v>
+      </c>
+      <c r="AH72" s="36" t="s">
+        <v>2364</v>
+      </c>
+      <c r="AI72" s="36">
+        <v>170</v>
+      </c>
+      <c r="AN72" s="36" t="str">
+        <f t="shared" si="1"/>
+        <v>{dwID=7503,nLevel=1,szName="减速·御城",nScrutinyType=1,szNote="御城·断股",col={31,63,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=37,col="#1F3FFFAA",colScreenHead="#1F3FFF",nColAlpha=170,},},},</v>
+      </c>
+    </row>
+    <row r="73" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C73" s="40">
+        <v>4038</v>
+      </c>
+      <c r="D73" s="36">
+        <v>1</v>
+      </c>
+      <c r="I73" s="36">
+        <v>1</v>
+      </c>
+      <c r="K73" s="36" t="s">
+        <v>2365</v>
+      </c>
+      <c r="L73" s="36" t="s">
+        <v>2361</v>
+      </c>
+      <c r="R73" s="36">
+        <v>1</v>
+      </c>
+      <c r="T73" s="36">
+        <v>1</v>
+      </c>
+      <c r="AE73" s="36" t="s">
+        <v>2362</v>
+      </c>
+      <c r="AF73" s="36">
+        <v>15</v>
+      </c>
+      <c r="AG73" s="36" t="s">
+        <v>2363</v>
+      </c>
+      <c r="AH73" s="36" t="s">
+        <v>2364</v>
+      </c>
+      <c r="AI73" s="36">
+        <v>255</v>
+      </c>
+      <c r="AL73" s="36">
+        <v>1</v>
+      </c>
+      <c r="AN73" s="36" t="str">
+        <f t="shared" si="1"/>
+        <v>{dwID=4038,nLevel=1,nScrutinyType=1,szNote="锁足·首领",col={31,63,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="锁",nPriority=15,col="#1F3FFFFF",colScreenHead="#1F3FFF",nColAlpha=255,bScreenHead=true,},},},</v>
+      </c>
+    </row>
+    <row r="74" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C74" s="40">
+        <v>29007</v>
+      </c>
+      <c r="D74" s="36">
+        <v>1</v>
+      </c>
+      <c r="I74" s="36">
+        <v>1</v>
+      </c>
+      <c r="K74" s="36" t="s">
+        <v>2160</v>
+      </c>
+      <c r="L74" s="36" t="s">
+        <v>2386</v>
+      </c>
+      <c r="AN74" s="36" t="str">
+        <f t="shared" si="1"/>
+        <v>{dwID=29007,nLevel=1,nScrutinyType=1,szNote="九素化生·伤害距离",col={128,238,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=1,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=1,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=1,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=1,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=1,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=1,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=1,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=1,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=1,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=1,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=1,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=1,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},{nClass=2,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=2,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=2,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=2,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=2,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=2,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=2,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=2,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=2,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=2,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=2,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=2,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=2,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
+      </c>
+      <c r="AO74" s="40" t="s">
+        <v>2409</v>
+      </c>
+      <c r="AP74" s="40" t="s">
+        <v>2408</v>
+      </c>
+      <c r="AQ74" s="38" t="s">
+        <v>2575</v>
+      </c>
+      <c r="AR74" s="38" t="s">
+        <v>2576</v>
+      </c>
+    </row>
+    <row r="75" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C75" s="40">
+        <v>11561</v>
+      </c>
+      <c r="D75" s="36">
+        <v>1</v>
+      </c>
+      <c r="G75" s="36" t="s">
+        <v>2586</v>
+      </c>
+      <c r="I75" s="36">
+        <v>1</v>
+      </c>
+      <c r="K75" s="36" t="s">
+        <v>2588</v>
+      </c>
+      <c r="L75" s="36" t="s">
+        <v>2587</v>
+      </c>
+      <c r="AN75" s="36" t="str">
+        <f t="shared" si="1"/>
+        <v>{dwID=11561,nLevel=1,szName="据点内",nScrutinyType=1,szNote="判断是否在大旗附近",col={80,231,236,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=1272,nFrame=2,szName="据点大旗·旗手提示",nTime=-1,key="据点大旗·旗手提示",},},},</v>
+      </c>
+      <c r="AO75" s="36" t="s">
+        <v>2730</v>
+      </c>
+      <c r="AP75" s="39"/>
+      <c r="AQ75" s="39"/>
+      <c r="AR75" s="39"/>
+    </row>
+    <row r="76" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C76" s="40">
+        <v>7723</v>
+      </c>
+      <c r="D76" s="36">
+        <v>1</v>
+      </c>
+      <c r="I76" s="36">
         <v>2</v>
       </c>
-      <c r="K72" s="36" t="s">
-        <v>1947</v>
-      </c>
-      <c r="L72" s="36" t="s">
-        <v>1964</v>
-      </c>
-      <c r="R72" s="36">
-        <v>1</v>
-      </c>
-      <c r="T72" s="36">
-        <v>1</v>
-      </c>
-      <c r="AE72" s="36" t="s">
-        <v>1974</v>
-      </c>
-      <c r="AF72" s="36">
-        <v>4</v>
-      </c>
-      <c r="AG72" s="36" t="s">
-        <v>1955</v>
-      </c>
-      <c r="AH72" s="36" t="s">
-        <v>1956</v>
-      </c>
-      <c r="AI72" s="36">
-        <v>255</v>
-      </c>
-      <c r="AJ72" s="36">
-        <v>1</v>
-      </c>
-      <c r="AL72" s="36">
-        <v>1</v>
-      </c>
-      <c r="AN72" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=7911,nLevel=1,nScrutinyType=2,szNote="繁忙",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="忙",nPriority=4,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
-      </c>
-    </row>
-    <row r="73" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C73" s="36">
-        <v>7756</v>
-      </c>
-      <c r="D73" s="36">
-        <v>1</v>
-      </c>
-      <c r="I73" s="36">
-        <v>1</v>
-      </c>
-      <c r="K73" s="36" t="s">
-        <v>2038</v>
-      </c>
-      <c r="L73" s="36" t="s">
-        <v>1781</v>
-      </c>
-      <c r="T73" s="36">
-        <v>1</v>
-      </c>
-      <c r="AE73" s="36" t="s">
-        <v>2039</v>
-      </c>
-      <c r="AF73" s="36">
-        <v>3</v>
-      </c>
-      <c r="AG73" s="36" t="s">
-        <v>2637</v>
-      </c>
-      <c r="AI73" s="36">
-        <v>0</v>
-      </c>
-      <c r="AN73" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=7756,nLevel=1,nScrutinyType=1,szNote="燃火20s",col={255,255,0,},[1]={bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="火",nPriority=3,col="#00FFFF00",},},tCountdown={{nClass=1,nIcon=5399,nFrame=0,szName="增益·燃火·持续剩余",nTime=20,key="燃火",},{nClass=2,nIcon=13,szName="燃火",nTime=-1,key="燃火",},},},</v>
-      </c>
-      <c r="AO73" s="36" t="s">
-        <v>2079</v>
-      </c>
-      <c r="AP73" s="36" t="s">
-        <v>2080</v>
-      </c>
-    </row>
-    <row r="74" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C74" s="36">
-        <v>7497</v>
-      </c>
-      <c r="D74" s="36">
-        <v>1</v>
-      </c>
-      <c r="G74" s="36" t="s">
-        <v>2041</v>
-      </c>
-      <c r="I74" s="36">
-        <v>2</v>
-      </c>
-      <c r="K74" s="36" t="s">
-        <v>2040</v>
-      </c>
-      <c r="L74" s="36" t="s">
-        <v>1781</v>
-      </c>
-      <c r="R74" s="36">
-        <v>1</v>
-      </c>
-      <c r="T74" s="36">
-        <v>1</v>
-      </c>
-      <c r="AE74" s="36" t="s">
-        <v>2042</v>
-      </c>
-      <c r="AF74" s="36">
-        <v>13</v>
-      </c>
-      <c r="AG74" s="36" t="s">
-        <v>2043</v>
-      </c>
-      <c r="AH74" s="36" t="s">
-        <v>2044</v>
-      </c>
-      <c r="AI74" s="36">
-        <v>255</v>
-      </c>
-      <c r="AL74" s="36">
-        <v>1</v>
-      </c>
-      <c r="AN74" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=7497,nLevel=1,szName="眩晕·抛掷",nScrutinyType=2,szNote="御城·抛掷",col={255,255,0,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="晕",nPriority=13,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
-      </c>
-    </row>
-    <row r="75" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C75" s="36">
-        <v>7504</v>
-      </c>
-      <c r="D75" s="36">
-        <v>1</v>
-      </c>
-      <c r="G75" s="36" t="s">
-        <v>2167</v>
-      </c>
-      <c r="I75" s="36">
-        <v>2</v>
-      </c>
-      <c r="K75" s="36" t="s">
-        <v>2166</v>
-      </c>
-      <c r="L75" s="36" t="s">
-        <v>1781</v>
-      </c>
-      <c r="R75" s="36">
-        <v>1</v>
-      </c>
-      <c r="T75" s="36">
-        <v>1</v>
-      </c>
-      <c r="AE75" s="36" t="s">
-        <v>2042</v>
-      </c>
-      <c r="AF75" s="36">
-        <v>13</v>
-      </c>
-      <c r="AG75" s="36" t="s">
-        <v>2043</v>
-      </c>
-      <c r="AH75" s="36" t="s">
-        <v>2044</v>
-      </c>
-      <c r="AI75" s="36">
-        <v>255</v>
-      </c>
-      <c r="AL75" s="36">
-        <v>1</v>
-      </c>
-      <c r="AN75" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=7504,nLevel=1,szName="眩晕·御城",nScrutinyType=2,szNote="御城·精准",col={255,255,0,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="晕",nPriority=13,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
-      </c>
-    </row>
-    <row r="76" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C76" s="36">
-        <v>7503</v>
-      </c>
-      <c r="D76" s="36">
-        <v>1</v>
-      </c>
-      <c r="G76" s="36" t="s">
-        <v>2509</v>
-      </c>
-      <c r="I76" s="36">
-        <v>1</v>
-      </c>
       <c r="K76" s="36" t="s">
-        <v>2510</v>
+        <v>1797</v>
       </c>
       <c r="L76" s="36" t="s">
-        <v>2361</v>
+        <v>1667</v>
       </c>
       <c r="T76" s="36">
         <v>1</v>
@@ -25313,175 +25125,184 @@
         <v>1</v>
       </c>
       <c r="AF76" s="36">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="AG76" s="36" t="s">
-        <v>2511</v>
-      </c>
-      <c r="AH76" s="36" t="s">
-        <v>2364</v>
+        <v>2491</v>
       </c>
       <c r="AI76" s="36">
         <v>170</v>
       </c>
       <c r="AN76" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=7503,nLevel=1,szName="减速·御城",nScrutinyType=1,szNote="御城·断股",col={31,63,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=37,col="#1F3FFFAA",colScreenHead="#1F3FFF",nColAlpha=170,},},},</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=7723,nLevel=1,nScrutinyType=2,szNote="神机雷",col={255,255,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=1,col="#FFFFFFAA",nColAlpha=170,},},},</v>
       </c>
     </row>
     <row r="77" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C77" s="36">
-        <v>4038</v>
-      </c>
-      <c r="D77" s="36">
-        <v>1</v>
-      </c>
-      <c r="I77" s="36">
-        <v>1</v>
-      </c>
-      <c r="K77" s="36" t="s">
-        <v>2365</v>
-      </c>
-      <c r="L77" s="36" t="s">
-        <v>2361</v>
-      </c>
-      <c r="R77" s="36">
-        <v>1</v>
-      </c>
-      <c r="T77" s="36">
-        <v>1</v>
-      </c>
-      <c r="AE77" s="36" t="s">
-        <v>2362</v>
-      </c>
-      <c r="AF77" s="36">
-        <v>15</v>
-      </c>
-      <c r="AG77" s="36" t="s">
-        <v>2363</v>
-      </c>
-      <c r="AH77" s="36" t="s">
-        <v>2364</v>
-      </c>
-      <c r="AI77" s="36">
+      <c r="A77" s="36" t="s">
+        <v>613</v>
+      </c>
+      <c r="B77" s="36">
+        <v>656</v>
+      </c>
+      <c r="AN77" s="36" t="str">
+        <f t="shared" si="1"/>
+        <v>},[656]={</v>
+      </c>
+    </row>
+    <row r="78" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C78" s="40">
+        <v>11567</v>
+      </c>
+      <c r="D78" s="36">
+        <v>1</v>
+      </c>
+      <c r="F78" s="36">
+        <v>1245</v>
+      </c>
+      <c r="G78" s="36" t="s">
+        <v>2091</v>
+      </c>
+      <c r="I78" s="36">
+        <v>1</v>
+      </c>
+      <c r="K78" s="36" t="s">
+        <v>1953</v>
+      </c>
+      <c r="L78" s="36" t="s">
+        <v>1781</v>
+      </c>
+      <c r="AN78" s="36" t="str">
+        <f t="shared" si="1"/>
+        <v>{dwID=11567,nLevel=1,nIcon=1245,szName="答对",nScrutinyType=1,szNote="回答奖励",col={255,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,nFrame=1,szName="答题验证·回答正确",nTime=5,key="挂机检测",},},},</v>
+      </c>
+      <c r="AO78" s="36" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="79" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C79" s="40">
+        <v>11559</v>
+      </c>
+      <c r="D79" s="36">
+        <v>1</v>
+      </c>
+      <c r="F79" s="36">
+        <v>1244</v>
+      </c>
+      <c r="G79" s="36" t="s">
+        <v>1957</v>
+      </c>
+      <c r="I79" s="36">
+        <v>1</v>
+      </c>
+      <c r="K79" s="36" t="s">
+        <v>1954</v>
+      </c>
+      <c r="L79" s="36" t="s">
+        <v>1964</v>
+      </c>
+      <c r="N79" s="36" t="s">
+        <v>1787</v>
+      </c>
+      <c r="O79" s="36">
+        <v>1</v>
+      </c>
+      <c r="P79" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q79" s="36">
+        <v>1</v>
+      </c>
+      <c r="R79" s="36">
+        <v>1</v>
+      </c>
+      <c r="T79" s="36">
+        <v>1</v>
+      </c>
+      <c r="U79" s="36">
+        <v>1</v>
+      </c>
+      <c r="V79" s="36">
+        <v>1</v>
+      </c>
+      <c r="AE79" s="36" t="s">
+        <v>1973</v>
+      </c>
+      <c r="AF79" s="36">
+        <v>3</v>
+      </c>
+      <c r="AG79" s="36" t="s">
+        <v>1955</v>
+      </c>
+      <c r="AH79" s="36" t="s">
+        <v>1956</v>
+      </c>
+      <c r="AI79" s="36">
         <v>255</v>
       </c>
-      <c r="AL77" s="36">
-        <v>1</v>
-      </c>
-      <c r="AN77" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=4038,nLevel=1,nScrutinyType=1,szNote="锁足·首领",col={31,63,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="锁",nPriority=15,col="#1F3FFFFF",colScreenHead="#1F3FFF",nColAlpha=255,bScreenHead=true,},},},</v>
-      </c>
-    </row>
-    <row r="78" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C78" s="36">
-        <v>1499</v>
-      </c>
-      <c r="D78" s="36">
-        <v>1</v>
-      </c>
-      <c r="G78" s="36" t="s">
-        <v>2375</v>
-      </c>
-      <c r="I78" s="36">
-        <v>1</v>
-      </c>
-      <c r="K78" s="36" t="s">
-        <v>2365</v>
-      </c>
-      <c r="L78" s="36" t="s">
-        <v>2361</v>
-      </c>
-      <c r="R78" s="36">
-        <v>1</v>
-      </c>
-      <c r="T78" s="36">
-        <v>1</v>
-      </c>
-      <c r="AN78" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=1499,nLevel=1,szName="锁足·呔",nScrutinyType=1,szNote="锁足·首领",col={31,63,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},},</v>
-      </c>
-    </row>
-    <row r="79" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C79" s="36">
-        <v>29007</v>
-      </c>
-      <c r="D79" s="36">
-        <v>1</v>
-      </c>
-      <c r="I79" s="36">
-        <v>1</v>
-      </c>
-      <c r="K79" s="36" t="s">
-        <v>2160</v>
-      </c>
-      <c r="L79" s="36" t="s">
-        <v>2386</v>
+      <c r="AJ79" s="36">
+        <v>1</v>
+      </c>
+      <c r="AK79" s="36">
+        <v>1</v>
+      </c>
+      <c r="AL79" s="36">
+        <v>1</v>
       </c>
       <c r="AN79" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=29007,nLevel=1,nScrutinyType=1,szNote="九素化生·伤害距离",col={128,238,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=1,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=1,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=1,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=1,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=1,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=1,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=1,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=1,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=1,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=1,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=1,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=1,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},{nClass=2,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=2,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=2,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=2,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=2,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=2,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=2,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=2,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=2,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=2,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=2,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=2,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=2,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
-      </c>
-      <c r="AO79" s="40" t="s">
-        <v>2409</v>
-      </c>
-      <c r="AP79" s="40" t="s">
-        <v>2408</v>
-      </c>
-      <c r="AQ79" s="38" t="s">
-        <v>2575</v>
-      </c>
-      <c r="AR79" s="38" t="s">
-        <v>2576</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=11559,nLevel=1,nIcon=1244,szName="答题",nScrutinyType=1,szNote="验证码答案",col={255,50,255,},[1]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bScreenHead=true,bBuffList=true,bFullScreen=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="题",nPriority=3,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bAttention=true,bCaution=true,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=1,szName="答题验证·剩余时间",nTime=30,key="挂机检测",},},},</v>
+      </c>
+      <c r="AO79" s="36" t="s">
+        <v>2084</v>
       </c>
     </row>
     <row r="80" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C80" s="36">
-        <v>11561</v>
+      <c r="C80" s="40">
+        <v>11565</v>
       </c>
       <c r="D80" s="36">
         <v>1</v>
       </c>
+      <c r="F80" s="36">
+        <v>592</v>
+      </c>
       <c r="G80" s="36" t="s">
-        <v>2586</v>
-      </c>
-      <c r="I80" s="36">
-        <v>1</v>
+        <v>2387</v>
       </c>
       <c r="K80" s="36" t="s">
-        <v>2588</v>
+        <v>2388</v>
       </c>
       <c r="L80" s="36" t="s">
-        <v>2587</v>
+        <v>2115</v>
+      </c>
+      <c r="R80" s="36">
+        <v>1</v>
       </c>
       <c r="AN80" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=11561,nLevel=1,szName="据点内",nScrutinyType=1,szNote="判断是否在大旗附近",col={80,231,236,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=1272,nFrame=2,szName="据点大旗·旗手提示",nTime=-1,key="据点大旗·旗手提示",},},},</v>
-      </c>
-      <c r="AO80" s="36" t="s">
-        <v>2730</v>
-      </c>
-      <c r="AP80" s="39"/>
-      <c r="AQ80" s="39"/>
-      <c r="AR80" s="39"/>
-    </row>
-    <row r="81" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C81" s="36">
-        <v>7723</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=11565,nLevel=1,nIcon=592,szName="大旗手",szNote="大旗手检测",col={0,255,255,},[1]={bScreenHead=true,},[2]={},},</v>
+      </c>
+    </row>
+    <row r="81" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C81" s="40">
+        <v>32813</v>
       </c>
       <c r="D81" s="36">
         <v>1</v>
       </c>
-      <c r="I81" s="36">
-        <v>2</v>
+      <c r="F81" s="36">
+        <v>16834</v>
+      </c>
+      <c r="G81" s="36" t="s">
+        <v>2704</v>
       </c>
       <c r="K81" s="36" t="s">
-        <v>1797</v>
+        <v>2699</v>
       </c>
       <c r="L81" s="36" t="s">
-        <v>1667</v>
+        <v>2701</v>
       </c>
       <c r="T81" s="36">
         <v>1</v>
@@ -25489,162 +25310,275 @@
       <c r="V81" s="36">
         <v>1</v>
       </c>
+      <c r="AE81" s="36" t="s">
+        <v>2700</v>
+      </c>
       <c r="AF81" s="36">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="AG81" s="36" t="s">
-        <v>2491</v>
+        <v>2702</v>
+      </c>
+      <c r="AH81" s="36" t="s">
+        <v>2703</v>
       </c>
       <c r="AI81" s="36">
-        <v>170</v>
+        <v>255</v>
       </c>
       <c r="AN81" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=7723,nLevel=1,nScrutinyType=2,szNote="神机雷",col={255,255,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=1,col="#FFFFFFAA",nColAlpha=170,},},},</v>
-      </c>
-    </row>
-    <row r="82" spans="1:74" x14ac:dyDescent="0.15">
-      <c r="A82" s="36" t="s">
-        <v>1767</v>
-      </c>
-      <c r="B82" s="36">
-        <v>214</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=32813,nLevel=1,nIcon=16834,szName="旗易伤",szNote="旗帜受损",col={255,153,204,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="损",nPriority=37,col="#FF99CCFF",colScreenHead="#FF99CC",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=1,key="大旗赛点·CD",},},},</v>
+      </c>
+      <c r="AO81" s="36" t="s">
+        <v>2708</v>
+      </c>
+    </row>
+    <row r="82" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C82" s="40">
+        <v>32812</v>
+      </c>
+      <c r="D82" s="36">
+        <v>1</v>
+      </c>
+      <c r="F82" s="36">
+        <v>3451</v>
+      </c>
+      <c r="G82" s="36" t="s">
+        <v>2705</v>
+      </c>
+      <c r="K82" s="36" t="s">
+        <v>2706</v>
+      </c>
+      <c r="L82" s="36" t="s">
+        <v>2707</v>
+      </c>
+      <c r="T82" s="36">
+        <v>1</v>
       </c>
       <c r="AN82" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>},[214]={</v>
-      </c>
-      <c r="BM82" s="36"/>
-      <c r="BN82" s="36"/>
-      <c r="BO82" s="36"/>
-      <c r="BP82" s="36"/>
-      <c r="BQ82" s="36"/>
-      <c r="BR82" s="36"/>
-      <c r="BS82" s="36"/>
-      <c r="BT82" s="36"/>
-      <c r="BU82" s="36"/>
-      <c r="BV82" s="36"/>
-    </row>
-    <row r="83" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C83" s="36">
-        <v>9992</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=32812,nLevel=1,nIcon=3451,szName="损CD",szNote="据点大旗赛点CD",col={255,50,50,},[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=0,key="大旗赛点·CD",},},},</v>
+      </c>
+      <c r="AO82" s="36" t="s">
+        <v>2710</v>
+      </c>
+    </row>
+    <row r="83" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C83" s="40">
+        <v>31381</v>
       </c>
       <c r="D83" s="36">
         <v>1</v>
       </c>
-      <c r="F83" s="36">
-        <v>8004</v>
-      </c>
       <c r="G83" s="36" t="s">
-        <v>2303</v>
-      </c>
-      <c r="I83" s="36">
-        <v>1</v>
+        <v>2563</v>
       </c>
       <c r="K83" s="36" t="s">
-        <v>2304</v>
+        <v>2385</v>
       </c>
       <c r="L83" s="36" t="s">
-        <v>1781</v>
+        <v>1964</v>
+      </c>
+      <c r="R83" s="36">
+        <v>1</v>
       </c>
       <c r="T83" s="36">
         <v>1</v>
       </c>
+      <c r="AE83" s="36" t="s">
+        <v>2579</v>
+      </c>
+      <c r="AF83" s="36">
+        <v>11</v>
+      </c>
+      <c r="AG83" s="36" t="s">
+        <v>1955</v>
+      </c>
+      <c r="AH83" s="36" t="s">
+        <v>1956</v>
+      </c>
+      <c r="AI83" s="36">
+        <v>255</v>
+      </c>
+      <c r="AL83" s="36">
+        <v>1</v>
+      </c>
       <c r="AN83" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=9992,nLevel=1,nIcon=8004,szName="大跑商",nScrutinyType=1,szNote="场景标记",col={255,255,0,},[1]={bBuffList=true,},[2]={},},</v>
-      </c>
-    </row>
-    <row r="84" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C84" s="36">
-        <v>9982</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=31381,nLevel=1,szName="禁捡旗",szNote="无法拾取大旗",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="捡",nPriority=11,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=2,szName="【{$receiver}】·禁止捡旗",nTime="30,【{$receiver}】·禁止捡旗;32,【{$receiver}】·可以捡旗",nRefresh=1,key="经脉逆行·{$receiver}",},{nClass=2,nIcon=13,nFrame=2,szName="【{$receiver}】·可以捡旗",nTime=5,key="经脉逆行·{$receiver}",},},},</v>
+      </c>
+      <c r="AO83" s="36" t="s">
+        <v>2690</v>
+      </c>
+      <c r="AP83" s="36" t="s">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="84" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C84" s="40">
+        <v>8807</v>
       </c>
       <c r="D84" s="36">
         <v>1</v>
       </c>
+      <c r="G84" s="36" t="s">
+        <v>1966</v>
+      </c>
       <c r="I84" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K84" s="36" t="s">
-        <v>2305</v>
+        <v>1967</v>
       </c>
       <c r="L84" s="36" t="s">
-        <v>1667</v>
+        <v>1964</v>
+      </c>
+      <c r="N84" s="36" t="s">
+        <v>1787</v>
+      </c>
+      <c r="O84" s="36">
+        <v>1</v>
+      </c>
+      <c r="P84" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q84" s="36">
+        <v>1</v>
+      </c>
+      <c r="T84" s="36">
+        <v>1</v>
+      </c>
+      <c r="U84" s="36">
+        <v>1</v>
       </c>
       <c r="AE84" s="36" t="s">
-        <v>2306</v>
+        <v>1972</v>
       </c>
       <c r="AF84" s="36">
         <v>2</v>
       </c>
       <c r="AG84" s="36" t="s">
-        <v>1970</v>
-      </c>
-      <c r="AH84" s="36" t="s">
-        <v>1970</v>
+        <v>1955</v>
       </c>
       <c r="AI84" s="36">
         <v>255</v>
       </c>
+      <c r="AJ84" s="36">
+        <v>1</v>
+      </c>
       <c r="AN84" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=9982,nLevel=1,nScrutinyType=2,szNote="运货首领",col={255,255,255,},[1]={},[2]={},aCataclysmBuff={{szReminder="镖",nPriority=2,col="#FFFFFFFF",colScreenHead="#FFFFFFFF",nColAlpha=255,},},},</v>
-      </c>
-    </row>
-    <row r="85" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C85" s="36">
-        <v>7851</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=8807,nLevel=1,szName="注视",nScrutinyType=1,szNote="据点挂机",col={255,50,255,},[1]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bBuffList=true,bFullScreen=true,},[2]={},aCataclysmBuff={{szReminder="视",nPriority=2,col="#FF32FFFF",nColAlpha=255,bAttention=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=2,szName="挂机检测·首领注视",nTime=30,key="挂机检测",},},},</v>
+      </c>
+      <c r="AO84" s="36" t="s">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="85" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C85" s="40">
+        <v>7913</v>
       </c>
       <c r="D85" s="36">
         <v>1</v>
       </c>
       <c r="I85" s="36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K85" s="36" t="s">
-        <v>2564</v>
+        <v>1833</v>
       </c>
       <c r="L85" s="36" t="s">
-        <v>2312</v>
+        <v>1830</v>
       </c>
       <c r="T85" s="36">
         <v>1</v>
       </c>
+      <c r="AE85" s="36" t="s">
+        <v>2374</v>
+      </c>
+      <c r="AF85" s="36">
+        <v>5</v>
+      </c>
+      <c r="AG85" s="36" t="s">
+        <v>1832</v>
+      </c>
+      <c r="AH85" s="36" t="s">
+        <v>1831</v>
+      </c>
+      <c r="AI85" s="36">
+        <v>255</v>
+      </c>
+      <c r="AJ85" s="36">
+        <v>1</v>
+      </c>
+      <c r="AL85" s="36">
+        <v>1</v>
+      </c>
       <c r="AN85" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=7851,nLevel=1,nScrutinyType=1,szNote="追踪·减速50%",col={31,63,255,},[1]={bBuffList=true,},[2]={},},</v>
-      </c>
-    </row>
-    <row r="86" spans="1:74" x14ac:dyDescent="0.15">
-      <c r="A86" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="B86" s="36">
-        <v>217</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=7913,nLevel=1,nScrutinyType=2,szNote="意涌系统通用抗百分比回血",col={255,204,0,},[1]={bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="涌",nPriority=5,col="#FFCC00FF",colScreenHead="#FFCC00",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
+      </c>
+    </row>
+    <row r="86" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C86" s="40">
+        <v>7911</v>
+      </c>
+      <c r="D86" s="36">
+        <v>1</v>
+      </c>
+      <c r="I86" s="36">
+        <v>2</v>
+      </c>
+      <c r="K86" s="36" t="s">
+        <v>1947</v>
+      </c>
+      <c r="L86" s="36" t="s">
+        <v>1964</v>
+      </c>
+      <c r="R86" s="36">
+        <v>1</v>
+      </c>
+      <c r="T86" s="36">
+        <v>1</v>
+      </c>
+      <c r="AE86" s="36" t="s">
+        <v>1974</v>
+      </c>
+      <c r="AF86" s="36">
+        <v>4</v>
+      </c>
+      <c r="AG86" s="36" t="s">
+        <v>1955</v>
+      </c>
+      <c r="AH86" s="36" t="s">
+        <v>1956</v>
+      </c>
+      <c r="AI86" s="36">
+        <v>255</v>
+      </c>
+      <c r="AJ86" s="36">
+        <v>1</v>
+      </c>
+      <c r="AL86" s="36">
+        <v>1</v>
       </c>
       <c r="AN86" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>},[217]={</v>
-      </c>
-    </row>
-    <row r="87" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C87" s="36">
-        <v>9992</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=7911,nLevel=1,nScrutinyType=2,szNote="繁忙",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="忙",nPriority=4,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
+      </c>
+    </row>
+    <row r="87" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C87" s="40">
+        <v>7756</v>
       </c>
       <c r="D87" s="36">
         <v>1</v>
       </c>
-      <c r="F87" s="36">
-        <v>8004</v>
-      </c>
-      <c r="G87" s="36" t="s">
-        <v>2303</v>
-      </c>
       <c r="I87" s="36">
         <v>1</v>
       </c>
       <c r="K87" s="36" t="s">
-        <v>2304</v>
+        <v>2038</v>
       </c>
       <c r="L87" s="36" t="s">
         <v>1781</v>
@@ -25652,184 +25586,319 @@
       <c r="T87" s="36">
         <v>1</v>
       </c>
+      <c r="AE87" s="36" t="s">
+        <v>2039</v>
+      </c>
+      <c r="AF87" s="36">
+        <v>3</v>
+      </c>
+      <c r="AG87" s="36" t="s">
+        <v>2637</v>
+      </c>
+      <c r="AI87" s="36">
+        <v>0</v>
+      </c>
       <c r="AN87" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=9992,nLevel=1,nIcon=8004,szName="大跑商",nScrutinyType=1,szNote="场景标记",col={255,255,0,},[1]={bBuffList=true,},[2]={},},</v>
-      </c>
-    </row>
-    <row r="88" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C88" s="36">
-        <v>9982</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=7756,nLevel=1,nScrutinyType=1,szNote="燃火20s",col={255,255,0,},[1]={bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="火",nPriority=3,col="#00FFFF00",},},tCountdown={{nClass=1,nIcon=5399,nFrame=0,szName="增益·燃火·持续剩余",nTime=20,key="燃火",},{nClass=2,nIcon=13,szName="燃火",nTime=-1,key="燃火",},},},</v>
+      </c>
+      <c r="AO87" s="36" t="s">
+        <v>2079</v>
+      </c>
+      <c r="AP87" s="36" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="88" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C88" s="40">
+        <v>7497</v>
       </c>
       <c r="D88" s="36">
         <v>1</v>
+      </c>
+      <c r="G88" s="36" t="s">
+        <v>2041</v>
       </c>
       <c r="I88" s="36">
         <v>2</v>
       </c>
       <c r="K88" s="36" t="s">
-        <v>2305</v>
+        <v>2040</v>
       </c>
       <c r="L88" s="36" t="s">
-        <v>1667</v>
+        <v>1781</v>
+      </c>
+      <c r="R88" s="36">
+        <v>1</v>
+      </c>
+      <c r="T88" s="36">
+        <v>1</v>
       </c>
       <c r="AE88" s="36" t="s">
-        <v>2306</v>
+        <v>2042</v>
       </c>
       <c r="AF88" s="36">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="AG88" s="36" t="s">
-        <v>1970</v>
+        <v>2043</v>
       </c>
       <c r="AH88" s="36" t="s">
-        <v>1970</v>
+        <v>2044</v>
       </c>
       <c r="AI88" s="36">
         <v>255</v>
       </c>
+      <c r="AL88" s="36">
+        <v>1</v>
+      </c>
       <c r="AN88" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=9982,nLevel=1,nScrutinyType=2,szNote="运货首领",col={255,255,255,},[1]={},[2]={},aCataclysmBuff={{szReminder="镖",nPriority=2,col="#FFFFFFFF",colScreenHead="#FFFFFFFF",nColAlpha=255,},},},</v>
-      </c>
-    </row>
-    <row r="89" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C89" s="36">
-        <v>7851</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=7497,nLevel=1,szName="眩晕·抛掷",nScrutinyType=2,szNote="御城·抛掷",col={255,255,0,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="晕",nPriority=13,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
+      </c>
+    </row>
+    <row r="89" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C89" s="40">
+        <v>7504</v>
       </c>
       <c r="D89" s="36">
         <v>1</v>
       </c>
+      <c r="G89" s="36" t="s">
+        <v>2167</v>
+      </c>
       <c r="I89" s="36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K89" s="36" t="s">
-        <v>2564</v>
+        <v>2166</v>
       </c>
       <c r="L89" s="36" t="s">
-        <v>2312</v>
+        <v>1781</v>
+      </c>
+      <c r="R89" s="36">
+        <v>1</v>
       </c>
       <c r="T89" s="36">
         <v>1</v>
       </c>
+      <c r="AE89" s="36" t="s">
+        <v>2042</v>
+      </c>
+      <c r="AF89" s="36">
+        <v>13</v>
+      </c>
+      <c r="AG89" s="36" t="s">
+        <v>2043</v>
+      </c>
+      <c r="AH89" s="36" t="s">
+        <v>2044</v>
+      </c>
+      <c r="AI89" s="36">
+        <v>255</v>
+      </c>
+      <c r="AL89" s="36">
+        <v>1</v>
+      </c>
       <c r="AN89" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=7851,nLevel=1,nScrutinyType=1,szNote="追踪·减速50%",col={31,63,255,},[1]={bBuffList=true,},[2]={},},</v>
-      </c>
-    </row>
-    <row r="90" spans="1:74" x14ac:dyDescent="0.15">
-      <c r="A90" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="B90" s="36">
-        <v>216</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=7504,nLevel=1,szName="眩晕·御城",nScrutinyType=2,szNote="御城·精准",col={255,255,0,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="晕",nPriority=13,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
+      </c>
+    </row>
+    <row r="90" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C90" s="40">
+        <v>7503</v>
+      </c>
+      <c r="D90" s="36">
+        <v>1</v>
+      </c>
+      <c r="G90" s="36" t="s">
+        <v>2509</v>
+      </c>
+      <c r="I90" s="36">
+        <v>1</v>
+      </c>
+      <c r="K90" s="36" t="s">
+        <v>2510</v>
+      </c>
+      <c r="L90" s="36" t="s">
+        <v>2361</v>
+      </c>
+      <c r="T90" s="36">
+        <v>1</v>
+      </c>
+      <c r="V90" s="36">
+        <v>1</v>
+      </c>
+      <c r="AF90" s="36">
+        <v>37</v>
+      </c>
+      <c r="AG90" s="36" t="s">
+        <v>2511</v>
+      </c>
+      <c r="AH90" s="36" t="s">
+        <v>2364</v>
+      </c>
+      <c r="AI90" s="36">
+        <v>170</v>
       </c>
       <c r="AN90" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>},[216]={</v>
-      </c>
-    </row>
-    <row r="91" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C91" s="36">
-        <v>9992</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=7503,nLevel=1,szName="减速·御城",nScrutinyType=1,szNote="御城·断股",col={31,63,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=37,col="#1F3FFFAA",colScreenHead="#1F3FFF",nColAlpha=170,},},},</v>
+      </c>
+    </row>
+    <row r="91" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C91" s="40">
+        <v>4038</v>
       </c>
       <c r="D91" s="36">
         <v>1</v>
       </c>
-      <c r="F91" s="36">
-        <v>8004</v>
-      </c>
-      <c r="G91" s="36" t="s">
-        <v>2303</v>
-      </c>
       <c r="I91" s="36">
         <v>1</v>
       </c>
       <c r="K91" s="36" t="s">
-        <v>2304</v>
+        <v>2365</v>
       </c>
       <c r="L91" s="36" t="s">
-        <v>1781</v>
+        <v>2361</v>
+      </c>
+      <c r="R91" s="36">
+        <v>1</v>
       </c>
       <c r="T91" s="36">
         <v>1</v>
       </c>
+      <c r="AE91" s="36" t="s">
+        <v>2362</v>
+      </c>
+      <c r="AF91" s="36">
+        <v>15</v>
+      </c>
+      <c r="AG91" s="36" t="s">
+        <v>2363</v>
+      </c>
+      <c r="AH91" s="36" t="s">
+        <v>2364</v>
+      </c>
+      <c r="AI91" s="36">
+        <v>255</v>
+      </c>
+      <c r="AL91" s="36">
+        <v>1</v>
+      </c>
       <c r="AN91" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=9992,nLevel=1,nIcon=8004,szName="大跑商",nScrutinyType=1,szNote="场景标记",col={255,255,0,},[1]={bBuffList=true,},[2]={},},</v>
-      </c>
-    </row>
-    <row r="92" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C92" s="36">
-        <v>9982</v>
+        <f t="shared" si="1"/>
+        <v>{dwID=4038,nLevel=1,nScrutinyType=1,szNote="锁足·首领",col={31,63,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="锁",nPriority=15,col="#1F3FFFFF",colScreenHead="#1F3FFF",nColAlpha=255,bScreenHead=true,},},},</v>
+      </c>
+    </row>
+    <row r="92" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C92" s="40">
+        <v>29007</v>
       </c>
       <c r="D92" s="36">
         <v>1</v>
       </c>
       <c r="I92" s="36">
+        <v>1</v>
+      </c>
+      <c r="K92" s="36" t="s">
+        <v>2160</v>
+      </c>
+      <c r="L92" s="36" t="s">
+        <v>2386</v>
+      </c>
+      <c r="AN92" s="36" t="str">
+        <f t="shared" si="1"/>
+        <v>{dwID=29007,nLevel=1,nScrutinyType=1,szNote="九素化生·伤害距离",col={128,238,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=1,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=1,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=1,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=1,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=1,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=1,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=1,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=1,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=1,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=1,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=1,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=1,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},{nClass=2,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=2,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=2,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=2,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=2,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=2,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=2,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=2,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=2,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=2,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=2,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=2,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=2,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
+      </c>
+      <c r="AO92" s="40" t="s">
+        <v>2409</v>
+      </c>
+      <c r="AP92" s="40" t="s">
+        <v>2408</v>
+      </c>
+      <c r="AQ92" s="38" t="s">
+        <v>2575</v>
+      </c>
+      <c r="AR92" s="38" t="s">
+        <v>2576</v>
+      </c>
+    </row>
+    <row r="93" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C93" s="40">
+        <v>11561</v>
+      </c>
+      <c r="D93" s="36">
+        <v>1</v>
+      </c>
+      <c r="G93" s="36" t="s">
+        <v>2586</v>
+      </c>
+      <c r="I93" s="36">
+        <v>1</v>
+      </c>
+      <c r="K93" s="36" t="s">
+        <v>2588</v>
+      </c>
+      <c r="L93" s="36" t="s">
+        <v>2587</v>
+      </c>
+      <c r="AN93" s="36" t="str">
+        <f t="shared" si="1"/>
+        <v>{dwID=11561,nLevel=1,szName="据点内",nScrutinyType=1,szNote="判断是否在大旗附近",col={80,231,236,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=1272,nFrame=2,szName="据点大旗·旗手提示",nTime=-1,key="据点大旗·旗手提示",},},},</v>
+      </c>
+      <c r="AO93" s="36" t="s">
+        <v>2730</v>
+      </c>
+      <c r="AP93" s="39"/>
+      <c r="AQ93" s="39"/>
+      <c r="AR93" s="39"/>
+    </row>
+    <row r="94" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C94" s="40">
+        <v>7723</v>
+      </c>
+      <c r="D94" s="36">
+        <v>1</v>
+      </c>
+      <c r="I94" s="36">
         <v>2</v>
       </c>
-      <c r="K92" s="36" t="s">
-        <v>2305</v>
-      </c>
-      <c r="L92" s="36" t="s">
+      <c r="K94" s="36" t="s">
+        <v>1797</v>
+      </c>
+      <c r="L94" s="36" t="s">
         <v>1667</v>
       </c>
-      <c r="AE92" s="36" t="s">
-        <v>2306</v>
-      </c>
-      <c r="AF92" s="36">
-        <v>2</v>
-      </c>
-      <c r="AG92" s="36" t="s">
-        <v>1970</v>
-      </c>
-      <c r="AH92" s="36" t="s">
-        <v>1970</v>
-      </c>
-      <c r="AI92" s="36">
-        <v>255</v>
-      </c>
-      <c r="AN92" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=9982,nLevel=1,nScrutinyType=2,szNote="运货首领",col={255,255,255,},[1]={},[2]={},aCataclysmBuff={{szReminder="镖",nPriority=2,col="#FFFFFFFF",colScreenHead="#FFFFFFFF",nColAlpha=255,},},},</v>
-      </c>
-    </row>
-    <row r="93" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C93" s="36">
-        <v>7851</v>
-      </c>
-      <c r="D93" s="36">
-        <v>1</v>
-      </c>
-      <c r="I93" s="36">
-        <v>1</v>
-      </c>
-      <c r="K93" s="36" t="s">
-        <v>2564</v>
-      </c>
-      <c r="L93" s="36" t="s">
-        <v>2312</v>
-      </c>
-      <c r="T93" s="36">
-        <v>1</v>
-      </c>
-      <c r="AN93" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v>{dwID=7851,nLevel=1,nScrutinyType=1,szNote="追踪·减速50%",col={31,63,255,},[1]={bBuffList=true,},[2]={},},</v>
-      </c>
-    </row>
-    <row r="94" spans="1:74" x14ac:dyDescent="0.15">
+      <c r="T94" s="36">
+        <v>1</v>
+      </c>
+      <c r="V94" s="36">
+        <v>1</v>
+      </c>
+      <c r="AF94" s="36">
+        <v>1</v>
+      </c>
+      <c r="AG94" s="36" t="s">
+        <v>2491</v>
+      </c>
+      <c r="AI94" s="36">
+        <v>170</v>
+      </c>
       <c r="AN94" s="36" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
+        <v>{dwID=7723,nLevel=1,nScrutinyType=2,szNote="神机雷",col={255,255,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=1,col="#FFFFFFAA",nColAlpha=170,},},},</v>
+      </c>
+    </row>
+    <row r="95" spans="3:44" x14ac:dyDescent="0.15">
+      <c r="AN95" s="36" t="str">
+        <f t="shared" si="1"/>
         <v>},},}</v>
       </c>
     </row>
-    <row r="95" spans="1:74" x14ac:dyDescent="0.15">
-      <c r="AN95" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+    <row r="96" spans="3:44" x14ac:dyDescent="0.15">
+      <c r="AN96" s="36"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
@@ -26001,7 +26070,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7123522-3835-4C9C-9EE8-73D49C8C2672}">
-  <dimension ref="A1:X408"/>
+  <dimension ref="A1:X414"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -34111,446 +34180,473 @@
         <v>{dwID=123867,nFrame=47,szNote="小曾",[3]={},[4]={},aFocus={{dwMapID=-1,szDisplay="分线·传送",nMaxDistance=12,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
-    <row r="369" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A369" t="s">
-        <v>1988</v>
-      </c>
-      <c r="B369">
-        <v>656</v>
+    <row r="369" spans="1:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C369" s="40">
+        <v>66809</v>
+      </c>
+      <c r="D369" s="36">
+        <v>57</v>
+      </c>
+      <c r="G369" s="36" t="s">
+        <v>2068</v>
+      </c>
+      <c r="I369" s="36" t="s">
+        <v>2069</v>
+      </c>
+      <c r="O369" s="36">
+        <v>1</v>
+      </c>
+      <c r="U369" s="36" t="s">
+        <v>2116</v>
       </c>
       <c r="V369" s="36" t="str">
         <f t="shared" si="5"/>
-        <v>},[656]={</v>
-      </c>
-    </row>
-    <row r="370" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="C370">
-        <v>123840</v>
-      </c>
-      <c r="D370">
+        <v>{dwID=66809,nFrame=57,szName="火圈",szNote="减疗火圈",[3]={bCenterAlarm=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="火圈·减疗",nMaxDistance=8,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+      </c>
+    </row>
+    <row r="370" spans="1:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C370" s="40">
+        <v>36396</v>
+      </c>
+      <c r="D370" s="36">
         <v>52</v>
       </c>
-      <c r="I370" t="s">
-        <v>1912</v>
-      </c>
-      <c r="J370" t="s">
-        <v>1527</v>
-      </c>
-      <c r="O370">
-        <v>1</v>
-      </c>
-      <c r="P370">
-        <v>1</v>
-      </c>
-      <c r="U370" t="s">
-        <v>1975</v>
+      <c r="G370" s="36" t="s">
+        <v>2037</v>
+      </c>
+      <c r="I370" s="36" t="s">
+        <v>2090</v>
+      </c>
+      <c r="O370" s="36">
+        <v>1</v>
+      </c>
+      <c r="P370" s="36">
+        <v>1</v>
+      </c>
+      <c r="U370" s="36" t="s">
+        <v>2036</v>
       </c>
       <c r="V370" s="36" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=123840,nFrame=52,szNote="大旗·云台营",col={0,255,0,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="大旗·云台营",nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
-      </c>
-    </row>
-    <row r="371" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="C371">
-        <v>123841</v>
-      </c>
-      <c r="D371">
+        <v>{dwID=36396,nFrame=52,szName="神机台·有人",szNote="神机台·有人状态",[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="神机台·敌方",nMaxDistance=60,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="神机台·有人",nMaxDistance=60,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nFrame=1,nIcon=361,nTime=10,szName="神机台·已摧毁",},},},</v>
+      </c>
+      <c r="W370" s="36" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="371" spans="1:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C371" s="40">
+        <v>36005</v>
+      </c>
+      <c r="D371" s="36">
         <v>52</v>
       </c>
-      <c r="I371" t="s">
-        <v>1913</v>
-      </c>
-      <c r="J371" t="s">
-        <v>1527</v>
-      </c>
-      <c r="O371">
-        <v>1</v>
-      </c>
-      <c r="P371">
-        <v>1</v>
-      </c>
-      <c r="U371" t="s">
-        <v>1976</v>
+      <c r="I371" s="36" t="s">
+        <v>2088</v>
+      </c>
+      <c r="P371" s="36">
+        <v>1</v>
       </c>
       <c r="V371" s="36" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=123841,nFrame=52,szNote="大旗·高阳营",col={0,255,0,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="大旗·高阳营",nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
-      </c>
-    </row>
-    <row r="372" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="C372">
-        <v>123976</v>
-      </c>
-      <c r="D372">
-        <v>47</v>
-      </c>
-      <c r="I372" t="s">
-        <v>1709</v>
-      </c>
-      <c r="P372">
-        <v>1</v>
-      </c>
-      <c r="U372" t="s">
-        <v>1769</v>
+        <v>{dwID=36005,nFrame=52,szNote="神机台·没人状态",[3]={bScreenHead=true,},[4]={},},</v>
+      </c>
+    </row>
+    <row r="372" spans="1:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C372" s="40">
+        <v>100133</v>
+      </c>
+      <c r="D372" s="36">
+        <v>57</v>
+      </c>
+      <c r="I372" s="36" t="s">
+        <v>2691</v>
+      </c>
+      <c r="P372" s="36">
+        <v>1</v>
+      </c>
+      <c r="U372" s="36" t="s">
+        <v>2692</v>
       </c>
       <c r="V372" s="36" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=123976,nFrame=47,szNote="恶人谷大将",[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=90,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=60,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},},tCountdown={{nClass=12,nFrame=3,nIcon=18830,nTime=10,szName="恶人谷大将·退场",nRefresh=2,key="恶人谷大将",},},},</v>
-      </c>
-      <c r="W372" s="36" t="s">
-        <v>2501</v>
-      </c>
-    </row>
-    <row r="373" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="C373">
-        <v>123975</v>
-      </c>
-      <c r="D373">
+        <v>{dwID=100133,nFrame=57,szNote="狼牙先锋首领",[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=90,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+      </c>
+    </row>
+    <row r="373" spans="1:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C373" s="40">
+        <v>30537</v>
+      </c>
+      <c r="D373" s="36">
         <v>47</v>
       </c>
-      <c r="I373" t="s">
-        <v>1710</v>
-      </c>
-      <c r="P373">
-        <v>1</v>
-      </c>
-      <c r="U373" t="s">
-        <v>1769</v>
+      <c r="I373" s="36" t="s">
+        <v>1749</v>
+      </c>
+      <c r="J373" s="36" t="s">
+        <v>1751</v>
+      </c>
+      <c r="P373" s="36">
+        <v>1</v>
+      </c>
+      <c r="U373" s="36" t="s">
+        <v>1750</v>
       </c>
       <c r="V373" s="36" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=123975,nFrame=47,szNote="浩气盟大将",[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=90,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=60,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},},tCountdown={{nClass=12,nFrame=7,nIcon=18829,nTime=10,szName="浩气盟大将·退场",nRefresh=2,key="浩气盟大将",},},},</v>
-      </c>
-      <c r="W373" s="36" t="s">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="374" spans="1:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C374" s="36">
-        <v>124104</v>
-      </c>
-      <c r="D374" s="36">
-        <v>52</v>
-      </c>
-      <c r="I374" s="36" t="s">
-        <v>1989</v>
-      </c>
-      <c r="U374" s="36" t="s">
-        <v>2384</v>
+        <v>{dwID=30537,nFrame=47,szNote="据点伙计",col={100,255,100,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=10,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+      </c>
+    </row>
+    <row r="374" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A374" t="s">
+        <v>1988</v>
+      </c>
+      <c r="B374">
+        <v>656</v>
       </c>
       <c r="V374" s="36" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124104,nFrame=52,szNote="城门·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,szDisplay="城门·关闭",nMaxDistance=60,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;=",nValue=50,},},{dwMapID=-1,szDisplay="城门·破损",nMaxDistance=60,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;=",nValue=30,},},},tCountdown={{nClass=12,nFrame=1,nIcon=1904,nTime=30,szName="城门·已摧毁",},},},</v>
-      </c>
-      <c r="W374" s="36" t="s">
-        <v>1992</v>
-      </c>
-    </row>
-    <row r="375" spans="1:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C375" s="36">
-        <v>124103</v>
-      </c>
-      <c r="D375" s="36">
+        <v>},[656]={</v>
+      </c>
+    </row>
+    <row r="375" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="C375">
+        <v>123840</v>
+      </c>
+      <c r="D375">
         <v>52</v>
       </c>
-      <c r="I375" s="36" t="s">
-        <v>1989</v>
-      </c>
-      <c r="U375" s="36" t="s">
-        <v>2384</v>
+      <c r="I375" t="s">
+        <v>1912</v>
+      </c>
+      <c r="J375" t="s">
+        <v>1527</v>
+      </c>
+      <c r="O375">
+        <v>1</v>
+      </c>
+      <c r="P375">
+        <v>1</v>
+      </c>
+      <c r="U375" t="s">
+        <v>1975</v>
       </c>
       <c r="V375" s="36" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124103,nFrame=52,szNote="城门·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,szDisplay="城门·关闭",nMaxDistance=60,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;=",nValue=50,},},{dwMapID=-1,szDisplay="城门·破损",nMaxDistance=60,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;=",nValue=30,},},},tCountdown={{nClass=12,nFrame=1,nIcon=1904,nTime=30,szName="城门·已摧毁",},},},</v>
-      </c>
-      <c r="W375" s="36" t="s">
-        <v>1992</v>
-      </c>
-    </row>
-    <row r="376" spans="1:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C376" s="36">
-        <v>124102</v>
-      </c>
-      <c r="D376" s="36">
+        <v>{dwID=123840,nFrame=52,szNote="大旗·云台营",col={0,255,0,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="大旗·云台营",nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+      </c>
+    </row>
+    <row r="376" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="C376">
+        <v>123841</v>
+      </c>
+      <c r="D376">
         <v>52</v>
       </c>
-      <c r="I376" s="36" t="s">
-        <v>1989</v>
-      </c>
-      <c r="U376" s="36" t="s">
-        <v>2384</v>
+      <c r="I376" t="s">
+        <v>1913</v>
+      </c>
+      <c r="J376" t="s">
+        <v>1527</v>
+      </c>
+      <c r="O376">
+        <v>1</v>
+      </c>
+      <c r="P376">
+        <v>1</v>
+      </c>
+      <c r="U376" t="s">
+        <v>1976</v>
       </c>
       <c r="V376" s="36" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124102,nFrame=52,szNote="城门·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,szDisplay="城门·关闭",nMaxDistance=60,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;=",nValue=50,},},{dwMapID=-1,szDisplay="城门·破损",nMaxDistance=60,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;=",nValue=30,},},},tCountdown={{nClass=12,nFrame=1,nIcon=1904,nTime=30,szName="城门·已摧毁",},},},</v>
-      </c>
-      <c r="W376" s="36" t="s">
-        <v>1992</v>
-      </c>
-    </row>
-    <row r="377" spans="1:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C377" s="36">
-        <v>124101</v>
-      </c>
-      <c r="D377" s="36">
-        <v>52</v>
-      </c>
-      <c r="I377" s="36" t="s">
-        <v>1989</v>
-      </c>
-      <c r="U377" s="36" t="s">
-        <v>2384</v>
+        <v>{dwID=123841,nFrame=52,szNote="大旗·高阳营",col={0,255,0,},[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="大旗·高阳营",nMaxDistance=30,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+      </c>
+    </row>
+    <row r="377" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="C377">
+        <v>123976</v>
+      </c>
+      <c r="D377">
+        <v>47</v>
+      </c>
+      <c r="I377" t="s">
+        <v>1709</v>
+      </c>
+      <c r="P377">
+        <v>1</v>
+      </c>
+      <c r="U377" t="s">
+        <v>1769</v>
       </c>
       <c r="V377" s="36" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124101,nFrame=52,szNote="城门·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,szDisplay="城门·关闭",nMaxDistance=60,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;=",nValue=50,},},{dwMapID=-1,szDisplay="城门·破损",nMaxDistance=60,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;=",nValue=30,},},},tCountdown={{nClass=12,nFrame=1,nIcon=1904,nTime=30,szName="城门·已摧毁",},},},</v>
+        <v>{dwID=123976,nFrame=47,szNote="恶人谷大将",[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=90,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=60,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},},tCountdown={{nClass=12,nFrame=3,nIcon=18830,nTime=10,szName="恶人谷大将·退场",nRefresh=2,key="恶人谷大将",},},},</v>
       </c>
       <c r="W377" s="36" t="s">
-        <v>1992</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="378" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C378">
-        <v>124280</v>
+        <v>123975</v>
       </c>
       <c r="D378">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="I378" t="s">
-        <v>1754</v>
-      </c>
-      <c r="U378" s="36" t="s">
-        <v>2684</v>
+        <v>1710</v>
+      </c>
+      <c r="P378">
+        <v>1</v>
+      </c>
+      <c r="U378" t="s">
+        <v>1769</v>
       </c>
       <c r="V378" s="36" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124280,nFrame=52,szNote="工坊·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},},},</v>
-      </c>
-    </row>
-    <row r="379" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="C379">
-        <v>124281</v>
-      </c>
-      <c r="D379">
+        <v>{dwID=123975,nFrame=47,szNote="浩气盟大将",[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=90,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=60,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},},tCountdown={{nClass=12,nFrame=7,nIcon=18829,nTime=10,szName="浩气盟大将·退场",nRefresh=2,key="浩气盟大将",},},},</v>
+      </c>
+      <c r="W378" s="36" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="379" spans="1:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C379" s="36">
+        <v>124104</v>
+      </c>
+      <c r="D379" s="36">
         <v>52</v>
       </c>
       <c r="I379" s="36" t="s">
-        <v>1754</v>
+        <v>1989</v>
       </c>
       <c r="U379" s="36" t="s">
-        <v>2684</v>
+        <v>2384</v>
       </c>
       <c r="V379" s="36" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124281,nFrame=52,szNote="工坊·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},},},</v>
-      </c>
-    </row>
-    <row r="380" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="C380">
-        <v>124290</v>
-      </c>
-      <c r="D380">
+        <v>{dwID=124104,nFrame=52,szNote="城门·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,szDisplay="城门·关闭",nMaxDistance=60,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;=",nValue=50,},},{dwMapID=-1,szDisplay="城门·破损",nMaxDistance=60,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;=",nValue=30,},},},tCountdown={{nClass=12,nFrame=1,nIcon=1904,nTime=30,szName="城门·已摧毁",},},},</v>
+      </c>
+      <c r="W379" s="36" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="380" spans="1:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C380" s="36">
+        <v>124103</v>
+      </c>
+      <c r="D380" s="36">
         <v>52</v>
       </c>
       <c r="I380" s="36" t="s">
-        <v>1754</v>
+        <v>1989</v>
       </c>
       <c r="U380" s="36" t="s">
-        <v>2684</v>
+        <v>2384</v>
       </c>
       <c r="V380" s="36" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124290,nFrame=52,szNote="工坊·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},},},</v>
-      </c>
-    </row>
-    <row r="381" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="C381">
-        <v>124291</v>
-      </c>
-      <c r="D381">
+        <v>{dwID=124103,nFrame=52,szNote="城门·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,szDisplay="城门·关闭",nMaxDistance=60,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;=",nValue=50,},},{dwMapID=-1,szDisplay="城门·破损",nMaxDistance=60,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;=",nValue=30,},},},tCountdown={{nClass=12,nFrame=1,nIcon=1904,nTime=30,szName="城门·已摧毁",},},},</v>
+      </c>
+      <c r="W380" s="36" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="381" spans="1:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C381" s="36">
+        <v>124102</v>
+      </c>
+      <c r="D381" s="36">
         <v>52</v>
       </c>
       <c r="I381" s="36" t="s">
-        <v>1754</v>
+        <v>1989</v>
       </c>
       <c r="U381" s="36" t="s">
-        <v>2684</v>
+        <v>2384</v>
       </c>
       <c r="V381" s="36" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124291,nFrame=52,szNote="工坊·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},},},</v>
-      </c>
-    </row>
-    <row r="382" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="C382">
-        <v>124260</v>
-      </c>
-      <c r="D382">
+        <v>{dwID=124102,nFrame=52,szNote="城门·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,szDisplay="城门·关闭",nMaxDistance=60,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;=",nValue=50,},},{dwMapID=-1,szDisplay="城门·破损",nMaxDistance=60,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;=",nValue=30,},},},tCountdown={{nClass=12,nFrame=1,nIcon=1904,nTime=30,szName="城门·已摧毁",},},},</v>
+      </c>
+      <c r="W381" s="36" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="382" spans="1:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C382" s="36">
+        <v>124101</v>
+      </c>
+      <c r="D382" s="36">
         <v>52</v>
       </c>
-      <c r="I382" t="s">
-        <v>1755</v>
+      <c r="I382" s="36" t="s">
+        <v>1989</v>
       </c>
       <c r="U382" s="36" t="s">
-        <v>2684</v>
+        <v>2384</v>
       </c>
       <c r="V382" s="36" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124260,nFrame=52,szNote="粮仓·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},},},</v>
+        <v>{dwID=124101,nFrame=52,szNote="城门·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,szDisplay="城门·关闭",nMaxDistance=60,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;=",nValue=50,},},{dwMapID=-1,szDisplay="城门·破损",nMaxDistance=60,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;=",nValue=30,},},},tCountdown={{nClass=12,nFrame=1,nIcon=1904,nTime=30,szName="城门·已摧毁",},},},</v>
+      </c>
+      <c r="W382" s="36" t="s">
+        <v>1992</v>
       </c>
     </row>
     <row r="383" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C383">
-        <v>124261</v>
+        <v>124280</v>
       </c>
       <c r="D383">
         <v>52</v>
       </c>
-      <c r="I383" s="36" t="s">
-        <v>1755</v>
+      <c r="I383" t="s">
+        <v>1754</v>
       </c>
       <c r="U383" s="36" t="s">
         <v>2684</v>
       </c>
       <c r="V383" s="36" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124261,nFrame=52,szNote="粮仓·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},},},</v>
+        <v>{dwID=124280,nFrame=52,szNote="工坊·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},},},</v>
       </c>
     </row>
     <row r="384" spans="1:23" x14ac:dyDescent="0.15">
       <c r="C384">
-        <v>124270</v>
+        <v>124281</v>
       </c>
       <c r="D384">
         <v>52</v>
       </c>
       <c r="I384" s="36" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="U384" s="36" t="s">
         <v>2684</v>
       </c>
       <c r="V384" s="36" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124270,nFrame=52,szNote="粮仓·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},},},</v>
+        <v>{dwID=124281,nFrame=52,szNote="工坊·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},},},</v>
       </c>
     </row>
     <row r="385" spans="3:22" x14ac:dyDescent="0.15">
       <c r="C385">
-        <v>124271</v>
+        <v>124290</v>
       </c>
       <c r="D385">
         <v>52</v>
       </c>
       <c r="I385" s="36" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="U385" s="36" t="s">
         <v>2684</v>
       </c>
       <c r="V385" s="36" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124271,nFrame=52,szNote="粮仓·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},},},</v>
+        <v>{dwID=124290,nFrame=52,szNote="工坊·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},},},</v>
       </c>
     </row>
     <row r="386" spans="3:22" x14ac:dyDescent="0.15">
       <c r="C386">
-        <v>124109</v>
+        <v>124291</v>
       </c>
       <c r="D386">
         <v>52</v>
       </c>
-      <c r="I386" t="s">
-        <v>1756</v>
+      <c r="I386" s="36" t="s">
+        <v>1754</v>
       </c>
       <c r="U386" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V386" s="36" t="str">
-        <f t="shared" ref="V386:V404" si="6">IF(ISBLANK(B386)=FALSE,IF(ISBLANK(B385),"},["&amp;B386&amp;"]={","["&amp;B386&amp;"]={"),IF(AND(ISBLANK(B386),ISBLANK(D386),ISBLANK(C386),OR(ISBLANK(B385)=FALSE,ISBLANK(D385)=FALSE,ISBLANK(C385)=FALSE)),"},},}",IF(ISBLANK(C386),"","{dwID="&amp;C386&amp;","&amp;"nFrame="&amp;D386&amp;","&amp;IF(E386&gt;0,"nCount="&amp;E386&amp;",","")&amp;IF(F386&gt;0,"bAllLeave=true,","")&amp;IF(G386&lt;&gt;"","szName="""&amp;G386&amp;""",","")&amp;IF(H386&lt;&gt;"","tKungFu={"&amp;H386&amp;"},","")&amp;IF(I386&lt;&gt;"","szNote="""&amp;I386&amp;""",","")&amp;IF(J386&lt;&gt;"","col={"&amp;J386&amp;"},","")&amp;"[3]={"&amp;IF(K386&lt;&gt;"","tMark={"&amp;K386&amp;"},","")&amp;IF(L386&lt;&gt;"","szVoice="""&amp;L386&amp;""",","")&amp;IF(M386&gt;0,"bTeamChannel=true,","")&amp;IF(N386&gt;0,"bWhisperChannel=true,","")&amp;IF(O386&gt;0,"bCenterAlarm=true,","")&amp;IF(P386&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q386&lt;&gt;"","szVoice="""&amp;Q386&amp;""",","")&amp;IF(R386&gt;0,"bTeamChannel=true,","")&amp;IF(S386&gt;0,"bWhisperChannel=true,","")&amp;IF(T386&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U386&lt;&gt;"","aFocus={"&amp;U386&amp;"},","")&amp;IF(W386&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W386:ZZ386)&amp;"},","")&amp;"},")))</f>
-        <v>{dwID=124109,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <f t="shared" ref="V386:V414" si="6">IF(ISBLANK(B386)=FALSE,IF(ISBLANK(B385),"},["&amp;B386&amp;"]={","["&amp;B386&amp;"]={"),IF(AND(ISBLANK(B386),ISBLANK(D386),ISBLANK(C386),OR(ISBLANK(B385)=FALSE,ISBLANK(D385)=FALSE,ISBLANK(C385)=FALSE)),"},},}",IF(ISBLANK(C386),"","{dwID="&amp;C386&amp;","&amp;"nFrame="&amp;D386&amp;","&amp;IF(E386&gt;0,"nCount="&amp;E386&amp;",","")&amp;IF(F386&gt;0,"bAllLeave=true,","")&amp;IF(G386&lt;&gt;"","szName="""&amp;G386&amp;""",","")&amp;IF(H386&lt;&gt;"","tKungFu={"&amp;H386&amp;"},","")&amp;IF(I386&lt;&gt;"","szNote="""&amp;I386&amp;""",","")&amp;IF(J386&lt;&gt;"","col={"&amp;J386&amp;"},","")&amp;"[3]={"&amp;IF(K386&lt;&gt;"","tMark={"&amp;K386&amp;"},","")&amp;IF(L386&lt;&gt;"","szVoice="""&amp;L386&amp;""",","")&amp;IF(M386&gt;0,"bTeamChannel=true,","")&amp;IF(N386&gt;0,"bWhisperChannel=true,","")&amp;IF(O386&gt;0,"bCenterAlarm=true,","")&amp;IF(P386&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q386&lt;&gt;"","szVoice="""&amp;Q386&amp;""",","")&amp;IF(R386&gt;0,"bTeamChannel=true,","")&amp;IF(S386&gt;0,"bWhisperChannel=true,","")&amp;IF(T386&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U386&lt;&gt;"","aFocus={"&amp;U386&amp;"},","")&amp;IF(W386&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W386:ZZ386)&amp;"},","")&amp;"},")))</f>
+        <v>{dwID=124291,nFrame=52,szNote="工坊·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},},},</v>
       </c>
     </row>
     <row r="387" spans="3:22" x14ac:dyDescent="0.15">
       <c r="C387">
-        <v>124110</v>
+        <v>124260</v>
       </c>
       <c r="D387">
         <v>52</v>
       </c>
-      <c r="I387" s="36" t="s">
-        <v>1756</v>
+      <c r="I387" t="s">
+        <v>1755</v>
       </c>
       <c r="U387" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V387" s="36" t="str">
         <f t="shared" si="6"/>
-        <v>{dwID=124110,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124260,nFrame=52,szNote="粮仓·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},},},</v>
       </c>
     </row>
     <row r="388" spans="3:22" x14ac:dyDescent="0.15">
       <c r="C388">
-        <v>124111</v>
+        <v>124261</v>
       </c>
       <c r="D388">
         <v>52</v>
       </c>
       <c r="I388" s="36" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="U388" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V388" s="36" t="str">
         <f t="shared" si="6"/>
-        <v>{dwID=124111,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124261,nFrame=52,szNote="粮仓·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},},},</v>
       </c>
     </row>
     <row r="389" spans="3:22" x14ac:dyDescent="0.15">
       <c r="C389">
-        <v>124112</v>
+        <v>124270</v>
       </c>
       <c r="D389">
         <v>52</v>
       </c>
       <c r="I389" s="36" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="U389" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V389" s="36" t="str">
         <f t="shared" si="6"/>
-        <v>{dwID=124112,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124270,nFrame=52,szNote="粮仓·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},},},</v>
       </c>
     </row>
     <row r="390" spans="3:22" x14ac:dyDescent="0.15">
       <c r="C390">
-        <v>124113</v>
+        <v>124271</v>
       </c>
       <c r="D390">
         <v>52</v>
       </c>
       <c r="I390" s="36" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="U390" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V390" s="36" t="str">
         <f t="shared" si="6"/>
-        <v>{dwID=124113,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124271,nFrame=52,szNote="粮仓·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},},},</v>
       </c>
     </row>
     <row r="391" spans="3:22" x14ac:dyDescent="0.15">
       <c r="C391">
-        <v>124114</v>
+        <v>124109</v>
       </c>
       <c r="D391">
         <v>52</v>
       </c>
-      <c r="I391" s="36" t="s">
+      <c r="I391" t="s">
         <v>1756</v>
       </c>
       <c r="U391" s="36" t="s">
@@ -34558,12 +34654,12 @@
       </c>
       <c r="V391" s="36" t="str">
         <f t="shared" si="6"/>
-        <v>{dwID=124114,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124109,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="392" spans="3:22" x14ac:dyDescent="0.15">
       <c r="C392">
-        <v>124115</v>
+        <v>124110</v>
       </c>
       <c r="D392">
         <v>52</v>
@@ -34576,12 +34672,12 @@
       </c>
       <c r="V392" s="36" t="str">
         <f t="shared" si="6"/>
-        <v>{dwID=124115,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124110,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="393" spans="3:22" x14ac:dyDescent="0.15">
       <c r="C393">
-        <v>124116</v>
+        <v>124111</v>
       </c>
       <c r="D393">
         <v>52</v>
@@ -34594,12 +34690,12 @@
       </c>
       <c r="V393" s="36" t="str">
         <f t="shared" si="6"/>
-        <v>{dwID=124116,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124111,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="394" spans="3:22" x14ac:dyDescent="0.15">
       <c r="C394">
-        <v>124117</v>
+        <v>124112</v>
       </c>
       <c r="D394">
         <v>52</v>
@@ -34612,12 +34708,12 @@
       </c>
       <c r="V394" s="36" t="str">
         <f t="shared" si="6"/>
-        <v>{dwID=124117,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124112,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="395" spans="3:22" x14ac:dyDescent="0.15">
       <c r="C395">
-        <v>124118</v>
+        <v>124113</v>
       </c>
       <c r="D395">
         <v>52</v>
@@ -34630,12 +34726,12 @@
       </c>
       <c r="V395" s="36" t="str">
         <f t="shared" si="6"/>
-        <v>{dwID=124118,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124113,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="396" spans="3:22" x14ac:dyDescent="0.15">
       <c r="C396">
-        <v>124119</v>
+        <v>124114</v>
       </c>
       <c r="D396">
         <v>52</v>
@@ -34648,12 +34744,12 @@
       </c>
       <c r="V396" s="36" t="str">
         <f t="shared" si="6"/>
-        <v>{dwID=124119,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124114,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="397" spans="3:22" x14ac:dyDescent="0.15">
       <c r="C397">
-        <v>124120</v>
+        <v>124115</v>
       </c>
       <c r="D397">
         <v>52</v>
@@ -34666,12 +34762,12 @@
       </c>
       <c r="V397" s="36" t="str">
         <f t="shared" si="6"/>
-        <v>{dwID=124120,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124115,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="398" spans="3:22" x14ac:dyDescent="0.15">
       <c r="C398">
-        <v>124121</v>
+        <v>124116</v>
       </c>
       <c r="D398">
         <v>52</v>
@@ -34684,12 +34780,12 @@
       </c>
       <c r="V398" s="36" t="str">
         <f t="shared" si="6"/>
-        <v>{dwID=124121,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124116,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="399" spans="3:22" x14ac:dyDescent="0.15">
       <c r="C399">
-        <v>124122</v>
+        <v>124117</v>
       </c>
       <c r="D399">
         <v>52</v>
@@ -34702,12 +34798,12 @@
       </c>
       <c r="V399" s="36" t="str">
         <f t="shared" si="6"/>
-        <v>{dwID=124122,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124117,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="400" spans="3:22" x14ac:dyDescent="0.15">
       <c r="C400">
-        <v>124123</v>
+        <v>124118</v>
       </c>
       <c r="D400">
         <v>52</v>
@@ -34720,12 +34816,12 @@
       </c>
       <c r="V400" s="36" t="str">
         <f t="shared" si="6"/>
-        <v>{dwID=124123,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
-      </c>
-    </row>
-    <row r="401" spans="3:22" x14ac:dyDescent="0.15">
+        <v>{dwID=124118,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+      </c>
+    </row>
+    <row r="401" spans="3:23" x14ac:dyDescent="0.15">
       <c r="C401">
-        <v>124124</v>
+        <v>124119</v>
       </c>
       <c r="D401">
         <v>52</v>
@@ -34738,65 +34834,260 @@
       </c>
       <c r="V401" s="36" t="str">
         <f t="shared" si="6"/>
-        <v>{dwID=124124,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
-      </c>
-    </row>
-    <row r="402" spans="3:22" x14ac:dyDescent="0.15">
+        <v>{dwID=124119,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+      </c>
+    </row>
+    <row r="402" spans="3:23" x14ac:dyDescent="0.15">
       <c r="C402">
-        <v>123871</v>
+        <v>124120</v>
       </c>
       <c r="D402">
-        <v>47</v>
-      </c>
-      <c r="I402" t="s">
-        <v>1704</v>
-      </c>
-      <c r="U402" t="s">
-        <v>1921</v>
+        <v>52</v>
+      </c>
+      <c r="I402" s="36" t="s">
+        <v>1756</v>
+      </c>
+      <c r="U402" s="36" t="s">
+        <v>2686</v>
       </c>
       <c r="V402" s="36" t="str">
         <f t="shared" si="6"/>
-        <v>{dwID=123871,nFrame=47,szNote="小珍",[3]={},[4]={},aFocus={{dwMapID=-1,szDisplay="分线·传送",nMaxDistance=12,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
-      </c>
-    </row>
-    <row r="403" spans="3:22" x14ac:dyDescent="0.15">
+        <v>{dwID=124120,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+      </c>
+    </row>
+    <row r="403" spans="3:23" x14ac:dyDescent="0.15">
       <c r="C403">
-        <v>123867</v>
+        <v>124121</v>
       </c>
       <c r="D403">
-        <v>47</v>
-      </c>
-      <c r="I403" t="s">
-        <v>1705</v>
-      </c>
-      <c r="U403" t="s">
-        <v>1921</v>
+        <v>52</v>
+      </c>
+      <c r="I403" s="36" t="s">
+        <v>1756</v>
+      </c>
+      <c r="U403" s="36" t="s">
+        <v>2686</v>
       </c>
       <c r="V403" s="36" t="str">
         <f t="shared" si="6"/>
-        <v>{dwID=123867,nFrame=47,szNote="小曾",[3]={},[4]={},aFocus={{dwMapID=-1,szDisplay="分线·传送",nMaxDistance=12,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
-      </c>
-    </row>
-    <row r="404" spans="3:22" x14ac:dyDescent="0.15">
+        <v>{dwID=124121,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+      </c>
+    </row>
+    <row r="404" spans="3:23" x14ac:dyDescent="0.15">
+      <c r="C404">
+        <v>124122</v>
+      </c>
+      <c r="D404">
+        <v>52</v>
+      </c>
+      <c r="I404" s="36" t="s">
+        <v>1756</v>
+      </c>
+      <c r="U404" s="36" t="s">
+        <v>2686</v>
+      </c>
       <c r="V404" s="36" t="str">
         <f t="shared" si="6"/>
+        <v>{dwID=124122,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+      </c>
+    </row>
+    <row r="405" spans="3:23" x14ac:dyDescent="0.15">
+      <c r="C405">
+        <v>124123</v>
+      </c>
+      <c r="D405">
+        <v>52</v>
+      </c>
+      <c r="I405" s="36" t="s">
+        <v>1756</v>
+      </c>
+      <c r="U405" s="36" t="s">
+        <v>2686</v>
+      </c>
+      <c r="V405" s="36" t="str">
+        <f t="shared" si="6"/>
+        <v>{dwID=124123,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+      </c>
+    </row>
+    <row r="406" spans="3:23" x14ac:dyDescent="0.15">
+      <c r="C406">
+        <v>124124</v>
+      </c>
+      <c r="D406">
+        <v>52</v>
+      </c>
+      <c r="I406" s="36" t="s">
+        <v>1756</v>
+      </c>
+      <c r="U406" s="36" t="s">
+        <v>2686</v>
+      </c>
+      <c r="V406" s="36" t="str">
+        <f t="shared" si="6"/>
+        <v>{dwID=124124,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+      </c>
+    </row>
+    <row r="407" spans="3:23" x14ac:dyDescent="0.15">
+      <c r="C407">
+        <v>123871</v>
+      </c>
+      <c r="D407">
+        <v>47</v>
+      </c>
+      <c r="I407" t="s">
+        <v>1704</v>
+      </c>
+      <c r="U407" t="s">
+        <v>1921</v>
+      </c>
+      <c r="V407" s="36" t="str">
+        <f t="shared" si="6"/>
+        <v>{dwID=123871,nFrame=47,szNote="小珍",[3]={},[4]={},aFocus={{dwMapID=-1,szDisplay="分线·传送",nMaxDistance=12,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+      </c>
+    </row>
+    <row r="408" spans="3:23" x14ac:dyDescent="0.15">
+      <c r="C408">
+        <v>123867</v>
+      </c>
+      <c r="D408">
+        <v>47</v>
+      </c>
+      <c r="I408" t="s">
+        <v>1705</v>
+      </c>
+      <c r="U408" t="s">
+        <v>1921</v>
+      </c>
+      <c r="V408" s="36" t="str">
+        <f t="shared" si="6"/>
+        <v>{dwID=123867,nFrame=47,szNote="小曾",[3]={},[4]={},aFocus={{dwMapID=-1,szDisplay="分线·传送",nMaxDistance=12,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+      </c>
+    </row>
+    <row r="409" spans="3:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C409" s="40">
+        <v>66809</v>
+      </c>
+      <c r="D409" s="36">
+        <v>57</v>
+      </c>
+      <c r="G409" s="36" t="s">
+        <v>2068</v>
+      </c>
+      <c r="I409" s="36" t="s">
+        <v>2069</v>
+      </c>
+      <c r="O409" s="36">
+        <v>1</v>
+      </c>
+      <c r="U409" s="36" t="s">
+        <v>2116</v>
+      </c>
+      <c r="V409" s="36" t="str">
+        <f t="shared" si="6"/>
+        <v>{dwID=66809,nFrame=57,szName="火圈",szNote="减疗火圈",[3]={bCenterAlarm=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="火圈·减疗",nMaxDistance=8,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+      </c>
+    </row>
+    <row r="410" spans="3:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C410" s="40">
+        <v>36396</v>
+      </c>
+      <c r="D410" s="36">
+        <v>52</v>
+      </c>
+      <c r="G410" s="36" t="s">
+        <v>2037</v>
+      </c>
+      <c r="I410" s="36" t="s">
+        <v>2090</v>
+      </c>
+      <c r="O410" s="36">
+        <v>1</v>
+      </c>
+      <c r="P410" s="36">
+        <v>1</v>
+      </c>
+      <c r="U410" s="36" t="s">
+        <v>2036</v>
+      </c>
+      <c r="V410" s="36" t="str">
+        <f t="shared" si="6"/>
+        <v>{dwID=36396,nFrame=52,szName="神机台·有人",szNote="神机台·有人状态",[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="神机台·敌方",nMaxDistance=60,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="神机台·有人",nMaxDistance=60,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nFrame=1,nIcon=361,nTime=10,szName="神机台·已摧毁",},},},</v>
+      </c>
+      <c r="W410" s="36" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="411" spans="3:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C411" s="40">
+        <v>36005</v>
+      </c>
+      <c r="D411" s="36">
+        <v>52</v>
+      </c>
+      <c r="I411" s="36" t="s">
+        <v>2088</v>
+      </c>
+      <c r="P411" s="36">
+        <v>1</v>
+      </c>
+      <c r="V411" s="36" t="str">
+        <f t="shared" si="6"/>
+        <v>{dwID=36005,nFrame=52,szNote="神机台·没人状态",[3]={bScreenHead=true,},[4]={},},</v>
+      </c>
+    </row>
+    <row r="412" spans="3:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C412" s="40">
+        <v>100133</v>
+      </c>
+      <c r="D412" s="36">
+        <v>57</v>
+      </c>
+      <c r="I412" s="36" t="s">
+        <v>2691</v>
+      </c>
+      <c r="P412" s="36">
+        <v>1</v>
+      </c>
+      <c r="U412" s="36" t="s">
+        <v>2692</v>
+      </c>
+      <c r="V412" s="36" t="str">
+        <f t="shared" si="6"/>
+        <v>{dwID=100133,nFrame=57,szNote="狼牙先锋首领",[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=90,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+      </c>
+    </row>
+    <row r="413" spans="3:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C413" s="40">
+        <v>30537</v>
+      </c>
+      <c r="D413" s="36">
+        <v>47</v>
+      </c>
+      <c r="I413" s="36" t="s">
+        <v>1749</v>
+      </c>
+      <c r="J413" s="36" t="s">
+        <v>1751</v>
+      </c>
+      <c r="P413" s="36">
+        <v>1</v>
+      </c>
+      <c r="U413" s="36" t="s">
+        <v>1750</v>
+      </c>
+      <c r="V413" s="36" t="str">
+        <f t="shared" si="6"/>
+        <v>{dwID=30537,nFrame=47,szNote="据点伙计",col={100,255,100,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=10,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
+      </c>
+    </row>
+    <row r="414" spans="3:23" x14ac:dyDescent="0.15">
+      <c r="V414" s="36" t="str">
+        <f t="shared" si="6"/>
         <v>},},}</v>
       </c>
     </row>
-    <row r="405" spans="3:22" x14ac:dyDescent="0.15">
-      <c r="V405" s="36"/>
-    </row>
-    <row r="406" spans="3:22" x14ac:dyDescent="0.15">
-      <c r="V406" s="36"/>
-    </row>
-    <row r="407" spans="3:22" x14ac:dyDescent="0.15">
-      <c r="V407" s="36"/>
-    </row>
-    <row r="408" spans="3:22" x14ac:dyDescent="0.15">
-      <c r="V408" s="36"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:X404" xr:uid="{10984C6C-FFE6-4A9E-B65E-B3CAE577EA25}"/>
+  <autoFilter ref="A1:X409" xr:uid="{10984C6C-FFE6-4A9E-B65E-B3CAE577EA25}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A151:X158">
     <sortCondition ref="I151:I158"/>
     <sortCondition ref="C151:C158"/>
@@ -35102,7 +35393,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="C13" s="36">
+      <c r="C13" s="40">
         <v>8418</v>
       </c>
       <c r="F13" s="36" t="s">
@@ -35126,7 +35417,7 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="C14" s="36">
+      <c r="C14" s="40">
         <v>6971</v>
       </c>
       <c r="F14" s="36" t="s">
@@ -35162,7 +35453,7 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="C16" s="36">
+      <c r="C16" s="40">
         <v>8418</v>
       </c>
       <c r="F16" s="36" t="s">
@@ -35186,7 +35477,7 @@
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="C17" s="36">
+      <c r="C17" s="40">
         <v>6971</v>
       </c>
       <c r="F17" s="36" t="s">
@@ -35650,7 +35941,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D30CAB81-FD57-4F97-A85B-88A947D91C00}">
-  <dimension ref="A1:BM184"/>
+  <dimension ref="A1:BM195"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="4" max="4" width="52.125" customWidth="1"/>
@@ -41070,7 +41361,7 @@
       </c>
       <c r="T131" s="36"/>
       <c r="V131" s="36" t="str">
-        <f t="shared" ref="V131:V183" si="27">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(D131),ISBLANK(N131),ISBLANK(O131),OR(ISBLANK(B130)=FALSE,ISBLANK(D130)=FALSE,ISBLANK(N130)=FALSE,ISBLANK(O130)=FALSE)),"},},}",IF(ISBLANK(D131),"","{szContent="""&amp;D131&amp;""","&amp;IF(C131&lt;&gt;"","szTarget="""&amp;C131&amp;""",","")&amp;IF(E131&lt;&gt;"","szNote="""&amp;E131&amp;""",","")&amp;IF(M131&lt;&gt;"","col={"&amp;M131&amp;"},","")&amp;IF(N131&gt;0,"bSearch=true,","")&amp;IF(O131&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P131&gt;0,"szVoice="""&amp;P131&amp;""",","")&amp;IF(Q131&gt;0,"bTeamChannel=true,","")&amp;IF(R131&gt;0,"bWhisperChannel=true,","")&amp;IF(S131&gt;0,"bCenterAlarm=true,","")&amp;IF(T131&gt;0,"bScreenHead=true,","")&amp;IF(U131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W131:AAH131)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="V131:V194" si="27">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(D131),ISBLANK(N131),ISBLANK(O131),OR(ISBLANK(B130)=FALSE,ISBLANK(D130)=FALSE,ISBLANK(N130)=FALSE,ISBLANK(O130)=FALSE)),"},},}",IF(ISBLANK(D131),"","{szContent="""&amp;D131&amp;""","&amp;IF(C131&lt;&gt;"","szTarget="""&amp;C131&amp;""",","")&amp;IF(E131&lt;&gt;"","szNote="""&amp;E131&amp;""",","")&amp;IF(M131&lt;&gt;"","col={"&amp;M131&amp;"},","")&amp;IF(N131&gt;0,"bSearch=true,","")&amp;IF(O131&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P131&gt;0,"szVoice="""&amp;P131&amp;""",","")&amp;IF(Q131&gt;0,"bTeamChannel=true,","")&amp;IF(R131&gt;0,"bWhisperChannel=true,","")&amp;IF(S131&gt;0,"bCenterAlarm=true,","")&amp;IF(T131&gt;0,"bScreenHead=true,","")&amp;IF(U131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W131:AAH131)&amp;"},","")&amp;"},")))</f>
         <v>},[30]={</v>
       </c>
     </row>
@@ -41909,313 +42200,590 @@
       <c r="C172" s="36" t="s">
         <v>2188</v>
       </c>
-      <c r="D172" s="36" t="s">
-        <v>2492</v>
+      <c r="D172" s="43" t="s">
+        <v>1946</v>
       </c>
       <c r="E172" s="36" t="s">
-        <v>2493</v>
+        <v>1945</v>
       </c>
       <c r="M172" s="36" t="s">
-        <v>1748</v>
+        <v>1432</v>
+      </c>
+      <c r="O172" s="36">
+        <v>1</v>
       </c>
       <c r="S172" s="36">
         <v>1</v>
       </c>
       <c r="V172" s="36" t="str">
         <f t="shared" si="27"/>
-        <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},},},</v>
+        <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
       </c>
       <c r="W172" s="36" t="s">
-        <v>2495</v>
+        <v>2558</v>
       </c>
       <c r="X172" s="36" t="s">
-        <v>2496</v>
+        <v>2559</v>
       </c>
       <c r="Y172" s="36" t="s">
-        <v>2497</v>
-      </c>
-      <c r="Z172" s="36" t="s">
-        <v>2499</v>
-      </c>
-      <c r="AA172" s="36" t="s">
-        <v>2498</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="173" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C173" s="36" t="s">
-        <v>1431</v>
+      <c r="C173" s="40" t="s">
+        <v>2188</v>
       </c>
       <c r="D173" s="36" t="s">
-        <v>2506</v>
-      </c>
-      <c r="E173" s="36" t="s">
-        <v>2507</v>
+        <v>1578</v>
       </c>
       <c r="M173" s="36" t="s">
-        <v>1432</v>
-      </c>
-      <c r="O173" s="36">
-        <v>1</v>
-      </c>
-      <c r="S173" s="36">
+        <v>1565</v>
+      </c>
+      <c r="N173" s="36">
         <v>1</v>
       </c>
       <c r="V173" s="36" t="str">
         <f t="shared" si="27"/>
-        <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
+        <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W173" s="36" t="s">
-        <v>2508</v>
+        <v>2436</v>
+      </c>
+      <c r="X173" s="36" t="s">
+        <v>2648</v>
       </c>
     </row>
     <row r="174" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C174" s="36" t="s">
+      <c r="C174" s="40" t="s">
         <v>2188</v>
       </c>
-      <c r="D174" s="43" t="s">
-        <v>1946</v>
-      </c>
-      <c r="E174" s="36" t="s">
-        <v>1945</v>
+      <c r="D174" s="36" t="s">
+        <v>1579</v>
       </c>
       <c r="M174" s="36" t="s">
-        <v>1432</v>
-      </c>
-      <c r="O174" s="36">
-        <v>1</v>
-      </c>
-      <c r="S174" s="36">
+        <v>1438</v>
+      </c>
+      <c r="N174" s="36">
         <v>1</v>
       </c>
       <c r="V174" s="36" t="str">
         <f t="shared" si="27"/>
-        <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
+        <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W174" s="36" t="s">
-        <v>2558</v>
+        <v>2436</v>
       </c>
       <c r="X174" s="36" t="s">
-        <v>2559</v>
-      </c>
-      <c r="Y174" s="36" t="s">
-        <v>2560</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="175" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C175" s="40" t="s">
+        <v>2188</v>
+      </c>
       <c r="D175" s="36" t="s">
-        <v>2502</v>
+        <v>2492</v>
       </c>
       <c r="E175" s="36" t="s">
-        <v>2503</v>
+        <v>2493</v>
       </c>
       <c r="M175" s="36" t="s">
-        <v>2504</v>
-      </c>
-      <c r="P175" s="36" t="s">
-        <v>1089</v>
-      </c>
-      <c r="Q175" s="36">
-        <v>1</v>
-      </c>
-      <c r="R175" s="36">
-        <v>1</v>
+        <v>1748</v>
       </c>
       <c r="S175" s="36">
-        <v>1</v>
-      </c>
-      <c r="U175" s="36">
         <v>1</v>
       </c>
       <c r="V175" s="36" t="str">
         <f t="shared" si="27"/>
-        <v>{szContent="系统检测您有挂机行为，如果长期维持该状态将被传送出图！",szNote="挂机检测·快活跃起来",col={255,50,255,},[14]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},},},</v>
+        <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},},},</v>
       </c>
       <c r="W175" s="36" t="s">
-        <v>2505</v>
+        <v>2495</v>
+      </c>
+      <c r="X175" s="36" t="s">
+        <v>2496</v>
+      </c>
+      <c r="Y175" s="36" t="s">
+        <v>2497</v>
+      </c>
+      <c r="Z175" s="36" t="s">
+        <v>2499</v>
+      </c>
+      <c r="AA175" s="36" t="s">
+        <v>2498</v>
       </c>
     </row>
     <row r="176" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C176" s="40" t="s">
+        <v>1431</v>
+      </c>
       <c r="D176" s="36" t="s">
-        <v>1899</v>
+        <v>2506</v>
+      </c>
+      <c r="E176" s="36" t="s">
+        <v>2507</v>
       </c>
       <c r="M176" s="36" t="s">
-        <v>1748</v>
+        <v>1432</v>
+      </c>
+      <c r="O176" s="36">
+        <v>1</v>
+      </c>
+      <c r="S176" s="36">
+        <v>1</v>
       </c>
       <c r="V176" s="36" t="str">
         <f t="shared" si="27"/>
-        <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="离开据点·大旗重置",},},},</v>
+        <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W176" s="36" t="s">
-        <v>1909</v>
-      </c>
-    </row>
-    <row r="177" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A177" s="36" t="s">
-        <v>613</v>
-      </c>
-      <c r="B177" s="36">
-        <v>656</v>
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="177" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C177" s="40"/>
+      <c r="D177" s="36" t="s">
+        <v>2502</v>
+      </c>
+      <c r="E177" s="36" t="s">
+        <v>2503</v>
+      </c>
+      <c r="M177" s="36" t="s">
+        <v>2504</v>
+      </c>
+      <c r="P177" s="36" t="s">
+        <v>1089</v>
+      </c>
+      <c r="Q177" s="36">
+        <v>1</v>
+      </c>
+      <c r="R177" s="36">
+        <v>1</v>
+      </c>
+      <c r="S177" s="36">
+        <v>1</v>
+      </c>
+      <c r="U177" s="36">
+        <v>1</v>
       </c>
       <c r="V177" s="36" t="str">
         <f t="shared" si="27"/>
-        <v>},[656]={</v>
+        <v>{szContent="系统检测您有挂机行为，如果长期维持该状态将被传送出图！",szNote="挂机检测·快活跃起来",col={255,50,255,},[14]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},},},</v>
+      </c>
+      <c r="W177" s="36" t="s">
+        <v>2505</v>
       </c>
     </row>
     <row r="178" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C178" s="36" t="s">
-        <v>2188</v>
-      </c>
+      <c r="C178" s="40"/>
       <c r="D178" s="36" t="s">
-        <v>2492</v>
-      </c>
-      <c r="E178" s="36" t="s">
-        <v>2493</v>
+        <v>1899</v>
       </c>
       <c r="M178" s="36" t="s">
         <v>1748</v>
       </c>
-      <c r="S178" s="36">
-        <v>1</v>
-      </c>
       <c r="V178" s="36" t="str">
         <f t="shared" si="27"/>
-        <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},},},</v>
+        <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W178" s="36" t="s">
-        <v>2495</v>
-      </c>
-      <c r="X178" s="36" t="s">
-        <v>2496</v>
-      </c>
-      <c r="Y178" s="36" t="s">
-        <v>2497</v>
-      </c>
-      <c r="Z178" s="36" t="s">
-        <v>2499</v>
-      </c>
-      <c r="AA178" s="36" t="s">
-        <v>2498</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="179" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C179" s="36" t="s">
-        <v>1431</v>
+      <c r="C179" s="40" t="s">
+        <v>2191</v>
       </c>
       <c r="D179" s="36" t="s">
-        <v>2506</v>
+        <v>2366</v>
       </c>
       <c r="E179" s="36" t="s">
-        <v>2507</v>
-      </c>
-      <c r="M179" s="36" t="s">
-        <v>1432</v>
-      </c>
-      <c r="O179" s="36">
-        <v>1</v>
-      </c>
-      <c r="S179" s="36">
-        <v>1</v>
+        <v>2367</v>
       </c>
       <c r="V179" s="36" t="str">
         <f t="shared" si="27"/>
-        <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
+        <v>{szContent="哼，还有要事要办，今日收获甚多，来日定多来领略你们的武功！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·攻防结束",[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领·离开",nTime=0,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="W179" s="36" t="s">
-        <v>2508</v>
+        <v>2368</v>
+      </c>
+      <c r="X179" s="38" t="s">
+        <v>2561</v>
+      </c>
+      <c r="Y179" s="38" t="s">
+        <v>2562</v>
       </c>
     </row>
     <row r="180" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C180" s="36" t="s">
-        <v>2188</v>
-      </c>
-      <c r="D180" s="43" t="s">
-        <v>1946</v>
+      <c r="C180" s="40" t="s">
+        <v>2191</v>
+      </c>
+      <c r="D180" s="36" t="s">
+        <v>1580</v>
       </c>
       <c r="E180" s="36" t="s">
-        <v>1945</v>
-      </c>
-      <c r="M180" s="36" t="s">
-        <v>1432</v>
-      </c>
-      <c r="O180" s="36">
-        <v>1</v>
-      </c>
-      <c r="S180" s="36">
-        <v>1</v>
+        <v>2194</v>
       </c>
       <c r="V180" s="36" t="str">
         <f t="shared" si="27"/>
-        <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
+        <v>{szContent="哼，打扰本大爷休息！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话1",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W180" s="36" t="s">
-        <v>2558</v>
-      </c>
-      <c r="X180" s="36" t="s">
-        <v>2559</v>
-      </c>
-      <c r="Y180" s="36" t="s">
-        <v>2560</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="181" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C181" s="40" t="s">
+        <v>2191</v>
+      </c>
       <c r="D181" s="36" t="s">
-        <v>2502</v>
+        <v>1581</v>
       </c>
       <c r="E181" s="36" t="s">
-        <v>2503</v>
-      </c>
-      <c r="M181" s="36" t="s">
-        <v>2504</v>
-      </c>
-      <c r="P181" s="36" t="s">
-        <v>1089</v>
-      </c>
-      <c r="Q181" s="36">
-        <v>1</v>
-      </c>
-      <c r="R181" s="36">
-        <v>1</v>
-      </c>
-      <c r="S181" s="36">
-        <v>1</v>
-      </c>
-      <c r="U181" s="36">
-        <v>1</v>
+        <v>2195</v>
       </c>
       <c r="V181" s="36" t="str">
         <f t="shared" si="27"/>
-        <v>{szContent="系统检测您有挂机行为，如果长期维持该状态将被传送出图！",szNote="挂机检测·快活跃起来",col={255,50,255,},[14]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},},},</v>
+        <v>{szContent="你爷爷我年轻些时候，也是翻云覆雨的江湖响当当一号人物！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话2",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W181" s="36" t="s">
-        <v>2505</v>
+        <v>2190</v>
+      </c>
+      <c r="X181" s="40" t="s">
+        <v>2412</v>
+      </c>
+      <c r="Y181" s="40" t="s">
+        <v>2413</v>
       </c>
     </row>
     <row r="182" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C182" s="40" t="s">
+        <v>2191</v>
+      </c>
       <c r="D182" s="36" t="s">
-        <v>1899</v>
-      </c>
-      <c r="M182" s="36" t="s">
-        <v>1748</v>
+        <v>1582</v>
+      </c>
+      <c r="E182" s="36" t="s">
+        <v>2689</v>
       </c>
       <c r="V182" s="36" t="str">
         <f t="shared" si="27"/>
-        <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="离开据点·大旗重置",},},},</v>
+        <v>{szContent="我竟然败给你们这群小辈！",szTarget="狼牙先锋首领",szNote="防冲突禁用·击退·狼牙先锋首领",[14]={},tCountdown={{nClass=-1,nIcon=3556,nFrame=1,szName="狼牙先锋首领·拾取掉落",nTime="10,狼牙先锋首领·已击退;300,狼牙先锋首领·拾取剩余;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=2,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W182" s="36" t="s">
-        <v>1909</v>
+        <v>2647</v>
+      </c>
+      <c r="X182" s="40" t="s">
+        <v>2412</v>
+      </c>
+      <c r="Y182" s="40" t="s">
+        <v>2413</v>
       </c>
     </row>
     <row r="183" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A183" s="36" t="s">
+        <v>613</v>
+      </c>
+      <c r="B183" s="36">
+        <v>656</v>
+      </c>
       <c r="V183" s="36" t="str">
         <f t="shared" si="27"/>
+        <v>},[656]={</v>
+      </c>
+    </row>
+    <row r="184" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C184" s="36" t="s">
+        <v>2188</v>
+      </c>
+      <c r="D184" s="43" t="s">
+        <v>1946</v>
+      </c>
+      <c r="E184" s="36" t="s">
+        <v>1945</v>
+      </c>
+      <c r="M184" s="36" t="s">
+        <v>1432</v>
+      </c>
+      <c r="O184" s="36">
+        <v>1</v>
+      </c>
+      <c r="S184" s="36">
+        <v>1</v>
+      </c>
+      <c r="V184" s="36" t="str">
+        <f t="shared" si="27"/>
+        <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
+      </c>
+      <c r="W184" s="36" t="s">
+        <v>2558</v>
+      </c>
+      <c r="X184" s="36" t="s">
+        <v>2559</v>
+      </c>
+      <c r="Y184" s="36" t="s">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="185" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C185" s="40" t="s">
+        <v>2188</v>
+      </c>
+      <c r="D185" s="36" t="s">
+        <v>1578</v>
+      </c>
+      <c r="M185" s="36" t="s">
+        <v>1565</v>
+      </c>
+      <c r="N185" s="36">
+        <v>1</v>
+      </c>
+      <c r="V185" s="36" t="str">
+        <f t="shared" si="27"/>
+        <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
+      </c>
+      <c r="W185" s="36" t="s">
+        <v>2436</v>
+      </c>
+      <c r="X185" s="36" t="s">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="186" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C186" s="40" t="s">
+        <v>2188</v>
+      </c>
+      <c r="D186" s="36" t="s">
+        <v>1579</v>
+      </c>
+      <c r="M186" s="36" t="s">
+        <v>1438</v>
+      </c>
+      <c r="N186" s="36">
+        <v>1</v>
+      </c>
+      <c r="V186" s="36" t="str">
+        <f t="shared" si="27"/>
+        <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
+      </c>
+      <c r="W186" s="36" t="s">
+        <v>2436</v>
+      </c>
+      <c r="X186" s="36" t="s">
+        <v>2649</v>
+      </c>
+    </row>
+    <row r="187" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C187" s="40" t="s">
+        <v>2188</v>
+      </c>
+      <c r="D187" s="36" t="s">
+        <v>2492</v>
+      </c>
+      <c r="E187" s="36" t="s">
+        <v>2493</v>
+      </c>
+      <c r="M187" s="36" t="s">
+        <v>1748</v>
+      </c>
+      <c r="S187" s="36">
+        <v>1</v>
+      </c>
+      <c r="V187" s="36" t="str">
+        <f t="shared" si="27"/>
+        <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},},},</v>
+      </c>
+      <c r="W187" s="36" t="s">
+        <v>2495</v>
+      </c>
+      <c r="X187" s="36" t="s">
+        <v>2496</v>
+      </c>
+      <c r="Y187" s="36" t="s">
+        <v>2497</v>
+      </c>
+      <c r="Z187" s="36" t="s">
+        <v>2499</v>
+      </c>
+      <c r="AA187" s="36" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="188" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C188" s="40" t="s">
+        <v>1431</v>
+      </c>
+      <c r="D188" s="36" t="s">
+        <v>2506</v>
+      </c>
+      <c r="E188" s="36" t="s">
+        <v>2507</v>
+      </c>
+      <c r="M188" s="36" t="s">
+        <v>1432</v>
+      </c>
+      <c r="O188" s="36">
+        <v>1</v>
+      </c>
+      <c r="S188" s="36">
+        <v>1</v>
+      </c>
+      <c r="V188" s="36" t="str">
+        <f t="shared" si="27"/>
+        <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
+      </c>
+      <c r="W188" s="36" t="s">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="189" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C189" s="40"/>
+      <c r="D189" s="36" t="s">
+        <v>2502</v>
+      </c>
+      <c r="E189" s="36" t="s">
+        <v>2503</v>
+      </c>
+      <c r="M189" s="36" t="s">
+        <v>2504</v>
+      </c>
+      <c r="P189" s="36" t="s">
+        <v>1089</v>
+      </c>
+      <c r="Q189" s="36">
+        <v>1</v>
+      </c>
+      <c r="R189" s="36">
+        <v>1</v>
+      </c>
+      <c r="S189" s="36">
+        <v>1</v>
+      </c>
+      <c r="U189" s="36">
+        <v>1</v>
+      </c>
+      <c r="V189" s="36" t="str">
+        <f t="shared" si="27"/>
+        <v>{szContent="系统检测您有挂机行为，如果长期维持该状态将被传送出图！",szNote="挂机检测·快活跃起来",col={255,50,255,},[14]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},},},</v>
+      </c>
+      <c r="W189" s="36" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="190" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C190" s="40"/>
+      <c r="D190" s="36" t="s">
+        <v>1899</v>
+      </c>
+      <c r="M190" s="36" t="s">
+        <v>1748</v>
+      </c>
+      <c r="V190" s="36" t="str">
+        <f t="shared" si="27"/>
+        <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="离开据点·大旗重置",},},},</v>
+      </c>
+      <c r="W190" s="36" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="191" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C191" s="40" t="s">
+        <v>2191</v>
+      </c>
+      <c r="D191" s="36" t="s">
+        <v>2366</v>
+      </c>
+      <c r="E191" s="36" t="s">
+        <v>2367</v>
+      </c>
+      <c r="V191" s="36" t="str">
+        <f t="shared" si="27"/>
+        <v>{szContent="哼，还有要事要办，今日收获甚多，来日定多来领略你们的武功！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·攻防结束",[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领·离开",nTime=0,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
+      </c>
+      <c r="W191" s="36" t="s">
+        <v>2368</v>
+      </c>
+      <c r="X191" s="38" t="s">
+        <v>2561</v>
+      </c>
+      <c r="Y191" s="38" t="s">
+        <v>2562</v>
+      </c>
+    </row>
+    <row r="192" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C192" s="40" t="s">
+        <v>2191</v>
+      </c>
+      <c r="D192" s="36" t="s">
+        <v>1580</v>
+      </c>
+      <c r="E192" s="36" t="s">
+        <v>2194</v>
+      </c>
+      <c r="V192" s="36" t="str">
+        <f t="shared" si="27"/>
+        <v>{szContent="哼，打扰本大爷休息！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话1",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},},},</v>
+      </c>
+      <c r="W192" s="36" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="193" spans="3:25" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C193" s="40" t="s">
+        <v>2191</v>
+      </c>
+      <c r="D193" s="36" t="s">
+        <v>1581</v>
+      </c>
+      <c r="E193" s="36" t="s">
+        <v>2195</v>
+      </c>
+      <c r="V193" s="36" t="str">
+        <f t="shared" si="27"/>
+        <v>{szContent="你爷爷我年轻些时候，也是翻云覆雨的江湖响当当一号人物！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话2",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
+      </c>
+      <c r="W193" s="36" t="s">
+        <v>2190</v>
+      </c>
+      <c r="X193" s="40" t="s">
+        <v>2412</v>
+      </c>
+      <c r="Y193" s="40" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="194" spans="3:25" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C194" s="40" t="s">
+        <v>2191</v>
+      </c>
+      <c r="D194" s="36" t="s">
+        <v>1582</v>
+      </c>
+      <c r="E194" s="36" t="s">
+        <v>2689</v>
+      </c>
+      <c r="V194" s="36" t="str">
+        <f t="shared" si="27"/>
+        <v>{szContent="我竟然败给你们这群小辈！",szTarget="狼牙先锋首领",szNote="防冲突禁用·击退·狼牙先锋首领",[14]={},tCountdown={{nClass=-1,nIcon=3556,nFrame=1,szName="狼牙先锋首领·拾取掉落",nTime="10,狼牙先锋首领·已击退;300,狼牙先锋首领·拾取剩余;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=2,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
+      </c>
+      <c r="W194" s="36" t="s">
+        <v>2647</v>
+      </c>
+      <c r="X194" s="40" t="s">
+        <v>2412</v>
+      </c>
+      <c r="Y194" s="40" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="195" spans="3:25" x14ac:dyDescent="0.15">
+      <c r="V195" s="36" t="str">
+        <f t="shared" ref="V195" si="28">IF(ISBLANK(B195)=FALSE,IF(ISBLANK(B194),"},["&amp;B195&amp;"]={","["&amp;B195&amp;"]={"),IF(AND(ISBLANK(B195),ISBLANK(D195),ISBLANK(N195),ISBLANK(O195),OR(ISBLANK(B194)=FALSE,ISBLANK(D194)=FALSE,ISBLANK(N194)=FALSE,ISBLANK(O194)=FALSE)),"},},}",IF(ISBLANK(D195),"","{szContent="""&amp;D195&amp;""","&amp;IF(C195&lt;&gt;"","szTarget="""&amp;C195&amp;""",","")&amp;IF(E195&lt;&gt;"","szNote="""&amp;E195&amp;""",","")&amp;IF(M195&lt;&gt;"","col={"&amp;M195&amp;"},","")&amp;IF(N195&gt;0,"bSearch=true,","")&amp;IF(O195&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P195&gt;0,"szVoice="""&amp;P195&amp;""",","")&amp;IF(Q195&gt;0,"bTeamChannel=true,","")&amp;IF(R195&gt;0,"bWhisperChannel=true,","")&amp;IF(S195&gt;0,"bCenterAlarm=true,","")&amp;IF(T195&gt;0,"bScreenHead=true,","")&amp;IF(U195&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W195&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W195:AAH195)&amp;"},","")&amp;"},")))</f>
         <v>},},}</v>
       </c>
     </row>
-    <row r="184" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="V184" s="36"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AV183" xr:uid="{9930944F-0E8A-459B-9EBC-D31B651D3108}"/>
+  <autoFilter ref="A1:AV191" xr:uid="{9930944F-0E8A-459B-9EBC-D31B651D3108}"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -45953,7 +46521,7 @@
         <v>1</v>
       </c>
       <c r="T131" s="36" t="str">
-        <f t="shared" ref="T131:T149" si="2">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(C131),ISBLANK(L131),ISBLANK(M131),OR(ISBLANK(B130)=FALSE,ISBLANK(C130)=FALSE,ISBLANK(L130)=FALSE,ISBLANK(M130)=FALSE)),"},},}",IF(ISBLANK(C131),"","{szContent="""&amp;C131&amp;""","&amp;IF(D131&lt;&gt;"","szNote="""&amp;D131&amp;""",","")&amp;IF(K131&lt;&gt;"","col={"&amp;K131&amp;"},","")&amp;IF(L131&gt;0,"bSearch=true,","")&amp;IF(M131&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N131&gt;0,"szVoice="""&amp;N131&amp;""",","")&amp;IF(O131&gt;0,"bTeamChannel=true,","")&amp;IF(P131&gt;0,"bWhisperChannel=true,","")&amp;IF(Q131&gt;0,"bCenterAlarm=true,","")&amp;IF(R131&gt;0,"bScreenHead=true,","")&amp;IF(S131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U131:AAF131)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="T131:T150" si="2">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(C131),ISBLANK(L131),ISBLANK(M131),OR(ISBLANK(B130)=FALSE,ISBLANK(C130)=FALSE,ISBLANK(L130)=FALSE,ISBLANK(M130)=FALSE)),"},},}",IF(ISBLANK(C131),"","{szContent="""&amp;C131&amp;""","&amp;IF(D131&lt;&gt;"","szNote="""&amp;D131&amp;""",","")&amp;IF(K131&lt;&gt;"","col={"&amp;K131&amp;"},","")&amp;IF(L131&gt;0,"bSearch=true,","")&amp;IF(M131&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N131&gt;0,"szVoice="""&amp;N131&amp;""",","")&amp;IF(O131&gt;0,"bTeamChannel=true,","")&amp;IF(P131&gt;0,"bWhisperChannel=true,","")&amp;IF(Q131&gt;0,"bCenterAlarm=true,","")&amp;IF(R131&gt;0,"bScreenHead=true,","")&amp;IF(S131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U131:AAF131)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凤鸣堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【惊虬谷】恶人·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凤鸣堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【惊虬谷】浩气·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·恶人大旗",},},},</v>
       </c>
       <c r="U131" s="36" t="s">
@@ -46521,7 +47089,7 @@
       <c r="AA144" s="36"/>
     </row>
     <row r="145" spans="1:45" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C145" s="36" t="s">
+      <c r="C145" s="40" t="s">
         <v>1803</v>
       </c>
       <c r="D145" s="36" t="s">
@@ -46666,7 +47234,7 @@
       <c r="AS148" s="36"/>
     </row>
     <row r="149" spans="1:45" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C149" s="36" t="s">
+      <c r="C149" s="40" t="s">
         <v>1803</v>
       </c>
       <c r="D149" s="36" t="s">
@@ -46699,7 +47267,10 @@
       </c>
     </row>
     <row r="150" spans="1:45" x14ac:dyDescent="0.15">
-      <c r="T150" s="36"/>
+      <c r="T150" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>},},}</v>
+      </c>
     </row>
     <row r="151" spans="1:45" x14ac:dyDescent="0.15">
       <c r="T151" s="36"/>

--- a/阵营/大小攻防团队监控.xlsx
+++ b/阵营/大小攻防团队监控.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JX3\Game\JX3\bin\zhcn_hd\interface\MY#DATA\!all-users@zhcn_hd\userdata\team_mon\remote\打包\阵营\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{FEDEFBB9-91DA-492A-8D8F-082508D3EDCF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{BA942829-7B57-44CB-B3BF-D6DB7E83190F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据总控" sheetId="2" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="系统频道" sheetId="11" r:id="rId9"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">不利气劲!$A$1:$BY$95</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">角色喊话!$A$1:$AV$191</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">系统角色!$A$1:$X$409</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">系统频道!$A$1:$BG$149</definedName>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="5787" uniqueCount="2735">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="5787" uniqueCount="2734">
   <si>
     <t>标识</t>
   </si>
@@ -8118,14 +8119,6 @@
     <t>屹立不倒</t>
   </si>
   <si>
-    <t>{nClass=7,nIcon=1537,nFrame=0,nTime=30,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{nClass=4,nIcon=13,nTime=0,szName="屹立不倒",key="屹立不倒",},</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>243,53,8,</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -9207,10 +9200,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>{nClass=1,nIcon=13,nFrame=2,szName="【{$receiver}】·禁止捡旗",nTime="30,【{$receiver}】·禁止捡旗;32,【{$receiver}】·可以捡旗",nRefresh=1,key="经脉逆行·{$receiver}",},</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>狼牙先锋首领</t>
   </si>
   <si>
@@ -9324,14 +9313,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>{nClass=9,nIcon=1537,nFrame=0,nTime="9,屹立不倒·{$sender}·50减伤;33.5,屹立不倒·{$sender}·释放剩余;40,屹立不倒·{$sender}·释放延迟",szName="屹立不倒",nRefresh=1,key="屹立不倒",},</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{nClass=8,nIcon=1537,nFrame=0,nTime="1,屹立不倒·{$sender}·释放剩余;9.5,屹立不倒·{$sender}·50减伤;34,屹立不倒·{$sender}·释放剩余;40.5,屹立不倒·{$sender}·释放延迟",szName="屹立不倒",nRefresh=0,key="屹立不倒",},</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2702,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5402,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -9356,10 +9337,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>{nClass=14,nIcon=592,nFrame=8,szName="【{$me}】·拾取大旗",nTime=30,key="据点大旗·旗手提示",},</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>{nClass=1,nIcon=1272,nFrame=2,szName="据点大旗·旗手提示",nTime=-1,key="据点大旗·旗手提示",},</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -9377,6 +9354,26 @@
   </si>
   <si>
     <t>{nClass=-1,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=2,nRefresh=600,key="方超",},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=592,nFrame=8,szName="【{$me}】·拾取大旗",nTime=30,key="拾取大旗·{$me}",},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{nClass=8,nIcon=1537,nFrame=0,nTime="1,屹立不倒·{$sender}·正在释放;9.5,屹立不倒·{$sender}·50减伤;32.5,屹立不倒·{$sender}·释放剩余;40.5,屹立不倒·{$sender}·释放延迟",szName="屹立不倒",nRefresh=0,key="屹立不倒",},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{nClass=9,nIcon=1537,nFrame=0,nTime="9,屹立不倒·{$sender}·50减伤;31.5,屹立不倒·{$sender}·释放剩余;40,屹立不倒·{$sender}·释放延迟",szName="屹立不倒",nRefresh=1,key="屹立不倒",},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{nClass=4,nIcon=13,nTime=-1,szName="屹立不倒",key="屹立不倒",},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{nClass=7,nIcon=1537,nFrame=0,nTime=32.5,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -10747,7 +10744,7 @@
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="21" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1774974165490,</v>
+        <v>nTimeStamp = 1775972827640,</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>34</v>
@@ -14320,10 +14317,10 @@
         <v>91</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>2397</v>
+        <v>2395</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>2396</v>
+        <v>2394</v>
       </c>
       <c r="M38" s="3" t="s">
         <v>1120</v>
@@ -14343,7 +14340,7 @@
         <v>95</v>
       </c>
       <c r="K39" s="44" t="s">
-        <v>2638</v>
+        <v>2636</v>
       </c>
       <c r="M39" s="3" t="s">
         <v>1123</v>
@@ -14363,7 +14360,7 @@
         <v>99</v>
       </c>
       <c r="K40" s="45" t="s">
-        <v>2639</v>
+        <v>2637</v>
       </c>
       <c r="M40" s="3" t="s">
         <v>1125</v>
@@ -14383,7 +14380,7 @@
         <v>104</v>
       </c>
       <c r="K41" s="46" t="s">
-        <v>2640</v>
+        <v>2638</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>1128</v>
@@ -14403,7 +14400,7 @@
         <v>107</v>
       </c>
       <c r="K42" s="47" t="s">
-        <v>2641</v>
+        <v>2639</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>1131</v>
@@ -14423,7 +14420,7 @@
         <v>111</v>
       </c>
       <c r="K43" s="49" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>1133</v>
@@ -14443,7 +14440,7 @@
         <v>115</v>
       </c>
       <c r="K44" s="48" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>1136</v>
@@ -20689,13 +20686,13 @@
         <v>1</v>
       </c>
       <c r="G6" s="36" t="s">
-        <v>2682</v>
+        <v>2680</v>
       </c>
       <c r="I6" s="36">
         <v>2</v>
       </c>
       <c r="K6" s="36" t="s">
-        <v>2681</v>
+        <v>2679</v>
       </c>
       <c r="T6" s="36">
         <v>1</v>
@@ -20722,7 +20719,7 @@
         <v>1801</v>
       </c>
       <c r="L7" s="36" t="s">
-        <v>2634</v>
+        <v>2632</v>
       </c>
       <c r="T7" s="36">
         <v>1</v>
@@ -20838,7 +20835,7 @@
       <c r="E10" s="35"/>
       <c r="F10" s="35"/>
       <c r="G10" s="35" t="s">
-        <v>2683</v>
+        <v>2681</v>
       </c>
       <c r="H10" s="35"/>
       <c r="I10" s="35">
@@ -20951,7 +20948,7 @@
     </row>
     <row r="12" spans="1:45" x14ac:dyDescent="0.15">
       <c r="A12" s="31" t="s">
-        <v>2687</v>
+        <v>2685</v>
       </c>
       <c r="B12" s="31">
         <v>-20</v>
@@ -21014,7 +21011,7 @@
       <c r="E13" s="31"/>
       <c r="F13" s="31"/>
       <c r="G13" s="31" t="s">
-        <v>2635</v>
+        <v>2633</v>
       </c>
       <c r="H13" s="31"/>
       <c r="I13" s="31"/>
@@ -21076,10 +21073,10 @@
         <v>{dwID=7561,nLevel=1,szName="守据点",szNote="守卫据点",col={0,255,255,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="旗",nPriority=2,col="#00FFFFFF",colScreenHead="#00FFFF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nTime=30,szName="【{$receiver}】·拾取大旗",nFrame=8,nIcon=592,key="拾取大旗·{$receiver}",},{nClass=2,nTime=-1,szName="拾取大旗",nIcon=592,key="拾取大旗·{$receiver}",},},},</v>
       </c>
       <c r="AO13" s="36" t="s">
-        <v>2578</v>
+        <v>2576</v>
       </c>
       <c r="AP13" s="36" t="s">
-        <v>2577</v>
+        <v>2575</v>
       </c>
       <c r="AQ13" s="31"/>
       <c r="AR13" s="31"/>
@@ -21097,7 +21094,7 @@
       <c r="E14" s="31"/>
       <c r="F14" s="31"/>
       <c r="G14" s="31" t="s">
-        <v>2636</v>
+        <v>2634</v>
       </c>
       <c r="H14" s="31"/>
       <c r="I14" s="31"/>
@@ -21159,10 +21156,10 @@
         <v>{dwID=7525,nLevel=1,szName="占据点",szNote="据点大旗",col={0,255,255,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="旗",nPriority=2,col="#00FFFFFF",colScreenHead="#00FFFF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nTime=30,szName="【{$receiver}】·拾取大旗",nFrame=8,nIcon=592,key="拾取大旗·{$receiver}",},{nClass=2,nTime=-1,szName="拾取大旗",nIcon=592,key="拾取大旗·{$receiver}",},},},</v>
       </c>
       <c r="AO14" s="31" t="s">
-        <v>2578</v>
+        <v>2576</v>
       </c>
       <c r="AP14" s="31" t="s">
-        <v>2577</v>
+        <v>2575</v>
       </c>
       <c r="AQ14" s="31"/>
       <c r="AR14" s="31"/>
@@ -21302,7 +21299,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="36" t="s">
-        <v>2683</v>
+        <v>2681</v>
       </c>
       <c r="I20" s="36">
         <v>1</v>
@@ -21623,7 +21620,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="36" t="s">
-        <v>2635</v>
+        <v>2633</v>
       </c>
       <c r="K34" s="36" t="s">
         <v>1653</v>
@@ -21666,10 +21663,10 @@
         <v>{dwID=7561,nLevel=1,szName="守据点",szNote="守卫据点",col={0,255,255,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="旗",nPriority=2,col="#00FFFFFF",colScreenHead="#00FFFF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nTime=30,szName="【{$receiver}】·拾取大旗",nFrame=8,nIcon=592,key="拾取大旗·{$receiver}",},{nClass=2,nTime=-1,szName="拾取大旗",nIcon=592,key="拾取大旗·{$receiver}",},},},</v>
       </c>
       <c r="AO34" s="36" t="s">
-        <v>2578</v>
+        <v>2576</v>
       </c>
       <c r="AP34" s="36" t="s">
-        <v>2577</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="35" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -21680,7 +21677,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="36" t="s">
-        <v>2636</v>
+        <v>2634</v>
       </c>
       <c r="K35" s="36" t="s">
         <v>1652</v>
@@ -21723,10 +21720,10 @@
         <v>{dwID=7525,nLevel=1,szName="占据点",szNote="据点大旗",col={0,255,255,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="旗",nPriority=2,col="#00FFFFFF",colScreenHead="#00FFFF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nTime=30,szName="【{$receiver}】·拾取大旗",nFrame=8,nIcon=592,key="拾取大旗·{$receiver}",},{nClass=2,nTime=-1,szName="拾取大旗",nIcon=592,key="拾取大旗·{$receiver}",},},},</v>
       </c>
       <c r="AO35" s="36" t="s">
-        <v>2578</v>
+        <v>2576</v>
       </c>
       <c r="AP35" s="36" t="s">
-        <v>2577</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="36" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -21830,7 +21827,7 @@
         <v>1</v>
       </c>
       <c r="G40" s="36" t="s">
-        <v>2635</v>
+        <v>2633</v>
       </c>
       <c r="K40" s="36" t="s">
         <v>1653</v>
@@ -21873,10 +21870,10 @@
         <v>{dwID=7561,nLevel=1,szName="守据点",szNote="守卫据点",col={0,255,255,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="旗",nPriority=2,col="#00FFFFFF",colScreenHead="#00FFFF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nTime=30,szName="【{$receiver}】·拾取大旗",nFrame=8,nIcon=592,key="拾取大旗·{$receiver}",},{nClass=2,nTime=-1,szName="拾取大旗",nIcon=592,key="拾取大旗·{$receiver}",},},},</v>
       </c>
       <c r="AO40" s="36" t="s">
-        <v>2578</v>
+        <v>2576</v>
       </c>
       <c r="AP40" s="36" t="s">
-        <v>2577</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="41" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -21887,7 +21884,7 @@
         <v>1</v>
       </c>
       <c r="G41" s="36" t="s">
-        <v>2636</v>
+        <v>2634</v>
       </c>
       <c r="K41" s="36" t="s">
         <v>1652</v>
@@ -21930,10 +21927,10 @@
         <v>{dwID=7525,nLevel=1,szName="占据点",szNote="据点大旗",col={0,255,255,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="旗",nPriority=2,col="#00FFFFFF",colScreenHead="#00FFFF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nTime=30,szName="【{$receiver}】·拾取大旗",nFrame=8,nIcon=592,key="拾取大旗·{$receiver}",},{nClass=2,nTime=-1,szName="拾取大旗",nIcon=592,key="拾取大旗·{$receiver}",},},},</v>
       </c>
       <c r="AO41" s="36" t="s">
-        <v>2578</v>
+        <v>2576</v>
       </c>
       <c r="AP41" s="36" t="s">
-        <v>2577</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="42" spans="1:42" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -22651,7 +22648,7 @@
         <v>3</v>
       </c>
       <c r="AG13" s="36" t="s">
-        <v>2637</v>
+        <v>2635</v>
       </c>
       <c r="AI13" s="36">
         <v>0</v>
@@ -22688,7 +22685,7 @@
         <v>{dwID=29721,nLevel=1,nScrutinyType=1,szNote="业务繁忙",col={255,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,szName="通用事件",nTime=-1,nRefresh=99999,key="通用事件",},{nClass=2,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},},},</v>
       </c>
       <c r="AO14" s="36" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="AP14" s="36" t="s">
         <v>2169</v>
@@ -22715,10 +22712,10 @@
         <v>{dwID=25654,nLevel=1,nScrutinyType=1,szNote="攻防场景特殊规则",col={255,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=99999,key="诛恶事件",},{nClass=1,nIcon=13,szName="通用事件",nTime=-1,nRefresh=99999,key="通用事件",},{nClass=1,nIcon=13,szName="绣球花",nTime=-1,key="绣球花",},{nClass=1,nIcon=13,szName="郁金香",nTime=-1,key="郁金香",},{nClass=1,nIcon=13,szName="牵牛花",nTime=-1,key="牵牛花",},},},</v>
       </c>
       <c r="AO15" s="36" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
       <c r="AP15" s="36" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="AQ15" s="36" t="s">
         <v>1822</v>
@@ -22817,10 +22814,10 @@
         <v>1943</v>
       </c>
       <c r="AS17" s="36" t="s">
-        <v>2625</v>
+        <v>2623</v>
       </c>
       <c r="AT17" s="52" t="s">
-        <v>2652</v>
+        <v>2650</v>
       </c>
       <c r="AU17" s="36"/>
       <c r="AV17" s="36"/>
@@ -22908,13 +22905,13 @@
         <v>{dwID=2105,nLevel=1,nScrutinyType=1,szNote="偃旗息鼓·攻防阶段",col={255,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=1,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=1,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=1,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=1,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=1,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=1,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=1,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=1,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=1,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=1,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=1,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=1,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},{nClass=1,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="AO18" s="40" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="AP18" s="40" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
       <c r="AQ18" s="36" t="s">
-        <v>2626</v>
+        <v>2624</v>
       </c>
       <c r="AR18" s="36"/>
       <c r="AS18" s="36"/>
@@ -23275,7 +23272,7 @@
         <v>1</v>
       </c>
       <c r="AG27" s="36" t="s">
-        <v>2491</v>
+        <v>2489</v>
       </c>
       <c r="AI27" s="36">
         <v>170</v>
@@ -23329,7 +23326,7 @@
     </row>
     <row r="30" spans="1:77" x14ac:dyDescent="0.15">
       <c r="A30" s="36" t="s">
-        <v>2687</v>
+        <v>2685</v>
       </c>
       <c r="B30" s="36">
         <v>-20</v>
@@ -23485,13 +23482,13 @@
         <v>16834</v>
       </c>
       <c r="G34" s="36" t="s">
-        <v>2704</v>
+        <v>2701</v>
       </c>
       <c r="K34" s="36" t="s">
-        <v>2699</v>
+        <v>2696</v>
       </c>
       <c r="L34" s="36" t="s">
-        <v>2701</v>
+        <v>2698</v>
       </c>
       <c r="T34" s="36">
         <v>1</v>
@@ -23500,26 +23497,26 @@
         <v>1</v>
       </c>
       <c r="AE34" s="36" t="s">
-        <v>2700</v>
+        <v>2697</v>
       </c>
       <c r="AF34" s="36">
         <v>37</v>
       </c>
       <c r="AG34" s="36" t="s">
-        <v>2702</v>
+        <v>2699</v>
       </c>
       <c r="AH34" s="36" t="s">
-        <v>2703</v>
+        <v>2700</v>
       </c>
       <c r="AI34" s="36">
         <v>255</v>
       </c>
       <c r="AN34" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=32813,nLevel=1,nIcon=16834,szName="旗易伤",szNote="旗帜受损",col={255,153,204,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="损",nPriority=37,col="#FF99CCFF",colScreenHead="#FF99CC",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=1,key="大旗赛点·CD",},},},</v>
+        <v>{dwID=32813,nLevel=1,nIcon=16834,szName="旗易伤",szNote="旗帜受损",col={255,153,204,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="损",nPriority=37,col="#FF99CCFF",colScreenHead="#FF99CC",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=0,key="大旗赛点·CD",},},},</v>
       </c>
       <c r="AO34" s="36" t="s">
-        <v>2708</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="35" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -23533,23 +23530,23 @@
         <v>3451</v>
       </c>
       <c r="G35" s="36" t="s">
-        <v>2705</v>
+        <v>2702</v>
       </c>
       <c r="K35" s="36" t="s">
-        <v>2706</v>
+        <v>2703</v>
       </c>
       <c r="L35" s="36" t="s">
-        <v>2707</v>
+        <v>2704</v>
       </c>
       <c r="T35" s="36">
         <v>1</v>
       </c>
       <c r="AN35" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=32812,nLevel=1,nIcon=3451,szName="损CD",szNote="据点大旗赛点CD",col={255,50,50,},[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=0,key="大旗赛点·CD",},},},</v>
+        <v>{dwID=32812,nLevel=1,nIcon=3451,szName="损CD",szNote="据点大旗赛点CD",col={255,50,50,},[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=1,key="大旗赛点·CD",},},},</v>
       </c>
       <c r="AO35" s="36" t="s">
-        <v>2710</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="36" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -23560,7 +23557,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="36" t="s">
-        <v>2563</v>
+        <v>2561</v>
       </c>
       <c r="K36" s="36" t="s">
         <v>2385</v>
@@ -23575,7 +23572,7 @@
         <v>1</v>
       </c>
       <c r="AE36" s="36" t="s">
-        <v>2579</v>
+        <v>2577</v>
       </c>
       <c r="AF36" s="36">
         <v>11</v>
@@ -23597,10 +23594,10 @@
         <v>{dwID=31381,nLevel=1,szName="禁捡旗",szNote="无法拾取大旗",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="捡",nPriority=11,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=22928,nFrame=2,szName="【{$receiver}】·禁止捡旗",nTime="30,【{$receiver}】·禁止捡旗;32,【{$receiver}】·可以捡旗",nRefresh=1,key="经脉逆行·{$receiver}",},{nClass=2,nIcon=22928,nFrame=2,szName="【{$receiver}】·可以捡旗",nTime=5,key="经脉逆行·{$receiver}",},},},</v>
       </c>
       <c r="AO36" s="36" t="s">
-        <v>2726</v>
+        <v>2721</v>
       </c>
       <c r="AP36" s="36" t="s">
-        <v>2727</v>
+        <v>2722</v>
       </c>
     </row>
     <row r="37" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -23782,7 +23779,7 @@
         <v>3</v>
       </c>
       <c r="AG40" s="36" t="s">
-        <v>2637</v>
+        <v>2635</v>
       </c>
       <c r="AI40" s="36">
         <v>0</v>
@@ -23902,13 +23899,13 @@
         <v>1</v>
       </c>
       <c r="G43" s="36" t="s">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="I43" s="36">
         <v>1</v>
       </c>
       <c r="K43" s="36" t="s">
-        <v>2510</v>
+        <v>2508</v>
       </c>
       <c r="L43" s="36" t="s">
         <v>2361</v>
@@ -23923,7 +23920,7 @@
         <v>37</v>
       </c>
       <c r="AG43" s="36" t="s">
-        <v>2511</v>
+        <v>2509</v>
       </c>
       <c r="AH43" s="36" t="s">
         <v>2364</v>
@@ -24002,16 +23999,16 @@
         <v>{dwID=29007,nLevel=1,nScrutinyType=1,szNote="九素化生·伤害距离",col={128,238,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=1,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=1,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=1,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=1,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=1,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=1,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=1,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=1,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=1,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=1,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=1,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=1,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},{nClass=2,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=2,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=2,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=2,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=2,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=2,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=2,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=2,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=2,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=2,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=2,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=2,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=2,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="AO45" s="40" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="AP45" s="40" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
       <c r="AQ45" s="38" t="s">
-        <v>2575</v>
+        <v>2573</v>
       </c>
       <c r="AR45" s="38" t="s">
-        <v>2576</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="46" spans="1:74" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -24022,23 +24019,23 @@
         <v>1</v>
       </c>
       <c r="G46" s="36" t="s">
+        <v>2584</v>
+      </c>
+      <c r="I46" s="36">
+        <v>1</v>
+      </c>
+      <c r="K46" s="36" t="s">
         <v>2586</v>
       </c>
-      <c r="I46" s="36">
-        <v>1</v>
-      </c>
-      <c r="K46" s="36" t="s">
-        <v>2588</v>
-      </c>
       <c r="L46" s="36" t="s">
-        <v>2587</v>
+        <v>2585</v>
       </c>
       <c r="AN46" s="36" t="str">
         <f t="shared" si="0"/>
         <v>{dwID=11561,nLevel=1,szName="据点内",nScrutinyType=1,szNote="判断是否在大旗附近",col={80,231,236,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=1272,nFrame=2,szName="据点大旗·旗手提示",nTime=-1,key="据点大旗·旗手提示",},},},</v>
       </c>
       <c r="AO46" s="36" t="s">
-        <v>2730</v>
+        <v>2724</v>
       </c>
       <c r="AP46" s="39"/>
       <c r="AQ46" s="39"/>
@@ -24070,7 +24067,7 @@
         <v>1</v>
       </c>
       <c r="AG47" s="36" t="s">
-        <v>2491</v>
+        <v>2489</v>
       </c>
       <c r="AH47" s="36"/>
       <c r="AI47" s="36">
@@ -24180,7 +24177,7 @@
         <v>1</v>
       </c>
       <c r="K51" s="36" t="s">
-        <v>2564</v>
+        <v>2562</v>
       </c>
       <c r="L51" s="36" t="s">
         <v>2312</v>
@@ -24282,7 +24279,7 @@
         <v>1</v>
       </c>
       <c r="K55" s="36" t="s">
-        <v>2564</v>
+        <v>2562</v>
       </c>
       <c r="L55" s="36" t="s">
         <v>2312</v>
@@ -24384,7 +24381,7 @@
         <v>1</v>
       </c>
       <c r="K59" s="36" t="s">
-        <v>2564</v>
+        <v>2562</v>
       </c>
       <c r="L59" s="36" t="s">
         <v>2312</v>
@@ -24543,13 +24540,13 @@
         <v>16834</v>
       </c>
       <c r="G63" s="36" t="s">
-        <v>2704</v>
+        <v>2701</v>
       </c>
       <c r="K63" s="36" t="s">
-        <v>2699</v>
+        <v>2696</v>
       </c>
       <c r="L63" s="36" t="s">
-        <v>2701</v>
+        <v>2698</v>
       </c>
       <c r="T63" s="36">
         <v>1</v>
@@ -24558,26 +24555,26 @@
         <v>1</v>
       </c>
       <c r="AE63" s="36" t="s">
-        <v>2700</v>
+        <v>2697</v>
       </c>
       <c r="AF63" s="36">
         <v>37</v>
       </c>
       <c r="AG63" s="36" t="s">
-        <v>2702</v>
+        <v>2699</v>
       </c>
       <c r="AH63" s="36" t="s">
-        <v>2703</v>
+        <v>2700</v>
       </c>
       <c r="AI63" s="36">
         <v>255</v>
       </c>
       <c r="AN63" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=32813,nLevel=1,nIcon=16834,szName="旗易伤",szNote="旗帜受损",col={255,153,204,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="损",nPriority=37,col="#FF99CCFF",colScreenHead="#FF99CC",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=1,key="大旗赛点·CD",},},},</v>
+        <v>{dwID=32813,nLevel=1,nIcon=16834,szName="旗易伤",szNote="旗帜受损",col={255,153,204,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="损",nPriority=37,col="#FF99CCFF",colScreenHead="#FF99CC",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=0,key="大旗赛点·CD",},},},</v>
       </c>
       <c r="AO63" s="36" t="s">
-        <v>2708</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="64" spans="1:41" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -24591,23 +24588,23 @@
         <v>3451</v>
       </c>
       <c r="G64" s="36" t="s">
-        <v>2705</v>
+        <v>2702</v>
       </c>
       <c r="K64" s="36" t="s">
-        <v>2706</v>
+        <v>2703</v>
       </c>
       <c r="L64" s="36" t="s">
-        <v>2707</v>
+        <v>2704</v>
       </c>
       <c r="T64" s="36">
         <v>1</v>
       </c>
       <c r="AN64" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=32812,nLevel=1,nIcon=3451,szName="损CD",szNote="据点大旗赛点CD",col={255,50,50,},[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=0,key="大旗赛点·CD",},},},</v>
+        <v>{dwID=32812,nLevel=1,nIcon=3451,szName="损CD",szNote="据点大旗赛点CD",col={255,50,50,},[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=1,key="大旗赛点·CD",},},},</v>
       </c>
       <c r="AO64" s="36" t="s">
-        <v>2710</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="65" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -24618,7 +24615,7 @@
         <v>1</v>
       </c>
       <c r="G65" s="36" t="s">
-        <v>2563</v>
+        <v>2561</v>
       </c>
       <c r="K65" s="36" t="s">
         <v>2385</v>
@@ -24633,7 +24630,7 @@
         <v>1</v>
       </c>
       <c r="AE65" s="36" t="s">
-        <v>2579</v>
+        <v>2577</v>
       </c>
       <c r="AF65" s="36">
         <v>11</v>
@@ -24652,10 +24649,10 @@
       </c>
       <c r="AN65" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=31381,nLevel=1,szName="禁捡旗",szNote="无法拾取大旗",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="捡",nPriority=11,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=2,szName="【{$receiver}】·禁止捡旗",nTime="30,【{$receiver}】·禁止捡旗;32,【{$receiver}】·可以捡旗",nRefresh=1,key="经脉逆行·{$receiver}",},{nClass=2,nIcon=13,nFrame=2,szName="【{$receiver}】·可以捡旗",nTime=5,key="经脉逆行·{$receiver}",},},},</v>
+        <v>{dwID=31381,nLevel=1,szName="禁捡旗",szNote="无法拾取大旗",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="捡",nPriority=11,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=22928,nFrame=2,szName="【{$receiver}】·禁止捡旗",nTime="30,【{$receiver}】·禁止捡旗;32,【{$receiver}】·可以捡旗",nRefresh=1,key="经脉逆行·{$receiver}",},{nClass=2,nIcon=13,nFrame=2,szName="【{$receiver}】·可以捡旗",nTime=5,key="经脉逆行·{$receiver}",},},},</v>
       </c>
       <c r="AO65" s="36" t="s">
-        <v>2690</v>
+        <v>2721</v>
       </c>
       <c r="AP65" s="36" t="s">
         <v>2391</v>
@@ -24840,7 +24837,7 @@
         <v>3</v>
       </c>
       <c r="AG69" s="36" t="s">
-        <v>2637</v>
+        <v>2635</v>
       </c>
       <c r="AI69" s="36">
         <v>0</v>
@@ -24960,13 +24957,13 @@
         <v>1</v>
       </c>
       <c r="G72" s="36" t="s">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="I72" s="36">
         <v>1</v>
       </c>
       <c r="K72" s="36" t="s">
-        <v>2510</v>
+        <v>2508</v>
       </c>
       <c r="L72" s="36" t="s">
         <v>2361</v>
@@ -24981,7 +24978,7 @@
         <v>37</v>
       </c>
       <c r="AG72" s="36" t="s">
-        <v>2511</v>
+        <v>2509</v>
       </c>
       <c r="AH72" s="36" t="s">
         <v>2364</v>
@@ -25060,16 +25057,16 @@
         <v>{dwID=29007,nLevel=1,nScrutinyType=1,szNote="九素化生·伤害距离",col={128,238,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=1,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=1,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=1,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=1,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=1,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=1,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=1,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=1,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=1,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=1,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=1,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=1,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},{nClass=2,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=2,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=2,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=2,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=2,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=2,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=2,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=2,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=2,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=2,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=2,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=2,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=2,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="AO74" s="40" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="AP74" s="40" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
       <c r="AQ74" s="38" t="s">
-        <v>2575</v>
+        <v>2573</v>
       </c>
       <c r="AR74" s="38" t="s">
-        <v>2576</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="75" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -25080,23 +25077,23 @@
         <v>1</v>
       </c>
       <c r="G75" s="36" t="s">
+        <v>2584</v>
+      </c>
+      <c r="I75" s="36">
+        <v>1</v>
+      </c>
+      <c r="K75" s="36" t="s">
         <v>2586</v>
       </c>
-      <c r="I75" s="36">
-        <v>1</v>
-      </c>
-      <c r="K75" s="36" t="s">
-        <v>2588</v>
-      </c>
       <c r="L75" s="36" t="s">
-        <v>2587</v>
+        <v>2585</v>
       </c>
       <c r="AN75" s="36" t="str">
         <f t="shared" si="1"/>
         <v>{dwID=11561,nLevel=1,szName="据点内",nScrutinyType=1,szNote="判断是否在大旗附近",col={80,231,236,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=1272,nFrame=2,szName="据点大旗·旗手提示",nTime=-1,key="据点大旗·旗手提示",},},},</v>
       </c>
       <c r="AO75" s="36" t="s">
-        <v>2730</v>
+        <v>2724</v>
       </c>
       <c r="AP75" s="39"/>
       <c r="AQ75" s="39"/>
@@ -25128,7 +25125,7 @@
         <v>1</v>
       </c>
       <c r="AG76" s="36" t="s">
-        <v>2491</v>
+        <v>2489</v>
       </c>
       <c r="AI76" s="36">
         <v>170</v>
@@ -25296,13 +25293,13 @@
         <v>16834</v>
       </c>
       <c r="G81" s="36" t="s">
-        <v>2704</v>
+        <v>2701</v>
       </c>
       <c r="K81" s="36" t="s">
-        <v>2699</v>
+        <v>2696</v>
       </c>
       <c r="L81" s="36" t="s">
-        <v>2701</v>
+        <v>2698</v>
       </c>
       <c r="T81" s="36">
         <v>1</v>
@@ -25311,26 +25308,26 @@
         <v>1</v>
       </c>
       <c r="AE81" s="36" t="s">
-        <v>2700</v>
+        <v>2697</v>
       </c>
       <c r="AF81" s="36">
         <v>37</v>
       </c>
       <c r="AG81" s="36" t="s">
-        <v>2702</v>
+        <v>2699</v>
       </c>
       <c r="AH81" s="36" t="s">
-        <v>2703</v>
+        <v>2700</v>
       </c>
       <c r="AI81" s="36">
         <v>255</v>
       </c>
       <c r="AN81" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=32813,nLevel=1,nIcon=16834,szName="旗易伤",szNote="旗帜受损",col={255,153,204,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="损",nPriority=37,col="#FF99CCFF",colScreenHead="#FF99CC",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=1,key="大旗赛点·CD",},},},</v>
+        <v>{dwID=32813,nLevel=1,nIcon=16834,szName="旗易伤",szNote="旗帜受损",col={255,153,204,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="损",nPriority=37,col="#FF99CCFF",colScreenHead="#FF99CC",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=0,key="大旗赛点·CD",},},},</v>
       </c>
       <c r="AO81" s="36" t="s">
-        <v>2708</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="82" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -25344,23 +25341,23 @@
         <v>3451</v>
       </c>
       <c r="G82" s="36" t="s">
-        <v>2705</v>
+        <v>2702</v>
       </c>
       <c r="K82" s="36" t="s">
-        <v>2706</v>
+        <v>2703</v>
       </c>
       <c r="L82" s="36" t="s">
-        <v>2707</v>
+        <v>2704</v>
       </c>
       <c r="T82" s="36">
         <v>1</v>
       </c>
       <c r="AN82" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=32812,nLevel=1,nIcon=3451,szName="损CD",szNote="据点大旗赛点CD",col={255,50,50,},[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=0,key="大旗赛点·CD",},},},</v>
+        <v>{dwID=32812,nLevel=1,nIcon=3451,szName="损CD",szNote="据点大旗赛点CD",col={255,50,50,},[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=1,key="大旗赛点·CD",},},},</v>
       </c>
       <c r="AO82" s="36" t="s">
-        <v>2710</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="83" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -25371,7 +25368,7 @@
         <v>1</v>
       </c>
       <c r="G83" s="36" t="s">
-        <v>2563</v>
+        <v>2561</v>
       </c>
       <c r="K83" s="36" t="s">
         <v>2385</v>
@@ -25386,7 +25383,7 @@
         <v>1</v>
       </c>
       <c r="AE83" s="36" t="s">
-        <v>2579</v>
+        <v>2577</v>
       </c>
       <c r="AF83" s="36">
         <v>11</v>
@@ -25405,10 +25402,10 @@
       </c>
       <c r="AN83" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=31381,nLevel=1,szName="禁捡旗",szNote="无法拾取大旗",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="捡",nPriority=11,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=2,szName="【{$receiver}】·禁止捡旗",nTime="30,【{$receiver}】·禁止捡旗;32,【{$receiver}】·可以捡旗",nRefresh=1,key="经脉逆行·{$receiver}",},{nClass=2,nIcon=13,nFrame=2,szName="【{$receiver}】·可以捡旗",nTime=5,key="经脉逆行·{$receiver}",},},},</v>
+        <v>{dwID=31381,nLevel=1,szName="禁捡旗",szNote="无法拾取大旗",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="捡",nPriority=11,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=22928,nFrame=2,szName="【{$receiver}】·禁止捡旗",nTime="30,【{$receiver}】·禁止捡旗;32,【{$receiver}】·可以捡旗",nRefresh=1,key="经脉逆行·{$receiver}",},{nClass=2,nIcon=13,nFrame=2,szName="【{$receiver}】·可以捡旗",nTime=5,key="经脉逆行·{$receiver}",},},},</v>
       </c>
       <c r="AO83" s="36" t="s">
-        <v>2690</v>
+        <v>2721</v>
       </c>
       <c r="AP83" s="36" t="s">
         <v>2391</v>
@@ -25593,7 +25590,7 @@
         <v>3</v>
       </c>
       <c r="AG87" s="36" t="s">
-        <v>2637</v>
+        <v>2635</v>
       </c>
       <c r="AI87" s="36">
         <v>0</v>
@@ -25713,13 +25710,13 @@
         <v>1</v>
       </c>
       <c r="G90" s="36" t="s">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="I90" s="36">
         <v>1</v>
       </c>
       <c r="K90" s="36" t="s">
-        <v>2510</v>
+        <v>2508</v>
       </c>
       <c r="L90" s="36" t="s">
         <v>2361</v>
@@ -25734,7 +25731,7 @@
         <v>37</v>
       </c>
       <c r="AG90" s="36" t="s">
-        <v>2511</v>
+        <v>2509</v>
       </c>
       <c r="AH90" s="36" t="s">
         <v>2364</v>
@@ -25813,16 +25810,16 @@
         <v>{dwID=29007,nLevel=1,nScrutinyType=1,szNote="九素化生·伤害距离",col={128,238,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=1,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=1,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=1,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=1,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=1,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=1,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=1,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=1,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=1,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=1,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=1,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=1,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},{nClass=2,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=2,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=2,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=2,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=2,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=2,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=2,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=2,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=2,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=2,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=2,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=2,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=2,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="AO92" s="40" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="AP92" s="40" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
       <c r="AQ92" s="38" t="s">
-        <v>2575</v>
+        <v>2573</v>
       </c>
       <c r="AR92" s="38" t="s">
-        <v>2576</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="93" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -25833,23 +25830,23 @@
         <v>1</v>
       </c>
       <c r="G93" s="36" t="s">
+        <v>2584</v>
+      </c>
+      <c r="I93" s="36">
+        <v>1</v>
+      </c>
+      <c r="K93" s="36" t="s">
         <v>2586</v>
       </c>
-      <c r="I93" s="36">
-        <v>1</v>
-      </c>
-      <c r="K93" s="36" t="s">
-        <v>2588</v>
-      </c>
       <c r="L93" s="36" t="s">
-        <v>2587</v>
+        <v>2585</v>
       </c>
       <c r="AN93" s="36" t="str">
         <f t="shared" si="1"/>
         <v>{dwID=11561,nLevel=1,szName="据点内",nScrutinyType=1,szNote="判断是否在大旗附近",col={80,231,236,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=1272,nFrame=2,szName="据点大旗·旗手提示",nTime=-1,key="据点大旗·旗手提示",},},},</v>
       </c>
       <c r="AO93" s="36" t="s">
-        <v>2730</v>
+        <v>2724</v>
       </c>
       <c r="AP93" s="39"/>
       <c r="AQ93" s="39"/>
@@ -25881,7 +25878,7 @@
         <v>1</v>
       </c>
       <c r="AG94" s="36" t="s">
-        <v>2491</v>
+        <v>2489</v>
       </c>
       <c r="AI94" s="36">
         <v>170</v>
@@ -25901,6 +25898,7 @@
       <c r="AN96" s="36"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:BY95" xr:uid="{ABA792D9-52CC-4EDA-9BC4-CFEC1886BBBF}"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -26046,13 +26044,13 @@
       </c>
       <c r="X4" s="36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7242,nLevel=1,szNote="屹立不倒",[9]={},[8]={bScreenHead=true,},tCountdown={{nClass=8,nIcon=1537,nFrame=0,nTime="1,屹立不倒·{$sender}·释放剩余;9.5,屹立不倒·{$sender}·50减伤;34,屹立不倒·{$sender}·释放剩余;40.5,屹立不倒·{$sender}·释放延迟",szName="屹立不倒",nRefresh=0,key="屹立不倒",},{nClass=9,nIcon=1537,nFrame=0,nTime="9,屹立不倒·{$sender}·50减伤;33.5,屹立不倒·{$sender}·释放剩余;40,屹立不倒·{$sender}·释放延迟",szName="屹立不倒",nRefresh=1,key="屹立不倒",},},},</v>
+        <v>{dwID=7242,nLevel=1,szNote="屹立不倒",[9]={},[8]={bScreenHead=true,},tCountdown={{nClass=8,nIcon=1537,nFrame=0,nTime="1,屹立不倒·{$sender}·正在释放;9.5,屹立不倒·{$sender}·50减伤;32.5,屹立不倒·{$sender}·释放剩余;40.5,屹立不倒·{$sender}·释放延迟",szName="屹立不倒",nRefresh=0,key="屹立不倒",},{nClass=9,nIcon=1537,nFrame=0,nTime="9,屹立不倒·{$sender}·50减伤;31.5,屹立不倒·{$sender}·释放剩余;40,屹立不倒·{$sender}·释放延迟",szName="屹立不倒",nRefresh=1,key="屹立不倒",},},},</v>
       </c>
       <c r="Y4" s="36" t="s">
-        <v>2722</v>
+        <v>2730</v>
       </c>
       <c r="Z4" s="36" t="s">
-        <v>2721</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.15">
@@ -26211,7 +26209,7 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>2687</v>
+        <v>2685</v>
       </c>
       <c r="B5">
         <v>-20</v>
@@ -26232,7 +26230,7 @@
         <v>2146</v>
       </c>
       <c r="U6" t="s">
-        <v>2685</v>
+        <v>2683</v>
       </c>
       <c r="V6" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26250,7 +26248,7 @@
         <v>2146</v>
       </c>
       <c r="U7" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V7" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26268,7 +26266,7 @@
         <v>2146</v>
       </c>
       <c r="U8" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V8" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26286,7 +26284,7 @@
         <v>2146</v>
       </c>
       <c r="U9" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V9" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26304,7 +26302,7 @@
         <v>2146</v>
       </c>
       <c r="U10" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V10" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26322,7 +26320,7 @@
         <v>2146</v>
       </c>
       <c r="U11" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V11" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26340,7 +26338,7 @@
         <v>2148</v>
       </c>
       <c r="U12" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V12" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26358,7 +26356,7 @@
         <v>2148</v>
       </c>
       <c r="U13" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V13" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26376,7 +26374,7 @@
         <v>2148</v>
       </c>
       <c r="U14" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V14" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26394,7 +26392,7 @@
         <v>2148</v>
       </c>
       <c r="U15" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V15" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26412,7 +26410,7 @@
         <v>2148</v>
       </c>
       <c r="U16" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V16" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26430,7 +26428,7 @@
         <v>2148</v>
       </c>
       <c r="U17" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V17" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26448,7 +26446,7 @@
         <v>2148</v>
       </c>
       <c r="U18" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V18" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26466,7 +26464,7 @@
         <v>2148</v>
       </c>
       <c r="U19" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V19" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26484,7 +26482,7 @@
         <v>2140</v>
       </c>
       <c r="U20" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V20" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26502,7 +26500,7 @@
         <v>2140</v>
       </c>
       <c r="U21" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V21" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26520,7 +26518,7 @@
         <v>2140</v>
       </c>
       <c r="U22" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V22" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26538,7 +26536,7 @@
         <v>2140</v>
       </c>
       <c r="U23" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V23" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26556,7 +26554,7 @@
         <v>2140</v>
       </c>
       <c r="U24" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V24" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26574,7 +26572,7 @@
         <v>2140</v>
       </c>
       <c r="U25" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V25" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26592,7 +26590,7 @@
         <v>2140</v>
       </c>
       <c r="U26" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V26" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26610,7 +26608,7 @@
         <v>2140</v>
       </c>
       <c r="U27" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V27" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26628,7 +26626,7 @@
         <v>2140</v>
       </c>
       <c r="U28" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V28" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26646,7 +26644,7 @@
         <v>2140</v>
       </c>
       <c r="U29" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V29" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26664,7 +26662,7 @@
         <v>2140</v>
       </c>
       <c r="U30" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V30" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26682,7 +26680,7 @@
         <v>2140</v>
       </c>
       <c r="U31" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V31" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26700,7 +26698,7 @@
         <v>2140</v>
       </c>
       <c r="U32" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V32" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26718,7 +26716,7 @@
         <v>2140</v>
       </c>
       <c r="U33" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V33" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26736,7 +26734,7 @@
         <v>2140</v>
       </c>
       <c r="U34" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V34" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26754,7 +26752,7 @@
         <v>2140</v>
       </c>
       <c r="U35" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V35" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26772,7 +26770,7 @@
         <v>2140</v>
       </c>
       <c r="U36" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V36" s="36" t="str">
         <f t="shared" si="0"/>
@@ -26922,7 +26920,7 @@
         <v>2071</v>
       </c>
       <c r="J43" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="O43" s="36">
         <v>1</v>
@@ -26955,7 +26953,7 @@
         <v>2070</v>
       </c>
       <c r="J44" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="O44" s="36">
         <v>1</v>
@@ -27042,7 +27040,7 @@
         <v>2072</v>
       </c>
       <c r="J47" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="P47" s="36">
         <v>1</v>
@@ -27066,7 +27064,7 @@
         <v>2073</v>
       </c>
       <c r="J48" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="P48" s="36">
         <v>1</v>
@@ -27090,7 +27088,7 @@
         <v>2065</v>
       </c>
       <c r="J49" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="P49" s="36">
         <v>1</v>
@@ -27114,7 +27112,7 @@
         <v>2066</v>
       </c>
       <c r="J50" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="P50" s="36">
         <v>1</v>
@@ -27180,13 +27178,13 @@
         <v>57</v>
       </c>
       <c r="I53" s="36" t="s">
-        <v>2691</v>
+        <v>2688</v>
       </c>
       <c r="P53" s="36">
         <v>1</v>
       </c>
       <c r="U53" s="36" t="s">
-        <v>2692</v>
+        <v>2689</v>
       </c>
       <c r="V53" s="36" t="str">
         <f t="shared" si="0"/>
@@ -27214,7 +27212,7 @@
         <v>{dwID=30310,nFrame=47,szNote="恶人谷大将",[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=90,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=60,tRelation={bAll=false,bEnemy=fals,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},},tCountdown={{nClass=12,nFrame=3,nIcon=18830,nTime=10,szName="恶人谷大将·退场",nRefresh=2,key="恶人谷大将",},},},</v>
       </c>
       <c r="W54" s="36" t="s">
-        <v>2501</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="55" spans="1:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -27238,7 +27236,7 @@
         <v>{dwID=30322,nFrame=47,szNote="浩气盟大将",[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=90,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=60,tRelation={bAll=false,bEnemy=fals,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},},tCountdown={{nClass=12,nFrame=7,nIcon=18829,nTime=10,szName="浩气盟大将·退场",nRefresh=2,key="浩气盟大将",},},},</v>
       </c>
       <c r="W55" s="36" t="s">
-        <v>2500</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="56" spans="1:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -27252,7 +27250,7 @@
         <v>1747</v>
       </c>
       <c r="J56" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="P56" s="36">
         <v>1</v>
@@ -27273,7 +27271,7 @@
         <v>1746</v>
       </c>
       <c r="J57" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="P57" s="36">
         <v>1</v>
@@ -27369,7 +27367,7 @@
         <v>2033</v>
       </c>
       <c r="J62" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="O62" s="36">
         <v>1</v>
@@ -27402,7 +27400,7 @@
         <v>2032</v>
       </c>
       <c r="J63" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="O63" s="36">
         <v>1</v>
@@ -27486,7 +27484,7 @@
         <v>52</v>
       </c>
       <c r="I66" s="36" t="s">
-        <v>2644</v>
+        <v>2642</v>
       </c>
       <c r="P66" s="36">
         <v>1</v>
@@ -27507,7 +27505,7 @@
         <v>1600</v>
       </c>
       <c r="J67" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="P67">
         <v>1</v>
@@ -27531,7 +27529,7 @@
         <v>1601</v>
       </c>
       <c r="J68" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="P68">
         <v>1</v>
@@ -27564,7 +27562,7 @@
         <v>1</v>
       </c>
       <c r="U69" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="V69" s="36" t="str">
         <f t="shared" si="1"/>
@@ -27663,7 +27661,7 @@
         <v>1599</v>
       </c>
       <c r="J74" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="P74">
         <v>1</v>
@@ -27687,7 +27685,7 @@
         <v>1599</v>
       </c>
       <c r="J75" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="P75">
         <v>1</v>
@@ -27708,7 +27706,7 @@
         <v>47</v>
       </c>
       <c r="I76" s="36" t="s">
-        <v>2618</v>
+        <v>2616</v>
       </c>
       <c r="J76" s="36" t="s">
         <v>1667</v>
@@ -27718,7 +27716,7 @@
         <v>1</v>
       </c>
       <c r="U76" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V76" s="36" t="str">
         <f t="shared" si="1"/>
@@ -27743,7 +27741,7 @@
         <v>1</v>
       </c>
       <c r="U77" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V77" s="36" t="str">
         <f t="shared" si="1"/>
@@ -27768,7 +27766,7 @@
         <v>1</v>
       </c>
       <c r="U78" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V78" s="36" t="str">
         <f t="shared" si="1"/>
@@ -27793,7 +27791,7 @@
         <v>1</v>
       </c>
       <c r="U79" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V79" s="36" t="str">
         <f t="shared" si="1"/>
@@ -27808,7 +27806,7 @@
         <v>47</v>
       </c>
       <c r="I80" s="36" t="s">
-        <v>2617</v>
+        <v>2615</v>
       </c>
       <c r="J80" s="36" t="s">
         <v>1667</v>
@@ -27818,7 +27816,7 @@
         <v>1</v>
       </c>
       <c r="U80" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V80" s="36" t="str">
         <f t="shared" si="1"/>
@@ -27843,7 +27841,7 @@
         <v>1</v>
       </c>
       <c r="U81" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V81" s="36" t="str">
         <f t="shared" si="1"/>
@@ -27868,7 +27866,7 @@
         <v>1</v>
       </c>
       <c r="U82" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V82" s="36" t="str">
         <f t="shared" si="1"/>
@@ -27893,7 +27891,7 @@
         <v>1</v>
       </c>
       <c r="U83" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V83" s="36" t="str">
         <f t="shared" si="1"/>
@@ -27918,7 +27916,7 @@
         <v>1</v>
       </c>
       <c r="U84" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V84" s="36" t="str">
         <f t="shared" si="1"/>
@@ -27943,7 +27941,7 @@
         <v>1</v>
       </c>
       <c r="U85" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V85" s="36" t="str">
         <f t="shared" si="1"/>
@@ -27968,7 +27966,7 @@
         <v>1</v>
       </c>
       <c r="U86" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V86" s="36" t="str">
         <f t="shared" si="1"/>
@@ -27993,7 +27991,7 @@
         <v>1</v>
       </c>
       <c r="U87" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V87" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28008,7 +28006,7 @@
         <v>47</v>
       </c>
       <c r="I88" t="s">
-        <v>2605</v>
+        <v>2603</v>
       </c>
       <c r="J88" s="36" t="s">
         <v>1667</v>
@@ -28018,7 +28016,7 @@
         <v>1</v>
       </c>
       <c r="U88" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V88" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28043,7 +28041,7 @@
         <v>1</v>
       </c>
       <c r="U89" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V89" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28068,7 +28066,7 @@
         <v>1</v>
       </c>
       <c r="U90" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V90" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28093,7 +28091,7 @@
         <v>1</v>
       </c>
       <c r="U91" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V91" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28118,7 +28116,7 @@
         <v>1</v>
       </c>
       <c r="U92" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V92" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28142,7 +28140,7 @@
         <v>1</v>
       </c>
       <c r="U93" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V93" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28167,7 +28165,7 @@
         <v>1</v>
       </c>
       <c r="U94" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V94" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28182,7 +28180,7 @@
         <v>47</v>
       </c>
       <c r="I95" s="36" t="s">
-        <v>2607</v>
+        <v>2605</v>
       </c>
       <c r="J95" s="36" t="s">
         <v>1667</v>
@@ -28194,7 +28192,7 @@
         <v>1</v>
       </c>
       <c r="U95" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V95" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28221,7 +28219,7 @@
         <v>1</v>
       </c>
       <c r="U96" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V96" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28248,7 +28246,7 @@
         <v>1</v>
       </c>
       <c r="U97" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V97" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28275,7 +28273,7 @@
         <v>1</v>
       </c>
       <c r="U98" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V98" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28302,7 +28300,7 @@
         <v>1</v>
       </c>
       <c r="U99" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V99" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28329,7 +28327,7 @@
         <v>1</v>
       </c>
       <c r="U100" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V100" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28356,7 +28354,7 @@
         <v>1</v>
       </c>
       <c r="U101" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V101" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28371,7 +28369,7 @@
         <v>47</v>
       </c>
       <c r="I102" s="36" t="s">
-        <v>2622</v>
+        <v>2620</v>
       </c>
       <c r="J102" s="36" t="s">
         <v>1667</v>
@@ -28383,7 +28381,7 @@
         <v>1</v>
       </c>
       <c r="U102" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V102" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28398,7 +28396,7 @@
         <v>47</v>
       </c>
       <c r="I103" s="36" t="s">
-        <v>2621</v>
+        <v>2619</v>
       </c>
       <c r="J103" s="36" t="s">
         <v>1667</v>
@@ -28410,7 +28408,7 @@
         <v>1</v>
       </c>
       <c r="U103" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V103" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28437,7 +28435,7 @@
         <v>1</v>
       </c>
       <c r="U104" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V104" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28464,7 +28462,7 @@
         <v>1</v>
       </c>
       <c r="U105" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V105" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28491,7 +28489,7 @@
         <v>1</v>
       </c>
       <c r="U106" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V106" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28515,17 +28513,17 @@
         <v>1</v>
       </c>
       <c r="U107" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V107" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=17237,nFrame=47,szNote="复活·恶人·顾延恶",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=30,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=0,szName="屹立不倒",key="屹立不倒",},},},</v>
+        <v>{dwID=17237,nFrame=47,szNote="复活·恶人·顾延恶",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=32.5,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=-1,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="W107" s="36" t="s">
-        <v>2394</v>
+        <v>2733</v>
       </c>
       <c r="X107" s="36" t="s">
-        <v>2395</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="108" spans="3:24" x14ac:dyDescent="0.15">
@@ -28546,17 +28544,17 @@
         <v>1</v>
       </c>
       <c r="U108" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V108" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=17238,nFrame=47,szNote="复活·恶人·吕沛杰",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=30,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=0,szName="屹立不倒",key="屹立不倒",},},},</v>
+        <v>{dwID=17238,nFrame=47,szNote="复活·恶人·吕沛杰",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=32.5,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=-1,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="W108" s="36" t="s">
-        <v>2394</v>
+        <v>2733</v>
       </c>
       <c r="X108" s="36" t="s">
-        <v>2395</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="109" spans="3:24" x14ac:dyDescent="0.15">
@@ -28577,17 +28575,17 @@
         <v>1</v>
       </c>
       <c r="U109" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V109" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=17240,nFrame=47,szNote="复活·恶人·陶国栋",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=30,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=0,szName="屹立不倒",key="屹立不倒",},},},</v>
+        <v>{dwID=17240,nFrame=47,szNote="复活·恶人·陶国栋",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=32.5,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=-1,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="W109" s="36" t="s">
-        <v>2394</v>
+        <v>2733</v>
       </c>
       <c r="X109" s="36" t="s">
-        <v>2395</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="110" spans="3:24" x14ac:dyDescent="0.15">
@@ -28608,17 +28606,17 @@
         <v>1</v>
       </c>
       <c r="U110" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V110" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=17239,nFrame=47,szNote="复活·恶人·张一洋",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=30,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=0,szName="屹立不倒",key="屹立不倒",},},},</v>
+        <v>{dwID=17239,nFrame=47,szNote="复活·恶人·张一洋",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=32.5,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=-1,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="W110" s="36" t="s">
-        <v>2394</v>
+        <v>2733</v>
       </c>
       <c r="X110" s="36" t="s">
-        <v>2395</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="111" spans="3:24" x14ac:dyDescent="0.15">
@@ -28639,17 +28637,17 @@
         <v>1</v>
       </c>
       <c r="U111" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V111" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=8954,nFrame=47,szNote="复活·浩气·陶杰",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=30,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=0,szName="屹立不倒",key="屹立不倒",},},},</v>
+        <v>{dwID=8954,nFrame=47,szNote="复活·浩气·陶杰",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=32.5,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=-1,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="W111" s="36" t="s">
-        <v>2394</v>
+        <v>2733</v>
       </c>
       <c r="X111" s="36" t="s">
-        <v>2395</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="112" spans="3:24" x14ac:dyDescent="0.15">
@@ -28670,17 +28668,17 @@
         <v>1</v>
       </c>
       <c r="U112" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V112" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=6230,nFrame=47,szNote="复活·浩气·谢烟客",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=30,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=0,szName="屹立不倒",key="屹立不倒",},},},</v>
+        <v>{dwID=6230,nFrame=47,szNote="复活·浩气·谢烟客",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=32.5,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=-1,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="W112" s="36" t="s">
-        <v>2394</v>
+        <v>2733</v>
       </c>
       <c r="X112" s="36" t="s">
-        <v>2395</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.15">
@@ -28701,17 +28699,17 @@
         <v>1</v>
       </c>
       <c r="U113" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V113" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=8952,nFrame=47,szNote="复活·浩气·郑鸥",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=30,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=0,szName="屹立不倒",key="屹立不倒",},},},</v>
+        <v>{dwID=8952,nFrame=47,szNote="复活·浩气·郑鸥",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=32.5,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=-1,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="W113" s="36" t="s">
-        <v>2394</v>
+        <v>2733</v>
       </c>
       <c r="X113" s="36" t="s">
-        <v>2395</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="114" spans="1:24" x14ac:dyDescent="0.15">
@@ -28732,17 +28730,17 @@
         <v>1</v>
       </c>
       <c r="U114" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V114" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=8953,nFrame=47,szNote="复活·浩气·周峰",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=30,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=0,szName="屹立不倒",key="屹立不倒",},},},</v>
+        <v>{dwID=8953,nFrame=47,szNote="复活·浩气·周峰",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=32.5,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=-1,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="W114" s="36" t="s">
-        <v>2394</v>
+        <v>2733</v>
       </c>
       <c r="X114" s="36" t="s">
-        <v>2395</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="115" spans="1:24" x14ac:dyDescent="0.15">
@@ -28810,7 +28808,7 @@
         <v>1603</v>
       </c>
       <c r="J118" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="P118">
         <v>1</v>
@@ -28834,7 +28832,7 @@
         <v>1598</v>
       </c>
       <c r="J119" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="P119">
         <v>1</v>
@@ -28855,7 +28853,7 @@
         <v>47</v>
       </c>
       <c r="I120" t="s">
-        <v>2618</v>
+        <v>2616</v>
       </c>
       <c r="J120" s="36" t="s">
         <v>1667</v>
@@ -28865,7 +28863,7 @@
         <v>1</v>
       </c>
       <c r="U120" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V120" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28880,7 +28878,7 @@
         <v>47</v>
       </c>
       <c r="I121" t="s">
-        <v>2620</v>
+        <v>2618</v>
       </c>
       <c r="J121" s="36" t="s">
         <v>1667</v>
@@ -28890,7 +28888,7 @@
         <v>1</v>
       </c>
       <c r="U121" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V121" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28915,7 +28913,7 @@
         <v>1</v>
       </c>
       <c r="U122" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V122" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28940,7 +28938,7 @@
         <v>1</v>
       </c>
       <c r="U123" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V123" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28955,7 +28953,7 @@
         <v>47</v>
       </c>
       <c r="I124" s="36" t="s">
-        <v>2617</v>
+        <v>2615</v>
       </c>
       <c r="J124" s="36" t="s">
         <v>1667</v>
@@ -28965,7 +28963,7 @@
         <v>1</v>
       </c>
       <c r="U124" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V124" s="36" t="str">
         <f t="shared" si="1"/>
@@ -28990,7 +28988,7 @@
         <v>1</v>
       </c>
       <c r="U125" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V125" s="36" t="str">
         <f t="shared" si="1"/>
@@ -29015,7 +29013,7 @@
         <v>1</v>
       </c>
       <c r="U126" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V126" s="36" t="str">
         <f t="shared" si="1"/>
@@ -29040,7 +29038,7 @@
         <v>1</v>
       </c>
       <c r="U127" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V127" s="36" t="str">
         <f t="shared" si="1"/>
@@ -29065,7 +29063,7 @@
         <v>1</v>
       </c>
       <c r="U128" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V128" s="36" t="str">
         <f t="shared" si="1"/>
@@ -29090,7 +29088,7 @@
         <v>1</v>
       </c>
       <c r="U129" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V129" s="36" t="str">
         <f t="shared" si="1"/>
@@ -29115,7 +29113,7 @@
         <v>1</v>
       </c>
       <c r="U130" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V130" s="36" t="str">
         <f t="shared" ref="V130:V193" si="2">IF(ISBLANK(B130)=FALSE,IF(ISBLANK(B129),"},["&amp;B130&amp;"]={","["&amp;B130&amp;"]={"),IF(AND(ISBLANK(B130),ISBLANK(D130),ISBLANK(C130),OR(ISBLANK(B129)=FALSE,ISBLANK(D129)=FALSE,ISBLANK(C129)=FALSE)),"},},}",IF(ISBLANK(C130),"","{dwID="&amp;C130&amp;","&amp;"nFrame="&amp;D130&amp;","&amp;IF(E130&gt;0,"nCount="&amp;E130&amp;",","")&amp;IF(F130&gt;0,"bAllLeave=true,","")&amp;IF(G130&lt;&gt;"","szName="""&amp;G130&amp;""",","")&amp;IF(H130&lt;&gt;"","tKungFu={"&amp;H130&amp;"},","")&amp;IF(I130&lt;&gt;"","szNote="""&amp;I130&amp;""",","")&amp;IF(J130&lt;&gt;"","col={"&amp;J130&amp;"},","")&amp;"[3]={"&amp;IF(K130&lt;&gt;"","tMark={"&amp;K130&amp;"},","")&amp;IF(L130&lt;&gt;"","szVoice="""&amp;L130&amp;""",","")&amp;IF(M130&gt;0,"bTeamChannel=true,","")&amp;IF(N130&gt;0,"bWhisperChannel=true,","")&amp;IF(O130&gt;0,"bCenterAlarm=true,","")&amp;IF(P130&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q130&lt;&gt;"","szVoice="""&amp;Q130&amp;""",","")&amp;IF(R130&gt;0,"bTeamChannel=true,","")&amp;IF(S130&gt;0,"bWhisperChannel=true,","")&amp;IF(T130&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U130&lt;&gt;"","aFocus={"&amp;U130&amp;"},","")&amp;IF(W130&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W130:ZZ130)&amp;"},","")&amp;"},")))</f>
@@ -29140,7 +29138,7 @@
         <v>1</v>
       </c>
       <c r="U131" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V131" s="36" t="str">
         <f t="shared" si="2"/>
@@ -29155,7 +29153,7 @@
         <v>47</v>
       </c>
       <c r="I132" t="s">
-        <v>2619</v>
+        <v>2617</v>
       </c>
       <c r="J132" s="36" t="s">
         <v>1667</v>
@@ -29165,7 +29163,7 @@
         <v>1</v>
       </c>
       <c r="U132" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V132" s="36" t="str">
         <f t="shared" si="2"/>
@@ -29190,7 +29188,7 @@
         <v>1</v>
       </c>
       <c r="U133" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V133" s="36" t="str">
         <f t="shared" si="2"/>
@@ -29215,7 +29213,7 @@
         <v>1</v>
       </c>
       <c r="U134" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V134" s="36" t="str">
         <f t="shared" si="2"/>
@@ -29240,7 +29238,7 @@
         <v>1</v>
       </c>
       <c r="U135" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V135" s="36" t="str">
         <f t="shared" si="2"/>
@@ -29265,7 +29263,7 @@
         <v>1</v>
       </c>
       <c r="U136" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V136" s="36" t="str">
         <f t="shared" si="2"/>
@@ -29289,7 +29287,7 @@
         <v>1</v>
       </c>
       <c r="U137" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V137" s="36" t="str">
         <f t="shared" si="2"/>
@@ -29314,7 +29312,7 @@
         <v>1</v>
       </c>
       <c r="U138" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V138" s="36" t="str">
         <f t="shared" si="2"/>
@@ -29329,7 +29327,7 @@
         <v>47</v>
       </c>
       <c r="I139" t="s">
-        <v>2606</v>
+        <v>2604</v>
       </c>
       <c r="J139" s="36" t="s">
         <v>1667</v>
@@ -29341,7 +29339,7 @@
         <v>1</v>
       </c>
       <c r="U139" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V139" s="36" t="str">
         <f t="shared" si="2"/>
@@ -29368,7 +29366,7 @@
         <v>1</v>
       </c>
       <c r="U140" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V140" s="36" t="str">
         <f t="shared" si="2"/>
@@ -29395,7 +29393,7 @@
         <v>1</v>
       </c>
       <c r="U141" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V141" s="36" t="str">
         <f t="shared" si="2"/>
@@ -29422,7 +29420,7 @@
         <v>1</v>
       </c>
       <c r="U142" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V142" s="36" t="str">
         <f t="shared" si="2"/>
@@ -29449,7 +29447,7 @@
         <v>1</v>
       </c>
       <c r="U143" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V143" s="36" t="str">
         <f t="shared" si="2"/>
@@ -29476,7 +29474,7 @@
         <v>1</v>
       </c>
       <c r="U144" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V144" s="36" t="str">
         <f t="shared" si="2"/>
@@ -29503,7 +29501,7 @@
         <v>1</v>
       </c>
       <c r="U145" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V145" s="36" t="str">
         <f t="shared" si="2"/>
@@ -29530,7 +29528,7 @@
         <v>1</v>
       </c>
       <c r="U146" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V146" s="36" t="str">
         <f t="shared" si="2"/>
@@ -29557,7 +29555,7 @@
         <v>1</v>
       </c>
       <c r="U147" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V147" s="36" t="str">
         <f t="shared" si="2"/>
@@ -29584,7 +29582,7 @@
         <v>1</v>
       </c>
       <c r="U148" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V148" s="36" t="str">
         <f t="shared" si="2"/>
@@ -29611,7 +29609,7 @@
         <v>1</v>
       </c>
       <c r="U149" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V149" s="36" t="str">
         <f t="shared" si="2"/>
@@ -29638,7 +29636,7 @@
         <v>1</v>
       </c>
       <c r="U150" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V150" s="36" t="str">
         <f t="shared" si="2"/>
@@ -29663,17 +29661,17 @@
         <v>1</v>
       </c>
       <c r="U151" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V151" s="36" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=6233,nFrame=47,szNote="复活·恶人·顾延恶",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=30,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=0,szName="屹立不倒",key="屹立不倒",},},},</v>
+        <v>{dwID=6233,nFrame=47,szNote="复活·恶人·顾延恶",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=32.5,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=-1,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="W151" s="36" t="s">
-        <v>2394</v>
+        <v>2733</v>
       </c>
       <c r="X151" s="36" t="s">
-        <v>2395</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="152" spans="1:24" x14ac:dyDescent="0.15">
@@ -29694,17 +29692,17 @@
         <v>1</v>
       </c>
       <c r="U152" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V152" s="36" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=8956,nFrame=47,szNote="复活·恶人·吕沛杰",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=30,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=0,szName="屹立不倒",key="屹立不倒",},},},</v>
+        <v>{dwID=8956,nFrame=47,szNote="复活·恶人·吕沛杰",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=32.5,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=-1,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="W152" s="36" t="s">
-        <v>2394</v>
+        <v>2733</v>
       </c>
       <c r="X152" s="36" t="s">
-        <v>2395</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="153" spans="1:24" x14ac:dyDescent="0.15">
@@ -29725,17 +29723,17 @@
         <v>1</v>
       </c>
       <c r="U153" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V153" s="36" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=8955,nFrame=47,szNote="复活·恶人·陶国栋",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=30,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=0,szName="屹立不倒",key="屹立不倒",},},},</v>
+        <v>{dwID=8955,nFrame=47,szNote="复活·恶人·陶国栋",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=32.5,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=-1,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="W153" s="36" t="s">
-        <v>2394</v>
+        <v>2733</v>
       </c>
       <c r="X153" s="36" t="s">
-        <v>2395</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="154" spans="1:24" x14ac:dyDescent="0.15">
@@ -29756,17 +29754,17 @@
         <v>1</v>
       </c>
       <c r="U154" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V154" s="36" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=8957,nFrame=47,szNote="复活·恶人·张一洋",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=30,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=0,szName="屹立不倒",key="屹立不倒",},},},</v>
+        <v>{dwID=8957,nFrame=47,szNote="复活·恶人·张一洋",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=32.5,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=-1,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="W154" s="36" t="s">
-        <v>2394</v>
+        <v>2733</v>
       </c>
       <c r="X154" s="36" t="s">
-        <v>2395</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="155" spans="1:24" x14ac:dyDescent="0.15">
@@ -29787,17 +29785,17 @@
         <v>1</v>
       </c>
       <c r="U155" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V155" s="36" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=17234,nFrame=47,szNote="复活·浩气·陶杰",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=30,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=0,szName="屹立不倒",key="屹立不倒",},},},</v>
+        <v>{dwID=17234,nFrame=47,szNote="复活·浩气·陶杰",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=32.5,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=-1,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="W155" s="36" t="s">
-        <v>2394</v>
+        <v>2733</v>
       </c>
       <c r="X155" s="36" t="s">
-        <v>2395</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="156" spans="1:24" x14ac:dyDescent="0.15">
@@ -29818,17 +29816,17 @@
         <v>1</v>
       </c>
       <c r="U156" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V156" s="36" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=17233,nFrame=47,szNote="复活·浩气·谢烟客",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=30,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=0,szName="屹立不倒",key="屹立不倒",},},},</v>
+        <v>{dwID=17233,nFrame=47,szNote="复活·浩气·谢烟客",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=32.5,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=-1,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="W156" s="36" t="s">
-        <v>2394</v>
+        <v>2733</v>
       </c>
       <c r="X156" s="36" t="s">
-        <v>2395</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="157" spans="1:24" x14ac:dyDescent="0.15">
@@ -29849,17 +29847,17 @@
         <v>1</v>
       </c>
       <c r="U157" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V157" s="36" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=17236,nFrame=47,szNote="复活·浩气·郑鸥",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=30,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=0,szName="屹立不倒",key="屹立不倒",},},},</v>
+        <v>{dwID=17236,nFrame=47,szNote="复活·浩气·郑鸥",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=32.5,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=-1,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="W157" s="36" t="s">
-        <v>2394</v>
+        <v>2733</v>
       </c>
       <c r="X157" s="36" t="s">
-        <v>2395</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="158" spans="1:24" x14ac:dyDescent="0.15">
@@ -29880,17 +29878,17 @@
         <v>1</v>
       </c>
       <c r="U158" s="36" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="V158" s="36" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=17235,nFrame=47,szNote="复活·浩气·周峰",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=30,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=0,szName="屹立不倒",key="屹立不倒",},},},</v>
+        <v>{dwID=17235,nFrame=47,szNote="复活·浩气·周峰",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=120,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=50,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;=",nValue=99,},},{dwMapID=-1,nMaxDistance=20,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=99,},},},tCountdown={{nClass=7,nIcon=1537,nFrame=0,nTime=32.5,szName="屹立不倒·{$receiver}·释放剩余",key="屹立不倒",},{nClass=4,nIcon=13,nTime=-1,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="W158" s="36" t="s">
-        <v>2394</v>
+        <v>2733</v>
       </c>
       <c r="X158" s="36" t="s">
-        <v>2395</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="159" spans="1:24" x14ac:dyDescent="0.15">
@@ -29916,7 +29914,7 @@
         <v>1692</v>
       </c>
       <c r="J160" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="P160">
         <v>1</v>
@@ -29940,7 +29938,7 @@
         <v>1690</v>
       </c>
       <c r="J161" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="P161">
         <v>1</v>
@@ -30138,7 +30136,7 @@
         <v>2316</v>
       </c>
       <c r="J170" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="P170" s="36">
         <v>1</v>
@@ -30198,7 +30196,7 @@
         <v>1692</v>
       </c>
       <c r="J173" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="P173">
         <v>1</v>
@@ -30222,7 +30220,7 @@
         <v>1690</v>
       </c>
       <c r="J174" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="P174">
         <v>1</v>
@@ -30468,7 +30466,7 @@
         <v>2315</v>
       </c>
       <c r="J185" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="P185" s="36">
         <v>1</v>
@@ -30537,7 +30535,7 @@
         <v>2142</v>
       </c>
       <c r="U188" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V188" s="36" t="str">
         <f t="shared" si="2"/>
@@ -30555,7 +30553,7 @@
         <v>2142</v>
       </c>
       <c r="U189" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V189" s="36" t="str">
         <f t="shared" si="2"/>
@@ -30573,7 +30571,7 @@
         <v>2142</v>
       </c>
       <c r="U190" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V190" s="36" t="str">
         <f t="shared" si="2"/>
@@ -30591,7 +30589,7 @@
         <v>2142</v>
       </c>
       <c r="U191" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V191" s="36" t="str">
         <f t="shared" si="2"/>
@@ -30609,7 +30607,7 @@
         <v>2158</v>
       </c>
       <c r="U192" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V192" s="36" t="str">
         <f t="shared" si="2"/>
@@ -30627,7 +30625,7 @@
         <v>2158</v>
       </c>
       <c r="U193" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V193" s="36" t="str">
         <f t="shared" si="2"/>
@@ -30645,7 +30643,7 @@
         <v>2158</v>
       </c>
       <c r="U194" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V194" s="36" t="str">
         <f t="shared" ref="V194:V257" si="3">IF(ISBLANK(B194)=FALSE,IF(ISBLANK(B193),"},["&amp;B194&amp;"]={","["&amp;B194&amp;"]={"),IF(AND(ISBLANK(B194),ISBLANK(D194),ISBLANK(C194),OR(ISBLANK(B193)=FALSE,ISBLANK(D193)=FALSE,ISBLANK(C193)=FALSE)),"},},}",IF(ISBLANK(C194),"","{dwID="&amp;C194&amp;","&amp;"nFrame="&amp;D194&amp;","&amp;IF(E194&gt;0,"nCount="&amp;E194&amp;",","")&amp;IF(F194&gt;0,"bAllLeave=true,","")&amp;IF(G194&lt;&gt;"","szName="""&amp;G194&amp;""",","")&amp;IF(H194&lt;&gt;"","tKungFu={"&amp;H194&amp;"},","")&amp;IF(I194&lt;&gt;"","szNote="""&amp;I194&amp;""",","")&amp;IF(J194&lt;&gt;"","col={"&amp;J194&amp;"},","")&amp;"[3]={"&amp;IF(K194&lt;&gt;"","tMark={"&amp;K194&amp;"},","")&amp;IF(L194&lt;&gt;"","szVoice="""&amp;L194&amp;""",","")&amp;IF(M194&gt;0,"bTeamChannel=true,","")&amp;IF(N194&gt;0,"bWhisperChannel=true,","")&amp;IF(O194&gt;0,"bCenterAlarm=true,","")&amp;IF(P194&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q194&lt;&gt;"","szVoice="""&amp;Q194&amp;""",","")&amp;IF(R194&gt;0,"bTeamChannel=true,","")&amp;IF(S194&gt;0,"bWhisperChannel=true,","")&amp;IF(T194&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U194&lt;&gt;"","aFocus={"&amp;U194&amp;"},","")&amp;IF(W194&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W194:ZZ194)&amp;"},","")&amp;"},")))</f>
@@ -30663,7 +30661,7 @@
         <v>2158</v>
       </c>
       <c r="U195" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V195" s="36" t="str">
         <f t="shared" si="3"/>
@@ -30681,7 +30679,7 @@
         <v>2158</v>
       </c>
       <c r="U196" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V196" s="36" t="str">
         <f t="shared" si="3"/>
@@ -30699,7 +30697,7 @@
         <v>2158</v>
       </c>
       <c r="U197" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V197" s="36" t="str">
         <f t="shared" si="3"/>
@@ -30729,7 +30727,7 @@
         <v>2316</v>
       </c>
       <c r="J199" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="P199" s="36">
         <v>1</v>
@@ -30954,7 +30952,7 @@
         <v>2315</v>
       </c>
       <c r="J209" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="P209" s="36">
         <v>1</v>
@@ -31299,7 +31297,7 @@
         <v>2147</v>
       </c>
       <c r="U224" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V224" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31317,7 +31315,7 @@
         <v>2147</v>
       </c>
       <c r="U225" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V225" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31335,7 +31333,7 @@
         <v>2147</v>
       </c>
       <c r="U226" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V226" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31353,7 +31351,7 @@
         <v>2147</v>
       </c>
       <c r="U227" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V227" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31371,7 +31369,7 @@
         <v>2149</v>
       </c>
       <c r="U228" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V228" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31389,7 +31387,7 @@
         <v>2149</v>
       </c>
       <c r="U229" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V229" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31407,7 +31405,7 @@
         <v>2149</v>
       </c>
       <c r="U230" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V230" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31425,7 +31423,7 @@
         <v>2141</v>
       </c>
       <c r="U231" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V231" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31443,7 +31441,7 @@
         <v>2141</v>
       </c>
       <c r="U232" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V232" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31461,7 +31459,7 @@
         <v>2141</v>
       </c>
       <c r="U233" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V233" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31479,7 +31477,7 @@
         <v>2141</v>
       </c>
       <c r="U234" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V234" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31497,7 +31495,7 @@
         <v>2141</v>
       </c>
       <c r="U235" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V235" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31515,7 +31513,7 @@
         <v>2141</v>
       </c>
       <c r="U236" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V236" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31533,7 +31531,7 @@
         <v>2141</v>
       </c>
       <c r="U237" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V237" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31551,7 +31549,7 @@
         <v>2141</v>
       </c>
       <c r="U238" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V238" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31569,7 +31567,7 @@
         <v>2141</v>
       </c>
       <c r="U239" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V239" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31587,7 +31585,7 @@
         <v>2141</v>
       </c>
       <c r="U240" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V240" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31605,7 +31603,7 @@
         <v>2159</v>
       </c>
       <c r="U241" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V241" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31623,7 +31621,7 @@
         <v>2141</v>
       </c>
       <c r="U242" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V242" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31653,7 +31651,7 @@
         <v>2316</v>
       </c>
       <c r="J244" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="P244" s="36">
         <v>1</v>
@@ -31860,7 +31858,7 @@
         <v>2157</v>
       </c>
       <c r="U253" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V253" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31878,7 +31876,7 @@
         <v>2143</v>
       </c>
       <c r="U254" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V254" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31896,7 +31894,7 @@
         <v>2143</v>
       </c>
       <c r="U255" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V255" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31914,7 +31912,7 @@
         <v>2143</v>
       </c>
       <c r="U256" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V256" s="36" t="str">
         <f t="shared" si="3"/>
@@ -31932,7 +31930,7 @@
         <v>2143</v>
       </c>
       <c r="U257" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V257" s="36" t="str">
         <f t="shared" si="3"/>
@@ -32145,7 +32143,7 @@
         <v>2144</v>
       </c>
       <c r="U267" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V267" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32175,7 +32173,7 @@
         <v>2315</v>
       </c>
       <c r="J269" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="P269" s="36">
         <v>1</v>
@@ -32328,7 +32326,7 @@
         <v>2316</v>
       </c>
       <c r="J276" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="P276" s="36">
         <v>1</v>
@@ -32508,7 +32506,7 @@
         <v>2151</v>
       </c>
       <c r="U284" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V284" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32526,7 +32524,7 @@
         <v>2151</v>
       </c>
       <c r="U285" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V285" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32544,7 +32542,7 @@
         <v>2150</v>
       </c>
       <c r="U286" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V286" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32562,7 +32560,7 @@
         <v>2150</v>
       </c>
       <c r="U287" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V287" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32580,7 +32578,7 @@
         <v>2158</v>
       </c>
       <c r="U288" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V288" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32598,7 +32596,7 @@
         <v>2158</v>
       </c>
       <c r="U289" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V289" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32616,7 +32614,7 @@
         <v>2158</v>
       </c>
       <c r="U290" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V290" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32634,7 +32632,7 @@
         <v>2158</v>
       </c>
       <c r="U291" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V291" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32652,7 +32650,7 @@
         <v>2158</v>
       </c>
       <c r="U292" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V292" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32670,7 +32668,7 @@
         <v>2158</v>
       </c>
       <c r="U293" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V293" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32688,7 +32686,7 @@
         <v>2145</v>
       </c>
       <c r="U294" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V294" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32706,7 +32704,7 @@
         <v>2145</v>
       </c>
       <c r="U295" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V295" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32724,7 +32722,7 @@
         <v>2145</v>
       </c>
       <c r="U296" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V296" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32742,7 +32740,7 @@
         <v>2145</v>
       </c>
       <c r="U297" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V297" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32760,7 +32758,7 @@
         <v>2145</v>
       </c>
       <c r="U298" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V298" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32778,7 +32776,7 @@
         <v>2145</v>
       </c>
       <c r="U299" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V299" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32796,7 +32794,7 @@
         <v>2145</v>
       </c>
       <c r="U300" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V300" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32814,7 +32812,7 @@
         <v>2145</v>
       </c>
       <c r="U301" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V301" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32898,7 +32896,7 @@
         <v>2157</v>
       </c>
       <c r="U305" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V305" s="36" t="str">
         <f t="shared" si="4"/>
@@ -32928,7 +32926,7 @@
         <v>2315</v>
       </c>
       <c r="J307" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="P307" s="36">
         <v>1</v>
@@ -33066,7 +33064,7 @@
         <v>2152</v>
       </c>
       <c r="U313" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V313" s="36" t="str">
         <f t="shared" si="4"/>
@@ -33084,7 +33082,7 @@
         <v>2159</v>
       </c>
       <c r="U314" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V314" s="36" t="str">
         <f t="shared" si="4"/>
@@ -33213,7 +33211,7 @@
         <v>1707</v>
       </c>
       <c r="J321" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="P321">
         <v>1</v>
@@ -33237,7 +33235,7 @@
         <v>1708</v>
       </c>
       <c r="J322" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="P322">
         <v>1</v>
@@ -33261,7 +33259,7 @@
         <v>2313</v>
       </c>
       <c r="J323" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="P323">
         <v>1</v>
@@ -33285,7 +33283,7 @@
         <v>2314</v>
       </c>
       <c r="J324" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="P324">
         <v>1</v>
@@ -33414,7 +33412,7 @@
         <v>1707</v>
       </c>
       <c r="J329" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="P329">
         <v>1</v>
@@ -33438,7 +33436,7 @@
         <v>1708</v>
       </c>
       <c r="J330" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="P330">
         <v>1</v>
@@ -33601,7 +33599,7 @@
         <v>{dwID=123976,nFrame=47,szNote="恶人谷大将",[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=90,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=60,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},},tCountdown={{nClass=12,nFrame=3,nIcon=18830,nTime=10,szName="恶人谷大将·退场",nRefresh=2,key="恶人谷大将",},},},</v>
       </c>
       <c r="W337" s="36" t="s">
-        <v>2501</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="338" spans="3:23" x14ac:dyDescent="0.15">
@@ -33625,7 +33623,7 @@
         <v>{dwID=123975,nFrame=47,szNote="浩气盟大将",[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=90,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=60,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},},tCountdown={{nClass=12,nFrame=7,nIcon=18829,nTime=10,szName="浩气盟大将·退场",nRefresh=2,key="浩气盟大将",},},},</v>
       </c>
       <c r="W338" s="36" t="s">
-        <v>2500</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="339" spans="3:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -33723,7 +33721,7 @@
         <v>1752</v>
       </c>
       <c r="U343" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V343" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33741,7 +33739,7 @@
         <v>1752</v>
       </c>
       <c r="U344" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V344" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33759,7 +33757,7 @@
         <v>1752</v>
       </c>
       <c r="U345" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V345" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33777,7 +33775,7 @@
         <v>1752</v>
       </c>
       <c r="U346" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V346" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33795,7 +33793,7 @@
         <v>1753</v>
       </c>
       <c r="U347" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V347" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33813,7 +33811,7 @@
         <v>1753</v>
       </c>
       <c r="U348" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V348" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33831,7 +33829,7 @@
         <v>1753</v>
       </c>
       <c r="U349" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V349" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33849,7 +33847,7 @@
         <v>1753</v>
       </c>
       <c r="U350" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V350" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33867,7 +33865,7 @@
         <v>1757</v>
       </c>
       <c r="U351" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V351" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33885,7 +33883,7 @@
         <v>1757</v>
       </c>
       <c r="U352" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V352" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33903,7 +33901,7 @@
         <v>1757</v>
       </c>
       <c r="U353" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V353" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33921,7 +33919,7 @@
         <v>1757</v>
       </c>
       <c r="U354" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V354" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33939,7 +33937,7 @@
         <v>1757</v>
       </c>
       <c r="U355" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V355" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33957,7 +33955,7 @@
         <v>1757</v>
       </c>
       <c r="U356" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V356" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33975,7 +33973,7 @@
         <v>1757</v>
       </c>
       <c r="U357" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V357" s="36" t="str">
         <f t="shared" si="5"/>
@@ -33993,7 +33991,7 @@
         <v>1757</v>
       </c>
       <c r="U358" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V358" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34011,7 +34009,7 @@
         <v>1757</v>
       </c>
       <c r="U359" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V359" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34029,7 +34027,7 @@
         <v>1757</v>
       </c>
       <c r="U360" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V360" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34047,7 +34045,7 @@
         <v>1757</v>
       </c>
       <c r="U361" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V361" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34065,7 +34063,7 @@
         <v>1757</v>
       </c>
       <c r="U362" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V362" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34083,7 +34081,7 @@
         <v>1757</v>
       </c>
       <c r="U363" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V363" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34101,7 +34099,7 @@
         <v>1757</v>
       </c>
       <c r="U364" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V364" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34119,7 +34117,7 @@
         <v>1757</v>
       </c>
       <c r="U365" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V365" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34137,7 +34135,7 @@
         <v>1757</v>
       </c>
       <c r="U366" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V366" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34260,13 +34258,13 @@
         <v>57</v>
       </c>
       <c r="I372" s="36" t="s">
-        <v>2691</v>
+        <v>2688</v>
       </c>
       <c r="P372" s="36">
         <v>1</v>
       </c>
       <c r="U372" s="36" t="s">
-        <v>2692</v>
+        <v>2689</v>
       </c>
       <c r="V372" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34384,7 +34382,7 @@
         <v>{dwID=123976,nFrame=47,szNote="恶人谷大将",[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=90,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=60,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},},tCountdown={{nClass=12,nFrame=3,nIcon=18830,nTime=10,szName="恶人谷大将·退场",nRefresh=2,key="恶人谷大将",},},},</v>
       </c>
       <c r="W377" s="36" t="s">
-        <v>2501</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="378" spans="1:23" x14ac:dyDescent="0.15">
@@ -34408,7 +34406,7 @@
         <v>{dwID=123975,nFrame=47,szNote="浩气盟大将",[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=90,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,nMaxDistance=60,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},},tCountdown={{nClass=12,nFrame=7,nIcon=18829,nTime=10,szName="浩气盟大将·退场",nRefresh=2,key="浩气盟大将",},},},</v>
       </c>
       <c r="W378" s="36" t="s">
-        <v>2500</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="379" spans="1:23" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -34506,7 +34504,7 @@
         <v>1754</v>
       </c>
       <c r="U383" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V383" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34524,7 +34522,7 @@
         <v>1754</v>
       </c>
       <c r="U384" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V384" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34542,7 +34540,7 @@
         <v>1754</v>
       </c>
       <c r="U385" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V385" s="36" t="str">
         <f t="shared" si="5"/>
@@ -34560,7 +34558,7 @@
         <v>1754</v>
       </c>
       <c r="U386" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V386" s="36" t="str">
         <f t="shared" ref="V386:V414" si="6">IF(ISBLANK(B386)=FALSE,IF(ISBLANK(B385),"},["&amp;B386&amp;"]={","["&amp;B386&amp;"]={"),IF(AND(ISBLANK(B386),ISBLANK(D386),ISBLANK(C386),OR(ISBLANK(B385)=FALSE,ISBLANK(D385)=FALSE,ISBLANK(C385)=FALSE)),"},},}",IF(ISBLANK(C386),"","{dwID="&amp;C386&amp;","&amp;"nFrame="&amp;D386&amp;","&amp;IF(E386&gt;0,"nCount="&amp;E386&amp;",","")&amp;IF(F386&gt;0,"bAllLeave=true,","")&amp;IF(G386&lt;&gt;"","szName="""&amp;G386&amp;""",","")&amp;IF(H386&lt;&gt;"","tKungFu={"&amp;H386&amp;"},","")&amp;IF(I386&lt;&gt;"","szNote="""&amp;I386&amp;""",","")&amp;IF(J386&lt;&gt;"","col={"&amp;J386&amp;"},","")&amp;"[3]={"&amp;IF(K386&lt;&gt;"","tMark={"&amp;K386&amp;"},","")&amp;IF(L386&lt;&gt;"","szVoice="""&amp;L386&amp;""",","")&amp;IF(M386&gt;0,"bTeamChannel=true,","")&amp;IF(N386&gt;0,"bWhisperChannel=true,","")&amp;IF(O386&gt;0,"bCenterAlarm=true,","")&amp;IF(P386&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q386&lt;&gt;"","szVoice="""&amp;Q386&amp;""",","")&amp;IF(R386&gt;0,"bTeamChannel=true,","")&amp;IF(S386&gt;0,"bWhisperChannel=true,","")&amp;IF(T386&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U386&lt;&gt;"","aFocus={"&amp;U386&amp;"},","")&amp;IF(W386&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W386:ZZ386)&amp;"},","")&amp;"},")))</f>
@@ -34578,7 +34576,7 @@
         <v>1755</v>
       </c>
       <c r="U387" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V387" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34596,7 +34594,7 @@
         <v>1755</v>
       </c>
       <c r="U388" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V388" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34614,7 +34612,7 @@
         <v>1755</v>
       </c>
       <c r="U389" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V389" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34632,7 +34630,7 @@
         <v>1755</v>
       </c>
       <c r="U390" s="36" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="V390" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34650,7 +34648,7 @@
         <v>1756</v>
       </c>
       <c r="U391" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V391" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34668,7 +34666,7 @@
         <v>1756</v>
       </c>
       <c r="U392" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V392" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34686,7 +34684,7 @@
         <v>1756</v>
       </c>
       <c r="U393" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V393" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34704,7 +34702,7 @@
         <v>1756</v>
       </c>
       <c r="U394" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V394" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34722,7 +34720,7 @@
         <v>1756</v>
       </c>
       <c r="U395" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V395" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34740,7 +34738,7 @@
         <v>1756</v>
       </c>
       <c r="U396" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V396" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34758,7 +34756,7 @@
         <v>1756</v>
       </c>
       <c r="U397" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V397" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34776,7 +34774,7 @@
         <v>1756</v>
       </c>
       <c r="U398" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V398" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34794,7 +34792,7 @@
         <v>1756</v>
       </c>
       <c r="U399" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V399" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34812,7 +34810,7 @@
         <v>1756</v>
       </c>
       <c r="U400" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V400" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34830,7 +34828,7 @@
         <v>1756</v>
       </c>
       <c r="U401" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V401" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34848,7 +34846,7 @@
         <v>1756</v>
       </c>
       <c r="U402" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V402" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34866,7 +34864,7 @@
         <v>1756</v>
       </c>
       <c r="U403" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V403" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34884,7 +34882,7 @@
         <v>1756</v>
       </c>
       <c r="U404" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V404" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34902,7 +34900,7 @@
         <v>1756</v>
       </c>
       <c r="U405" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V405" s="36" t="str">
         <f t="shared" si="6"/>
@@ -34920,7 +34918,7 @@
         <v>1756</v>
       </c>
       <c r="U406" s="36" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="V406" s="36" t="str">
         <f t="shared" si="6"/>
@@ -35043,13 +35041,13 @@
         <v>57</v>
       </c>
       <c r="I412" s="36" t="s">
-        <v>2691</v>
+        <v>2688</v>
       </c>
       <c r="P412" s="36">
         <v>1</v>
       </c>
       <c r="U412" s="36" t="s">
-        <v>2692</v>
+        <v>2689</v>
       </c>
       <c r="V412" s="36" t="str">
         <f t="shared" si="6"/>
@@ -35137,40 +35135,40 @@
         <v>1421</v>
       </c>
       <c r="J1" s="36" t="s">
+        <v>2651</v>
+      </c>
+      <c r="K1" s="36" t="s">
+        <v>2652</v>
+      </c>
+      <c r="L1" s="36" t="s">
         <v>2653</v>
       </c>
-      <c r="K1" s="36" t="s">
+      <c r="M1" s="36" t="s">
         <v>2654</v>
       </c>
-      <c r="L1" s="36" t="s">
+      <c r="N1" s="36" t="s">
         <v>2655</v>
       </c>
-      <c r="M1" s="36" t="s">
+      <c r="O1" s="36" t="s">
         <v>2656</v>
       </c>
-      <c r="N1" s="36" t="s">
+      <c r="P1" s="36" t="s">
         <v>2657</v>
       </c>
-      <c r="O1" s="36" t="s">
+      <c r="Q1" s="36" t="s">
         <v>2658</v>
       </c>
-      <c r="P1" s="36" t="s">
+      <c r="R1" s="36" t="s">
         <v>2659</v>
       </c>
-      <c r="Q1" s="36" t="s">
+      <c r="S1" s="36" t="s">
         <v>2660</v>
-      </c>
-      <c r="R1" s="36" t="s">
-        <v>2661</v>
-      </c>
-      <c r="S1" s="36" t="s">
-        <v>2662</v>
       </c>
       <c r="T1" s="36" t="s">
         <v>1526</v>
       </c>
       <c r="U1" s="36" t="s">
-        <v>2663</v>
+        <v>2661</v>
       </c>
       <c r="V1" s="36" t="s">
         <v>1422</v>
@@ -35178,7 +35176,7 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A2" s="36" t="s">
-        <v>2664</v>
+        <v>2662</v>
       </c>
       <c r="B2" s="36">
         <v>-19</v>
@@ -35196,13 +35194,13 @@
         <v>1561</v>
       </c>
       <c r="I3" s="36" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="N3" s="36">
         <v>1</v>
       </c>
       <c r="T3" s="36" t="s">
-        <v>2666</v>
+        <v>2664</v>
       </c>
       <c r="U3" s="36" t="str">
         <f t="shared" si="0"/>
@@ -35217,7 +35215,7 @@
         <v>1562</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="N4" s="36">
         <v>1</v>
@@ -35235,10 +35233,10 @@
         <v>7518</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>2667</v>
+        <v>2665</v>
       </c>
       <c r="I5" s="36" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="M5" s="36">
         <v>1</v>
@@ -35247,7 +35245,7 @@
         <v>1</v>
       </c>
       <c r="T5" s="36" t="s">
-        <v>2668</v>
+        <v>2666</v>
       </c>
       <c r="U5" s="36" t="str">
         <f t="shared" si="0"/>
@@ -35259,10 +35257,10 @@
         <v>5626</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>2669</v>
+        <v>2667</v>
       </c>
       <c r="I6" s="36" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="M6" s="36">
         <v>1</v>
@@ -35271,7 +35269,7 @@
         <v>1</v>
       </c>
       <c r="T6" s="36" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="U6" s="36" t="str">
         <f t="shared" si="0"/>
@@ -35280,7 +35278,7 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A7" s="36" t="s">
-        <v>2687</v>
+        <v>2685</v>
       </c>
       <c r="B7" s="36">
         <v>-20</v>
@@ -35298,13 +35296,13 @@
         <v>1978</v>
       </c>
       <c r="I8" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="N8" s="36">
         <v>1</v>
       </c>
       <c r="T8" s="36" t="s">
-        <v>2671</v>
+        <v>2669</v>
       </c>
       <c r="U8" s="36" t="str">
         <f t="shared" si="0"/>
@@ -35319,13 +35317,13 @@
         <v>1979</v>
       </c>
       <c r="I9" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="N9" s="36">
         <v>1</v>
       </c>
       <c r="T9" s="36" t="s">
-        <v>2671</v>
+        <v>2669</v>
       </c>
       <c r="U9" s="36" t="str">
         <f t="shared" si="0"/>
@@ -35340,7 +35338,7 @@
         <v>1550</v>
       </c>
       <c r="I10" s="36" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="M10" s="36">
         <v>1</v>
@@ -35364,7 +35362,7 @@
         <v>1552</v>
       </c>
       <c r="I11" s="36" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="M11" s="36">
         <v>1</v>
@@ -35400,7 +35398,7 @@
         <v>1550</v>
       </c>
       <c r="I13" s="36" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="M13" s="36">
         <v>1</v>
@@ -35424,7 +35422,7 @@
         <v>1552</v>
       </c>
       <c r="I14" s="36" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="M14" s="36">
         <v>1</v>
@@ -35460,7 +35458,7 @@
         <v>1550</v>
       </c>
       <c r="I16" s="36" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="M16" s="36">
         <v>1</v>
@@ -35484,7 +35482,7 @@
         <v>1552</v>
       </c>
       <c r="I17" s="36" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="M17" s="36">
         <v>1</v>
@@ -35517,10 +35515,10 @@
         <v>3444</v>
       </c>
       <c r="H19" s="36" t="s">
-        <v>2672</v>
+        <v>2670</v>
       </c>
       <c r="I19" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="M19" s="36">
         <v>1</v>
@@ -35541,10 +35539,10 @@
         <v>3443</v>
       </c>
       <c r="H20" s="36" t="s">
-        <v>2673</v>
+        <v>2671</v>
       </c>
       <c r="I20" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="M20" s="36">
         <v>1</v>
@@ -35565,10 +35563,10 @@
         <v>843</v>
       </c>
       <c r="H21" s="36" t="s">
-        <v>2674</v>
+        <v>2672</v>
       </c>
       <c r="I21" s="36" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="N21" s="36">
         <v>1</v>
@@ -35598,10 +35596,10 @@
         <v>843</v>
       </c>
       <c r="H23" s="36" t="s">
-        <v>2674</v>
+        <v>2672</v>
       </c>
       <c r="I23" s="36" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="N23" s="36">
         <v>1</v>
@@ -35619,10 +35617,10 @@
         <v>7662</v>
       </c>
       <c r="H24" s="36" t="s">
-        <v>2675</v>
+        <v>2673</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="M24" s="36">
         <v>1</v>
@@ -35643,10 +35641,10 @@
         <v>7663</v>
       </c>
       <c r="H25" s="36" t="s">
-        <v>2676</v>
+        <v>2674</v>
       </c>
       <c r="I25" s="36" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="M25" s="36">
         <v>1</v>
@@ -35667,10 +35665,10 @@
         <v>3444</v>
       </c>
       <c r="H26" s="36" t="s">
-        <v>2672</v>
+        <v>2670</v>
       </c>
       <c r="I26" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="M26" s="36">
         <v>1</v>
@@ -35691,10 +35689,10 @@
         <v>3443</v>
       </c>
       <c r="H27" s="36" t="s">
-        <v>2673</v>
+        <v>2671</v>
       </c>
       <c r="I27" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="M27" s="36">
         <v>1</v>
@@ -35730,10 +35728,10 @@
         <v>3445</v>
       </c>
       <c r="H29" s="36" t="s">
-        <v>2677</v>
+        <v>2675</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="M29" s="36">
         <v>1</v>
@@ -35754,10 +35752,10 @@
         <v>3442</v>
       </c>
       <c r="H30" s="36" t="s">
-        <v>2678</v>
+        <v>2676</v>
       </c>
       <c r="I30" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="M30" s="36">
         <v>1</v>
@@ -35778,10 +35776,10 @@
         <v>6474</v>
       </c>
       <c r="H31" s="36" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
       <c r="I31" s="36" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="T31" s="36" t="s">
         <v>1560</v>
@@ -35808,10 +35806,10 @@
         <v>1519</v>
       </c>
       <c r="H33" s="36" t="s">
-        <v>2680</v>
+        <v>2678</v>
       </c>
       <c r="I33" s="36" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="N33" s="36">
         <v>1</v>
@@ -35829,10 +35827,10 @@
         <v>7662</v>
       </c>
       <c r="H34" s="36" t="s">
-        <v>2675</v>
+        <v>2673</v>
       </c>
       <c r="I34" s="36" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="M34" s="36">
         <v>1</v>
@@ -35853,10 +35851,10 @@
         <v>7663</v>
       </c>
       <c r="H35" s="36" t="s">
-        <v>2676</v>
+        <v>2674</v>
       </c>
       <c r="I35" s="36" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="M35" s="36">
         <v>1</v>
@@ -35877,10 +35875,10 @@
         <v>3445</v>
       </c>
       <c r="H36" s="36" t="s">
-        <v>2677</v>
+        <v>2675</v>
       </c>
       <c r="I36" s="51" t="s">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="M36" s="36">
         <v>1</v>
@@ -35901,10 +35899,10 @@
         <v>3442</v>
       </c>
       <c r="H37" s="36" t="s">
-        <v>2678</v>
+        <v>2676</v>
       </c>
       <c r="I37" s="50" t="s">
-        <v>2642</v>
+        <v>2640</v>
       </c>
       <c r="M37" s="36">
         <v>1</v>
@@ -36095,10 +36093,10 @@
         <v>2188</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>2712</v>
+        <v>2709</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>2717</v>
+        <v>2714</v>
       </c>
       <c r="M5" s="36" t="s">
         <v>1432</v>
@@ -36114,22 +36112,22 @@
         <v>{szContent="^本场攻防“(.-)”“(.-)·(.-)”已结束，(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分；(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分。请再接再厉！",szTarget="%",szNote="{$2}·{$3}·[{$4}·{$6}]:[{$7}·{$9}]",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2401,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=14,nIcon=2397,nFrame=-1,nTime=-1,szName="破阵点将·一",nRefresh=2,key="破阵点将·一",},{nClass=14,nIcon=2398,nFrame=-1,nTime=-1,szName="破阵点将·二",nRefresh=2,key="破阵点将·二",},{nClass=14,nIcon=2396,nFrame=-1,nTime=-2,szName="{$2}·{$3}",key="{$2}·{$3}",},{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}·{$6}分·{$7}·{$9}分;840,阶段·物资车2·出发剩余;850,阶段·物资车2·正在出发;900,阶段·首领出战·助战剩余;905,阶段·首领出战·助战结束;2700,阶段·破阵点将2·结算剩余;2702,阶段·破阵点将2·正在结算;2710,阶段·物资车3·正在出发;4500,阶段·本场攻防·结束剩余;4505,阶段·本场攻防·已经结束",szName="{$4}·{$6}分·{$7}·{$9}分",nRefresh=1,key="破阵点将·一",},{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}·{$6}分·{$7}·{$9}分;1800,阶段·本场攻防·结束剩余;1805,阶段·本场攻防·已经结束",szName="{$4}·{$6}分·{$7}·{$9}分",nRefresh=1,key="破阵点将·二",},},},</v>
       </c>
       <c r="W5" s="36" t="s">
+        <v>2710</v>
+      </c>
+      <c r="X5" s="36" t="s">
         <v>2713</v>
       </c>
-      <c r="X5" s="36" t="s">
-        <v>2716</v>
-      </c>
       <c r="Y5" s="36" t="s">
-        <v>2714</v>
+        <v>2711</v>
       </c>
       <c r="Z5" s="36" t="s">
-        <v>2715</v>
+        <v>2712</v>
       </c>
       <c r="AA5" s="36" t="s">
-        <v>2724</v>
+        <v>2719</v>
       </c>
       <c r="AB5" s="36" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="6" spans="1:65" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -36137,10 +36135,10 @@
         <v>1431</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>2581</v>
+        <v>2579</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>2582</v>
+        <v>2580</v>
       </c>
       <c r="M6" s="36" t="s">
         <v>1432</v>
@@ -36161,10 +36159,10 @@
         <v>1431</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>2584</v>
+        <v>2582</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>2585</v>
+        <v>2583</v>
       </c>
       <c r="M7" s="36" t="s">
         <v>1432</v>
@@ -36198,7 +36196,7 @@
         <v>{szContent="([浩气恶人]-)前线战况焦灼，(.-)，有劳你速速前往支援！",szTarget="%",szNote="{$1}·{$2}·即将到达",col={255,255,100,},bReg=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="谢渊·月弄痕·减伤",nTime=-2,key="谢渊·月弄痕·减伤",},{nClass=14,nIcon=13,szName="谢渊·游驹·减伤",nTime=-2,key="谢渊·游驹·减伤",},{nClass=14,nIcon=13,szName="谢渊·穆玄英·减伤",nTime=-2,key="谢渊·穆玄英·减伤",},{nClass=14,nIcon=13,szName="谢渊·张桎辕·减伤",nTime=-2,key="谢渊·张桎辕·减伤",},{nClass=14,nIcon=13,szName="谢渊·司空仲平·减伤",nTime=-2,key="谢渊·司空仲平·减伤",},{nClass=14,nIcon=13,szName="王遗风·万兽王·减伤",nTime=-2,key="王遗风·万兽王·减伤",},{nClass=14,nIcon=13,szName="王遗风·莫雨·减伤",nTime=-2,key="王遗风·莫雨·减伤",},{nClass=14,nIcon=13,szName="王遗风·米丽古丽·减伤",nTime=-2,key="王遗风·米丽古丽·减伤",},{nClass=14,nIcon=13,szName="王遗风·陶寒亭·减伤",nTime=-2,key="王遗风·陶寒亭·减伤",},{nClass=14,nIcon=13,szName="王遗风·肖药儿·减伤",nTime=-2,key="王遗风·肖药儿·减伤",},},},</v>
       </c>
       <c r="W8" s="52" t="s">
-        <v>2650</v>
+        <v>2648</v>
       </c>
     </row>
     <row r="9" spans="1:65" x14ac:dyDescent="0.15">
@@ -36226,13 +36224,13 @@
         <v>{szContent="(.-)力不能敌，暂时败退。(.-)进攻顺利，此战有功，请即刻回营，准备下一步战略。",szTarget="%",szNote="{$1}·败退|{$2}·回营",col={255,255,100,},bReg=true,[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=7,szName="浩气·{$2}·助战",nTime=0,key="浩气·{$2}·助战",},{nClass=14,nIcon=13,nFrame=3,szName="恶人·{$2}·助战",nTime=0,key="恶人·{$2}·助战",},{nClass=14,nIcon=16834,nFrame=8,szName="{$2}·助战胜利·已回营",nTime=10,key="{$2}·助战",},},},</v>
       </c>
       <c r="W9" t="s">
+        <v>2549</v>
+      </c>
+      <c r="X9" t="s">
+        <v>2550</v>
+      </c>
+      <c r="Y9" s="36" t="s">
         <v>2551</v>
-      </c>
-      <c r="X9" t="s">
-        <v>2552</v>
-      </c>
-      <c r="Y9" s="36" t="s">
-        <v>2553</v>
       </c>
       <c r="Z9" s="36"/>
       <c r="AA9" s="36"/>
@@ -36262,13 +36260,13 @@
         <v>{szContent="(.-)误入埋伏，防守不利，暂时败退。请(.-)暂且撤回驻守之地，务必小心防守。",szTarget="%",szNote="{$1}·败退|{$2}·回防",col={255,255,100,},bReg=true,[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=7,szName="浩气·{$2}·助战",nTime=0,key="浩气·{$2}·助战",},{nClass=14,nIcon=13,nFrame=3,szName="恶人·{$2}·助战",nTime=0,key="恶人·{$2}·助战",},{nClass=14,nIcon=16834,nFrame=8,szName="{$2}·助战退场·易伤30%",nTime=10,key="{$2}·助战",},},},</v>
       </c>
       <c r="W10" t="s">
-        <v>2551</v>
+        <v>2549</v>
       </c>
       <c r="X10" t="s">
-        <v>2552</v>
+        <v>2550</v>
       </c>
       <c r="Y10" s="36" t="s">
-        <v>2694</v>
+        <v>2691</v>
       </c>
       <c r="Z10" s="36"/>
       <c r="AA10" s="36"/>
@@ -36298,13 +36296,13 @@
         <v>{szContent="(.-)出手协助众人酣战一场，其力有所不支，暂且从前线撤回。",szTarget="%",szNote="{$1}·助战失利·回营",col={255,255,100,},bReg=true,[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=7,szName="浩气·{$1}·助战",nTime=0,key="浩气·{$1}·助战",},{nClass=14,nIcon=13,nFrame=3,szName="恶人·{$1}·助战",nTime=0,key="恶人·{$1}·助战",},{nClass=14,nIcon=16834,nFrame=8,szName="{$1}·助战失利·易伤30%",nTime=10,key="{$1}·助战",},},},</v>
       </c>
       <c r="W11" t="s">
-        <v>2554</v>
+        <v>2552</v>
       </c>
       <c r="X11" t="s">
-        <v>2555</v>
+        <v>2553</v>
       </c>
       <c r="Y11" s="36" t="s">
-        <v>2695</v>
+        <v>2692</v>
       </c>
       <c r="Z11" s="36"/>
       <c r="AA11" s="36"/>
@@ -36330,13 +36328,13 @@
         <v>{szContent="(.-)出手协助众人酣战一场，回到驻守之地。",szTarget="%",szNote="{$1}·助战结束·回营",col={255,255,100,},bReg=true,[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=7,szName="浩气·{$1}·助战",nTime=0,key="浩气·{$1}·助战",},{nClass=14,nIcon=13,nFrame=3,szName="恶人·{$1}·助战",nTime=0,key="恶人·{$1}·助战",},{nClass=14,nIcon=16834,nFrame=8,szName="{$1}·助战结束·易伤30%",nTime=10,key="{$1}·助战",},},},</v>
       </c>
       <c r="W12" s="36" t="s">
-        <v>2554</v>
+        <v>2552</v>
       </c>
       <c r="X12" s="36" t="s">
-        <v>2555</v>
+        <v>2553</v>
       </c>
       <c r="Y12" s="36" t="s">
-        <v>2696</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="13" spans="1:65" x14ac:dyDescent="0.15">
@@ -36367,19 +36365,19 @@
         <v>{szContent="(.-)已经尽力，请暂且退回疗伤。",szTarget="%",szNote="{$1}·败退",col={255,255,100,},bReg=true,[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=7,szName="谢渊·{$1}·减伤",nTime=-1,nRefresh=2,key="谢渊·{$1}·减伤",},{nClass=14,nIcon=13,nFrame=3,szName="王遗风·{$1}·减伤",nTime=-1,nRefresh=2,key="王遗风·{$1}·减伤",},{nClass=14,nIcon=13,nFrame=-1,szName="{$sender}·{$1}·减伤",nTime=-2,key="{$sender}·{$1}·减伤",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气·{$1}·败退·易伤30%",nTime=10,nRefresh=5,key="谢渊·{$1}·减伤",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人·{$1}·败退·易伤30%",nTime=10,nRefresh=5,key="王遗风·{$1}·减伤",},},},</v>
       </c>
       <c r="W13" t="s">
-        <v>2410</v>
+        <v>2408</v>
       </c>
       <c r="X13" t="s">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="Y13" t="s">
         <v>1508</v>
       </c>
       <c r="Z13" t="s">
-        <v>2697</v>
+        <v>2694</v>
       </c>
       <c r="AA13" t="s">
-        <v>2698</v>
+        <v>2695</v>
       </c>
       <c r="AB13" s="36"/>
       <c r="AZ13" s="36"/>
@@ -36402,10 +36400,10 @@
         <v>1431</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
       <c r="M14" s="36" t="s">
         <v>1432</v>
@@ -36415,13 +36413,13 @@
         <v>{szContent="兄弟们，辛苦了，在此谢过。",szTarget="%",szNote="{$sender}·撤退",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=13,szName="谢渊·{$sender}·减伤",nTime=-1,key="谢渊·{$sender}·减伤",},{nClass=14,nIcon=13,szName="王遗风·{$sender}·减伤",nTime=-1,key="王遗风·{$sender}·减伤",},{nClass=14,nIcon=13,nTime=-1,szName="屹立不倒",nRefresh=14400,key="屹立不倒",},},},</v>
       </c>
       <c r="W14" s="36" t="s">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="X14" s="36" t="s">
-        <v>2517</v>
+        <v>2515</v>
       </c>
       <c r="Y14" s="36" t="s">
-        <v>2628</v>
+        <v>2626</v>
       </c>
     </row>
     <row r="15" spans="1:65" x14ac:dyDescent="0.15">
@@ -36449,10 +36447,10 @@
         <v>{szContent="罢了，青山不改，绿水长流，后会有期！",szTarget="%",szNote="{$sender}·败退",col={255,255,100,},bSearch=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,szName="谢渊·{$sender}·减伤",nTime=-2,key="谢渊·{$sender}·减伤",},{nClass=14,nIcon=13,szName="王遗风·{$sender}·减伤",nTime=-2,key="王遗风·{$sender}·减伤",},},},</v>
       </c>
       <c r="W15" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="X15" t="s">
-        <v>2633</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="16" spans="1:65" s="39" customFormat="1" x14ac:dyDescent="0.15">
@@ -36849,7 +36847,7 @@
         <v>1609</v>
       </c>
       <c r="L22" s="39" t="s">
-        <v>2608</v>
+        <v>2606</v>
       </c>
       <c r="M22" s="39" t="s">
         <v>1454</v>
@@ -37209,7 +37207,7 @@
         <v>1609</v>
       </c>
       <c r="J28" s="39" t="s">
-        <v>2608</v>
+        <v>2606</v>
       </c>
       <c r="K28" s="39" t="s">
         <v>1607</v>
@@ -37376,10 +37374,10 @@
         <v>1444</v>
       </c>
       <c r="D31" s="39" t="s">
-        <v>2611</v>
+        <v>2609</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>2612</v>
+        <v>2610</v>
       </c>
       <c r="F31" s="36" t="s">
         <v>1444</v>
@@ -37397,7 +37395,7 @@
         <v>1607</v>
       </c>
       <c r="L31" s="36" t="s">
-        <v>2613</v>
+        <v>2611</v>
       </c>
       <c r="M31" s="36" t="s">
         <v>1486</v>
@@ -37500,10 +37498,10 @@
         <v>1444</v>
       </c>
       <c r="D33" s="39" t="s">
-        <v>2616</v>
+        <v>2614</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>2615</v>
+        <v>2613</v>
       </c>
       <c r="F33" s="36" t="s">
         <v>1444</v>
@@ -37521,7 +37519,7 @@
         <v>1607</v>
       </c>
       <c r="L33" s="36" t="s">
-        <v>2614</v>
+        <v>2612</v>
       </c>
       <c r="M33" s="36" t="s">
         <v>1486</v>
@@ -37624,10 +37622,10 @@
         <v>1446</v>
       </c>
       <c r="D35" s="39" t="s">
-        <v>2609</v>
+        <v>2607</v>
       </c>
       <c r="E35" s="36" t="s">
-        <v>2610</v>
+        <v>2608</v>
       </c>
       <c r="F35" s="36" t="s">
         <v>1446</v>
@@ -37701,7 +37699,7 @@
         <v>1607</v>
       </c>
       <c r="J36" s="36" t="s">
-        <v>2613</v>
+        <v>2611</v>
       </c>
       <c r="K36" s="36" t="s">
         <v>1609</v>
@@ -37825,7 +37823,7 @@
         <v>1607</v>
       </c>
       <c r="J38" s="36" t="s">
-        <v>2614</v>
+        <v>2612</v>
       </c>
       <c r="K38" s="36" t="s">
         <v>1609</v>
@@ -37950,7 +37948,7 @@
         <v>{szContent="浩气盟物资车已被拦截，车内装大量物资，望侠士们前来拾取，切莫错过。",szTarget="%",szNote="浩气·物资车·被截",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=4562,nFrame=3,szName="恶人·截车奖励",nTime=10,nRefresh=1,key="浩气·物资车·护送",},},},</v>
       </c>
       <c r="W40" s="36" t="s">
-        <v>2556</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="41" spans="3:28" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -37974,7 +37972,7 @@
         <v>{szContent="恶人谷物资车已被拦截，车内装大量物资，望侠士们前来拾取，切莫错过。",szTarget="%",szNote="恶人·物资车·被截",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=4561,nFrame=7,szName="浩气·截车奖励",nTime=10,nRefresh=1,key="恶人·物资车·护送",},},},</v>
       </c>
       <c r="W41" s="36" t="s">
-        <v>2557</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="42" spans="3:28" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -37982,7 +37980,7 @@
         <v>2188</v>
       </c>
       <c r="D42" s="43" t="s">
-        <v>2580</v>
+        <v>2578</v>
       </c>
       <c r="E42" s="36" t="s">
         <v>2134</v>
@@ -37995,7 +37993,7 @@
         <v>{szContent="奇袭场战阶达到2000后，战阶换算贡献比例降低为2:1",szTarget="%",szNote="奇袭·贡献值·限速50%",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=7200,key="首领拾取间隔",},},},</v>
       </c>
       <c r="W42" s="36" t="s">
-        <v>2518</v>
+        <v>2516</v>
       </c>
       <c r="AB42" s="39"/>
     </row>
@@ -38004,7 +38002,7 @@
         <v>2188</v>
       </c>
       <c r="D43" s="43" t="s">
-        <v>2583</v>
+        <v>2581</v>
       </c>
       <c r="E43" s="36" t="s">
         <v>2133</v>
@@ -38017,7 +38015,7 @@
         <v>{szContent="奇袭场战阶达到4000后，战阶换算贡献比例降低为10:1",szTarget="%",szNote="奇袭·贡献值·限速90%",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=7200,key="首领拾取间隔",},},},</v>
       </c>
       <c r="W43" s="36" t="s">
-        <v>2518</v>
+        <v>2516</v>
       </c>
       <c r="AB43" s="39"/>
     </row>
@@ -38026,7 +38024,7 @@
         <v>2188</v>
       </c>
       <c r="D44" s="43" t="s">
-        <v>2531</v>
+        <v>2529</v>
       </c>
       <c r="E44" s="36" t="s">
         <v>2035</v>
@@ -38039,7 +38037,7 @@
         <v>{szContent="军情速递！浩气盟物资车已从复活点出发，物资车内装有大量物资，望浩气侠士们前来护送，以防不法之徒前来抢夺。",szTarget="%",szNote="浩气·物资车·出发",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=3101,nFrame=7,szName="浩气盟·物资车·正在出发",nTime=10,nRefresh=1,key="浩气·物资车·护送",},},},</v>
       </c>
       <c r="W44" s="36" t="s">
-        <v>2533</v>
+        <v>2531</v>
       </c>
       <c r="AB44" s="39"/>
     </row>
@@ -38048,7 +38046,7 @@
         <v>2188</v>
       </c>
       <c r="D45" s="43" t="s">
-        <v>2532</v>
+        <v>2530</v>
       </c>
       <c r="E45" s="36" t="s">
         <v>2034</v>
@@ -38061,7 +38059,7 @@
         <v>{szContent="军情速递！恶人谷物资车已从复活点出发，物资车内装有大量物资，望恶人侠士们前来护送，以防不法之徒前来抢夺。",szTarget="%",szNote="恶人·物资车·出发",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=3103,nFrame=3,szName="恶人谷·物资车·正在出发",nTime=10,nRefresh=1,key="恶人·物资车·护送",},},},</v>
       </c>
       <c r="W45" s="36" t="s">
-        <v>2534</v>
+        <v>2532</v>
       </c>
       <c r="AB45" s="39"/>
     </row>
@@ -38090,7 +38088,7 @@
         <v>{szContent="你获得了100点威名、100点战阶。",szNote="堆堆·助战首领",[14]={},tCountdown={{nClass=14,nIcon=13564,nFrame=1,szName="拾取间隔",nTime="300,助战堆·拾取物资·间隔剩余;310,助战堆·可以拾取物资了",nRefresh=1,key="首领拾取间隔",},},},</v>
       </c>
       <c r="W47" s="36" t="s">
-        <v>2646</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="48" spans="3:28" x14ac:dyDescent="0.15">
@@ -39260,10 +39258,10 @@
         <v>2188</v>
       </c>
       <c r="D68" s="43" t="s">
-        <v>2523</v>
+        <v>2521</v>
       </c>
       <c r="E68" s="36" t="s">
-        <v>2524</v>
+        <v>2522</v>
       </c>
       <c r="M68" s="36" t="s">
         <v>1565</v>
@@ -39273,10 +39271,10 @@
         <v>{szContent="军情速递！浩气盟物资官传来消息，现有一批新物资运至各复活点，望浩气侠士们前来领取，以便增强战斗实力。",szTarget="%",szNote="复活点·物资箱·已刷新",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,szName="进攻方·速战速决·未达成",nTime=10,nRefresh=99999,key="速战速决",},{nClass=14,nIcon=3557,nFrame=6,szName="复活点·物资箱·已经刷新",nTime=10.1,nRefresh=5,key="复活点·物资箱",},},},</v>
       </c>
       <c r="W68" s="36" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
       <c r="X68" s="36" t="s">
-        <v>2645</v>
+        <v>2643</v>
       </c>
       <c r="AA68" s="39"/>
     </row>
@@ -39285,10 +39283,10 @@
         <v>2188</v>
       </c>
       <c r="D69" s="43" t="s">
-        <v>2521</v>
+        <v>2519</v>
       </c>
       <c r="E69" s="36" t="s">
-        <v>2519</v>
+        <v>2517</v>
       </c>
       <c r="M69" s="36" t="s">
         <v>1438</v>
@@ -39298,7 +39296,7 @@
         <v>{szContent="军情速递！恶人谷物资车已运达，车内装有大量物资，望侠士们前来拾取，切莫错过。",szTarget="%",szNote="恶人谷·物资车·已运达",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=10450,nFrame=4,szName="恶人谷·营地物资·刷新",nTime="10,恶人谷·营地物资·刷新;300,恶人谷·营地物资·拾取剩余;305,恶人谷·营地物资·已消失",nRefresh=0,key="恶人·物资车·运达",},},},</v>
       </c>
       <c r="W69" s="36" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
       <c r="AA69" s="39"/>
     </row>
@@ -39307,10 +39305,10 @@
         <v>2188</v>
       </c>
       <c r="D70" s="43" t="s">
-        <v>2522</v>
+        <v>2520</v>
       </c>
       <c r="E70" s="36" t="s">
-        <v>2520</v>
+        <v>2518</v>
       </c>
       <c r="M70" s="36" t="s">
         <v>1565</v>
@@ -39320,7 +39318,7 @@
         <v>{szContent="军情速递！浩气盟物资车已运达，车内装有大量物资，望侠士们前来拾取，切莫错过。",szTarget="%",szNote="浩气盟·物资车·已运达",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=10449,nFrame=4,szName="浩气盟·内城物资·刷新",nTime="10,浩气盟·内城物资·刷新;300,浩气盟·内城物资·拾取剩余;305,浩气盟·内城物资·已消失",nRefresh=0,key="浩气·物资车·运达",},},},</v>
       </c>
       <c r="W70" s="36" t="s">
-        <v>2527</v>
+        <v>2525</v>
       </c>
       <c r="AA70" s="39"/>
     </row>
@@ -40459,10 +40457,10 @@
         <v>2188</v>
       </c>
       <c r="D89" s="43" t="s">
-        <v>2528</v>
+        <v>2526</v>
       </c>
       <c r="E89" s="36" t="s">
-        <v>2524</v>
+        <v>2522</v>
       </c>
       <c r="M89" s="36" t="s">
         <v>1565</v>
@@ -40472,10 +40470,10 @@
         <v>{szContent="军情速递！恶人谷物资官传来消息，现有一批新物资运至各复活点，望恶人侠士们前来领取，以便增强战斗实力。",szTarget="%",szNote="复活点·物资箱·已刷新",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,szName="进攻方·速战速决·未达成",nTime=10,nRefresh=99999,key="速战速决",},{nClass=14,nIcon=3557,nFrame=6,szName="复活点·物资箱·已经刷新",nTime=10.1,nRefresh=5,key="复活点·物资箱",},},},</v>
       </c>
       <c r="W89" s="36" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
       <c r="X89" s="36" t="s">
-        <v>2645</v>
+        <v>2643</v>
       </c>
       <c r="AA89" s="39"/>
     </row>
@@ -40484,10 +40482,10 @@
         <v>2188</v>
       </c>
       <c r="D90" s="43" t="s">
-        <v>2521</v>
+        <v>2519</v>
       </c>
       <c r="E90" s="36" t="s">
-        <v>2519</v>
+        <v>2517</v>
       </c>
       <c r="M90" s="36" t="s">
         <v>1438</v>
@@ -40497,7 +40495,7 @@
         <v>{szContent="军情速递！恶人谷物资车已运达，车内装有大量物资，望侠士们前来拾取，切莫错过。",szTarget="%",szNote="恶人谷·物资车·已运达",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=10450,nFrame=4,szName="恶人谷·内城物资·刷新",nTime="10,恶人谷·内城物资·刷新;300,恶人谷·内城物资·拾取剩余;305,恶人谷·内城物资·已消失",nRefresh=0,key="恶人·物资车·运达",},},},</v>
       </c>
       <c r="W90" s="36" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
       <c r="AA90" s="39"/>
     </row>
@@ -40506,10 +40504,10 @@
         <v>2188</v>
       </c>
       <c r="D91" s="43" t="s">
-        <v>2522</v>
+        <v>2520</v>
       </c>
       <c r="E91" s="36" t="s">
-        <v>2520</v>
+        <v>2518</v>
       </c>
       <c r="M91" s="36" t="s">
         <v>1565</v>
@@ -40519,13 +40517,13 @@
         <v>{szContent="军情速递！浩气盟物资车已运达，车内装有大量物资，望侠士们前来拾取，切莫错过。",szTarget="%",szNote="浩气盟·物资车·已运达",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=10449,nFrame=4,szName="浩气盟·营地物资·刷新",nTime="10,浩气盟·营地物资·刷新;300,浩气盟·营地物资·拾取剩余;305,浩气盟·营地物资·已消失",nRefresh=0,key="浩气·物资车·运达",},},},</v>
       </c>
       <c r="W91" s="36" t="s">
-        <v>2530</v>
+        <v>2528</v>
       </c>
       <c r="AA91" s="39"/>
     </row>
     <row r="92" spans="1:38" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A92" s="36" t="s">
-        <v>2693</v>
+        <v>2690</v>
       </c>
       <c r="B92" s="36">
         <v>-21</v>
@@ -40652,7 +40650,7 @@
     </row>
     <row r="101" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A101" s="36" t="s">
-        <v>2687</v>
+        <v>2685</v>
       </c>
       <c r="B101" s="36">
         <v>-20</v>
@@ -40664,13 +40662,13 @@
     </row>
     <row r="102" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="D102" s="36" t="s">
-        <v>2592</v>
+        <v>2590</v>
       </c>
       <c r="E102" s="36" t="s">
-        <v>2593</v>
+        <v>2591</v>
       </c>
       <c r="M102" s="36" t="s">
-        <v>2504</v>
+        <v>2502</v>
       </c>
       <c r="S102" s="36">
         <v>1</v>
@@ -40680,18 +40678,18 @@
         <v>{szContent="因侠士近来行为异常，逐鹿中原期间，禁止参与，你即将被传送到百溪！",szNote="据点攻防·禁止参与",col={255,50,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,bHold=true,nTime=30,szName="据点攻防·禁止参与本场",key="挂机检测",},},},</v>
       </c>
       <c r="W102" s="36" t="s">
-        <v>2594</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="103" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="D103" s="36" t="s">
+        <v>2500</v>
+      </c>
+      <c r="E103" s="36" t="s">
+        <v>2501</v>
+      </c>
+      <c r="M103" s="36" t="s">
         <v>2502</v>
-      </c>
-      <c r="E103" s="36" t="s">
-        <v>2503</v>
-      </c>
-      <c r="M103" s="36" t="s">
-        <v>2504</v>
       </c>
       <c r="P103" s="36" t="s">
         <v>1089</v>
@@ -40713,7 +40711,7 @@
         <v>{szContent="系统检测您有挂机行为，如果长期维持该状态将被传送出图！",szNote="挂机检测·快活跃起来",col={255,50,255,},[14]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},},},</v>
       </c>
       <c r="W103" s="36" t="s">
-        <v>2505</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="104" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -40728,15 +40726,15 @@
         <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="据点大旗·旗手提示",},},},</v>
       </c>
       <c r="W104" s="36" t="s">
-        <v>2728</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="105" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="D105" s="36" t="s">
-        <v>2709</v>
+        <v>2706</v>
       </c>
       <c r="E105" s="36" t="s">
-        <v>2711</v>
+        <v>2708</v>
       </c>
       <c r="M105" s="36" t="s">
         <v>1432</v>
@@ -40749,7 +40747,7 @@
       </c>
       <c r="V105" s="36" t="str">
         <f t="shared" si="23"/>
-        <v>{szContent="身负据点大旗，当心被夺！",szNote="[{$me}]·扛起大旗",col={255,255,100,},[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=8,szName="【{$me}】·拾取大旗",nTime=30,key="据点大旗·旗手提示",},},},</v>
+        <v>{szContent="身负据点大旗，当心被夺！",szNote="[{$me}]·扛起大旗",col={255,255,100,},[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=8,szName="【{$me}】·拾取大旗",nTime=30,key="拾取大旗·{$me}",},},},</v>
       </c>
       <c r="W105" s="36" t="s">
         <v>2729</v>
@@ -40760,10 +40758,10 @@
         <v>1431</v>
       </c>
       <c r="D106" s="36" t="s">
-        <v>2598</v>
+        <v>2596</v>
       </c>
       <c r="E106" s="36" t="s">
-        <v>2599</v>
+        <v>2597</v>
       </c>
       <c r="M106" s="36" t="s">
         <v>1432</v>
@@ -40779,19 +40777,19 @@
         <v>{szContent="^%[逐鹿中原%]%[(.-)%]：正在(.-)城门！",szTarget="%",szNote="[{$1}]·{$2}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,nFrame=5,nTime=-2,szName="打开·城门",nRefresh=10,key="打开·城门",},{nClass=14,nIcon=1465,nFrame=5,nTime=-2,szName="关闭·城门",nRefresh=10,key="关闭·城门",},{nClass=14,nIcon=13,nFrame=5,nTime=-2,szName="{$2}·城门",key="{$2}·城门",},{nClass=14,nIcon=2310,nFrame=1,nTime=10,szName="城门·打开·[{$1}]",nRefresh=10,key="打开·城门",},{nClass=14,nIcon=4839,nFrame=1,nTime=10,szName="城门·关闭·[{$1}]",nRefresh=10,key="关闭·城门",},},},</v>
       </c>
       <c r="W106" s="36" t="s">
+        <v>2598</v>
+      </c>
+      <c r="X106" s="36" t="s">
+        <v>2599</v>
+      </c>
+      <c r="Y106" s="36" t="s">
         <v>2600</v>
       </c>
-      <c r="X106" s="36" t="s">
+      <c r="Z106" s="36" t="s">
         <v>2601</v>
       </c>
-      <c r="Y106" s="36" t="s">
+      <c r="AA106" s="36" t="s">
         <v>2602</v>
-      </c>
-      <c r="Z106" s="36" t="s">
-        <v>2603</v>
-      </c>
-      <c r="AA106" s="36" t="s">
-        <v>2604</v>
       </c>
     </row>
     <row r="107" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -40799,10 +40797,10 @@
         <v>1431</v>
       </c>
       <c r="D107" s="36" t="s">
-        <v>2506</v>
+        <v>2504</v>
       </c>
       <c r="E107" s="36" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="M107" s="36" t="s">
         <v>1432</v>
@@ -40818,7 +40816,7 @@
         <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W107" s="36" t="s">
-        <v>2508</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="108" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -40883,13 +40881,13 @@
         <v>1431</v>
       </c>
       <c r="D110" s="36" t="s">
-        <v>2589</v>
+        <v>2587</v>
       </c>
       <c r="E110" s="36" t="s">
-        <v>2590</v>
+        <v>2588</v>
       </c>
       <c r="M110" s="36" t="s">
-        <v>2504</v>
+        <v>2502</v>
       </c>
       <c r="S110" s="36">
         <v>1</v>
@@ -40902,7 +40900,7 @@
         <v>{szContent="您因消极怠战,扰乱阵营秩序，被阵营督查官请离当前地图，但同时给予250点贡献积分！",szTarget="%",szNote="阵营督查官·请离据点攻防",col={255,50,255,},[14]={bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,bHold=true,nTime=30,szName="阵营督查·请离据点攻防",key="挂机检测",},},},</v>
       </c>
       <c r="W110" s="36" t="s">
-        <v>2591</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="111" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -40923,10 +40921,10 @@
         <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W111" s="36" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="X111" s="36" t="s">
-        <v>2648</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="112" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -40947,10 +40945,10 @@
         <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W112" s="36" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="X112" s="36" t="s">
-        <v>2649</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="113" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -40958,10 +40956,10 @@
         <v>2188</v>
       </c>
       <c r="D113" s="36" t="s">
-        <v>2492</v>
+        <v>2490</v>
       </c>
       <c r="E113" s="36" t="s">
-        <v>2493</v>
+        <v>2491</v>
       </c>
       <c r="M113" s="36" t="s">
         <v>1748</v>
@@ -40974,19 +40972,19 @@
         <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},},},</v>
       </c>
       <c r="W113" s="36" t="s">
+        <v>2493</v>
+      </c>
+      <c r="X113" s="36" t="s">
+        <v>2494</v>
+      </c>
+      <c r="Y113" s="36" t="s">
         <v>2495</v>
       </c>
-      <c r="X113" s="36" t="s">
+      <c r="Z113" s="36" t="s">
+        <v>2497</v>
+      </c>
+      <c r="AA113" s="36" t="s">
         <v>2496</v>
-      </c>
-      <c r="Y113" s="36" t="s">
-        <v>2497</v>
-      </c>
-      <c r="Z113" s="36" t="s">
-        <v>2499</v>
-      </c>
-      <c r="AA113" s="36" t="s">
-        <v>2498</v>
       </c>
     </row>
     <row r="114" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -41007,13 +41005,13 @@
         <v>{szContent="尔等鼠辈！谁敢与我一战！",szTarget="%",szNote="据点攻防·正式开始",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime="2,据点攻防·正式开始;10,建议关闭·江湖身份",nRefresh=2,key="阵营活动",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W114" s="36" t="s">
-        <v>2624</v>
+        <v>2622</v>
       </c>
       <c r="X114" s="40" t="s">
-        <v>2412</v>
+        <v>2410</v>
       </c>
       <c r="Y114" s="40" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="115" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -41034,10 +41032,10 @@
         <v>2368</v>
       </c>
       <c r="X115" s="38" t="s">
-        <v>2561</v>
+        <v>2559</v>
       </c>
       <c r="Y115" s="38" t="s">
-        <v>2562</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="116" spans="1:27" x14ac:dyDescent="0.15">
@@ -41078,10 +41076,10 @@
         <v>2190</v>
       </c>
       <c r="X117" s="40" t="s">
-        <v>2412</v>
+        <v>2410</v>
       </c>
       <c r="Y117" s="40" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="118" spans="1:27" x14ac:dyDescent="0.15">
@@ -41092,7 +41090,7 @@
         <v>1582</v>
       </c>
       <c r="E118" t="s">
-        <v>2689</v>
+        <v>2687</v>
       </c>
       <c r="T118" s="36"/>
       <c r="V118" s="36" t="str">
@@ -41100,13 +41098,13 @@
         <v>{szContent="我竟然败给你们这群小辈！",szTarget="狼牙先锋首领",szNote="防冲突禁用·击退·狼牙先锋首领",[14]={},tCountdown={{nClass=-1,nIcon=3556,nFrame=1,szName="狼牙先锋首领·拾取掉落",nTime="10,狼牙先锋首领·已击退;300,狼牙先锋首领·拾取剩余;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=2,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W118" t="s">
-        <v>2647</v>
+        <v>2645</v>
       </c>
       <c r="X118" s="40" t="s">
-        <v>2412</v>
+        <v>2410</v>
       </c>
       <c r="Y118" s="40" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="119" spans="1:27" x14ac:dyDescent="0.15">
@@ -41143,7 +41141,7 @@
         <v>{szContent="增援已至武王城，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·武王城",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·武王城",nTime="10,浩气·兵符增援·武王城;300,浩气·武王城·兵符冷却;305,浩气·武王城·可用兵符",nRefresh=1,key="兵符·武王城",},},},</v>
       </c>
       <c r="W120" s="36" t="s">
-        <v>2494</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="121" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -41151,7 +41149,7 @@
         <v>2188</v>
       </c>
       <c r="D121" s="43" t="s">
-        <v>2547</v>
+        <v>2545</v>
       </c>
       <c r="M121" s="36" t="s">
         <v>1438</v>
@@ -41161,10 +41159,10 @@
         <v>{szContent="赵新宇死亡时，从他身上遗落一把短笛，貌似是他的随身信物。",szTarget="%",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=589,nFrame=7,szName="赵新宇",nTime=0,key="赵新宇",},{nClass=14,nIcon=589,nFrame=7,szName="赵新宇",nTime="60,赵新宇的信物;302,赵新宇·刷新剩余;304,赵新宇·即将刷新;310,赵新宇·延迟刷新",nRefresh=60,key="赵新宇",},},},</v>
       </c>
       <c r="W121" s="36" t="s">
-        <v>2535</v>
+        <v>2533</v>
       </c>
       <c r="X121" s="36" t="s">
-        <v>2536</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="122" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -41172,7 +41170,7 @@
         <v>2188</v>
       </c>
       <c r="D122" s="43" t="s">
-        <v>2548</v>
+        <v>2546</v>
       </c>
       <c r="M122" s="36" t="s">
         <v>1565</v>
@@ -41182,10 +41180,10 @@
         <v>{szContent="随着方超的死亡，一把短笛掉了出来，貌似是他的随身信物。",szTarget="%",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=308,nFrame=3,szName="方超",nTime=0,key="方超",},{nClass=14,nIcon=308,nFrame=3,szName="方超",nTime="60,方超的信物;302,方超·刷新剩余;304,方超·即将刷新;310,方超·延迟刷新",nRefresh=60,key="方超",},},},</v>
       </c>
       <c r="W122" s="36" t="s">
-        <v>2537</v>
+        <v>2535</v>
       </c>
       <c r="X122" s="36" t="s">
-        <v>2538</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="123" spans="1:27" x14ac:dyDescent="0.15">
@@ -41204,7 +41202,7 @@
         <v>{szContent="恶人谷老友们可在我这里传送到恶人谷！",szTarget="赵新宇",col={255,100,100,},[14]={},tCountdown={{nClass=-1,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=2,nRefresh=600,key="赵新宇",},},},</v>
       </c>
       <c r="W123" t="s">
-        <v>2733</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="124" spans="1:27" x14ac:dyDescent="0.15">
@@ -41223,7 +41221,7 @@
         <v>{szContent="浩气盟侠士们可在我这里传送到浩气盟！",szTarget="方超",col={100,100,255,},[14]={},tCountdown={{nClass=-1,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=2,nRefresh=600,key="方超",},},},</v>
       </c>
       <c r="W124" t="s">
-        <v>2734</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="125" spans="1:27" x14ac:dyDescent="0.15">
@@ -41386,7 +41384,7 @@
         <v>{szContent="增援已至凛风堡，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·凛风堡",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·凛风堡",nTime="10,恶人·兵符增援·凛风堡;300,恶人·凛风堡·兵符冷却;305,恶人·凛风堡·可用兵符",nRefresh=1,key="兵符·凛风堡",},},},</v>
       </c>
       <c r="W132" s="36" t="s">
-        <v>2444</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="133" spans="1:24" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -41451,7 +41449,7 @@
         <v>2188</v>
       </c>
       <c r="D135" s="43" t="s">
-        <v>2549</v>
+        <v>2547</v>
       </c>
       <c r="M135" s="36" t="s">
         <v>1438</v>
@@ -41461,10 +41459,10 @@
         <v>{szContent="随着霸图的死亡，一柄钢刀从他身上滑落，似乎是他的随身信物。",szTarget="%",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=2864,nFrame=7,szName="霸图",nTime=0,key="霸图",},{nClass=14,nIcon=2864,nFrame=7,szName="霸图",nTime="60,霸图的信物;302,霸图·刷新剩余;304,霸图·即将刷新;310,霸图·延迟刷新",nRefresh=60,key="霸图",},},},</v>
       </c>
       <c r="W135" s="36" t="s">
-        <v>2539</v>
+        <v>2537</v>
       </c>
       <c r="X135" s="36" t="s">
-        <v>2540</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="136" spans="1:24" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -41472,7 +41470,7 @@
         <v>2188</v>
       </c>
       <c r="D136" s="43" t="s">
-        <v>2550</v>
+        <v>2548</v>
       </c>
       <c r="M136" s="36" t="s">
         <v>1565</v>
@@ -41482,10 +41480,10 @@
         <v>{szContent="随着孙永恒的死亡，一柄短剑从他身上滑落，似乎是他的随身信物。",szTarget="%",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=845,nFrame=3,szName="孙永恒",nTime=0,key="孙永恒",},{nClass=14,nIcon=845,nFrame=3,szName="孙永恒",nTime="60,孙永恒的信物;302,孙永恒·刷新剩余;304,孙永恒·即将刷新;310,孙永恒·延迟刷新",nRefresh=60,key="孙永恒",},},},</v>
       </c>
       <c r="W136" s="36" t="s">
-        <v>2541</v>
+        <v>2539</v>
       </c>
       <c r="X136" s="36" t="s">
-        <v>2542</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="137" spans="1:24" x14ac:dyDescent="0.15">
@@ -41503,7 +41501,7 @@
         <v>{szContent="恶人谷老友们可在我这里传送到恶人谷！",szTarget="霸图",col={255,100,100,},[14]={},tCountdown={{nClass=-1,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=2,nRefresh=600,key="霸图",},},},</v>
       </c>
       <c r="W137" t="s">
-        <v>2731</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="138" spans="1:24" x14ac:dyDescent="0.15">
@@ -41521,7 +41519,7 @@
         <v>{szContent="浩气盟侠士们可在我这里传送到浩气盟！",szTarget="孙永恒",col={100,100,255,},[14]={},tCountdown={{nClass=-1,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=2,nRefresh=600,key="孙永恒",},},},</v>
       </c>
       <c r="W138" t="s">
-        <v>2732</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="139" spans="1:24" x14ac:dyDescent="0.15">
@@ -41677,7 +41675,7 @@
         <v>{szContent="增援已至盘龙坞，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·盘龙坞",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·盘龙坞",nTime="10,浩气·兵符增援·盘龙坞;300,浩气·盘龙坞·兵符冷却;305,浩气·盘龙坞·可用兵符",nRefresh=1,key="兵符·盘龙坞",},},},</v>
       </c>
       <c r="W146" s="36" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="147" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -41701,7 +41699,7 @@
         <v>{szContent="增援已至逐鹿坪，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·逐鹿坪",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·逐鹿坪",nTime="10,浩气·兵符增援·逐鹿坪;300,浩气·逐鹿坪·兵符冷却;305,浩气·逐鹿坪·可用兵符",nRefresh=1,key="兵符·逐鹿坪",},},},</v>
       </c>
       <c r="W147" s="36" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="148" spans="1:27" x14ac:dyDescent="0.15">
@@ -41709,7 +41707,7 @@
         <v>2188</v>
       </c>
       <c r="D148" s="43" t="s">
-        <v>2547</v>
+        <v>2545</v>
       </c>
       <c r="G148"/>
       <c r="I148"/>
@@ -41723,10 +41721,10 @@
         <v>{szContent="赵新宇死亡时，从他身上遗落一把短笛，貌似是他的随身信物。",szTarget="%",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=589,nFrame=7,szName="赵新宇",nTime=0,key="赵新宇",},{nClass=14,nIcon=589,nFrame=7,szName="赵新宇",nTime="60,赵新宇的信物;302,赵新宇·刷新剩余;304,赵新宇·即将刷新",nRefresh=60,key="赵新宇",},},},</v>
       </c>
       <c r="W148" t="s">
-        <v>2535</v>
+        <v>2533</v>
       </c>
       <c r="X148" s="36" t="s">
-        <v>2543</v>
+        <v>2541</v>
       </c>
       <c r="Z148" s="36"/>
       <c r="AA148" s="36"/>
@@ -41736,7 +41734,7 @@
         <v>2188</v>
       </c>
       <c r="D149" s="43" t="s">
-        <v>2548</v>
+        <v>2546</v>
       </c>
       <c r="G149"/>
       <c r="I149"/>
@@ -41750,10 +41748,10 @@
         <v>{szContent="随着方超的死亡，一把短笛掉了出来，貌似是他的随身信物。",szTarget="%",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=308,nFrame=3,szName="方超",nTime=0,key="方超",},{nClass=14,nIcon=308,nFrame=3,szName="方超",nTime="60,方超的信物;302,方超·刷新剩余;304,方超·即将刷新",nRefresh=60,key="方超",},},},</v>
       </c>
       <c r="W149" t="s">
-        <v>2537</v>
+        <v>2535</v>
       </c>
       <c r="X149" s="36" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
       <c r="Z149" s="36"/>
       <c r="AA149" s="36"/>
@@ -41773,7 +41771,7 @@
         <v>{szContent="恶人谷老友们可在我这里传送到恶人谷！",szTarget="赵新宇",col={255,100,100,},[14]={},tCountdown={{nClass=-1,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=2,nRefresh=600,key="赵新宇",},},},</v>
       </c>
       <c r="W150" s="36" t="s">
-        <v>2733</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="151" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -41791,7 +41789,7 @@
         <v>{szContent="浩气盟侠士们可在我这里传送到浩气盟！",szTarget="方超",col={100,100,255,},[14]={},tCountdown={{nClass=-1,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=2,nRefresh=600,key="方超",},},},</v>
       </c>
       <c r="W151" s="36" t="s">
-        <v>2734</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="152" spans="1:27" x14ac:dyDescent="0.15">
@@ -41827,7 +41825,7 @@
         <v>{szContent="增援已至龙门镇，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·龙门镇",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·龙门镇",nTime="10,恶人·兵符增援·龙门镇;300,恶人·龙门镇·兵符冷却;305,恶人·龙门镇·可用兵符",nRefresh=1,key="兵符·龙门镇",},},},</v>
       </c>
       <c r="W153" s="36" t="s">
-        <v>2445</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="154" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -41851,7 +41849,7 @@
         <v>{szContent="增援已至飞沙关，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·飞沙关",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·飞沙关",nTime="10,恶人·兵符增援·飞沙关;300,恶人·飞沙关·兵符冷却;305,恶人·飞沙关·可用兵符",nRefresh=1,key="兵符·飞沙关",},},},</v>
       </c>
       <c r="W154" s="36" t="s">
-        <v>2446</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="155" spans="1:27" x14ac:dyDescent="0.15">
@@ -41859,7 +41857,7 @@
         <v>2188</v>
       </c>
       <c r="D155" s="43" t="s">
-        <v>2549</v>
+        <v>2547</v>
       </c>
       <c r="G155"/>
       <c r="I155"/>
@@ -41873,10 +41871,10 @@
         <v>{szContent="随着霸图的死亡，一柄钢刀从他身上滑落，似乎是他的随身信物。",szTarget="%",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=2864,nFrame=7,szName="霸图",nTime=0,key="霸图",},{nClass=14,nIcon=2864,nFrame=7,szName="霸图",nTime="60,霸图的信物;302,霸图·刷新剩余;304,霸图·即将刷新",nRefresh=60,key="霸图",},},},</v>
       </c>
       <c r="W155" s="36" t="s">
-        <v>2539</v>
+        <v>2537</v>
       </c>
       <c r="X155" s="36" t="s">
-        <v>2545</v>
+        <v>2543</v>
       </c>
       <c r="Z155" s="36"/>
       <c r="AA155" s="36"/>
@@ -41886,7 +41884,7 @@
         <v>2188</v>
       </c>
       <c r="D156" s="43" t="s">
-        <v>2550</v>
+        <v>2548</v>
       </c>
       <c r="G156"/>
       <c r="I156"/>
@@ -41900,10 +41898,10 @@
         <v>{szContent="随着孙永恒的死亡，一柄短剑从他身上滑落，似乎是他的随身信物。",szTarget="%",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=845,nFrame=3,szName="孙永恒",nTime=0,key="孙永恒",},{nClass=14,nIcon=845,nFrame=3,szName="孙永恒",nTime="60,孙永恒的信物;302,孙永恒·刷新剩余;304,孙永恒·即将刷新",nRefresh=60,key="孙永恒",},},},</v>
       </c>
       <c r="W156" s="36" t="s">
-        <v>2541</v>
+        <v>2539</v>
       </c>
       <c r="X156" s="36" t="s">
-        <v>2546</v>
+        <v>2544</v>
       </c>
       <c r="Z156" s="36"/>
       <c r="AA156" s="36"/>
@@ -41923,7 +41921,7 @@
         <v>{szContent="恶人谷老友们可在我这里传送到恶人谷！",szTarget="霸图",col={255,100,100,},[14]={},tCountdown={{nClass=-1,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=2,nRefresh=600,key="霸图",},},},</v>
       </c>
       <c r="W157" s="36" t="s">
-        <v>2731</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="158" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -41941,7 +41939,7 @@
         <v>{szContent="浩气盟侠士们可在我这里传送到浩气盟！",szTarget="孙永恒",col={100,100,255,},[14]={},tCountdown={{nClass=-1,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=2,nRefresh=600,key="孙永恒",},},},</v>
       </c>
       <c r="W158" s="36" t="s">
-        <v>2732</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="159" spans="1:27" x14ac:dyDescent="0.15">
@@ -41977,7 +41975,7 @@
         <v>{szContent="增援已至红莲岗，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·红莲岗",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·红莲岗",nTime="10,浩气·兵符增援·红莲岗;300,浩气·红莲岗·兵符冷却;305,浩气·红莲岗·可用兵符",nRefresh=1,key="兵符·红莲岗",},},},</v>
       </c>
       <c r="W160" s="36" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="161" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -42001,7 +41999,7 @@
         <v>{szContent="增援已至秋雨堡，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·秋雨堡",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·秋雨堡",nTime="10,浩气·兵符增援·秋雨堡;300,浩气·秋雨堡·兵符冷却;305,浩气·秋雨堡·可用兵符",nRefresh=1,key="兵符·秋雨堡",},},},</v>
       </c>
       <c r="W161" s="36" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="162" spans="1:27" x14ac:dyDescent="0.15">
@@ -42037,7 +42035,7 @@
         <v>{szContent="增援已至神池岭，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·神池岭",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·神池岭",nTime="10,恶人·兵符增援·神池岭;300,恶人·神池岭·兵符冷却;305,恶人·神池岭·可用兵符",nRefresh=1,key="兵符·神池岭",},},},</v>
       </c>
       <c r="W163" s="36" t="s">
-        <v>2447</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="164" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -42061,7 +42059,7 @@
         <v>{szContent="增援已至烈日岗，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·烈日岗",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·烈日岗",nTime="10,恶人·兵符增援·烈日岗;300,恶人·烈日岗·兵符冷却;305,恶人·烈日岗·可用兵符",nRefresh=1,key="兵符·烈日岗",},},},</v>
       </c>
       <c r="W164" s="36" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="165" spans="1:27" x14ac:dyDescent="0.15">
@@ -42097,7 +42095,7 @@
         <v>{szContent="增援已至大理山城，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·大理山城",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·大理山城",nTime="10,浩气·兵符增援·大理山城;300,浩气·大理山城·兵符冷却;305,浩气·大理山城·可用兵符",nRefresh=1,key="兵符·大理山城",},},},</v>
       </c>
       <c r="W166" s="36" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="167" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -42121,7 +42119,7 @@
         <v>{szContent="增援已至千岩关，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·千岩关",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·千岩关",nTime="10,浩气·兵符增援·千岩关;300,浩气·千岩关·兵符冷却;305,浩气·千岩关·可用兵符",nRefresh=1,key="兵符·千岩关",},},},</v>
       </c>
       <c r="W167" s="36" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="168" spans="1:27" x14ac:dyDescent="0.15">
@@ -42157,7 +42155,7 @@
         <v>{szContent="增援已至扶风郡，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·扶风郡",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·扶风郡",nTime="10,恶人·兵符增援·扶风郡;300,恶人·扶风郡·兵符冷却;305,恶人·扶风郡·可用兵符",nRefresh=1,key="兵符·扶风郡",},},},</v>
       </c>
       <c r="W169" s="36" t="s">
-        <v>2449</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="170" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -42181,7 +42179,7 @@
         <v>{szContent="增援已至世外坡，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·世外坡",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·世外坡",nTime="10,恶人·兵符增援·世外坡;300,恶人·世外坡·兵符冷却;305,恶人·世外坡·可用兵符",nRefresh=1,key="兵符·世外坡",},},},</v>
       </c>
       <c r="W170" s="36" t="s">
-        <v>2443</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="171" spans="1:27" x14ac:dyDescent="0.15">
@@ -42220,13 +42218,13 @@
         <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
       </c>
       <c r="W172" s="36" t="s">
+        <v>2556</v>
+      </c>
+      <c r="X172" s="36" t="s">
+        <v>2557</v>
+      </c>
+      <c r="Y172" s="36" t="s">
         <v>2558</v>
-      </c>
-      <c r="X172" s="36" t="s">
-        <v>2559</v>
-      </c>
-      <c r="Y172" s="36" t="s">
-        <v>2560</v>
       </c>
     </row>
     <row r="173" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -42247,10 +42245,10 @@
         <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W173" s="36" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="X173" s="36" t="s">
-        <v>2648</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="174" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -42271,10 +42269,10 @@
         <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W174" s="36" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="X174" s="36" t="s">
-        <v>2649</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="175" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -42282,10 +42280,10 @@
         <v>2188</v>
       </c>
       <c r="D175" s="36" t="s">
-        <v>2492</v>
+        <v>2490</v>
       </c>
       <c r="E175" s="36" t="s">
-        <v>2493</v>
+        <v>2491</v>
       </c>
       <c r="M175" s="36" t="s">
         <v>1748</v>
@@ -42298,19 +42296,19 @@
         <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},},},</v>
       </c>
       <c r="W175" s="36" t="s">
+        <v>2493</v>
+      </c>
+      <c r="X175" s="36" t="s">
+        <v>2494</v>
+      </c>
+      <c r="Y175" s="36" t="s">
         <v>2495</v>
       </c>
-      <c r="X175" s="36" t="s">
+      <c r="Z175" s="36" t="s">
+        <v>2497</v>
+      </c>
+      <c r="AA175" s="36" t="s">
         <v>2496</v>
-      </c>
-      <c r="Y175" s="36" t="s">
-        <v>2497</v>
-      </c>
-      <c r="Z175" s="36" t="s">
-        <v>2499</v>
-      </c>
-      <c r="AA175" s="36" t="s">
-        <v>2498</v>
       </c>
     </row>
     <row r="176" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -42318,10 +42316,10 @@
         <v>1431</v>
       </c>
       <c r="D176" s="36" t="s">
-        <v>2506</v>
+        <v>2504</v>
       </c>
       <c r="E176" s="36" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="M176" s="36" t="s">
         <v>1432</v>
@@ -42337,19 +42335,19 @@
         <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W176" s="36" t="s">
-        <v>2508</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="177" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C177" s="40"/>
       <c r="D177" s="36" t="s">
+        <v>2500</v>
+      </c>
+      <c r="E177" s="36" t="s">
+        <v>2501</v>
+      </c>
+      <c r="M177" s="36" t="s">
         <v>2502</v>
-      </c>
-      <c r="E177" s="36" t="s">
-        <v>2503</v>
-      </c>
-      <c r="M177" s="36" t="s">
-        <v>2504</v>
       </c>
       <c r="P177" s="36" t="s">
         <v>1089</v>
@@ -42371,7 +42369,7 @@
         <v>{szContent="系统检测您有挂机行为，如果长期维持该状态将被传送出图！",szNote="挂机检测·快活跃起来",col={255,50,255,},[14]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},},},</v>
       </c>
       <c r="W177" s="36" t="s">
-        <v>2505</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="178" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -42408,10 +42406,10 @@
         <v>2368</v>
       </c>
       <c r="X179" s="38" t="s">
-        <v>2561</v>
+        <v>2559</v>
       </c>
       <c r="Y179" s="38" t="s">
-        <v>2562</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="180" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -42450,10 +42448,10 @@
         <v>2190</v>
       </c>
       <c r="X181" s="40" t="s">
-        <v>2412</v>
+        <v>2410</v>
       </c>
       <c r="Y181" s="40" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="182" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -42464,20 +42462,20 @@
         <v>1582</v>
       </c>
       <c r="E182" s="36" t="s">
-        <v>2689</v>
+        <v>2687</v>
       </c>
       <c r="V182" s="36" t="str">
         <f t="shared" si="27"/>
         <v>{szContent="我竟然败给你们这群小辈！",szTarget="狼牙先锋首领",szNote="防冲突禁用·击退·狼牙先锋首领",[14]={},tCountdown={{nClass=-1,nIcon=3556,nFrame=1,szName="狼牙先锋首领·拾取掉落",nTime="10,狼牙先锋首领·已击退;300,狼牙先锋首领·拾取剩余;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=2,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W182" s="36" t="s">
-        <v>2647</v>
+        <v>2645</v>
       </c>
       <c r="X182" s="40" t="s">
-        <v>2412</v>
+        <v>2410</v>
       </c>
       <c r="Y182" s="40" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="183" spans="1:27" x14ac:dyDescent="0.15">
@@ -42516,13 +42514,13 @@
         <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
       </c>
       <c r="W184" s="36" t="s">
+        <v>2556</v>
+      </c>
+      <c r="X184" s="36" t="s">
+        <v>2557</v>
+      </c>
+      <c r="Y184" s="36" t="s">
         <v>2558</v>
-      </c>
-      <c r="X184" s="36" t="s">
-        <v>2559</v>
-      </c>
-      <c r="Y184" s="36" t="s">
-        <v>2560</v>
       </c>
     </row>
     <row r="185" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -42543,10 +42541,10 @@
         <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W185" s="36" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="X185" s="36" t="s">
-        <v>2648</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="186" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -42567,10 +42565,10 @@
         <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W186" s="36" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="X186" s="36" t="s">
-        <v>2649</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="187" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -42578,10 +42576,10 @@
         <v>2188</v>
       </c>
       <c r="D187" s="36" t="s">
-        <v>2492</v>
+        <v>2490</v>
       </c>
       <c r="E187" s="36" t="s">
-        <v>2493</v>
+        <v>2491</v>
       </c>
       <c r="M187" s="36" t="s">
         <v>1748</v>
@@ -42594,19 +42592,19 @@
         <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},},},</v>
       </c>
       <c r="W187" s="36" t="s">
+        <v>2493</v>
+      </c>
+      <c r="X187" s="36" t="s">
+        <v>2494</v>
+      </c>
+      <c r="Y187" s="36" t="s">
         <v>2495</v>
       </c>
-      <c r="X187" s="36" t="s">
+      <c r="Z187" s="36" t="s">
+        <v>2497</v>
+      </c>
+      <c r="AA187" s="36" t="s">
         <v>2496</v>
-      </c>
-      <c r="Y187" s="36" t="s">
-        <v>2497</v>
-      </c>
-      <c r="Z187" s="36" t="s">
-        <v>2499</v>
-      </c>
-      <c r="AA187" s="36" t="s">
-        <v>2498</v>
       </c>
     </row>
     <row r="188" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -42614,10 +42612,10 @@
         <v>1431</v>
       </c>
       <c r="D188" s="36" t="s">
-        <v>2506</v>
+        <v>2504</v>
       </c>
       <c r="E188" s="36" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="M188" s="36" t="s">
         <v>1432</v>
@@ -42633,19 +42631,19 @@
         <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W188" s="36" t="s">
-        <v>2508</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="189" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C189" s="40"/>
       <c r="D189" s="36" t="s">
+        <v>2500</v>
+      </c>
+      <c r="E189" s="36" t="s">
+        <v>2501</v>
+      </c>
+      <c r="M189" s="36" t="s">
         <v>2502</v>
-      </c>
-      <c r="E189" s="36" t="s">
-        <v>2503</v>
-      </c>
-      <c r="M189" s="36" t="s">
-        <v>2504</v>
       </c>
       <c r="P189" s="36" t="s">
         <v>1089</v>
@@ -42667,7 +42665,7 @@
         <v>{szContent="系统检测您有挂机行为，如果长期维持该状态将被传送出图！",szNote="挂机检测·快活跃起来",col={255,50,255,},[14]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},},},</v>
       </c>
       <c r="W189" s="36" t="s">
-        <v>2505</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="190" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -42704,10 +42702,10 @@
         <v>2368</v>
       </c>
       <c r="X191" s="38" t="s">
-        <v>2561</v>
+        <v>2559</v>
       </c>
       <c r="Y191" s="38" t="s">
-        <v>2562</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="192" spans="1:27" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -42746,10 +42744,10 @@
         <v>2190</v>
       </c>
       <c r="X193" s="40" t="s">
-        <v>2412</v>
+        <v>2410</v>
       </c>
       <c r="Y193" s="40" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="194" spans="3:25" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -42760,20 +42758,20 @@
         <v>1582</v>
       </c>
       <c r="E194" s="36" t="s">
-        <v>2689</v>
+        <v>2687</v>
       </c>
       <c r="V194" s="36" t="str">
         <f t="shared" si="27"/>
         <v>{szContent="我竟然败给你们这群小辈！",szTarget="狼牙先锋首领",szNote="防冲突禁用·击退·狼牙先锋首领",[14]={},tCountdown={{nClass=-1,nIcon=3556,nFrame=1,szName="狼牙先锋首领·拾取掉落",nTime="10,狼牙先锋首领·已击退;300,狼牙先锋首领·拾取剩余;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=2,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W194" s="36" t="s">
-        <v>2647</v>
+        <v>2645</v>
       </c>
       <c r="X194" s="40" t="s">
-        <v>2412</v>
+        <v>2410</v>
       </c>
       <c r="Y194" s="40" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="195" spans="3:25" x14ac:dyDescent="0.15">
@@ -42910,18 +42908,18 @@
         <v>{szContent="[团队监控]数据加载成功",szNote="关闭刷马等计时条",bSearch=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},},},</v>
       </c>
       <c r="U3" s="40" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
       <c r="V3" s="40" t="s">
-        <v>2570</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="4" spans="1:72" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C4" s="36" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="K4" s="36" t="s">
         <v>1748</v>
@@ -42931,7 +42929,7 @@
         <v>{szContent="驿马快报！本周浩气盟和恶人谷最终战为平手，未分胜负！\n",szNote="阵营事件·本周战平",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13354,nFrame=4,szName="阵营事件·本周战平",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U4" s="36" t="s">
-        <v>2631</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="5" spans="1:72" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -42985,16 +42983,16 @@
         <v>{szContent="本场攻防“奇袭场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手。战利品稍后开始拍卖，请留意！\n",szNote="奇袭场·平局",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2402,nFrame=4,szName="奇袭场·平局",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·一",key="破阵点将·一",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·二",key="破阵点将·二",},{nClass=20,nIcon=13,szName="牛车拾取间隔",nTime=-1,key="牛车拾取间隔",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,key="首领拾取间隔",},{nClass=20,nIcon=13,nFrame=4,szName="浩气·物资车·运达",nTime=-1,key="浩气·物资车·运达",},{nClass=20,nIcon=13,nFrame=4,szName="恶人·物资车·运达",nTime=-1,key="恶人·物资车·运达",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·月弄痕·减伤",nTime=-1,key="谢渊·月弄痕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·游驹·减伤",nTime=-1,key="谢渊·游驹·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·小七·减伤",nTime=-1,key="谢渊·小七·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·张桎辕·减伤",nTime=-1,key="谢渊·张桎辕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·司空仲平·减伤",nTime=-1,key="谢渊·司空仲平·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·韩非池·减伤",nTime=-1,key="谢渊·韩非池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·赵紫儿·减伤",nTime=-1,key="谢渊·赵紫儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·叶镜池·减伤",nTime=-1,key="谢渊·叶镜池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郭珠·减伤",nTime=-1,key="谢渊·郭珠·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·穆玄英·减伤",nTime=-1,key="谢渊·穆玄英·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·影·减伤",nTime=-1,key="谢渊·影·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·司徒一一·减伤",nTime=-1,key="王遗风·司徒一一·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·白某·减伤",nTime=-1,key="王遗风·白某·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·米丽古丽·减伤",nTime=-1,key="王遗风·米丽古丽·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶寒亭·减伤",nTime=-1,key="王遗风·陶寒亭·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·肖药儿·减伤",nTime=-1,key="王遗风·肖药儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·伊夜·减伤",nTime=-1,key="王遗风·伊夜·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·丁丁·减伤",nTime=-1,key="王遗风·丁丁·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·岳琅·减伤",nTime=-1,key="王遗风·岳琅·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·毕罗巴·减伤",nTime=-1,key="王遗风·毕罗巴·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·烟·减伤",nTime=-1,key="王遗风·烟·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·独孤修·减伤",nTime=-1,key="王遗风·独孤修·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·周峰·减伤",nTime=-1,key="谢渊·周峰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郑鸥·减伤",nTime=-1,key="谢渊·郑鸥·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·陶杰·减伤",nTime=-1,key="谢渊·陶杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢烟客·减伤",nTime=-1,key="谢渊·谢烟客·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·张一洋·减伤",nTime=-1,key="王遗风·张一洋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶国栋·减伤",nTime=-1,key="王遗风·陶国栋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·吕沛杰·减伤",nTime=-1,key="王遗风·吕沛杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·顾延恶·减伤",nTime=-1,key="王遗风·顾延恶·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·莫雨·减伤",nTime=-1,key="王遗风·莫雨·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·万兽王·减伤",nTime=-1,key="王遗风·万兽王·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢铃儿·减伤",nTime=-1,key="谢渊·谢铃儿·减伤",},},},</v>
       </c>
       <c r="U7" t="s">
-        <v>2401</v>
+        <v>2399</v>
       </c>
       <c r="V7" s="36" t="s">
-        <v>2720</v>
+        <v>2717</v>
       </c>
       <c r="W7" s="36" t="s">
-        <v>2718</v>
+        <v>2715</v>
       </c>
       <c r="X7" s="36" t="s">
-        <v>2719</v>
+        <v>2716</v>
       </c>
       <c r="Y7" s="36" t="s">
         <v>2113</v>
@@ -43009,7 +43007,7 @@
         <v>1941</v>
       </c>
       <c r="AC7" s="52" t="s">
-        <v>2651</v>
+        <v>2649</v>
       </c>
       <c r="AD7" s="36"/>
       <c r="AE7" s="36"/>
@@ -43066,16 +43064,16 @@
         <v>{szContent="本场攻防“主战场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手。战利品稍后开始拍卖，请留意！\n",szNote="主战场·平局",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="主战场·平局",nTime=57,nRefresh=5,key="大攻防·主战场",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·一",key="破阵点将·一",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·二",key="破阵点将·二",},{nClass=20,nIcon=13,szName="牛车拾取间隔",nTime=-1,key="牛车拾取间隔",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,key="首领拾取间隔",},{nClass=20,nIcon=13,nFrame=4,szName="浩气·物资车·运达",nTime=-1,key="浩气·物资车·运达",},{nClass=20,nIcon=13,nFrame=4,szName="恶人·物资车·运达",nTime=-1,key="恶人·物资车·运达",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·月弄痕·减伤",nTime=-1,key="谢渊·月弄痕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·游驹·减伤",nTime=-1,key="谢渊·游驹·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·小七·减伤",nTime=-1,key="谢渊·小七·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·张桎辕·减伤",nTime=-1,key="谢渊·张桎辕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·司空仲平·减伤",nTime=-1,key="谢渊·司空仲平·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·韩非池·减伤",nTime=-1,key="谢渊·韩非池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·赵紫儿·减伤",nTime=-1,key="谢渊·赵紫儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·叶镜池·减伤",nTime=-1,key="谢渊·叶镜池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郭珠·减伤",nTime=-1,key="谢渊·郭珠·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·穆玄英·减伤",nTime=-1,key="谢渊·穆玄英·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·影·减伤",nTime=-1,key="谢渊·影·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·司徒一一·减伤",nTime=-1,key="王遗风·司徒一一·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·白某·减伤",nTime=-1,key="王遗风·白某·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·米丽古丽·减伤",nTime=-1,key="王遗风·米丽古丽·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶寒亭·减伤",nTime=-1,key="王遗风·陶寒亭·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·肖药儿·减伤",nTime=-1,key="王遗风·肖药儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·伊夜·减伤",nTime=-1,key="王遗风·伊夜·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·丁丁·减伤",nTime=-1,key="王遗风·丁丁·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·岳琅·减伤",nTime=-1,key="王遗风·岳琅·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·毕罗巴·减伤",nTime=-1,key="王遗风·毕罗巴·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·烟·减伤",nTime=-1,key="王遗风·烟·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·独孤修·减伤",nTime=-1,key="王遗风·独孤修·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·周峰·减伤",nTime=-1,key="谢渊·周峰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郑鸥·减伤",nTime=-1,key="谢渊·郑鸥·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·陶杰·减伤",nTime=-1,key="谢渊·陶杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢烟客·减伤",nTime=-1,key="谢渊·谢烟客·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·张一洋·减伤",nTime=-1,key="王遗风·张一洋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶国栋·减伤",nTime=-1,key="王遗风·陶国栋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·吕沛杰·减伤",nTime=-1,key="王遗风·吕沛杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·顾延恶·减伤",nTime=-1,key="王遗风·顾延恶·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·莫雨·减伤",nTime=-1,key="王遗风·莫雨·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·万兽王·减伤",nTime=-1,key="王遗风·万兽王·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢铃儿·减伤",nTime=-1,key="谢渊·谢铃儿·减伤",},},},</v>
       </c>
       <c r="U8" t="s">
-        <v>2400</v>
+        <v>2398</v>
       </c>
       <c r="V8" s="36" t="s">
-        <v>2720</v>
+        <v>2717</v>
       </c>
       <c r="W8" s="36" t="s">
-        <v>2718</v>
+        <v>2715</v>
       </c>
       <c r="X8" s="36" t="s">
-        <v>2719</v>
+        <v>2716</v>
       </c>
       <c r="Y8" s="36" t="s">
         <v>2113</v>
@@ -43090,7 +43088,7 @@
         <v>1941</v>
       </c>
       <c r="AC8" s="52" t="s">
-        <v>2651</v>
+        <v>2649</v>
       </c>
       <c r="AD8" s="36"/>
       <c r="AE8" s="36"/>
@@ -43153,28 +43151,28 @@
         <v>{szContent="^本场攻防“([主战奇袭场]+)”已结束，([浩气盟恶人谷]+)[侠士们众志成城和，]-([大完险胜]+)([浩气盟恶人谷]+)[！，]+",szNote="{$1}·{$2}·{$3}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,szName="大攻防·奇袭场",nTime=-2,nRefresh=10,key="大攻防·奇袭场",},{nClass=20,nIcon=13,szName="大攻防·主战场",nTime=-2,nRefresh=10,key="大攻防·主战场",},{nClass=20,nIcon=13,szName="大攻防·{$1}",nTime=-2,key="大攻防·{$1}",},{nClass=20,nIcon=2402,nFrame=4,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·主战场",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·一",key="破阵点将·一",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·二",key="破阵点将·二",},{nClass=20,nIcon=13,szName="牛车拾取间隔",nTime=-1,key="牛车拾取间隔",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,key="首领拾取间隔",},{nClass=20,nIcon=13,nFrame=4,szName="浩气·物资车·运达",nTime=-1,key="浩气·物资车·运达",},{nClass=20,nIcon=13,nFrame=4,szName="恶人·物资车·运达",nTime=-1,key="恶人·物资车·运达",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·月弄痕·减伤",nTime=-1,key="谢渊·月弄痕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·游驹·减伤",nTime=-1,key="谢渊·游驹·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·小七·减伤",nTime=-1,key="谢渊·小七·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·张桎辕·减伤",nTime=-1,key="谢渊·张桎辕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·司空仲平·减伤",nTime=-1,key="谢渊·司空仲平·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·韩非池·减伤",nTime=-1,key="谢渊·韩非池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·赵紫儿·减伤",nTime=-1,key="谢渊·赵紫儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·叶镜池·减伤",nTime=-1,key="谢渊·叶镜池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郭珠·减伤",nTime=-1,key="谢渊·郭珠·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·穆玄英·减伤",nTime=-1,key="谢渊·穆玄英·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·影·减伤",nTime=-1,key="谢渊·影·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·司徒一一·减伤",nTime=-1,key="王遗风·司徒一一·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·白某·减伤",nTime=-1,key="王遗风·白某·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·米丽古丽·减伤",nTime=-1,key="王遗风·米丽古丽·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶寒亭·减伤",nTime=-1,key="王遗风·陶寒亭·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·肖药儿·减伤",nTime=-1,key="王遗风·肖药儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·伊夜·减伤",nTime=-1,key="王遗风·伊夜·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·丁丁·减伤",nTime=-1,key="王遗风·丁丁·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·岳琅·减伤",nTime=-1,key="王遗风·岳琅·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·毕罗巴·减伤",nTime=-1,key="王遗风·毕罗巴·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·烟·减伤",nTime=-1,key="王遗风·烟·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·独孤修·减伤",nTime=-1,key="王遗风·独孤修·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·周峰·减伤",nTime=-1,key="谢渊·周峰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郑鸥·减伤",nTime=-1,key="谢渊·郑鸥·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·陶杰·减伤",nTime=-1,key="谢渊·陶杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢烟客·减伤",nTime=-1,key="谢渊·谢烟客·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·张一洋·减伤",nTime=-1,key="王遗风·张一洋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶国栋·减伤",nTime=-1,key="王遗风·陶国栋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·吕沛杰·减伤",nTime=-1,key="王遗风·吕沛杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·顾延恶·减伤",nTime=-1,key="王遗风·顾延恶·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·莫雨·减伤",nTime=-1,key="王遗风·莫雨·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·万兽王·减伤",nTime=-1,key="王遗风·万兽王·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢铃儿·减伤",nTime=-1,key="谢渊·谢铃儿·减伤",},},},</v>
       </c>
       <c r="U9" s="36" t="s">
-        <v>2512</v>
+        <v>2510</v>
       </c>
       <c r="V9" s="36" t="s">
-        <v>2513</v>
+        <v>2511</v>
       </c>
       <c r="W9" t="s">
         <v>2187</v>
       </c>
       <c r="X9" s="36" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
       <c r="Y9" s="36" t="s">
-        <v>2398</v>
+        <v>2396</v>
       </c>
       <c r="Z9" s="36" t="s">
-        <v>2720</v>
+        <v>2717</v>
       </c>
       <c r="AA9" s="36" t="s">
-        <v>2718</v>
+        <v>2715</v>
       </c>
       <c r="AB9" s="36" t="s">
-        <v>2719</v>
+        <v>2716</v>
       </c>
       <c r="AC9" s="36" t="s">
         <v>2113</v>
@@ -43189,7 +43187,7 @@
         <v>1941</v>
       </c>
       <c r="AG9" s="40" t="s">
-        <v>2651</v>
+        <v>2649</v>
       </c>
       <c r="AH9" s="36"/>
       <c r="AI9" s="36"/>
@@ -43249,10 +43247,10 @@
         <v>2298</v>
       </c>
       <c r="V10" s="38" t="s">
-        <v>2573</v>
+        <v>2571</v>
       </c>
       <c r="W10" s="38" t="s">
-        <v>2572</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="11" spans="1:72" x14ac:dyDescent="0.15">
@@ -43456,13 +43454,13 @@
         <v>1834</v>
       </c>
       <c r="X17" s="36" t="s">
-        <v>2416</v>
+        <v>2414</v>
       </c>
       <c r="Y17" s="36" t="s">
-        <v>2417</v>
+        <v>2415</v>
       </c>
       <c r="Z17" s="40" t="s">
-        <v>2570</v>
+        <v>2568</v>
       </c>
       <c r="AA17" s="36"/>
       <c r="AB17" s="36"/>
@@ -43502,13 +43500,13 @@
         <v>1939</v>
       </c>
       <c r="V18" s="36" t="s">
-        <v>2415</v>
+        <v>2413</v>
       </c>
       <c r="W18" s="40" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
       <c r="X18" s="36" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="19" spans="1:72" x14ac:dyDescent="0.15">
@@ -43529,19 +43527,19 @@
         <v>{szContent="王遗风已率恶人谷众首领抵达浩气盟，请各位恶人谷侠士速到浩气盟支援。浩气盟侠士也请速回浩气盟防御！\n",szNote="主场攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2702,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5402,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=30,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="速战速决",nTime=-2,key="速战速决",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U19" s="36" t="s">
-        <v>2723</v>
+        <v>2718</v>
       </c>
       <c r="V19" s="36" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="W19" s="36" t="s">
         <v>2302</v>
       </c>
       <c r="X19" s="40" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
       <c r="Y19" s="36" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="Z19" s="36"/>
       <c r="AA19" s="36"/>
@@ -43615,13 +43613,13 @@
         <v>1834</v>
       </c>
       <c r="X21" s="36" t="s">
-        <v>2416</v>
+        <v>2414</v>
       </c>
       <c r="Y21" s="36" t="s">
-        <v>2417</v>
+        <v>2415</v>
       </c>
       <c r="Z21" s="40" t="s">
-        <v>2570</v>
+        <v>2568</v>
       </c>
       <c r="AA21" s="36"/>
       <c r="AB21" s="36"/>
@@ -43691,13 +43689,13 @@
         <v>1939</v>
       </c>
       <c r="V22" s="36" t="s">
-        <v>2415</v>
+        <v>2413</v>
       </c>
       <c r="W22" s="40" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
       <c r="X22" s="36" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="23" spans="1:72" x14ac:dyDescent="0.15">
@@ -43718,19 +43716,19 @@
         <v>{szContent="谢渊已率浩气盟众首领抵达恶人谷，请各位浩气盟侠士速到恶人谷支援。恶人谷侠士也请速回恶人谷防御！\n",szNote="主场攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2702,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5402,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=30,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="速战速决",nTime=-2,key="速战速决",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U23" s="36" t="s">
-        <v>2723</v>
+        <v>2718</v>
       </c>
       <c r="V23" s="36" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="W23" s="36" t="s">
         <v>2302</v>
       </c>
       <c r="X23" s="40" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
       <c r="Y23" s="36" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="Z23" s="36"/>
       <c r="AA23" s="36"/>
@@ -43780,10 +43778,10 @@
     </row>
     <row r="25" spans="1:72" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C25" s="36" t="s">
-        <v>2595</v>
+        <v>2593</v>
       </c>
       <c r="D25" s="36" t="s">
-        <v>2596</v>
+        <v>2594</v>
       </c>
       <c r="K25" s="36" t="s">
         <v>1432</v>
@@ -43796,7 +43794,7 @@
         <v>{szContent="(.-)【(.-)】帮会的(.-)大侠成功护送祭祀物资到达(.-)据点，该据点将士备受鼓舞，战意高昂，战时必将固若金汤！",szNote="祭天·{$1}·[{$2}]·{$4}",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=8838,nFrame=1,szName="{$1}祭天·[{$2}]·{$4}",nTime=30,key="通用事件",},},},</v>
       </c>
       <c r="U25" s="36" t="s">
-        <v>2597</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="26" spans="1:72" x14ac:dyDescent="0.15">
@@ -43811,7 +43809,7 @@
         <v>{szContent="为保障各位侠士的安全，浩气盟和恶人谷重新派出了守卫，在野外地图侠士重伤后复活可回到阵营复活点！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="据点攻防·消失模式",nTime=1799.795,key="阵营活动",},},},</v>
       </c>
       <c r="U26" t="s">
-        <v>2565</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="27" spans="1:72" x14ac:dyDescent="0.15">
@@ -43841,7 +43839,7 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“恶人谷”地图进行清场操作，并在“下午六点三十分”开始攻防排队，请勿在下午六点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·恶人谷·18:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U28" t="s">
-        <v>2566</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="29" spans="1:72" x14ac:dyDescent="0.15">
@@ -43856,7 +43854,7 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“恶人谷”地图进行清场操作，并在“中午十二点三十分”开始攻防排队，请勿在中午十二点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·恶人谷·12:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U29" t="s">
-        <v>2567</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="30" spans="1:72" x14ac:dyDescent="0.15">
@@ -43871,7 +43869,7 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“浩气盟”地图进行清场操作，并在“下午六点三十分”开始攻防排队，请勿在下午六点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·浩气盟·18:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U30" t="s">
-        <v>2568</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="31" spans="1:72" x14ac:dyDescent="0.15">
@@ -43886,7 +43884,7 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“浩气盟”地图进行清场操作，并在“中午十二点三十分”开始攻防排队，请勿在中午十二点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·浩气盟·12:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U31" t="s">
-        <v>2569</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="32" spans="1:72" x14ac:dyDescent="0.15">
@@ -43933,7 +43931,7 @@
     </row>
     <row r="34" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A34" s="36" t="s">
-        <v>2693</v>
+        <v>2690</v>
       </c>
       <c r="B34" s="36">
         <v>-21</v>
@@ -43982,13 +43980,13 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U36" s="36" t="s">
+        <v>2417</v>
+      </c>
+      <c r="V36" s="36" t="s">
+        <v>2418</v>
+      </c>
+      <c r="W36" s="36" t="s">
         <v>2419</v>
-      </c>
-      <c r="V36" s="36" t="s">
-        <v>2420</v>
-      </c>
-      <c r="W36" s="36" t="s">
-        <v>2421</v>
       </c>
       <c r="X36" s="36" t="s">
         <v>2293</v>
@@ -44018,13 +44016,13 @@
         <v>1861</v>
       </c>
       <c r="V37" s="36" t="s">
+        <v>2421</v>
+      </c>
+      <c r="W37" s="36" t="s">
         <v>2423</v>
       </c>
-      <c r="W37" s="36" t="s">
-        <v>2425</v>
-      </c>
       <c r="X37" s="36" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="Y37" s="36" t="s">
         <v>2200</v>
@@ -44266,13 +44264,13 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U50" s="36" t="s">
+        <v>2417</v>
+      </c>
+      <c r="V50" s="36" t="s">
+        <v>2418</v>
+      </c>
+      <c r="W50" s="36" t="s">
         <v>2419</v>
-      </c>
-      <c r="V50" s="36" t="s">
-        <v>2420</v>
-      </c>
-      <c r="W50" s="36" t="s">
-        <v>2421</v>
       </c>
       <c r="X50" s="36" t="s">
         <v>2293</v>
@@ -44302,13 +44300,13 @@
         <v>1861</v>
       </c>
       <c r="V51" s="36" t="s">
+        <v>2421</v>
+      </c>
+      <c r="W51" s="36" t="s">
         <v>2423</v>
       </c>
-      <c r="W51" s="36" t="s">
-        <v>2425</v>
-      </c>
       <c r="X51" s="36" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="Y51" s="36" t="s">
         <v>2200</v>
@@ -44600,13 +44598,13 @@
         <v>1861</v>
       </c>
       <c r="V65" s="36" t="s">
+        <v>2421</v>
+      </c>
+      <c r="W65" s="36" t="s">
         <v>2423</v>
       </c>
-      <c r="W65" s="36" t="s">
-        <v>2425</v>
-      </c>
       <c r="X65" s="36" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="Y65" s="36" t="s">
         <v>2200</v>
@@ -44684,10 +44682,10 @@
         <v>2299</v>
       </c>
       <c r="V69" s="38" t="s">
-        <v>2574</v>
+        <v>2572</v>
       </c>
       <c r="W69" s="38" t="s">
-        <v>2571</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="70" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -44761,7 +44759,7 @@
         <v>1573</v>
       </c>
       <c r="D73" t="s">
-        <v>2688</v>
+        <v>2686</v>
       </c>
       <c r="K73" t="s">
         <v>1432</v>
@@ -44792,7 +44790,7 @@
         <v>{szContent="前线据点之争已经打响，争夺正式开始，沙盘地图（CTRL + M）绘有详细战略意图，谁将称霸中原，我们拭目以待！\n",szNote="据点攻防·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime=10,key="阵营活动",},},},</v>
       </c>
       <c r="U74" t="s">
-        <v>2623</v>
+        <v>2621</v>
       </c>
     </row>
     <row r="75" spans="1:26" x14ac:dyDescent="0.15">
@@ -44812,7 +44810,7 @@
     </row>
     <row r="76" spans="1:26" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A76" s="36" t="s">
-        <v>2687</v>
+        <v>2685</v>
       </c>
       <c r="B76" s="36">
         <v>-20</v>
@@ -44840,13 +44838,13 @@
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U77" s="36" t="s">
+        <v>2425</v>
+      </c>
+      <c r="V77" s="36" t="s">
+        <v>2426</v>
+      </c>
+      <c r="W77" s="36" t="s">
         <v>2427</v>
-      </c>
-      <c r="V77" s="36" t="s">
-        <v>2428</v>
-      </c>
-      <c r="W77" s="36" t="s">
-        <v>2429</v>
       </c>
       <c r="X77" s="36" t="s">
         <v>1771</v>
@@ -44924,7 +44922,7 @@
         <v>{szContent="本场攻防“奇袭场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="奇袭场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2402,nFrame=4,szName="奇袭场·平手",nTime=57,nRefresh=5,key="大攻防·奇袭场",},},},</v>
       </c>
       <c r="U82" s="36" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="83" spans="1:30" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -44942,7 +44940,7 @@
         <v>{szContent="本场攻防“主战场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="主战场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="主战场·平手",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U83" s="36" t="s">
-        <v>2402</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="84" spans="1:30" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -44966,19 +44964,19 @@
         <v>{szContent="^本场攻防“([主战奇袭场]+)”已结束，([浩气盟恶人谷]+)[侠士们众志成城和，]-([大完险胜]+)([浩气盟恶人谷]+)[！，]+",szNote="{$1}·{$2}·{$3}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,szName="大攻防·奇袭场",nTime=-2,nRefresh=10,key="大攻防·奇袭场",},{nClass=20,nIcon=13,szName="大攻防·主战场",nTime=-2,nRefresh=10,key="大攻防·主战场",},{nClass=20,nIcon=13,szName="大攻防·{$1}",nTime=-2,key="大攻防·{$1}",},{nClass=20,nIcon=2402,nFrame=4,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U84" s="36" t="s">
-        <v>2512</v>
+        <v>2510</v>
       </c>
       <c r="V84" s="36" t="s">
-        <v>2513</v>
+        <v>2511</v>
       </c>
       <c r="W84" s="36" t="s">
         <v>2187</v>
       </c>
       <c r="X84" s="36" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
       <c r="Y84" s="36" t="s">
-        <v>2398</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="85" spans="1:30" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -45023,13 +45021,13 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U86" s="36" t="s">
+        <v>2417</v>
+      </c>
+      <c r="V86" s="36" t="s">
+        <v>2418</v>
+      </c>
+      <c r="W86" s="36" t="s">
         <v>2419</v>
-      </c>
-      <c r="V86" s="36" t="s">
-        <v>2420</v>
-      </c>
-      <c r="W86" s="36" t="s">
-        <v>2421</v>
       </c>
       <c r="X86" s="36" t="s">
         <v>2293</v>
@@ -45059,13 +45057,13 @@
         <v>1861</v>
       </c>
       <c r="V87" s="36" t="s">
+        <v>2421</v>
+      </c>
+      <c r="W87" s="36" t="s">
         <v>2423</v>
       </c>
-      <c r="W87" s="36" t="s">
-        <v>2425</v>
-      </c>
       <c r="X87" s="36" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="Y87" s="36" t="s">
         <v>2200</v>
@@ -45234,13 +45232,13 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·恶人大旗",},</v>
       </c>
       <c r="X95" s="36" t="s">
+        <v>2421</v>
+      </c>
+      <c r="Y95" s="36" t="s">
         <v>2423</v>
       </c>
-      <c r="Y95" s="36" t="s">
-        <v>2425</v>
-      </c>
       <c r="Z95" s="36" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="AA95" s="36" t="s">
         <v>2232</v>
@@ -45259,7 +45257,7 @@
     </row>
     <row r="96" spans="1:30" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C96" s="36" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="D96" s="36" t="s">
         <v>1820</v>
@@ -45275,16 +45273,16 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="武王城·大旗重置",nTime=-2,nRefresh=7200,key="武王城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【武王城】大旗重置",nTime=180,nRefresh=7200,key="武王城·大旗重置",},},},</v>
       </c>
       <c r="U96" s="36" t="s">
-        <v>2451</v>
+        <v>2449</v>
       </c>
       <c r="V96" s="36" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="W96" s="36" t="s">
         <v>1898</v>
       </c>
       <c r="X96" s="36" t="s">
-        <v>2452</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="97" spans="1:34" s="36" customFormat="1" x14ac:dyDescent="0.15">
@@ -45382,13 +45380,13 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·恶人大旗",},</v>
       </c>
       <c r="X101" s="36" t="s">
+        <v>2421</v>
+      </c>
+      <c r="Y101" s="36" t="s">
         <v>2423</v>
       </c>
-      <c r="Y101" s="36" t="s">
-        <v>2425</v>
-      </c>
       <c r="Z101" s="36" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="AA101" s="36" t="s">
         <v>2232</v>
@@ -45423,10 +45421,10 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凛风堡·大旗重置",nTime=-2,nRefresh=7200,key="凛风堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凛风堡】大旗重置",nTime=180,nRefresh=7200,key="凛风堡·大旗重置",},},},</v>
       </c>
       <c r="U102" s="36" t="s">
-        <v>2450</v>
+        <v>2448</v>
       </c>
       <c r="V102" s="36" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="W102" s="36" t="s">
         <v>1898</v>
@@ -45544,13 +45542,13 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·恶人大旗",},</v>
       </c>
       <c r="Z107" s="36" t="s">
+        <v>2420</v>
+      </c>
+      <c r="AA107" s="36" t="s">
         <v>2422</v>
       </c>
-      <c r="AA107" s="36" t="s">
-        <v>2424</v>
-      </c>
       <c r="AB107" s="36" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="AC107" s="36" t="s">
         <v>2232</v>
@@ -45593,13 +45591,13 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="盘龙坞·大旗重置",nTime=-2,nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=1465,szName="逐鹿坪·大旗重置",nTime=-2,nRefresh=7200,key="逐鹿坪·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【盘龙坞】大旗重置",nTime=180,nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【逐鹿坪】大旗重置",nTime=180,nRefresh=7200,key="逐鹿坪·大旗重置",},},},</v>
       </c>
       <c r="U108" s="36" t="s">
-        <v>2465</v>
+        <v>2463</v>
       </c>
       <c r="V108" s="36" t="s">
-        <v>2478</v>
+        <v>2476</v>
       </c>
       <c r="W108" s="36" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="X108" s="36" t="s">
         <v>1897</v>
@@ -45608,7 +45606,7 @@
         <v>1870</v>
       </c>
       <c r="Z108" s="36" t="s">
-        <v>2453</v>
+        <v>2451</v>
       </c>
       <c r="AA108" s="36"/>
     </row>
@@ -45669,13 +45667,13 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·恶人大旗",},</v>
       </c>
       <c r="Z110" s="36" t="s">
+        <v>2420</v>
+      </c>
+      <c r="AA110" s="36" t="s">
         <v>2422</v>
       </c>
-      <c r="AA110" s="36" t="s">
-        <v>2424</v>
-      </c>
       <c r="AB110" s="36" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="AC110" s="36" t="s">
         <v>2232</v>
@@ -45718,13 +45716,13 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="龙门镇·大旗重置",nTime=-2,nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=1465,szName="飞沙关·大旗重置",nTime=-2,nRefresh=7200,key="飞沙关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【龙门镇】大旗重置",nTime=180,nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【飞沙关】大旗重置",nTime=180,nRefresh=7200,key="飞沙关·大旗重置",},},},</v>
       </c>
       <c r="U111" s="36" t="s">
-        <v>2466</v>
+        <v>2464</v>
       </c>
       <c r="V111" s="36" t="s">
-        <v>2479</v>
+        <v>2477</v>
       </c>
       <c r="W111" s="36" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="X111" s="36" t="s">
         <v>1897</v>
@@ -45733,7 +45731,7 @@
         <v>1879</v>
       </c>
       <c r="Z111" s="36" t="s">
-        <v>2454</v>
+        <v>2452</v>
       </c>
       <c r="AA111" s="36"/>
     </row>
@@ -45794,13 +45792,13 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},</v>
       </c>
       <c r="Z113" s="36" t="s">
+        <v>2420</v>
+      </c>
+      <c r="AA113" s="36" t="s">
         <v>2422</v>
       </c>
-      <c r="AA113" s="36" t="s">
-        <v>2424</v>
-      </c>
       <c r="AB113" s="36" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="AC113" s="36" t="s">
         <v>2232</v>
@@ -45843,13 +45841,13 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="红莲岗·大旗重置",nTime=-2,nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=1465,szName="秋雨堡·大旗重置",nTime=-2,nRefresh=7200,key="秋雨堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【红莲岗】大旗重置",nTime=180,nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【秋雨堡】大旗重置",nTime=180,nRefresh=7200,key="秋雨堡·大旗重置",},},},</v>
       </c>
       <c r="U114" s="36" t="s">
-        <v>2467</v>
+        <v>2465</v>
       </c>
       <c r="V114" s="36" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
       <c r="W114" s="36" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="X114" s="36" t="s">
         <v>1897</v>
@@ -45858,7 +45856,7 @@
         <v>1881</v>
       </c>
       <c r="Z114" s="36" t="s">
-        <v>2455</v>
+        <v>2453</v>
       </c>
       <c r="AA114" s="36"/>
     </row>
@@ -45919,13 +45917,13 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·恶人大旗",},</v>
       </c>
       <c r="Z116" s="36" t="s">
+        <v>2420</v>
+      </c>
+      <c r="AA116" s="36" t="s">
         <v>2422</v>
       </c>
-      <c r="AA116" s="36" t="s">
-        <v>2424</v>
-      </c>
       <c r="AB116" s="36" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="AC116" s="36" t="s">
         <v>2232</v>
@@ -45968,13 +45966,13 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="金门关·大旗重置",nTime=-2,nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=1465,szName="青云坞·大旗重置",nTime=-2,nRefresh=7200,key="青云坞·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【金门关】大旗重置",nTime=180,nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【青云坞】大旗重置",nTime=180,nRefresh=7200,key="青云坞·大旗重置",},},},</v>
       </c>
       <c r="U117" s="36" t="s">
-        <v>2468</v>
+        <v>2466</v>
       </c>
       <c r="V117" s="36" t="s">
-        <v>2481</v>
+        <v>2479</v>
       </c>
       <c r="W117" s="36" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="X117" s="36" t="s">
         <v>1897</v>
@@ -45983,7 +45981,7 @@
         <v>1882</v>
       </c>
       <c r="Z117" s="36" t="s">
-        <v>2456</v>
+        <v>2454</v>
       </c>
       <c r="AA117" s="36"/>
     </row>
@@ -46044,13 +46042,13 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·恶人大旗",},</v>
       </c>
       <c r="Z119" s="36" t="s">
+        <v>2420</v>
+      </c>
+      <c r="AA119" s="36" t="s">
         <v>2422</v>
       </c>
-      <c r="AA119" s="36" t="s">
-        <v>2424</v>
-      </c>
       <c r="AB119" s="36" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="AC119" s="36" t="s">
         <v>2232</v>
@@ -46093,13 +46091,13 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="激流坞·大旗重置",nTime=-2,nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=1465,szName="不空关·大旗重置",nTime=-2,nRefresh=7200,key="不空关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【激流坞】大旗重置",nTime=180,nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【不空关】大旗重置",nTime=180,nRefresh=7200,key="不空关·大旗重置",},},},</v>
       </c>
       <c r="U120" s="36" t="s">
-        <v>2469</v>
+        <v>2467</v>
       </c>
       <c r="V120" s="36" t="s">
-        <v>2482</v>
+        <v>2480</v>
       </c>
       <c r="W120" s="36" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="X120" s="36" t="s">
         <v>1897</v>
@@ -46108,7 +46106,7 @@
         <v>1884</v>
       </c>
       <c r="Z120" s="36" t="s">
-        <v>2457</v>
+        <v>2455</v>
       </c>
       <c r="AA120" s="36"/>
     </row>
@@ -46169,13 +46167,13 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·恶人大旗",},</v>
       </c>
       <c r="Z122" s="36" t="s">
+        <v>2420</v>
+      </c>
+      <c r="AA122" s="36" t="s">
         <v>2422</v>
       </c>
-      <c r="AA122" s="36" t="s">
-        <v>2424</v>
-      </c>
       <c r="AB122" s="36" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="AC122" s="36" t="s">
         <v>2232</v>
@@ -46218,13 +46216,13 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="日月崖·大旗重置",nTime=-2,nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=1465,szName="卧龙坡·大旗重置",nTime=-2,nRefresh=7200,key="卧龙坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【日月崖】大旗重置",nTime=180,nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【卧龙坡】大旗重置",nTime=180,nRefresh=7200,key="卧龙坡·大旗重置",},},},</v>
       </c>
       <c r="U123" s="36" t="s">
-        <v>2470</v>
+        <v>2468</v>
       </c>
       <c r="V123" s="36" t="s">
-        <v>2483</v>
+        <v>2481</v>
       </c>
       <c r="W123" s="36" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="X123" s="36" t="s">
         <v>1897</v>
@@ -46233,7 +46231,7 @@
         <v>1886</v>
       </c>
       <c r="Z123" s="36" t="s">
-        <v>2458</v>
+        <v>2456</v>
       </c>
       <c r="AA123" s="36"/>
     </row>
@@ -46294,13 +46292,13 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·恶人大旗",},</v>
       </c>
       <c r="Z125" s="36" t="s">
+        <v>2420</v>
+      </c>
+      <c r="AA125" s="36" t="s">
         <v>2422</v>
       </c>
-      <c r="AA125" s="36" t="s">
-        <v>2424</v>
-      </c>
       <c r="AB125" s="36" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="AC125" s="36" t="s">
         <v>2232</v>
@@ -46343,13 +46341,13 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="霜戈堡·大旗重置",nTime=-2,nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=1465,szName="澜沧城·大旗重置",nTime=-2,nRefresh=7200,key="澜沧城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【霜戈堡】大旗重置",nTime=180,nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【澜沧城】大旗重置",nTime=180,nRefresh=7200,key="澜沧城·大旗重置",},},},</v>
       </c>
       <c r="U126" s="36" t="s">
-        <v>2471</v>
+        <v>2469</v>
       </c>
       <c r="V126" s="36" t="s">
-        <v>2484</v>
+        <v>2482</v>
       </c>
       <c r="W126" s="36" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="X126" s="36" t="s">
         <v>1897</v>
@@ -46358,7 +46356,7 @@
         <v>1888</v>
       </c>
       <c r="Z126" s="36" t="s">
-        <v>2459</v>
+        <v>2457</v>
       </c>
       <c r="AA126" s="36"/>
     </row>
@@ -46419,13 +46417,13 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·恶人大旗",},</v>
       </c>
       <c r="Z128" s="36" t="s">
+        <v>2420</v>
+      </c>
+      <c r="AA128" s="36" t="s">
         <v>2422</v>
       </c>
-      <c r="AA128" s="36" t="s">
-        <v>2424</v>
-      </c>
       <c r="AB128" s="36" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="AC128" s="36" t="s">
         <v>2232</v>
@@ -46468,13 +46466,13 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="神池岭·大旗重置",nTime=-2,nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=1465,szName="烈日岗·大旗重置",nTime=-2,nRefresh=7200,key="烈日岗·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【神池岭】大旗重置",nTime=180,nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【烈日岗】大旗重置",nTime=180,nRefresh=7200,key="烈日岗·大旗重置",},},},</v>
       </c>
       <c r="U129" s="36" t="s">
-        <v>2472</v>
+        <v>2470</v>
       </c>
       <c r="V129" s="36" t="s">
-        <v>2485</v>
+        <v>2483</v>
       </c>
       <c r="W129" s="36" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="X129" s="36" t="s">
         <v>1897</v>
@@ -46483,7 +46481,7 @@
         <v>1890</v>
       </c>
       <c r="Z129" s="36" t="s">
-        <v>2460</v>
+        <v>2458</v>
       </c>
       <c r="AA129" s="36"/>
     </row>
@@ -46544,13 +46542,13 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},</v>
       </c>
       <c r="Z131" s="36" t="s">
+        <v>2420</v>
+      </c>
+      <c r="AA131" s="36" t="s">
         <v>2422</v>
       </c>
-      <c r="AA131" s="36" t="s">
-        <v>2424</v>
-      </c>
       <c r="AB131" s="36" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="AC131" s="36" t="s">
         <v>2232</v>
@@ -46593,13 +46591,13 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凤鸣堡·大旗重置",nTime=-2,nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=1465,szName="惊虬谷·大旗重置",nTime=-2,nRefresh=7200,key="惊虬谷·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凤鸣堡】大旗重置",nTime=180,nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【惊虬谷】大旗重置",nTime=180,nRefresh=7200,key="惊虬谷·大旗重置",},},},</v>
       </c>
       <c r="U132" s="36" t="s">
-        <v>2473</v>
+        <v>2471</v>
       </c>
       <c r="V132" s="36" t="s">
-        <v>2486</v>
+        <v>2484</v>
       </c>
       <c r="W132" s="36" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="X132" s="36" t="s">
         <v>1897</v>
@@ -46608,7 +46606,7 @@
         <v>1892</v>
       </c>
       <c r="Z132" s="36" t="s">
-        <v>2461</v>
+        <v>2459</v>
       </c>
       <c r="AA132" s="36"/>
     </row>
@@ -46669,13 +46667,13 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·恶人大旗",},</v>
       </c>
       <c r="Z134" s="36" t="s">
+        <v>2420</v>
+      </c>
+      <c r="AA134" s="36" t="s">
         <v>2422</v>
       </c>
-      <c r="AA134" s="36" t="s">
-        <v>2424</v>
-      </c>
       <c r="AB134" s="36" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="AC134" s="36" t="s">
         <v>2232</v>
@@ -46718,13 +46716,13 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="大理山城·大旗重置",nTime=-2,nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=1465,szName="千岩关·大旗重置",nTime=-2,nRefresh=7200,key="千岩关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【大理山城】大旗重置",nTime=180,nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【千岩关】大旗重置",nTime=180,nRefresh=7200,key="千岩关·大旗重置",},},},</v>
       </c>
       <c r="U135" s="36" t="s">
-        <v>2474</v>
+        <v>2472</v>
       </c>
       <c r="V135" s="36" t="s">
-        <v>2487</v>
+        <v>2485</v>
       </c>
       <c r="W135" s="36" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="X135" s="36" t="s">
         <v>1897</v>
@@ -46733,7 +46731,7 @@
         <v>1894</v>
       </c>
       <c r="Z135" s="36" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="AA135" s="36"/>
     </row>
@@ -46794,13 +46792,13 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·恶人大旗",},</v>
       </c>
       <c r="Z137" s="36" t="s">
+        <v>2420</v>
+      </c>
+      <c r="AA137" s="36" t="s">
         <v>2422</v>
       </c>
-      <c r="AA137" s="36" t="s">
-        <v>2424</v>
-      </c>
       <c r="AB137" s="36" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="AC137" s="36" t="s">
         <v>2232</v>
@@ -46843,13 +46841,13 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="枫湖寨·大旗重置",nTime=-2,nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=1465,szName="啖杏林·大旗重置",nTime=-2,nRefresh=7200,key="啖杏林·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【枫湖寨】大旗重置",nTime=180,nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【啖杏林】大旗重置",nTime=180,nRefresh=7200,key="啖杏林·大旗重置",},},},</v>
       </c>
       <c r="U138" s="36" t="s">
-        <v>2475</v>
+        <v>2473</v>
       </c>
       <c r="V138" s="36" t="s">
-        <v>2488</v>
+        <v>2486</v>
       </c>
       <c r="W138" s="36" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="X138" s="36" t="s">
         <v>1897</v>
@@ -46858,7 +46856,7 @@
         <v>1896</v>
       </c>
       <c r="Z138" s="36" t="s">
-        <v>2463</v>
+        <v>2461</v>
       </c>
       <c r="AA138" s="36"/>
     </row>
@@ -46919,13 +46917,13 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·恶人大旗",},</v>
       </c>
       <c r="Z140" s="36" t="s">
+        <v>2420</v>
+      </c>
+      <c r="AA140" s="36" t="s">
         <v>2422</v>
       </c>
-      <c r="AA140" s="36" t="s">
-        <v>2424</v>
-      </c>
       <c r="AB140" s="36" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="AC140" s="36" t="s">
         <v>2232</v>
@@ -46968,13 +46966,13 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="扶风郡·大旗重置",nTime=-2,nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=1465,szName="世外坡·大旗重置",nTime=-2,nRefresh=7200,key="世外坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【扶风郡】大旗重置",nTime=180,nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【世外坡】大旗重置",nTime=180,nRefresh=7200,key="世外坡·大旗重置",},},},</v>
       </c>
       <c r="U141" s="36" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="V141" s="36" t="s">
-        <v>2489</v>
+        <v>2487</v>
       </c>
       <c r="W141" s="36" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="X141" s="36" t="s">
         <v>1898</v>
@@ -46983,7 +46981,7 @@
         <v>1868</v>
       </c>
       <c r="Z141" s="36" t="s">
-        <v>2464</v>
+        <v>2462</v>
       </c>
       <c r="AA141" s="36"/>
     </row>
@@ -47028,13 +47026,13 @@
         <v>1861</v>
       </c>
       <c r="V143" s="36" t="s">
+        <v>2420</v>
+      </c>
+      <c r="W143" s="36" t="s">
         <v>2422</v>
       </c>
-      <c r="W143" s="36" t="s">
-        <v>2424</v>
-      </c>
       <c r="X143" s="36" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="Y143" s="36" t="s">
         <v>2200</v>
@@ -47069,13 +47067,13 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime=180,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime=180,nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U144" s="36" t="s">
-        <v>2477</v>
+        <v>2475</v>
       </c>
       <c r="V144" s="36" t="s">
-        <v>2490</v>
+        <v>2488</v>
       </c>
       <c r="W144" s="36" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="X144" s="36" t="s">
         <v>1897</v>
@@ -47106,13 +47104,13 @@
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U145" s="36" t="s">
+        <v>2425</v>
+      </c>
+      <c r="V145" s="36" t="s">
+        <v>2426</v>
+      </c>
+      <c r="W145" s="36" t="s">
         <v>2427</v>
-      </c>
-      <c r="V145" s="36" t="s">
-        <v>2428</v>
-      </c>
-      <c r="W145" s="36" t="s">
-        <v>2429</v>
       </c>
       <c r="X145" s="36" t="s">
         <v>1771</v>
@@ -47160,13 +47158,13 @@
         <v>1861</v>
       </c>
       <c r="V147" t="s">
+        <v>2420</v>
+      </c>
+      <c r="W147" t="s">
         <v>2422</v>
       </c>
-      <c r="W147" t="s">
-        <v>2424</v>
-      </c>
       <c r="X147" s="36" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="Y147" s="36" t="s">
         <v>2200</v>
@@ -47196,13 +47194,13 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime=180,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime=180,nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U148" s="36" t="s">
-        <v>2477</v>
+        <v>2475</v>
       </c>
       <c r="V148" s="36" t="s">
-        <v>2490</v>
+        <v>2488</v>
       </c>
       <c r="W148" s="36" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="X148" s="36" t="s">
         <v>1897</v>
@@ -47251,13 +47249,13 @@
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U149" s="36" t="s">
+        <v>2425</v>
+      </c>
+      <c r="V149" s="36" t="s">
+        <v>2426</v>
+      </c>
+      <c r="W149" s="36" t="s">
         <v>2427</v>
-      </c>
-      <c r="V149" s="36" t="s">
-        <v>2428</v>
-      </c>
-      <c r="W149" s="36" t="s">
-        <v>2429</v>
       </c>
       <c r="X149" s="36" t="s">
         <v>1771</v>

--- a/阵营/大小攻防团队监控.xlsx
+++ b/阵营/大小攻防团队监控.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JX3\Game\JX3\bin\zhcn_hd\interface\MY#DATA\!all-users@zhcn_hd\userdata\team_mon\remote\打包\阵营\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{BA942829-7B57-44CB-B3BF-D6DB7E83190F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{84B6456B-19DD-404B-B03E-263A3422CF7E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据总控" sheetId="2" r:id="rId1"/>
@@ -10744,7 +10744,7 @@
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="21" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1775972827640,</v>
+        <v>nTimeStamp = 1775973048860,</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>34</v>

--- a/阵营/大小攻防团队监控.xlsx
+++ b/阵营/大小攻防团队监控.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JX3\Game\JX3\bin\zhcn_hd\interface\MY#DATA\!all-users@zhcn_hd\userdata\team_mon\remote\打包\阵营\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{07A321DB-61AD-4B8F-9705-D0E47E3002D2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{42B998F2-84EE-4C3E-88D5-4A651CB0AF3A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据总控" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="系统频道" sheetId="11" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">不利气劲!$A$1:$BY$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">不利气劲!$A$1:$BY$98</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">角色喊话!$A$1:$AV$192</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">系统角色!$A$1:$X$409</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">系统频道!$A$1:$BG$149</definedName>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="5796" uniqueCount="2744">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="5808" uniqueCount="2744">
   <si>
     <t>标识</t>
   </si>
@@ -10783,7 +10783,7 @@
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="21" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1777187204220,</v>
+        <v>nTimeStamp = 1777555632360,</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>34</v>
@@ -22072,7 +22072,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA35C877-1799-48AF-987C-71E994537D5C}">
-  <dimension ref="A1:BY97"/>
+  <dimension ref="A1:BY99"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="11" max="11" width="18.5" customWidth="1"/>
@@ -24745,94 +24745,94 @@
     </row>
     <row r="67" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C67" s="40">
-        <v>8807</v>
+        <v>12888</v>
       </c>
       <c r="D67" s="36">
         <v>1</v>
       </c>
       <c r="G67" s="36" t="s">
-        <v>1966</v>
+        <v>2732</v>
       </c>
       <c r="I67" s="36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K67" s="36" t="s">
-        <v>1967</v>
+        <v>2733</v>
       </c>
       <c r="L67" s="36" t="s">
-        <v>1964</v>
-      </c>
-      <c r="N67" s="36" t="s">
-        <v>1787</v>
-      </c>
-      <c r="O67" s="36">
-        <v>1</v>
-      </c>
-      <c r="P67" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q67" s="36">
-        <v>1</v>
+        <v>2737</v>
       </c>
       <c r="T67" s="36">
         <v>1</v>
       </c>
-      <c r="U67" s="36">
+      <c r="V67" s="36">
         <v>1</v>
       </c>
       <c r="AE67" s="36" t="s">
-        <v>1972</v>
+        <v>2734</v>
       </c>
       <c r="AF67" s="36">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="AG67" s="36" t="s">
-        <v>1955</v>
+        <v>2736</v>
+      </c>
+      <c r="AH67" s="36" t="s">
+        <v>2735</v>
       </c>
       <c r="AI67" s="36">
         <v>255</v>
       </c>
-      <c r="AJ67" s="36">
-        <v>1</v>
-      </c>
       <c r="AN67" s="36" t="str">
-        <f t="shared" ref="AN67:AN96" si="1">IF(B67&lt;&gt;"",IF(IFERROR(VALUE(C66),0)&lt;=0,"["&amp;B67&amp;"]={","},["&amp;B67&amp;"]={"),IF(C67&gt;0,"{dwID="&amp;C67&amp;","&amp;"nLevel="&amp;D67&amp;","&amp;IF(E67&gt;0,"nCount="&amp;E67&amp;",","")&amp;IF(F67&gt;0,"nIcon="&amp;F67&amp;",","")&amp;IF(G67&lt;&gt;"","szName="""&amp;G67&amp;""",","")&amp;IF(H67&gt;0,"bCheckLevel=true,","")&amp;IF(I67&gt;0,"nScrutinyType="&amp;I67&amp;",","")&amp;IF(J67&lt;&gt;"","tKungFu={"&amp;J67&amp;"},","")&amp;IF(K67&lt;&gt;"","szNote="""&amp;K67&amp;""",","")&amp;IF(L67&lt;&gt;"","col={"&amp;L67&amp;"},","")&amp;"[1]={"&amp;IF(M67&lt;&gt;"","tMark={"&amp;M67&amp;"},","")&amp;IF(N67&lt;&gt;"","szVoice="""&amp;N67&amp;""",","")&amp;IF(O67&gt;0,"bTeamChannel=true,","")&amp;IF(P67&gt;0,"bWhisperChannel=true,","")&amp;IF(Q67&gt;0,"bCenterAlarm=true,","")&amp;IF(R67&gt;0,"bScreenHead=true,","")&amp;IF(S67&gt;0,"bPartyBuffList=true,","")&amp;IF(T67&gt;0,"bBuffList=true,","")&amp;IF(U67&gt;0,"bFullScreen=true,","")&amp;IF(V67&gt;0,"bTeamPanel=true,","")&amp;IF(W67&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(X67&gt;0,"bTeamChannel=true,","")&amp;IF(Y67&gt;0,"bWhisperChannel=true,","")&amp;IF(Z67&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AA67&gt;0,AE67&lt;&gt;"",AF67&gt;0,AG67&lt;&gt;"",AH67&lt;&gt;"",AI67&gt;0,AJ67&gt;0,AK67&gt;0,AL67&gt;0),"aCataclysmBuff={{"&amp;IF(AA67&gt;0,"nStackNum="&amp;AA67&amp;",","")&amp;IF(AB67&lt;&gt;"","szStackOp="""&amp;AB67&amp;""",","")&amp;IF(AC67&gt;0,"bOnlyMine=true,","")&amp;IF(AD67&gt;0,"bOnlyMe=true,","")&amp;IF(AE67&lt;&gt;"","szReminder="""&amp;AE67&amp;""",","")&amp;IF(AF67&gt;0,"nPriority="&amp;AF67&amp;",","")&amp;IF(AG67&lt;&gt;"","col="""&amp;AG67&amp;""",","")&amp;IF(AH67&lt;&gt;"","colScreenHead="""&amp;AH67&amp;""",","")&amp;IF(AI67&gt;0,"nColAlpha="&amp;AI67&amp;",","")&amp;IF(AJ67&gt;0,"bAttention=true,","")&amp;IF(AK67&gt;0,"bCaution=true,","")&amp;IF(AL67&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AM67&amp;"},","")&amp;IF(AO67&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AO67:ZZ67)&amp;"},","")&amp;"},",IF(C66&gt;0,"},","")&amp;IF(AND(B67="",C67="",OR(B66&lt;&gt;"",C66&lt;&gt;"")),"},}","")))</f>
-        <v>{dwID=8807,nLevel=1,szName="注视",nScrutinyType=1,szNote="据点挂机",col={255,50,255,},[1]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bBuffList=true,bFullScreen=true,},[2]={},aCataclysmBuff={{szReminder="视",nPriority=2,col="#FF32FFFF",nColAlpha=255,bAttention=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=2,szName="挂机检测·首领注视",nTime=30,key="挂机检测",},},},</v>
-      </c>
-      <c r="AO67" s="36" t="s">
-        <v>2082</v>
+        <f t="shared" ref="AN67:AN98" si="1">IF(B67&lt;&gt;"",IF(IFERROR(VALUE(C66),0)&lt;=0,"["&amp;B67&amp;"]={","},["&amp;B67&amp;"]={"),IF(C67&gt;0,"{dwID="&amp;C67&amp;","&amp;"nLevel="&amp;D67&amp;","&amp;IF(E67&gt;0,"nCount="&amp;E67&amp;",","")&amp;IF(F67&gt;0,"nIcon="&amp;F67&amp;",","")&amp;IF(G67&lt;&gt;"","szName="""&amp;G67&amp;""",","")&amp;IF(H67&gt;0,"bCheckLevel=true,","")&amp;IF(I67&gt;0,"nScrutinyType="&amp;I67&amp;",","")&amp;IF(J67&lt;&gt;"","tKungFu={"&amp;J67&amp;"},","")&amp;IF(K67&lt;&gt;"","szNote="""&amp;K67&amp;""",","")&amp;IF(L67&lt;&gt;"","col={"&amp;L67&amp;"},","")&amp;"[1]={"&amp;IF(M67&lt;&gt;"","tMark={"&amp;M67&amp;"},","")&amp;IF(N67&lt;&gt;"","szVoice="""&amp;N67&amp;""",","")&amp;IF(O67&gt;0,"bTeamChannel=true,","")&amp;IF(P67&gt;0,"bWhisperChannel=true,","")&amp;IF(Q67&gt;0,"bCenterAlarm=true,","")&amp;IF(R67&gt;0,"bScreenHead=true,","")&amp;IF(S67&gt;0,"bPartyBuffList=true,","")&amp;IF(T67&gt;0,"bBuffList=true,","")&amp;IF(U67&gt;0,"bFullScreen=true,","")&amp;IF(V67&gt;0,"bTeamPanel=true,","")&amp;IF(W67&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(X67&gt;0,"bTeamChannel=true,","")&amp;IF(Y67&gt;0,"bWhisperChannel=true,","")&amp;IF(Z67&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AA67&gt;0,AE67&lt;&gt;"",AF67&gt;0,AG67&lt;&gt;"",AH67&lt;&gt;"",AI67&gt;0,AJ67&gt;0,AK67&gt;0,AL67&gt;0),"aCataclysmBuff={{"&amp;IF(AA67&gt;0,"nStackNum="&amp;AA67&amp;",","")&amp;IF(AB67&lt;&gt;"","szStackOp="""&amp;AB67&amp;""",","")&amp;IF(AC67&gt;0,"bOnlyMine=true,","")&amp;IF(AD67&gt;0,"bOnlyMe=true,","")&amp;IF(AE67&lt;&gt;"","szReminder="""&amp;AE67&amp;""",","")&amp;IF(AF67&gt;0,"nPriority="&amp;AF67&amp;",","")&amp;IF(AG67&lt;&gt;"","col="""&amp;AG67&amp;""",","")&amp;IF(AH67&lt;&gt;"","colScreenHead="""&amp;AH67&amp;""",","")&amp;IF(AI67&gt;0,"nColAlpha="&amp;AI67&amp;",","")&amp;IF(AJ67&gt;0,"bAttention=true,","")&amp;IF(AK67&gt;0,"bCaution=true,","")&amp;IF(AL67&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AM67&amp;"},","")&amp;IF(AO67&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AO67:ZZ67)&amp;"},","")&amp;"},",IF(C66&gt;0,"},","")&amp;IF(AND(B67="",C67="",OR(B66&lt;&gt;"",C66&lt;&gt;"")),"},}","")))</f>
+        <v>{dwID=12888,nLevel=1,szName="减疗",nScrutinyType=2,szNote="火圈每层减疗10%",col={170,170,170,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="疗",nPriority=29,col="#AAAAAAFF",colScreenHead="#AAAAAA",nColAlpha=255,},},},</v>
       </c>
     </row>
     <row r="68" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C68" s="40">
-        <v>7913</v>
+        <v>8807</v>
       </c>
       <c r="D68" s="36">
         <v>1</v>
       </c>
+      <c r="G68" s="36" t="s">
+        <v>1966</v>
+      </c>
       <c r="I68" s="36">
+        <v>1</v>
+      </c>
+      <c r="K68" s="36" t="s">
+        <v>1967</v>
+      </c>
+      <c r="L68" s="36" t="s">
+        <v>1964</v>
+      </c>
+      <c r="N68" s="36" t="s">
+        <v>1787</v>
+      </c>
+      <c r="O68" s="36">
+        <v>1</v>
+      </c>
+      <c r="P68" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q68" s="36">
+        <v>1</v>
+      </c>
+      <c r="T68" s="36">
+        <v>1</v>
+      </c>
+      <c r="U68" s="36">
+        <v>1</v>
+      </c>
+      <c r="AE68" s="36" t="s">
+        <v>1972</v>
+      </c>
+      <c r="AF68" s="36">
         <v>2</v>
       </c>
-      <c r="K68" s="36" t="s">
-        <v>1833</v>
-      </c>
-      <c r="L68" s="36" t="s">
-        <v>1830</v>
-      </c>
-      <c r="T68" s="36">
-        <v>1</v>
-      </c>
-      <c r="AE68" s="36" t="s">
-        <v>2374</v>
-      </c>
-      <c r="AF68" s="36">
-        <v>5</v>
-      </c>
       <c r="AG68" s="36" t="s">
-        <v>1832</v>
-      </c>
-      <c r="AH68" s="36" t="s">
-        <v>1831</v>
+        <v>1955</v>
       </c>
       <c r="AI68" s="36">
         <v>255</v>
@@ -24840,17 +24840,17 @@
       <c r="AJ68" s="36">
         <v>1</v>
       </c>
-      <c r="AL68" s="36">
-        <v>1</v>
-      </c>
       <c r="AN68" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7913,nLevel=1,nScrutinyType=2,szNote="意涌系统通用抗百分比回血",col={255,204,0,},[1]={bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="涌",nPriority=5,col="#FFCC00FF",colScreenHead="#FFCC00",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
+        <v>{dwID=8807,nLevel=1,szName="注视",nScrutinyType=1,szNote="据点挂机",col={255,50,255,},[1]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bBuffList=true,bFullScreen=true,},[2]={},aCataclysmBuff={{szReminder="视",nPriority=2,col="#FF32FFFF",nColAlpha=255,bAttention=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=2,szName="挂机检测·首领注视",nTime=30,key="挂机检测",},},},</v>
+      </c>
+      <c r="AO68" s="36" t="s">
+        <v>2082</v>
       </c>
     </row>
     <row r="69" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C69" s="40">
-        <v>7911</v>
+        <v>7913</v>
       </c>
       <c r="D69" s="36">
         <v>1</v>
@@ -24859,28 +24859,25 @@
         <v>2</v>
       </c>
       <c r="K69" s="36" t="s">
-        <v>1947</v>
+        <v>1833</v>
       </c>
       <c r="L69" s="36" t="s">
-        <v>1964</v>
-      </c>
-      <c r="R69" s="36">
-        <v>1</v>
+        <v>1830</v>
       </c>
       <c r="T69" s="36">
         <v>1</v>
       </c>
       <c r="AE69" s="36" t="s">
-        <v>1974</v>
+        <v>2374</v>
       </c>
       <c r="AF69" s="36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG69" s="36" t="s">
-        <v>1955</v>
+        <v>1832</v>
       </c>
       <c r="AH69" s="36" t="s">
-        <v>1956</v>
+        <v>1831</v>
       </c>
       <c r="AI69" s="36">
         <v>255</v>
@@ -24893,114 +24890,114 @@
       </c>
       <c r="AN69" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7911,nLevel=1,nScrutinyType=2,szNote="繁忙",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="忙",nPriority=4,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
+        <v>{dwID=7913,nLevel=1,nScrutinyType=2,szNote="意涌系统通用抗百分比回血",col={255,204,0,},[1]={bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="涌",nPriority=5,col="#FFCC00FF",colScreenHead="#FFCC00",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="70" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C70" s="40">
-        <v>7756</v>
+        <v>7911</v>
       </c>
       <c r="D70" s="36">
         <v>1</v>
       </c>
       <c r="I70" s="36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K70" s="36" t="s">
-        <v>2038</v>
+        <v>1947</v>
       </c>
       <c r="L70" s="36" t="s">
-        <v>1781</v>
+        <v>1964</v>
+      </c>
+      <c r="R70" s="36">
+        <v>1</v>
       </c>
       <c r="T70" s="36">
         <v>1</v>
       </c>
       <c r="AE70" s="36" t="s">
-        <v>2039</v>
+        <v>1974</v>
       </c>
       <c r="AF70" s="36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG70" s="36" t="s">
-        <v>2633</v>
+        <v>1955</v>
+      </c>
+      <c r="AH70" s="36" t="s">
+        <v>1956</v>
       </c>
       <c r="AI70" s="36">
-        <v>0</v>
+        <v>255</v>
+      </c>
+      <c r="AJ70" s="36">
+        <v>1</v>
+      </c>
+      <c r="AL70" s="36">
+        <v>1</v>
       </c>
       <c r="AN70" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7756,nLevel=1,nScrutinyType=1,szNote="燃火20s",col={255,255,0,},[1]={bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="火",nPriority=3,col="#00FFFF00",},},tCountdown={{nClass=1,nIcon=5399,nFrame=0,szName="增益·燃火·持续剩余",nTime=20,key="燃火",},{nClass=2,nIcon=13,szName="燃火",nTime=-1,key="燃火",},},},</v>
-      </c>
-      <c r="AO70" s="36" t="s">
-        <v>2079</v>
-      </c>
-      <c r="AP70" s="36" t="s">
-        <v>2080</v>
+        <v>{dwID=7911,nLevel=1,nScrutinyType=2,szNote="繁忙",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="忙",nPriority=4,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="71" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C71" s="40">
-        <v>7497</v>
+        <v>7756</v>
       </c>
       <c r="D71" s="36">
         <v>1</v>
       </c>
-      <c r="G71" s="36" t="s">
-        <v>2041</v>
-      </c>
       <c r="I71" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K71" s="36" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="L71" s="36" t="s">
         <v>1781</v>
       </c>
-      <c r="R71" s="36">
-        <v>1</v>
-      </c>
       <c r="T71" s="36">
         <v>1</v>
       </c>
       <c r="AE71" s="36" t="s">
-        <v>2042</v>
+        <v>2039</v>
       </c>
       <c r="AF71" s="36">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AG71" s="36" t="s">
-        <v>2043</v>
-      </c>
-      <c r="AH71" s="36" t="s">
-        <v>2044</v>
+        <v>2633</v>
       </c>
       <c r="AI71" s="36">
-        <v>255</v>
-      </c>
-      <c r="AL71" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN71" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7497,nLevel=1,szName="眩晕·抛掷",nScrutinyType=2,szNote="御城·抛掷",col={255,255,0,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="晕",nPriority=13,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
+        <v>{dwID=7756,nLevel=1,nScrutinyType=1,szNote="燃火20s",col={255,255,0,},[1]={bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="火",nPriority=3,col="#00FFFF00",},},tCountdown={{nClass=1,nIcon=5399,nFrame=0,szName="增益·燃火·持续剩余",nTime=20,key="燃火",},{nClass=2,nIcon=13,szName="燃火",nTime=-1,key="燃火",},},},</v>
+      </c>
+      <c r="AO71" s="36" t="s">
+        <v>2079</v>
+      </c>
+      <c r="AP71" s="36" t="s">
+        <v>2080</v>
       </c>
     </row>
     <row r="72" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C72" s="40">
-        <v>7504</v>
+        <v>7497</v>
       </c>
       <c r="D72" s="36">
         <v>1</v>
       </c>
       <c r="G72" s="36" t="s">
-        <v>2167</v>
+        <v>2041</v>
       </c>
       <c r="I72" s="36">
         <v>2</v>
       </c>
       <c r="K72" s="36" t="s">
-        <v>2166</v>
+        <v>2040</v>
       </c>
       <c r="L72" s="36" t="s">
         <v>1781</v>
@@ -25031,99 +25028,102 @@
       </c>
       <c r="AN72" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7504,nLevel=1,szName="眩晕·御城",nScrutinyType=2,szNote="御城·精准",col={255,255,0,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="晕",nPriority=13,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
+        <v>{dwID=7497,nLevel=1,szName="眩晕·抛掷",nScrutinyType=2,szNote="御城·抛掷",col={255,255,0,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="晕",nPriority=13,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="73" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C73" s="40">
-        <v>7503</v>
+        <v>7504</v>
       </c>
       <c r="D73" s="36">
         <v>1</v>
       </c>
       <c r="G73" s="36" t="s">
-        <v>2505</v>
+        <v>2167</v>
       </c>
       <c r="I73" s="36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K73" s="36" t="s">
-        <v>2506</v>
+        <v>2166</v>
       </c>
       <c r="L73" s="36" t="s">
-        <v>2361</v>
+        <v>1781</v>
+      </c>
+      <c r="R73" s="36">
+        <v>1</v>
       </c>
       <c r="T73" s="36">
         <v>1</v>
       </c>
-      <c r="V73" s="36">
-        <v>1</v>
+      <c r="AE73" s="36" t="s">
+        <v>2042</v>
       </c>
       <c r="AF73" s="36">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="AG73" s="36" t="s">
-        <v>2507</v>
+        <v>2043</v>
       </c>
       <c r="AH73" s="36" t="s">
-        <v>2364</v>
+        <v>2044</v>
       </c>
       <c r="AI73" s="36">
-        <v>170</v>
+        <v>255</v>
+      </c>
+      <c r="AL73" s="36">
+        <v>1</v>
       </c>
       <c r="AN73" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7503,nLevel=1,szName="减速·御城",nScrutinyType=1,szNote="御城·断股",col={31,63,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=37,col="#1F3FFFAA",colScreenHead="#1F3FFF",nColAlpha=170,},},},</v>
+        <v>{dwID=7504,nLevel=1,szName="眩晕·御城",nScrutinyType=2,szNote="御城·精准",col={255,255,0,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="晕",nPriority=13,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="74" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C74" s="40">
-        <v>4038</v>
+        <v>7503</v>
       </c>
       <c r="D74" s="36">
         <v>1</v>
       </c>
+      <c r="G74" s="36" t="s">
+        <v>2505</v>
+      </c>
       <c r="I74" s="36">
         <v>1</v>
       </c>
       <c r="K74" s="36" t="s">
-        <v>2365</v>
+        <v>2506</v>
       </c>
       <c r="L74" s="36" t="s">
         <v>2361</v>
       </c>
-      <c r="R74" s="36">
-        <v>1</v>
-      </c>
       <c r="T74" s="36">
         <v>1</v>
       </c>
-      <c r="AE74" s="36" t="s">
-        <v>2362</v>
+      <c r="V74" s="36">
+        <v>1</v>
       </c>
       <c r="AF74" s="36">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="AG74" s="36" t="s">
-        <v>2363</v>
+        <v>2507</v>
       </c>
       <c r="AH74" s="36" t="s">
         <v>2364</v>
       </c>
       <c r="AI74" s="36">
-        <v>255</v>
-      </c>
-      <c r="AL74" s="36">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="AN74" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=4038,nLevel=1,nScrutinyType=1,szNote="锁足·首领",col={31,63,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="锁",nPriority=15,col="#1F3FFFFF",colScreenHead="#1F3FFF",nColAlpha=255,bScreenHead=true,},},},</v>
+        <v>{dwID=7503,nLevel=1,szName="减速·御城",nScrutinyType=1,szNote="御城·断股",col={31,63,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=37,col="#1F3FFFAA",colScreenHead="#1F3FFF",nColAlpha=170,},},},</v>
       </c>
     </row>
     <row r="75" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C75" s="40">
-        <v>29007</v>
+        <v>4038</v>
       </c>
       <c r="D75" s="36">
         <v>1</v>
@@ -25132,583 +25132,580 @@
         <v>1</v>
       </c>
       <c r="K75" s="36" t="s">
-        <v>2160</v>
+        <v>2365</v>
       </c>
       <c r="L75" s="36" t="s">
-        <v>2386</v>
+        <v>2361</v>
+      </c>
+      <c r="R75" s="36">
+        <v>1</v>
+      </c>
+      <c r="T75" s="36">
+        <v>1</v>
+      </c>
+      <c r="AE75" s="36" t="s">
+        <v>2362</v>
+      </c>
+      <c r="AF75" s="36">
+        <v>15</v>
+      </c>
+      <c r="AG75" s="36" t="s">
+        <v>2363</v>
+      </c>
+      <c r="AH75" s="36" t="s">
+        <v>2364</v>
+      </c>
+      <c r="AI75" s="36">
+        <v>255</v>
+      </c>
+      <c r="AL75" s="36">
+        <v>1</v>
       </c>
       <c r="AN75" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=29007,nLevel=1,nScrutinyType=1,szNote="九素化生·伤害距离",col={128,238,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=1,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=1,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=1,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=1,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=1,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=1,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=1,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=1,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=1,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=1,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=1,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=1,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},{nClass=2,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=2,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=2,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=2,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=2,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=2,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=2,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=2,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=2,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=2,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=2,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=2,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=2,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
-      </c>
-      <c r="AO75" s="40" t="s">
-        <v>2405</v>
-      </c>
-      <c r="AP75" s="40" t="s">
-        <v>2404</v>
-      </c>
-      <c r="AQ75" s="38" t="s">
-        <v>2571</v>
-      </c>
-      <c r="AR75" s="38" t="s">
-        <v>2572</v>
+        <v>{dwID=4038,nLevel=1,nScrutinyType=1,szNote="锁足·首领",col={31,63,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="锁",nPriority=15,col="#1F3FFFFF",colScreenHead="#1F3FFF",nColAlpha=255,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="76" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C76" s="40">
-        <v>11561</v>
+        <v>29007</v>
       </c>
       <c r="D76" s="36">
         <v>1</v>
       </c>
-      <c r="G76" s="36" t="s">
-        <v>2582</v>
-      </c>
       <c r="I76" s="36">
         <v>1</v>
       </c>
       <c r="K76" s="36" t="s">
-        <v>2584</v>
+        <v>2160</v>
       </c>
       <c r="L76" s="36" t="s">
-        <v>2583</v>
+        <v>2386</v>
       </c>
       <c r="AN76" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=11561,nLevel=1,szName="据点内",nScrutinyType=1,szNote="判断是否在大旗附近",col={80,231,236,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=1272,nFrame=2,szName="据点大旗·旗手提示",nTime=-1,key="据点大旗·旗手提示",},},},</v>
-      </c>
-      <c r="AO76" s="36" t="s">
-        <v>2722</v>
-      </c>
-      <c r="AP76" s="39"/>
-      <c r="AQ76" s="39"/>
-      <c r="AR76" s="39"/>
+        <v>{dwID=29007,nLevel=1,nScrutinyType=1,szNote="九素化生·伤害距离",col={128,238,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=1,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=1,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=1,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=1,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=1,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=1,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=1,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=1,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=1,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=1,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=1,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=1,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},{nClass=2,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=2,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=2,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=2,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=2,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=2,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=2,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=2,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=2,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=2,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=2,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=2,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=2,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
+      </c>
+      <c r="AO76" s="40" t="s">
+        <v>2405</v>
+      </c>
+      <c r="AP76" s="40" t="s">
+        <v>2404</v>
+      </c>
+      <c r="AQ76" s="38" t="s">
+        <v>2571</v>
+      </c>
+      <c r="AR76" s="38" t="s">
+        <v>2572</v>
+      </c>
     </row>
     <row r="77" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C77" s="40">
-        <v>7723</v>
+        <v>11561</v>
       </c>
       <c r="D77" s="36">
         <v>1</v>
       </c>
+      <c r="G77" s="36" t="s">
+        <v>2582</v>
+      </c>
       <c r="I77" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K77" s="36" t="s">
-        <v>1797</v>
+        <v>2584</v>
       </c>
       <c r="L77" s="36" t="s">
-        <v>1667</v>
-      </c>
-      <c r="T77" s="36">
-        <v>1</v>
-      </c>
-      <c r="V77" s="36">
-        <v>1</v>
-      </c>
-      <c r="AF77" s="36">
-        <v>1</v>
-      </c>
-      <c r="AG77" s="36" t="s">
-        <v>2487</v>
-      </c>
-      <c r="AI77" s="36">
-        <v>170</v>
+        <v>2583</v>
       </c>
       <c r="AN77" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7723,nLevel=1,nScrutinyType=2,szNote="神机雷",col={255,255,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=1,col="#FFFFFFAA",nColAlpha=170,},},},</v>
-      </c>
+        <v>{dwID=11561,nLevel=1,szName="据点内",nScrutinyType=1,szNote="判断是否在大旗附近",col={80,231,236,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=1272,nFrame=2,szName="据点大旗·旗手提示",nTime=-1,key="据点大旗·旗手提示",},},},</v>
+      </c>
+      <c r="AO77" s="36" t="s">
+        <v>2722</v>
+      </c>
+      <c r="AP77" s="39"/>
+      <c r="AQ77" s="39"/>
+      <c r="AR77" s="39"/>
     </row>
     <row r="78" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="36" t="s">
-        <v>613</v>
-      </c>
-      <c r="B78" s="36">
-        <v>656</v>
+      <c r="C78" s="40">
+        <v>7723</v>
+      </c>
+      <c r="D78" s="36">
+        <v>1</v>
+      </c>
+      <c r="I78" s="36">
+        <v>2</v>
+      </c>
+      <c r="K78" s="36" t="s">
+        <v>1797</v>
+      </c>
+      <c r="L78" s="36" t="s">
+        <v>1667</v>
+      </c>
+      <c r="T78" s="36">
+        <v>1</v>
+      </c>
+      <c r="V78" s="36">
+        <v>1</v>
+      </c>
+      <c r="AF78" s="36">
+        <v>1</v>
+      </c>
+      <c r="AG78" s="36" t="s">
+        <v>2487</v>
+      </c>
+      <c r="AI78" s="36">
+        <v>170</v>
       </c>
       <c r="AN78" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>},[656]={</v>
+        <v>{dwID=7723,nLevel=1,nScrutinyType=2,szNote="神机雷",col={255,255,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=1,col="#FFFFFFAA",nColAlpha=170,},},},</v>
       </c>
     </row>
     <row r="79" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C79" s="40">
-        <v>11567</v>
-      </c>
-      <c r="D79" s="36">
-        <v>1</v>
-      </c>
-      <c r="F79" s="36">
-        <v>1245</v>
-      </c>
-      <c r="G79" s="36" t="s">
-        <v>2091</v>
-      </c>
-      <c r="I79" s="36">
-        <v>1</v>
-      </c>
-      <c r="K79" s="36" t="s">
-        <v>1953</v>
-      </c>
-      <c r="L79" s="36" t="s">
-        <v>1781</v>
+      <c r="A79" s="36" t="s">
+        <v>613</v>
+      </c>
+      <c r="B79" s="36">
+        <v>656</v>
       </c>
       <c r="AN79" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=11567,nLevel=1,nIcon=1245,szName="答对",nScrutinyType=1,szNote="回答奖励",col={255,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,nFrame=1,szName="答题验证·回答正确",nTime=5,key="挂机检测",},},},</v>
-      </c>
-      <c r="AO79" s="36" t="s">
-        <v>2083</v>
+        <v>},[656]={</v>
       </c>
     </row>
     <row r="80" spans="1:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C80" s="40">
-        <v>11559</v>
+        <v>11567</v>
       </c>
       <c r="D80" s="36">
         <v>1</v>
       </c>
       <c r="F80" s="36">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="G80" s="36" t="s">
-        <v>1957</v>
+        <v>2091</v>
       </c>
       <c r="I80" s="36">
         <v>1</v>
       </c>
       <c r="K80" s="36" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="L80" s="36" t="s">
-        <v>1964</v>
-      </c>
-      <c r="N80" s="36" t="s">
-        <v>1787</v>
-      </c>
-      <c r="O80" s="36">
-        <v>1</v>
-      </c>
-      <c r="P80" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q80" s="36">
-        <v>1</v>
-      </c>
-      <c r="R80" s="36">
-        <v>1</v>
-      </c>
-      <c r="T80" s="36">
-        <v>1</v>
-      </c>
-      <c r="U80" s="36">
-        <v>1</v>
-      </c>
-      <c r="V80" s="36">
-        <v>1</v>
-      </c>
-      <c r="AE80" s="36" t="s">
-        <v>1973</v>
-      </c>
-      <c r="AF80" s="36">
-        <v>3</v>
-      </c>
-      <c r="AG80" s="36" t="s">
-        <v>1955</v>
-      </c>
-      <c r="AH80" s="36" t="s">
-        <v>1956</v>
-      </c>
-      <c r="AI80" s="36">
-        <v>255</v>
-      </c>
-      <c r="AJ80" s="36">
-        <v>1</v>
-      </c>
-      <c r="AK80" s="36">
-        <v>1</v>
-      </c>
-      <c r="AL80" s="36">
-        <v>1</v>
+        <v>1781</v>
       </c>
       <c r="AN80" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=11559,nLevel=1,nIcon=1244,szName="答题",nScrutinyType=1,szNote="验证码答案",col={255,50,255,},[1]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bScreenHead=true,bBuffList=true,bFullScreen=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="题",nPriority=3,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bAttention=true,bCaution=true,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=1,szName="答题验证·剩余时间",nTime=30,key="挂机检测",},},},</v>
+        <v>{dwID=11567,nLevel=1,nIcon=1245,szName="答对",nScrutinyType=1,szNote="回答奖励",col={255,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,nFrame=1,szName="答题验证·回答正确",nTime=5,key="挂机检测",},},},</v>
       </c>
       <c r="AO80" s="36" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="81" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C81" s="40">
-        <v>11565</v>
+        <v>11559</v>
       </c>
       <c r="D81" s="36">
         <v>1</v>
       </c>
       <c r="F81" s="36">
-        <v>592</v>
+        <v>1244</v>
       </c>
       <c r="G81" s="36" t="s">
-        <v>2387</v>
+        <v>1957</v>
+      </c>
+      <c r="I81" s="36">
+        <v>1</v>
       </c>
       <c r="K81" s="36" t="s">
-        <v>2388</v>
+        <v>1954</v>
       </c>
       <c r="L81" s="36" t="s">
-        <v>2115</v>
+        <v>1964</v>
+      </c>
+      <c r="N81" s="36" t="s">
+        <v>1787</v>
+      </c>
+      <c r="O81" s="36">
+        <v>1</v>
+      </c>
+      <c r="P81" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q81" s="36">
+        <v>1</v>
       </c>
       <c r="R81" s="36">
+        <v>1</v>
+      </c>
+      <c r="T81" s="36">
+        <v>1</v>
+      </c>
+      <c r="U81" s="36">
+        <v>1</v>
+      </c>
+      <c r="V81" s="36">
+        <v>1</v>
+      </c>
+      <c r="AE81" s="36" t="s">
+        <v>1973</v>
+      </c>
+      <c r="AF81" s="36">
+        <v>3</v>
+      </c>
+      <c r="AG81" s="36" t="s">
+        <v>1955</v>
+      </c>
+      <c r="AH81" s="36" t="s">
+        <v>1956</v>
+      </c>
+      <c r="AI81" s="36">
+        <v>255</v>
+      </c>
+      <c r="AJ81" s="36">
+        <v>1</v>
+      </c>
+      <c r="AK81" s="36">
+        <v>1</v>
+      </c>
+      <c r="AL81" s="36">
         <v>1</v>
       </c>
       <c r="AN81" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=11565,nLevel=1,nIcon=592,szName="大旗手",szNote="大旗手检测",col={0,255,255,},[1]={bScreenHead=true,},[2]={},},</v>
+        <v>{dwID=11559,nLevel=1,nIcon=1244,szName="答题",nScrutinyType=1,szNote="验证码答案",col={255,50,255,},[1]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bScreenHead=true,bBuffList=true,bFullScreen=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="题",nPriority=3,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bAttention=true,bCaution=true,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=1,szName="答题验证·剩余时间",nTime=30,key="挂机检测",},},},</v>
+      </c>
+      <c r="AO81" s="36" t="s">
+        <v>2084</v>
       </c>
     </row>
     <row r="82" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C82" s="40">
-        <v>32813</v>
+        <v>11565</v>
       </c>
       <c r="D82" s="36">
         <v>1</v>
       </c>
       <c r="F82" s="36">
-        <v>16834</v>
+        <v>592</v>
       </c>
       <c r="G82" s="36" t="s">
-        <v>2699</v>
+        <v>2387</v>
       </c>
       <c r="K82" s="36" t="s">
-        <v>2694</v>
+        <v>2388</v>
       </c>
       <c r="L82" s="36" t="s">
-        <v>2696</v>
-      </c>
-      <c r="T82" s="36">
-        <v>1</v>
-      </c>
-      <c r="V82" s="36">
-        <v>1</v>
-      </c>
-      <c r="AE82" s="36" t="s">
-        <v>2695</v>
-      </c>
-      <c r="AF82" s="36">
-        <v>37</v>
-      </c>
-      <c r="AG82" s="36" t="s">
-        <v>2697</v>
-      </c>
-      <c r="AH82" s="36" t="s">
-        <v>2698</v>
-      </c>
-      <c r="AI82" s="36">
-        <v>255</v>
+        <v>2115</v>
+      </c>
+      <c r="R82" s="36">
+        <v>1</v>
       </c>
       <c r="AN82" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=32813,nLevel=1,nIcon=16834,szName="旗易伤",szNote="旗帜受损",col={255,153,204,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="损",nPriority=37,col="#FF99CCFF",colScreenHead="#FF99CC",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=0,key="大旗赛点·CD",},},},</v>
-      </c>
-      <c r="AO82" s="36" t="s">
-        <v>2705</v>
+        <v>{dwID=11565,nLevel=1,nIcon=592,szName="大旗手",szNote="大旗手检测",col={0,255,255,},[1]={bScreenHead=true,},[2]={},},</v>
       </c>
     </row>
     <row r="83" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C83" s="40">
-        <v>32812</v>
+        <v>32813</v>
       </c>
       <c r="D83" s="36">
         <v>1</v>
       </c>
       <c r="F83" s="36">
-        <v>3451</v>
+        <v>16834</v>
       </c>
       <c r="G83" s="36" t="s">
-        <v>2700</v>
+        <v>2699</v>
       </c>
       <c r="K83" s="36" t="s">
-        <v>2701</v>
+        <v>2694</v>
       </c>
       <c r="L83" s="36" t="s">
-        <v>2702</v>
+        <v>2696</v>
       </c>
       <c r="T83" s="36">
         <v>1</v>
+      </c>
+      <c r="V83" s="36">
+        <v>1</v>
+      </c>
+      <c r="AE83" s="36" t="s">
+        <v>2695</v>
+      </c>
+      <c r="AF83" s="36">
+        <v>37</v>
+      </c>
+      <c r="AG83" s="36" t="s">
+        <v>2697</v>
+      </c>
+      <c r="AH83" s="36" t="s">
+        <v>2698</v>
+      </c>
+      <c r="AI83" s="36">
+        <v>255</v>
       </c>
       <c r="AN83" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=32812,nLevel=1,nIcon=3451,szName="损CD",szNote="据点大旗赛点CD",col={255,50,50,},[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=1,key="大旗赛点·CD",},},},</v>
+        <v>{dwID=32813,nLevel=1,nIcon=16834,szName="旗易伤",szNote="旗帜受损",col={255,153,204,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="损",nPriority=37,col="#FF99CCFF",colScreenHead="#FF99CC",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=0,key="大旗赛点·CD",},},},</v>
       </c>
       <c r="AO83" s="36" t="s">
-        <v>2703</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="84" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C84" s="40">
-        <v>31381</v>
+        <v>32812</v>
       </c>
       <c r="D84" s="36">
         <v>1</v>
       </c>
+      <c r="F84" s="36">
+        <v>3451</v>
+      </c>
       <c r="G84" s="36" t="s">
-        <v>2559</v>
+        <v>2700</v>
       </c>
       <c r="K84" s="36" t="s">
-        <v>2385</v>
+        <v>2701</v>
       </c>
       <c r="L84" s="36" t="s">
-        <v>1964</v>
-      </c>
-      <c r="R84" s="36">
-        <v>1</v>
+        <v>2702</v>
       </c>
       <c r="T84" s="36">
-        <v>1</v>
-      </c>
-      <c r="AE84" s="36" t="s">
-        <v>2575</v>
-      </c>
-      <c r="AF84" s="36">
-        <v>11</v>
-      </c>
-      <c r="AG84" s="36" t="s">
-        <v>1955</v>
-      </c>
-      <c r="AH84" s="36" t="s">
-        <v>1956</v>
-      </c>
-      <c r="AI84" s="36">
-        <v>255</v>
-      </c>
-      <c r="AL84" s="36">
         <v>1</v>
       </c>
       <c r="AN84" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=31381,nLevel=1,szName="禁捡旗",szNote="无法拾取大旗",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="捡",nPriority=11,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=22928,nFrame=2,szName="【{$receiver}】·禁止捡旗",nTime="30,【{$receiver}】·禁止捡旗;32,【{$receiver}】·可以捡旗",nRefresh=1,key="经脉逆行·{$receiver}",},{nClass=2,nIcon=13,nFrame=2,szName="【{$receiver}】·可以捡旗",nTime=5,key="经脉逆行·{$receiver}",},},},</v>
+        <v>{dwID=32812,nLevel=1,nIcon=3451,szName="损CD",szNote="据点大旗赛点CD",col={255,50,50,},[1]={bBuffList=true,},[2]={},tCountdown={{nClass=1,nIcon=16834,nFrame=1,szName="大旗赛点·CD",nTime="60,大旗赛点·触发冷却;62,大旗赛点·解除冷却",nRefresh=1,key="大旗赛点·CD",},},},</v>
       </c>
       <c r="AO84" s="36" t="s">
-        <v>2719</v>
-      </c>
-      <c r="AP84" s="36" t="s">
-        <v>2391</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="85" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C85" s="40">
-        <v>8807</v>
+        <v>31381</v>
       </c>
       <c r="D85" s="36">
         <v>1</v>
       </c>
       <c r="G85" s="36" t="s">
-        <v>1966</v>
-      </c>
-      <c r="I85" s="36">
-        <v>1</v>
+        <v>2559</v>
       </c>
       <c r="K85" s="36" t="s">
-        <v>1967</v>
+        <v>2385</v>
       </c>
       <c r="L85" s="36" t="s">
         <v>1964</v>
       </c>
-      <c r="N85" s="36" t="s">
-        <v>1787</v>
-      </c>
-      <c r="O85" s="36">
-        <v>1</v>
-      </c>
-      <c r="P85" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q85" s="36">
+      <c r="R85" s="36">
         <v>1</v>
       </c>
       <c r="T85" s="36">
         <v>1</v>
       </c>
-      <c r="U85" s="36">
-        <v>1</v>
-      </c>
       <c r="AE85" s="36" t="s">
-        <v>1972</v>
+        <v>2575</v>
       </c>
       <c r="AF85" s="36">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AG85" s="36" t="s">
         <v>1955</v>
       </c>
+      <c r="AH85" s="36" t="s">
+        <v>1956</v>
+      </c>
       <c r="AI85" s="36">
         <v>255</v>
       </c>
-      <c r="AJ85" s="36">
+      <c r="AL85" s="36">
         <v>1</v>
       </c>
       <c r="AN85" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=8807,nLevel=1,szName="注视",nScrutinyType=1,szNote="据点挂机",col={255,50,255,},[1]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bBuffList=true,bFullScreen=true,},[2]={},aCataclysmBuff={{szReminder="视",nPriority=2,col="#FF32FFFF",nColAlpha=255,bAttention=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=2,szName="挂机检测·首领注视",nTime=30,key="挂机检测",},},},</v>
+        <v>{dwID=31381,nLevel=1,szName="禁捡旗",szNote="无法拾取大旗",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="捡",nPriority=11,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=22928,nFrame=2,szName="【{$receiver}】·禁止捡旗",nTime="30,【{$receiver}】·禁止捡旗;32,【{$receiver}】·可以捡旗",nRefresh=1,key="经脉逆行·{$receiver}",},{nClass=2,nIcon=13,nFrame=2,szName="【{$receiver}】·可以捡旗",nTime=5,key="经脉逆行·{$receiver}",},},},</v>
       </c>
       <c r="AO85" s="36" t="s">
-        <v>2082</v>
+        <v>2719</v>
+      </c>
+      <c r="AP85" s="36" t="s">
+        <v>2391</v>
       </c>
     </row>
     <row r="86" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C86" s="40">
-        <v>7913</v>
+        <v>12888</v>
       </c>
       <c r="D86" s="36">
         <v>1</v>
+      </c>
+      <c r="G86" s="36" t="s">
+        <v>2732</v>
       </c>
       <c r="I86" s="36">
         <v>2</v>
       </c>
       <c r="K86" s="36" t="s">
-        <v>1833</v>
+        <v>2733</v>
       </c>
       <c r="L86" s="36" t="s">
-        <v>1830</v>
+        <v>2737</v>
       </c>
       <c r="T86" s="36">
         <v>1</v>
       </c>
+      <c r="V86" s="36">
+        <v>1</v>
+      </c>
       <c r="AE86" s="36" t="s">
-        <v>2374</v>
+        <v>2734</v>
       </c>
       <c r="AF86" s="36">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="AG86" s="36" t="s">
-        <v>1832</v>
+        <v>2736</v>
       </c>
       <c r="AH86" s="36" t="s">
-        <v>1831</v>
+        <v>2735</v>
       </c>
       <c r="AI86" s="36">
         <v>255</v>
       </c>
-      <c r="AJ86" s="36">
-        <v>1</v>
-      </c>
-      <c r="AL86" s="36">
-        <v>1</v>
-      </c>
       <c r="AN86" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7913,nLevel=1,nScrutinyType=2,szNote="意涌系统通用抗百分比回血",col={255,204,0,},[1]={bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="涌",nPriority=5,col="#FFCC00FF",colScreenHead="#FFCC00",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
+        <v>{dwID=12888,nLevel=1,szName="减疗",nScrutinyType=2,szNote="火圈每层减疗10%",col={170,170,170,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="疗",nPriority=29,col="#AAAAAAFF",colScreenHead="#AAAAAA",nColAlpha=255,},},},</v>
       </c>
     </row>
     <row r="87" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C87" s="40">
-        <v>7911</v>
+        <v>8807</v>
       </c>
       <c r="D87" s="36">
         <v>1</v>
       </c>
+      <c r="G87" s="36" t="s">
+        <v>1966</v>
+      </c>
       <c r="I87" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K87" s="36" t="s">
-        <v>1947</v>
+        <v>1967</v>
       </c>
       <c r="L87" s="36" t="s">
         <v>1964</v>
       </c>
-      <c r="R87" s="36">
+      <c r="N87" s="36" t="s">
+        <v>1787</v>
+      </c>
+      <c r="O87" s="36">
+        <v>1</v>
+      </c>
+      <c r="P87" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q87" s="36">
         <v>1</v>
       </c>
       <c r="T87" s="36">
         <v>1</v>
       </c>
+      <c r="U87" s="36">
+        <v>1</v>
+      </c>
       <c r="AE87" s="36" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="AF87" s="36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG87" s="36" t="s">
         <v>1955</v>
       </c>
-      <c r="AH87" s="36" t="s">
-        <v>1956</v>
-      </c>
       <c r="AI87" s="36">
         <v>255</v>
       </c>
       <c r="AJ87" s="36">
         <v>1</v>
       </c>
-      <c r="AL87" s="36">
-        <v>1</v>
-      </c>
       <c r="AN87" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7911,nLevel=1,nScrutinyType=2,szNote="繁忙",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="忙",nPriority=4,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
+        <v>{dwID=8807,nLevel=1,szName="注视",nScrutinyType=1,szNote="据点挂机",col={255,50,255,},[1]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bBuffList=true,bFullScreen=true,},[2]={},aCataclysmBuff={{szReminder="视",nPriority=2,col="#FF32FFFF",nColAlpha=255,bAttention=true,},},tCountdown={{nClass=1,nIcon=13,nFrame=2,szName="挂机检测·首领注视",nTime=30,key="挂机检测",},},},</v>
+      </c>
+      <c r="AO87" s="36" t="s">
+        <v>2082</v>
       </c>
     </row>
     <row r="88" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C88" s="40">
-        <v>7756</v>
+        <v>7913</v>
       </c>
       <c r="D88" s="36">
         <v>1</v>
       </c>
       <c r="I88" s="36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K88" s="36" t="s">
-        <v>2038</v>
+        <v>1833</v>
       </c>
       <c r="L88" s="36" t="s">
-        <v>1781</v>
+        <v>1830</v>
       </c>
       <c r="T88" s="36">
         <v>1</v>
       </c>
       <c r="AE88" s="36" t="s">
-        <v>2039</v>
+        <v>2374</v>
       </c>
       <c r="AF88" s="36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG88" s="36" t="s">
-        <v>2633</v>
+        <v>1832</v>
+      </c>
+      <c r="AH88" s="36" t="s">
+        <v>1831</v>
       </c>
       <c r="AI88" s="36">
-        <v>0</v>
+        <v>255</v>
+      </c>
+      <c r="AJ88" s="36">
+        <v>1</v>
+      </c>
+      <c r="AL88" s="36">
+        <v>1</v>
       </c>
       <c r="AN88" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7756,nLevel=1,nScrutinyType=1,szNote="燃火20s",col={255,255,0,},[1]={bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="火",nPriority=3,col="#00FFFF00",},},tCountdown={{nClass=1,nIcon=5399,nFrame=0,szName="增益·燃火·持续剩余",nTime=20,key="燃火",},{nClass=2,nIcon=13,szName="燃火",nTime=-1,key="燃火",},},},</v>
-      </c>
-      <c r="AO88" s="36" t="s">
-        <v>2079</v>
-      </c>
-      <c r="AP88" s="36" t="s">
-        <v>2080</v>
+        <v>{dwID=7913,nLevel=1,nScrutinyType=2,szNote="意涌系统通用抗百分比回血",col={255,204,0,},[1]={bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="涌",nPriority=5,col="#FFCC00FF",colScreenHead="#FFCC00",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="89" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C89" s="40">
-        <v>7497</v>
+        <v>7911</v>
       </c>
       <c r="D89" s="36">
         <v>1</v>
-      </c>
-      <c r="G89" s="36" t="s">
-        <v>2041</v>
       </c>
       <c r="I89" s="36">
         <v>2</v>
       </c>
       <c r="K89" s="36" t="s">
-        <v>2040</v>
+        <v>1947</v>
       </c>
       <c r="L89" s="36" t="s">
-        <v>1781</v>
+        <v>1964</v>
       </c>
       <c r="R89" s="36">
         <v>1</v>
@@ -25717,133 +25714,139 @@
         <v>1</v>
       </c>
       <c r="AE89" s="36" t="s">
-        <v>2042</v>
+        <v>1974</v>
       </c>
       <c r="AF89" s="36">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AG89" s="36" t="s">
-        <v>2043</v>
+        <v>1955</v>
       </c>
       <c r="AH89" s="36" t="s">
-        <v>2044</v>
+        <v>1956</v>
       </c>
       <c r="AI89" s="36">
         <v>255</v>
       </c>
+      <c r="AJ89" s="36">
+        <v>1</v>
+      </c>
       <c r="AL89" s="36">
         <v>1</v>
       </c>
       <c r="AN89" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7497,nLevel=1,szName="眩晕·抛掷",nScrutinyType=2,szNote="御城·抛掷",col={255,255,0,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="晕",nPriority=13,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
+        <v>{dwID=7911,nLevel=1,nScrutinyType=2,szNote="繁忙",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="忙",nPriority=4,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bAttention=true,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="90" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C90" s="40">
-        <v>7504</v>
+        <v>7756</v>
       </c>
       <c r="D90" s="36">
         <v>1</v>
       </c>
-      <c r="G90" s="36" t="s">
-        <v>2167</v>
-      </c>
       <c r="I90" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K90" s="36" t="s">
-        <v>2166</v>
+        <v>2038</v>
       </c>
       <c r="L90" s="36" t="s">
         <v>1781</v>
       </c>
-      <c r="R90" s="36">
-        <v>1</v>
-      </c>
       <c r="T90" s="36">
         <v>1</v>
       </c>
       <c r="AE90" s="36" t="s">
-        <v>2042</v>
+        <v>2039</v>
       </c>
       <c r="AF90" s="36">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AG90" s="36" t="s">
-        <v>2043</v>
-      </c>
-      <c r="AH90" s="36" t="s">
-        <v>2044</v>
+        <v>2633</v>
       </c>
       <c r="AI90" s="36">
-        <v>255</v>
-      </c>
-      <c r="AL90" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN90" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7504,nLevel=1,szName="眩晕·御城",nScrutinyType=2,szNote="御城·精准",col={255,255,0,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="晕",nPriority=13,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
+        <v>{dwID=7756,nLevel=1,nScrutinyType=1,szNote="燃火20s",col={255,255,0,},[1]={bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="火",nPriority=3,col="#00FFFF00",},},tCountdown={{nClass=1,nIcon=5399,nFrame=0,szName="增益·燃火·持续剩余",nTime=20,key="燃火",},{nClass=2,nIcon=13,szName="燃火",nTime=-1,key="燃火",},},},</v>
+      </c>
+      <c r="AO90" s="36" t="s">
+        <v>2079</v>
+      </c>
+      <c r="AP90" s="36" t="s">
+        <v>2080</v>
       </c>
     </row>
     <row r="91" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C91" s="40">
-        <v>7503</v>
+        <v>7497</v>
       </c>
       <c r="D91" s="36">
         <v>1</v>
       </c>
       <c r="G91" s="36" t="s">
-        <v>2505</v>
+        <v>2041</v>
       </c>
       <c r="I91" s="36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K91" s="36" t="s">
-        <v>2506</v>
+        <v>2040</v>
       </c>
       <c r="L91" s="36" t="s">
-        <v>2361</v>
+        <v>1781</v>
+      </c>
+      <c r="R91" s="36">
+        <v>1</v>
       </c>
       <c r="T91" s="36">
         <v>1</v>
       </c>
-      <c r="V91" s="36">
-        <v>1</v>
+      <c r="AE91" s="36" t="s">
+        <v>2042</v>
       </c>
       <c r="AF91" s="36">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="AG91" s="36" t="s">
-        <v>2507</v>
+        <v>2043</v>
       </c>
       <c r="AH91" s="36" t="s">
-        <v>2364</v>
+        <v>2044</v>
       </c>
       <c r="AI91" s="36">
-        <v>170</v>
+        <v>255</v>
+      </c>
+      <c r="AL91" s="36">
+        <v>1</v>
       </c>
       <c r="AN91" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7503,nLevel=1,szName="减速·御城",nScrutinyType=1,szNote="御城·断股",col={31,63,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=37,col="#1F3FFFAA",colScreenHead="#1F3FFF",nColAlpha=170,},},},</v>
+        <v>{dwID=7497,nLevel=1,szName="眩晕·抛掷",nScrutinyType=2,szNote="御城·抛掷",col={255,255,0,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="晕",nPriority=13,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="92" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C92" s="40">
-        <v>4038</v>
+        <v>7504</v>
       </c>
       <c r="D92" s="36">
         <v>1</v>
       </c>
+      <c r="G92" s="36" t="s">
+        <v>2167</v>
+      </c>
       <c r="I92" s="36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K92" s="36" t="s">
-        <v>2365</v>
+        <v>2166</v>
       </c>
       <c r="L92" s="36" t="s">
-        <v>2361</v>
+        <v>1781</v>
       </c>
       <c r="R92" s="36">
         <v>1</v>
@@ -25852,16 +25855,16 @@
         <v>1</v>
       </c>
       <c r="AE92" s="36" t="s">
-        <v>2362</v>
+        <v>2042</v>
       </c>
       <c r="AF92" s="36">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG92" s="36" t="s">
-        <v>2363</v>
+        <v>2043</v>
       </c>
       <c r="AH92" s="36" t="s">
-        <v>2364</v>
+        <v>2044</v>
       </c>
       <c r="AI92" s="36">
         <v>255</v>
@@ -25871,119 +25874,206 @@
       </c>
       <c r="AN92" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=4038,nLevel=1,nScrutinyType=1,szNote="锁足·首领",col={31,63,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="锁",nPriority=15,col="#1F3FFFFF",colScreenHead="#1F3FFF",nColAlpha=255,bScreenHead=true,},},},</v>
+        <v>{dwID=7504,nLevel=1,szName="眩晕·御城",nScrutinyType=2,szNote="御城·精准",col={255,255,0,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="晕",nPriority=13,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="93" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C93" s="40">
-        <v>29007</v>
+        <v>7503</v>
       </c>
       <c r="D93" s="36">
         <v>1</v>
       </c>
+      <c r="G93" s="36" t="s">
+        <v>2505</v>
+      </c>
       <c r="I93" s="36">
         <v>1</v>
       </c>
       <c r="K93" s="36" t="s">
-        <v>2160</v>
+        <v>2506</v>
       </c>
       <c r="L93" s="36" t="s">
-        <v>2386</v>
+        <v>2361</v>
+      </c>
+      <c r="T93" s="36">
+        <v>1</v>
+      </c>
+      <c r="V93" s="36">
+        <v>1</v>
+      </c>
+      <c r="AF93" s="36">
+        <v>37</v>
+      </c>
+      <c r="AG93" s="36" t="s">
+        <v>2507</v>
+      </c>
+      <c r="AH93" s="36" t="s">
+        <v>2364</v>
+      </c>
+      <c r="AI93" s="36">
+        <v>170</v>
       </c>
       <c r="AN93" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=29007,nLevel=1,nScrutinyType=1,szNote="九素化生·伤害距离",col={128,238,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=1,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=1,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=1,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=1,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=1,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=1,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=1,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=1,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=1,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=1,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=1,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=1,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},{nClass=2,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=2,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=2,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=2,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=2,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=2,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=2,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=2,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=2,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=2,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=2,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=2,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=2,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
-      </c>
-      <c r="AO93" s="40" t="s">
-        <v>2405</v>
-      </c>
-      <c r="AP93" s="40" t="s">
-        <v>2404</v>
-      </c>
-      <c r="AQ93" s="38" t="s">
-        <v>2571</v>
-      </c>
-      <c r="AR93" s="38" t="s">
-        <v>2572</v>
+        <v>{dwID=7503,nLevel=1,szName="减速·御城",nScrutinyType=1,szNote="御城·断股",col={31,63,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=37,col="#1F3FFFAA",colScreenHead="#1F3FFF",nColAlpha=170,},},},</v>
       </c>
     </row>
     <row r="94" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C94" s="40">
-        <v>11561</v>
+        <v>4038</v>
       </c>
       <c r="D94" s="36">
         <v>1</v>
       </c>
-      <c r="G94" s="36" t="s">
-        <v>2582</v>
-      </c>
       <c r="I94" s="36">
         <v>1</v>
       </c>
       <c r="K94" s="36" t="s">
-        <v>2584</v>
+        <v>2365</v>
       </c>
       <c r="L94" s="36" t="s">
-        <v>2583</v>
+        <v>2361</v>
+      </c>
+      <c r="R94" s="36">
+        <v>1</v>
+      </c>
+      <c r="T94" s="36">
+        <v>1</v>
+      </c>
+      <c r="AE94" s="36" t="s">
+        <v>2362</v>
+      </c>
+      <c r="AF94" s="36">
+        <v>15</v>
+      </c>
+      <c r="AG94" s="36" t="s">
+        <v>2363</v>
+      </c>
+      <c r="AH94" s="36" t="s">
+        <v>2364</v>
+      </c>
+      <c r="AI94" s="36">
+        <v>255</v>
+      </c>
+      <c r="AL94" s="36">
+        <v>1</v>
       </c>
       <c r="AN94" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=11561,nLevel=1,szName="据点内",nScrutinyType=1,szNote="判断是否在大旗附近",col={80,231,236,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=1272,nFrame=2,szName="据点大旗·旗手提示",nTime=-1,key="据点大旗·旗手提示",},},},</v>
-      </c>
-      <c r="AO94" s="36" t="s">
-        <v>2722</v>
-      </c>
-      <c r="AP94" s="39"/>
-      <c r="AQ94" s="39"/>
-      <c r="AR94" s="39"/>
+        <v>{dwID=4038,nLevel=1,nScrutinyType=1,szNote="锁足·首领",col={31,63,255,},[1]={bScreenHead=true,bBuffList=true,},[2]={},aCataclysmBuff={{szReminder="锁",nPriority=15,col="#1F3FFFFF",colScreenHead="#1F3FFF",nColAlpha=255,bScreenHead=true,},},},</v>
+      </c>
     </row>
     <row r="95" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C95" s="40">
-        <v>7723</v>
+        <v>29007</v>
       </c>
       <c r="D95" s="36">
         <v>1</v>
       </c>
       <c r="I95" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K95" s="36" t="s">
-        <v>1797</v>
+        <v>2160</v>
       </c>
       <c r="L95" s="36" t="s">
-        <v>1667</v>
-      </c>
-      <c r="T95" s="36">
-        <v>1</v>
-      </c>
-      <c r="V95" s="36">
-        <v>1</v>
-      </c>
-      <c r="AF95" s="36">
-        <v>1</v>
-      </c>
-      <c r="AG95" s="36" t="s">
-        <v>2487</v>
-      </c>
-      <c r="AI95" s="36">
-        <v>170</v>
+        <v>2386</v>
       </c>
       <c r="AN95" s="36" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7723,nLevel=1,nScrutinyType=2,szNote="神机雷",col={255,255,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=1,col="#FFFFFFAA",nColAlpha=170,},},},</v>
-      </c>
-    </row>
-    <row r="96" spans="3:44" x14ac:dyDescent="0.15">
+        <v>{dwID=29007,nLevel=1,nScrutinyType=1,szNote="九素化生·伤害距离",col={128,238,255,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=1,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=1,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=1,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=1,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=1,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=1,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=1,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=1,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=1,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=1,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=1,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=1,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},{nClass=2,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=2,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=2,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=2,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=2,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=2,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=2,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=2,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=2,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=2,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=2,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=2,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=2,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
+      </c>
+      <c r="AO95" s="40" t="s">
+        <v>2405</v>
+      </c>
+      <c r="AP95" s="40" t="s">
+        <v>2404</v>
+      </c>
+      <c r="AQ95" s="38" t="s">
+        <v>2571</v>
+      </c>
+      <c r="AR95" s="38" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="96" spans="3:44" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C96" s="40">
+        <v>11561</v>
+      </c>
+      <c r="D96" s="36">
+        <v>1</v>
+      </c>
+      <c r="G96" s="36" t="s">
+        <v>2582</v>
+      </c>
+      <c r="I96" s="36">
+        <v>1</v>
+      </c>
+      <c r="K96" s="36" t="s">
+        <v>2584</v>
+      </c>
+      <c r="L96" s="36" t="s">
+        <v>2583</v>
+      </c>
       <c r="AN96" s="36" t="str">
         <f t="shared" si="1"/>
+        <v>{dwID=11561,nLevel=1,szName="据点内",nScrutinyType=1,szNote="判断是否在大旗附近",col={80,231,236,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=1272,nFrame=2,szName="据点大旗·旗手提示",nTime=-1,key="据点大旗·旗手提示",},},},</v>
+      </c>
+      <c r="AO96" s="36" t="s">
+        <v>2722</v>
+      </c>
+      <c r="AP96" s="39"/>
+      <c r="AQ96" s="39"/>
+      <c r="AR96" s="39"/>
+    </row>
+    <row r="97" spans="3:40" s="36" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C97" s="40">
+        <v>7723</v>
+      </c>
+      <c r="D97" s="36">
+        <v>1</v>
+      </c>
+      <c r="I97" s="36">
+        <v>2</v>
+      </c>
+      <c r="K97" s="36" t="s">
+        <v>1797</v>
+      </c>
+      <c r="L97" s="36" t="s">
+        <v>1667</v>
+      </c>
+      <c r="T97" s="36">
+        <v>1</v>
+      </c>
+      <c r="V97" s="36">
+        <v>1</v>
+      </c>
+      <c r="AF97" s="36">
+        <v>1</v>
+      </c>
+      <c r="AG97" s="36" t="s">
+        <v>2487</v>
+      </c>
+      <c r="AI97" s="36">
+        <v>170</v>
+      </c>
+      <c r="AN97" s="36" t="str">
+        <f t="shared" si="1"/>
+        <v>{dwID=7723,nLevel=1,nScrutinyType=2,szNote="神机雷",col={255,255,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=1,col="#FFFFFFAA",nColAlpha=170,},},},</v>
+      </c>
+    </row>
+    <row r="98" spans="3:40" x14ac:dyDescent="0.15">
+      <c r="AN98" s="36" t="str">
+        <f t="shared" si="1"/>
         <v>},},}</v>
       </c>
     </row>
-    <row r="97" spans="40:40" x14ac:dyDescent="0.15">
-      <c r="AN97" s="36"/>
+    <row r="99" spans="3:40" x14ac:dyDescent="0.15">
+      <c r="AN99" s="36"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BY96" xr:uid="{ABA792D9-52CC-4EDA-9BC4-CFEC1886BBBF}"/>
+  <autoFilter ref="A1:BY98" xr:uid="{ABA792D9-52CC-4EDA-9BC4-CFEC1886BBBF}"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/阵营/大小攻防团队监控.xlsx
+++ b/阵营/大小攻防团队监控.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="3"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据总控" sheetId="2" r:id="rId1"/>
@@ -5034,10 +5034,10 @@
     <t>屹立不倒</t>
   </si>
   <si>
-    <t>{nClass=8,nIcon=1537,nFrame=0,nTime="1,屹立不倒·{$sender}·正在释放;9.5,屹立不倒·{$sender}·50减伤;32.5,屹立不倒·{$sender}·释放剩余;40.5,屹立不倒·{$sender}·释放延迟",szName="屹立不倒",nRefresh=0,key="屹立不倒",},</t>
-  </si>
-  <si>
-    <t>{nClass=9,nIcon=1537,nFrame=0,nTime="9,屹立不倒·{$sender}·50减伤;31.5,屹立不倒·{$sender}·释放剩余;40,屹立不倒·{$sender}·释放延迟",szName="屹立不倒",nRefresh=1,key="屹立不倒",},</t>
+    <t>{nClass=8,nIcon=1537,nFrame=0,nTime="1,屹立不倒·{$sender}·正在释放;9.5,屹立不倒·{$sender}·50减伤;32.5,屹立不倒·{$sender}·释放剩余;40.5,屹立不倒·{$sender}·延迟释放;50,屹立不倒·{$sender}·随时释放",szName="屹立不倒",nRefresh=0,key="屹立不倒",},</t>
+  </si>
+  <si>
+    <t>{nClass=9,nIcon=1537,nFrame=0,nTime="9,屹立不倒·{$sender}·50减伤;31.5,屹立不倒·{$sender}·释放剩余;40,屹立不倒·{$sender}·延迟释放;50,屹立不倒·{$sender}·随时释放",szName="屹立不倒",nRefresh=1,key="屹立不倒",},</t>
   </si>
   <si>
     <t>数量</t>
@@ -6267,7 +6267,7 @@
     <t>^本场攻防“(.-)”“(.-)·(.-)”已结束，(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分；(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分。请再接再厉！</t>
   </si>
   <si>
-    <t>{$2}·{$3}·[{$4}·{$6}]:[{$7}·{$9}]</t>
+    <t>{$2}·{$3}·[{$4}{$5}·{$6}]:[{$7}{$8}·{$9}]</t>
   </si>
   <si>
     <t>{nClass=14,nIcon=2401,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},</t>
@@ -6282,10 +6282,10 @@
     <t>{nClass=14,nIcon=2396,nFrame=-1,nTime=-2,szName="{$2}·{$3}",key="{$2}·{$3}",},</t>
   </si>
   <si>
-    <t>{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}·{$6}分·{$7}·{$9}分;840,阶段·物资车2·出发剩余;850,阶段·物资车2·正在出发;900,阶段·首领出战·助战剩余;905,阶段·首领出战·助战结束;2700,阶段·破阵点将2·结算剩余;2702,阶段·破阵点将2·正在结算;2710,阶段·物资车3·正在出发;4500,阶段·本场攻防·结束剩余;4505,阶段·本场攻防·已经结束",szName="{$4}·{$6}分·{$7}·{$9}分",nRefresh=1,key="破阵点将·一",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}·{$6}分·{$7}·{$9}分;1800,阶段·本场攻防·结束剩余;1805,阶段·本场攻防·已经结束",szName="{$4}·{$6}分·{$7}·{$9}分",nRefresh=1,key="破阵点将·二",},</t>
+    <t>{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;840,阶段·物资车2·出发剩余;850,阶段·物资车2·正在出发;900,阶段·首领出战·助战剩余;905,阶段·首领出战·助战结束;2695,阶段·破阵点将2·结算剩余;2705,阶段·破阵点将2·正在结算;2710,阶段·物资车3·正在出发;4500,阶段·本场攻防·结束剩余;4505,阶段·本场攻防·已经结束",szName="{$4}·{$6}分·{$7}·{$9}分",nRefresh=1,key="破阵点将·一",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;1800,阶段·本场攻防·结束剩余;1805,阶段·本场攻防·已经结束",szName="{$4}·{$6}分·{$7}·{$9}分",nRefresh=1,key="破阵点将·二",},</t>
   </si>
   <si>
     <t>^本周累计从(.-)奖励堆获得战阶：(%d-)/(%d+)</t>
@@ -7446,7 +7446,7 @@
     <t>主场攻防·正式开启</t>
   </si>
   <si>
-    <t>{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2702,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5402,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},</t>
+    <t>{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2710,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5405,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},</t>
   </si>
   <si>
     <t>{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=30,key="首领拾取间隔",},</t>
@@ -9376,7 +9376,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="33" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1779197618000,</v>
+        <v>nTimeStamp = 1780242678000,</v>
       </c>
       <c r="B4" s="37" t="s">
         <v>11</v>
@@ -24405,7 +24405,7 @@
       </c>
       <c r="X4" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7242,nLevel=1,szNote="屹立不倒",[9]={},[8]={bScreenHead=true,},tCountdown={{nClass=8,nIcon=1537,nFrame=0,nTime="1,屹立不倒·{$sender}·正在释放;9.5,屹立不倒·{$sender}·50减伤;32.5,屹立不倒·{$sender}·释放剩余;40.5,屹立不倒·{$sender}·释放延迟",szName="屹立不倒",nRefresh=0,key="屹立不倒",},{nClass=9,nIcon=1537,nFrame=0,nTime="9,屹立不倒·{$sender}·50减伤;31.5,屹立不倒·{$sender}·释放剩余;40,屹立不倒·{$sender}·释放延迟",szName="屹立不倒",nRefresh=1,key="屹立不倒",},},},</v>
+        <v>{dwID=7242,nLevel=1,szNote="屹立不倒",[9]={},[8]={bScreenHead=true,},tCountdown={{nClass=8,nIcon=1537,nFrame=0,nTime="1,屹立不倒·{$sender}·正在释放;9.5,屹立不倒·{$sender}·50减伤;32.5,屹立不倒·{$sender}·释放剩余;40.5,屹立不倒·{$sender}·延迟释放;50,屹立不倒·{$sender}·随时释放",szName="屹立不倒",nRefresh=0,key="屹立不倒",},{nClass=9,nIcon=1537,nFrame=0,nTime="9,屹立不倒·{$sender}·50减伤;31.5,屹立不倒·{$sender}·释放剩余;40,屹立不倒·{$sender}·延迟释放;50,屹立不倒·{$sender}·随时释放",szName="屹立不倒",nRefresh=1,key="屹立不倒",},},},</v>
       </c>
       <c r="Y4" t="s">
         <v>1658</v>
@@ -34443,7 +34443,7 @@
       </c>
       <c r="V6" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^本场攻防“(.-)”“(.-)·(.-)”已结束，(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分；(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分。请再接再厉！",szTarget="%",szNote="{$2}·{$3}·[{$4}·{$6}]:[{$7}·{$9}]",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2401,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=14,nIcon=2397,nFrame=-1,nTime=-1,szName="破阵点将·一",nRefresh=2,key="破阵点将·一",},{nClass=14,nIcon=2398,nFrame=-1,nTime=-1,szName="破阵点将·二",nRefresh=2,key="破阵点将·二",},{nClass=14,nIcon=2396,nFrame=-1,nTime=-2,szName="{$2}·{$3}",key="{$2}·{$3}",},{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}·{$6}分·{$7}·{$9}分;840,阶段·物资车2·出发剩余;850,阶段·物资车2·正在出发;900,阶段·首领出战·助战剩余;905,阶段·首领出战·助战结束;2700,阶段·破阵点将2·结算剩余;2702,阶段·破阵点将2·正在结算;2710,阶段·物资车3·正在出发;4500,阶段·本场攻防·结束剩余;4505,阶段·本场攻防·已经结束",szName="{$4}·{$6}分·{$7}·{$9}分",nRefresh=1,key="破阵点将·一",},{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}·{$6}分·{$7}·{$9}分;1800,阶段·本场攻防·结束剩余;1805,阶段·本场攻防·已经结束",szName="{$4}·{$6}分·{$7}·{$9}分",nRefresh=1,key="破阵点将·二",},},},</v>
+        <v>{szContent="^本场攻防“(.-)”“(.-)·(.-)”已结束，(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分；(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分。请再接再厉！",szTarget="%",szNote="{$2}·{$3}·[{$4}{$5}·{$6}]:[{$7}{$8}·{$9}]",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2401,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=14,nIcon=2397,nFrame=-1,nTime=-1,szName="破阵点将·一",nRefresh=2,key="破阵点将·一",},{nClass=14,nIcon=2398,nFrame=-1,nTime=-1,szName="破阵点将·二",nRefresh=2,key="破阵点将·二",},{nClass=14,nIcon=2396,nFrame=-1,nTime=-2,szName="{$2}·{$3}",key="{$2}·{$3}",},{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;840,阶段·物资车2·出发剩余;850,阶段·物资车2·正在出发;900,阶段·首领出战·助战剩余;905,阶段·首领出战·助战结束;2695,阶段·破阵点将2·结算剩余;2705,阶段·破阵点将2·正在结算;2710,阶段·物资车3·正在出发;4500,阶段·本场攻防·结束剩余;4505,阶段·本场攻防·已经结束",szName="{$4}·{$6}分·{$7}·{$9}分",nRefresh=1,key="破阵点将·一",},{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;1800,阶段·本场攻防·结束剩余;1805,阶段·本场攻防·已经结束",szName="{$4}·{$6}分·{$7}·{$9}分",nRefresh=1,key="破阵点将·二",},},},</v>
       </c>
       <c r="W6" t="s">
         <v>2070</v>
@@ -40992,7 +40992,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="str">
-        <f t="shared" ref="T3:T66" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(L3),ISBLANK(M3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(L2)=FALSE,ISBLANK(M2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(K3&lt;&gt;"","col={"&amp;K3&amp;"},","")&amp;IF(L3&gt;0,"bSearch=true,","")&amp;IF(M3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N3&gt;0,"szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bTeamChannel=true,","")&amp;IF(P3&gt;0,"bWhisperChannel=true,","")&amp;IF(Q3&gt;0,"bCenterAlarm=true,","")&amp;IF(R3&gt;0,"bScreenHead=true,","")&amp;IF(S3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U3:AAF3)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="T3:T34" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(L3),ISBLANK(M3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(L2)=FALSE,ISBLANK(M2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(K3&lt;&gt;"","col={"&amp;K3&amp;"},","")&amp;IF(L3&gt;0,"bSearch=true,","")&amp;IF(M3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N3&gt;0,"szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bTeamChannel=true,","")&amp;IF(P3&gt;0,"bWhisperChannel=true,","")&amp;IF(Q3&gt;0,"bCenterAlarm=true,","")&amp;IF(R3&gt;0,"bScreenHead=true,","")&amp;IF(S3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U3:AAF3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="[团队监控]数据加载成功",szNote="关闭刷马等计时条",bSearch=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},},},</v>
       </c>
       <c r="U3" s="2" t="s">
@@ -41477,7 +41477,7 @@
       </c>
       <c r="T19" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="王遗风已率恶人谷众首领抵达浩气盟，请各位恶人谷侠士速到浩气盟支援。浩气盟侠士也请速回浩气盟防御！\n",szNote="主场攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2702,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5402,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=30,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="速战速决",nTime=-2,key="速战速决",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
+        <v>{szContent="王遗风已率恶人谷众首领抵达浩气盟，请各位恶人谷侠士速到浩气盟支援。浩气盟侠士也请速回浩气盟防御！\n",szNote="主场攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2710,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5405,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=30,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="速战速决",nTime=-2,key="速战速决",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U19" t="s">
         <v>2462</v>
@@ -41582,7 +41582,7 @@
       </c>
       <c r="T23" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="谢渊已率浩气盟众首领抵达恶人谷，请各位浩气盟侠士速到恶人谷支援。恶人谷侠士也请速回恶人谷防御！\n",szNote="主场攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2702,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5402,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=30,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="速战速决",nTime=-2,key="速战速决",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
+        <v>{szContent="谢渊已率浩气盟众首领抵达恶人谷，请各位浩气盟侠士速到恶人谷支援。恶人谷侠士也请速回恶人谷防御！\n",szNote="主场攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2710,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5405,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=30,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="速战速决",nTime=-2,key="速战速决",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U23" t="s">
         <v>2462</v>
@@ -41765,16 +41765,16 @@
         <v>2490</v>
       </c>
     </row>
-    <row r="34" customFormat="1" spans="1:26">
+    <row r="34" spans="1:26">
       <c r="A34" t="s">
-        <v>2231</v>
+        <v>1673</v>
       </c>
       <c r="B34">
-        <v>-21</v>
+        <v>-2</v>
       </c>
       <c r="T34" t="str">
         <f t="shared" si="0"/>
-        <v>},[-21]={</v>
+        <v>},[-2]={</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:26">
@@ -41791,7 +41791,7 @@
         <v>1</v>
       </c>
       <c r="T35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="T35:T66" si="1">IF(ISBLANK(B35)=FALSE,IF(ISBLANK(B34),"},["&amp;B35&amp;"]={","["&amp;B35&amp;"]={"),IF(AND(ISBLANK(B35),ISBLANK(C35),ISBLANK(L35),ISBLANK(M35),OR(ISBLANK(B34)=FALSE,ISBLANK(C34)=FALSE,ISBLANK(L34)=FALSE,ISBLANK(M34)=FALSE)),"},},}",IF(ISBLANK(C35),"","{szContent="""&amp;C35&amp;""","&amp;IF(D35&lt;&gt;"","szNote="""&amp;D35&amp;""",","")&amp;IF(K35&lt;&gt;"","col={"&amp;K35&amp;"},","")&amp;IF(L35&gt;0,"bSearch=true,","")&amp;IF(M35&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N35&gt;0,"szVoice="""&amp;N35&amp;""",","")&amp;IF(O35&gt;0,"bTeamChannel=true,","")&amp;IF(P35&gt;0,"bWhisperChannel=true,","")&amp;IF(Q35&gt;0,"bCenterAlarm=true,","")&amp;IF(R35&gt;0,"bScreenHead=true,","")&amp;IF(S35&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U35&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U35:AAF35)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U35" t="s">
@@ -41812,7 +41812,7 @@
         <v>1</v>
       </c>
       <c r="T36" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U36" t="s">
@@ -41845,7 +41845,7 @@
         <v>1</v>
       </c>
       <c r="T37" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U37" t="s">
@@ -41878,7 +41878,7 @@
         <v>2120</v>
       </c>
       <c r="T38" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U38" t="s">
@@ -41896,7 +41896,7 @@
         <v>2119</v>
       </c>
       <c r="T39" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U39" t="s">
@@ -41917,7 +41917,7 @@
         <v>1</v>
       </c>
       <c r="T40" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U40" t="s">
@@ -41935,7 +41935,7 @@
         <v>1656</v>
       </c>
       <c r="T41" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U41" t="s">
@@ -41954,7 +41954,7 @@
         <v>1656</v>
       </c>
       <c r="T42" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U42" t="s">
@@ -41973,7 +41973,7 @@
         <v>1656</v>
       </c>
       <c r="T43" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U43" t="s">
@@ -41983,7 +41983,7 @@
         <v>2518</v>
       </c>
     </row>
-    <row r="44" customFormat="1" spans="1:26">
+    <row r="44" spans="1:26">
       <c r="C44" t="s">
         <v>2519</v>
       </c>
@@ -41991,7 +41991,7 @@
         <v>1656</v>
       </c>
       <c r="T44" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U44" t="s">
@@ -42001,7 +42001,7 @@
         <v>2521</v>
       </c>
     </row>
-    <row r="45" customFormat="1" spans="1:26">
+    <row r="45" spans="1:26">
       <c r="C45" t="s">
         <v>2522</v>
       </c>
@@ -42009,14 +42009,14 @@
         <v>1656</v>
       </c>
       <c r="T45" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U45" t="s">
         <v>2523</v>
       </c>
     </row>
-    <row r="46" customFormat="1" spans="1:26">
+    <row r="46" spans="1:26">
       <c r="C46" t="s">
         <v>2524</v>
       </c>
@@ -42024,7 +42024,7 @@
         <v>1656</v>
       </c>
       <c r="T46" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U46" t="s">
@@ -42034,7 +42034,7 @@
         <v>2525</v>
       </c>
     </row>
-    <row r="47" customFormat="1" spans="1:26">
+    <row r="47" spans="1:26">
       <c r="C47" t="s">
         <v>2526</v>
       </c>
@@ -42042,23 +42042,23 @@
         <v>1656</v>
       </c>
       <c r="T47" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·分线·开启",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
       <c r="U47" t="s">
         <v>2527</v>
       </c>
     </row>
-    <row r="48" spans="1:26">
-      <c r="A48" t="s">
-        <v>1673</v>
-      </c>
-      <c r="B48">
-        <v>-2</v>
+    <row r="48" s="1" customFormat="1" spans="1:26">
+      <c r="A48" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B48" s="1">
+        <v>-7</v>
       </c>
       <c r="T48" t="str">
-        <f t="shared" si="0"/>
-        <v>},[-2]={</v>
+        <f t="shared" si="1"/>
+        <v>},[-7]={</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:26">
@@ -42074,15 +42074,18 @@
       <c r="M49">
         <v>1</v>
       </c>
+      <c r="Q49">
+        <v>1</v>
+      </c>
       <c r="T49" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U49" t="s">
         <v>2493</v>
       </c>
     </row>
-    <row r="50" customFormat="1" spans="1:26">
+    <row r="50" spans="1:26">
       <c r="C50" t="s">
         <v>2494</v>
       </c>
@@ -42096,23 +42099,23 @@
         <v>1</v>
       </c>
       <c r="T50" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,key="{$3}·恶人大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气占领",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人占领",},{nClass=20,nIcon=13,szName="{$3}·{$1}占领",nTime=-1,key="{$3}·{$1}占领",},},},</v>
       </c>
       <c r="U50" t="s">
-        <v>2496</v>
+        <v>2528</v>
       </c>
       <c r="V50" t="s">
-        <v>2497</v>
+        <v>2529</v>
       </c>
       <c r="W50" t="s">
-        <v>2498</v>
+        <v>2530</v>
       </c>
       <c r="X50" t="s">
-        <v>2499</v>
+        <v>2531</v>
       </c>
       <c r="Y50" t="s">
-        <v>2500</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:26">
@@ -42129,7 +42132,7 @@
         <v>1</v>
       </c>
       <c r="T51" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U51" t="s">
@@ -42162,7 +42165,7 @@
         <v>2120</v>
       </c>
       <c r="T52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U52" t="s">
@@ -42180,32 +42183,26 @@
         <v>2119</v>
       </c>
       <c r="T53" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U53" t="s">
         <v>2409</v>
       </c>
     </row>
-    <row r="54" customFormat="1" spans="1:26">
+    <row r="54" spans="1:26">
       <c r="C54" t="s">
-        <v>2509</v>
-      </c>
-      <c r="D54" t="s">
-        <v>2510</v>
+        <v>2533</v>
       </c>
       <c r="K54" t="s">
         <v>1656</v>
       </c>
-      <c r="Q54">
-        <v>1</v>
-      </c>
       <c r="T54" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="本场贡献值进入前1200名，额外获得3000威名，可通过邮件领取\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=6,szName="攻防进入前1200名",nTime=10,key="阵营活动",},},},</v>
       </c>
       <c r="U54" t="s">
-        <v>2511</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:26">
@@ -42219,34 +42216,41 @@
         <v>1656</v>
       </c>
       <c r="T55" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=20,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=20,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=20,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=20,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=20,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=20,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=20,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=20,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=20,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="U55" t="s">
         <v>2514</v>
       </c>
-      <c r="V55" s="6"/>
+      <c r="V55" s="4" t="s">
+        <v>2434</v>
+      </c>
+      <c r="W55" s="4" t="s">
+        <v>2435</v>
+      </c>
     </row>
     <row r="56" customFormat="1" spans="1:26">
       <c r="C56" t="s">
-        <v>2431</v>
+        <v>2509</v>
       </c>
       <c r="D56" t="s">
-        <v>2432</v>
+        <v>2510</v>
       </c>
       <c r="K56" t="s">
         <v>1656</v>
       </c>
+      <c r="Q56">
+        <v>1</v>
+      </c>
       <c r="T56" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U56" t="s">
-        <v>2433</v>
-      </c>
-      <c r="V56" s="6"/>
-    </row>
-    <row r="57" customFormat="1" spans="1:26">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="57" spans="1:26">
       <c r="C57" t="s">
         <v>2515</v>
       </c>
@@ -42257,13 +42261,19 @@
         <v>1656</v>
       </c>
       <c r="T57" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=13,szName="狼牙先锋首领",nTime=0,key="狼牙先锋首领",},{nClass=20,nIcon=13,szName="离开据点·大旗重置",nTime=0,key="离开据点·大旗重置",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U57" t="s">
-        <v>2517</v>
-      </c>
-      <c r="V57" s="5" t="s">
+        <v>2535</v>
+      </c>
+      <c r="V57" t="s">
+        <v>2536</v>
+      </c>
+      <c r="W57" t="s">
+        <v>2537</v>
+      </c>
+      <c r="X57" s="5" t="s">
         <v>2518</v>
       </c>
     </row>
@@ -42275,7 +42285,7 @@
         <v>1656</v>
       </c>
       <c r="T58" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U58" t="s">
@@ -42287,35 +42297,41 @@
     </row>
     <row r="59" spans="1:26">
       <c r="C59" t="s">
-        <v>2522</v>
+        <v>2524</v>
+      </c>
+      <c r="D59" t="s">
+        <v>2538</v>
       </c>
       <c r="K59" t="s">
         <v>1656</v>
       </c>
       <c r="T59" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·5分钟·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U59" t="s">
-        <v>2523</v>
+        <v>2520</v>
+      </c>
+      <c r="V59" t="s">
+        <v>2525</v>
       </c>
     </row>
     <row r="60" spans="1:26">
       <c r="C60" t="s">
-        <v>2524</v>
+        <v>2539</v>
+      </c>
+      <c r="D60" t="s">
+        <v>2283</v>
       </c>
       <c r="K60" t="s">
         <v>1656</v>
       </c>
       <c r="T60" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="前线据点之争已经打响，争夺正式开始，沙盘地图（CTRL + M）绘有详细战略意图，谁将称霸中原，我们拭目以待！\n",szNote="据点攻防·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime=10,key="阵营活动",},},},</v>
       </c>
       <c r="U60" t="s">
-        <v>2520</v>
-      </c>
-      <c r="V60" t="s">
-        <v>2525</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="61" spans="1:26">
@@ -42326,31 +42342,31 @@
         <v>1656</v>
       </c>
       <c r="T61" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·分线·开启",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
       <c r="U61" t="s">
         <v>2527</v>
       </c>
     </row>
-    <row r="62" s="1" customFormat="1" spans="1:26">
-      <c r="A62" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="B62" s="1">
-        <v>-7</v>
+    <row r="62" customFormat="1" spans="1:26">
+      <c r="A62" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B62">
+        <v>-20</v>
       </c>
       <c r="T62" t="str">
-        <f t="shared" si="0"/>
-        <v>},[-7]={</v>
+        <f t="shared" si="1"/>
+        <v>},[-20]={</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:26">
       <c r="C63" t="s">
-        <v>2491</v>
+        <v>2541</v>
       </c>
       <c r="D63" t="s">
-        <v>2492</v>
+        <v>2542</v>
       </c>
       <c r="K63" t="s">
         <v>1656</v>
@@ -42358,56 +42374,44 @@
       <c r="M63">
         <v>1</v>
       </c>
-      <c r="Q63">
-        <v>1</v>
-      </c>
       <c r="T63" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U63" t="s">
-        <v>2493</v>
-      </c>
-    </row>
-    <row r="64" spans="1:26">
-      <c r="C64" t="s">
-        <v>2494</v>
-      </c>
-      <c r="D64" t="s">
-        <v>2495</v>
-      </c>
-      <c r="K64" t="s">
-        <v>1656</v>
-      </c>
-      <c r="M64">
-        <v>1</v>
+        <v>2543</v>
+      </c>
+      <c r="V63" t="s">
+        <v>2544</v>
+      </c>
+      <c r="W63" t="s">
+        <v>2545</v>
+      </c>
+      <c r="X63" t="s">
+        <v>2546</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>2547</v>
+      </c>
+    </row>
+    <row r="64" customFormat="1" spans="1:26">
+      <c r="A64" t="s">
+        <v>2231</v>
+      </c>
+      <c r="B64">
+        <v>-21</v>
       </c>
       <c r="T64" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,key="{$3}·恶人大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气占领",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人占领",},{nClass=20,nIcon=13,szName="{$3}·{$1}占领",nTime=-1,key="{$3}·{$1}占领",},},},</v>
-      </c>
-      <c r="U64" t="s">
-        <v>2528</v>
-      </c>
-      <c r="V64" t="s">
-        <v>2529</v>
-      </c>
-      <c r="W64" t="s">
-        <v>2530</v>
-      </c>
-      <c r="X64" t="s">
-        <v>2531</v>
-      </c>
-      <c r="Y64" t="s">
-        <v>2532</v>
+        <f t="shared" si="1"/>
+        <v>},[-21]={</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:26">
       <c r="C65" t="s">
-        <v>2501</v>
+        <v>2491</v>
       </c>
       <c r="D65" t="s">
-        <v>2502</v>
+        <v>2492</v>
       </c>
       <c r="K65" t="s">
         <v>1656</v>
@@ -42416,101 +42420,116 @@
         <v>1</v>
       </c>
       <c r="T65" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U65" t="s">
-        <v>2503</v>
-      </c>
-      <c r="V65" t="s">
-        <v>2504</v>
-      </c>
-      <c r="W65" t="s">
-        <v>2505</v>
-      </c>
-      <c r="X65" t="s">
-        <v>2506</v>
-      </c>
-      <c r="Y65" t="s">
-        <v>2507</v>
-      </c>
-      <c r="Z65" t="s">
-        <v>2508</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="66" customFormat="1" spans="1:26">
       <c r="C66" t="s">
-        <v>2404</v>
+        <v>2494</v>
       </c>
       <c r="D66" t="s">
-        <v>2405</v>
+        <v>2495</v>
       </c>
       <c r="K66" t="s">
-        <v>2120</v>
+        <v>1656</v>
+      </c>
+      <c r="M66">
+        <v>1</v>
       </c>
       <c r="T66" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U66" t="s">
-        <v>2406</v>
+        <v>2496</v>
+      </c>
+      <c r="V66" t="s">
+        <v>2497</v>
+      </c>
+      <c r="W66" t="s">
+        <v>2498</v>
+      </c>
+      <c r="X66" t="s">
+        <v>2499</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>2500</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:26">
       <c r="C67" t="s">
-        <v>2407</v>
+        <v>2501</v>
       </c>
       <c r="D67" t="s">
-        <v>2408</v>
+        <v>2502</v>
       </c>
       <c r="K67" t="s">
-        <v>2119</v>
+        <v>1656</v>
+      </c>
+      <c r="M67">
+        <v>1</v>
       </c>
       <c r="T67" t="str">
-        <f t="shared" ref="T67:T130" si="1">IF(ISBLANK(B67)=FALSE,IF(ISBLANK(B66),"},["&amp;B67&amp;"]={","["&amp;B67&amp;"]={"),IF(AND(ISBLANK(B67),ISBLANK(C67),ISBLANK(L67),ISBLANK(M67),OR(ISBLANK(B66)=FALSE,ISBLANK(C66)=FALSE,ISBLANK(L66)=FALSE,ISBLANK(M66)=FALSE)),"},},}",IF(ISBLANK(C67),"","{szContent="""&amp;C67&amp;""","&amp;IF(D67&lt;&gt;"","szNote="""&amp;D67&amp;""",","")&amp;IF(K67&lt;&gt;"","col={"&amp;K67&amp;"},","")&amp;IF(L67&gt;0,"bSearch=true,","")&amp;IF(M67&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N67&gt;0,"szVoice="""&amp;N67&amp;""",","")&amp;IF(O67&gt;0,"bTeamChannel=true,","")&amp;IF(P67&gt;0,"bWhisperChannel=true,","")&amp;IF(Q67&gt;0,"bCenterAlarm=true,","")&amp;IF(R67&gt;0,"bScreenHead=true,","")&amp;IF(S67&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U67&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U67:AAF67)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
+        <f t="shared" ref="T67:T98" si="2">IF(ISBLANK(B67)=FALSE,IF(ISBLANK(B66),"},["&amp;B67&amp;"]={","["&amp;B67&amp;"]={"),IF(AND(ISBLANK(B67),ISBLANK(C67),ISBLANK(L67),ISBLANK(M67),OR(ISBLANK(B66)=FALSE,ISBLANK(C66)=FALSE,ISBLANK(L66)=FALSE,ISBLANK(M66)=FALSE)),"},},}",IF(ISBLANK(C67),"","{szContent="""&amp;C67&amp;""","&amp;IF(D67&lt;&gt;"","szNote="""&amp;D67&amp;""",","")&amp;IF(K67&lt;&gt;"","col={"&amp;K67&amp;"},","")&amp;IF(L67&gt;0,"bSearch=true,","")&amp;IF(M67&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N67&gt;0,"szVoice="""&amp;N67&amp;""",","")&amp;IF(O67&gt;0,"bTeamChannel=true,","")&amp;IF(P67&gt;0,"bWhisperChannel=true,","")&amp;IF(Q67&gt;0,"bCenterAlarm=true,","")&amp;IF(R67&gt;0,"bScreenHead=true,","")&amp;IF(S67&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U67&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U67:AAF67)&amp;"},","")&amp;"},")))</f>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U67" t="s">
-        <v>2409</v>
-      </c>
-    </row>
-    <row r="68" spans="1:26">
+        <v>2503</v>
+      </c>
+      <c r="V67" t="s">
+        <v>2504</v>
+      </c>
+      <c r="W67" t="s">
+        <v>2505</v>
+      </c>
+      <c r="X67" t="s">
+        <v>2506</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>2507</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="68" customFormat="1" spans="1:26">
       <c r="C68" t="s">
-        <v>2533</v>
+        <v>2404</v>
+      </c>
+      <c r="D68" t="s">
+        <v>2405</v>
       </c>
       <c r="K68" t="s">
-        <v>1656</v>
+        <v>2120</v>
       </c>
       <c r="T68" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="本场贡献值进入前1200名，额外获得3000威名，可通过邮件领取\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=6,szName="攻防进入前1200名",nTime=10,key="阵营活动",},},},</v>
+        <f t="shared" si="2"/>
+        <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U68" t="s">
-        <v>2534</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:26">
       <c r="C69" t="s">
-        <v>2512</v>
+        <v>2407</v>
       </c>
       <c r="D69" t="s">
-        <v>2513</v>
+        <v>2408</v>
       </c>
       <c r="K69" t="s">
-        <v>1656</v>
+        <v>2119</v>
       </c>
       <c r="T69" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=20,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=20,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=20,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=20,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=20,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=20,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=20,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=20,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=20,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
+        <f t="shared" si="2"/>
+        <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U69" t="s">
-        <v>2514</v>
-      </c>
-      <c r="V69" s="4" t="s">
-        <v>2434</v>
-      </c>
-      <c r="W69" s="4" t="s">
-        <v>2435</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="70" customFormat="1" spans="1:26">
@@ -42527,155 +42546,136 @@
         <v>1</v>
       </c>
       <c r="T70" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U70" t="s">
         <v>2511</v>
       </c>
     </row>
-    <row r="71" spans="1:26">
+    <row r="71" customFormat="1" spans="1:26">
       <c r="C71" t="s">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="D71" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
       <c r="K71" t="s">
         <v>1656</v>
       </c>
       <c r="T71" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=13,szName="狼牙先锋首领",nTime=0,key="狼牙先锋首领",},{nClass=20,nIcon=13,szName="离开据点·大旗重置",nTime=0,key="离开据点·大旗重置",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
+        <f t="shared" si="2"/>
+        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U71" t="s">
-        <v>2535</v>
-      </c>
-      <c r="V71" t="s">
-        <v>2536</v>
-      </c>
-      <c r="W71" t="s">
-        <v>2537</v>
-      </c>
-      <c r="X71" s="5" t="s">
-        <v>2518</v>
-      </c>
-    </row>
-    <row r="72" spans="1:26">
+        <v>2514</v>
+      </c>
+      <c r="V71" s="6"/>
+    </row>
+    <row r="72" customFormat="1" spans="1:26">
       <c r="C72" t="s">
-        <v>2519</v>
+        <v>2431</v>
+      </c>
+      <c r="D72" t="s">
+        <v>2432</v>
       </c>
       <c r="K72" t="s">
         <v>1656</v>
       </c>
       <c r="T72" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
+        <f t="shared" si="2"/>
+        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U72" t="s">
-        <v>2520</v>
-      </c>
-      <c r="V72" t="s">
-        <v>2521</v>
-      </c>
-    </row>
-    <row r="73" spans="1:26">
+        <v>2433</v>
+      </c>
+      <c r="V72" s="6"/>
+    </row>
+    <row r="73" customFormat="1" spans="1:26">
       <c r="C73" t="s">
-        <v>2524</v>
+        <v>2515</v>
       </c>
       <c r="D73" t="s">
-        <v>2538</v>
+        <v>2516</v>
       </c>
       <c r="K73" t="s">
         <v>1656</v>
       </c>
       <c r="T73" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·5分钟·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
+        <f t="shared" si="2"/>
+        <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U73" t="s">
-        <v>2520</v>
-      </c>
-      <c r="V73" t="s">
-        <v>2525</v>
-      </c>
-    </row>
-    <row r="74" spans="1:26">
+        <v>2517</v>
+      </c>
+      <c r="V73" s="5" t="s">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="74" customFormat="1" spans="1:26">
       <c r="C74" t="s">
-        <v>2539</v>
-      </c>
-      <c r="D74" t="s">
-        <v>2283</v>
+        <v>2519</v>
       </c>
       <c r="K74" t="s">
         <v>1656</v>
       </c>
       <c r="T74" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="前线据点之争已经打响，争夺正式开始，沙盘地图（CTRL + M）绘有详细战略意图，谁将称霸中原，我们拭目以待！\n",szNote="据点攻防·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime=10,key="阵营活动",},},},</v>
+        <f t="shared" si="2"/>
+        <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U74" t="s">
-        <v>2540</v>
-      </c>
-    </row>
-    <row r="75" spans="1:26">
+        <v>2520</v>
+      </c>
+      <c r="V74" t="s">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="75" customFormat="1" spans="1:26">
       <c r="C75" t="s">
-        <v>2526</v>
+        <v>2522</v>
       </c>
       <c r="K75" t="s">
         <v>1656</v>
       </c>
       <c r="T75" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·分线·开启",nTime=30,nRefresh=10,key="分流活动",},},},</v>
+        <f t="shared" si="2"/>
+        <v>{szContent="前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U75" t="s">
-        <v>2527</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="76" customFormat="1" spans="1:26">
-      <c r="A76" t="s">
-        <v>1488</v>
-      </c>
-      <c r="B76">
-        <v>-20</v>
+      <c r="C76" t="s">
+        <v>2524</v>
+      </c>
+      <c r="K76" t="s">
+        <v>1656</v>
       </c>
       <c r="T76" t="str">
-        <f t="shared" si="1"/>
-        <v>},[-20]={</v>
+        <f t="shared" si="2"/>
+        <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
+      </c>
+      <c r="U76" t="s">
+        <v>2520</v>
+      </c>
+      <c r="V76" t="s">
+        <v>2525</v>
       </c>
     </row>
     <row r="77" customFormat="1" spans="1:26">
       <c r="C77" t="s">
-        <v>2541</v>
-      </c>
-      <c r="D77" t="s">
-        <v>2542</v>
+        <v>2526</v>
       </c>
       <c r="K77" t="s">
         <v>1656</v>
       </c>
-      <c r="M77">
-        <v>1</v>
-      </c>
       <c r="T77" t="str">
-        <f t="shared" si="1"/>
-        <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
+        <f t="shared" si="2"/>
+        <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·分线·开启",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
       <c r="U77" t="s">
-        <v>2543</v>
-      </c>
-      <c r="V77" t="s">
-        <v>2544</v>
-      </c>
-      <c r="W77" t="s">
-        <v>2545</v>
-      </c>
-      <c r="X77" t="s">
-        <v>2546</v>
-      </c>
-      <c r="Y77" t="s">
-        <v>2547</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="78" customFormat="1" spans="1:26">
@@ -42686,7 +42686,7 @@
         <v>-3</v>
       </c>
       <c r="T78" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>},[-3]={</v>
       </c>
     </row>
@@ -42698,7 +42698,7 @@
         <v>2120</v>
       </c>
       <c r="T79" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往恶人谷地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=3,szName="主战场·恶人谷",nTime="1,阵营攻防·开始排队·恶人谷;10,阵营攻防·开始排队·恶人谷",key="大攻防·主战场",},},},</v>
       </c>
       <c r="U79" t="s">
@@ -42713,7 +42713,7 @@
         <v>2119</v>
       </c>
       <c r="T80" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往浩气盟地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=7,szName="主战场·浩气盟",nTime="1,阵营攻防·开始排队·浩气盟;10,阵营攻防·开始排队·浩气盟",key="大攻防·主战场",},},},</v>
       </c>
       <c r="U80" t="s">
@@ -42728,7 +42728,7 @@
         <v>74</v>
       </c>
       <c r="T81" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>},[74]={</v>
       </c>
     </row>
@@ -42743,7 +42743,7 @@
         <v>1656</v>
       </c>
       <c r="T82" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>{szContent="本场攻防“奇袭场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="奇袭场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2402,nFrame=4,szName="奇袭场·平手",nTime=57,nRefresh=5,key="大攻防·奇袭场",},},},</v>
       </c>
       <c r="U82" t="s">
@@ -42761,7 +42761,7 @@
         <v>1656</v>
       </c>
       <c r="T83" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>{szContent="本场攻防“主战场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="主战场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="主战场·平手",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U83" t="s">
@@ -42785,7 +42785,7 @@
         <v>1</v>
       </c>
       <c r="T84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>{szContent="^本场攻防“([主战奇袭场]+)”已结束，([浩气盟恶人谷]+)[侠士们众志成城和，]-([大完险胜]+)([浩气盟恶人谷]+)[！，]+",szNote="{$1}·{$2}·{$3}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,szName="大攻防·奇袭场",nTime=-2,nRefresh=10,key="大攻防·奇袭场",},{nClass=20,nIcon=13,szName="大攻防·主战场",nTime=-2,nRefresh=10,key="大攻防·主战场",},{nClass=20,nIcon=13,szName="大攻防·{$1}",nTime=-2,key="大攻防·{$1}",},{nClass=20,nIcon=2402,nFrame=4,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U84" t="s">
@@ -42821,7 +42821,7 @@
         <v>1</v>
       </c>
       <c r="T85" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U85" t="s">
@@ -42842,7 +42842,7 @@
         <v>1</v>
       </c>
       <c r="T86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U86" t="s">
@@ -42875,7 +42875,7 @@
         <v>1</v>
       </c>
       <c r="T87" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U87" t="s">
@@ -42908,7 +42908,7 @@
         <v>2120</v>
       </c>
       <c r="T88" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U88" t="s">
@@ -42926,7 +42926,7 @@
         <v>2119</v>
       </c>
       <c r="T89" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U89" t="s">
@@ -42947,7 +42947,7 @@
         <v>1</v>
       </c>
       <c r="T90" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U90" t="s">
@@ -42965,7 +42965,7 @@
         <v>1656</v>
       </c>
       <c r="T91" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U91" t="s">
@@ -42986,7 +42986,7 @@
         <v>1656</v>
       </c>
       <c r="T92" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U92" t="s">
@@ -43005,7 +43005,7 @@
         <v>1656</v>
       </c>
       <c r="T93" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U93" t="s">
@@ -43021,7 +43021,7 @@
         <v>22</v>
       </c>
       <c r="T94" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>},[22]={</v>
       </c>
     </row>
@@ -43042,7 +43042,7 @@
         <v>1</v>
       </c>
       <c r="T95" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【武王城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="武王城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【武王城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="武王城·恶人大旗",},},},</v>
       </c>
       <c r="U95" t="s">
@@ -43094,7 +43094,7 @@
         <v>1</v>
       </c>
       <c r="T96" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="武王城·大旗重置",nTime=-2,nRefresh=7200,key="武王城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【武王城】大旗重置",nTime=180,nRefresh=7200,key="武王城·大旗重置",},},},</v>
       </c>
       <c r="U96" t="s">
@@ -43118,7 +43118,7 @@
         <v>1656</v>
       </c>
       <c r="T97" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>{szContent="本场浩气盟攻防即将结束，南屏山物资运送暂且休整，等待下一场攻防开启！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="粮草先行·活动结束",nTime=5,key="粮草先行·浩气盟",},{nClass=20,nIcon=13,szName="粮草先行·恶人谷",nTime=0,key="粮草先行·恶人谷",},{nClass=20,nIcon=589,nFrame=7,szName="赵新宇",nTime="60,赵新宇·刷新剩余;62,赵新宇·即将刷新",nRefresh=0,key="赵新宇",},},},</v>
       </c>
       <c r="U97" t="s">
@@ -43139,7 +43139,7 @@
         <v>2120</v>
       </c>
       <c r="T98" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>{szContent="南屏山恶人谷伴江村援军已到，营地夺回，交通恢复！\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=10,nRefresh=600,key="赵新宇",},},},</v>
       </c>
       <c r="U98" t="s">
@@ -43154,7 +43154,7 @@
         <v>2119</v>
       </c>
       <c r="T99" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="T99:T130" si="3">IF(ISBLANK(B99)=FALSE,IF(ISBLANK(B98),"},["&amp;B99&amp;"]={","["&amp;B99&amp;"]={"),IF(AND(ISBLANK(B99),ISBLANK(C99),ISBLANK(L99),ISBLANK(M99),OR(ISBLANK(B98)=FALSE,ISBLANK(C98)=FALSE,ISBLANK(L98)=FALSE,ISBLANK(M98)=FALSE)),"},},}",IF(ISBLANK(C99),"","{szContent="""&amp;C99&amp;""","&amp;IF(D99&lt;&gt;"","szNote="""&amp;D99&amp;""",","")&amp;IF(K99&lt;&gt;"","col={"&amp;K99&amp;"},","")&amp;IF(L99&gt;0,"bSearch=true,","")&amp;IF(M99&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N99&gt;0,"szVoice="""&amp;N99&amp;""",","")&amp;IF(O99&gt;0,"bTeamChannel=true,","")&amp;IF(P99&gt;0,"bWhisperChannel=true,","")&amp;IF(Q99&gt;0,"bCenterAlarm=true,","")&amp;IF(R99&gt;0,"bScreenHead=true,","")&amp;IF(S99&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U99&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U99:AAF99)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="南屏山浩气盟望北村援军已到，营地夺回，交通恢复！\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=10,nRefresh=600,key="方超",},},},</v>
       </c>
       <c r="U99" t="s">
@@ -43169,7 +43169,7 @@
         <v>30</v>
       </c>
       <c r="T100" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>},[30]={</v>
       </c>
     </row>
@@ -43190,7 +43190,7 @@
         <v>1</v>
       </c>
       <c r="T101" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凛风堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凛风堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·恶人大旗",},},},</v>
       </c>
       <c r="U101" t="s">
@@ -43242,7 +43242,7 @@
         <v>1</v>
       </c>
       <c r="T102" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凛风堡·大旗重置",nTime=-2,nRefresh=7200,key="凛风堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凛风堡】大旗重置",nTime=180,nRefresh=7200,key="凛风堡·大旗重置",},},},</v>
       </c>
       <c r="U102" t="s">
@@ -43266,7 +43266,7 @@
         <v>1656</v>
       </c>
       <c r="T103" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>{szContent="本场恶人谷攻防即将结束，昆仑物资运送暂且休整，等待下一场攻防开启！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="粮草先行·活动结束",nTime=5,key="粮草先行·恶人谷",},{nClass=20,nIcon=13,szName="粮草先行·浩气盟",nTime=0,key="粮草先行·浩气盟",},{nClass=20,nIcon=2864,nFrame=7,szName="霸图",nTime="60,霸图·刷新剩余;62,霸图·即将刷新",nRefresh=0,key="霸图",},{nClass=20,nIcon=845,nFrame=3,szName="孙永恒",nTime="60,孙永恒·刷新剩余;62,孙永恒·即将刷新",nRefresh=0,key="孙永恒",},},},</v>
       </c>
       <c r="U103" t="s">
@@ -43290,7 +43290,7 @@
         <v>2120</v>
       </c>
       <c r="T104" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>{szContent="昆仑山恶人谷西昆仑高地援军已到，营地夺回，交通恢复！\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=10,nRefresh=600,key="霸图",},},},</v>
       </c>
       <c r="U104" t="s">
@@ -43305,7 +43305,7 @@
         <v>2119</v>
       </c>
       <c r="T105" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>{szContent="昆仑山浩气盟东昆仑高地援军已到，营地夺回，交通恢复！\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=10,nRefresh=600,key="孙永恒",},},},</v>
       </c>
       <c r="U105" t="s">
@@ -43320,7 +43320,7 @@
         <v>21</v>
       </c>
       <c r="T106" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>},[21]={</v>
       </c>
     </row>
@@ -43344,7 +43344,7 @@
         <v>1</v>
       </c>
       <c r="T107" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【盘龙坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【逐鹿坪】恶人·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【盘龙坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【逐鹿坪】浩气·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·恶人大旗",},},},</v>
       </c>
       <c r="U107" t="s">
@@ -43412,7 +43412,7 @@
         <v>1</v>
       </c>
       <c r="T108" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="盘龙坞·大旗重置",nTime=-2,nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=1465,szName="逐鹿坪·大旗重置",nTime=-2,nRefresh=7200,key="逐鹿坪·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【盘龙坞】大旗重置",nTime=180,nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【逐鹿坪】大旗重置",nTime=180,nRefresh=7200,key="逐鹿坪·大旗重置",},},},</v>
       </c>
       <c r="U108" t="s">
@@ -43442,7 +43442,7 @@
         <v>23</v>
       </c>
       <c r="T109" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>},[23]={</v>
       </c>
     </row>
@@ -43466,7 +43466,7 @@
         <v>1</v>
       </c>
       <c r="T110" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【龙门镇】恶人·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【飞沙关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【龙门镇】浩气·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【飞沙关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·恶人大旗",},},},</v>
       </c>
       <c r="U110" t="s">
@@ -43534,7 +43534,7 @@
         <v>1</v>
       </c>
       <c r="T111" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="龙门镇·大旗重置",nTime=-2,nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=1465,szName="飞沙关·大旗重置",nTime=-2,nRefresh=7200,key="飞沙关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【龙门镇】大旗重置",nTime=180,nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【飞沙关】大旗重置",nTime=180,nRefresh=7200,key="飞沙关·大旗重置",},},},</v>
       </c>
       <c r="U111" t="s">
@@ -43564,7 +43564,7 @@
         <v>9</v>
       </c>
       <c r="T112" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>},[9]={</v>
       </c>
     </row>
@@ -43588,7 +43588,7 @@
         <v>1</v>
       </c>
       <c r="T113" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【红莲岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【秋雨堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【红莲岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【秋雨堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·恶人大旗",},},},</v>
       </c>
       <c r="U113" t="s">
@@ -43656,7 +43656,7 @@
         <v>1</v>
       </c>
       <c r="T114" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="红莲岗·大旗重置",nTime=-2,nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=1465,szName="秋雨堡·大旗重置",nTime=-2,nRefresh=7200,key="秋雨堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【红莲岗】大旗重置",nTime=180,nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【秋雨堡】大旗重置",nTime=180,nRefresh=7200,key="秋雨堡·大旗重置",},},},</v>
       </c>
       <c r="U114" t="s">
@@ -43686,7 +43686,7 @@
         <v>13</v>
       </c>
       <c r="T115" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>},[13]={</v>
       </c>
     </row>
@@ -43710,7 +43710,7 @@
         <v>1</v>
       </c>
       <c r="T116" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【金门关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="金门关·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【青云坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【金门关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="金门关·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【青云坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·恶人大旗",},},},</v>
       </c>
       <c r="U116" t="s">
@@ -43778,7 +43778,7 @@
         <v>1</v>
       </c>
       <c r="T117" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="金门关·大旗重置",nTime=-2,nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=1465,szName="青云坞·大旗重置",nTime=-2,nRefresh=7200,key="青云坞·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【金门关】大旗重置",nTime=180,nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【青云坞】大旗重置",nTime=180,nRefresh=7200,key="青云坞·大旗重置",},},},</v>
       </c>
       <c r="U117" t="s">
@@ -43808,7 +43808,7 @@
         <v>35</v>
       </c>
       <c r="T118" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>},[35]={</v>
       </c>
     </row>
@@ -43832,7 +43832,7 @@
         <v>1</v>
       </c>
       <c r="T119" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【激流坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【不空关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="不空关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【激流坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【不空关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="不空关·恶人大旗",},},},</v>
       </c>
       <c r="U119" t="s">
@@ -43900,7 +43900,7 @@
         <v>1</v>
       </c>
       <c r="T120" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="激流坞·大旗重置",nTime=-2,nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=1465,szName="不空关·大旗重置",nTime=-2,nRefresh=7200,key="不空关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【激流坞】大旗重置",nTime=180,nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【不空关】大旗重置",nTime=180,nRefresh=7200,key="不空关·大旗重置",},},},</v>
       </c>
       <c r="U120" t="s">
@@ -43930,7 +43930,7 @@
         <v>100</v>
       </c>
       <c r="T121" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>},[100]={</v>
       </c>
     </row>
@@ -43954,7 +43954,7 @@
         <v>1</v>
       </c>
       <c r="T122" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【日月崖】恶人·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【卧龙坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【日月崖】浩气·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【卧龙坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·恶人大旗",},},},</v>
       </c>
       <c r="U122" t="s">
@@ -44022,7 +44022,7 @@
         <v>1</v>
       </c>
       <c r="T123" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="日月崖·大旗重置",nTime=-2,nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=1465,szName="卧龙坡·大旗重置",nTime=-2,nRefresh=7200,key="卧龙坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【日月崖】大旗重置",nTime=180,nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【卧龙坡】大旗重置",nTime=180,nRefresh=7200,key="卧龙坡·大旗重置",},},},</v>
       </c>
       <c r="U123" t="s">
@@ -44052,7 +44052,7 @@
         <v>101</v>
       </c>
       <c r="T124" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>},[101]={</v>
       </c>
     </row>
@@ -44076,7 +44076,7 @@
         <v>1</v>
       </c>
       <c r="T125" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【霜戈堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【澜沧城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【霜戈堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【澜沧城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·恶人大旗",},},},</v>
       </c>
       <c r="U125" t="s">
@@ -44144,7 +44144,7 @@
         <v>1</v>
       </c>
       <c r="T126" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="霜戈堡·大旗重置",nTime=-2,nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=1465,szName="澜沧城·大旗重置",nTime=-2,nRefresh=7200,key="澜沧城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【霜戈堡】大旗重置",nTime=180,nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【澜沧城】大旗重置",nTime=180,nRefresh=7200,key="澜沧城·大旗重置",},},},</v>
       </c>
       <c r="U126" t="s">
@@ -44174,7 +44174,7 @@
         <v>103</v>
       </c>
       <c r="T127" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>},[103]={</v>
       </c>
     </row>
@@ -44198,7 +44198,7 @@
         <v>1</v>
       </c>
       <c r="T128" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【神池岭】恶人·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【烈日岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【神池岭】浩气·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【烈日岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·恶人大旗",},},},</v>
       </c>
       <c r="U128" t="s">
@@ -44266,7 +44266,7 @@
         <v>1</v>
       </c>
       <c r="T129" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="神池岭·大旗重置",nTime=-2,nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=1465,szName="烈日岗·大旗重置",nTime=-2,nRefresh=7200,key="烈日岗·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【神池岭】大旗重置",nTime=180,nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【烈日岗】大旗重置",nTime=180,nRefresh=7200,key="烈日岗·大旗重置",},},},</v>
       </c>
       <c r="U129" t="s">
@@ -44296,7 +44296,7 @@
         <v>104</v>
       </c>
       <c r="T130" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>},[104]={</v>
       </c>
     </row>
@@ -44320,7 +44320,7 @@
         <v>1</v>
       </c>
       <c r="T131" t="str">
-        <f t="shared" ref="T131:T150" si="2">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(C131),ISBLANK(L131),ISBLANK(M131),OR(ISBLANK(B130)=FALSE,ISBLANK(C130)=FALSE,ISBLANK(L130)=FALSE,ISBLANK(M130)=FALSE)),"},},}",IF(ISBLANK(C131),"","{szContent="""&amp;C131&amp;""","&amp;IF(D131&lt;&gt;"","szNote="""&amp;D131&amp;""",","")&amp;IF(K131&lt;&gt;"","col={"&amp;K131&amp;"},","")&amp;IF(L131&gt;0,"bSearch=true,","")&amp;IF(M131&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N131&gt;0,"szVoice="""&amp;N131&amp;""",","")&amp;IF(O131&gt;0,"bTeamChannel=true,","")&amp;IF(P131&gt;0,"bWhisperChannel=true,","")&amp;IF(Q131&gt;0,"bCenterAlarm=true,","")&amp;IF(R131&gt;0,"bScreenHead=true,","")&amp;IF(S131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U131:AAF131)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="T131:T150" si="4">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(C131),ISBLANK(L131),ISBLANK(M131),OR(ISBLANK(B130)=FALSE,ISBLANK(C130)=FALSE,ISBLANK(L130)=FALSE,ISBLANK(M130)=FALSE)),"},},}",IF(ISBLANK(C131),"","{szContent="""&amp;C131&amp;""","&amp;IF(D131&lt;&gt;"","szNote="""&amp;D131&amp;""",","")&amp;IF(K131&lt;&gt;"","col={"&amp;K131&amp;"},","")&amp;IF(L131&gt;0,"bSearch=true,","")&amp;IF(M131&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N131&gt;0,"szVoice="""&amp;N131&amp;""",","")&amp;IF(O131&gt;0,"bTeamChannel=true,","")&amp;IF(P131&gt;0,"bWhisperChannel=true,","")&amp;IF(Q131&gt;0,"bCenterAlarm=true,","")&amp;IF(R131&gt;0,"bScreenHead=true,","")&amp;IF(S131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U131:AAF131)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凤鸣堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【惊虬谷】恶人·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凤鸣堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【惊虬谷】浩气·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·恶人大旗",},},},</v>
       </c>
       <c r="U131" t="s">
@@ -44388,7 +44388,7 @@
         <v>1</v>
       </c>
       <c r="T132" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凤鸣堡·大旗重置",nTime=-2,nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=1465,szName="惊虬谷·大旗重置",nTime=-2,nRefresh=7200,key="惊虬谷·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凤鸣堡】大旗重置",nTime=180,nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【惊虬谷】大旗重置",nTime=180,nRefresh=7200,key="惊虬谷·大旗重置",},},},</v>
       </c>
       <c r="U132" t="s">
@@ -44418,7 +44418,7 @@
         <v>105</v>
       </c>
       <c r="T133" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>},[105]={</v>
       </c>
     </row>
@@ -44442,7 +44442,7 @@
         <v>1</v>
       </c>
       <c r="T134" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【大理山城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【千岩关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【大理山城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【千岩关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·恶人大旗",},},},</v>
       </c>
       <c r="U134" t="s">
@@ -44510,7 +44510,7 @@
         <v>1</v>
       </c>
       <c r="T135" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="大理山城·大旗重置",nTime=-2,nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=1465,szName="千岩关·大旗重置",nTime=-2,nRefresh=7200,key="千岩关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【大理山城】大旗重置",nTime=180,nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【千岩关】大旗重置",nTime=180,nRefresh=7200,key="千岩关·大旗重置",},},},</v>
       </c>
       <c r="U135" t="s">
@@ -44540,7 +44540,7 @@
         <v>139</v>
       </c>
       <c r="T136" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>},[139]={</v>
       </c>
     </row>
@@ -44564,7 +44564,7 @@
         <v>1</v>
       </c>
       <c r="T137" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【枫湖寨】恶人·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【啖杏林】恶人·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【枫湖寨】浩气·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【啖杏林】浩气·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·恶人大旗",},},},</v>
       </c>
       <c r="U137" t="s">
@@ -44632,7 +44632,7 @@
         <v>1</v>
       </c>
       <c r="T138" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="枫湖寨·大旗重置",nTime=-2,nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=1465,szName="啖杏林·大旗重置",nTime=-2,nRefresh=7200,key="啖杏林·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【枫湖寨】大旗重置",nTime=180,nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【啖杏林】大旗重置",nTime=180,nRefresh=7200,key="啖杏林·大旗重置",},},},</v>
       </c>
       <c r="U138" t="s">
@@ -44662,7 +44662,7 @@
         <v>153</v>
       </c>
       <c r="T139" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>},[153]={</v>
       </c>
     </row>
@@ -44686,7 +44686,7 @@
         <v>1</v>
       </c>
       <c r="T140" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【扶风郡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【世外坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【扶风郡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【世外坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U140" t="s">
@@ -44754,7 +44754,7 @@
         <v>1</v>
       </c>
       <c r="T141" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="扶风郡·大旗重置",nTime=-2,nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=1465,szName="世外坡·大旗重置",nTime=-2,nRefresh=7200,key="世外坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【扶风郡】大旗重置",nTime=180,nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【世外坡】大旗重置",nTime=180,nRefresh=7200,key="世外坡·大旗重置",},},},</v>
       </c>
       <c r="U141" t="s">
@@ -44784,7 +44784,7 @@
         <v>216</v>
       </c>
       <c r="T142" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>},[216]={</v>
       </c>
     </row>
@@ -44808,7 +44808,7 @@
         <v>1</v>
       </c>
       <c r="T143" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U143" t="s">
@@ -44844,7 +44844,7 @@
         <v>1</v>
       </c>
       <c r="T144" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime=180,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime=180,nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U144" t="s">
@@ -44880,7 +44880,7 @@
         <v>1</v>
       </c>
       <c r="T145" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U145" t="s">
@@ -44907,7 +44907,7 @@
         <v>656</v>
       </c>
       <c r="T146" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>},[656]={</v>
       </c>
     </row>
@@ -44931,7 +44931,7 @@
         <v>1</v>
       </c>
       <c r="T147" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U147" t="s">
@@ -44967,7 +44967,7 @@
         <v>1</v>
       </c>
       <c r="T148" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime=180,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime=180,nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U148" t="s">
@@ -45003,7 +45003,7 @@
         <v>1</v>
       </c>
       <c r="T149" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U149" t="s">
@@ -45024,7 +45024,7 @@
     </row>
     <row r="150" spans="1:26">
       <c r="T150" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>},},}</v>
       </c>
     </row>

--- a/阵营/大小攻防团队监控.xlsx
+++ b/阵营/大小攻防团队监控.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="4"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据总控" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">不利气劲!$A$1:$BY$98</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">系统角色!$A$1:$X$414</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">角色喊话!$A$1:$AV$197</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">系统频道!$A$1:$BG$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">系统频道!$A$1:$BG$154</definedName>
     <definedName name="JunSun1" localSheetId="6">DATE(交互物件!日历年份,6,1)-WEEKDAY(DATE(交互物件!日历年份,6,1))</definedName>
     <definedName name="JunSun1" localSheetId="4">DATE(武学招式!日历年份,6,1)-WEEKDAY(DATE(武学招式!日历年份,6,1))</definedName>
     <definedName name="JunSun1" localSheetId="5">DATE(系统角色!日历年份,6,1)-WEEKDAY(DATE(系统角色!日历年份,6,1))</definedName>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5910" uniqueCount="2697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5932" uniqueCount="2703">
   <si>
     <t>__meta = {</t>
   </si>
@@ -7627,6 +7627,9 @@
     <t>阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n</t>
   </si>
   <si>
+    <t>据点攻防·阴山大草原·分线·正式开始</t>
+  </si>
+  <si>
     <t>{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},</t>
   </si>
   <si>
@@ -7636,19 +7639,37 @@
     <t>前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n</t>
   </si>
   <si>
+    <t>据点攻防·阴山大草原</t>
+  </si>
+  <si>
     <t>{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},</t>
   </si>
   <si>
     <t>逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n</t>
   </si>
   <si>
+    <t>据点攻防·阴山大草原·开启分线·5分钟</t>
+  </si>
+  <si>
     <t>{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},</t>
   </si>
   <si>
+    <t>阵营攻防首领战紧张火热，本服今日无奇袭场分线模式，请侠士速速前往主战场及奇袭场参与活动。\n</t>
+  </si>
+  <si>
+    <t>阵营攻防·奇袭场·未开分线</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·未开分线",nTime=30,key="分流活动",},</t>
+  </si>
+  <si>
     <t>阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n</t>
   </si>
   <si>
-    <t>{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·分线·开启",nTime=30,nRefresh=10,key="分流活动",},</t>
+    <t>阵营攻防·奇袭场·开启分线</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·开启分线",nTime=30,nRefresh=10,key="分流活动",},</t>
   </si>
   <si>
     <t>{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,key="{$3}·浩气大旗",},</t>
@@ -7679,9 +7700,6 @@
   </si>
   <si>
     <t>{nClass=20,nIcon=13,szName="离开据点·大旗重置",nTime=0,key="离开据点·大旗重置",},</t>
-  </si>
-  <si>
-    <t>据点攻防·5分钟·开启分线</t>
   </si>
   <si>
     <t>前线据点之争已经打响，争夺正式开始，沙盘地图（CTRL + M）绘有详细战略意图，谁将称霸中原，我们拭目以待！\n</t>
@@ -9470,7 +9488,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="34" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1781614909000,</v>
+        <v>nTimeStamp = 1781955736000,</v>
       </c>
       <c r="B4" s="38" t="s">
         <v>11</v>
@@ -11213,10 +11231,10 @@
         <v>1817</v>
       </c>
       <c r="B3" t="s">
-        <v>2561</v>
+        <v>2567</v>
       </c>
       <c r="C3" t="s">
-        <v>2669</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -11224,10 +11242,10 @@
         <v>1837</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2578</v>
+        <v>2584</v>
       </c>
       <c r="C4" t="s">
-        <v>2670</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -11235,10 +11253,10 @@
         <v>1844</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2589</v>
+        <v>2595</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>2671</v>
+        <v>2677</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -11246,10 +11264,10 @@
         <v>1848</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2590</v>
+        <v>2596</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2672</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -11257,10 +11275,10 @@
         <v>1856</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2595</v>
+        <v>2601</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>2673</v>
+        <v>2679</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -11268,10 +11286,10 @@
         <v>1860</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2596</v>
+        <v>2602</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>2674</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -11279,10 +11297,10 @@
         <v>1873</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2601</v>
+        <v>2607</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>2675</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -11290,10 +11308,10 @@
         <v>1877</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2602</v>
+        <v>2608</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>2676</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -11301,10 +11319,10 @@
         <v>1881</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2607</v>
+        <v>2613</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>2677</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -11312,10 +11330,10 @@
         <v>1885</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2608</v>
+        <v>2614</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>2678</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -11323,10 +11341,10 @@
         <v>1889</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2613</v>
+        <v>2619</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>2679</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -11334,10 +11352,10 @@
         <v>1893</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>2614</v>
+        <v>2620</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>2680</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -11345,10 +11363,10 @@
         <v>1899</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>2619</v>
+        <v>2625</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>2681</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -11356,10 +11374,10 @@
         <v>1903</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2620</v>
+        <v>2626</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>2682</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -11367,10 +11385,10 @@
         <v>1907</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2625</v>
+        <v>2631</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>2683</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -11378,10 +11396,10 @@
         <v>1911</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>2626</v>
+        <v>2632</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>2684</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -11389,10 +11407,10 @@
         <v>1917</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>2631</v>
+        <v>2637</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>2685</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -11400,10 +11418,10 @@
         <v>1921</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2632</v>
+        <v>2638</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>2686</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -11411,10 +11429,10 @@
         <v>1925</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>2637</v>
+        <v>2643</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>2687</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -11422,10 +11440,10 @@
         <v>1929</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2638</v>
+        <v>2644</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>2688</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -11433,10 +11451,10 @@
         <v>1933</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>2643</v>
+        <v>2649</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>2689</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -11444,10 +11462,10 @@
         <v>1937</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2644</v>
+        <v>2650</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>2690</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -11455,10 +11473,10 @@
         <v>1945</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2649</v>
+        <v>2655</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>2691</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -11466,10 +11484,10 @@
         <v>1949</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2650</v>
+        <v>2656</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>2692</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -11477,10 +11495,10 @@
         <v>1953</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2655</v>
+        <v>2661</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>2693</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -11488,10 +11506,10 @@
         <v>1957</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2656</v>
+        <v>2662</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2694</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -11499,10 +11517,10 @@
         <v>1978</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2662</v>
+        <v>2668</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2695</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -11510,10 +11528,10 @@
         <v>1982</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>2663</v>
+        <v>2669</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>2696</v>
+        <v>2702</v>
       </c>
     </row>
   </sheetData>
@@ -41317,7 +41335,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH151"/>
+  <dimension ref="A1:AH154"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="88" customWidth="1"/>
@@ -42425,110 +42443,116 @@
       <c r="C44" t="s">
         <v>2521</v>
       </c>
+      <c r="D44" t="s">
+        <v>2522</v>
+      </c>
       <c r="K44" t="s">
         <v>1656</v>
       </c>
       <c r="T44" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
+        <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",szNote="据点攻防·阴山大草原·分线·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U44" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="V44" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="45" spans="1:26">
       <c r="C45" t="s">
-        <v>2524</v>
+        <v>2525</v>
+      </c>
+      <c r="D45" t="s">
+        <v>2526</v>
       </c>
       <c r="K45" t="s">
         <v>1656</v>
       </c>
       <c r="T45" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
+        <v>{szContent="前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n",szNote="据点攻防·阴山大草原",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U45" t="s">
-        <v>2525</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="46" spans="1:26">
       <c r="C46" t="s">
-        <v>2526</v>
+        <v>2528</v>
+      </c>
+      <c r="D46" t="s">
+        <v>2529</v>
       </c>
       <c r="K46" t="s">
         <v>1656</v>
       </c>
       <c r="T46" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
+        <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·阴山大草原·开启分线·5分钟",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U46" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="V46" t="s">
-        <v>2527</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="47" spans="1:26">
       <c r="C47" t="s">
-        <v>2528</v>
+        <v>2531</v>
+      </c>
+      <c r="D47" t="s">
+        <v>2532</v>
       </c>
       <c r="K47" t="s">
         <v>1656</v>
       </c>
       <c r="T47" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·分线·开启",nTime=30,nRefresh=10,key="分流活动",},},},</v>
+        <v>{szContent="阵营攻防首领战紧张火热，本服今日无奇袭场分线模式，请侠士速速前往主战场及奇袭场参与活动。\n",szNote="阵营攻防·奇袭场·未开分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·未开分线",nTime=30,key="分流活动",},},},</v>
       </c>
       <c r="U47" t="s">
-        <v>2529</v>
-      </c>
-    </row>
-    <row r="48" s="2" customFormat="1" spans="1:26">
-      <c r="A48" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="B48" s="2">
-        <v>-7</v>
+        <v>2533</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26">
+      <c r="C48" t="s">
+        <v>2534</v>
+      </c>
+      <c r="D48" t="s">
+        <v>2535</v>
+      </c>
+      <c r="K48" t="s">
+        <v>1656</v>
       </c>
       <c r="T48" t="str">
         <f t="shared" si="1"/>
-        <v>},[-7]={</v>
-      </c>
-    </row>
-    <row r="49" customFormat="1" spans="1:26">
-      <c r="C49" t="s">
-        <v>2493</v>
-      </c>
-      <c r="D49" t="s">
-        <v>2494</v>
-      </c>
-      <c r="K49" t="s">
-        <v>1656</v>
-      </c>
-      <c r="M49">
-        <v>1</v>
-      </c>
-      <c r="Q49">
-        <v>1</v>
+        <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",szNote="阵营攻防·奇袭场·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·开启分线",nTime=30,nRefresh=10,key="分流活动",},},},</v>
+      </c>
+      <c r="U48" t="s">
+        <v>2536</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" spans="1:26">
+      <c r="A49" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B49" s="2">
+        <v>-7</v>
       </c>
       <c r="T49" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
-      </c>
-      <c r="U49" t="s">
-        <v>2495</v>
-      </c>
-    </row>
-    <row r="50" spans="1:26">
+        <v>},[-7]={</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" spans="1:26">
       <c r="C50" t="s">
-        <v>2496</v>
+        <v>2493</v>
       </c>
       <c r="D50" t="s">
-        <v>2497</v>
+        <v>2494</v>
       </c>
       <c r="K50" t="s">
         <v>1656</v>
@@ -42536,32 +42560,23 @@
       <c r="M50">
         <v>1</v>
       </c>
+      <c r="Q50">
+        <v>1</v>
+      </c>
       <c r="T50" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,key="{$3}·恶人大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气占领",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人占领",},{nClass=20,nIcon=13,szName="{$3}·{$1}占领",nTime=-1,key="{$3}·{$1}占领",},},},</v>
+        <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U50" t="s">
-        <v>2530</v>
-      </c>
-      <c r="V50" t="s">
-        <v>2531</v>
-      </c>
-      <c r="W50" t="s">
-        <v>2532</v>
-      </c>
-      <c r="X50" t="s">
-        <v>2533</v>
-      </c>
-      <c r="Y50" t="s">
-        <v>2534</v>
-      </c>
-    </row>
-    <row r="51" customFormat="1" spans="1:26">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="51" spans="1:26">
       <c r="C51" t="s">
-        <v>2503</v>
+        <v>2496</v>
       </c>
       <c r="D51" t="s">
-        <v>2504</v>
+        <v>2497</v>
       </c>
       <c r="K51" t="s">
         <v>1656</v>
@@ -42571,304 +42586,316 @@
       </c>
       <c r="T51" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
+        <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,key="{$3}·恶人大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气占领",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人占领",},{nClass=20,nIcon=13,szName="{$3}·{$1}占领",nTime=-1,key="{$3}·{$1}占领",},},},</v>
       </c>
       <c r="U51" t="s">
-        <v>2505</v>
+        <v>2537</v>
       </c>
       <c r="V51" t="s">
-        <v>2506</v>
+        <v>2538</v>
       </c>
       <c r="W51" t="s">
-        <v>2507</v>
+        <v>2539</v>
       </c>
       <c r="X51" t="s">
-        <v>2508</v>
+        <v>2540</v>
       </c>
       <c r="Y51" t="s">
-        <v>2509</v>
-      </c>
-      <c r="Z51" t="s">
-        <v>2510</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="52" customFormat="1" spans="1:26">
       <c r="C52" t="s">
-        <v>2406</v>
+        <v>2503</v>
       </c>
       <c r="D52" t="s">
-        <v>2407</v>
+        <v>2504</v>
       </c>
       <c r="K52" t="s">
-        <v>2121</v>
+        <v>1656</v>
+      </c>
+      <c r="M52">
+        <v>1</v>
       </c>
       <c r="T52" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U52" t="s">
-        <v>2408</v>
+        <v>2505</v>
+      </c>
+      <c r="V52" t="s">
+        <v>2506</v>
+      </c>
+      <c r="W52" t="s">
+        <v>2507</v>
+      </c>
+      <c r="X52" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>2509</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>2510</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:26">
       <c r="C53" t="s">
-        <v>2409</v>
+        <v>2406</v>
       </c>
       <c r="D53" t="s">
-        <v>2410</v>
+        <v>2407</v>
       </c>
       <c r="K53" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="T53" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
+        <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U53" t="s">
-        <v>2411</v>
-      </c>
-    </row>
-    <row r="54" spans="1:26">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" spans="1:26">
       <c r="C54" t="s">
-        <v>2535</v>
+        <v>2409</v>
+      </c>
+      <c r="D54" t="s">
+        <v>2410</v>
       </c>
       <c r="K54" t="s">
-        <v>1656</v>
+        <v>2120</v>
       </c>
       <c r="T54" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="本场贡献值进入前1200名，额外获得3000威名，可通过邮件领取\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=6,szName="攻防进入前1200名",nTime=10,key="阵营活动",},},},</v>
+        <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U54" t="s">
-        <v>2536</v>
-      </c>
-    </row>
-    <row r="55" customFormat="1" spans="1:26">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="55" spans="1:26">
       <c r="C55" t="s">
-        <v>2514</v>
-      </c>
-      <c r="D55" t="s">
-        <v>2515</v>
+        <v>2542</v>
       </c>
       <c r="K55" t="s">
         <v>1656</v>
       </c>
       <c r="T55" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=20,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=20,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=20,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=20,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=20,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=20,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=20,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=20,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=20,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
+        <v>{szContent="本场贡献值进入前1200名，额外获得3000威名，可通过邮件领取\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=6,szName="攻防进入前1200名",nTime=10,key="阵营活动",},},},</v>
       </c>
       <c r="U55" t="s">
-        <v>2516</v>
-      </c>
-      <c r="V55" s="5" t="s">
-        <v>2436</v>
-      </c>
-      <c r="W55" s="5" t="s">
-        <v>2437</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:26">
       <c r="C56" t="s">
-        <v>2433</v>
+        <v>2514</v>
       </c>
       <c r="D56" t="s">
-        <v>2434</v>
+        <v>2515</v>
       </c>
       <c r="K56" t="s">
         <v>1656</v>
       </c>
       <c r="T56" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
+        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=20,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=20,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=20,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=20,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=20,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=20,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=20,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=20,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=20,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="U56" t="s">
-        <v>2435</v>
-      </c>
-      <c r="V56" s="7"/>
+        <v>2516</v>
+      </c>
+      <c r="V56" s="5" t="s">
+        <v>2436</v>
+      </c>
+      <c r="W56" s="5" t="s">
+        <v>2437</v>
+      </c>
     </row>
     <row r="57" customFormat="1" spans="1:26">
       <c r="C57" t="s">
-        <v>2511</v>
+        <v>2433</v>
       </c>
       <c r="D57" t="s">
-        <v>2512</v>
+        <v>2434</v>
       </c>
       <c r="K57" t="s">
         <v>1656</v>
       </c>
-      <c r="Q57">
-        <v>1</v>
-      </c>
       <c r="T57" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
+        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U57" t="s">
-        <v>2513</v>
-      </c>
-    </row>
-    <row r="58" spans="1:26">
+        <v>2435</v>
+      </c>
+      <c r="V57" s="7"/>
+    </row>
+    <row r="58" customFormat="1" spans="1:26">
       <c r="C58" t="s">
-        <v>2517</v>
+        <v>2511</v>
       </c>
       <c r="D58" t="s">
-        <v>2518</v>
+        <v>2512</v>
       </c>
       <c r="K58" t="s">
         <v>1656</v>
       </c>
+      <c r="Q58">
+        <v>1</v>
+      </c>
       <c r="T58" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=13,szName="狼牙先锋首领",nTime=0,key="狼牙先锋首领",},{nClass=20,nIcon=13,szName="离开据点·大旗重置",nTime=0,key="离开据点·大旗重置",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
+        <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U58" t="s">
-        <v>2537</v>
-      </c>
-      <c r="V58" t="s">
-        <v>2538</v>
-      </c>
-      <c r="W58" t="s">
-        <v>2539</v>
-      </c>
-      <c r="X58" s="6" t="s">
-        <v>2520</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="59" spans="1:26">
       <c r="C59" t="s">
-        <v>2521</v>
+        <v>2517</v>
+      </c>
+      <c r="D59" t="s">
+        <v>2518</v>
       </c>
       <c r="K59" t="s">
         <v>1656</v>
       </c>
       <c r="T59" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
+        <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=13,szName="狼牙先锋首领",nTime=0,key="狼牙先锋首领",},{nClass=20,nIcon=13,szName="离开据点·大旗重置",nTime=0,key="离开据点·大旗重置",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U59" t="s">
-        <v>2522</v>
+        <v>2544</v>
       </c>
       <c r="V59" t="s">
-        <v>2523</v>
+        <v>2545</v>
+      </c>
+      <c r="W59" t="s">
+        <v>2546</v>
+      </c>
+      <c r="X59" s="6" t="s">
+        <v>2520</v>
       </c>
     </row>
     <row r="60" spans="1:26">
       <c r="C60" t="s">
-        <v>2526</v>
+        <v>2521</v>
       </c>
       <c r="D60" t="s">
-        <v>2540</v>
+        <v>2522</v>
       </c>
       <c r="K60" t="s">
         <v>1656</v>
       </c>
       <c r="T60" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·5分钟·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
+        <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",szNote="据点攻防·阴山大草原·分线·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U60" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="V60" t="s">
-        <v>2527</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="61" spans="1:26">
       <c r="C61" t="s">
-        <v>2541</v>
+        <v>2528</v>
       </c>
       <c r="D61" t="s">
-        <v>2284</v>
+        <v>2529</v>
       </c>
       <c r="K61" t="s">
         <v>1656</v>
       </c>
       <c r="T61" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="前线据点之争已经打响，争夺正式开始，沙盘地图（CTRL + M）绘有详细战略意图，谁将称霸中原，我们拭目以待！\n",szNote="据点攻防·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime=10,key="阵营活动",},},},</v>
+        <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·阴山大草原·开启分线·5分钟",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U61" t="s">
-        <v>2542</v>
+        <v>2523</v>
+      </c>
+      <c r="V61" t="s">
+        <v>2530</v>
       </c>
     </row>
     <row r="62" spans="1:26">
       <c r="C62" t="s">
-        <v>2528</v>
+        <v>2547</v>
+      </c>
+      <c r="D62" t="s">
+        <v>2284</v>
       </c>
       <c r="K62" t="s">
         <v>1656</v>
       </c>
       <c r="T62" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·分线·开启",nTime=30,nRefresh=10,key="分流活动",},},},</v>
+        <v>{szContent="前线据点之争已经打响，争夺正式开始，沙盘地图（CTRL + M）绘有详细战略意图，谁将称霸中原，我们拭目以待！\n",szNote="据点攻防·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime=10,key="阵营活动",},},},</v>
       </c>
       <c r="U62" t="s">
-        <v>2529</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:26">
-      <c r="A63" t="s">
-        <v>1488</v>
-      </c>
-      <c r="B63">
-        <v>-20</v>
+      <c r="C63" t="s">
+        <v>2531</v>
+      </c>
+      <c r="D63" t="s">
+        <v>2532</v>
+      </c>
+      <c r="K63" t="s">
+        <v>1656</v>
       </c>
       <c r="T63" t="str">
         <f t="shared" si="1"/>
-        <v>},[-20]={</v>
+        <v>{szContent="阵营攻防首领战紧张火热，本服今日无奇袭场分线模式，请侠士速速前往主战场及奇袭场参与活动。\n",szNote="阵营攻防·奇袭场·未开分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·未开分线",nTime=30,key="分流活动",},},},</v>
+      </c>
+      <c r="U63" t="s">
+        <v>2533</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:26">
       <c r="C64" t="s">
-        <v>2543</v>
+        <v>2534</v>
       </c>
       <c r="D64" t="s">
-        <v>2544</v>
+        <v>2535</v>
       </c>
       <c r="K64" t="s">
         <v>1656</v>
       </c>
-      <c r="M64">
-        <v>1</v>
-      </c>
       <c r="T64" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
+        <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",szNote="阵营攻防·奇袭场·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·开启分线",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
       <c r="U64" t="s">
-        <v>2545</v>
-      </c>
-      <c r="V64" t="s">
-        <v>2546</v>
-      </c>
-      <c r="W64" t="s">
-        <v>2547</v>
-      </c>
-      <c r="X64" t="s">
-        <v>2548</v>
-      </c>
-      <c r="Y64" t="s">
-        <v>2549</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:26">
       <c r="A65" t="s">
-        <v>2232</v>
+        <v>1488</v>
       </c>
       <c r="B65">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="T65" t="str">
         <f t="shared" si="1"/>
-        <v>},[-21]={</v>
+        <v>},[-20]={</v>
       </c>
     </row>
     <row r="66" customFormat="1" spans="1:26">
       <c r="C66" t="s">
-        <v>2493</v>
+        <v>2549</v>
       </c>
       <c r="D66" t="s">
-        <v>2494</v>
+        <v>2550</v>
       </c>
       <c r="K66" t="s">
         <v>1656</v>
@@ -42878,51 +42905,42 @@
       </c>
       <c r="T66" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
+        <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U66" t="s">
-        <v>2495</v>
+        <v>2551</v>
+      </c>
+      <c r="V66" t="s">
+        <v>2552</v>
+      </c>
+      <c r="W66" t="s">
+        <v>2553</v>
+      </c>
+      <c r="X66" t="s">
+        <v>2554</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>2555</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:26">
-      <c r="C67" t="s">
-        <v>2496</v>
-      </c>
-      <c r="D67" t="s">
-        <v>2497</v>
-      </c>
-      <c r="K67" t="s">
-        <v>1656</v>
-      </c>
-      <c r="M67">
-        <v>1</v>
+      <c r="A67" t="s">
+        <v>2232</v>
+      </c>
+      <c r="B67">
+        <v>-21</v>
       </c>
       <c r="T67" t="str">
         <f t="shared" ref="T67:T98" si="2">IF(ISBLANK(B67)=FALSE,IF(ISBLANK(B66),"},["&amp;B67&amp;"]={","["&amp;B67&amp;"]={"),IF(AND(ISBLANK(B67),ISBLANK(C67),ISBLANK(L67),ISBLANK(M67),OR(ISBLANK(B66)=FALSE,ISBLANK(C66)=FALSE,ISBLANK(L66)=FALSE,ISBLANK(M66)=FALSE)),"},},}",IF(ISBLANK(C67),"","{szContent="""&amp;C67&amp;""","&amp;IF(D67&lt;&gt;"","szNote="""&amp;D67&amp;""",","")&amp;IF(K67&lt;&gt;"","col={"&amp;K67&amp;"},","")&amp;IF(L67&gt;0,"bSearch=true,","")&amp;IF(M67&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N67&gt;0,"szVoice="""&amp;N67&amp;""",","")&amp;IF(O67&gt;0,"bTeamChannel=true,","")&amp;IF(P67&gt;0,"bWhisperChannel=true,","")&amp;IF(Q67&gt;0,"bCenterAlarm=true,","")&amp;IF(R67&gt;0,"bScreenHead=true,","")&amp;IF(S67&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U67&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U67:AAF67)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
-      </c>
-      <c r="U67" t="s">
-        <v>2498</v>
-      </c>
-      <c r="V67" t="s">
-        <v>2499</v>
-      </c>
-      <c r="W67" t="s">
-        <v>2500</v>
-      </c>
-      <c r="X67" t="s">
-        <v>2501</v>
-      </c>
-      <c r="Y67" t="s">
-        <v>2502</v>
+        <v>},[-21]={</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="1:26">
       <c r="C68" t="s">
-        <v>2503</v>
+        <v>2493</v>
       </c>
       <c r="D68" t="s">
-        <v>2504</v>
+        <v>2494</v>
       </c>
       <c r="K68" t="s">
         <v>1656</v>
@@ -42932,398 +42950,389 @@
       </c>
       <c r="T68" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
+        <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U68" t="s">
-        <v>2505</v>
-      </c>
-      <c r="V68" t="s">
-        <v>2506</v>
-      </c>
-      <c r="W68" t="s">
-        <v>2507</v>
-      </c>
-      <c r="X68" t="s">
-        <v>2508</v>
-      </c>
-      <c r="Y68" t="s">
-        <v>2509</v>
-      </c>
-      <c r="Z68" t="s">
-        <v>2510</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:26">
       <c r="C69" t="s">
-        <v>2406</v>
+        <v>2496</v>
       </c>
       <c r="D69" t="s">
-        <v>2407</v>
+        <v>2497</v>
       </c>
       <c r="K69" t="s">
-        <v>2121</v>
+        <v>1656</v>
+      </c>
+      <c r="M69">
+        <v>1</v>
       </c>
       <c r="T69" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
+        <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U69" t="s">
-        <v>2408</v>
+        <v>2498</v>
+      </c>
+      <c r="V69" t="s">
+        <v>2499</v>
+      </c>
+      <c r="W69" t="s">
+        <v>2500</v>
+      </c>
+      <c r="X69" t="s">
+        <v>2501</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>2502</v>
       </c>
     </row>
     <row r="70" customFormat="1" spans="1:26">
       <c r="C70" t="s">
-        <v>2409</v>
+        <v>2503</v>
       </c>
       <c r="D70" t="s">
-        <v>2410</v>
+        <v>2504</v>
       </c>
       <c r="K70" t="s">
-        <v>2120</v>
+        <v>1656</v>
+      </c>
+      <c r="M70">
+        <v>1</v>
       </c>
       <c r="T70" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U70" t="s">
-        <v>2411</v>
+        <v>2505</v>
+      </c>
+      <c r="V70" t="s">
+        <v>2506</v>
+      </c>
+      <c r="W70" t="s">
+        <v>2507</v>
+      </c>
+      <c r="X70" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>2509</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>2510</v>
       </c>
     </row>
     <row r="71" customFormat="1" spans="1:26">
       <c r="C71" t="s">
-        <v>2514</v>
+        <v>2406</v>
       </c>
       <c r="D71" t="s">
-        <v>2515</v>
+        <v>2407</v>
       </c>
       <c r="K71" t="s">
-        <v>1656</v>
+        <v>2121</v>
       </c>
       <c r="T71" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
+        <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U71" t="s">
-        <v>2516</v>
-      </c>
-      <c r="V71" s="7"/>
+        <v>2408</v>
+      </c>
     </row>
     <row r="72" customFormat="1" spans="1:26">
       <c r="C72" t="s">
-        <v>2433</v>
+        <v>2409</v>
       </c>
       <c r="D72" t="s">
-        <v>2434</v>
+        <v>2410</v>
       </c>
       <c r="K72" t="s">
-        <v>1656</v>
+        <v>2120</v>
       </c>
       <c r="T72" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
+        <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U72" t="s">
-        <v>2435</v>
-      </c>
-      <c r="V72" s="7"/>
+        <v>2411</v>
+      </c>
     </row>
     <row r="73" customFormat="1" spans="1:26">
       <c r="C73" t="s">
-        <v>2511</v>
+        <v>2514</v>
       </c>
       <c r="D73" t="s">
-        <v>2512</v>
+        <v>2515</v>
       </c>
       <c r="K73" t="s">
         <v>1656</v>
       </c>
-      <c r="Q73">
-        <v>1</v>
-      </c>
       <c r="T73" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
+        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U73" t="s">
-        <v>2513</v>
-      </c>
+        <v>2516</v>
+      </c>
+      <c r="V73" s="7"/>
     </row>
     <row r="74" customFormat="1" spans="1:26">
       <c r="C74" t="s">
-        <v>2517</v>
+        <v>2433</v>
       </c>
       <c r="D74" t="s">
-        <v>2518</v>
+        <v>2434</v>
       </c>
       <c r="K74" t="s">
         <v>1656</v>
       </c>
       <c r="T74" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
+        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U74" t="s">
-        <v>2519</v>
-      </c>
-      <c r="V74" s="6" t="s">
-        <v>2520</v>
-      </c>
+        <v>2435</v>
+      </c>
+      <c r="V74" s="7"/>
     </row>
     <row r="75" customFormat="1" spans="1:26">
       <c r="C75" t="s">
-        <v>2521</v>
+        <v>2511</v>
+      </c>
+      <c r="D75" t="s">
+        <v>2512</v>
       </c>
       <c r="K75" t="s">
         <v>1656</v>
       </c>
+      <c r="Q75">
+        <v>1</v>
+      </c>
       <c r="T75" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
+        <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U75" t="s">
-        <v>2522</v>
-      </c>
-      <c r="V75" t="s">
-        <v>2523</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="76" customFormat="1" spans="1:26">
       <c r="C76" t="s">
-        <v>2524</v>
+        <v>2517</v>
+      </c>
+      <c r="D76" t="s">
+        <v>2518</v>
       </c>
       <c r="K76" t="s">
         <v>1656</v>
       </c>
       <c r="T76" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
+        <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U76" t="s">
-        <v>2525</v>
+        <v>2519</v>
+      </c>
+      <c r="V76" s="6" t="s">
+        <v>2520</v>
       </c>
     </row>
     <row r="77" customFormat="1" spans="1:26">
       <c r="C77" t="s">
-        <v>2526</v>
+        <v>2521</v>
+      </c>
+      <c r="D77" t="s">
+        <v>2522</v>
       </c>
       <c r="K77" t="s">
         <v>1656</v>
       </c>
       <c r="T77" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
+        <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",szNote="据点攻防·阴山大草原·分线·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U77" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="V77" t="s">
-        <v>2527</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="78" customFormat="1" spans="1:26">
       <c r="C78" t="s">
-        <v>2528</v>
+        <v>2525</v>
+      </c>
+      <c r="D78" t="s">
+        <v>2526</v>
       </c>
       <c r="K78" t="s">
         <v>1656</v>
       </c>
       <c r="T78" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·分线·开启",nTime=30,nRefresh=10,key="分流活动",},},},</v>
+        <v>{szContent="前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n",szNote="据点攻防·阴山大草原",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U78" t="s">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="79" customFormat="1" spans="1:26">
+      <c r="C79" t="s">
+        <v>2528</v>
+      </c>
+      <c r="D79" t="s">
         <v>2529</v>
       </c>
-    </row>
-    <row r="79" customFormat="1" spans="1:26">
-      <c r="A79" t="s">
-        <v>2550</v>
-      </c>
-      <c r="B79">
-        <v>-3</v>
+      <c r="K79" t="s">
+        <v>1656</v>
       </c>
       <c r="T79" t="str">
         <f t="shared" si="2"/>
-        <v>},[-3]={</v>
+        <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·阴山大草原·开启分线·5分钟",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
+      </c>
+      <c r="U79" t="s">
+        <v>2523</v>
+      </c>
+      <c r="V79" t="s">
+        <v>2530</v>
       </c>
     </row>
     <row r="80" customFormat="1" spans="1:26">
       <c r="C80" t="s">
-        <v>2486</v>
+        <v>2531</v>
+      </c>
+      <c r="D80" t="s">
+        <v>2532</v>
       </c>
       <c r="K80" t="s">
-        <v>2121</v>
+        <v>1656</v>
       </c>
       <c r="T80" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往恶人谷地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=3,szName="主战场·恶人谷",nTime="1,阵营攻防·开始排队·恶人谷;10,阵营攻防·开始排队·恶人谷",key="大攻防·主战场",},},},</v>
+        <v>{szContent="阵营攻防首领战紧张火热，本服今日无奇袭场分线模式，请侠士速速前往主战场及奇袭场参与活动。\n",szNote="阵营攻防·奇袭场·未开分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·未开分线",nTime=30,key="分流活动",},},},</v>
       </c>
       <c r="U80" t="s">
-        <v>2551</v>
-      </c>
-    </row>
-    <row r="81" customFormat="1" spans="1:30">
+        <v>2533</v>
+      </c>
+    </row>
+    <row r="81" customFormat="1" spans="1:26">
       <c r="C81" t="s">
-        <v>2490</v>
+        <v>2534</v>
+      </c>
+      <c r="D81" t="s">
+        <v>2535</v>
       </c>
       <c r="K81" t="s">
-        <v>2120</v>
+        <v>1656</v>
       </c>
       <c r="T81" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往浩气盟地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=7,szName="主战场·浩气盟",nTime="1,阵营攻防·开始排队·浩气盟;10,阵营攻防·开始排队·浩气盟",key="大攻防·主战场",},},},</v>
+        <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",szNote="阵营攻防·奇袭场·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·开启分线",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
       <c r="U81" t="s">
-        <v>2552</v>
-      </c>
-    </row>
-    <row r="82" customFormat="1" spans="1:30">
+        <v>2536</v>
+      </c>
+    </row>
+    <row r="82" customFormat="1" spans="1:26">
       <c r="A82" t="s">
-        <v>833</v>
+        <v>2556</v>
       </c>
       <c r="B82">
-        <v>74</v>
+        <v>-3</v>
       </c>
       <c r="T82" t="str">
         <f t="shared" si="2"/>
-        <v>},[74]={</v>
-      </c>
-    </row>
-    <row r="83" customFormat="1" spans="1:30">
+        <v>},[-3]={</v>
+      </c>
+    </row>
+    <row r="83" customFormat="1" spans="1:26">
       <c r="C83" t="s">
-        <v>2553</v>
-      </c>
-      <c r="D83" t="s">
-        <v>2554</v>
+        <v>2486</v>
       </c>
       <c r="K83" t="s">
-        <v>1656</v>
+        <v>2121</v>
       </c>
       <c r="T83" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="本场攻防“奇袭场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="奇袭场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2402,nFrame=4,szName="奇袭场·平手",nTime=57,nRefresh=5,key="大攻防·奇袭场",},},},</v>
+        <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往恶人谷地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=3,szName="主战场·恶人谷",nTime="1,阵营攻防·开始排队·恶人谷;10,阵营攻防·开始排队·恶人谷",key="大攻防·主战场",},},},</v>
       </c>
       <c r="U83" t="s">
-        <v>2555</v>
-      </c>
-    </row>
-    <row r="84" customFormat="1" spans="1:30">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="84" customFormat="1" spans="1:26">
       <c r="C84" t="s">
-        <v>2556</v>
-      </c>
-      <c r="D84" t="s">
-        <v>2557</v>
+        <v>2490</v>
       </c>
       <c r="K84" t="s">
-        <v>1656</v>
+        <v>2120</v>
       </c>
       <c r="T84" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="本场攻防“主战场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="主战场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="主战场·平手",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
+        <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往浩气盟地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=7,szName="主战场·浩气盟",nTime="1,阵营攻防·开始排队·浩气盟;10,阵营攻防·开始排队·浩气盟",key="大攻防·主战场",},},},</v>
       </c>
       <c r="U84" t="s">
         <v>2558</v>
       </c>
     </row>
-    <row r="85" customFormat="1" spans="1:30">
-      <c r="C85" t="s">
-        <v>2426</v>
-      </c>
-      <c r="D85" t="s">
-        <v>2427</v>
-      </c>
-      <c r="K85" t="s">
-        <v>1656</v>
-      </c>
-      <c r="M85">
-        <v>1</v>
-      </c>
-      <c r="Q85">
-        <v>1</v>
+    <row r="85" customFormat="1" spans="1:26">
+      <c r="A85" t="s">
+        <v>833</v>
+      </c>
+      <c r="B85">
+        <v>74</v>
       </c>
       <c r="T85" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="^本场攻防“([主战奇袭场]+)”已结束，([浩气盟恶人谷]+)[侠士们众志成城和，]-([大完险胜]+)([浩气盟恶人谷]+)[！，]+",szNote="{$1}·{$2}·{$3}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,szName="大攻防·奇袭场",nTime=-2,nRefresh=10,key="大攻防·奇袭场",},{nClass=20,nIcon=13,szName="大攻防·主战场",nTime=-2,nRefresh=10,key="大攻防·主战场",},{nClass=20,nIcon=13,szName="大攻防·{$1}",nTime=-2,key="大攻防·{$1}",},{nClass=20,nIcon=2402,nFrame=4,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
-      </c>
-      <c r="U85" t="s">
-        <v>2428</v>
-      </c>
-      <c r="V85" t="s">
-        <v>2429</v>
-      </c>
-      <c r="W85" t="s">
-        <v>2430</v>
-      </c>
-      <c r="X85" t="s">
+        <v>},[74]={</v>
+      </c>
+    </row>
+    <row r="86" customFormat="1" spans="1:26">
+      <c r="C86" t="s">
         <v>2559</v>
       </c>
-      <c r="Y85" t="s">
+      <c r="D86" t="s">
         <v>2560</v>
-      </c>
-    </row>
-    <row r="86" customFormat="1" spans="1:30">
-      <c r="C86" t="s">
-        <v>2493</v>
-      </c>
-      <c r="D86" t="s">
-        <v>2494</v>
       </c>
       <c r="K86" t="s">
         <v>1656</v>
       </c>
-      <c r="M86">
-        <v>1</v>
-      </c>
-      <c r="Q86">
-        <v>1</v>
-      </c>
       <c r="T86" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
+        <v>{szContent="本场攻防“奇袭场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="奇袭场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2402,nFrame=4,szName="奇袭场·平手",nTime=57,nRefresh=5,key="大攻防·奇袭场",},},},</v>
       </c>
       <c r="U86" t="s">
-        <v>2495</v>
-      </c>
-    </row>
-    <row r="87" customFormat="1" spans="1:30">
+        <v>2561</v>
+      </c>
+    </row>
+    <row r="87" customFormat="1" spans="1:26">
       <c r="C87" t="s">
-        <v>2496</v>
+        <v>2562</v>
       </c>
       <c r="D87" t="s">
-        <v>2497</v>
+        <v>2563</v>
       </c>
       <c r="K87" t="s">
         <v>1656</v>
       </c>
-      <c r="M87">
-        <v>1</v>
-      </c>
       <c r="T87" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
+        <v>{szContent="本场攻防“主战场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="主战场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="主战场·平手",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U87" t="s">
-        <v>2498</v>
-      </c>
-      <c r="V87" t="s">
-        <v>2499</v>
-      </c>
-      <c r="W87" t="s">
-        <v>2500</v>
-      </c>
-      <c r="X87" t="s">
-        <v>2501</v>
-      </c>
-      <c r="Y87" t="s">
-        <v>2502</v>
-      </c>
-    </row>
-    <row r="88" customFormat="1" spans="1:30">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="88" customFormat="1" spans="1:26">
       <c r="C88" t="s">
-        <v>2503</v>
+        <v>2426</v>
       </c>
       <c r="D88" t="s">
-        <v>2504</v>
+        <v>2427</v>
       </c>
       <c r="K88" t="s">
         <v>1656</v>
@@ -43331,576 +43340,547 @@
       <c r="M88">
         <v>1</v>
       </c>
+      <c r="Q88">
+        <v>1</v>
+      </c>
       <c r="T88" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
+        <v>{szContent="^本场攻防“([主战奇袭场]+)”已结束，([浩气盟恶人谷]+)[侠士们众志成城和，]-([大完险胜]+)([浩气盟恶人谷]+)[！，]+",szNote="{$1}·{$2}·{$3}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,szName="大攻防·奇袭场",nTime=-2,nRefresh=10,key="大攻防·奇袭场",},{nClass=20,nIcon=13,szName="大攻防·主战场",nTime=-2,nRefresh=10,key="大攻防·主战场",},{nClass=20,nIcon=13,szName="大攻防·{$1}",nTime=-2,key="大攻防·{$1}",},{nClass=20,nIcon=2402,nFrame=4,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U88" t="s">
-        <v>2505</v>
+        <v>2428</v>
       </c>
       <c r="V88" t="s">
-        <v>2506</v>
+        <v>2429</v>
       </c>
       <c r="W88" t="s">
-        <v>2507</v>
+        <v>2430</v>
       </c>
       <c r="X88" t="s">
-        <v>2508</v>
+        <v>2565</v>
       </c>
       <c r="Y88" t="s">
-        <v>2509</v>
-      </c>
-      <c r="Z88" t="s">
-        <v>2510</v>
-      </c>
-    </row>
-    <row r="89" customFormat="1" spans="1:30">
+        <v>2566</v>
+      </c>
+    </row>
+    <row r="89" customFormat="1" spans="1:26">
       <c r="C89" t="s">
-        <v>2406</v>
+        <v>2493</v>
       </c>
       <c r="D89" t="s">
-        <v>2407</v>
+        <v>2494</v>
       </c>
       <c r="K89" t="s">
-        <v>2121</v>
+        <v>1656</v>
+      </c>
+      <c r="M89">
+        <v>1</v>
+      </c>
+      <c r="Q89">
+        <v>1</v>
       </c>
       <c r="T89" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
+        <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U89" t="s">
-        <v>2408</v>
-      </c>
-    </row>
-    <row r="90" customFormat="1" spans="1:30">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="90" customFormat="1" spans="1:26">
       <c r="C90" t="s">
-        <v>2409</v>
+        <v>2496</v>
       </c>
       <c r="D90" t="s">
-        <v>2410</v>
+        <v>2497</v>
       </c>
       <c r="K90" t="s">
-        <v>2120</v>
+        <v>1656</v>
+      </c>
+      <c r="M90">
+        <v>1</v>
       </c>
       <c r="T90" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
+        <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U90" t="s">
-        <v>2411</v>
-      </c>
-    </row>
-    <row r="91" customFormat="1" spans="1:30">
+        <v>2498</v>
+      </c>
+      <c r="V90" t="s">
+        <v>2499</v>
+      </c>
+      <c r="W90" t="s">
+        <v>2500</v>
+      </c>
+      <c r="X90" t="s">
+        <v>2501</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="91" customFormat="1" spans="1:26">
       <c r="C91" t="s">
-        <v>2511</v>
+        <v>2503</v>
       </c>
       <c r="D91" t="s">
-        <v>2512</v>
+        <v>2504</v>
       </c>
       <c r="K91" t="s">
         <v>1656</v>
       </c>
-      <c r="Q91">
+      <c r="M91">
         <v>1</v>
       </c>
       <c r="T91" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U91" t="s">
-        <v>2513</v>
-      </c>
-    </row>
-    <row r="92" customFormat="1" spans="1:30">
+        <v>2505</v>
+      </c>
+      <c r="V91" t="s">
+        <v>2506</v>
+      </c>
+      <c r="W91" t="s">
+        <v>2507</v>
+      </c>
+      <c r="X91" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>2509</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="92" customFormat="1" spans="1:26">
       <c r="C92" t="s">
-        <v>2517</v>
+        <v>2406</v>
       </c>
       <c r="D92" t="s">
-        <v>2518</v>
+        <v>2407</v>
       </c>
       <c r="K92" t="s">
-        <v>1656</v>
+        <v>2121</v>
       </c>
       <c r="T92" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
+        <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U92" t="s">
-        <v>2519</v>
-      </c>
-      <c r="V92" s="6" t="s">
-        <v>2520</v>
-      </c>
-    </row>
-    <row r="93" customFormat="1" spans="1:30">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="93" customFormat="1" spans="1:26">
       <c r="C93" t="s">
-        <v>2514</v>
+        <v>2409</v>
       </c>
       <c r="D93" t="s">
-        <v>2515</v>
+        <v>2410</v>
       </c>
       <c r="K93" t="s">
-        <v>1656</v>
+        <v>2120</v>
       </c>
       <c r="T93" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
+        <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U93" t="s">
-        <v>2516</v>
-      </c>
-      <c r="V93" s="7"/>
-    </row>
-    <row r="94" customFormat="1" spans="1:30">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="94" customFormat="1" spans="1:26">
       <c r="C94" t="s">
-        <v>2433</v>
+        <v>2511</v>
       </c>
       <c r="D94" t="s">
-        <v>2434</v>
+        <v>2512</v>
       </c>
       <c r="K94" t="s">
         <v>1656</v>
       </c>
+      <c r="Q94">
+        <v>1</v>
+      </c>
       <c r="T94" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
+        <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U94" t="s">
-        <v>2435</v>
-      </c>
-      <c r="V94" s="7"/>
-    </row>
-    <row r="95" customFormat="1" spans="1:30">
-      <c r="A95" t="s">
-        <v>683</v>
-      </c>
-      <c r="B95">
-        <v>22</v>
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="95" customFormat="1" spans="1:26">
+      <c r="C95" t="s">
+        <v>2517</v>
+      </c>
+      <c r="D95" t="s">
+        <v>2518</v>
+      </c>
+      <c r="K95" t="s">
+        <v>1656</v>
       </c>
       <c r="T95" t="str">
         <f t="shared" si="2"/>
-        <v>},[22]={</v>
-      </c>
-    </row>
-    <row r="96" customFormat="1" spans="1:30">
+        <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
+      </c>
+      <c r="U95" t="s">
+        <v>2519</v>
+      </c>
+      <c r="V95" s="6" t="s">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="96" customFormat="1" spans="1:26">
       <c r="C96" t="s">
-        <v>2503</v>
+        <v>2514</v>
       </c>
       <c r="D96" t="s">
-        <v>2504</v>
-      </c>
-      <c r="G96" t="s">
-        <v>2561</v>
+        <v>2515</v>
       </c>
       <c r="K96" t="s">
         <v>1656</v>
       </c>
-      <c r="M96">
-        <v>1</v>
-      </c>
       <c r="T96" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【武王城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="武王城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【武王城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="武王城·恶人大旗",},},},</v>
+        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U96" t="s">
-        <v>2505</v>
-      </c>
-      <c r="V96" t="str">
-        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G96&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·浩气大旗",},</v>
-      </c>
-      <c r="W96" t="str">
-        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G96&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·恶人大旗",},</v>
-      </c>
-      <c r="X96" t="s">
-        <v>2506</v>
-      </c>
-      <c r="Y96" t="s">
-        <v>2507</v>
-      </c>
-      <c r="Z96" t="s">
-        <v>2562</v>
-      </c>
-      <c r="AA96" t="s">
-        <v>2563</v>
-      </c>
-      <c r="AB96" t="s">
-        <v>2564</v>
-      </c>
-      <c r="AC96" t="str">
-        <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G96&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G96&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【武王城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="武王城·浩气大旗",},</v>
-      </c>
-      <c r="AD96" t="str">
-        <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G96&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G96&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【武王城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="武王城·恶人大旗",},</v>
-      </c>
+        <v>2516</v>
+      </c>
+      <c r="V96" s="7"/>
     </row>
     <row r="97" customFormat="1" spans="1:34">
       <c r="C97" t="s">
-        <v>2565</v>
+        <v>2433</v>
       </c>
       <c r="D97" t="s">
-        <v>2566</v>
+        <v>2434</v>
       </c>
       <c r="K97" t="s">
         <v>1656</v>
       </c>
-      <c r="M97">
-        <v>1</v>
-      </c>
       <c r="T97" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="武王城·大旗重置",nTime=-2,nRefresh=7200,key="武王城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【武王城】大旗重置",nTime="180,【武王城】大旗重置;185,【武王城】大旗重置·结束",nRefresh=7200,key="武王城·大旗重置",},},},</v>
+        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U97" t="s">
-        <v>2567</v>
-      </c>
-      <c r="V97" t="s">
-        <v>2568</v>
-      </c>
-      <c r="W97" t="s">
-        <v>2569</v>
-      </c>
-      <c r="X97" t="s">
-        <v>2570</v>
-      </c>
+        <v>2435</v>
+      </c>
+      <c r="V97" s="7"/>
     </row>
     <row r="98" customFormat="1" spans="1:34">
-      <c r="C98" t="s">
-        <v>2442</v>
-      </c>
-      <c r="K98" t="s">
-        <v>1656</v>
+      <c r="A98" t="s">
+        <v>683</v>
+      </c>
+      <c r="B98">
+        <v>22</v>
       </c>
       <c r="T98" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="本场浩气盟攻防即将结束，南屏山物资运送暂且休整，等待下一场攻防开启！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="粮草先行·活动结束",nTime=5,key="粮草先行·浩气盟",},{nClass=20,nIcon=13,szName="粮草先行·恶人谷",nTime=0,key="粮草先行·恶人谷",},{nClass=20,nIcon=589,nFrame=7,szName="赵新宇",nTime="60,赵新宇·刷新剩余;62,赵新宇·即将刷新",nRefresh=0,key="赵新宇",},},},</v>
-      </c>
-      <c r="U98" t="s">
-        <v>2571</v>
-      </c>
-      <c r="V98" t="s">
-        <v>2572</v>
-      </c>
-      <c r="W98" t="s">
-        <v>2573</v>
+        <v>},[22]={</v>
       </c>
     </row>
     <row r="99" customFormat="1" spans="1:34">
       <c r="C99" t="s">
-        <v>2574</v>
+        <v>2503</v>
+      </c>
+      <c r="D99" t="s">
+        <v>2504</v>
+      </c>
+      <c r="G99" t="s">
+        <v>2567</v>
       </c>
       <c r="K99" t="s">
-        <v>2121</v>
+        <v>1656</v>
+      </c>
+      <c r="M99">
+        <v>1</v>
       </c>
       <c r="T99" t="str">
         <f t="shared" ref="T99:T130" si="3">IF(ISBLANK(B99)=FALSE,IF(ISBLANK(B98),"},["&amp;B99&amp;"]={","["&amp;B99&amp;"]={"),IF(AND(ISBLANK(B99),ISBLANK(C99),ISBLANK(L99),ISBLANK(M99),OR(ISBLANK(B98)=FALSE,ISBLANK(C98)=FALSE,ISBLANK(L98)=FALSE,ISBLANK(M98)=FALSE)),"},},}",IF(ISBLANK(C99),"","{szContent="""&amp;C99&amp;""","&amp;IF(D99&lt;&gt;"","szNote="""&amp;D99&amp;""",","")&amp;IF(K99&lt;&gt;"","col={"&amp;K99&amp;"},","")&amp;IF(L99&gt;0,"bSearch=true,","")&amp;IF(M99&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N99&gt;0,"szVoice="""&amp;N99&amp;""",","")&amp;IF(O99&gt;0,"bTeamChannel=true,","")&amp;IF(P99&gt;0,"bWhisperChannel=true,","")&amp;IF(Q99&gt;0,"bCenterAlarm=true,","")&amp;IF(R99&gt;0,"bScreenHead=true,","")&amp;IF(S99&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U99&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U99:AAF99)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="南屏山恶人谷伴江村援军已到，营地夺回，交通恢复！\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=10,nRefresh=600,key="赵新宇",},},},</v>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【武王城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="武王城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【武王城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="武王城·恶人大旗",},},},</v>
       </c>
       <c r="U99" t="s">
-        <v>2575</v>
+        <v>2505</v>
+      </c>
+      <c r="V99" t="str">
+        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G99&amp;"·浩气大旗"&amp;""",},"</f>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·浩气大旗",},</v>
+      </c>
+      <c r="W99" t="str">
+        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G99&amp;"·恶人大旗"&amp;""",},"</f>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·恶人大旗",},</v>
+      </c>
+      <c r="X99" t="s">
+        <v>2506</v>
+      </c>
+      <c r="Y99" t="s">
+        <v>2507</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>2568</v>
+      </c>
+      <c r="AA99" t="s">
+        <v>2569</v>
+      </c>
+      <c r="AB99" t="s">
+        <v>2570</v>
+      </c>
+      <c r="AC99" t="str">
+        <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G99&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G99&amp;"·浩气大旗"""&amp;",},"</f>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【武王城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="武王城·浩气大旗",},</v>
+      </c>
+      <c r="AD99" t="str">
+        <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G99&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G99&amp;"·恶人大旗"""&amp;",},"</f>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【武王城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="武王城·恶人大旗",},</v>
       </c>
     </row>
     <row r="100" customFormat="1" spans="1:34">
       <c r="C100" t="s">
-        <v>2576</v>
+        <v>2571</v>
+      </c>
+      <c r="D100" t="s">
+        <v>2572</v>
       </c>
       <c r="K100" t="s">
-        <v>2120</v>
+        <v>1656</v>
+      </c>
+      <c r="M100">
+        <v>1</v>
       </c>
       <c r="T100" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="南屏山浩气盟望北村援军已到，营地夺回，交通恢复！\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=10,nRefresh=600,key="方超",},},},</v>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="武王城·大旗重置",nTime=-2,nRefresh=7200,key="武王城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【武王城】大旗重置",nTime="180,【武王城】大旗重置;185,【武王城】大旗重置·结束",nRefresh=7200,key="武王城·大旗重置",},},},</v>
       </c>
       <c r="U100" t="s">
-        <v>2577</v>
-      </c>
-    </row>
-    <row r="101" spans="1:34">
-      <c r="A101" t="s">
-        <v>706</v>
-      </c>
-      <c r="B101">
-        <v>30</v>
+        <v>2573</v>
+      </c>
+      <c r="V100" t="s">
+        <v>2574</v>
+      </c>
+      <c r="W100" t="s">
+        <v>2575</v>
+      </c>
+      <c r="X100" t="s">
+        <v>2576</v>
+      </c>
+    </row>
+    <row r="101" customFormat="1" spans="1:34">
+      <c r="C101" t="s">
+        <v>2442</v>
+      </c>
+      <c r="K101" t="s">
+        <v>1656</v>
       </c>
       <c r="T101" t="str">
         <f t="shared" si="3"/>
-        <v>},[30]={</v>
+        <v>{szContent="本场浩气盟攻防即将结束，南屏山物资运送暂且休整，等待下一场攻防开启！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="粮草先行·活动结束",nTime=5,key="粮草先行·浩气盟",},{nClass=20,nIcon=13,szName="粮草先行·恶人谷",nTime=0,key="粮草先行·恶人谷",},{nClass=20,nIcon=589,nFrame=7,szName="赵新宇",nTime="60,赵新宇·刷新剩余;62,赵新宇·即将刷新",nRefresh=0,key="赵新宇",},},},</v>
+      </c>
+      <c r="U101" t="s">
+        <v>2577</v>
+      </c>
+      <c r="V101" t="s">
+        <v>2578</v>
+      </c>
+      <c r="W101" t="s">
+        <v>2579</v>
       </c>
     </row>
     <row r="102" customFormat="1" spans="1:34">
       <c r="C102" t="s">
-        <v>2503</v>
-      </c>
-      <c r="D102" t="s">
-        <v>2504</v>
-      </c>
-      <c r="G102" t="s">
-        <v>2578</v>
+        <v>2580</v>
       </c>
       <c r="K102" t="s">
-        <v>1656</v>
-      </c>
-      <c r="M102">
-        <v>1</v>
+        <v>2121</v>
       </c>
       <c r="T102" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凛风堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凛风堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·恶人大旗",},},},</v>
+        <v>{szContent="南屏山恶人谷伴江村援军已到，营地夺回，交通恢复！\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=10,nRefresh=600,key="赵新宇",},},},</v>
       </c>
       <c r="U102" t="s">
-        <v>2505</v>
-      </c>
-      <c r="V102" t="str">
-        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G102&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·浩气大旗",},</v>
-      </c>
-      <c r="W102" t="str">
-        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G102&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·恶人大旗",},</v>
-      </c>
-      <c r="X102" t="s">
-        <v>2506</v>
-      </c>
-      <c r="Y102" t="s">
-        <v>2507</v>
-      </c>
-      <c r="Z102" t="s">
-        <v>2562</v>
-      </c>
-      <c r="AA102" t="s">
-        <v>2563</v>
-      </c>
-      <c r="AB102" t="s">
-        <v>2564</v>
-      </c>
-      <c r="AC102" t="str">
-        <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G102&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G102&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【凛风堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·浩气大旗",},</v>
-      </c>
-      <c r="AD102" t="str">
-        <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G102&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G102&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【凛风堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·恶人大旗",},</v>
-      </c>
-    </row>
-    <row r="103" spans="1:34">
+        <v>2581</v>
+      </c>
+    </row>
+    <row r="103" customFormat="1" spans="1:34">
       <c r="C103" t="s">
-        <v>2565</v>
-      </c>
-      <c r="D103" t="s">
-        <v>2566</v>
+        <v>2582</v>
       </c>
       <c r="K103" t="s">
-        <v>1656</v>
-      </c>
-      <c r="M103">
-        <v>1</v>
+        <v>2120</v>
       </c>
       <c r="T103" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凛风堡·大旗重置",nTime=-2,nRefresh=7200,key="凛风堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凛风堡】大旗重置",nTime="180,【凛风堡】大旗重置;185,【凛风堡】大旗重置·结束",nRefresh=7200,key="凛风堡·大旗重置",},},},</v>
+        <v>{szContent="南屏山浩气盟望北村援军已到，营地夺回，交通恢复！\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=10,nRefresh=600,key="方超",},},},</v>
       </c>
       <c r="U103" t="s">
-        <v>2579</v>
-      </c>
-      <c r="V103" t="s">
-        <v>2568</v>
-      </c>
-      <c r="W103" t="s">
-        <v>2569</v>
-      </c>
-      <c r="X103" t="s">
-        <v>2580</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="104" spans="1:34">
-      <c r="C104" t="s">
-        <v>2438</v>
-      </c>
-      <c r="K104" t="s">
-        <v>1656</v>
+      <c r="A104" t="s">
+        <v>706</v>
+      </c>
+      <c r="B104">
+        <v>30</v>
       </c>
       <c r="T104" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="本场恶人谷攻防即将结束，昆仑物资运送暂且休整，等待下一场攻防开启！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="粮草先行·活动结束",nTime=5,key="粮草先行·恶人谷",},{nClass=20,nIcon=13,szName="粮草先行·浩气盟",nTime=0,key="粮草先行·浩气盟",},{nClass=20,nIcon=2864,nFrame=7,szName="霸图",nTime="60,霸图·刷新剩余;62,霸图·即将刷新",nRefresh=0,key="霸图",},{nClass=20,nIcon=845,nFrame=3,szName="孙永恒",nTime="60,孙永恒·刷新剩余;62,孙永恒·即将刷新",nRefresh=0,key="孙永恒",},},},</v>
-      </c>
-      <c r="U104" t="s">
-        <v>2581</v>
-      </c>
-      <c r="V104" t="s">
-        <v>2582</v>
-      </c>
-      <c r="W104" t="s">
-        <v>2583</v>
-      </c>
-      <c r="X104" t="s">
+        <v>},[30]={</v>
+      </c>
+    </row>
+    <row r="105" customFormat="1" spans="1:34">
+      <c r="C105" t="s">
+        <v>2503</v>
+      </c>
+      <c r="D105" t="s">
+        <v>2504</v>
+      </c>
+      <c r="G105" t="s">
         <v>2584</v>
       </c>
-    </row>
-    <row r="105" spans="1:34">
-      <c r="C105" t="s">
-        <v>2585</v>
-      </c>
       <c r="K105" t="s">
-        <v>2121</v>
+        <v>1656</v>
+      </c>
+      <c r="M105">
+        <v>1</v>
       </c>
       <c r="T105" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="昆仑山恶人谷西昆仑高地援军已到，营地夺回，交通恢复！\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=10,nRefresh=600,key="霸图",},},},</v>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凛风堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凛风堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·恶人大旗",},},},</v>
       </c>
       <c r="U105" t="s">
-        <v>2586</v>
+        <v>2505</v>
+      </c>
+      <c r="V105" t="str">
+        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G105&amp;"·浩气大旗"&amp;""",},"</f>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·浩气大旗",},</v>
+      </c>
+      <c r="W105" t="str">
+        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G105&amp;"·恶人大旗"&amp;""",},"</f>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·恶人大旗",},</v>
+      </c>
+      <c r="X105" t="s">
+        <v>2506</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>2507</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>2568</v>
+      </c>
+      <c r="AA105" t="s">
+        <v>2569</v>
+      </c>
+      <c r="AB105" t="s">
+        <v>2570</v>
+      </c>
+      <c r="AC105" t="str">
+        <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G105&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G105&amp;"·浩气大旗"""&amp;",},"</f>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【凛风堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·浩气大旗",},</v>
+      </c>
+      <c r="AD105" t="str">
+        <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G105&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G105&amp;"·恶人大旗"""&amp;",},"</f>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【凛风堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·恶人大旗",},</v>
       </c>
     </row>
     <row r="106" spans="1:34">
       <c r="C106" t="s">
-        <v>2587</v>
+        <v>2571</v>
+      </c>
+      <c r="D106" t="s">
+        <v>2572</v>
       </c>
       <c r="K106" t="s">
-        <v>2120</v>
+        <v>1656</v>
+      </c>
+      <c r="M106">
+        <v>1</v>
       </c>
       <c r="T106" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="昆仑山浩气盟东昆仑高地援军已到，营地夺回，交通恢复！\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=10,nRefresh=600,key="孙永恒",},},},</v>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凛风堡·大旗重置",nTime=-2,nRefresh=7200,key="凛风堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凛风堡】大旗重置",nTime="180,【凛风堡】大旗重置;185,【凛风堡】大旗重置·结束",nRefresh=7200,key="凛风堡·大旗重置",},},},</v>
       </c>
       <c r="U106" t="s">
-        <v>2588</v>
+        <v>2585</v>
+      </c>
+      <c r="V106" t="s">
+        <v>2574</v>
+      </c>
+      <c r="W106" t="s">
+        <v>2575</v>
+      </c>
+      <c r="X106" t="s">
+        <v>2586</v>
       </c>
     </row>
     <row r="107" spans="1:34">
-      <c r="A107" t="s">
-        <v>680</v>
-      </c>
-      <c r="B107">
-        <v>21</v>
+      <c r="C107" t="s">
+        <v>2438</v>
+      </c>
+      <c r="K107" t="s">
+        <v>1656</v>
       </c>
       <c r="T107" t="str">
         <f t="shared" si="3"/>
-        <v>},[21]={</v>
-      </c>
-    </row>
-    <row r="108" customFormat="1" spans="1:34">
+        <v>{szContent="本场恶人谷攻防即将结束，昆仑物资运送暂且休整，等待下一场攻防开启！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="粮草先行·活动结束",nTime=5,key="粮草先行·恶人谷",},{nClass=20,nIcon=13,szName="粮草先行·浩气盟",nTime=0,key="粮草先行·浩气盟",},{nClass=20,nIcon=2864,nFrame=7,szName="霸图",nTime="60,霸图·刷新剩余;62,霸图·即将刷新",nRefresh=0,key="霸图",},{nClass=20,nIcon=845,nFrame=3,szName="孙永恒",nTime="60,孙永恒·刷新剩余;62,孙永恒·即将刷新",nRefresh=0,key="孙永恒",},},},</v>
+      </c>
+      <c r="U107" t="s">
+        <v>2587</v>
+      </c>
+      <c r="V107" t="s">
+        <v>2588</v>
+      </c>
+      <c r="W107" t="s">
+        <v>2589</v>
+      </c>
+      <c r="X107" t="s">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="108" spans="1:34">
       <c r="C108" t="s">
-        <v>2503</v>
-      </c>
-      <c r="D108" t="s">
-        <v>2504</v>
-      </c>
-      <c r="G108" t="s">
-        <v>2589</v>
-      </c>
-      <c r="H108" t="s">
-        <v>2590</v>
+        <v>2591</v>
       </c>
       <c r="K108" t="s">
-        <v>1656</v>
-      </c>
-      <c r="M108">
-        <v>1</v>
+        <v>2121</v>
       </c>
       <c r="T108" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【盘龙坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【逐鹿坪】恶人·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【盘龙坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【逐鹿坪】浩气·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·恶人大旗",},},},</v>
+        <v>{szContent="昆仑山恶人谷西昆仑高地援军已到，营地夺回，交通恢复！\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=10,nRefresh=600,key="霸图",},},},</v>
       </c>
       <c r="U108" t="s">
-        <v>2505</v>
-      </c>
-      <c r="V108" t="str">
-        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G108&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·浩气大旗",},</v>
-      </c>
-      <c r="W108" t="str">
-        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H108&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·浩气大旗",},</v>
-      </c>
-      <c r="X108" t="str">
-        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G108&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·恶人大旗",},</v>
-      </c>
-      <c r="Y108" t="str">
-        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H108&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·恶人大旗",},</v>
-      </c>
-      <c r="Z108" t="s">
-        <v>2506</v>
-      </c>
-      <c r="AA108" t="s">
-        <v>2507</v>
-      </c>
-      <c r="AB108" t="s">
-        <v>2562</v>
-      </c>
-      <c r="AC108" t="s">
-        <v>2563</v>
-      </c>
-      <c r="AD108" t="s">
-        <v>2564</v>
-      </c>
-      <c r="AE108" t="str">
-        <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G108&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G108&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【盘龙坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·浩气大旗",},</v>
-      </c>
-      <c r="AF108" t="str">
-        <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H108&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H108&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【逐鹿坪】恶人·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·浩气大旗",},</v>
-      </c>
-      <c r="AG108" t="str">
-        <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G108&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G108&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【盘龙坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·恶人大旗",},</v>
-      </c>
-      <c r="AH108" t="str">
-        <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H108&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H108&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【逐鹿坪】浩气·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·恶人大旗",},</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="109" spans="1:34">
       <c r="C109" t="s">
-        <v>2565</v>
-      </c>
-      <c r="D109" t="s">
-        <v>2566</v>
+        <v>2593</v>
       </c>
       <c r="K109" t="s">
-        <v>1656</v>
-      </c>
-      <c r="M109">
-        <v>1</v>
+        <v>2120</v>
       </c>
       <c r="T109" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="盘龙坞·大旗重置",nTime=-2,nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=1465,szName="逐鹿坪·大旗重置",nTime=-2,nRefresh=7200,key="逐鹿坪·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【盘龙坞】大旗重置",nTime="180,【盘龙坞】大旗重置;185,【盘龙坞】大旗重置·结束",nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【逐鹿坪】大旗重置",nTime="180,【逐鹿坪】大旗重置;185,【逐鹿坪】大旗重置·结束",nRefresh=7200,key="逐鹿坪·大旗重置",},},},</v>
+        <v>{szContent="昆仑山浩气盟东昆仑高地援军已到，营地夺回，交通恢复！\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=10,nRefresh=600,key="孙永恒",},},},</v>
       </c>
       <c r="U109" t="s">
-        <v>2591</v>
-      </c>
-      <c r="V109" t="s">
-        <v>2592</v>
-      </c>
-      <c r="W109" t="s">
-        <v>2568</v>
-      </c>
-      <c r="X109" t="s">
-        <v>2569</v>
-      </c>
-      <c r="Y109" t="s">
-        <v>2593</v>
-      </c>
-      <c r="Z109" t="s">
         <v>2594</v>
       </c>
     </row>
     <row r="110" spans="1:34">
       <c r="A110" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="B110">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="T110" t="str">
         <f t="shared" si="3"/>
-        <v>},[23]={</v>
+        <v>},[21]={</v>
       </c>
     </row>
     <row r="111" customFormat="1" spans="1:34">
@@ -43924,26 +43904,26 @@
       </c>
       <c r="T111" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【龙门镇】恶人·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【飞沙关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【龙门镇】浩气·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【飞沙关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·恶人大旗",},},},</v>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【盘龙坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【逐鹿坪】恶人·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【盘龙坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【逐鹿坪】浩气·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·恶人大旗",},},},</v>
       </c>
       <c r="U111" t="s">
         <v>2505</v>
       </c>
       <c r="V111" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G111&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·浩气大旗",},</v>
       </c>
       <c r="W111" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H111&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·浩气大旗",},</v>
       </c>
       <c r="X111" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G111&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·恶人大旗",},</v>
       </c>
       <c r="Y111" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H111&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·恶人大旗",},</v>
       </c>
       <c r="Z111" t="s">
         <v>2506</v>
@@ -43952,37 +43932,37 @@
         <v>2507</v>
       </c>
       <c r="AB111" t="s">
-        <v>2562</v>
+        <v>2568</v>
       </c>
       <c r="AC111" t="s">
-        <v>2563</v>
+        <v>2569</v>
       </c>
       <c r="AD111" t="s">
-        <v>2564</v>
+        <v>2570</v>
       </c>
       <c r="AE111" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G111&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G111&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【龙门镇】恶人·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【盘龙坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·浩气大旗",},</v>
       </c>
       <c r="AF111" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H111&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H111&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【飞沙关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【逐鹿坪】恶人·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·浩气大旗",},</v>
       </c>
       <c r="AG111" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G111&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G111&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【龙门镇】浩气·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【盘龙坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·恶人大旗",},</v>
       </c>
       <c r="AH111" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H111&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H111&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【飞沙关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【逐鹿坪】浩气·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·恶人大旗",},</v>
       </c>
     </row>
     <row r="112" spans="1:34">
       <c r="C112" t="s">
-        <v>2565</v>
+        <v>2571</v>
       </c>
       <c r="D112" t="s">
-        <v>2566</v>
+        <v>2572</v>
       </c>
       <c r="K112" t="s">
         <v>1656</v>
@@ -43992,7 +43972,7 @@
       </c>
       <c r="T112" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="龙门镇·大旗重置",nTime=-2,nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=1465,szName="飞沙关·大旗重置",nTime=-2,nRefresh=7200,key="飞沙关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【龙门镇】大旗重置",nTime="180,【龙门镇】大旗重置;185,【龙门镇】大旗重置·结束",nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【飞沙关】大旗重置",nTime="180,【飞沙关】大旗重置;185,【飞沙关】大旗重置·结束",nRefresh=7200,key="飞沙关·大旗重置",},},},</v>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="盘龙坞·大旗重置",nTime=-2,nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=1465,szName="逐鹿坪·大旗重置",nTime=-2,nRefresh=7200,key="逐鹿坪·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【盘龙坞】大旗重置",nTime="180,【盘龙坞】大旗重置;185,【盘龙坞】大旗重置·结束",nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【逐鹿坪】大旗重置",nTime="180,【逐鹿坪】大旗重置;185,【逐鹿坪】大旗重置·结束",nRefresh=7200,key="逐鹿坪·大旗重置",},},},</v>
       </c>
       <c r="U112" t="s">
         <v>2597</v>
@@ -44001,10 +43981,10 @@
         <v>2598</v>
       </c>
       <c r="W112" t="s">
-        <v>2568</v>
+        <v>2574</v>
       </c>
       <c r="X112" t="s">
-        <v>2569</v>
+        <v>2575</v>
       </c>
       <c r="Y112" t="s">
         <v>2599</v>
@@ -44015,14 +43995,14 @@
     </row>
     <row r="113" spans="1:34">
       <c r="A113" t="s">
-        <v>634</v>
+        <v>686</v>
       </c>
       <c r="B113">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="T113" t="str">
         <f t="shared" si="3"/>
-        <v>},[9]={</v>
+        <v>},[23]={</v>
       </c>
     </row>
     <row r="114" customFormat="1" spans="1:34">
@@ -44046,26 +44026,26 @@
       </c>
       <c r="T114" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【红莲岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【秋雨堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【红莲岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【秋雨堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·恶人大旗",},},},</v>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【龙门镇】恶人·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【飞沙关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【龙门镇】浩气·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【飞沙关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·恶人大旗",},},},</v>
       </c>
       <c r="U114" t="s">
         <v>2505</v>
       </c>
       <c r="V114" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G114&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·浩气大旗",},</v>
       </c>
       <c r="W114" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H114&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·浩气大旗",},</v>
       </c>
       <c r="X114" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G114&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·恶人大旗",},</v>
       </c>
       <c r="Y114" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H114&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·恶人大旗",},</v>
       </c>
       <c r="Z114" t="s">
         <v>2506</v>
@@ -44074,37 +44054,37 @@
         <v>2507</v>
       </c>
       <c r="AB114" t="s">
-        <v>2562</v>
+        <v>2568</v>
       </c>
       <c r="AC114" t="s">
-        <v>2563</v>
+        <v>2569</v>
       </c>
       <c r="AD114" t="s">
-        <v>2564</v>
+        <v>2570</v>
       </c>
       <c r="AE114" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G114&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G114&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【红莲岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【龙门镇】恶人·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·浩气大旗",},</v>
       </c>
       <c r="AF114" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H114&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H114&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【秋雨堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【飞沙关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·浩气大旗",},</v>
       </c>
       <c r="AG114" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G114&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G114&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【红莲岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【龙门镇】浩气·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·恶人大旗",},</v>
       </c>
       <c r="AH114" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H114&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H114&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【秋雨堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【飞沙关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·恶人大旗",},</v>
       </c>
     </row>
     <row r="115" spans="1:34">
       <c r="C115" t="s">
-        <v>2565</v>
+        <v>2571</v>
       </c>
       <c r="D115" t="s">
-        <v>2566</v>
+        <v>2572</v>
       </c>
       <c r="K115" t="s">
         <v>1656</v>
@@ -44114,7 +44094,7 @@
       </c>
       <c r="T115" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="红莲岗·大旗重置",nTime=-2,nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=1465,szName="秋雨堡·大旗重置",nTime=-2,nRefresh=7200,key="秋雨堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【红莲岗】大旗重置",nTime="180,【红莲岗】大旗重置;185,【红莲岗】大旗重置·结束",nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【秋雨堡】大旗重置",nTime="180,【秋雨堡】大旗重置;185,【秋雨堡】大旗重置·结束",nRefresh=7200,key="秋雨堡·大旗重置",},},},</v>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="龙门镇·大旗重置",nTime=-2,nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=1465,szName="飞沙关·大旗重置",nTime=-2,nRefresh=7200,key="飞沙关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【龙门镇】大旗重置",nTime="180,【龙门镇】大旗重置;185,【龙门镇】大旗重置·结束",nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【飞沙关】大旗重置",nTime="180,【飞沙关】大旗重置;185,【飞沙关】大旗重置·结束",nRefresh=7200,key="飞沙关·大旗重置",},},},</v>
       </c>
       <c r="U115" t="s">
         <v>2603</v>
@@ -44123,10 +44103,10 @@
         <v>2604</v>
       </c>
       <c r="W115" t="s">
-        <v>2568</v>
+        <v>2574</v>
       </c>
       <c r="X115" t="s">
-        <v>2569</v>
+        <v>2575</v>
       </c>
       <c r="Y115" t="s">
         <v>2605</v>
@@ -44137,14 +44117,14 @@
     </row>
     <row r="116" spans="1:34">
       <c r="A116" t="s">
-        <v>652</v>
+        <v>634</v>
       </c>
       <c r="B116">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T116" t="str">
         <f t="shared" si="3"/>
-        <v>},[13]={</v>
+        <v>},[9]={</v>
       </c>
     </row>
     <row r="117" customFormat="1" spans="1:34">
@@ -44168,26 +44148,26 @@
       </c>
       <c r="T117" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【金门关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="金门关·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【青云坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【金门关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="金门关·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【青云坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·恶人大旗",},},},</v>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【红莲岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【秋雨堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【红莲岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【秋雨堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·恶人大旗",},},},</v>
       </c>
       <c r="U117" t="s">
         <v>2505</v>
       </c>
       <c r="V117" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G117&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·浩气大旗",},</v>
       </c>
       <c r="W117" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H117&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·浩气大旗",},</v>
       </c>
       <c r="X117" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G117&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·恶人大旗",},</v>
       </c>
       <c r="Y117" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H117&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},</v>
       </c>
       <c r="Z117" t="s">
         <v>2506</v>
@@ -44196,37 +44176,37 @@
         <v>2507</v>
       </c>
       <c r="AB117" t="s">
-        <v>2562</v>
+        <v>2568</v>
       </c>
       <c r="AC117" t="s">
-        <v>2563</v>
+        <v>2569</v>
       </c>
       <c r="AD117" t="s">
-        <v>2564</v>
+        <v>2570</v>
       </c>
       <c r="AE117" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G117&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G117&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【金门关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="金门关·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【红莲岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·浩气大旗",},</v>
       </c>
       <c r="AF117" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H117&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H117&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【青云坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【秋雨堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·浩气大旗",},</v>
       </c>
       <c r="AG117" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G117&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G117&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【金门关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="金门关·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【红莲岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·恶人大旗",},</v>
       </c>
       <c r="AH117" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H117&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H117&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【青云坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【秋雨堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·恶人大旗",},</v>
       </c>
     </row>
     <row r="118" spans="1:34">
       <c r="C118" t="s">
-        <v>2565</v>
+        <v>2571</v>
       </c>
       <c r="D118" t="s">
-        <v>2566</v>
+        <v>2572</v>
       </c>
       <c r="K118" t="s">
         <v>1656</v>
@@ -44236,7 +44216,7 @@
       </c>
       <c r="T118" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="金门关·大旗重置",nTime=-2,nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=1465,szName="青云坞·大旗重置",nTime=-2,nRefresh=7200,key="青云坞·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【金门关】大旗重置",nTime="180,【金门关】大旗重置;185,【金门关】大旗重置·结束",nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【青云坞】大旗重置",nTime="180,【青云坞】大旗重置;185,【青云坞】大旗重置·结束",nRefresh=7200,key="青云坞·大旗重置",},},},</v>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="红莲岗·大旗重置",nTime=-2,nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=1465,szName="秋雨堡·大旗重置",nTime=-2,nRefresh=7200,key="秋雨堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【红莲岗】大旗重置",nTime="180,【红莲岗】大旗重置;185,【红莲岗】大旗重置·结束",nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【秋雨堡】大旗重置",nTime="180,【秋雨堡】大旗重置;185,【秋雨堡】大旗重置·结束",nRefresh=7200,key="秋雨堡·大旗重置",},},},</v>
       </c>
       <c r="U118" t="s">
         <v>2609</v>
@@ -44245,10 +44225,10 @@
         <v>2610</v>
       </c>
       <c r="W118" t="s">
-        <v>2568</v>
+        <v>2574</v>
       </c>
       <c r="X118" t="s">
-        <v>2569</v>
+        <v>2575</v>
       </c>
       <c r="Y118" t="s">
         <v>2611</v>
@@ -44259,14 +44239,14 @@
     </row>
     <row r="119" spans="1:34">
       <c r="A119" t="s">
-        <v>721</v>
+        <v>652</v>
       </c>
       <c r="B119">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="T119" t="str">
         <f t="shared" si="3"/>
-        <v>},[35]={</v>
+        <v>},[13]={</v>
       </c>
     </row>
     <row r="120" customFormat="1" spans="1:34">
@@ -44290,26 +44270,26 @@
       </c>
       <c r="T120" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【激流坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【不空关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="不空关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【激流坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【不空关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="不空关·恶人大旗",},},},</v>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【金门关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="金门关·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【青云坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【金门关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="金门关·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【青云坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·恶人大旗",},},},</v>
       </c>
       <c r="U120" t="s">
         <v>2505</v>
       </c>
       <c r="V120" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G120&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·浩气大旗",},</v>
       </c>
       <c r="W120" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H120&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·浩气大旗",},</v>
       </c>
       <c r="X120" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G120&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·恶人大旗",},</v>
       </c>
       <c r="Y120" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H120&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·恶人大旗",},</v>
       </c>
       <c r="Z120" t="s">
         <v>2506</v>
@@ -44318,37 +44298,37 @@
         <v>2507</v>
       </c>
       <c r="AB120" t="s">
-        <v>2562</v>
+        <v>2568</v>
       </c>
       <c r="AC120" t="s">
-        <v>2563</v>
+        <v>2569</v>
       </c>
       <c r="AD120" t="s">
-        <v>2564</v>
+        <v>2570</v>
       </c>
       <c r="AE120" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G120&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G120&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【激流坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【金门关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="金门关·浩气大旗",},</v>
       </c>
       <c r="AF120" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H120&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H120&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【不空关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="不空关·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【青云坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·浩气大旗",},</v>
       </c>
       <c r="AG120" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G120&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G120&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【激流坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【金门关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="金门关·恶人大旗",},</v>
       </c>
       <c r="AH120" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H120&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H120&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【不空关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="不空关·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【青云坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·恶人大旗",},</v>
       </c>
     </row>
     <row r="121" spans="1:34">
       <c r="C121" t="s">
-        <v>2565</v>
+        <v>2571</v>
       </c>
       <c r="D121" t="s">
-        <v>2566</v>
+        <v>2572</v>
       </c>
       <c r="K121" t="s">
         <v>1656</v>
@@ -44358,7 +44338,7 @@
       </c>
       <c r="T121" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="激流坞·大旗重置",nTime=-2,nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=1465,szName="不空关·大旗重置",nTime=-2,nRefresh=7200,key="不空关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【激流坞】大旗重置",nTime="180,【激流坞】大旗重置;185,【激流坞】大旗重置·结束",nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【不空关】大旗重置",nTime="180,【不空关】大旗重置;185,【不空关】大旗重置·结束",nRefresh=7200,key="不空关·大旗重置",},},},</v>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="金门关·大旗重置",nTime=-2,nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=1465,szName="青云坞·大旗重置",nTime=-2,nRefresh=7200,key="青云坞·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【金门关】大旗重置",nTime="180,【金门关】大旗重置;185,【金门关】大旗重置·结束",nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【青云坞】大旗重置",nTime="180,【青云坞】大旗重置;185,【青云坞】大旗重置·结束",nRefresh=7200,key="青云坞·大旗重置",},},},</v>
       </c>
       <c r="U121" t="s">
         <v>2615</v>
@@ -44367,10 +44347,10 @@
         <v>2616</v>
       </c>
       <c r="W121" t="s">
-        <v>2568</v>
+        <v>2574</v>
       </c>
       <c r="X121" t="s">
-        <v>2569</v>
+        <v>2575</v>
       </c>
       <c r="Y121" t="s">
         <v>2617</v>
@@ -44381,14 +44361,14 @@
     </row>
     <row r="122" spans="1:34">
       <c r="A122" t="s">
-        <v>839</v>
+        <v>721</v>
       </c>
       <c r="B122">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="T122" t="str">
         <f t="shared" si="3"/>
-        <v>},[100]={</v>
+        <v>},[35]={</v>
       </c>
     </row>
     <row r="123" customFormat="1" spans="1:34">
@@ -44412,26 +44392,26 @@
       </c>
       <c r="T123" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【日月崖】恶人·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【卧龙坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【日月崖】浩气·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【卧龙坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·恶人大旗",},},},</v>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【激流坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【不空关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="不空关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【激流坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【不空关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="不空关·恶人大旗",},},},</v>
       </c>
       <c r="U123" t="s">
         <v>2505</v>
       </c>
       <c r="V123" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G123&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·浩气大旗",},</v>
       </c>
       <c r="W123" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H123&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·浩气大旗",},</v>
       </c>
       <c r="X123" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G123&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·恶人大旗",},</v>
       </c>
       <c r="Y123" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H123&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·恶人大旗",},</v>
       </c>
       <c r="Z123" t="s">
         <v>2506</v>
@@ -44440,37 +44420,37 @@
         <v>2507</v>
       </c>
       <c r="AB123" t="s">
-        <v>2562</v>
+        <v>2568</v>
       </c>
       <c r="AC123" t="s">
-        <v>2563</v>
+        <v>2569</v>
       </c>
       <c r="AD123" t="s">
-        <v>2564</v>
+        <v>2570</v>
       </c>
       <c r="AE123" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G123&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G123&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【日月崖】恶人·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【激流坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·浩气大旗",},</v>
       </c>
       <c r="AF123" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H123&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H123&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【卧龙坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【不空关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="不空关·浩气大旗",},</v>
       </c>
       <c r="AG123" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G123&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G123&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【日月崖】浩气·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【激流坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·恶人大旗",},</v>
       </c>
       <c r="AH123" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H123&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H123&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【卧龙坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【不空关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="不空关·恶人大旗",},</v>
       </c>
     </row>
     <row r="124" spans="1:34">
       <c r="C124" t="s">
-        <v>2565</v>
+        <v>2571</v>
       </c>
       <c r="D124" t="s">
-        <v>2566</v>
+        <v>2572</v>
       </c>
       <c r="K124" t="s">
         <v>1656</v>
@@ -44480,7 +44460,7 @@
       </c>
       <c r="T124" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="日月崖·大旗重置",nTime=-2,nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=1465,szName="卧龙坡·大旗重置",nTime=-2,nRefresh=7200,key="卧龙坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【日月崖】大旗重置",nTime="180,【日月崖】大旗重置;185,【日月崖】大旗重置·结束",nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【卧龙坡】大旗重置",nTime="180,【卧龙坡】大旗重置;185,【卧龙坡】大旗重置·结束",nRefresh=7200,key="卧龙坡·大旗重置",},},},</v>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="激流坞·大旗重置",nTime=-2,nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=1465,szName="不空关·大旗重置",nTime=-2,nRefresh=7200,key="不空关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【激流坞】大旗重置",nTime="180,【激流坞】大旗重置;185,【激流坞】大旗重置·结束",nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【不空关】大旗重置",nTime="180,【不空关】大旗重置;185,【不空关】大旗重置·结束",nRefresh=7200,key="不空关·大旗重置",},},},</v>
       </c>
       <c r="U124" t="s">
         <v>2621</v>
@@ -44489,10 +44469,10 @@
         <v>2622</v>
       </c>
       <c r="W124" t="s">
-        <v>2568</v>
+        <v>2574</v>
       </c>
       <c r="X124" t="s">
-        <v>2569</v>
+        <v>2575</v>
       </c>
       <c r="Y124" t="s">
         <v>2623</v>
@@ -44503,14 +44483,14 @@
     </row>
     <row r="125" spans="1:34">
       <c r="A125" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="B125">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T125" t="str">
         <f t="shared" si="3"/>
-        <v>},[101]={</v>
+        <v>},[100]={</v>
       </c>
     </row>
     <row r="126" customFormat="1" spans="1:34">
@@ -44534,26 +44514,26 @@
       </c>
       <c r="T126" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【霜戈堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【澜沧城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【霜戈堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【澜沧城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·恶人大旗",},},},</v>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【日月崖】恶人·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【卧龙坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【日月崖】浩气·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【卧龙坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·恶人大旗",},},},</v>
       </c>
       <c r="U126" t="s">
         <v>2505</v>
       </c>
       <c r="V126" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G126&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·浩气大旗",},</v>
       </c>
       <c r="W126" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H126&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·浩气大旗",},</v>
       </c>
       <c r="X126" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G126&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·恶人大旗",},</v>
       </c>
       <c r="Y126" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H126&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·恶人大旗",},</v>
       </c>
       <c r="Z126" t="s">
         <v>2506</v>
@@ -44562,37 +44542,37 @@
         <v>2507</v>
       </c>
       <c r="AB126" t="s">
-        <v>2562</v>
+        <v>2568</v>
       </c>
       <c r="AC126" t="s">
-        <v>2563</v>
+        <v>2569</v>
       </c>
       <c r="AD126" t="s">
-        <v>2564</v>
+        <v>2570</v>
       </c>
       <c r="AE126" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G126&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G126&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【霜戈堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【日月崖】恶人·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·浩气大旗",},</v>
       </c>
       <c r="AF126" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H126&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H126&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【澜沧城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【卧龙坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·浩气大旗",},</v>
       </c>
       <c r="AG126" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G126&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G126&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【霜戈堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【日月崖】浩气·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·恶人大旗",},</v>
       </c>
       <c r="AH126" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H126&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H126&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【澜沧城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【卧龙坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·恶人大旗",},</v>
       </c>
     </row>
     <row r="127" spans="1:34">
       <c r="C127" t="s">
-        <v>2565</v>
+        <v>2571</v>
       </c>
       <c r="D127" t="s">
-        <v>2566</v>
+        <v>2572</v>
       </c>
       <c r="K127" t="s">
         <v>1656</v>
@@ -44602,7 +44582,7 @@
       </c>
       <c r="T127" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="霜戈堡·大旗重置",nTime=-2,nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=1465,szName="澜沧城·大旗重置",nTime=-2,nRefresh=7200,key="澜沧城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【霜戈堡】大旗重置",nTime="180,【霜戈堡】大旗重置;185,【霜戈堡】大旗重置·结束",nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【澜沧城】大旗重置",nTime="180,【澜沧城】大旗重置;185,【澜沧城】大旗重置·结束",nRefresh=7200,key="澜沧城·大旗重置",},},},</v>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="日月崖·大旗重置",nTime=-2,nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=1465,szName="卧龙坡·大旗重置",nTime=-2,nRefresh=7200,key="卧龙坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【日月崖】大旗重置",nTime="180,【日月崖】大旗重置;185,【日月崖】大旗重置·结束",nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【卧龙坡】大旗重置",nTime="180,【卧龙坡】大旗重置;185,【卧龙坡】大旗重置·结束",nRefresh=7200,key="卧龙坡·大旗重置",},},},</v>
       </c>
       <c r="U127" t="s">
         <v>2627</v>
@@ -44611,10 +44591,10 @@
         <v>2628</v>
       </c>
       <c r="W127" t="s">
-        <v>2568</v>
+        <v>2574</v>
       </c>
       <c r="X127" t="s">
-        <v>2569</v>
+        <v>2575</v>
       </c>
       <c r="Y127" t="s">
         <v>2629</v>
@@ -44625,14 +44605,14 @@
     </row>
     <row r="128" spans="1:34">
       <c r="A128" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="B128">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="T128" t="str">
         <f t="shared" si="3"/>
-        <v>},[103]={</v>
+        <v>},[101]={</v>
       </c>
     </row>
     <row r="129" customFormat="1" spans="1:34">
@@ -44656,26 +44636,26 @@
       </c>
       <c r="T129" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【神池岭】恶人·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【烈日岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【神池岭】浩气·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【烈日岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·恶人大旗",},},},</v>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【霜戈堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【澜沧城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【霜戈堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【澜沧城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·恶人大旗",},},},</v>
       </c>
       <c r="U129" t="s">
         <v>2505</v>
       </c>
       <c r="V129" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G129&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·浩气大旗",},</v>
       </c>
       <c r="W129" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H129&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·浩气大旗",},</v>
       </c>
       <c r="X129" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G129&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·恶人大旗",},</v>
       </c>
       <c r="Y129" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H129&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·恶人大旗",},</v>
       </c>
       <c r="Z129" t="s">
         <v>2506</v>
@@ -44684,37 +44664,37 @@
         <v>2507</v>
       </c>
       <c r="AB129" t="s">
-        <v>2562</v>
+        <v>2568</v>
       </c>
       <c r="AC129" t="s">
-        <v>2563</v>
+        <v>2569</v>
       </c>
       <c r="AD129" t="s">
-        <v>2564</v>
+        <v>2570</v>
       </c>
       <c r="AE129" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G129&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G129&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【神池岭】恶人·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【霜戈堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·浩气大旗",},</v>
       </c>
       <c r="AF129" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H129&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H129&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【烈日岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【澜沧城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·浩气大旗",},</v>
       </c>
       <c r="AG129" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G129&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G129&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【神池岭】浩气·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【霜戈堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·恶人大旗",},</v>
       </c>
       <c r="AH129" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H129&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H129&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【烈日岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【澜沧城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·恶人大旗",},</v>
       </c>
     </row>
     <row r="130" spans="1:34">
       <c r="C130" t="s">
-        <v>2565</v>
+        <v>2571</v>
       </c>
       <c r="D130" t="s">
-        <v>2566</v>
+        <v>2572</v>
       </c>
       <c r="K130" t="s">
         <v>1656</v>
@@ -44724,7 +44704,7 @@
       </c>
       <c r="T130" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="神池岭·大旗重置",nTime=-2,nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=1465,szName="烈日岗·大旗重置",nTime=-2,nRefresh=7200,key="烈日岗·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【神池岭】大旗重置",nTime="180,【神池岭】大旗重置;185,【神池岭】大旗重置·结束",nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【烈日岗】大旗重置",nTime="180,【烈日岗】大旗重置;185,【烈日岗】大旗重置·结束",nRefresh=7200,key="烈日岗·大旗重置",},},},</v>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="霜戈堡·大旗重置",nTime=-2,nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=1465,szName="澜沧城·大旗重置",nTime=-2,nRefresh=7200,key="澜沧城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【霜戈堡】大旗重置",nTime="180,【霜戈堡】大旗重置;185,【霜戈堡】大旗重置·结束",nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【澜沧城】大旗重置",nTime="180,【澜沧城】大旗重置;185,【澜沧城】大旗重置·结束",nRefresh=7200,key="澜沧城·大旗重置",},},},</v>
       </c>
       <c r="U130" t="s">
         <v>2633</v>
@@ -44733,10 +44713,10 @@
         <v>2634</v>
       </c>
       <c r="W130" t="s">
-        <v>2568</v>
+        <v>2574</v>
       </c>
       <c r="X130" t="s">
-        <v>2569</v>
+        <v>2575</v>
       </c>
       <c r="Y130" t="s">
         <v>2635</v>
@@ -44747,14 +44727,14 @@
     </row>
     <row r="131" spans="1:34">
       <c r="A131" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="B131">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T131" t="str">
-        <f t="shared" ref="T131:T151" si="4">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(C131),ISBLANK(L131),ISBLANK(M131),OR(ISBLANK(B130)=FALSE,ISBLANK(C130)=FALSE,ISBLANK(L130)=FALSE,ISBLANK(M130)=FALSE)),"},},}",IF(ISBLANK(C131),"","{szContent="""&amp;C131&amp;""","&amp;IF(D131&lt;&gt;"","szNote="""&amp;D131&amp;""",","")&amp;IF(K131&lt;&gt;"","col={"&amp;K131&amp;"},","")&amp;IF(L131&gt;0,"bSearch=true,","")&amp;IF(M131&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N131&gt;0,"szVoice="""&amp;N131&amp;""",","")&amp;IF(O131&gt;0,"bTeamChannel=true,","")&amp;IF(P131&gt;0,"bWhisperChannel=true,","")&amp;IF(Q131&gt;0,"bCenterAlarm=true,","")&amp;IF(R131&gt;0,"bScreenHead=true,","")&amp;IF(S131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U131:AAF131)&amp;"},","")&amp;"},")))</f>
-        <v>},[104]={</v>
+        <f t="shared" ref="T131:T154" si="4">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(C131),ISBLANK(L131),ISBLANK(M131),OR(ISBLANK(B130)=FALSE,ISBLANK(C130)=FALSE,ISBLANK(L130)=FALSE,ISBLANK(M130)=FALSE)),"},},}",IF(ISBLANK(C131),"","{szContent="""&amp;C131&amp;""","&amp;IF(D131&lt;&gt;"","szNote="""&amp;D131&amp;""",","")&amp;IF(K131&lt;&gt;"","col={"&amp;K131&amp;"},","")&amp;IF(L131&gt;0,"bSearch=true,","")&amp;IF(M131&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N131&gt;0,"szVoice="""&amp;N131&amp;""",","")&amp;IF(O131&gt;0,"bTeamChannel=true,","")&amp;IF(P131&gt;0,"bWhisperChannel=true,","")&amp;IF(Q131&gt;0,"bCenterAlarm=true,","")&amp;IF(R131&gt;0,"bScreenHead=true,","")&amp;IF(S131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U131:AAF131)&amp;"},","")&amp;"},")))</f>
+        <v>},[103]={</v>
       </c>
     </row>
     <row r="132" customFormat="1" spans="1:34">
@@ -44778,26 +44758,26 @@
       </c>
       <c r="T132" t="str">
         <f t="shared" si="4"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凤鸣堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【惊虬谷】恶人·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凤鸣堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【惊虬谷】浩气·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·恶人大旗",},},},</v>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【神池岭】恶人·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【烈日岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【神池岭】浩气·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【烈日岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·恶人大旗",},},},</v>
       </c>
       <c r="U132" t="s">
         <v>2505</v>
       </c>
       <c r="V132" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G132&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·浩气大旗",},</v>
       </c>
       <c r="W132" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H132&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·浩气大旗",},</v>
       </c>
       <c r="X132" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G132&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·恶人大旗",},</v>
       </c>
       <c r="Y132" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H132&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·恶人大旗",},</v>
       </c>
       <c r="Z132" t="s">
         <v>2506</v>
@@ -44806,37 +44786,37 @@
         <v>2507</v>
       </c>
       <c r="AB132" t="s">
-        <v>2562</v>
+        <v>2568</v>
       </c>
       <c r="AC132" t="s">
-        <v>2563</v>
+        <v>2569</v>
       </c>
       <c r="AD132" t="s">
-        <v>2564</v>
+        <v>2570</v>
       </c>
       <c r="AE132" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G132&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G132&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【凤鸣堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【神池岭】恶人·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·浩气大旗",},</v>
       </c>
       <c r="AF132" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H132&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H132&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【惊虬谷】恶人·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【烈日岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·浩气大旗",},</v>
       </c>
       <c r="AG132" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G132&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G132&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【凤鸣堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【神池岭】浩气·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·恶人大旗",},</v>
       </c>
       <c r="AH132" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H132&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H132&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【惊虬谷】浩气·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【烈日岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·恶人大旗",},</v>
       </c>
     </row>
     <row r="133" spans="1:34">
       <c r="C133" t="s">
-        <v>2565</v>
+        <v>2571</v>
       </c>
       <c r="D133" t="s">
-        <v>2566</v>
+        <v>2572</v>
       </c>
       <c r="K133" t="s">
         <v>1656</v>
@@ -44846,7 +44826,7 @@
       </c>
       <c r="T133" t="str">
         <f t="shared" si="4"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凤鸣堡·大旗重置",nTime=-2,nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=1465,szName="惊虬谷·大旗重置",nTime=-2,nRefresh=7200,key="惊虬谷·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凤鸣堡】大旗重置",nTime="180,【凤鸣堡】大旗重置;185,【凤鸣堡】大旗重置·结束",nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【惊虬谷】大旗重置",nTime="180,【惊虬谷】大旗重置;185,【惊虬谷】大旗重置·结束",nRefresh=7200,key="惊虬谷·大旗重置",},},},</v>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="神池岭·大旗重置",nTime=-2,nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=1465,szName="烈日岗·大旗重置",nTime=-2,nRefresh=7200,key="烈日岗·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【神池岭】大旗重置",nTime="180,【神池岭】大旗重置;185,【神池岭】大旗重置·结束",nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【烈日岗】大旗重置",nTime="180,【烈日岗】大旗重置;185,【烈日岗】大旗重置·结束",nRefresh=7200,key="烈日岗·大旗重置",},},},</v>
       </c>
       <c r="U133" t="s">
         <v>2639</v>
@@ -44855,10 +44835,10 @@
         <v>2640</v>
       </c>
       <c r="W133" t="s">
-        <v>2568</v>
+        <v>2574</v>
       </c>
       <c r="X133" t="s">
-        <v>2569</v>
+        <v>2575</v>
       </c>
       <c r="Y133" t="s">
         <v>2641</v>
@@ -44869,14 +44849,14 @@
     </row>
     <row r="134" spans="1:34">
       <c r="A134" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="B134">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T134" t="str">
         <f t="shared" si="4"/>
-        <v>},[105]={</v>
+        <v>},[104]={</v>
       </c>
     </row>
     <row r="135" customFormat="1" spans="1:34">
@@ -44900,26 +44880,26 @@
       </c>
       <c r="T135" t="str">
         <f t="shared" si="4"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【大理山城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【千岩关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【大理山城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【千岩关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·恶人大旗",},},},</v>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凤鸣堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【惊虬谷】恶人·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凤鸣堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【惊虬谷】浩气·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·恶人大旗",},},},</v>
       </c>
       <c r="U135" t="s">
         <v>2505</v>
       </c>
       <c r="V135" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G135&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·浩气大旗",},</v>
       </c>
       <c r="W135" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H135&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·浩气大旗",},</v>
       </c>
       <c r="X135" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G135&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·恶人大旗",},</v>
       </c>
       <c r="Y135" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H135&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},</v>
       </c>
       <c r="Z135" t="s">
         <v>2506</v>
@@ -44928,37 +44908,37 @@
         <v>2507</v>
       </c>
       <c r="AB135" t="s">
-        <v>2562</v>
+        <v>2568</v>
       </c>
       <c r="AC135" t="s">
-        <v>2563</v>
+        <v>2569</v>
       </c>
       <c r="AD135" t="s">
-        <v>2564</v>
+        <v>2570</v>
       </c>
       <c r="AE135" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G135&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G135&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【大理山城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【凤鸣堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·浩气大旗",},</v>
       </c>
       <c r="AF135" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H135&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H135&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【千岩关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【惊虬谷】恶人·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·浩气大旗",},</v>
       </c>
       <c r="AG135" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G135&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G135&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【大理山城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【凤鸣堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·恶人大旗",},</v>
       </c>
       <c r="AH135" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H135&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H135&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【千岩关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【惊虬谷】浩气·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·恶人大旗",},</v>
       </c>
     </row>
     <row r="136" spans="1:34">
       <c r="C136" t="s">
-        <v>2565</v>
+        <v>2571</v>
       </c>
       <c r="D136" t="s">
-        <v>2566</v>
+        <v>2572</v>
       </c>
       <c r="K136" t="s">
         <v>1656</v>
@@ -44968,7 +44948,7 @@
       </c>
       <c r="T136" t="str">
         <f t="shared" si="4"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="大理山城·大旗重置",nTime=-2,nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=1465,szName="千岩关·大旗重置",nTime=-2,nRefresh=7200,key="千岩关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【大理山城】大旗重置",nTime="180,【大理山城】大旗重置;185,【大理山城】大旗重置·结束",nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【千岩关】大旗重置",nTime="180,【千岩关】大旗重置;185,【千岩关】大旗重置·结束",nRefresh=7200,key="千岩关·大旗重置",},},},</v>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凤鸣堡·大旗重置",nTime=-2,nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=1465,szName="惊虬谷·大旗重置",nTime=-2,nRefresh=7200,key="惊虬谷·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凤鸣堡】大旗重置",nTime="180,【凤鸣堡】大旗重置;185,【凤鸣堡】大旗重置·结束",nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【惊虬谷】大旗重置",nTime="180,【惊虬谷】大旗重置;185,【惊虬谷】大旗重置·结束",nRefresh=7200,key="惊虬谷·大旗重置",},},},</v>
       </c>
       <c r="U136" t="s">
         <v>2645</v>
@@ -44977,10 +44957,10 @@
         <v>2646</v>
       </c>
       <c r="W136" t="s">
-        <v>2568</v>
+        <v>2574</v>
       </c>
       <c r="X136" t="s">
-        <v>2569</v>
+        <v>2575</v>
       </c>
       <c r="Y136" t="s">
         <v>2647</v>
@@ -44991,14 +44971,14 @@
     </row>
     <row r="137" spans="1:34">
       <c r="A137" t="s">
-        <v>948</v>
+        <v>853</v>
       </c>
       <c r="B137">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="T137" t="str">
         <f t="shared" si="4"/>
-        <v>},[139]={</v>
+        <v>},[105]={</v>
       </c>
     </row>
     <row r="138" customFormat="1" spans="1:34">
@@ -45022,26 +45002,26 @@
       </c>
       <c r="T138" t="str">
         <f t="shared" si="4"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【枫湖寨】恶人·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【啖杏林】恶人·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【枫湖寨】浩气·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【啖杏林】浩气·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·恶人大旗",},},},</v>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【大理山城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【千岩关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【大理山城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【千岩关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·恶人大旗",},},},</v>
       </c>
       <c r="U138" t="s">
         <v>2505</v>
       </c>
       <c r="V138" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G138&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·浩气大旗",},</v>
       </c>
       <c r="W138" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H138&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·浩气大旗",},</v>
       </c>
       <c r="X138" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G138&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·恶人大旗",},</v>
       </c>
       <c r="Y138" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H138&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·恶人大旗",},</v>
       </c>
       <c r="Z138" t="s">
         <v>2506</v>
@@ -45050,37 +45030,37 @@
         <v>2507</v>
       </c>
       <c r="AB138" t="s">
-        <v>2562</v>
+        <v>2568</v>
       </c>
       <c r="AC138" t="s">
-        <v>2563</v>
+        <v>2569</v>
       </c>
       <c r="AD138" t="s">
-        <v>2564</v>
+        <v>2570</v>
       </c>
       <c r="AE138" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G138&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G138&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【枫湖寨】恶人·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【大理山城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·浩气大旗",},</v>
       </c>
       <c r="AF138" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H138&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H138&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【啖杏林】恶人·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【千岩关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·浩气大旗",},</v>
       </c>
       <c r="AG138" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G138&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G138&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【枫湖寨】浩气·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【大理山城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·恶人大旗",},</v>
       </c>
       <c r="AH138" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H138&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H138&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【啖杏林】浩气·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【千岩关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·恶人大旗",},</v>
       </c>
     </row>
     <row r="139" spans="1:34">
       <c r="C139" t="s">
-        <v>2565</v>
+        <v>2571</v>
       </c>
       <c r="D139" t="s">
-        <v>2566</v>
+        <v>2572</v>
       </c>
       <c r="K139" t="s">
         <v>1656</v>
@@ -45090,7 +45070,7 @@
       </c>
       <c r="T139" t="str">
         <f t="shared" si="4"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="枫湖寨·大旗重置",nTime=-2,nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=1465,szName="啖杏林·大旗重置",nTime=-2,nRefresh=7200,key="啖杏林·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【枫湖寨】大旗重置",nTime="180,【枫湖寨】大旗重置;185,【枫湖寨】大旗重置·结束",nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【啖杏林】大旗重置",nTime="180,【啖杏林】大旗重置;185,【啖杏林】大旗重置·结束",nRefresh=7200,key="啖杏林·大旗重置",},},},</v>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="大理山城·大旗重置",nTime=-2,nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=1465,szName="千岩关·大旗重置",nTime=-2,nRefresh=7200,key="千岩关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【大理山城】大旗重置",nTime="180,【大理山城】大旗重置;185,【大理山城】大旗重置·结束",nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【千岩关】大旗重置",nTime="180,【千岩关】大旗重置;185,【千岩关】大旗重置·结束",nRefresh=7200,key="千岩关·大旗重置",},},},</v>
       </c>
       <c r="U139" t="s">
         <v>2651</v>
@@ -45099,10 +45079,10 @@
         <v>2652</v>
       </c>
       <c r="W139" t="s">
-        <v>2568</v>
+        <v>2574</v>
       </c>
       <c r="X139" t="s">
-        <v>2569</v>
+        <v>2575</v>
       </c>
       <c r="Y139" t="s">
         <v>2653</v>
@@ -45113,14 +45093,14 @@
     </row>
     <row r="140" spans="1:34">
       <c r="A140" t="s">
-        <v>984</v>
+        <v>948</v>
       </c>
       <c r="B140">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="T140" t="str">
         <f t="shared" si="4"/>
-        <v>},[153]={</v>
+        <v>},[139]={</v>
       </c>
     </row>
     <row r="141" customFormat="1" spans="1:34">
@@ -45144,26 +45124,26 @@
       </c>
       <c r="T141" t="str">
         <f t="shared" si="4"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【扶风郡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【世外坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【扶风郡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【世外坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·恶人大旗",},},},</v>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【枫湖寨】恶人·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【啖杏林】恶人·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【枫湖寨】浩气·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【啖杏林】浩气·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·恶人大旗",},},},</v>
       </c>
       <c r="U141" t="s">
         <v>2505</v>
       </c>
       <c r="V141" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G141&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·浩气大旗",},</v>
       </c>
       <c r="W141" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H141&amp;"·浩气大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·浩气大旗",},</v>
       </c>
       <c r="X141" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G141&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·恶人大旗",},</v>
       </c>
       <c r="Y141" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H141&amp;"·恶人大旗"&amp;""",},"</f>
-        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·恶人大旗",},</v>
       </c>
       <c r="Z141" t="s">
         <v>2506</v>
@@ -45172,37 +45152,37 @@
         <v>2507</v>
       </c>
       <c r="AB141" t="s">
-        <v>2562</v>
+        <v>2568</v>
       </c>
       <c r="AC141" t="s">
-        <v>2563</v>
+        <v>2569</v>
       </c>
       <c r="AD141" t="s">
-        <v>2564</v>
+        <v>2570</v>
       </c>
       <c r="AE141" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G141&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G141&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【扶风郡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【枫湖寨】恶人·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·浩气大旗",},</v>
       </c>
       <c r="AF141" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H141&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H141&amp;"·浩气大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【世外坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·浩气大旗",},</v>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【啖杏林】恶人·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·浩气大旗",},</v>
       </c>
       <c r="AG141" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G141&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G141&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【扶风郡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【枫湖寨】浩气·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·恶人大旗",},</v>
       </c>
       <c r="AH141" t="str">
         <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H141&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H141&amp;"·恶人大旗"""&amp;",},"</f>
-        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【世外坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·恶人大旗",},</v>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【啖杏林】浩气·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·恶人大旗",},</v>
       </c>
     </row>
     <row r="142" spans="1:34">
       <c r="C142" t="s">
-        <v>2565</v>
+        <v>2571</v>
       </c>
       <c r="D142" t="s">
-        <v>2566</v>
+        <v>2572</v>
       </c>
       <c r="K142" t="s">
         <v>1656</v>
@@ -45212,7 +45192,7 @@
       </c>
       <c r="T142" t="str">
         <f t="shared" si="4"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="扶风郡·大旗重置",nTime=-2,nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=1465,szName="世外坡·大旗重置",nTime=-2,nRefresh=7200,key="世外坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【扶风郡】大旗重置",nTime="180,【扶风郡】大旗重置;185,【扶风郡】大旗重置·结束",nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【世外坡】大旗重置",nTime="180,【世外坡】大旗重置;185,【世外坡】大旗重置·结束",nRefresh=7200,key="世外坡·大旗重置",},},},</v>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="枫湖寨·大旗重置",nTime=-2,nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=1465,szName="啖杏林·大旗重置",nTime=-2,nRefresh=7200,key="啖杏林·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【枫湖寨】大旗重置",nTime="180,【枫湖寨】大旗重置;185,【枫湖寨】大旗重置·结束",nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【啖杏林】大旗重置",nTime="180,【啖杏林】大旗重置;185,【啖杏林】大旗重置·结束",nRefresh=7200,key="啖杏林·大旗重置",},},},</v>
       </c>
       <c r="U142" t="s">
         <v>2657</v>
@@ -45221,10 +45201,10 @@
         <v>2658</v>
       </c>
       <c r="W142" t="s">
-        <v>2568</v>
+        <v>2574</v>
       </c>
       <c r="X142" t="s">
-        <v>2569</v>
+        <v>2575</v>
       </c>
       <c r="Y142" t="s">
         <v>2659</v>
@@ -45235,28 +45215,28 @@
     </row>
     <row r="143" spans="1:34">
       <c r="A143" t="s">
-        <v>1062</v>
+        <v>984</v>
       </c>
       <c r="B143">
-        <v>216</v>
+        <v>153</v>
       </c>
       <c r="T143" t="str">
         <f t="shared" si="4"/>
-        <v>},[216]={</v>
-      </c>
-    </row>
-    <row r="144" spans="1:34">
+        <v>},[153]={</v>
+      </c>
+    </row>
+    <row r="144" customFormat="1" spans="1:34">
       <c r="C144" t="s">
-        <v>2661</v>
+        <v>2503</v>
       </c>
       <c r="D144" t="s">
         <v>2504</v>
       </c>
       <c r="G144" t="s">
+        <v>2661</v>
+      </c>
+      <c r="H144" t="s">
         <v>2662</v>
-      </c>
-      <c r="H144" t="s">
-        <v>2663</v>
       </c>
       <c r="K144" t="s">
         <v>1656</v>
@@ -45266,33 +45246,65 @@
       </c>
       <c r="T144" t="str">
         <f t="shared" si="4"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【扶风郡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【世外坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【扶风郡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【世外坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U144" t="s">
         <v>2505</v>
       </c>
-      <c r="V144" t="s">
+      <c r="V144" t="str">
+        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G144&amp;"·浩气大旗"&amp;""",},"</f>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·浩气大旗",},</v>
+      </c>
+      <c r="W144" t="str">
+        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H144&amp;"·浩气大旗"&amp;""",},"</f>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·浩气大旗",},</v>
+      </c>
+      <c r="X144" t="str">
+        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G144&amp;"·恶人大旗"&amp;""",},"</f>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·恶人大旗",},</v>
+      </c>
+      <c r="Y144" t="str">
+        <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;H144&amp;"·恶人大旗"&amp;""",},"</f>
+        <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·恶人大旗",},</v>
+      </c>
+      <c r="Z144" t="s">
         <v>2506</v>
       </c>
-      <c r="W144" t="s">
+      <c r="AA144" t="s">
         <v>2507</v>
       </c>
-      <c r="X144" t="s">
-        <v>2664</v>
-      </c>
-      <c r="Y144" t="s">
-        <v>2509</v>
-      </c>
-      <c r="Z144" t="s">
-        <v>2510</v>
+      <c r="AB144" t="s">
+        <v>2568</v>
+      </c>
+      <c r="AC144" t="s">
+        <v>2569</v>
+      </c>
+      <c r="AD144" t="s">
+        <v>2570</v>
+      </c>
+      <c r="AE144" t="str">
+        <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G144&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G144&amp;"·浩气大旗"""&amp;",},"</f>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【扶风郡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·浩气大旗",},</v>
+      </c>
+      <c r="AF144" t="str">
+        <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;H144&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H144&amp;"·浩气大旗"""&amp;",},"</f>
+        <v>{nClass=20,nIcon=3445,nFrame=3,szName="【世外坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·浩气大旗",},</v>
+      </c>
+      <c r="AG144" t="str">
+        <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;G144&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G144&amp;"·恶人大旗"""&amp;",},"</f>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【扶风郡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·恶人大旗",},</v>
+      </c>
+      <c r="AH144" t="str">
+        <f>"{nClass=20,nIcon=3444,nFrame=7,szName="&amp;"""【"&amp;H144&amp;"】浩气·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;H144&amp;"·恶人大旗"""&amp;",},"</f>
+        <v>{nClass=20,nIcon=3444,nFrame=7,szName="【世外坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·恶人大旗",},</v>
       </c>
     </row>
     <row r="145" spans="1:26">
       <c r="C145" t="s">
-        <v>2565</v>
+        <v>2571</v>
       </c>
       <c r="D145" t="s">
-        <v>2566</v>
+        <v>2572</v>
       </c>
       <c r="K145" t="s">
         <v>1656</v>
@@ -45302,84 +45314,87 @@
       </c>
       <c r="T145" t="str">
         <f t="shared" si="4"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime="180,【云台营】大旗重置;185,【云台营】大旗重置·结束",nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime="180,【高阳营】大旗重置;185,【高阳营】大旗重置·结束",nRefresh=7200,key="高阳营·大旗重置",},},},</v>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="扶风郡·大旗重置",nTime=-2,nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=1465,szName="世外坡·大旗重置",nTime=-2,nRefresh=7200,key="世外坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【扶风郡】大旗重置",nTime="180,【扶风郡】大旗重置;185,【扶风郡】大旗重置·结束",nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【世外坡】大旗重置",nTime="180,【世外坡】大旗重置;185,【世外坡】大旗重置·结束",nRefresh=7200,key="世外坡·大旗重置",},},},</v>
       </c>
       <c r="U145" t="s">
+        <v>2663</v>
+      </c>
+      <c r="V145" t="s">
+        <v>2664</v>
+      </c>
+      <c r="W145" t="s">
+        <v>2574</v>
+      </c>
+      <c r="X145" t="s">
+        <v>2575</v>
+      </c>
+      <c r="Y145" t="s">
         <v>2665</v>
       </c>
-      <c r="V145" t="s">
+      <c r="Z145" t="s">
         <v>2666</v>
       </c>
-      <c r="W145" t="s">
-        <v>2568</v>
-      </c>
-      <c r="X145" t="s">
-        <v>2569</v>
-      </c>
-      <c r="Y145" t="s">
-        <v>2667</v>
-      </c>
-      <c r="Z145" t="s">
-        <v>2668</v>
-      </c>
-    </row>
-    <row r="146" customFormat="1" spans="1:26">
-      <c r="C146" s="3" t="s">
-        <v>2543</v>
-      </c>
-      <c r="D146" t="s">
-        <v>2544</v>
-      </c>
-      <c r="K146" t="s">
-        <v>1656</v>
-      </c>
-      <c r="M146">
-        <v>1</v>
+    </row>
+    <row r="146" spans="1:26">
+      <c r="A146" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B146">
+        <v>216</v>
       </c>
       <c r="T146" t="str">
         <f t="shared" si="4"/>
-        <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
-      </c>
-      <c r="U146" t="s">
-        <v>2545</v>
-      </c>
-      <c r="V146" t="s">
-        <v>2546</v>
-      </c>
-      <c r="W146" t="s">
-        <v>2547</v>
-      </c>
-      <c r="X146" t="s">
-        <v>2548</v>
-      </c>
-      <c r="Y146" t="s">
-        <v>2549</v>
+        <v>},[216]={</v>
       </c>
     </row>
     <row r="147" spans="1:26">
-      <c r="A147" t="s">
-        <v>1415</v>
-      </c>
-      <c r="B147">
-        <v>656</v>
+      <c r="C147" t="s">
+        <v>2667</v>
+      </c>
+      <c r="D147" t="s">
+        <v>2504</v>
+      </c>
+      <c r="G147" t="s">
+        <v>2668</v>
+      </c>
+      <c r="H147" t="s">
+        <v>2669</v>
+      </c>
+      <c r="K147" t="s">
+        <v>1656</v>
+      </c>
+      <c r="M147">
+        <v>1</v>
       </c>
       <c r="T147" t="str">
         <f t="shared" si="4"/>
-        <v>},[656]={</v>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
+      </c>
+      <c r="U147" t="s">
+        <v>2505</v>
+      </c>
+      <c r="V147" t="s">
+        <v>2506</v>
+      </c>
+      <c r="W147" t="s">
+        <v>2507</v>
+      </c>
+      <c r="X147" t="s">
+        <v>2670</v>
+      </c>
+      <c r="Y147" t="s">
+        <v>2509</v>
+      </c>
+      <c r="Z147" t="s">
+        <v>2510</v>
       </c>
     </row>
     <row r="148" spans="1:26">
       <c r="C148" t="s">
-        <v>2661</v>
+        <v>2571</v>
       </c>
       <c r="D148" t="s">
-        <v>2504</v>
-      </c>
-      <c r="G148" t="s">
-        <v>2662</v>
-      </c>
-      <c r="H148" t="s">
-        <v>2663</v>
+        <v>2572</v>
       </c>
       <c r="K148" t="s">
         <v>1656</v>
@@ -45389,33 +45404,33 @@
       </c>
       <c r="T148" t="str">
         <f t="shared" si="4"/>
-        <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime="180,【云台营】大旗重置;185,【云台营】大旗重置·结束",nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime="180,【高阳营】大旗重置;185,【高阳营】大旗重置·结束",nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U148" t="s">
-        <v>2505</v>
+        <v>2671</v>
       </c>
       <c r="V148" t="s">
-        <v>2506</v>
+        <v>2672</v>
       </c>
       <c r="W148" t="s">
-        <v>2507</v>
+        <v>2574</v>
       </c>
       <c r="X148" t="s">
-        <v>2664</v>
+        <v>2575</v>
       </c>
       <c r="Y148" t="s">
-        <v>2509</v>
+        <v>2673</v>
       </c>
       <c r="Z148" t="s">
-        <v>2510</v>
-      </c>
-    </row>
-    <row r="149" spans="1:26">
-      <c r="C149" t="s">
-        <v>2565</v>
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="149" customFormat="1" spans="1:26">
+      <c r="C149" s="3" t="s">
+        <v>2549</v>
       </c>
       <c r="D149" t="s">
-        <v>2566</v>
+        <v>2550</v>
       </c>
       <c r="K149" t="s">
         <v>1656</v>
@@ -45425,68 +45440,155 @@
       </c>
       <c r="T149" t="str">
         <f t="shared" si="4"/>
-        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime="180,【云台营】大旗重置;185,【云台营】大旗重置·结束",nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime="180,【高阳营】大旗重置;185,【高阳营】大旗重置·结束",nRefresh=7200,key="高阳营·大旗重置",},},},</v>
+        <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U149" t="s">
-        <v>2665</v>
+        <v>2551</v>
       </c>
       <c r="V149" t="s">
-        <v>2666</v>
+        <v>2552</v>
       </c>
       <c r="W149" t="s">
-        <v>2568</v>
+        <v>2553</v>
       </c>
       <c r="X149" t="s">
-        <v>2569</v>
+        <v>2554</v>
       </c>
       <c r="Y149" t="s">
-        <v>2667</v>
-      </c>
-      <c r="Z149" t="s">
-        <v>2668</v>
-      </c>
-    </row>
-    <row r="150" customFormat="1" spans="1:26">
-      <c r="C150" s="3" t="s">
-        <v>2543</v>
-      </c>
-      <c r="D150" t="s">
-        <v>2544</v>
-      </c>
-      <c r="K150" t="s">
-        <v>1656</v>
-      </c>
-      <c r="M150">
-        <v>1</v>
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="150" spans="1:26">
+      <c r="A150" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B150">
+        <v>656</v>
       </c>
       <c r="T150" t="str">
         <f t="shared" si="4"/>
-        <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
-      </c>
-      <c r="U150" t="s">
-        <v>2545</v>
-      </c>
-      <c r="V150" t="s">
-        <v>2546</v>
-      </c>
-      <c r="W150" t="s">
-        <v>2547</v>
-      </c>
-      <c r="X150" t="s">
-        <v>2548</v>
-      </c>
-      <c r="Y150" t="s">
-        <v>2549</v>
+        <v>},[656]={</v>
       </c>
     </row>
     <row r="151" spans="1:26">
+      <c r="C151" t="s">
+        <v>2667</v>
+      </c>
+      <c r="D151" t="s">
+        <v>2504</v>
+      </c>
+      <c r="G151" t="s">
+        <v>2668</v>
+      </c>
+      <c r="H151" t="s">
+        <v>2669</v>
+      </c>
+      <c r="K151" t="s">
+        <v>1656</v>
+      </c>
+      <c r="M151">
+        <v>1</v>
+      </c>
       <c r="T151" t="str">
         <f t="shared" si="4"/>
+        <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
+      </c>
+      <c r="U151" t="s">
+        <v>2505</v>
+      </c>
+      <c r="V151" t="s">
+        <v>2506</v>
+      </c>
+      <c r="W151" t="s">
+        <v>2507</v>
+      </c>
+      <c r="X151" t="s">
+        <v>2670</v>
+      </c>
+      <c r="Y151" t="s">
+        <v>2509</v>
+      </c>
+      <c r="Z151" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="152" spans="1:26">
+      <c r="C152" t="s">
+        <v>2571</v>
+      </c>
+      <c r="D152" t="s">
+        <v>2572</v>
+      </c>
+      <c r="K152" t="s">
+        <v>1656</v>
+      </c>
+      <c r="M152">
+        <v>1</v>
+      </c>
+      <c r="T152" t="str">
+        <f t="shared" si="4"/>
+        <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime="180,【云台营】大旗重置;185,【云台营】大旗重置·结束",nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime="180,【高阳营】大旗重置;185,【高阳营】大旗重置·结束",nRefresh=7200,key="高阳营·大旗重置",},},},</v>
+      </c>
+      <c r="U152" t="s">
+        <v>2671</v>
+      </c>
+      <c r="V152" t="s">
+        <v>2672</v>
+      </c>
+      <c r="W152" t="s">
+        <v>2574</v>
+      </c>
+      <c r="X152" t="s">
+        <v>2575</v>
+      </c>
+      <c r="Y152" t="s">
+        <v>2673</v>
+      </c>
+      <c r="Z152" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="153" customFormat="1" spans="1:26">
+      <c r="C153" s="3" t="s">
+        <v>2549</v>
+      </c>
+      <c r="D153" t="s">
+        <v>2550</v>
+      </c>
+      <c r="K153" t="s">
+        <v>1656</v>
+      </c>
+      <c r="M153">
+        <v>1</v>
+      </c>
+      <c r="T153" t="str">
+        <f t="shared" si="4"/>
+        <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
+      </c>
+      <c r="U153" t="s">
+        <v>2551</v>
+      </c>
+      <c r="V153" t="s">
+        <v>2552</v>
+      </c>
+      <c r="W153" t="s">
+        <v>2553</v>
+      </c>
+      <c r="X153" t="s">
+        <v>2554</v>
+      </c>
+      <c r="Y153" t="s">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="154" spans="1:26">
+      <c r="T154" t="str">
+        <f t="shared" si="4"/>
         <v>},},}</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:BG151" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:BG154" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/阵营/大小攻防团队监控.xlsx
+++ b/阵营/大小攻防团队监控.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="8"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据总控" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">有利气劲!$A$1:$AS$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">不利气劲!$A$1:$BY$98</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">系统角色!$A$1:$X$414</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">角色喊话!$A$1:$AV$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">角色喊话!$A$1:$AV$198</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">系统频道!$A$1:$BG$154</definedName>
     <definedName name="JunSun1" localSheetId="6">DATE(交互物件!日历年份,6,1)-WEEKDAY(DATE(交互物件!日历年份,6,1))</definedName>
     <definedName name="JunSun1" localSheetId="4">DATE(武学招式!日历年份,6,1)-WEEKDAY(DATE(武学招式!日历年份,6,1))</definedName>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5932" uniqueCount="2703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5936" uniqueCount="2705">
   <si>
     <t>__meta = {</t>
   </si>
@@ -6772,6 +6772,12 @@
     <t>{nClass=14,nIcon=3536,nFrame=7,szName="巴陵·攻防前置分流",nTime=30,nRefresh=1800,key="分流活动",},</t>
   </si>
   <si>
+    <t>万水千山总是情，买满货物行不行？</t>
+  </si>
+  <si>
+    <t>据点贸易·货物不足</t>
+  </si>
+  <si>
     <t>因侠士近来行为异常，逐鹿中原期间，禁止参与，你即将被传送到百溪！</t>
   </si>
   <si>
@@ -7732,10 +7738,10 @@
     <t>秘境地图</t>
   </si>
   <si>
-    <t>{nClass=20,nIcon=5815,nFrame=3,szName="主战场·恶人谷",nTime="1,阵营攻防·开始排队·恶人谷;10,阵营攻防·开始排队·恶人谷",key="大攻防·主战场",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=5815,nFrame=7,szName="主战场·浩气盟",nTime="1,阵营攻防·开始排队·浩气盟;10,阵营攻防·开始排队·浩气盟",key="大攻防·主战场",},</t>
+    <t>{nClass=20,nIcon=5815,nFrame=3,szName="主战场·恶人谷",nTime="1,阵营攻防·开始排队·恶人谷;10,阵营攻防·开始排队·恶人谷",nRefresh=1,key="大攻防·主战场",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=5815,nFrame=7,szName="主战场·浩气盟",nTime="1,阵营攻防·开始排队·浩气盟;10,阵营攻防·开始排队·浩气盟",nRefresh=1,key="大攻防·主战场",},</t>
   </si>
   <si>
     <t>本场攻防“奇袭场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n</t>
@@ -9488,7 +9494,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="34" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1781955736000,</v>
+        <v>nTimeStamp = 1782111356000,</v>
       </c>
       <c r="B4" s="38" t="s">
         <v>11</v>
@@ -11231,10 +11237,10 @@
         <v>1817</v>
       </c>
       <c r="B3" t="s">
-        <v>2567</v>
+        <v>2569</v>
       </c>
       <c r="C3" t="s">
-        <v>2675</v>
+        <v>2677</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -11242,10 +11248,10 @@
         <v>1837</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2584</v>
+        <v>2586</v>
       </c>
       <c r="C4" t="s">
-        <v>2676</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -11253,10 +11259,10 @@
         <v>1844</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2595</v>
+        <v>2597</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>2677</v>
+        <v>2679</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -11264,10 +11270,10 @@
         <v>1848</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2596</v>
+        <v>2598</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2678</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -11275,10 +11281,10 @@
         <v>1856</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2601</v>
+        <v>2603</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>2679</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -11286,10 +11292,10 @@
         <v>1860</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2602</v>
+        <v>2604</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>2680</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -11297,10 +11303,10 @@
         <v>1873</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2607</v>
+        <v>2609</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>2681</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -11308,10 +11314,10 @@
         <v>1877</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2608</v>
+        <v>2610</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>2682</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -11319,10 +11325,10 @@
         <v>1881</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2613</v>
+        <v>2615</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>2683</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -11330,10 +11336,10 @@
         <v>1885</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2614</v>
+        <v>2616</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>2684</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -11341,10 +11347,10 @@
         <v>1889</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2619</v>
+        <v>2621</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>2685</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -11352,10 +11358,10 @@
         <v>1893</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>2620</v>
+        <v>2622</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>2686</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -11363,10 +11369,10 @@
         <v>1899</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>2625</v>
+        <v>2627</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>2687</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -11374,10 +11380,10 @@
         <v>1903</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2626</v>
+        <v>2628</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>2688</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -11385,10 +11391,10 @@
         <v>1907</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2631</v>
+        <v>2633</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>2689</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -11396,10 +11402,10 @@
         <v>1911</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>2632</v>
+        <v>2634</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>2690</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -11407,10 +11413,10 @@
         <v>1917</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>2637</v>
+        <v>2639</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>2691</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -11418,10 +11424,10 @@
         <v>1921</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2638</v>
+        <v>2640</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>2692</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -11429,10 +11435,10 @@
         <v>1925</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>2643</v>
+        <v>2645</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>2693</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -11440,10 +11446,10 @@
         <v>1929</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2644</v>
+        <v>2646</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>2694</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -11451,10 +11457,10 @@
         <v>1933</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>2649</v>
+        <v>2651</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>2695</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -11462,10 +11468,10 @@
         <v>1937</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2650</v>
+        <v>2652</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>2696</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -11473,10 +11479,10 @@
         <v>1945</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2655</v>
+        <v>2657</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>2697</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -11484,10 +11490,10 @@
         <v>1949</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2656</v>
+        <v>2658</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>2698</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -11495,10 +11501,10 @@
         <v>1953</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2661</v>
+        <v>2663</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>2699</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -11506,10 +11512,10 @@
         <v>1957</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2662</v>
+        <v>2664</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2700</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -11517,10 +11523,10 @@
         <v>1978</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2668</v>
+        <v>2670</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2701</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -11528,10 +11534,10 @@
         <v>1982</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>2669</v>
+        <v>2671</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>2702</v>
+        <v>2704</v>
       </c>
     </row>
   </sheetData>
@@ -34717,7 +34723,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB197"/>
+  <dimension ref="A1:AB198"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="4" width="52.125" customWidth="1"/>
@@ -39225,23 +39231,26 @@
       <c r="M103" t="s">
         <v>1470</v>
       </c>
+      <c r="P103" t="s">
+        <v>714</v>
+      </c>
       <c r="S103">
+        <v>1</v>
+      </c>
+      <c r="U103">
         <v>1</v>
       </c>
       <c r="V103" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="因侠士近来行为异常，逐鹿中原期间，禁止参与，你即将被传送到百溪！",szNote="据点攻防·禁止参与",col={255,50,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,bHold=true,nTime=30,szName="据点攻防·禁止参与本场",key="挂机检测",},},},</v>
-      </c>
-      <c r="W103" t="s">
-        <v>2239</v>
+        <v>{szContent="万水千山总是情，买满货物行不行？",szNote="据点贸易·货物不足",col={255,50,255,},[14]={szVoice="ShiYongDaoJu",bCenterAlarm=true,bFullScreen=true,},},</v>
       </c>
     </row>
     <row r="104" customFormat="1" spans="1:27">
       <c r="D104" t="s">
+        <v>2239</v>
+      </c>
+      <c r="E104" t="s">
         <v>2240</v>
-      </c>
-      <c r="E104" t="s">
-        <v>2241</v>
       </c>
       <c r="M104" t="s">
         <v>1470</v>
@@ -39251,55 +39260,61 @@
       </c>
       <c r="V104" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="侠士对抗类装分过低，请前往分流场景或黑戈壁参与。",szNote="据点攻防·装分过低",col={255,50,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,bHold=true,nTime=30,szName="据点攻防·装分过低",key="挂机检测",},},},</v>
+        <v>{szContent="因侠士近来行为异常，逐鹿中原期间，禁止参与，你即将被传送到百溪！",szNote="据点攻防·禁止参与",col={255,50,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,bHold=true,nTime=30,szName="据点攻防·禁止参与本场",key="挂机检测",},},},</v>
       </c>
       <c r="W104" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="105" customFormat="1" spans="1:27">
       <c r="D105" t="s">
+        <v>2242</v>
+      </c>
+      <c r="E105" t="s">
         <v>2243</v>
-      </c>
-      <c r="E105" t="s">
-        <v>2244</v>
       </c>
       <c r="M105" t="s">
         <v>1470</v>
       </c>
-      <c r="P105" t="s">
-        <v>538</v>
-      </c>
-      <c r="Q105">
-        <v>1</v>
-      </c>
-      <c r="R105">
-        <v>1</v>
-      </c>
       <c r="S105">
-        <v>1</v>
-      </c>
-      <c r="U105">
         <v>1</v>
       </c>
       <c r="V105" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="系统检测您有挂机行为，如果长期维持该状态将被传送出图！",szNote="挂机检测·快活跃起来",col={255,50,255,},[14]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},},},</v>
+        <v>{szContent="侠士对抗类装分过低，请前往分流场景或黑戈壁参与。",szNote="据点攻防·装分过低",col={255,50,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,bHold=true,nTime=30,szName="据点攻防·装分过低",key="挂机检测",},},},</v>
       </c>
       <c r="W105" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="106" customFormat="1" spans="1:27">
       <c r="D106" t="s">
+        <v>2245</v>
+      </c>
+      <c r="E106" t="s">
         <v>2246</v>
       </c>
       <c r="M106" t="s">
-        <v>1656</v>
+        <v>1470</v>
+      </c>
+      <c r="P106" t="s">
+        <v>538</v>
+      </c>
+      <c r="Q106">
+        <v>1</v>
+      </c>
+      <c r="R106">
+        <v>1</v>
+      </c>
+      <c r="S106">
+        <v>1</v>
+      </c>
+      <c r="U106">
+        <v>1</v>
       </c>
       <c r="V106" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="据点大旗·旗手提示",},},},</v>
+        <v>{szContent="系统检测您有挂机行为，如果长期维持该状态将被传送出图！",szNote="挂机检测·快活跃起来",col={255,50,255,},[14]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},},},</v>
       </c>
       <c r="W106" t="s">
         <v>2247</v>
@@ -39309,40 +39324,28 @@
       <c r="D107" t="s">
         <v>2248</v>
       </c>
-      <c r="E107" t="s">
-        <v>2249</v>
-      </c>
       <c r="M107" t="s">
         <v>1656</v>
       </c>
-      <c r="Q107">
-        <v>1</v>
-      </c>
-      <c r="S107">
-        <v>1</v>
-      </c>
       <c r="V107" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="身负据点大旗，当心被夺！",szNote="[{$me}]·扛起大旗",col={255,255,100,},[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=8,szName="【{$me}】·拾取大旗",nTime=30,key="拾取大旗·{$me}",},},},</v>
+        <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="据点大旗·旗手提示",},},},</v>
       </c>
       <c r="W107" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="108" customFormat="1" spans="1:27">
+      <c r="D108" t="s">
         <v>2250</v>
       </c>
-    </row>
-    <row r="108" customFormat="1" spans="1:27">
-      <c r="C108" t="s">
-        <v>2068</v>
-      </c>
-      <c r="D108" t="s">
+      <c r="E108" t="s">
         <v>2251</v>
-      </c>
-      <c r="E108" t="s">
-        <v>2252</v>
       </c>
       <c r="M108" t="s">
         <v>1656</v>
       </c>
-      <c r="O108">
+      <c r="Q108">
         <v>1</v>
       </c>
       <c r="S108">
@@ -39350,22 +39353,10 @@
       </c>
       <c r="V108" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="^%[逐鹿中原%]%[(.-)%]：正在(.-)城门！",szTarget="%",szNote="[{$1}]·{$2}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,nFrame=5,nTime=-2,szName="打开·城门",nRefresh=10,key="打开·城门",},{nClass=14,nIcon=1465,nFrame=5,nTime=-2,szName="关闭·城门",nRefresh=10,key="关闭·城门",},{nClass=14,nIcon=13,nFrame=5,nTime=-2,szName="{$2}·城门",key="{$2}·城门",},{nClass=14,nIcon=2310,nFrame=1,nTime=10,szName="城门·打开·[{$1}]",nRefresh=10,key="打开·城门",},{nClass=14,nIcon=4839,nFrame=1,nTime=10,szName="城门·关闭·[{$1}]",nRefresh=10,key="关闭·城门",},},},</v>
+        <v>{szContent="身负据点大旗，当心被夺！",szNote="[{$me}]·扛起大旗",col={255,255,100,},[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=8,szName="【{$me}】·拾取大旗",nTime=30,key="拾取大旗·{$me}",},},},</v>
       </c>
       <c r="W108" t="s">
-        <v>2253</v>
-      </c>
-      <c r="X108" t="s">
-        <v>2254</v>
-      </c>
-      <c r="Y108" t="s">
-        <v>2255</v>
-      </c>
-      <c r="Z108" t="s">
-        <v>2256</v>
-      </c>
-      <c r="AA108" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="109" customFormat="1" spans="1:27">
@@ -39373,10 +39364,10 @@
         <v>2068</v>
       </c>
       <c r="D109" t="s">
-        <v>2258</v>
+        <v>2253</v>
       </c>
       <c r="E109" t="s">
-        <v>2259</v>
+        <v>2254</v>
       </c>
       <c r="M109" t="s">
         <v>1656</v>
@@ -39389,64 +39380,79 @@
       </c>
       <c r="V109" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
+        <v>{szContent="^%[逐鹿中原%]%[(.-)%]：正在(.-)城门！",szTarget="%",szNote="[{$1}]·{$2}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,nFrame=5,nTime=-2,szName="打开·城门",nRefresh=10,key="打开·城门",},{nClass=14,nIcon=1465,nFrame=5,nTime=-2,szName="关闭·城门",nRefresh=10,key="关闭·城门",},{nClass=14,nIcon=13,nFrame=5,nTime=-2,szName="{$2}·城门",key="{$2}·城门",},{nClass=14,nIcon=2310,nFrame=1,nTime=10,szName="城门·打开·[{$1}]",nRefresh=10,key="打开·城门",},{nClass=14,nIcon=4839,nFrame=1,nTime=10,szName="城门·关闭·[{$1}]",nRefresh=10,key="关闭·城门",},},},</v>
       </c>
       <c r="W109" t="s">
-        <v>2260</v>
+        <v>2255</v>
+      </c>
+      <c r="X109" t="s">
+        <v>2256</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>2257</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>2258</v>
+      </c>
+      <c r="AA109" t="s">
+        <v>2259</v>
       </c>
     </row>
     <row r="110" customFormat="1" spans="1:27">
       <c r="C110" t="s">
+        <v>2068</v>
+      </c>
+      <c r="D110" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E110" t="s">
         <v>2261</v>
       </c>
-      <c r="D110" t="s">
-        <v>2262</v>
-      </c>
-      <c r="E110" t="s">
-        <v>2263</v>
-      </c>
       <c r="M110" t="s">
-        <v>1725</v>
+        <v>1656</v>
       </c>
       <c r="O110">
         <v>1</v>
       </c>
       <c r="S110">
-        <v>1</v>
-      </c>
-      <c r="T110">
         <v>1</v>
       </c>
       <c r="V110" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="已为.-补.-%[(.+)%].-(%d-)个.-消耗(%d+%.?%d-)金",szTarget="据点总管",szNote="补货·[{$1}]·{$2}",col={100,255,100,},bReg=true,[14]={bCenterAlarm=true,bScreenHead=true,},tCountdown={{nClass=14,nIcon=13,nFrame=6,szName="阵营模式",nTime=-2,key="阵营模式",},{nClass=14,nIcon=135,nFrame=6,szName="补货·[{$1}]·{$2}",nTime=10,nRefresh=600,key="阵营模式",},},},</v>
+        <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W110" t="s">
-        <v>2264</v>
-      </c>
-      <c r="X110" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="111" customFormat="1" spans="1:27">
       <c r="C111" t="s">
-        <v>2261</v>
+        <v>2263</v>
       </c>
       <c r="D111" t="s">
-        <v>2266</v>
+        <v>2264</v>
+      </c>
+      <c r="E111" t="s">
+        <v>2265</v>
       </c>
       <c r="M111" t="s">
-        <v>1656</v>
+        <v>1725</v>
       </c>
       <c r="O111">
+        <v>1</v>
+      </c>
+      <c r="S111">
+        <v>1</v>
+      </c>
+      <c r="T111">
         <v>1</v>
       </c>
       <c r="V111" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="好嘞，老夫开始收货了。本次特产转为(%d-)个(.-)，(.-)[，]-您辛苦了！",szTarget="据点总管",col={255,255,100,},bReg=true,[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,szName="阵营模式",nTime=-2,key="阵营模式",},{nClass=14,nIcon=374,nFrame=6,szName="{$2}·{$1}{$3}",nTime=10,nRefresh=600,key="阵营模式",},},},</v>
+        <v>{szContent="已为.-补.-%[(.+)%].-(%d-)个.-消耗(%d+%.?%d-)金",szTarget="据点总管",szNote="补货·[{$1}]·{$2}",col={100,255,100,},bReg=true,[14]={bCenterAlarm=true,bScreenHead=true,},tCountdown={{nClass=14,nIcon=13,nFrame=6,szName="阵营模式",nTime=-2,key="阵营模式",},{nClass=14,nIcon=135,nFrame=6,szName="补货·[{$1}]·{$2}",nTime=10,nRefresh=600,key="阵营模式",},},},</v>
       </c>
       <c r="W111" t="s">
-        <v>2264</v>
+        <v>2266</v>
       </c>
       <c r="X111" t="s">
         <v>2267</v>
@@ -39454,29 +39460,26 @@
     </row>
     <row r="112" customFormat="1" spans="1:27">
       <c r="C112" t="s">
-        <v>2068</v>
+        <v>2263</v>
       </c>
       <c r="D112" t="s">
         <v>2268</v>
       </c>
-      <c r="E112" t="s">
-        <v>2269</v>
-      </c>
       <c r="M112" t="s">
-        <v>1470</v>
-      </c>
-      <c r="S112">
-        <v>1</v>
-      </c>
-      <c r="U112">
+        <v>1656</v>
+      </c>
+      <c r="O112">
         <v>1</v>
       </c>
       <c r="V112" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="您因消极怠战,扰乱阵营秩序，被阵营督查官请离当前地图，但同时给予250点贡献积分！",szTarget="%",szNote="阵营督查官·请离据点攻防",col={255,50,255,},[14]={bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,bHold=true,nTime=30,szName="阵营督查·请离据点攻防",key="挂机检测",},},},</v>
+        <v>{szContent="好嘞，老夫开始收货了。本次特产转为(%d-)个(.-)，(.-)[，]-您辛苦了！",szTarget="据点总管",col={255,255,100,},bReg=true,[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,szName="阵营模式",nTime=-2,key="阵营模式",},{nClass=14,nIcon=374,nFrame=6,szName="{$2}·{$1}{$3}",nTime=10,nRefresh=600,key="阵营模式",},},},</v>
       </c>
       <c r="W112" t="s">
-        <v>2270</v>
+        <v>2266</v>
+      </c>
+      <c r="X112" t="s">
+        <v>2269</v>
       </c>
     </row>
     <row r="113" customFormat="1" spans="1:27">
@@ -39484,23 +39487,26 @@
         <v>2068</v>
       </c>
       <c r="D113" t="s">
+        <v>2270</v>
+      </c>
+      <c r="E113" t="s">
         <v>2271</v>
       </c>
       <c r="M113" t="s">
-        <v>2120</v>
-      </c>
-      <c r="N113">
+        <v>1470</v>
+      </c>
+      <c r="S113">
+        <v>1</v>
+      </c>
+      <c r="U113">
         <v>1</v>
       </c>
       <c r="V113" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
+        <v>{szContent="您因消极怠战,扰乱阵营秩序，被阵营督查官请离当前地图，但同时给予250点贡献积分！",szTarget="%",szNote="阵营督查官·请离据点攻防",col={255,50,255,},[14]={bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,bHold=true,nTime=30,szName="阵营督查·请离据点攻防",key="挂机检测",},},},</v>
       </c>
       <c r="W113" t="s">
         <v>2272</v>
-      </c>
-      <c r="X113" t="s">
-        <v>2273</v>
       </c>
     </row>
     <row r="114" customFormat="1" spans="1:27">
@@ -39508,20 +39514,20 @@
         <v>2068</v>
       </c>
       <c r="D114" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="M114" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="N114">
         <v>1</v>
       </c>
       <c r="V114" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
+        <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W114" t="s">
-        <v>2272</v>
+        <v>2274</v>
       </c>
       <c r="X114" t="s">
         <v>2275</v>
@@ -39534,33 +39540,21 @@
       <c r="D115" t="s">
         <v>2276</v>
       </c>
-      <c r="E115" t="s">
-        <v>2277</v>
-      </c>
       <c r="M115" t="s">
-        <v>1656</v>
-      </c>
-      <c r="S115">
+        <v>2121</v>
+      </c>
+      <c r="N115">
         <v>1</v>
       </c>
       <c r="V115" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},},},</v>
+        <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W115" t="s">
-        <v>2278</v>
+        <v>2274</v>
       </c>
       <c r="X115" t="s">
-        <v>2279</v>
-      </c>
-      <c r="Y115" t="s">
-        <v>2280</v>
-      </c>
-      <c r="Z115" t="s">
-        <v>2281</v>
-      </c>
-      <c r="AA115" t="s">
-        <v>2282</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="116" customFormat="1" spans="1:27">
@@ -39568,71 +39562,89 @@
         <v>2068</v>
       </c>
       <c r="D116" t="s">
-        <v>2283</v>
+        <v>2278</v>
       </c>
       <c r="E116" t="s">
-        <v>2284</v>
+        <v>2279</v>
+      </c>
+      <c r="M116" t="s">
+        <v>1656</v>
       </c>
       <c r="S116">
         <v>1</v>
       </c>
       <c r="V116" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="尔等鼠辈！谁敢与我一战！",szTarget="%",szNote="据点攻防·正式开始",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime="2,据点攻防·正式开始;10,建议关闭·江湖身份",nRefresh=2,key="阵营活动",},{nClass=14,nIcon=13,szName="绣球花",nTime=-1,key="绣球花",},{nClass=14,nIcon=13,szName="郁金香",nTime=-1,key="郁金香",},{nClass=14,nIcon=13,szName="牵牛花",nTime=-1,key="牵牛花",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
+        <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},},},</v>
       </c>
       <c r="W116" t="s">
-        <v>2285</v>
-      </c>
-      <c r="X116" s="3" t="s">
-        <v>2286</v>
-      </c>
-      <c r="Y116" s="3" t="s">
-        <v>2287</v>
-      </c>
-      <c r="Z116" s="3" t="s">
-        <v>2288</v>
+        <v>2280</v>
+      </c>
+      <c r="X116" t="s">
+        <v>2281</v>
+      </c>
+      <c r="Y116" t="s">
+        <v>2282</v>
+      </c>
+      <c r="Z116" t="s">
+        <v>2283</v>
+      </c>
+      <c r="AA116" t="s">
+        <v>2284</v>
       </c>
     </row>
     <row r="117" customFormat="1" spans="1:27">
       <c r="C117" t="s">
-        <v>1715</v>
+        <v>2068</v>
       </c>
       <c r="D117" t="s">
-        <v>2289</v>
+        <v>2285</v>
       </c>
       <c r="E117" t="s">
-        <v>2290</v>
+        <v>2286</v>
+      </c>
+      <c r="S117">
+        <v>1</v>
       </c>
       <c r="V117" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="哼，还有要事要办，今日收获甚多，来日定多来领略你们的武功！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·攻防结束",[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领·离开",nTime=0,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
+        <v>{szContent="尔等鼠辈！谁敢与我一战！",szTarget="%",szNote="据点攻防·正式开始",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime="2,据点攻防·正式开始;10,建议关闭·江湖身份",nRefresh=2,key="阵营活动",},{nClass=14,nIcon=13,szName="绣球花",nTime=-1,key="绣球花",},{nClass=14,nIcon=13,szName="郁金香",nTime=-1,key="郁金香",},{nClass=14,nIcon=13,szName="牵牛花",nTime=-1,key="牵牛花",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W117" t="s">
-        <v>2291</v>
-      </c>
-      <c r="X117" s="5" t="s">
-        <v>2292</v>
-      </c>
-      <c r="Y117" s="5" t="s">
-        <v>2293</v>
-      </c>
-    </row>
-    <row r="118" spans="1:27">
+        <v>2287</v>
+      </c>
+      <c r="X117" s="3" t="s">
+        <v>2288</v>
+      </c>
+      <c r="Y117" s="3" t="s">
+        <v>2289</v>
+      </c>
+      <c r="Z117" s="3" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="118" customFormat="1" spans="1:27">
       <c r="C118" t="s">
         <v>1715</v>
       </c>
       <c r="D118" t="s">
-        <v>2294</v>
+        <v>2291</v>
       </c>
       <c r="E118" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="V118" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="哼，打扰本大爷休息！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话1",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},},},</v>
+        <v>{szContent="哼，还有要事要办，今日收获甚多，来日定多来领略你们的武功！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·攻防结束",[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领·离开",nTime=0,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="W118" t="s">
-        <v>2296</v>
+        <v>2293</v>
+      </c>
+      <c r="X118" s="5" t="s">
+        <v>2294</v>
+      </c>
+      <c r="Y118" s="5" t="s">
+        <v>2295</v>
       </c>
     </row>
     <row r="119" spans="1:27">
@@ -39640,23 +39652,17 @@
         <v>1715</v>
       </c>
       <c r="D119" t="s">
+        <v>2296</v>
+      </c>
+      <c r="E119" t="s">
         <v>2297</v>
-      </c>
-      <c r="E119" t="s">
-        <v>2298</v>
       </c>
       <c r="V119" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="你爷爷我年轻些时候，也是翻云覆雨的江湖响当当一号人物！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话2",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
+        <v>{szContent="哼，打扰本大爷休息！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话1",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W119" t="s">
-        <v>2296</v>
-      </c>
-      <c r="X119" s="3" t="s">
-        <v>2287</v>
-      </c>
-      <c r="Y119" s="3" t="s">
-        <v>2288</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="120" spans="1:27">
@@ -39671,73 +39677,76 @@
       </c>
       <c r="V120" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="我竟然败给你们这群小辈！",szTarget="狼牙先锋首领",szNote="防冲突禁用·击退·狼牙先锋首领",[14]={},tCountdown={{nClass=-1,nIcon=3556,nFrame=1,szName="狼牙先锋首领·拾取掉落",nTime="10,狼牙先锋首领·已击退;300,狼牙先锋首领·拾取剩余;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=2,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
+        <v>{szContent="你爷爷我年轻些时候，也是翻云覆雨的江湖响当当一号人物！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话2",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W120" t="s">
+        <v>2298</v>
+      </c>
+      <c r="X120" s="3" t="s">
+        <v>2289</v>
+      </c>
+      <c r="Y120" s="3" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="121" spans="1:27">
+      <c r="C121" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D121" t="s">
         <v>2301</v>
       </c>
-      <c r="X120" s="3" t="s">
-        <v>2287</v>
-      </c>
-      <c r="Y120" s="3" t="s">
-        <v>2288</v>
-      </c>
-    </row>
-    <row r="121" spans="1:27">
-      <c r="A121" t="s">
-        <v>683</v>
-      </c>
-      <c r="B121">
-        <v>22</v>
+      <c r="E121" t="s">
+        <v>2302</v>
       </c>
       <c r="V121" t="str">
         <f t="shared" si="28"/>
-        <v>},[22]={</v>
-      </c>
-    </row>
-    <row r="122" customFormat="1" spans="1:27">
-      <c r="C122" t="s">
-        <v>2302</v>
-      </c>
-      <c r="D122" t="s">
+        <v>{szContent="我竟然败给你们这群小辈！",szTarget="狼牙先锋首领",szNote="防冲突禁用·击退·狼牙先锋首领",[14]={},tCountdown={{nClass=-1,nIcon=3556,nFrame=1,szName="狼牙先锋首领·拾取掉落",nTime="10,狼牙先锋首领·已击退;300,狼牙先锋首领·拾取剩余;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=2,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
+      </c>
+      <c r="W121" t="s">
         <v>2303</v>
       </c>
-      <c r="E122" t="s">
-        <v>2304</v>
-      </c>
-      <c r="M122" t="s">
-        <v>2120</v>
-      </c>
-      <c r="S122">
-        <v>1</v>
+      <c r="X121" s="3" t="s">
+        <v>2289</v>
+      </c>
+      <c r="Y121" s="3" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="122" spans="1:27">
+      <c r="A122" t="s">
+        <v>683</v>
+      </c>
+      <c r="B122">
+        <v>22</v>
       </c>
       <c r="V122" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="增援已至武王城，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·武王城",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·武王城",nTime="10,浩气·兵符增援·武王城;300,浩气·武王城·兵符冷却;305,浩气·武王城·可用兵符",nRefresh=1,key="兵符·武王城",},},},</v>
-      </c>
-      <c r="W122" t="s">
-        <v>2305</v>
+        <v>},[22]={</v>
       </c>
     </row>
     <row r="123" customFormat="1" spans="1:27">
       <c r="C123" t="s">
-        <v>2068</v>
-      </c>
-      <c r="D123" s="8" t="s">
+        <v>2304</v>
+      </c>
+      <c r="D123" t="s">
+        <v>2305</v>
+      </c>
+      <c r="E123" t="s">
         <v>2306</v>
       </c>
       <c r="M123" t="s">
-        <v>2121</v>
+        <v>2120</v>
+      </c>
+      <c r="S123">
+        <v>1</v>
       </c>
       <c r="V123" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="赵新宇死亡时，从他身上遗落一把短笛，貌似是他的随身信物。",szTarget="%",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=589,nFrame=7,szName="赵新宇",nTime=0,key="赵新宇",},{nClass=14,nIcon=589,nFrame=7,szName="赵新宇",nTime="60,赵新宇的信物;302,赵新宇·刷新剩余;304,赵新宇·即将刷新;310,赵新宇·延迟刷新",nRefresh=60,key="赵新宇",},},},</v>
+        <v>{szContent="增援已至武王城，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·武王城",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·武王城",nTime="10,浩气·兵符增援·武王城;300,浩气·武王城·兵符冷却;305,浩气·武王城·可用兵符",nRefresh=1,key="兵符·武王城",},},},</v>
       </c>
       <c r="W123" t="s">
         <v>2307</v>
-      </c>
-      <c r="X123" t="s">
-        <v>2308</v>
       </c>
     </row>
     <row r="124" customFormat="1" spans="1:27">
@@ -39745,79 +39754,82 @@
         <v>2068</v>
       </c>
       <c r="D124" s="8" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="M124" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="V124" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="随着方超的死亡，一把短笛掉了出来，貌似是他的随身信物。",szTarget="%",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=308,nFrame=3,szName="方超",nTime=0,key="方超",},{nClass=14,nIcon=308,nFrame=3,szName="方超",nTime="60,方超的信物;302,方超·刷新剩余;304,方超·即将刷新;310,方超·延迟刷新",nRefresh=60,key="方超",},},},</v>
+        <v>{szContent="赵新宇死亡时，从他身上遗落一把短笛，貌似是他的随身信物。",szTarget="%",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=589,nFrame=7,szName="赵新宇",nTime=0,key="赵新宇",},{nClass=14,nIcon=589,nFrame=7,szName="赵新宇",nTime="60,赵新宇的信物;302,赵新宇·刷新剩余;304,赵新宇·即将刷新;310,赵新宇·延迟刷新",nRefresh=60,key="赵新宇",},},},</v>
       </c>
       <c r="W124" t="s">
+        <v>2309</v>
+      </c>
+      <c r="X124" t="s">
         <v>2310</v>
       </c>
-      <c r="X124" t="s">
+    </row>
+    <row r="125" customFormat="1" spans="1:27">
+      <c r="C125" t="s">
+        <v>2068</v>
+      </c>
+      <c r="D125" s="8" t="s">
         <v>2311</v>
       </c>
-    </row>
-    <row r="125" spans="1:27">
-      <c r="C125" t="s">
-        <v>2312</v>
-      </c>
-      <c r="D125" t="s">
-        <v>2313</v>
-      </c>
       <c r="M125" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="V125" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="恶人谷老友们可在我这里传送到恶人谷！",szTarget="赵新宇",col={255,100,100,},[14]={},tCountdown={{nClass=-1,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=2,nRefresh=600,key="赵新宇",},},},</v>
+        <v>{szContent="随着方超的死亡，一把短笛掉了出来，貌似是他的随身信物。",szTarget="%",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=308,nFrame=3,szName="方超",nTime=0,key="方超",},{nClass=14,nIcon=308,nFrame=3,szName="方超",nTime="60,方超的信物;302,方超·刷新剩余;304,方超·即将刷新;310,方超·延迟刷新",nRefresh=60,key="方超",},},},</v>
       </c>
       <c r="W125" t="s">
-        <v>2314</v>
+        <v>2312</v>
+      </c>
+      <c r="X125" t="s">
+        <v>2313</v>
       </c>
     </row>
     <row r="126" spans="1:27">
       <c r="C126" t="s">
+        <v>2314</v>
+      </c>
+      <c r="D126" t="s">
         <v>2315</v>
       </c>
-      <c r="D126" t="s">
-        <v>2316</v>
-      </c>
       <c r="M126" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="V126" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="浩气盟侠士们可在我这里传送到浩气盟！",szTarget="方超",col={100,100,255,},[14]={},tCountdown={{nClass=-1,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=2,nRefresh=600,key="方超",},},},</v>
+        <v>{szContent="恶人谷老友们可在我这里传送到恶人谷！",szTarget="赵新宇",col={255,100,100,},[14]={},tCountdown={{nClass=-1,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=2,nRefresh=600,key="赵新宇",},},},</v>
       </c>
       <c r="W126" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="127" spans="1:27">
       <c r="C127" t="s">
+        <v>2317</v>
+      </c>
+      <c r="D127" t="s">
         <v>2318</v>
       </c>
-      <c r="D127" t="s">
-        <v>2319</v>
-      </c>
       <c r="M127" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="V127" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="护送不利，恶人谷的运输小队被浩气盟截下了！",szTarget="管良沧",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=7,szName="浩气·劫车奖励",nTime=60,key="恶人·矿车",},},},</v>
+        <v>{szContent="浩气盟侠士们可在我这里传送到浩气盟！",szTarget="方超",col={100,100,255,},[14]={},tCountdown={{nClass=-1,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=2,nRefresh=600,key="方超",},},},</v>
       </c>
       <c r="W127" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="128" spans="1:27">
       <c r="C128" t="s">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="D128" t="s">
         <v>2321</v>
@@ -39827,7 +39839,7 @@
       </c>
       <c r="V128" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="恶人谷的运输小队成功到达营地！接下来由他们将物资运往更前线，大伙继续加油，收集更多物资！",szTarget="管良沧",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=3,szName="恶人·领取护送奖赏",nTime=60,key="恶人·矿车",},},},</v>
+        <v>{szContent="护送不利，恶人谷的运输小队被浩气盟截下了！",szTarget="管良沧",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=7,szName="浩气·劫车奖励",nTime=60,key="恶人·矿车",},},},</v>
       </c>
       <c r="W128" t="s">
         <v>2322</v>
@@ -39835,49 +39847,49 @@
     </row>
     <row r="129" spans="1:24">
       <c r="C129" t="s">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="D129" t="s">
         <v>2323</v>
       </c>
-      <c r="E129" t="s">
-        <v>2324</v>
-      </c>
       <c r="M129" t="s">
         <v>2121</v>
       </c>
-      <c r="S129">
-        <v>1</v>
-      </c>
       <c r="V129" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="恶人谷的运输小队出现了，大伙快前去接送到我方营地，谷主重重有赏！",szTarget="管良沧",szNote="粮草先行·恶人牛车",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=3,szName="恶人·护送牛车",nTime="337,恶人·护送牛车;340,恶人·延迟护送牛车",nRefresh=0,key="恶人·矿车",},},},</v>
+        <v>{szContent="恶人谷的运输小队成功到达营地！接下来由他们将物资运往更前线，大伙继续加油，收集更多物资！",szTarget="管良沧",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=3,szName="恶人·领取护送奖赏",nTime=60,key="恶人·矿车",},},},</v>
       </c>
       <c r="W129" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="130" spans="1:24">
       <c r="C130" t="s">
+        <v>2320</v>
+      </c>
+      <c r="D130" t="s">
+        <v>2325</v>
+      </c>
+      <c r="E130" t="s">
         <v>2326</v>
       </c>
-      <c r="D130" t="s">
-        <v>2327</v>
-      </c>
       <c r="M130" t="s">
-        <v>2120</v>
+        <v>2121</v>
+      </c>
+      <c r="S130">
+        <v>1</v>
       </c>
       <c r="V130" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="护送不利，浩气盟的运输小队被恶人谷截下了！",szTarget="苏才寥",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=3,szName="恶人·劫车奖励",nTime=60,key="浩气·矿车",},},},</v>
+        <v>{szContent="恶人谷的运输小队出现了，大伙快前去接送到我方营地，谷主重重有赏！",szTarget="管良沧",szNote="粮草先行·恶人牛车",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=3,szName="恶人·护送牛车",nTime="337,恶人·护送牛车;340,恶人·延迟护送牛车",nRefresh=0,key="恶人·矿车",},},},</v>
       </c>
       <c r="W130" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="131" spans="1:24">
       <c r="C131" t="s">
-        <v>2326</v>
+        <v>2328</v>
       </c>
       <c r="D131" t="s">
         <v>2329</v>
@@ -39887,7 +39899,7 @@
       </c>
       <c r="V131" t="str">
         <f t="shared" ref="V131:V162" si="29">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(D131),ISBLANK(N131),ISBLANK(O131),OR(ISBLANK(B130)=FALSE,ISBLANK(D130)=FALSE,ISBLANK(N130)=FALSE,ISBLANK(O130)=FALSE)),"},},}",IF(ISBLANK(D131),"","{szContent="""&amp;D131&amp;""","&amp;IF(C131&lt;&gt;"","szTarget="""&amp;C131&amp;""",","")&amp;IF(E131&lt;&gt;"","szNote="""&amp;E131&amp;""",","")&amp;IF(M131&lt;&gt;"","col={"&amp;M131&amp;"},","")&amp;IF(N131&gt;0,"bSearch=true,","")&amp;IF(O131&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P131&gt;0,"szVoice="""&amp;P131&amp;""",","")&amp;IF(Q131&gt;0,"bTeamChannel=true,","")&amp;IF(R131&gt;0,"bWhisperChannel=true,","")&amp;IF(S131&gt;0,"bCenterAlarm=true,","")&amp;IF(T131&gt;0,"bScreenHead=true,","")&amp;IF(U131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W131:AAH131)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="浩气盟的运输小队成功到达营地！接下来由他们将物资运往更前线，大伙继续加油，收集更多物资！",szTarget="苏才寥",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=7,szName="浩气·领取护送奖赏",nTime=60,key="浩气·矿车",},},},</v>
+        <v>{szContent="护送不利，浩气盟的运输小队被恶人谷截下了！",szTarget="苏才寥",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=3,szName="恶人·劫车奖励",nTime=60,key="浩气·矿车",},},},</v>
       </c>
       <c r="W131" t="s">
         <v>2330</v>
@@ -39895,116 +39907,110 @@
     </row>
     <row r="132" spans="1:24">
       <c r="C132" t="s">
-        <v>2326</v>
+        <v>2328</v>
       </c>
       <c r="D132" t="s">
         <v>2331</v>
       </c>
-      <c r="E132" t="s">
-        <v>2332</v>
-      </c>
       <c r="M132" t="s">
         <v>2120</v>
       </c>
-      <c r="S132">
-        <v>1</v>
-      </c>
       <c r="V132" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="浩气盟的运输小队出现了，大伙快前去接送到我方营地，盟主重重有赏！",szTarget="苏才寥",szNote="粮草先行·浩气牛车",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=7,szName="浩气·护送牛车",nTime="337,浩气·护送牛车;340,浩气·延迟护送牛车",nRefresh=0,key="浩气·矿车",},},},</v>
+        <v>{szContent="浩气盟的运输小队成功到达营地！接下来由他们将物资运往更前线，大伙继续加油，收集更多物资！",szTarget="苏才寥",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=7,szName="浩气·领取护送奖赏",nTime=60,key="浩气·矿车",},},},</v>
       </c>
       <c r="W132" t="s">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="133" spans="1:24">
+      <c r="C133" t="s">
+        <v>2328</v>
+      </c>
+      <c r="D133" t="s">
         <v>2333</v>
       </c>
-    </row>
-    <row r="133" spans="1:24">
-      <c r="A133" t="s">
-        <v>706</v>
-      </c>
-      <c r="B133">
-        <v>30</v>
+      <c r="E133" t="s">
+        <v>2334</v>
+      </c>
+      <c r="M133" t="s">
+        <v>2120</v>
+      </c>
+      <c r="S133">
+        <v>1</v>
       </c>
       <c r="V133" t="str">
         <f t="shared" si="29"/>
-        <v>},[30]={</v>
-      </c>
-    </row>
-    <row r="134" customFormat="1" spans="1:24">
-      <c r="C134" t="s">
-        <v>2334</v>
-      </c>
-      <c r="D134" t="s">
+        <v>{szContent="浩气盟的运输小队出现了，大伙快前去接送到我方营地，盟主重重有赏！",szTarget="苏才寥",szNote="粮草先行·浩气牛车",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=7,szName="浩气·护送牛车",nTime="337,浩气·护送牛车;340,浩气·延迟护送牛车",nRefresh=0,key="浩气·矿车",},},},</v>
+      </c>
+      <c r="W133" t="s">
         <v>2335</v>
       </c>
-      <c r="E134" t="s">
-        <v>2336</v>
-      </c>
-      <c r="M134" t="s">
-        <v>2121</v>
-      </c>
-      <c r="S134">
-        <v>1</v>
+    </row>
+    <row r="134" spans="1:24">
+      <c r="A134" t="s">
+        <v>706</v>
+      </c>
+      <c r="B134">
+        <v>30</v>
       </c>
       <c r="V134" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="增援已至凛风堡，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·凛风堡",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·凛风堡",nTime="10,恶人·兵符增援·凛风堡;300,恶人·凛风堡·兵符冷却;305,恶人·凛风堡·可用兵符",nRefresh=1,key="兵符·凛风堡",},},},</v>
-      </c>
-      <c r="W134" t="s">
-        <v>2337</v>
+        <v>},[30]={</v>
       </c>
     </row>
     <row r="135" customFormat="1" spans="1:24">
       <c r="C135" t="s">
-        <v>2261</v>
+        <v>2336</v>
       </c>
       <c r="D135" t="s">
-        <v>2262</v>
+        <v>2337</v>
       </c>
       <c r="E135" t="s">
-        <v>2263</v>
+        <v>2338</v>
       </c>
       <c r="M135" t="s">
-        <v>1725</v>
-      </c>
-      <c r="O135">
-        <v>1</v>
+        <v>2121</v>
       </c>
       <c r="S135">
-        <v>1</v>
-      </c>
-      <c r="T135">
         <v>1</v>
       </c>
       <c r="V135" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="已为.-补.-%[(.+)%].-(%d-)个.-消耗(%d+%.?%d-)金",szTarget="据点总管",szNote="补货·[{$1}]·{$2}",col={100,255,100,},bReg=true,[14]={bCenterAlarm=true,bScreenHead=true,},tCountdown={{nClass=14,nIcon=13,nFrame=6,szName="阵营模式",nTime=-2,key="阵营模式",},{nClass=14,nIcon=135,nFrame=6,szName="补货·[{$1}]·{$2}",nTime=10,nRefresh=600,key="阵营模式",},},},</v>
+        <v>{szContent="增援已至凛风堡，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·凛风堡",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·凛风堡",nTime="10,恶人·兵符增援·凛风堡;300,恶人·凛风堡·兵符冷却;305,恶人·凛风堡·可用兵符",nRefresh=1,key="兵符·凛风堡",},},},</v>
       </c>
       <c r="W135" t="s">
-        <v>2264</v>
-      </c>
-      <c r="X135" t="s">
-        <v>2265</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="136" customFormat="1" spans="1:24">
       <c r="C136" t="s">
-        <v>2261</v>
+        <v>2263</v>
       </c>
       <c r="D136" t="s">
-        <v>2266</v>
+        <v>2264</v>
+      </c>
+      <c r="E136" t="s">
+        <v>2265</v>
       </c>
       <c r="M136" t="s">
-        <v>1656</v>
+        <v>1725</v>
       </c>
       <c r="O136">
+        <v>1</v>
+      </c>
+      <c r="S136">
+        <v>1</v>
+      </c>
+      <c r="T136">
         <v>1</v>
       </c>
       <c r="V136" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="好嘞，老夫开始收货了。本次特产转为(%d-)个(.-)，(.-)[，]-您辛苦了！",szTarget="据点总管",col={255,255,100,},bReg=true,[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,szName="阵营模式",nTime=-2,key="阵营模式",},{nClass=14,nIcon=374,nFrame=6,szName="{$2}·{$1}{$3}",nTime=10,nRefresh=600,key="阵营模式",},},},</v>
+        <v>{szContent="已为.-补.-%[(.+)%].-(%d-)个.-消耗(%d+%.?%d-)金",szTarget="据点总管",szNote="补货·[{$1}]·{$2}",col={100,255,100,},bReg=true,[14]={bCenterAlarm=true,bScreenHead=true,},tCountdown={{nClass=14,nIcon=13,nFrame=6,szName="阵营模式",nTime=-2,key="阵营模式",},{nClass=14,nIcon=135,nFrame=6,szName="补货·[{$1}]·{$2}",nTime=10,nRefresh=600,key="阵营模式",},},},</v>
       </c>
       <c r="W136" t="s">
-        <v>2264</v>
+        <v>2266</v>
       </c>
       <c r="X136" t="s">
         <v>2267</v>
@@ -40012,23 +40018,26 @@
     </row>
     <row r="137" customFormat="1" spans="1:24">
       <c r="C137" t="s">
-        <v>2068</v>
-      </c>
-      <c r="D137" s="8" t="s">
-        <v>2338</v>
+        <v>2263</v>
+      </c>
+      <c r="D137" t="s">
+        <v>2268</v>
       </c>
       <c r="M137" t="s">
-        <v>2121</v>
+        <v>1656</v>
+      </c>
+      <c r="O137">
+        <v>1</v>
       </c>
       <c r="V137" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="随着霸图的死亡，一柄钢刀从他身上滑落，似乎是他的随身信物。",szTarget="%",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=2864,nFrame=7,szName="霸图",nTime=0,key="霸图",},{nClass=14,nIcon=2864,nFrame=7,szName="霸图",nTime="60,霸图的信物;302,霸图·刷新剩余;304,霸图·即将刷新;310,霸图·延迟刷新",nRefresh=60,key="霸图",},},},</v>
+        <v>{szContent="好嘞，老夫开始收货了。本次特产转为(%d-)个(.-)，(.-)[，]-您辛苦了！",szTarget="据点总管",col={255,255,100,},bReg=true,[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,szName="阵营模式",nTime=-2,key="阵营模式",},{nClass=14,nIcon=374,nFrame=6,szName="{$2}·{$1}{$3}",nTime=10,nRefresh=600,key="阵营模式",},},},</v>
       </c>
       <c r="W137" t="s">
-        <v>2339</v>
+        <v>2266</v>
       </c>
       <c r="X137" t="s">
-        <v>2340</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="138" customFormat="1" spans="1:24">
@@ -40036,37 +40045,40 @@
         <v>2068</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="M138" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="V138" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="随着孙永恒的死亡，一柄短剑从他身上滑落，似乎是他的随身信物。",szTarget="%",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=845,nFrame=3,szName="孙永恒",nTime=0,key="孙永恒",},{nClass=14,nIcon=845,nFrame=3,szName="孙永恒",nTime="60,孙永恒的信物;302,孙永恒·刷新剩余;304,孙永恒·即将刷新;310,孙永恒·延迟刷新",nRefresh=60,key="孙永恒",},},},</v>
+        <v>{szContent="随着霸图的死亡，一柄钢刀从他身上滑落，似乎是他的随身信物。",szTarget="%",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=2864,nFrame=7,szName="霸图",nTime=0,key="霸图",},{nClass=14,nIcon=2864,nFrame=7,szName="霸图",nTime="60,霸图的信物;302,霸图·刷新剩余;304,霸图·即将刷新;310,霸图·延迟刷新",nRefresh=60,key="霸图",},},},</v>
       </c>
       <c r="W138" t="s">
+        <v>2341</v>
+      </c>
+      <c r="X138" t="s">
         <v>2342</v>
       </c>
-      <c r="X138" t="s">
+    </row>
+    <row r="139" customFormat="1" spans="1:24">
+      <c r="C139" t="s">
+        <v>2068</v>
+      </c>
+      <c r="D139" s="8" t="s">
         <v>2343</v>
       </c>
-    </row>
-    <row r="139" spans="1:24">
-      <c r="C139" t="s">
-        <v>2344</v>
-      </c>
-      <c r="D139" t="s">
-        <v>2313</v>
-      </c>
       <c r="M139" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="V139" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="恶人谷老友们可在我这里传送到恶人谷！",szTarget="霸图",col={255,100,100,},[14]={},tCountdown={{nClass=-1,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=2,nRefresh=600,key="霸图",},},},</v>
+        <v>{szContent="随着孙永恒的死亡，一柄短剑从他身上滑落，似乎是他的随身信物。",szTarget="%",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=845,nFrame=3,szName="孙永恒",nTime=0,key="孙永恒",},{nClass=14,nIcon=845,nFrame=3,szName="孙永恒",nTime="60,孙永恒的信物;302,孙永恒·刷新剩余;304,孙永恒·即将刷新;310,孙永恒·延迟刷新",nRefresh=60,key="孙永恒",},},},</v>
       </c>
       <c r="W139" t="s">
+        <v>2344</v>
+      </c>
+      <c r="X139" t="s">
         <v>2345</v>
       </c>
     </row>
@@ -40075,14 +40087,14 @@
         <v>2346</v>
       </c>
       <c r="D140" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="M140" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="V140" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="浩气盟侠士们可在我这里传送到浩气盟！",szTarget="孙永恒",col={100,100,255,},[14]={},tCountdown={{nClass=-1,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=2,nRefresh=600,key="孙永恒",},},},</v>
+        <v>{szContent="恶人谷老友们可在我这里传送到恶人谷！",szTarget="霸图",col={255,100,100,},[14]={},tCountdown={{nClass=-1,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=2,nRefresh=600,key="霸图",},},},</v>
       </c>
       <c r="W140" t="s">
         <v>2347</v>
@@ -40090,25 +40102,25 @@
     </row>
     <row r="141" spans="1:24">
       <c r="C141" t="s">
+        <v>2348</v>
+      </c>
+      <c r="D141" t="s">
         <v>2318</v>
       </c>
-      <c r="D141" t="s">
-        <v>2319</v>
-      </c>
       <c r="M141" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="V141" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="护送不利，恶人谷的运输小队被浩气盟截下了！",szTarget="管良沧",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=7,szName="浩气·劫车奖励",nTime=60,key="恶人·矿车",},},},</v>
+        <v>{szContent="浩气盟侠士们可在我这里传送到浩气盟！",szTarget="孙永恒",col={100,100,255,},[14]={},tCountdown={{nClass=-1,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=2,nRefresh=600,key="孙永恒",},},},</v>
       </c>
       <c r="W141" t="s">
-        <v>2320</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="142" spans="1:24">
       <c r="C142" t="s">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="D142" t="s">
         <v>2321</v>
@@ -40118,7 +40130,7 @@
       </c>
       <c r="V142" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="恶人谷的运输小队成功到达营地！接下来由他们将物资运往更前线，大伙继续加油，收集更多物资！",szTarget="管良沧",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=3,szName="恶人·领取护送奖赏",nTime=60,key="恶人·矿车",},},},</v>
+        <v>{szContent="护送不利，恶人谷的运输小队被浩气盟截下了！",szTarget="管良沧",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=7,szName="浩气·劫车奖励",nTime=60,key="恶人·矿车",},},},</v>
       </c>
       <c r="W142" t="s">
         <v>2322</v>
@@ -40126,49 +40138,49 @@
     </row>
     <row r="143" spans="1:24">
       <c r="C143" t="s">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="D143" t="s">
         <v>2323</v>
       </c>
-      <c r="E143" t="s">
-        <v>2324</v>
-      </c>
       <c r="M143" t="s">
         <v>2121</v>
       </c>
-      <c r="S143">
-        <v>1</v>
-      </c>
       <c r="V143" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="恶人谷的运输小队出现了，大伙快前去接送到我方营地，谷主重重有赏！",szTarget="管良沧",szNote="粮草先行·恶人牛车",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=3,szName="恶人·护送牛车",nTime="548,恶人·护送牛车;562,恶人·延迟护送牛车",nRefresh=0,key="恶人·矿车",},},},</v>
+        <v>{szContent="恶人谷的运输小队成功到达营地！接下来由他们将物资运往更前线，大伙继续加油，收集更多物资！",szTarget="管良沧",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=3,szName="恶人·领取护送奖赏",nTime=60,key="恶人·矿车",},},},</v>
       </c>
       <c r="W143" t="s">
-        <v>2348</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="144" spans="1:24">
       <c r="C144" t="s">
+        <v>2320</v>
+      </c>
+      <c r="D144" t="s">
+        <v>2325</v>
+      </c>
+      <c r="E144" t="s">
         <v>2326</v>
       </c>
-      <c r="D144" t="s">
-        <v>2327</v>
-      </c>
       <c r="M144" t="s">
-        <v>2120</v>
+        <v>2121</v>
+      </c>
+      <c r="S144">
+        <v>1</v>
       </c>
       <c r="V144" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="护送不利，浩气盟的运输小队被恶人谷截下了！",szTarget="苏才寥",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=3,szName="恶人·劫车奖励",nTime=60,key="浩气·矿车",},},},</v>
+        <v>{szContent="恶人谷的运输小队出现了，大伙快前去接送到我方营地，谷主重重有赏！",szTarget="管良沧",szNote="粮草先行·恶人牛车",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=3,szName="恶人·护送牛车",nTime="548,恶人·护送牛车;562,恶人·延迟护送牛车",nRefresh=0,key="恶人·矿车",},},},</v>
       </c>
       <c r="W144" t="s">
-        <v>2328</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="145" spans="1:24">
       <c r="C145" t="s">
-        <v>2326</v>
+        <v>2328</v>
       </c>
       <c r="D145" t="s">
         <v>2329</v>
@@ -40178,7 +40190,7 @@
       </c>
       <c r="V145" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="浩气盟的运输小队成功到达营地！接下来由他们将物资运往更前线，大伙继续加油，收集更多物资！",szTarget="苏才寥",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=7,szName="浩气·领取护送奖赏",nTime=60,key="浩气·矿车",},},},</v>
+        <v>{szContent="护送不利，浩气盟的运输小队被恶人谷截下了！",szTarget="苏才寥",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=3,szName="恶人·劫车奖励",nTime=60,key="浩气·矿车",},},},</v>
       </c>
       <c r="W145" t="s">
         <v>2330</v>
@@ -40186,73 +40198,67 @@
     </row>
     <row r="146" spans="1:24">
       <c r="C146" t="s">
-        <v>2326</v>
+        <v>2328</v>
       </c>
       <c r="D146" t="s">
         <v>2331</v>
       </c>
-      <c r="E146" t="s">
-        <v>2332</v>
-      </c>
       <c r="M146" t="s">
         <v>2120</v>
       </c>
-      <c r="S146">
-        <v>1</v>
-      </c>
       <c r="V146" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="浩气盟的运输小队出现了，大伙快前去接送到我方营地，盟主重重有赏！",szTarget="苏才寥",szNote="粮草先行·浩气牛车",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=7,szName="浩气·护送牛车",nTime="548,浩气·护送牛车;562,浩气·延迟护送牛车",nRefresh=0,key="浩气·矿车",},},},</v>
+        <v>{szContent="浩气盟的运输小队成功到达营地！接下来由他们将物资运往更前线，大伙继续加油，收集更多物资！",szTarget="苏才寥",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=7,szName="浩气·领取护送奖赏",nTime=60,key="浩气·矿车",},},},</v>
       </c>
       <c r="W146" t="s">
-        <v>2349</v>
-      </c>
-    </row>
-    <row r="147" customFormat="1" spans="1:24">
-      <c r="A147" t="s">
-        <v>680</v>
-      </c>
-      <c r="B147">
-        <v>21</v>
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="147" spans="1:24">
+      <c r="C147" t="s">
+        <v>2328</v>
+      </c>
+      <c r="D147" t="s">
+        <v>2333</v>
+      </c>
+      <c r="E147" t="s">
+        <v>2334</v>
+      </c>
+      <c r="M147" t="s">
+        <v>2120</v>
+      </c>
+      <c r="S147">
+        <v>1</v>
       </c>
       <c r="V147" t="str">
         <f t="shared" si="29"/>
-        <v>},[21]={</v>
+        <v>{szContent="浩气盟的运输小队出现了，大伙快前去接送到我方营地，盟主重重有赏！",szTarget="苏才寥",szNote="粮草先行·浩气牛车",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=7,szName="浩气·护送牛车",nTime="548,浩气·护送牛车;562,浩气·延迟护送牛车",nRefresh=0,key="浩气·矿车",},},},</v>
+      </c>
+      <c r="W147" t="s">
+        <v>2351</v>
       </c>
     </row>
     <row r="148" customFormat="1" spans="1:24">
-      <c r="C148" t="s">
-        <v>2302</v>
-      </c>
-      <c r="D148" t="s">
-        <v>2350</v>
-      </c>
-      <c r="E148" t="s">
-        <v>2351</v>
-      </c>
-      <c r="M148" t="s">
-        <v>2120</v>
-      </c>
-      <c r="S148">
-        <v>1</v>
+      <c r="A148" t="s">
+        <v>680</v>
+      </c>
+      <c r="B148">
+        <v>21</v>
       </c>
       <c r="V148" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="增援已至盘龙坞，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·盘龙坞",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·盘龙坞",nTime="10,浩气·兵符增援·盘龙坞;300,浩气·盘龙坞·兵符冷却;305,浩气·盘龙坞·可用兵符",nRefresh=1,key="兵符·盘龙坞",},},},</v>
-      </c>
-      <c r="W148" t="s">
-        <v>2352</v>
+        <v>},[21]={</v>
       </c>
     </row>
     <row r="149" customFormat="1" spans="1:24">
       <c r="C149" t="s">
-        <v>2302</v>
+        <v>2304</v>
       </c>
       <c r="D149" t="s">
+        <v>2352</v>
+      </c>
+      <c r="E149" t="s">
         <v>2353</v>
-      </c>
-      <c r="E149" t="s">
-        <v>2354</v>
       </c>
       <c r="M149" t="s">
         <v>2120</v>
@@ -40262,31 +40268,34 @@
       </c>
       <c r="V149" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="增援已至逐鹿坪，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·逐鹿坪",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·逐鹿坪",nTime="10,浩气·兵符增援·逐鹿坪;300,浩气·逐鹿坪·兵符冷却;305,浩气·逐鹿坪·可用兵符",nRefresh=1,key="兵符·逐鹿坪",},},},</v>
+        <v>{szContent="增援已至盘龙坞，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·盘龙坞",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·盘龙坞",nTime="10,浩气·兵符增援·盘龙坞;300,浩气·盘龙坞·兵符冷却;305,浩气·盘龙坞·可用兵符",nRefresh=1,key="兵符·盘龙坞",},},},</v>
       </c>
       <c r="W149" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="150" customFormat="1" spans="1:24">
+      <c r="C150" t="s">
+        <v>2304</v>
+      </c>
+      <c r="D150" t="s">
         <v>2355</v>
       </c>
-    </row>
-    <row r="150" spans="1:24">
-      <c r="C150" t="s">
-        <v>2068</v>
-      </c>
-      <c r="D150" s="8" t="s">
-        <v>2306</v>
+      <c r="E150" t="s">
+        <v>2356</v>
       </c>
       <c r="M150" t="s">
-        <v>2121</v>
+        <v>2120</v>
+      </c>
+      <c r="S150">
+        <v>1</v>
       </c>
       <c r="V150" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="赵新宇死亡时，从他身上遗落一把短笛，貌似是他的随身信物。",szTarget="%",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=589,nFrame=7,szName="赵新宇",nTime=0,key="赵新宇",},{nClass=14,nIcon=589,nFrame=7,szName="赵新宇",nTime="60,赵新宇的信物;302,赵新宇·刷新剩余;304,赵新宇·即将刷新",nRefresh=60,key="赵新宇",},},},</v>
+        <v>{szContent="增援已至逐鹿坪，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·逐鹿坪",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·逐鹿坪",nTime="10,浩气·兵符增援·逐鹿坪;300,浩气·逐鹿坪·兵符冷却;305,浩气·逐鹿坪·可用兵符",nRefresh=1,key="兵符·逐鹿坪",},},},</v>
       </c>
       <c r="W150" t="s">
-        <v>2307</v>
-      </c>
-      <c r="X150" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="151" spans="1:24">
@@ -40294,103 +40303,100 @@
         <v>2068</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="M151" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="V151" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="随着方超的死亡，一把短笛掉了出来，貌似是他的随身信物。",szTarget="%",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=308,nFrame=3,szName="方超",nTime=0,key="方超",},{nClass=14,nIcon=308,nFrame=3,szName="方超",nTime="60,方超的信物;302,方超·刷新剩余;304,方超·即将刷新",nRefresh=60,key="方超",},},},</v>
+        <v>{szContent="赵新宇死亡时，从他身上遗落一把短笛，貌似是他的随身信物。",szTarget="%",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=589,nFrame=7,szName="赵新宇",nTime=0,key="赵新宇",},{nClass=14,nIcon=589,nFrame=7,szName="赵新宇",nTime="60,赵新宇的信物;302,赵新宇·刷新剩余;304,赵新宇·即将刷新",nRefresh=60,key="赵新宇",},},},</v>
       </c>
       <c r="W151" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="X151" t="s">
-        <v>2357</v>
-      </c>
-    </row>
-    <row r="152" customFormat="1" spans="1:24">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="152" spans="1:24">
       <c r="C152" t="s">
-        <v>2312</v>
-      </c>
-      <c r="D152" t="s">
-        <v>2313</v>
+        <v>2068</v>
+      </c>
+      <c r="D152" s="8" t="s">
+        <v>2311</v>
       </c>
       <c r="M152" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="V152" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="恶人谷老友们可在我这里传送到恶人谷！",szTarget="赵新宇",col={255,100,100,},[14]={},tCountdown={{nClass=-1,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=2,nRefresh=600,key="赵新宇",},},},</v>
+        <v>{szContent="随着方超的死亡，一把短笛掉了出来，貌似是他的随身信物。",szTarget="%",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=308,nFrame=3,szName="方超",nTime=0,key="方超",},{nClass=14,nIcon=308,nFrame=3,szName="方超",nTime="60,方超的信物;302,方超·刷新剩余;304,方超·即将刷新",nRefresh=60,key="方超",},},},</v>
       </c>
       <c r="W152" t="s">
-        <v>2314</v>
+        <v>2312</v>
+      </c>
+      <c r="X152" t="s">
+        <v>2359</v>
       </c>
     </row>
     <row r="153" customFormat="1" spans="1:24">
       <c r="C153" t="s">
+        <v>2314</v>
+      </c>
+      <c r="D153" t="s">
         <v>2315</v>
       </c>
-      <c r="D153" t="s">
-        <v>2316</v>
-      </c>
       <c r="M153" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="V153" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="浩气盟侠士们可在我这里传送到浩气盟！",szTarget="方超",col={100,100,255,},[14]={},tCountdown={{nClass=-1,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=2,nRefresh=600,key="方超",},},},</v>
+        <v>{szContent="恶人谷老友们可在我这里传送到恶人谷！",szTarget="赵新宇",col={255,100,100,},[14]={},tCountdown={{nClass=-1,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=2,nRefresh=600,key="赵新宇",},},},</v>
       </c>
       <c r="W153" t="s">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="154" customFormat="1" spans="1:24">
+      <c r="C154" t="s">
         <v>2317</v>
       </c>
-    </row>
-    <row r="154" spans="1:24">
-      <c r="A154" t="s">
-        <v>686</v>
-      </c>
-      <c r="B154">
-        <v>23</v>
+      <c r="D154" t="s">
+        <v>2318</v>
+      </c>
+      <c r="M154" t="s">
+        <v>2120</v>
       </c>
       <c r="V154" t="str">
         <f t="shared" si="29"/>
-        <v>},[23]={</v>
-      </c>
-    </row>
-    <row r="155" customFormat="1" spans="1:24">
-      <c r="C155" t="s">
-        <v>2334</v>
-      </c>
-      <c r="D155" t="s">
-        <v>2358</v>
-      </c>
-      <c r="E155" t="s">
-        <v>2359</v>
-      </c>
-      <c r="M155" t="s">
-        <v>2121</v>
-      </c>
-      <c r="S155">
-        <v>1</v>
+        <v>{szContent="浩气盟侠士们可在我这里传送到浩气盟！",szTarget="方超",col={100,100,255,},[14]={},tCountdown={{nClass=-1,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=2,nRefresh=600,key="方超",},},},</v>
+      </c>
+      <c r="W154" t="s">
+        <v>2319</v>
+      </c>
+    </row>
+    <row r="155" spans="1:24">
+      <c r="A155" t="s">
+        <v>686</v>
+      </c>
+      <c r="B155">
+        <v>23</v>
       </c>
       <c r="V155" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="增援已至龙门镇，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·龙门镇",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·龙门镇",nTime="10,恶人·兵符增援·龙门镇;300,恶人·龙门镇·兵符冷却;305,恶人·龙门镇·可用兵符",nRefresh=1,key="兵符·龙门镇",},},},</v>
-      </c>
-      <c r="W155" t="s">
-        <v>2360</v>
+        <v>},[23]={</v>
       </c>
     </row>
     <row r="156" customFormat="1" spans="1:24">
       <c r="C156" t="s">
-        <v>2334</v>
+        <v>2336</v>
       </c>
       <c r="D156" t="s">
+        <v>2360</v>
+      </c>
+      <c r="E156" t="s">
         <v>2361</v>
-      </c>
-      <c r="E156" t="s">
-        <v>2362</v>
       </c>
       <c r="M156" t="s">
         <v>2121</v>
@@ -40400,31 +40406,34 @@
       </c>
       <c r="V156" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="增援已至飞沙关，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·飞沙关",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·飞沙关",nTime="10,恶人·兵符增援·飞沙关;300,恶人·飞沙关·兵符冷却;305,恶人·飞沙关·可用兵符",nRefresh=1,key="兵符·飞沙关",},},},</v>
+        <v>{szContent="增援已至龙门镇，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·龙门镇",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·龙门镇",nTime="10,恶人·兵符增援·龙门镇;300,恶人·龙门镇·兵符冷却;305,恶人·龙门镇·可用兵符",nRefresh=1,key="兵符·龙门镇",},},},</v>
       </c>
       <c r="W156" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="157" customFormat="1" spans="1:24">
+      <c r="C157" t="s">
+        <v>2336</v>
+      </c>
+      <c r="D157" t="s">
         <v>2363</v>
       </c>
-    </row>
-    <row r="157" spans="1:24">
-      <c r="C157" t="s">
-        <v>2068</v>
-      </c>
-      <c r="D157" s="8" t="s">
-        <v>2338</v>
+      <c r="E157" t="s">
+        <v>2364</v>
       </c>
       <c r="M157" t="s">
         <v>2121</v>
       </c>
+      <c r="S157">
+        <v>1</v>
+      </c>
       <c r="V157" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="随着霸图的死亡，一柄钢刀从他身上滑落，似乎是他的随身信物。",szTarget="%",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=2864,nFrame=7,szName="霸图",nTime=0,key="霸图",},{nClass=14,nIcon=2864,nFrame=7,szName="霸图",nTime="60,霸图的信物;302,霸图·刷新剩余;304,霸图·即将刷新",nRefresh=60,key="霸图",},},},</v>
+        <v>{szContent="增援已至飞沙关，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·飞沙关",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·飞沙关",nTime="10,恶人·兵符增援·飞沙关;300,恶人·飞沙关·兵符冷却;305,恶人·飞沙关·可用兵符",nRefresh=1,key="兵符·飞沙关",},},},</v>
       </c>
       <c r="W157" t="s">
-        <v>2339</v>
-      </c>
-      <c r="X157" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="158" spans="1:24">
@@ -40432,38 +40441,41 @@
         <v>2068</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="M158" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="V158" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="随着孙永恒的死亡，一柄短剑从他身上滑落，似乎是他的随身信物。",szTarget="%",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=845,nFrame=3,szName="孙永恒",nTime=0,key="孙永恒",},{nClass=14,nIcon=845,nFrame=3,szName="孙永恒",nTime="60,孙永恒的信物;302,孙永恒·刷新剩余;304,孙永恒·即将刷新",nRefresh=60,key="孙永恒",},},},</v>
+        <v>{szContent="随着霸图的死亡，一柄钢刀从他身上滑落，似乎是他的随身信物。",szTarget="%",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=2864,nFrame=7,szName="霸图",nTime=0,key="霸图",},{nClass=14,nIcon=2864,nFrame=7,szName="霸图",nTime="60,霸图的信物;302,霸图·刷新剩余;304,霸图·即将刷新",nRefresh=60,key="霸图",},},},</v>
       </c>
       <c r="W158" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="X158" t="s">
-        <v>2365</v>
-      </c>
-    </row>
-    <row r="159" customFormat="1" spans="1:24">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="159" spans="1:24">
       <c r="C159" t="s">
-        <v>2344</v>
-      </c>
-      <c r="D159" t="s">
-        <v>2313</v>
+        <v>2068</v>
+      </c>
+      <c r="D159" s="8" t="s">
+        <v>2343</v>
       </c>
       <c r="M159" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="V159" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="恶人谷老友们可在我这里传送到恶人谷！",szTarget="霸图",col={255,100,100,},[14]={},tCountdown={{nClass=-1,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=2,nRefresh=600,key="霸图",},},},</v>
+        <v>{szContent="随着孙永恒的死亡，一柄短剑从他身上滑落，似乎是他的随身信物。",szTarget="%",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=845,nFrame=3,szName="孙永恒",nTime=0,key="孙永恒",},{nClass=14,nIcon=845,nFrame=3,szName="孙永恒",nTime="60,孙永恒的信物;302,孙永恒·刷新剩余;304,孙永恒·即将刷新",nRefresh=60,key="孙永恒",},},},</v>
       </c>
       <c r="W159" t="s">
-        <v>2345</v>
+        <v>2344</v>
+      </c>
+      <c r="X159" t="s">
+        <v>2367</v>
       </c>
     </row>
     <row r="160" customFormat="1" spans="1:24">
@@ -40471,64 +40483,58 @@
         <v>2346</v>
       </c>
       <c r="D160" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="M160" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="V160" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="浩气盟侠士们可在我这里传送到浩气盟！",szTarget="孙永恒",col={100,100,255,},[14]={},tCountdown={{nClass=-1,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=2,nRefresh=600,key="孙永恒",},},},</v>
+        <v>{szContent="恶人谷老友们可在我这里传送到恶人谷！",szTarget="霸图",col={255,100,100,},[14]={},tCountdown={{nClass=-1,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=2,nRefresh=600,key="霸图",},},},</v>
       </c>
       <c r="W160" t="s">
         <v>2347</v>
       </c>
     </row>
-    <row r="161" spans="1:25">
-      <c r="A161" t="s">
-        <v>634</v>
-      </c>
-      <c r="B161">
-        <v>9</v>
+    <row r="161" customFormat="1" spans="1:25">
+      <c r="C161" t="s">
+        <v>2348</v>
+      </c>
+      <c r="D161" t="s">
+        <v>2318</v>
+      </c>
+      <c r="M161" t="s">
+        <v>2120</v>
       </c>
       <c r="V161" t="str">
         <f t="shared" si="29"/>
-        <v>},[9]={</v>
-      </c>
-    </row>
-    <row r="162" customFormat="1" spans="1:25">
-      <c r="C162" t="s">
-        <v>2302</v>
-      </c>
-      <c r="D162" t="s">
-        <v>2366</v>
-      </c>
-      <c r="E162" t="s">
-        <v>2367</v>
-      </c>
-      <c r="M162" t="s">
-        <v>2120</v>
-      </c>
-      <c r="S162">
-        <v>1</v>
+        <v>{szContent="浩气盟侠士们可在我这里传送到浩气盟！",szTarget="孙永恒",col={100,100,255,},[14]={},tCountdown={{nClass=-1,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=2,nRefresh=600,key="孙永恒",},},},</v>
+      </c>
+      <c r="W161" t="s">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="162" spans="1:25">
+      <c r="A162" t="s">
+        <v>634</v>
+      </c>
+      <c r="B162">
+        <v>9</v>
       </c>
       <c r="V162" t="str">
         <f t="shared" si="29"/>
-        <v>{szContent="增援已至红莲岗，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·红莲岗",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·红莲岗",nTime="10,浩气·兵符增援·红莲岗;300,浩气·红莲岗·兵符冷却;305,浩气·红莲岗·可用兵符",nRefresh=1,key="兵符·红莲岗",},},},</v>
-      </c>
-      <c r="W162" t="s">
-        <v>2368</v>
+        <v>},[9]={</v>
       </c>
     </row>
     <row r="163" customFormat="1" spans="1:25">
       <c r="C163" t="s">
-        <v>2302</v>
+        <v>2304</v>
       </c>
       <c r="D163" t="s">
+        <v>2368</v>
+      </c>
+      <c r="E163" t="s">
         <v>2369</v>
-      </c>
-      <c r="E163" t="s">
-        <v>2370</v>
       </c>
       <c r="M163" t="s">
         <v>2120</v>
@@ -40537,58 +40543,58 @@
         <v>1</v>
       </c>
       <c r="V163" t="str">
-        <f t="shared" ref="V163:V197" si="30">IF(ISBLANK(B163)=FALSE,IF(ISBLANK(B162),"},["&amp;B163&amp;"]={","["&amp;B163&amp;"]={"),IF(AND(ISBLANK(B163),ISBLANK(D163),ISBLANK(N163),ISBLANK(O163),OR(ISBLANK(B162)=FALSE,ISBLANK(D162)=FALSE,ISBLANK(N162)=FALSE,ISBLANK(O162)=FALSE)),"},},}",IF(ISBLANK(D163),"","{szContent="""&amp;D163&amp;""","&amp;IF(C163&lt;&gt;"","szTarget="""&amp;C163&amp;""",","")&amp;IF(E163&lt;&gt;"","szNote="""&amp;E163&amp;""",","")&amp;IF(M163&lt;&gt;"","col={"&amp;M163&amp;"},","")&amp;IF(N163&gt;0,"bSearch=true,","")&amp;IF(O163&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P163&gt;0,"szVoice="""&amp;P163&amp;""",","")&amp;IF(Q163&gt;0,"bTeamChannel=true,","")&amp;IF(R163&gt;0,"bWhisperChannel=true,","")&amp;IF(S163&gt;0,"bCenterAlarm=true,","")&amp;IF(T163&gt;0,"bScreenHead=true,","")&amp;IF(U163&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W163&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W163:AAH163)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="增援已至秋雨堡，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·秋雨堡",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·秋雨堡",nTime="10,浩气·兵符增援·秋雨堡;300,浩气·秋雨堡·兵符冷却;305,浩气·秋雨堡·可用兵符",nRefresh=1,key="兵符·秋雨堡",},},},</v>
+        <f t="shared" ref="V163:V194" si="30">IF(ISBLANK(B163)=FALSE,IF(ISBLANK(B162),"},["&amp;B163&amp;"]={","["&amp;B163&amp;"]={"),IF(AND(ISBLANK(B163),ISBLANK(D163),ISBLANK(N163),ISBLANK(O163),OR(ISBLANK(B162)=FALSE,ISBLANK(D162)=FALSE,ISBLANK(N162)=FALSE,ISBLANK(O162)=FALSE)),"},},}",IF(ISBLANK(D163),"","{szContent="""&amp;D163&amp;""","&amp;IF(C163&lt;&gt;"","szTarget="""&amp;C163&amp;""",","")&amp;IF(E163&lt;&gt;"","szNote="""&amp;E163&amp;""",","")&amp;IF(M163&lt;&gt;"","col={"&amp;M163&amp;"},","")&amp;IF(N163&gt;0,"bSearch=true,","")&amp;IF(O163&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P163&gt;0,"szVoice="""&amp;P163&amp;""",","")&amp;IF(Q163&gt;0,"bTeamChannel=true,","")&amp;IF(R163&gt;0,"bWhisperChannel=true,","")&amp;IF(S163&gt;0,"bCenterAlarm=true,","")&amp;IF(T163&gt;0,"bScreenHead=true,","")&amp;IF(U163&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W163&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W163:AAH163)&amp;"},","")&amp;"},")))</f>
+        <v>{szContent="增援已至红莲岗，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·红莲岗",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·红莲岗",nTime="10,浩气·兵符增援·红莲岗;300,浩气·红莲岗·兵符冷却;305,浩气·红莲岗·可用兵符",nRefresh=1,key="兵符·红莲岗",},},},</v>
       </c>
       <c r="W163" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="164" customFormat="1" spans="1:25">
+      <c r="C164" t="s">
+        <v>2304</v>
+      </c>
+      <c r="D164" t="s">
         <v>2371</v>
       </c>
-    </row>
-    <row r="164" spans="1:25">
-      <c r="A164" t="s">
-        <v>847</v>
-      </c>
-      <c r="B164">
-        <v>103</v>
+      <c r="E164" t="s">
+        <v>2372</v>
+      </c>
+      <c r="M164" t="s">
+        <v>2120</v>
+      </c>
+      <c r="S164">
+        <v>1</v>
       </c>
       <c r="V164" t="str">
         <f t="shared" si="30"/>
-        <v>},[103]={</v>
-      </c>
-    </row>
-    <row r="165" customFormat="1" spans="1:25">
-      <c r="C165" t="s">
-        <v>2334</v>
-      </c>
-      <c r="D165" t="s">
-        <v>2372</v>
-      </c>
-      <c r="E165" t="s">
+        <v>{szContent="增援已至秋雨堡，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·秋雨堡",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·秋雨堡",nTime="10,浩气·兵符增援·秋雨堡;300,浩气·秋雨堡·兵符冷却;305,浩气·秋雨堡·可用兵符",nRefresh=1,key="兵符·秋雨堡",},},},</v>
+      </c>
+      <c r="W164" t="s">
         <v>2373</v>
       </c>
-      <c r="M165" t="s">
-        <v>2121</v>
-      </c>
-      <c r="S165">
-        <v>1</v>
+    </row>
+    <row r="165" spans="1:25">
+      <c r="A165" t="s">
+        <v>847</v>
+      </c>
+      <c r="B165">
+        <v>103</v>
       </c>
       <c r="V165" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="增援已至神池岭，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·神池岭",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·神池岭",nTime="10,恶人·兵符增援·神池岭;300,恶人·神池岭·兵符冷却;305,恶人·神池岭·可用兵符",nRefresh=1,key="兵符·神池岭",},},},</v>
-      </c>
-      <c r="W165" t="s">
-        <v>2374</v>
+        <v>},[103]={</v>
       </c>
     </row>
     <row r="166" customFormat="1" spans="1:25">
       <c r="C166" t="s">
-        <v>2334</v>
+        <v>2336</v>
       </c>
       <c r="D166" t="s">
+        <v>2374</v>
+      </c>
+      <c r="E166" t="s">
         <v>2375</v>
-      </c>
-      <c r="E166" t="s">
-        <v>2376</v>
       </c>
       <c r="M166" t="s">
         <v>2121</v>
@@ -40598,57 +40604,57 @@
       </c>
       <c r="V166" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="增援已至烈日岗，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·烈日岗",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·烈日岗",nTime="10,恶人·兵符增援·烈日岗;300,恶人·烈日岗·兵符冷却;305,恶人·烈日岗·可用兵符",nRefresh=1,key="兵符·烈日岗",},},},</v>
+        <v>{szContent="增援已至神池岭，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·神池岭",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·神池岭",nTime="10,恶人·兵符增援·神池岭;300,恶人·神池岭·兵符冷却;305,恶人·神池岭·可用兵符",nRefresh=1,key="兵符·神池岭",},},},</v>
       </c>
       <c r="W166" t="s">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="167" customFormat="1" spans="1:25">
+      <c r="C167" t="s">
+        <v>2336</v>
+      </c>
+      <c r="D167" t="s">
         <v>2377</v>
       </c>
-    </row>
-    <row r="167" spans="1:25">
-      <c r="A167" t="s">
-        <v>853</v>
-      </c>
-      <c r="B167">
-        <v>105</v>
+      <c r="E167" t="s">
+        <v>2378</v>
+      </c>
+      <c r="M167" t="s">
+        <v>2121</v>
+      </c>
+      <c r="S167">
+        <v>1</v>
       </c>
       <c r="V167" t="str">
         <f t="shared" si="30"/>
-        <v>},[105]={</v>
-      </c>
-    </row>
-    <row r="168" customFormat="1" spans="1:25">
-      <c r="C168" t="s">
-        <v>2302</v>
-      </c>
-      <c r="D168" t="s">
-        <v>2378</v>
-      </c>
-      <c r="E168" t="s">
+        <v>{szContent="增援已至烈日岗，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·烈日岗",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·烈日岗",nTime="10,恶人·兵符增援·烈日岗;300,恶人·烈日岗·兵符冷却;305,恶人·烈日岗·可用兵符",nRefresh=1,key="兵符·烈日岗",},},},</v>
+      </c>
+      <c r="W167" t="s">
         <v>2379</v>
       </c>
-      <c r="M168" t="s">
-        <v>2120</v>
-      </c>
-      <c r="S168">
-        <v>1</v>
+    </row>
+    <row r="168" spans="1:25">
+      <c r="A168" t="s">
+        <v>853</v>
+      </c>
+      <c r="B168">
+        <v>105</v>
       </c>
       <c r="V168" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="增援已至大理山城，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·大理山城",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·大理山城",nTime="10,浩气·兵符增援·大理山城;300,浩气·大理山城·兵符冷却;305,浩气·大理山城·可用兵符",nRefresh=1,key="兵符·大理山城",},},},</v>
-      </c>
-      <c r="W168" t="s">
-        <v>2380</v>
+        <v>},[105]={</v>
       </c>
     </row>
     <row r="169" customFormat="1" spans="1:25">
       <c r="C169" t="s">
-        <v>2302</v>
+        <v>2304</v>
       </c>
       <c r="D169" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E169" t="s">
         <v>2381</v>
-      </c>
-      <c r="E169" t="s">
-        <v>2382</v>
       </c>
       <c r="M169" t="s">
         <v>2120</v>
@@ -40658,57 +40664,57 @@
       </c>
       <c r="V169" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="增援已至千岩关，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·千岩关",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·千岩关",nTime="10,浩气·兵符增援·千岩关;300,浩气·千岩关·兵符冷却;305,浩气·千岩关·可用兵符",nRefresh=1,key="兵符·千岩关",},},},</v>
+        <v>{szContent="增援已至大理山城，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·大理山城",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·大理山城",nTime="10,浩气·兵符增援·大理山城;300,浩气·大理山城·兵符冷却;305,浩气·大理山城·可用兵符",nRefresh=1,key="兵符·大理山城",},},},</v>
       </c>
       <c r="W169" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="170" customFormat="1" spans="1:25">
+      <c r="C170" t="s">
+        <v>2304</v>
+      </c>
+      <c r="D170" t="s">
         <v>2383</v>
       </c>
-    </row>
-    <row r="170" spans="1:25">
-      <c r="A170" t="s">
-        <v>984</v>
-      </c>
-      <c r="B170">
-        <v>153</v>
+      <c r="E170" t="s">
+        <v>2384</v>
+      </c>
+      <c r="M170" t="s">
+        <v>2120</v>
+      </c>
+      <c r="S170">
+        <v>1</v>
       </c>
       <c r="V170" t="str">
         <f t="shared" si="30"/>
-        <v>},[153]={</v>
-      </c>
-    </row>
-    <row r="171" customFormat="1" spans="1:25">
-      <c r="C171" t="s">
-        <v>2334</v>
-      </c>
-      <c r="D171" t="s">
-        <v>2384</v>
-      </c>
-      <c r="E171" t="s">
+        <v>{szContent="增援已至千岩关，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·千岩关",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·千岩关",nTime="10,浩气·兵符增援·千岩关;300,浩气·千岩关·兵符冷却;305,浩气·千岩关·可用兵符",nRefresh=1,key="兵符·千岩关",},},},</v>
+      </c>
+      <c r="W170" t="s">
         <v>2385</v>
       </c>
-      <c r="M171" t="s">
-        <v>2121</v>
-      </c>
-      <c r="S171">
-        <v>1</v>
+    </row>
+    <row r="171" spans="1:25">
+      <c r="A171" t="s">
+        <v>984</v>
+      </c>
+      <c r="B171">
+        <v>153</v>
       </c>
       <c r="V171" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="增援已至扶风郡，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·扶风郡",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·扶风郡",nTime="10,恶人·兵符增援·扶风郡;300,恶人·扶风郡·兵符冷却;305,恶人·扶风郡·可用兵符",nRefresh=1,key="兵符·扶风郡",},},},</v>
-      </c>
-      <c r="W171" t="s">
-        <v>2386</v>
+        <v>},[153]={</v>
       </c>
     </row>
     <row r="172" customFormat="1" spans="1:25">
       <c r="C172" t="s">
-        <v>2334</v>
+        <v>2336</v>
       </c>
       <c r="D172" t="s">
+        <v>2386</v>
+      </c>
+      <c r="E172" t="s">
         <v>2387</v>
-      </c>
-      <c r="E172" t="s">
-        <v>2388</v>
       </c>
       <c r="M172" t="s">
         <v>2121</v>
@@ -40718,79 +40724,79 @@
       </c>
       <c r="V172" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="增援已至世外坡，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·世外坡",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·世外坡",nTime="10,恶人·兵符增援·世外坡;300,恶人·世外坡·兵符冷却;305,恶人·世外坡·可用兵符",nRefresh=1,key="兵符·世外坡",},},},</v>
+        <v>{szContent="增援已至扶风郡，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·扶风郡",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·扶风郡",nTime="10,恶人·兵符增援·扶风郡;300,恶人·扶风郡·兵符冷却;305,恶人·扶风郡·可用兵符",nRefresh=1,key="兵符·扶风郡",},},},</v>
       </c>
       <c r="W172" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="173" customFormat="1" spans="1:25">
+      <c r="C173" t="s">
+        <v>2336</v>
+      </c>
+      <c r="D173" t="s">
         <v>2389</v>
       </c>
-    </row>
-    <row r="173" spans="1:25">
-      <c r="A173" t="s">
-        <v>1062</v>
-      </c>
-      <c r="B173">
-        <v>216</v>
+      <c r="E173" t="s">
+        <v>2390</v>
+      </c>
+      <c r="M173" t="s">
+        <v>2121</v>
+      </c>
+      <c r="S173">
+        <v>1</v>
       </c>
       <c r="V173" t="str">
         <f t="shared" si="30"/>
-        <v>},[216]={</v>
-      </c>
-    </row>
-    <row r="174" customFormat="1" spans="1:25">
-      <c r="C174" t="s">
-        <v>2068</v>
-      </c>
-      <c r="D174" s="8" t="s">
-        <v>2390</v>
-      </c>
-      <c r="E174" t="s">
+        <v>{szContent="增援已至世外坡，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·世外坡",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·世外坡",nTime="10,恶人·兵符增援·世外坡;300,恶人·世外坡·兵符冷却;305,恶人·世外坡·可用兵符",nRefresh=1,key="兵符·世外坡",},},},</v>
+      </c>
+      <c r="W173" t="s">
         <v>2391</v>
       </c>
-      <c r="M174" t="s">
-        <v>1656</v>
-      </c>
-      <c r="O174">
-        <v>1</v>
-      </c>
-      <c r="S174">
-        <v>1</v>
+    </row>
+    <row r="174" spans="1:25">
+      <c r="A174" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B174">
+        <v>216</v>
       </c>
       <c r="V174" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
-      </c>
-      <c r="W174" t="s">
+        <v>},[216]={</v>
+      </c>
+    </row>
+    <row r="175" customFormat="1" spans="1:25">
+      <c r="C175" t="s">
+        <v>2068</v>
+      </c>
+      <c r="D175" s="8" t="s">
         <v>2392</v>
       </c>
-      <c r="X174" t="s">
+      <c r="E175" t="s">
         <v>2393</v>
       </c>
-      <c r="Y174" t="s">
-        <v>2394</v>
-      </c>
-    </row>
-    <row r="175" customFormat="1" spans="1:25">
-      <c r="C175" s="3" t="s">
-        <v>2068</v>
-      </c>
-      <c r="D175" t="s">
-        <v>2271</v>
-      </c>
       <c r="M175" t="s">
-        <v>2120</v>
-      </c>
-      <c r="N175">
+        <v>1656</v>
+      </c>
+      <c r="O175">
+        <v>1</v>
+      </c>
+      <c r="S175">
         <v>1</v>
       </c>
       <c r="V175" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
+        <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
       </c>
       <c r="W175" t="s">
-        <v>2272</v>
+        <v>2394</v>
       </c>
       <c r="X175" t="s">
-        <v>2273</v>
+        <v>2395</v>
+      </c>
+      <c r="Y175" t="s">
+        <v>2396</v>
       </c>
     </row>
     <row r="176" customFormat="1" spans="1:25">
@@ -40798,20 +40804,20 @@
         <v>2068</v>
       </c>
       <c r="D176" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="M176" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="N176">
         <v>1</v>
       </c>
       <c r="V176" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
+        <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W176" t="s">
-        <v>2272</v>
+        <v>2274</v>
       </c>
       <c r="X176" t="s">
         <v>2275</v>
@@ -40824,33 +40830,21 @@
       <c r="D177" t="s">
         <v>2276</v>
       </c>
-      <c r="E177" t="s">
-        <v>2277</v>
-      </c>
       <c r="M177" t="s">
-        <v>1656</v>
-      </c>
-      <c r="S177">
+        <v>2121</v>
+      </c>
+      <c r="N177">
         <v>1</v>
       </c>
       <c r="V177" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},},},</v>
+        <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W177" t="s">
-        <v>2278</v>
+        <v>2274</v>
       </c>
       <c r="X177" t="s">
-        <v>2279</v>
-      </c>
-      <c r="Y177" t="s">
-        <v>2280</v>
-      </c>
-      <c r="Z177" t="s">
-        <v>2281</v>
-      </c>
-      <c r="AA177" t="s">
-        <v>2282</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="178" customFormat="1" spans="1:27">
@@ -40858,100 +40852,112 @@
         <v>2068</v>
       </c>
       <c r="D178" t="s">
-        <v>2258</v>
+        <v>2278</v>
       </c>
       <c r="E178" t="s">
-        <v>2259</v>
+        <v>2279</v>
       </c>
       <c r="M178" t="s">
         <v>1656</v>
       </c>
-      <c r="O178">
-        <v>1</v>
-      </c>
       <c r="S178">
         <v>1</v>
       </c>
       <c r="V178" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
+        <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},},},</v>
       </c>
       <c r="W178" t="s">
+        <v>2280</v>
+      </c>
+      <c r="X178" t="s">
+        <v>2281</v>
+      </c>
+      <c r="Y178" t="s">
+        <v>2282</v>
+      </c>
+      <c r="Z178" t="s">
+        <v>2283</v>
+      </c>
+      <c r="AA178" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="179" customFormat="1" spans="1:27">
+      <c r="C179" s="3" t="s">
+        <v>2068</v>
+      </c>
+      <c r="D179" t="s">
         <v>2260</v>
       </c>
-    </row>
-    <row r="179" customFormat="1" spans="1:27">
-      <c r="C179" s="3"/>
-      <c r="D179" t="s">
-        <v>2243</v>
-      </c>
       <c r="E179" t="s">
-        <v>2244</v>
+        <v>2261</v>
       </c>
       <c r="M179" t="s">
-        <v>1470</v>
-      </c>
-      <c r="P179" t="s">
-        <v>538</v>
-      </c>
-      <c r="Q179">
-        <v>1</v>
-      </c>
-      <c r="R179">
+        <v>1656</v>
+      </c>
+      <c r="O179">
         <v>1</v>
       </c>
       <c r="S179">
-        <v>1</v>
-      </c>
-      <c r="U179">
         <v>1</v>
       </c>
       <c r="V179" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="系统检测您有挂机行为，如果长期维持该状态将被传送出图！",szNote="挂机检测·快活跃起来",col={255,50,255,},[14]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},},},</v>
+        <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W179" t="s">
-        <v>2245</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="180" customFormat="1" spans="1:27">
       <c r="C180" s="3"/>
       <c r="D180" t="s">
+        <v>2245</v>
+      </c>
+      <c r="E180" t="s">
         <v>2246</v>
       </c>
       <c r="M180" t="s">
-        <v>1656</v>
+        <v>1470</v>
+      </c>
+      <c r="P180" t="s">
+        <v>538</v>
+      </c>
+      <c r="Q180">
+        <v>1</v>
+      </c>
+      <c r="R180">
+        <v>1</v>
+      </c>
+      <c r="S180">
+        <v>1</v>
+      </c>
+      <c r="U180">
+        <v>1</v>
       </c>
       <c r="V180" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="离开据点·大旗重置",},},},</v>
+        <v>{szContent="系统检测您有挂机行为，如果长期维持该状态将被传送出图！",szNote="挂机检测·快活跃起来",col={255,50,255,},[14]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},},},</v>
       </c>
       <c r="W180" t="s">
-        <v>2395</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="181" customFormat="1" spans="1:27">
-      <c r="C181" s="3" t="s">
-        <v>1715</v>
-      </c>
+      <c r="C181" s="3"/>
       <c r="D181" t="s">
-        <v>2289</v>
-      </c>
-      <c r="E181" t="s">
-        <v>2290</v>
+        <v>2248</v>
+      </c>
+      <c r="M181" t="s">
+        <v>1656</v>
       </c>
       <c r="V181" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="哼，还有要事要办，今日收获甚多，来日定多来领略你们的武功！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·攻防结束",[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领·离开",nTime=0,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
+        <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W181" t="s">
-        <v>2291</v>
-      </c>
-      <c r="X181" s="5" t="s">
-        <v>2292</v>
-      </c>
-      <c r="Y181" s="5" t="s">
-        <v>2293</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="182" customFormat="1" spans="1:27">
@@ -40959,17 +40965,23 @@
         <v>1715</v>
       </c>
       <c r="D182" t="s">
-        <v>2294</v>
+        <v>2291</v>
       </c>
       <c r="E182" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="V182" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="哼，打扰本大爷休息！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话1",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},},},</v>
+        <v>{szContent="哼，还有要事要办，今日收获甚多，来日定多来领略你们的武功！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·攻防结束",[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领·离开",nTime=0,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="W182" t="s">
-        <v>2296</v>
+        <v>2293</v>
+      </c>
+      <c r="X182" s="5" t="s">
+        <v>2294</v>
+      </c>
+      <c r="Y182" s="5" t="s">
+        <v>2295</v>
       </c>
     </row>
     <row r="183" customFormat="1" spans="1:27">
@@ -40977,23 +40989,17 @@
         <v>1715</v>
       </c>
       <c r="D183" t="s">
+        <v>2296</v>
+      </c>
+      <c r="E183" t="s">
         <v>2297</v>
-      </c>
-      <c r="E183" t="s">
-        <v>2298</v>
       </c>
       <c r="V183" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="你爷爷我年轻些时候，也是翻云覆雨的江湖响当当一号人物！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话2",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
+        <v>{szContent="哼，打扰本大爷休息！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话1",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W183" t="s">
-        <v>2296</v>
-      </c>
-      <c r="X183" s="3" t="s">
-        <v>2287</v>
-      </c>
-      <c r="Y183" s="3" t="s">
-        <v>2288</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="184" customFormat="1" spans="1:27">
@@ -41008,85 +41014,85 @@
       </c>
       <c r="V184" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="我竟然败给你们这群小辈！",szTarget="狼牙先锋首领",szNote="防冲突禁用·击退·狼牙先锋首领",[14]={},tCountdown={{nClass=-1,nIcon=3556,nFrame=1,szName="狼牙先锋首领·拾取掉落",nTime="10,狼牙先锋首领·已击退;300,狼牙先锋首领·拾取剩余;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=2,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
+        <v>{szContent="你爷爷我年轻些时候，也是翻云覆雨的江湖响当当一号人物！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话2",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W184" t="s">
+        <v>2298</v>
+      </c>
+      <c r="X184" s="3" t="s">
+        <v>2289</v>
+      </c>
+      <c r="Y184" s="3" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="185" customFormat="1" spans="1:27">
+      <c r="C185" s="3" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D185" t="s">
         <v>2301</v>
       </c>
-      <c r="X184" s="3" t="s">
-        <v>2287</v>
-      </c>
-      <c r="Y184" s="3" t="s">
-        <v>2288</v>
-      </c>
-    </row>
-    <row r="185" spans="1:27">
-      <c r="A185" t="s">
-        <v>1415</v>
-      </c>
-      <c r="B185">
-        <v>656</v>
+      <c r="E185" t="s">
+        <v>2302</v>
       </c>
       <c r="V185" t="str">
         <f t="shared" si="30"/>
-        <v>},[656]={</v>
-      </c>
-    </row>
-    <row r="186" customFormat="1" spans="1:27">
-      <c r="C186" t="s">
-        <v>2068</v>
-      </c>
-      <c r="D186" s="8" t="s">
-        <v>2390</v>
-      </c>
-      <c r="E186" t="s">
-        <v>2391</v>
-      </c>
-      <c r="M186" t="s">
-        <v>1656</v>
-      </c>
-      <c r="O186">
-        <v>1</v>
-      </c>
-      <c r="S186">
-        <v>1</v>
+        <v>{szContent="我竟然败给你们这群小辈！",szTarget="狼牙先锋首领",szNote="防冲突禁用·击退·狼牙先锋首领",[14]={},tCountdown={{nClass=-1,nIcon=3556,nFrame=1,szName="狼牙先锋首领·拾取掉落",nTime="10,狼牙先锋首领·已击退;300,狼牙先锋首领·拾取剩余;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=2,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
+      </c>
+      <c r="W185" t="s">
+        <v>2303</v>
+      </c>
+      <c r="X185" s="3" t="s">
+        <v>2289</v>
+      </c>
+      <c r="Y185" s="3" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="186" spans="1:27">
+      <c r="A186" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B186">
+        <v>656</v>
       </c>
       <c r="V186" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
-      </c>
-      <c r="W186" t="s">
+        <v>},[656]={</v>
+      </c>
+    </row>
+    <row r="187" customFormat="1" spans="1:27">
+      <c r="C187" t="s">
+        <v>2068</v>
+      </c>
+      <c r="D187" s="8" t="s">
         <v>2392</v>
       </c>
-      <c r="X186" t="s">
+      <c r="E187" t="s">
         <v>2393</v>
       </c>
-      <c r="Y186" t="s">
-        <v>2394</v>
-      </c>
-    </row>
-    <row r="187" customFormat="1" spans="1:27">
-      <c r="C187" s="3" t="s">
-        <v>2068</v>
-      </c>
-      <c r="D187" t="s">
-        <v>2271</v>
-      </c>
       <c r="M187" t="s">
-        <v>2120</v>
-      </c>
-      <c r="N187">
+        <v>1656</v>
+      </c>
+      <c r="O187">
+        <v>1</v>
+      </c>
+      <c r="S187">
         <v>1</v>
       </c>
       <c r="V187" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
+        <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
       </c>
       <c r="W187" t="s">
-        <v>2272</v>
+        <v>2394</v>
       </c>
       <c r="X187" t="s">
-        <v>2273</v>
+        <v>2395</v>
+      </c>
+      <c r="Y187" t="s">
+        <v>2396</v>
       </c>
     </row>
     <row r="188" customFormat="1" spans="1:27">
@@ -41094,20 +41100,20 @@
         <v>2068</v>
       </c>
       <c r="D188" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="M188" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="N188">
         <v>1</v>
       </c>
       <c r="V188" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
+        <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W188" t="s">
-        <v>2272</v>
+        <v>2274</v>
       </c>
       <c r="X188" t="s">
         <v>2275</v>
@@ -41120,33 +41126,21 @@
       <c r="D189" t="s">
         <v>2276</v>
       </c>
-      <c r="E189" t="s">
-        <v>2277</v>
-      </c>
       <c r="M189" t="s">
-        <v>1656</v>
-      </c>
-      <c r="S189">
+        <v>2121</v>
+      </c>
+      <c r="N189">
         <v>1</v>
       </c>
       <c r="V189" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},},},</v>
+        <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W189" t="s">
-        <v>2278</v>
+        <v>2274</v>
       </c>
       <c r="X189" t="s">
-        <v>2279</v>
-      </c>
-      <c r="Y189" t="s">
-        <v>2280</v>
-      </c>
-      <c r="Z189" t="s">
-        <v>2281</v>
-      </c>
-      <c r="AA189" t="s">
-        <v>2282</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="190" customFormat="1" spans="1:27">
@@ -41154,100 +41148,112 @@
         <v>2068</v>
       </c>
       <c r="D190" t="s">
-        <v>2258</v>
+        <v>2278</v>
       </c>
       <c r="E190" t="s">
-        <v>2259</v>
+        <v>2279</v>
       </c>
       <c r="M190" t="s">
         <v>1656</v>
       </c>
-      <c r="O190">
-        <v>1</v>
-      </c>
       <c r="S190">
         <v>1</v>
       </c>
       <c r="V190" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
+        <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},},},</v>
       </c>
       <c r="W190" t="s">
+        <v>2280</v>
+      </c>
+      <c r="X190" t="s">
+        <v>2281</v>
+      </c>
+      <c r="Y190" t="s">
+        <v>2282</v>
+      </c>
+      <c r="Z190" t="s">
+        <v>2283</v>
+      </c>
+      <c r="AA190" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="191" customFormat="1" spans="1:27">
+      <c r="C191" s="3" t="s">
+        <v>2068</v>
+      </c>
+      <c r="D191" t="s">
         <v>2260</v>
       </c>
-    </row>
-    <row r="191" customFormat="1" spans="1:27">
-      <c r="C191" s="3"/>
-      <c r="D191" t="s">
-        <v>2243</v>
-      </c>
       <c r="E191" t="s">
-        <v>2244</v>
+        <v>2261</v>
       </c>
       <c r="M191" t="s">
-        <v>1470</v>
-      </c>
-      <c r="P191" t="s">
-        <v>538</v>
-      </c>
-      <c r="Q191">
-        <v>1</v>
-      </c>
-      <c r="R191">
+        <v>1656</v>
+      </c>
+      <c r="O191">
         <v>1</v>
       </c>
       <c r="S191">
-        <v>1</v>
-      </c>
-      <c r="U191">
         <v>1</v>
       </c>
       <c r="V191" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="系统检测您有挂机行为，如果长期维持该状态将被传送出图！",szNote="挂机检测·快活跃起来",col={255,50,255,},[14]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},},},</v>
+        <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W191" t="s">
-        <v>2245</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="192" customFormat="1" spans="1:27">
       <c r="C192" s="3"/>
       <c r="D192" t="s">
+        <v>2245</v>
+      </c>
+      <c r="E192" t="s">
         <v>2246</v>
       </c>
       <c r="M192" t="s">
-        <v>1656</v>
+        <v>1470</v>
+      </c>
+      <c r="P192" t="s">
+        <v>538</v>
+      </c>
+      <c r="Q192">
+        <v>1</v>
+      </c>
+      <c r="R192">
+        <v>1</v>
+      </c>
+      <c r="S192">
+        <v>1</v>
+      </c>
+      <c r="U192">
+        <v>1</v>
       </c>
       <c r="V192" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="离开据点·大旗重置",},},},</v>
+        <v>{szContent="系统检测您有挂机行为，如果长期维持该状态将被传送出图！",szNote="挂机检测·快活跃起来",col={255,50,255,},[14]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},},},</v>
       </c>
       <c r="W192" t="s">
-        <v>2395</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="193" customFormat="1" spans="3:25">
-      <c r="C193" s="3" t="s">
-        <v>1715</v>
-      </c>
+      <c r="C193" s="3"/>
       <c r="D193" t="s">
-        <v>2289</v>
-      </c>
-      <c r="E193" t="s">
-        <v>2290</v>
+        <v>2248</v>
+      </c>
+      <c r="M193" t="s">
+        <v>1656</v>
       </c>
       <c r="V193" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="哼，还有要事要办，今日收获甚多，来日定多来领略你们的武功！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·攻防结束",[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领·离开",nTime=0,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
+        <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W193" t="s">
-        <v>2291</v>
-      </c>
-      <c r="X193" s="5" t="s">
-        <v>2292</v>
-      </c>
-      <c r="Y193" s="5" t="s">
-        <v>2293</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="194" customFormat="1" spans="3:25">
@@ -41255,17 +41261,23 @@
         <v>1715</v>
       </c>
       <c r="D194" t="s">
-        <v>2294</v>
+        <v>2291</v>
       </c>
       <c r="E194" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="V194" t="str">
         <f t="shared" si="30"/>
-        <v>{szContent="哼，打扰本大爷休息！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话1",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},},},</v>
+        <v>{szContent="哼，还有要事要办，今日收获甚多，来日定多来领略你们的武功！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·攻防结束",[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领·离开",nTime=0,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="W194" t="s">
-        <v>2296</v>
+        <v>2293</v>
+      </c>
+      <c r="X194" s="5" t="s">
+        <v>2294</v>
+      </c>
+      <c r="Y194" s="5" t="s">
+        <v>2295</v>
       </c>
     </row>
     <row r="195" customFormat="1" spans="3:25">
@@ -41273,23 +41285,17 @@
         <v>1715</v>
       </c>
       <c r="D195" t="s">
+        <v>2296</v>
+      </c>
+      <c r="E195" t="s">
         <v>2297</v>
       </c>
-      <c r="E195" t="s">
+      <c r="V195" t="str">
+        <f>IF(ISBLANK(B195)=FALSE,IF(ISBLANK(B194),"},["&amp;B195&amp;"]={","["&amp;B195&amp;"]={"),IF(AND(ISBLANK(B195),ISBLANK(D195),ISBLANK(N195),ISBLANK(O195),OR(ISBLANK(B194)=FALSE,ISBLANK(D194)=FALSE,ISBLANK(N194)=FALSE,ISBLANK(O194)=FALSE)),"},},}",IF(ISBLANK(D195),"","{szContent="""&amp;D195&amp;""","&amp;IF(C195&lt;&gt;"","szTarget="""&amp;C195&amp;""",","")&amp;IF(E195&lt;&gt;"","szNote="""&amp;E195&amp;""",","")&amp;IF(M195&lt;&gt;"","col={"&amp;M195&amp;"},","")&amp;IF(N195&gt;0,"bSearch=true,","")&amp;IF(O195&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P195&gt;0,"szVoice="""&amp;P195&amp;""",","")&amp;IF(Q195&gt;0,"bTeamChannel=true,","")&amp;IF(R195&gt;0,"bWhisperChannel=true,","")&amp;IF(S195&gt;0,"bCenterAlarm=true,","")&amp;IF(T195&gt;0,"bScreenHead=true,","")&amp;IF(U195&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W195&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W195:AAH195)&amp;"},","")&amp;"},")))</f>
+        <v>{szContent="哼，打扰本大爷休息！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话1",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},},},</v>
+      </c>
+      <c r="W195" t="s">
         <v>2298</v>
-      </c>
-      <c r="V195" t="str">
-        <f t="shared" si="30"/>
-        <v>{szContent="你爷爷我年轻些时候，也是翻云覆雨的江湖响当当一号人物！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话2",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
-      </c>
-      <c r="W195" t="s">
-        <v>2296</v>
-      </c>
-      <c r="X195" s="3" t="s">
-        <v>2287</v>
-      </c>
-      <c r="Y195" s="3" t="s">
-        <v>2288</v>
       </c>
     </row>
     <row r="196" customFormat="1" spans="3:25">
@@ -41303,27 +41309,51 @@
         <v>2300</v>
       </c>
       <c r="V196" t="str">
-        <f t="shared" si="30"/>
+        <f>IF(ISBLANK(B196)=FALSE,IF(ISBLANK(B195),"},["&amp;B196&amp;"]={","["&amp;B196&amp;"]={"),IF(AND(ISBLANK(B196),ISBLANK(D196),ISBLANK(N196),ISBLANK(O196),OR(ISBLANK(B195)=FALSE,ISBLANK(D195)=FALSE,ISBLANK(N195)=FALSE,ISBLANK(O195)=FALSE)),"},},}",IF(ISBLANK(D196),"","{szContent="""&amp;D196&amp;""","&amp;IF(C196&lt;&gt;"","szTarget="""&amp;C196&amp;""",","")&amp;IF(E196&lt;&gt;"","szNote="""&amp;E196&amp;""",","")&amp;IF(M196&lt;&gt;"","col={"&amp;M196&amp;"},","")&amp;IF(N196&gt;0,"bSearch=true,","")&amp;IF(O196&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P196&gt;0,"szVoice="""&amp;P196&amp;""",","")&amp;IF(Q196&gt;0,"bTeamChannel=true,","")&amp;IF(R196&gt;0,"bWhisperChannel=true,","")&amp;IF(S196&gt;0,"bCenterAlarm=true,","")&amp;IF(T196&gt;0,"bScreenHead=true,","")&amp;IF(U196&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W196&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W196:AAH196)&amp;"},","")&amp;"},")))</f>
+        <v>{szContent="你爷爷我年轻些时候，也是翻云覆雨的江湖响当当一号人物！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话2",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
+      </c>
+      <c r="W196" t="s">
+        <v>2298</v>
+      </c>
+      <c r="X196" s="3" t="s">
+        <v>2289</v>
+      </c>
+      <c r="Y196" s="3" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="197" customFormat="1" spans="3:25">
+      <c r="C197" s="3" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D197" t="s">
+        <v>2301</v>
+      </c>
+      <c r="E197" t="s">
+        <v>2302</v>
+      </c>
+      <c r="V197" t="str">
+        <f>IF(ISBLANK(B197)=FALSE,IF(ISBLANK(B196),"},["&amp;B197&amp;"]={","["&amp;B197&amp;"]={"),IF(AND(ISBLANK(B197),ISBLANK(D197),ISBLANK(N197),ISBLANK(O197),OR(ISBLANK(B196)=FALSE,ISBLANK(D196)=FALSE,ISBLANK(N196)=FALSE,ISBLANK(O196)=FALSE)),"},},}",IF(ISBLANK(D197),"","{szContent="""&amp;D197&amp;""","&amp;IF(C197&lt;&gt;"","szTarget="""&amp;C197&amp;""",","")&amp;IF(E197&lt;&gt;"","szNote="""&amp;E197&amp;""",","")&amp;IF(M197&lt;&gt;"","col={"&amp;M197&amp;"},","")&amp;IF(N197&gt;0,"bSearch=true,","")&amp;IF(O197&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P197&gt;0,"szVoice="""&amp;P197&amp;""",","")&amp;IF(Q197&gt;0,"bTeamChannel=true,","")&amp;IF(R197&gt;0,"bWhisperChannel=true,","")&amp;IF(S197&gt;0,"bCenterAlarm=true,","")&amp;IF(T197&gt;0,"bScreenHead=true,","")&amp;IF(U197&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W197&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W197:AAH197)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="我竟然败给你们这群小辈！",szTarget="狼牙先锋首领",szNote="防冲突禁用·击退·狼牙先锋首领",[14]={},tCountdown={{nClass=-1,nIcon=3556,nFrame=1,szName="狼牙先锋首领·拾取掉落",nTime="10,狼牙先锋首领·已击退;300,狼牙先锋首领·拾取剩余;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=2,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
-      <c r="W196" t="s">
-        <v>2301</v>
-      </c>
-      <c r="X196" s="3" t="s">
-        <v>2287</v>
-      </c>
-      <c r="Y196" s="3" t="s">
-        <v>2288</v>
-      </c>
-    </row>
-    <row r="197" spans="3:25">
-      <c r="V197" t="str">
-        <f t="shared" si="30"/>
+      <c r="W197" t="s">
+        <v>2303</v>
+      </c>
+      <c r="X197" s="3" t="s">
+        <v>2289</v>
+      </c>
+      <c r="Y197" s="3" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="198" spans="3:25">
+      <c r="V198" t="str">
+        <f>IF(ISBLANK(B198)=FALSE,IF(ISBLANK(B197),"},["&amp;B198&amp;"]={","["&amp;B198&amp;"]={"),IF(AND(ISBLANK(B198),ISBLANK(D198),ISBLANK(N198),ISBLANK(O198),OR(ISBLANK(B197)=FALSE,ISBLANK(D197)=FALSE,ISBLANK(N197)=FALSE,ISBLANK(O197)=FALSE)),"},},}",IF(ISBLANK(D198),"","{szContent="""&amp;D198&amp;""","&amp;IF(C198&lt;&gt;"","szTarget="""&amp;C198&amp;""",","")&amp;IF(E198&lt;&gt;"","szNote="""&amp;E198&amp;""",","")&amp;IF(M198&lt;&gt;"","col={"&amp;M198&amp;"},","")&amp;IF(N198&gt;0,"bSearch=true,","")&amp;IF(O198&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P198&gt;0,"szVoice="""&amp;P198&amp;""",","")&amp;IF(Q198&gt;0,"bTeamChannel=true,","")&amp;IF(R198&gt;0,"bWhisperChannel=true,","")&amp;IF(S198&gt;0,"bCenterAlarm=true,","")&amp;IF(T198&gt;0,"bScreenHead=true,","")&amp;IF(U198&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W198&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W198:AAH198)&amp;"},","")&amp;"},")))</f>
         <v>},},}</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AV197" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AV198" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -41377,10 +41407,10 @@
         <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="F1" t="s">
-        <v>2397</v>
+        <v>2399</v>
       </c>
       <c r="G1" t="s">
         <v>2047</v>
@@ -41422,7 +41452,7 @@
         <v>2058</v>
       </c>
       <c r="T1" t="s">
-        <v>2398</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="2" customFormat="1" spans="1:33">
@@ -41439,10 +41469,10 @@
     </row>
     <row r="3" customFormat="1" spans="1:33">
       <c r="C3" t="s">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="D3" t="s">
-        <v>2400</v>
+        <v>2402</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -41452,18 +41482,18 @@
         <v>{szContent="[团队监控]数据加载成功",szNote="关闭刷马等计时条",bSearch=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},},},</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>2402</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="4" customFormat="1" spans="1:33">
       <c r="C4" t="s">
-        <v>2403</v>
+        <v>2405</v>
       </c>
       <c r="D4" t="s">
-        <v>2404</v>
+        <v>2406</v>
       </c>
       <c r="K4" t="s">
         <v>1656</v>
@@ -41473,15 +41503,15 @@
         <v>{szContent="驿马快报！本周浩气盟和恶人谷最终战为平手，未分胜负！\n",szNote="阵营事件·本周战平",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13354,nFrame=4,szName="阵营事件·本周战平",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U4" t="s">
-        <v>2405</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:33">
       <c r="C5" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="D5" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
       <c r="K5" t="s">
         <v>2121</v>
@@ -41491,15 +41521,15 @@
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U5" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:33">
       <c r="C6" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="D6" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="K6" t="s">
         <v>2120</v>
@@ -41509,15 +41539,15 @@
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U6" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="7" spans="1:33">
       <c r="C7" t="s">
-        <v>2412</v>
+        <v>2414</v>
       </c>
       <c r="D7" t="s">
-        <v>2413</v>
+        <v>2415</v>
       </c>
       <c r="K7" t="s">
         <v>1656</v>
@@ -41527,39 +41557,39 @@
         <v>{szContent="本场攻防“奇袭场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手。战利品稍后开始拍卖，请留意！\n",szNote="奇袭场·平局",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2402,nFrame=4,bHold=true,szName="奇袭场·平局",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·一",key="破阵点将·一",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·二",key="破阵点将·二",},{nClass=20,nIcon=13,szName="牛车拾取间隔",nTime=-1,key="牛车拾取间隔",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,key="首领拾取间隔",},{nClass=20,nIcon=13,nFrame=4,szName="浩气·物资车·运达",nTime=-1,key="浩气·物资车·运达",},{nClass=20,nIcon=13,nFrame=4,szName="恶人·物资车·运达",nTime=-1,key="恶人·物资车·运达",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·月弄痕·减伤",nTime=-1,key="谢渊·月弄痕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·游驹·减伤",nTime=-1,key="谢渊·游驹·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·小七·减伤",nTime=-1,key="谢渊·小七·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·张桎辕·减伤",nTime=-1,key="谢渊·张桎辕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·司空仲平·减伤",nTime=-1,key="谢渊·司空仲平·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·韩非池·减伤",nTime=-1,key="谢渊·韩非池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·赵紫儿·减伤",nTime=-1,key="谢渊·赵紫儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·叶镜池·减伤",nTime=-1,key="谢渊·叶镜池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郭珠·减伤",nTime=-1,key="谢渊·郭珠·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·穆玄英·减伤",nTime=-1,key="谢渊·穆玄英·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·影·减伤",nTime=-1,key="谢渊·影·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·司徒一一·减伤",nTime=-1,key="王遗风·司徒一一·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·白某·减伤",nTime=-1,key="王遗风·白某·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·米丽古丽·减伤",nTime=-1,key="王遗风·米丽古丽·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶寒亭·减伤",nTime=-1,key="王遗风·陶寒亭·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·肖药儿·减伤",nTime=-1,key="王遗风·肖药儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·伊夜·减伤",nTime=-1,key="王遗风·伊夜·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·丁丁·减伤",nTime=-1,key="王遗风·丁丁·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·岳琅·减伤",nTime=-1,key="王遗风·岳琅·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·毕罗巴·减伤",nTime=-1,key="王遗风·毕罗巴·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·烟·减伤",nTime=-1,key="王遗风·烟·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·独孤修·减伤",nTime=-1,key="王遗风·独孤修·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·周峰·减伤",nTime=-1,key="谢渊·周峰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郑鸥·减伤",nTime=-1,key="谢渊·郑鸥·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·陶杰·减伤",nTime=-1,key="谢渊·陶杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢烟客·减伤",nTime=-1,key="谢渊·谢烟客·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·张一洋·减伤",nTime=-1,key="王遗风·张一洋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶国栋·减伤",nTime=-1,key="王遗风·陶国栋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·吕沛杰·减伤",nTime=-1,key="王遗风·吕沛杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·顾延恶·减伤",nTime=-1,key="王遗风·顾延恶·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·莫雨·减伤",nTime=-1,key="王遗风·莫雨·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·万兽王·减伤",nTime=-1,key="王遗风·万兽王·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢铃儿·减伤",nTime=-1,key="谢渊·谢铃儿·减伤",},},},</v>
       </c>
       <c r="U7" t="s">
-        <v>2414</v>
+        <v>2416</v>
       </c>
       <c r="V7" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="W7" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
       <c r="X7" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="Y7" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
       <c r="Z7" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="AA7" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="AB7" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="AC7" s="4" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="8" spans="1:33">
       <c r="C8" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="D8" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="K8" t="s">
         <v>1656</v>
@@ -41569,39 +41599,39 @@
         <v>{szContent="本场攻防“主战场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手。战利品稍后开始拍卖，请留意！\n",szNote="主战场·平局",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,bHold=true,szName="主战场·平局",nTime=57,nRefresh=5,key="大攻防·主战场",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·一",key="破阵点将·一",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·二",key="破阵点将·二",},{nClass=20,nIcon=13,szName="牛车拾取间隔",nTime=-1,key="牛车拾取间隔",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,key="首领拾取间隔",},{nClass=20,nIcon=13,nFrame=4,szName="浩气·物资车·运达",nTime=-1,key="浩气·物资车·运达",},{nClass=20,nIcon=13,nFrame=4,szName="恶人·物资车·运达",nTime=-1,key="恶人·物资车·运达",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·月弄痕·减伤",nTime=-1,key="谢渊·月弄痕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·游驹·减伤",nTime=-1,key="谢渊·游驹·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·小七·减伤",nTime=-1,key="谢渊·小七·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·张桎辕·减伤",nTime=-1,key="谢渊·张桎辕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·司空仲平·减伤",nTime=-1,key="谢渊·司空仲平·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·韩非池·减伤",nTime=-1,key="谢渊·韩非池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·赵紫儿·减伤",nTime=-1,key="谢渊·赵紫儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·叶镜池·减伤",nTime=-1,key="谢渊·叶镜池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郭珠·减伤",nTime=-1,key="谢渊·郭珠·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·穆玄英·减伤",nTime=-1,key="谢渊·穆玄英·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·影·减伤",nTime=-1,key="谢渊·影·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·司徒一一·减伤",nTime=-1,key="王遗风·司徒一一·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·白某·减伤",nTime=-1,key="王遗风·白某·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·米丽古丽·减伤",nTime=-1,key="王遗风·米丽古丽·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶寒亭·减伤",nTime=-1,key="王遗风·陶寒亭·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·肖药儿·减伤",nTime=-1,key="王遗风·肖药儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·伊夜·减伤",nTime=-1,key="王遗风·伊夜·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·丁丁·减伤",nTime=-1,key="王遗风·丁丁·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·岳琅·减伤",nTime=-1,key="王遗风·岳琅·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·毕罗巴·减伤",nTime=-1,key="王遗风·毕罗巴·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·烟·减伤",nTime=-1,key="王遗风·烟·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·独孤修·减伤",nTime=-1,key="王遗风·独孤修·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·周峰·减伤",nTime=-1,key="谢渊·周峰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郑鸥·减伤",nTime=-1,key="谢渊·郑鸥·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·陶杰·减伤",nTime=-1,key="谢渊·陶杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢烟客·减伤",nTime=-1,key="谢渊·谢烟客·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·张一洋·减伤",nTime=-1,key="王遗风·张一洋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶国栋·减伤",nTime=-1,key="王遗风·陶国栋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·吕沛杰·减伤",nTime=-1,key="王遗风·吕沛杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·顾延恶·减伤",nTime=-1,key="王遗风·顾延恶·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·莫雨·减伤",nTime=-1,key="王遗风·莫雨·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·万兽王·减伤",nTime=-1,key="王遗风·万兽王·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢铃儿·减伤",nTime=-1,key="谢渊·谢铃儿·减伤",},},},</v>
       </c>
       <c r="U8" t="s">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="V8" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="W8" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
       <c r="X8" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="Y8" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
       <c r="Z8" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="AA8" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="AB8" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="AC8" s="4" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="9" spans="1:33">
       <c r="C9" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
       <c r="D9" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
       <c r="K9" t="s">
         <v>1656</v>
@@ -41617,51 +41647,51 @@
         <v>{szContent="^本场攻防“([主战奇袭场]+)”已结束，([浩气盟恶人谷]+)[侠士们众志成城和，]-([大完险胜]+)([浩气盟恶人谷]+)[！，]+",szNote="{$1}·{$2}·{$3}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,szName="大攻防·奇袭场",nTime=-2,nRefresh=10,key="大攻防·奇袭场",},{nClass=20,nIcon=13,szName="大攻防·主战场",nTime=-2,nRefresh=10,key="大攻防·主战场",},{nClass=20,nIcon=13,szName="大攻防·{$1}",nTime=-2,key="大攻防·{$1}",},{nClass=20,nIcon=2402,nFrame=4,bHold=true,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=2400,nFrame=0,bHold=true,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·主战场",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·一",key="破阵点将·一",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·二",key="破阵点将·二",},{nClass=20,nIcon=13,szName="牛车拾取间隔",nTime=-1,key="牛车拾取间隔",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,key="首领拾取间隔",},{nClass=20,nIcon=13,nFrame=4,szName="浩气·物资车·运达",nTime=-1,key="浩气·物资车·运达",},{nClass=20,nIcon=13,nFrame=4,szName="恶人·物资车·运达",nTime=-1,key="恶人·物资车·运达",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·月弄痕·减伤",nTime=-1,key="谢渊·月弄痕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·游驹·减伤",nTime=-1,key="谢渊·游驹·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·小七·减伤",nTime=-1,key="谢渊·小七·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·张桎辕·减伤",nTime=-1,key="谢渊·张桎辕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·司空仲平·减伤",nTime=-1,key="谢渊·司空仲平·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·韩非池·减伤",nTime=-1,key="谢渊·韩非池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·赵紫儿·减伤",nTime=-1,key="谢渊·赵紫儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·叶镜池·减伤",nTime=-1,key="谢渊·叶镜池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郭珠·减伤",nTime=-1,key="谢渊·郭珠·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·穆玄英·减伤",nTime=-1,key="谢渊·穆玄英·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·影·减伤",nTime=-1,key="谢渊·影·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·司徒一一·减伤",nTime=-1,key="王遗风·司徒一一·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·白某·减伤",nTime=-1,key="王遗风·白某·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·米丽古丽·减伤",nTime=-1,key="王遗风·米丽古丽·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶寒亭·减伤",nTime=-1,key="王遗风·陶寒亭·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·肖药儿·减伤",nTime=-1,key="王遗风·肖药儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·伊夜·减伤",nTime=-1,key="王遗风·伊夜·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·丁丁·减伤",nTime=-1,key="王遗风·丁丁·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·岳琅·减伤",nTime=-1,key="王遗风·岳琅·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·毕罗巴·减伤",nTime=-1,key="王遗风·毕罗巴·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·烟·减伤",nTime=-1,key="王遗风·烟·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·独孤修·减伤",nTime=-1,key="王遗风·独孤修·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·周峰·减伤",nTime=-1,key="谢渊·周峰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郑鸥·减伤",nTime=-1,key="谢渊·郑鸥·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·陶杰·减伤",nTime=-1,key="谢渊·陶杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢烟客·减伤",nTime=-1,key="谢渊·谢烟客·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·张一洋·减伤",nTime=-1,key="王遗风·张一洋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶国栋·减伤",nTime=-1,key="王遗风·陶国栋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·吕沛杰·减伤",nTime=-1,key="王遗风·吕沛杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·顾延恶·减伤",nTime=-1,key="王遗风·顾延恶·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·莫雨·减伤",nTime=-1,key="王遗风·莫雨·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·万兽王·减伤",nTime=-1,key="王遗风·万兽王·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢铃儿·减伤",nTime=-1,key="谢渊·谢铃儿·减伤",},},},</v>
       </c>
       <c r="U9" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="V9" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="W9" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="X9" t="s">
-        <v>2431</v>
+        <v>2433</v>
       </c>
       <c r="Y9" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
       <c r="Z9" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="AA9" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
       <c r="AB9" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="AC9" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
       <c r="AD9" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="AE9" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="AF9" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="AG9" s="3" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:33">
       <c r="C10" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="D10" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
       <c r="K10" t="s">
         <v>1656</v>
@@ -41671,21 +41701,21 @@
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=20,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=20,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=20,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=20,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=20,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=20,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=20,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=20,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=20,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="U10" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="V10" s="5" t="s">
-        <v>2436</v>
+        <v>2438</v>
       </c>
       <c r="W10" s="5" t="s">
-        <v>2437</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="11" spans="1:33">
       <c r="C11" t="s">
-        <v>2438</v>
+        <v>2440</v>
       </c>
       <c r="D11" t="s">
-        <v>2439</v>
+        <v>2441</v>
       </c>
       <c r="K11" t="s">
         <v>1656</v>
@@ -41698,18 +41728,18 @@
         <v>{szContent="本场恶人谷攻防即将结束，昆仑物资运送暂且休整，等待下一场攻防开启！\n",szNote="本场攻防·即将结束",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=0,szName="本场攻防·结束剩余",nTime=60,nRefresh=5,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·肖药儿",nTime=-1,key="浩气·召请CD·肖药儿",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·司徒一一",nTime=-1,key="浩气·召请CD·司徒一一",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·陶寒亭",nTime=-1,key="浩气·召请CD·陶寒亭",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·白某",nTime=-1,key="浩气·召请CD·白某",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·米丽古丽",nTime=-1,key="浩气·召请CD·米丽古丽",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·小七",nTime=-1,key="恶人·召请CD·小七",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·游驹",nTime=-1,key="恶人·召请CD·游驹",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·张桎辕",nTime=-1,key="恶人·召请CD·张桎辕",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·月弄痕",nTime=-1,key="恶人·召请CD·月弄痕",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·司空仲平",nTime=-1,key="恶人·召请CD·司空仲平",},},},</v>
       </c>
       <c r="U11" t="s">
-        <v>2440</v>
+        <v>2442</v>
       </c>
       <c r="V11" s="6" t="s">
-        <v>2441</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="12" spans="1:33">
       <c r="C12" t="s">
-        <v>2442</v>
+        <v>2444</v>
       </c>
       <c r="D12" t="s">
-        <v>2439</v>
+        <v>2441</v>
       </c>
       <c r="K12" t="s">
         <v>1656</v>
@@ -41722,18 +41752,18 @@
         <v>{szContent="本场浩气盟攻防即将结束，南屏山物资运送暂且休整，等待下一场攻防开启！\n",szNote="本场攻防·即将结束",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=0,szName="本场攻防·结束剩余",nTime=60,nRefresh=5,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·肖药儿",nTime=-1,key="浩气·召请CD·肖药儿",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·司徒一一",nTime=-1,key="浩气·召请CD·司徒一一",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·陶寒亭",nTime=-1,key="浩气·召请CD·陶寒亭",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·白某",nTime=-1,key="浩气·召请CD·白某",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·米丽古丽",nTime=-1,key="浩气·召请CD·米丽古丽",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·小七",nTime=-1,key="恶人·召请CD·小七",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·游驹",nTime=-1,key="恶人·召请CD·游驹",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·张桎辕",nTime=-1,key="恶人·召请CD·张桎辕",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·月弄痕",nTime=-1,key="恶人·召请CD·月弄痕",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·司空仲平",nTime=-1,key="恶人·召请CD·司空仲平",},},},</v>
       </c>
       <c r="U12" t="s">
-        <v>2440</v>
+        <v>2442</v>
       </c>
       <c r="V12" s="6" t="s">
-        <v>2441</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="13" spans="1:33">
       <c r="C13" t="s">
-        <v>2443</v>
+        <v>2445</v>
       </c>
       <c r="D13" t="s">
-        <v>2444</v>
+        <v>2446</v>
       </c>
       <c r="K13" t="s">
         <v>1656</v>
@@ -41749,21 +41779,21 @@
         <v>{szContent="侠士 [{$me}] 在拾取复活点物资时意外获得了[便携装置·神机车]。",szNote="获得·便携装置·神机车",col={255,255,100,},bSearch=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=134,nFrame=0,szName="获得·[便携装置·神机车]",nTime=10,nRefresh=1,key="交互事件",},},},</v>
       </c>
       <c r="U13" t="s">
-        <v>2445</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="14" spans="1:33">
       <c r="C14" t="s">
-        <v>2446</v>
+        <v>2448</v>
       </c>
       <c r="D14" t="s">
-        <v>2447</v>
+        <v>2449</v>
       </c>
       <c r="E14" t="s">
         <v>2117</v>
       </c>
       <c r="F14" t="s">
-        <v>2448</v>
+        <v>2450</v>
       </c>
       <c r="G14" t="s">
         <v>2118</v>
@@ -41801,16 +41831,16 @@
     </row>
     <row r="15" spans="1:33">
       <c r="C15" t="s">
-        <v>2449</v>
+        <v>2451</v>
       </c>
       <c r="D15" t="s">
-        <v>2450</v>
+        <v>2452</v>
       </c>
       <c r="E15" t="s">
         <v>2116</v>
       </c>
       <c r="F15" t="s">
-        <v>2448</v>
+        <v>2450</v>
       </c>
       <c r="G15" t="s">
         <v>2119</v>
@@ -41860,40 +41890,40 @@
     </row>
     <row r="17" spans="1:26">
       <c r="C17" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
       <c r="D17" t="s">
-        <v>2400</v>
+        <v>2402</v>
       </c>
       <c r="T17" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="你已进入地图【浩气盟】。",szNote="关闭刷马等计时条",[20]={},tCountdown={{nClass=20,nIcon=13,szName="天气事件1",nTime=-2,key="天气事件1",},{nClass=20,nIcon=13,szName="天气事件2",nTime=-2,key="天气事件2",},{nClass=20,nIcon=13,nFrame=-1,szName="阵营活动",nTime=-2,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="创意食品",nTime=-1,nRefresh=5,key="创意食品",},{nClass=20,nIcon=13,szName="速战速决",nTime=-1,nRefresh=99999,key="速战速决",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},},},</v>
       </c>
       <c r="U17" t="s">
-        <v>2452</v>
+        <v>2454</v>
       </c>
       <c r="V17" t="s">
-        <v>2453</v>
+        <v>2455</v>
       </c>
       <c r="W17" t="s">
-        <v>2454</v>
+        <v>2456</v>
       </c>
       <c r="X17" t="s">
-        <v>2455</v>
+        <v>2457</v>
       </c>
       <c r="Y17" t="s">
-        <v>2456</v>
+        <v>2458</v>
       </c>
       <c r="Z17" s="3" t="s">
-        <v>2402</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:26">
       <c r="C18" t="s">
-        <v>2457</v>
+        <v>2459</v>
       </c>
       <c r="D18" t="s">
-        <v>2458</v>
+        <v>2460</v>
       </c>
       <c r="K18" t="s">
         <v>1656</v>
@@ -41906,24 +41936,24 @@
         <v>{szContent="伊夜使用了一招围魏救赵的妙计，率众客将奇袭了浩气盟大本营，浩气盟侠士也请速回救援！\n",szNote="奇袭攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=0,szName="奇袭攻防·正式开始",nTime="30,奇袭攻防·正式开始;60,建议关闭·江湖身份",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=7200,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U18" t="s">
-        <v>2459</v>
+        <v>2461</v>
       </c>
       <c r="V18" t="s">
-        <v>2460</v>
+        <v>2462</v>
       </c>
       <c r="W18" s="3" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
       <c r="X18" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="19" spans="1:26">
       <c r="C19" t="s">
-        <v>2462</v>
+        <v>2464</v>
       </c>
       <c r="D19" t="s">
-        <v>2463</v>
+        <v>2465</v>
       </c>
       <c r="K19" t="s">
         <v>1656</v>
@@ -41936,19 +41966,19 @@
         <v>{szContent="王遗风已率恶人谷众首领抵达浩气盟，请各位恶人谷侠士速到浩气盟支援。浩气盟侠士也请速回浩气盟防御！\n",szNote="主场攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2710,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5405,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·正在结算;7210,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=30,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="速战速决",nTime=-2,key="速战速决",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U19" t="s">
-        <v>2464</v>
+        <v>2466</v>
       </c>
       <c r="V19" t="s">
-        <v>2465</v>
+        <v>2467</v>
       </c>
       <c r="W19" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="X19" s="3" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
       <c r="Y19" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="20" spans="1:26">
@@ -41965,40 +41995,40 @@
     </row>
     <row r="21" spans="1:26">
       <c r="C21" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="D21" t="s">
-        <v>2400</v>
+        <v>2402</v>
       </c>
       <c r="T21" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="你已进入地图【恶人谷】。",szNote="关闭刷马等计时条",[20]={},tCountdown={{nClass=20,nIcon=13,szName="天气事件1",nTime=-2,key="天气事件1",},{nClass=20,nIcon=13,szName="天气事件2",nTime=-2,key="天气事件2",},{nClass=20,nIcon=13,nFrame=-1,szName="阵营活动",nTime=-2,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="创意食品",nTime=-1,nRefresh=5,key="创意食品",},{nClass=20,nIcon=13,szName="速战速决",nTime=-1,nRefresh=99999,key="速战速决",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},},},</v>
       </c>
       <c r="U21" t="s">
-        <v>2452</v>
+        <v>2454</v>
       </c>
       <c r="V21" t="s">
-        <v>2453</v>
+        <v>2455</v>
       </c>
       <c r="W21" t="s">
-        <v>2454</v>
+        <v>2456</v>
       </c>
       <c r="X21" t="s">
-        <v>2455</v>
+        <v>2457</v>
       </c>
       <c r="Y21" t="s">
-        <v>2456</v>
+        <v>2458</v>
       </c>
       <c r="Z21" s="3" t="s">
-        <v>2402</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:26">
       <c r="C22" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="D22" t="s">
-        <v>2458</v>
+        <v>2460</v>
       </c>
       <c r="K22" t="s">
         <v>1656</v>
@@ -42011,24 +42041,24 @@
         <v>{szContent="韩非池使用了一招围魏救赵的妙计，率众客将奇袭了恶人谷大本营，恶人谷侠士也请速回救援！\n",szNote="奇袭攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=0,szName="奇袭攻防·正式开始",nTime="30,奇袭攻防·正式开始;60,建议关闭·江湖身份",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=7200,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U22" t="s">
-        <v>2459</v>
+        <v>2461</v>
       </c>
       <c r="V22" t="s">
-        <v>2460</v>
+        <v>2462</v>
       </c>
       <c r="W22" s="3" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
       <c r="X22" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="23" spans="1:26">
       <c r="C23" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="D23" t="s">
-        <v>2463</v>
+        <v>2465</v>
       </c>
       <c r="K23" t="s">
         <v>1656</v>
@@ -42041,24 +42071,24 @@
         <v>{szContent="谢渊已率浩气盟众首领抵达恶人谷，请各位浩气盟侠士速到恶人谷支援。恶人谷侠士也请速回恶人谷防御！\n",szNote="主场攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2710,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5405,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·正在结算;7210,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=30,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="速战速决",nTime=-2,key="速战速决",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U23" t="s">
-        <v>2464</v>
+        <v>2466</v>
       </c>
       <c r="V23" t="s">
-        <v>2465</v>
+        <v>2467</v>
       </c>
       <c r="W23" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
       <c r="Y23" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="24" customFormat="1" spans="1:26">
       <c r="A24" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="B24">
         <v>-1</v>
@@ -42070,10 +42100,10 @@
     </row>
     <row r="25" customFormat="1" spans="1:26">
       <c r="C25" t="s">
-        <v>2471</v>
+        <v>2473</v>
       </c>
       <c r="D25" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="K25" t="s">
         <v>1656</v>
@@ -42086,12 +42116,12 @@
         <v>{szContent="(.-)【(.-)】帮会的(.-)大侠成功护送祭祀物资到达(.-)据点，该据点将士备受鼓舞，战意高昂，战时必将固若金汤！",szNote="祭天·{$1}·[{$2}]·{$4}",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=8838,nFrame=1,szName="{$1}祭天·[{$2}]·{$4}",nTime=30,key="通用事件",},},},</v>
       </c>
       <c r="U25" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="26" spans="1:26">
       <c r="C26" t="s">
-        <v>2474</v>
+        <v>2476</v>
       </c>
       <c r="K26" t="s">
         <v>1656</v>
@@ -42101,12 +42131,12 @@
         <v>{szContent="为保障各位侠士的安全，浩气盟和恶人谷重新派出了守卫，在野外地图侠士重伤后复活可回到阵营复活点！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="据点攻防·消失模式",nTime=1799.795,key="阵营活动",},},},</v>
       </c>
       <c r="U26" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="27" spans="1:26">
       <c r="C27" t="s">
-        <v>2476</v>
+        <v>2478</v>
       </c>
       <c r="K27" t="s">
         <v>1656</v>
@@ -42116,12 +42146,12 @@
         <v>{szContent="据点争夺战即将开始，为防弄虚作假者，即将对据点活动地图进行清场操作，同时清空此前所有排队队列，请各阵营侠士做好准备。拥有据点地图优先进入权的帮众可提前进入地图以作防守准备，不会被清出地图。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=-1,szName="阵营活动",nTime="1,据点攻防·开始排队;10,据点攻防·开始排队;60,据点攻防·等待排队",nRefresh=1,key="阵营活动",},},},</v>
       </c>
       <c r="U27" t="s">
-        <v>2477</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="28" spans="1:26">
       <c r="C28" t="s">
-        <v>2478</v>
+        <v>2480</v>
       </c>
       <c r="K28" t="s">
         <v>2121</v>
@@ -42131,12 +42161,12 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“恶人谷”地图进行清场操作，并在“下午六点三十分”开始攻防排队，请勿在下午六点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·恶人谷·18:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U28" t="s">
-        <v>2479</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="29" spans="1:26">
       <c r="C29" t="s">
-        <v>2480</v>
+        <v>2482</v>
       </c>
       <c r="K29" t="s">
         <v>2121</v>
@@ -42146,12 +42176,12 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“恶人谷”地图进行清场操作，并在“中午十二点三十分”开始攻防排队，请勿在中午十二点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·恶人谷·12:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U29" t="s">
-        <v>2481</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="30" spans="1:26">
       <c r="C30" t="s">
-        <v>2482</v>
+        <v>2484</v>
       </c>
       <c r="K30" t="s">
         <v>2120</v>
@@ -42161,12 +42191,12 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“浩气盟”地图进行清场操作，并在“下午六点三十分”开始攻防排队，请勿在下午六点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·浩气盟·18:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U30" t="s">
-        <v>2483</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="31" spans="1:26">
       <c r="C31" t="s">
-        <v>2484</v>
+        <v>2486</v>
       </c>
       <c r="K31" t="s">
         <v>2120</v>
@@ -42176,12 +42206,12 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“浩气盟”地图进行清场操作，并在“中午十二点三十分”开始攻防排队，请勿在中午十二点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·浩气盟·12:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U31" t="s">
-        <v>2485</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="32" spans="1:26">
       <c r="C32" t="s">
-        <v>2486</v>
+        <v>2488</v>
       </c>
       <c r="K32" t="s">
         <v>2121</v>
@@ -42191,18 +42221,18 @@
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往恶人谷地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=-1,szName="阵营攻防·开始排队",nTime="1,阵营攻防·开始排队;10,阵营攻防·开始排队",nRefresh=1,key="阵营活动",},{nClass=20,nIcon=14889,nFrame=3,szName="主战场·恶人谷",nTime=60,key="大攻防·主战场",},{nClass=20,nIcon=14890,nFrame=7,szName="奇袭场·浩气盟",nTime=60,key="大攻防·奇袭场",},},},</v>
       </c>
       <c r="U32" t="s">
-        <v>2487</v>
+        <v>2489</v>
       </c>
       <c r="V32" t="s">
-        <v>2488</v>
+        <v>2490</v>
       </c>
       <c r="W32" t="s">
-        <v>2489</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="33" spans="1:26">
       <c r="C33" t="s">
-        <v>2490</v>
+        <v>2492</v>
       </c>
       <c r="K33" t="s">
         <v>2120</v>
@@ -42212,13 +42242,13 @@
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往浩气盟地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=-1,szName="阵营攻防·开始排队",nTime="1,阵营攻防·开始排队;10,阵营攻防·开始排队",nRefresh=1,key="阵营活动",},{nClass=20,nIcon=14890,nFrame=7,szName="主战场·浩气盟",nTime=60,key="大攻防·主战场",},{nClass=20,nIcon=14889,nFrame=3,szName="奇袭场·恶人谷",nTime=60,key="大攻防·奇袭场",},},},</v>
       </c>
       <c r="U33" t="s">
-        <v>2487</v>
+        <v>2489</v>
       </c>
       <c r="V33" t="s">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="W33" t="s">
-        <v>2492</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="34" spans="1:26">
@@ -42235,10 +42265,10 @@
     </row>
     <row r="35" customFormat="1" spans="1:26">
       <c r="C35" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
       <c r="D35" t="s">
-        <v>2494</v>
+        <v>2496</v>
       </c>
       <c r="K35" t="s">
         <v>1656</v>
@@ -42251,15 +42281,15 @@
         <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U35" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="1:26">
       <c r="C36" t="s">
-        <v>2496</v>
+        <v>2498</v>
       </c>
       <c r="D36" t="s">
-        <v>2497</v>
+        <v>2499</v>
       </c>
       <c r="K36" t="s">
         <v>1656</v>
@@ -42272,27 +42302,27 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U36" t="s">
-        <v>2498</v>
+        <v>2500</v>
       </c>
       <c r="V36" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="W36" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="X36" t="s">
-        <v>2501</v>
+        <v>2503</v>
       </c>
       <c r="Y36" t="s">
-        <v>2502</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="1:26">
       <c r="C37" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="D37" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="K37" t="s">
         <v>1656</v>
@@ -42305,30 +42335,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U37" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="V37" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="W37" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="X37" t="s">
-        <v>2508</v>
+        <v>2510</v>
       </c>
       <c r="Y37" t="s">
-        <v>2509</v>
+        <v>2511</v>
       </c>
       <c r="Z37" t="s">
-        <v>2510</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="1:26">
       <c r="C38" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="D38" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
       <c r="K38" t="s">
         <v>2121</v>
@@ -42338,15 +42368,15 @@
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U38" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="39" customFormat="1" spans="1:26">
       <c r="C39" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="D39" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="K39" t="s">
         <v>2120</v>
@@ -42356,15 +42386,15 @@
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U39" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="40" customFormat="1" spans="1:26">
       <c r="C40" t="s">
-        <v>2511</v>
+        <v>2513</v>
       </c>
       <c r="D40" t="s">
-        <v>2512</v>
+        <v>2514</v>
       </c>
       <c r="K40" t="s">
         <v>1656</v>
@@ -42377,15 +42407,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U40" t="s">
-        <v>2513</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:26">
       <c r="C41" t="s">
-        <v>2514</v>
+        <v>2516</v>
       </c>
       <c r="D41" t="s">
-        <v>2515</v>
+        <v>2517</v>
       </c>
       <c r="K41" t="s">
         <v>1656</v>
@@ -42395,16 +42425,16 @@
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U41" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="V41" s="7"/>
     </row>
     <row r="42" customFormat="1" spans="1:26">
       <c r="C42" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="D42" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
       <c r="K42" t="s">
         <v>1656</v>
@@ -42414,16 +42444,16 @@
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U42" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="V42" s="7"/>
     </row>
     <row r="43" customFormat="1" spans="1:26">
       <c r="C43" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="D43" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="K43" t="s">
         <v>1656</v>
@@ -42433,18 +42463,18 @@
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U43" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="V43" s="6" t="s">
-        <v>2520</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="44" spans="1:26">
       <c r="C44" t="s">
-        <v>2521</v>
+        <v>2523</v>
       </c>
       <c r="D44" t="s">
-        <v>2522</v>
+        <v>2524</v>
       </c>
       <c r="K44" t="s">
         <v>1656</v>
@@ -42454,18 +42484,18 @@
         <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",szNote="据点攻防·阴山大草原·分线·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U44" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="V44" t="s">
-        <v>2524</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="45" spans="1:26">
       <c r="C45" t="s">
-        <v>2525</v>
+        <v>2527</v>
       </c>
       <c r="D45" t="s">
-        <v>2526</v>
+        <v>2528</v>
       </c>
       <c r="K45" t="s">
         <v>1656</v>
@@ -42475,15 +42505,15 @@
         <v>{szContent="前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n",szNote="据点攻防·阴山大草原",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U45" t="s">
-        <v>2527</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="46" spans="1:26">
       <c r="C46" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="D46" t="s">
-        <v>2529</v>
+        <v>2531</v>
       </c>
       <c r="K46" t="s">
         <v>1656</v>
@@ -42493,18 +42523,18 @@
         <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·阴山大草原·开启分线·5分钟",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U46" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="V46" t="s">
-        <v>2530</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="47" spans="1:26">
       <c r="C47" t="s">
-        <v>2531</v>
+        <v>2533</v>
       </c>
       <c r="D47" t="s">
-        <v>2532</v>
+        <v>2534</v>
       </c>
       <c r="K47" t="s">
         <v>1656</v>
@@ -42514,15 +42544,15 @@
         <v>{szContent="阵营攻防首领战紧张火热，本服今日无奇袭场分线模式，请侠士速速前往主战场及奇袭场参与活动。\n",szNote="阵营攻防·奇袭场·未开分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·未开分线",nTime=30,key="分流活动",},},},</v>
       </c>
       <c r="U47" t="s">
-        <v>2533</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="48" spans="1:26">
       <c r="C48" t="s">
-        <v>2534</v>
+        <v>2536</v>
       </c>
       <c r="D48" t="s">
-        <v>2535</v>
+        <v>2537</v>
       </c>
       <c r="K48" t="s">
         <v>1656</v>
@@ -42532,7 +42562,7 @@
         <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",szNote="阵营攻防·奇袭场·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·开启分线",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
       <c r="U48" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" spans="1:26">
@@ -42549,10 +42579,10 @@
     </row>
     <row r="50" customFormat="1" spans="1:26">
       <c r="C50" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
       <c r="D50" t="s">
-        <v>2494</v>
+        <v>2496</v>
       </c>
       <c r="K50" t="s">
         <v>1656</v>
@@ -42568,15 +42598,15 @@
         <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U50" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="51" spans="1:26">
       <c r="C51" t="s">
-        <v>2496</v>
+        <v>2498</v>
       </c>
       <c r="D51" t="s">
-        <v>2497</v>
+        <v>2499</v>
       </c>
       <c r="K51" t="s">
         <v>1656</v>
@@ -42589,27 +42619,27 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,key="{$3}·恶人大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气占领",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人占领",},{nClass=20,nIcon=13,szName="{$3}·{$1}占领",nTime=-1,key="{$3}·{$1}占领",},},},</v>
       </c>
       <c r="U51" t="s">
-        <v>2537</v>
+        <v>2539</v>
       </c>
       <c r="V51" t="s">
-        <v>2538</v>
+        <v>2540</v>
       </c>
       <c r="W51" t="s">
-        <v>2539</v>
+        <v>2541</v>
       </c>
       <c r="X51" t="s">
-        <v>2540</v>
+        <v>2542</v>
       </c>
       <c r="Y51" t="s">
-        <v>2541</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="52" customFormat="1" spans="1:26">
       <c r="C52" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="D52" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="K52" t="s">
         <v>1656</v>
@@ -42622,30 +42652,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U52" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="V52" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="W52" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="X52" t="s">
-        <v>2508</v>
+        <v>2510</v>
       </c>
       <c r="Y52" t="s">
-        <v>2509</v>
+        <v>2511</v>
       </c>
       <c r="Z52" t="s">
-        <v>2510</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:26">
       <c r="C53" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="D53" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
       <c r="K53" t="s">
         <v>2121</v>
@@ -42655,15 +42685,15 @@
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U53" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:26">
       <c r="C54" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="D54" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="K54" t="s">
         <v>2120</v>
@@ -42673,12 +42703,12 @@
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U54" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="55" spans="1:26">
       <c r="C55" t="s">
-        <v>2542</v>
+        <v>2544</v>
       </c>
       <c r="K55" t="s">
         <v>1656</v>
@@ -42688,15 +42718,15 @@
         <v>{szContent="本场贡献值进入前1200名，额外获得3000威名，可通过邮件领取\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=6,szName="攻防进入前1200名",nTime=10,key="阵营活动",},},},</v>
       </c>
       <c r="U55" t="s">
-        <v>2543</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:26">
       <c r="C56" t="s">
-        <v>2514</v>
+        <v>2516</v>
       </c>
       <c r="D56" t="s">
-        <v>2515</v>
+        <v>2517</v>
       </c>
       <c r="K56" t="s">
         <v>1656</v>
@@ -42706,21 +42736,21 @@
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=20,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=20,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=20,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=20,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=20,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=20,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=20,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=20,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=20,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="U56" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="V56" s="5" t="s">
-        <v>2436</v>
+        <v>2438</v>
       </c>
       <c r="W56" s="5" t="s">
-        <v>2437</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="57" customFormat="1" spans="1:26">
       <c r="C57" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="D57" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
       <c r="K57" t="s">
         <v>1656</v>
@@ -42730,16 +42760,16 @@
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U57" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="V57" s="7"/>
     </row>
     <row r="58" customFormat="1" spans="1:26">
       <c r="C58" t="s">
-        <v>2511</v>
+        <v>2513</v>
       </c>
       <c r="D58" t="s">
-        <v>2512</v>
+        <v>2514</v>
       </c>
       <c r="K58" t="s">
         <v>1656</v>
@@ -42752,15 +42782,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U58" t="s">
-        <v>2513</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="59" spans="1:26">
       <c r="C59" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="D59" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="K59" t="s">
         <v>1656</v>
@@ -42770,24 +42800,24 @@
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=13,szName="狼牙先锋首领",nTime=0,key="狼牙先锋首领",},{nClass=20,nIcon=13,szName="离开据点·大旗重置",nTime=0,key="离开据点·大旗重置",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U59" t="s">
-        <v>2544</v>
+        <v>2546</v>
       </c>
       <c r="V59" t="s">
-        <v>2545</v>
+        <v>2547</v>
       </c>
       <c r="W59" t="s">
-        <v>2546</v>
+        <v>2548</v>
       </c>
       <c r="X59" s="6" t="s">
-        <v>2520</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="60" spans="1:26">
       <c r="C60" t="s">
-        <v>2521</v>
+        <v>2523</v>
       </c>
       <c r="D60" t="s">
-        <v>2522</v>
+        <v>2524</v>
       </c>
       <c r="K60" t="s">
         <v>1656</v>
@@ -42797,18 +42827,18 @@
         <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",szNote="据点攻防·阴山大草原·分线·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U60" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="V60" t="s">
-        <v>2524</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="61" spans="1:26">
       <c r="C61" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="D61" t="s">
-        <v>2529</v>
+        <v>2531</v>
       </c>
       <c r="K61" t="s">
         <v>1656</v>
@@ -42818,18 +42848,18 @@
         <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·阴山大草原·开启分线·5分钟",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U61" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="V61" t="s">
-        <v>2530</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="62" spans="1:26">
       <c r="C62" t="s">
-        <v>2547</v>
+        <v>2549</v>
       </c>
       <c r="D62" t="s">
-        <v>2284</v>
+        <v>2286</v>
       </c>
       <c r="K62" t="s">
         <v>1656</v>
@@ -42839,15 +42869,15 @@
         <v>{szContent="前线据点之争已经打响，争夺正式开始，沙盘地图（CTRL + M）绘有详细战略意图，谁将称霸中原，我们拭目以待！\n",szNote="据点攻防·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime=10,key="阵营活动",},},},</v>
       </c>
       <c r="U62" t="s">
-        <v>2548</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:26">
       <c r="C63" t="s">
-        <v>2531</v>
+        <v>2533</v>
       </c>
       <c r="D63" t="s">
-        <v>2532</v>
+        <v>2534</v>
       </c>
       <c r="K63" t="s">
         <v>1656</v>
@@ -42857,15 +42887,15 @@
         <v>{szContent="阵营攻防首领战紧张火热，本服今日无奇袭场分线模式，请侠士速速前往主战场及奇袭场参与活动。\n",szNote="阵营攻防·奇袭场·未开分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·未开分线",nTime=30,key="分流活动",},},},</v>
       </c>
       <c r="U63" t="s">
-        <v>2533</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:26">
       <c r="C64" t="s">
-        <v>2534</v>
+        <v>2536</v>
       </c>
       <c r="D64" t="s">
-        <v>2535</v>
+        <v>2537</v>
       </c>
       <c r="K64" t="s">
         <v>1656</v>
@@ -42875,7 +42905,7 @@
         <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",szNote="阵营攻防·奇袭场·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·开启分线",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
       <c r="U64" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:26">
@@ -42892,10 +42922,10 @@
     </row>
     <row r="66" customFormat="1" spans="1:26">
       <c r="C66" t="s">
-        <v>2549</v>
+        <v>2551</v>
       </c>
       <c r="D66" t="s">
-        <v>2550</v>
+        <v>2552</v>
       </c>
       <c r="K66" t="s">
         <v>1656</v>
@@ -42908,19 +42938,19 @@
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U66" t="s">
-        <v>2551</v>
+        <v>2553</v>
       </c>
       <c r="V66" t="s">
-        <v>2552</v>
+        <v>2554</v>
       </c>
       <c r="W66" t="s">
-        <v>2553</v>
+        <v>2555</v>
       </c>
       <c r="X66" t="s">
-        <v>2554</v>
+        <v>2556</v>
       </c>
       <c r="Y66" t="s">
-        <v>2555</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:26">
@@ -42937,10 +42967,10 @@
     </row>
     <row r="68" customFormat="1" spans="1:26">
       <c r="C68" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
       <c r="D68" t="s">
-        <v>2494</v>
+        <v>2496</v>
       </c>
       <c r="K68" t="s">
         <v>1656</v>
@@ -42953,15 +42983,15 @@
         <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U68" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:26">
       <c r="C69" t="s">
-        <v>2496</v>
+        <v>2498</v>
       </c>
       <c r="D69" t="s">
-        <v>2497</v>
+        <v>2499</v>
       </c>
       <c r="K69" t="s">
         <v>1656</v>
@@ -42974,27 +43004,27 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U69" t="s">
-        <v>2498</v>
+        <v>2500</v>
       </c>
       <c r="V69" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="W69" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="X69" t="s">
-        <v>2501</v>
+        <v>2503</v>
       </c>
       <c r="Y69" t="s">
-        <v>2502</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="70" customFormat="1" spans="1:26">
       <c r="C70" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="D70" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="K70" t="s">
         <v>1656</v>
@@ -43007,30 +43037,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U70" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="V70" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="W70" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="X70" t="s">
-        <v>2508</v>
+        <v>2510</v>
       </c>
       <c r="Y70" t="s">
-        <v>2509</v>
+        <v>2511</v>
       </c>
       <c r="Z70" t="s">
-        <v>2510</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="71" customFormat="1" spans="1:26">
       <c r="C71" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="D71" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
       <c r="K71" t="s">
         <v>2121</v>
@@ -43040,15 +43070,15 @@
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U71" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="72" customFormat="1" spans="1:26">
       <c r="C72" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="D72" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="K72" t="s">
         <v>2120</v>
@@ -43058,15 +43088,15 @@
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U72" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="73" customFormat="1" spans="1:26">
       <c r="C73" t="s">
-        <v>2514</v>
+        <v>2516</v>
       </c>
       <c r="D73" t="s">
-        <v>2515</v>
+        <v>2517</v>
       </c>
       <c r="K73" t="s">
         <v>1656</v>
@@ -43076,16 +43106,16 @@
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U73" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="V73" s="7"/>
     </row>
     <row r="74" customFormat="1" spans="1:26">
       <c r="C74" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="D74" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
       <c r="K74" t="s">
         <v>1656</v>
@@ -43095,16 +43125,16 @@
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U74" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="V74" s="7"/>
     </row>
     <row r="75" customFormat="1" spans="1:26">
       <c r="C75" t="s">
-        <v>2511</v>
+        <v>2513</v>
       </c>
       <c r="D75" t="s">
-        <v>2512</v>
+        <v>2514</v>
       </c>
       <c r="K75" t="s">
         <v>1656</v>
@@ -43117,15 +43147,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U75" t="s">
-        <v>2513</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="76" customFormat="1" spans="1:26">
       <c r="C76" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="D76" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="K76" t="s">
         <v>1656</v>
@@ -43135,18 +43165,18 @@
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U76" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="V76" s="6" t="s">
-        <v>2520</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="77" customFormat="1" spans="1:26">
       <c r="C77" t="s">
-        <v>2521</v>
+        <v>2523</v>
       </c>
       <c r="D77" t="s">
-        <v>2522</v>
+        <v>2524</v>
       </c>
       <c r="K77" t="s">
         <v>1656</v>
@@ -43156,18 +43186,18 @@
         <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",szNote="据点攻防·阴山大草原·分线·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U77" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="V77" t="s">
-        <v>2524</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="78" customFormat="1" spans="1:26">
       <c r="C78" t="s">
-        <v>2525</v>
+        <v>2527</v>
       </c>
       <c r="D78" t="s">
-        <v>2526</v>
+        <v>2528</v>
       </c>
       <c r="K78" t="s">
         <v>1656</v>
@@ -43177,15 +43207,15 @@
         <v>{szContent="前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n",szNote="据点攻防·阴山大草原",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U78" t="s">
-        <v>2527</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="79" customFormat="1" spans="1:26">
       <c r="C79" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="D79" t="s">
-        <v>2529</v>
+        <v>2531</v>
       </c>
       <c r="K79" t="s">
         <v>1656</v>
@@ -43195,18 +43225,18 @@
         <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·阴山大草原·开启分线·5分钟",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U79" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="V79" t="s">
-        <v>2530</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="80" customFormat="1" spans="1:26">
       <c r="C80" t="s">
-        <v>2531</v>
+        <v>2533</v>
       </c>
       <c r="D80" t="s">
-        <v>2532</v>
+        <v>2534</v>
       </c>
       <c r="K80" t="s">
         <v>1656</v>
@@ -43216,15 +43246,15 @@
         <v>{szContent="阵营攻防首领战紧张火热，本服今日无奇袭场分线模式，请侠士速速前往主战场及奇袭场参与活动。\n",szNote="阵营攻防·奇袭场·未开分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·未开分线",nTime=30,key="分流活动",},},},</v>
       </c>
       <c r="U80" t="s">
-        <v>2533</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="81" customFormat="1" spans="1:26">
       <c r="C81" t="s">
-        <v>2534</v>
+        <v>2536</v>
       </c>
       <c r="D81" t="s">
-        <v>2535</v>
+        <v>2537</v>
       </c>
       <c r="K81" t="s">
         <v>1656</v>
@@ -43234,12 +43264,12 @@
         <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",szNote="阵营攻防·奇袭场·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·开启分线",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
       <c r="U81" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="82" customFormat="1" spans="1:26">
       <c r="A82" t="s">
-        <v>2556</v>
+        <v>2558</v>
       </c>
       <c r="B82">
         <v>-3</v>
@@ -43251,32 +43281,32 @@
     </row>
     <row r="83" customFormat="1" spans="1:26">
       <c r="C83" t="s">
-        <v>2486</v>
+        <v>2488</v>
       </c>
       <c r="K83" t="s">
         <v>2121</v>
       </c>
       <c r="T83" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往恶人谷地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=3,szName="主战场·恶人谷",nTime="1,阵营攻防·开始排队·恶人谷;10,阵营攻防·开始排队·恶人谷",key="大攻防·主战场",},},},</v>
+        <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往恶人谷地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=3,szName="主战场·恶人谷",nTime="1,阵营攻防·开始排队·恶人谷;10,阵营攻防·开始排队·恶人谷",nRefresh=1,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U83" t="s">
-        <v>2557</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="1:26">
       <c r="C84" t="s">
-        <v>2490</v>
+        <v>2492</v>
       </c>
       <c r="K84" t="s">
         <v>2120</v>
       </c>
       <c r="T84" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往浩气盟地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=7,szName="主战场·浩气盟",nTime="1,阵营攻防·开始排队·浩气盟;10,阵营攻防·开始排队·浩气盟",key="大攻防·主战场",},},},</v>
+        <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往浩气盟地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=7,szName="主战场·浩气盟",nTime="1,阵营攻防·开始排队·浩气盟;10,阵营攻防·开始排队·浩气盟",nRefresh=1,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U84" t="s">
-        <v>2558</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="85" customFormat="1" spans="1:26">
@@ -43293,10 +43323,10 @@
     </row>
     <row r="86" customFormat="1" spans="1:26">
       <c r="C86" t="s">
-        <v>2559</v>
+        <v>2561</v>
       </c>
       <c r="D86" t="s">
-        <v>2560</v>
+        <v>2562</v>
       </c>
       <c r="K86" t="s">
         <v>1656</v>
@@ -43306,15 +43336,15 @@
         <v>{szContent="本场攻防“奇袭场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="奇袭场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2402,nFrame=4,szName="奇袭场·平手",nTime=57,nRefresh=5,key="大攻防·奇袭场",},},},</v>
       </c>
       <c r="U86" t="s">
-        <v>2561</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="87" customFormat="1" spans="1:26">
       <c r="C87" t="s">
-        <v>2562</v>
+        <v>2564</v>
       </c>
       <c r="D87" t="s">
-        <v>2563</v>
+        <v>2565</v>
       </c>
       <c r="K87" t="s">
         <v>1656</v>
@@ -43324,15 +43354,15 @@
         <v>{szContent="本场攻防“主战场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="主战场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="主战场·平手",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U87" t="s">
-        <v>2564</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="88" customFormat="1" spans="1:26">
       <c r="C88" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
       <c r="D88" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
       <c r="K88" t="s">
         <v>1656</v>
@@ -43348,27 +43378,27 @@
         <v>{szContent="^本场攻防“([主战奇袭场]+)”已结束，([浩气盟恶人谷]+)[侠士们众志成城和，]-([大完险胜]+)([浩气盟恶人谷]+)[！，]+",szNote="{$1}·{$2}·{$3}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,szName="大攻防·奇袭场",nTime=-2,nRefresh=10,key="大攻防·奇袭场",},{nClass=20,nIcon=13,szName="大攻防·主战场",nTime=-2,nRefresh=10,key="大攻防·主战场",},{nClass=20,nIcon=13,szName="大攻防·{$1}",nTime=-2,key="大攻防·{$1}",},{nClass=20,nIcon=2402,nFrame=4,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U88" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="V88" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="W88" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="X88" t="s">
-        <v>2565</v>
+        <v>2567</v>
       </c>
       <c r="Y88" t="s">
-        <v>2566</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="89" customFormat="1" spans="1:26">
       <c r="C89" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
       <c r="D89" t="s">
-        <v>2494</v>
+        <v>2496</v>
       </c>
       <c r="K89" t="s">
         <v>1656</v>
@@ -43384,15 +43414,15 @@
         <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U89" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="90" customFormat="1" spans="1:26">
       <c r="C90" t="s">
-        <v>2496</v>
+        <v>2498</v>
       </c>
       <c r="D90" t="s">
-        <v>2497</v>
+        <v>2499</v>
       </c>
       <c r="K90" t="s">
         <v>1656</v>
@@ -43405,27 +43435,27 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U90" t="s">
-        <v>2498</v>
+        <v>2500</v>
       </c>
       <c r="V90" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="W90" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="X90" t="s">
-        <v>2501</v>
+        <v>2503</v>
       </c>
       <c r="Y90" t="s">
-        <v>2502</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="91" customFormat="1" spans="1:26">
       <c r="C91" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="D91" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="K91" t="s">
         <v>1656</v>
@@ -43438,30 +43468,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U91" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="V91" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="W91" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="X91" t="s">
-        <v>2508</v>
+        <v>2510</v>
       </c>
       <c r="Y91" t="s">
-        <v>2509</v>
+        <v>2511</v>
       </c>
       <c r="Z91" t="s">
-        <v>2510</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="92" customFormat="1" spans="1:26">
       <c r="C92" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="D92" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
       <c r="K92" t="s">
         <v>2121</v>
@@ -43471,15 +43501,15 @@
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U92" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="93" customFormat="1" spans="1:26">
       <c r="C93" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="D93" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="K93" t="s">
         <v>2120</v>
@@ -43489,15 +43519,15 @@
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U93" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="1:26">
       <c r="C94" t="s">
-        <v>2511</v>
+        <v>2513</v>
       </c>
       <c r="D94" t="s">
-        <v>2512</v>
+        <v>2514</v>
       </c>
       <c r="K94" t="s">
         <v>1656</v>
@@ -43510,15 +43540,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U94" t="s">
-        <v>2513</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="95" customFormat="1" spans="1:26">
       <c r="C95" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="D95" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="K95" t="s">
         <v>1656</v>
@@ -43528,18 +43558,18 @@
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U95" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="V95" s="6" t="s">
-        <v>2520</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="96" customFormat="1" spans="1:26">
       <c r="C96" t="s">
-        <v>2514</v>
+        <v>2516</v>
       </c>
       <c r="D96" t="s">
-        <v>2515</v>
+        <v>2517</v>
       </c>
       <c r="K96" t="s">
         <v>1656</v>
@@ -43549,16 +43579,16 @@
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U96" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="V96" s="7"/>
     </row>
     <row r="97" customFormat="1" spans="1:34">
       <c r="C97" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="D97" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
       <c r="K97" t="s">
         <v>1656</v>
@@ -43568,7 +43598,7 @@
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U97" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="V97" s="7"/>
     </row>
@@ -43586,13 +43616,13 @@
     </row>
     <row r="99" customFormat="1" spans="1:34">
       <c r="C99" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="D99" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="G99" t="s">
-        <v>2567</v>
+        <v>2569</v>
       </c>
       <c r="K99" t="s">
         <v>1656</v>
@@ -43605,7 +43635,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【武王城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="武王城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【武王城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="武王城·恶人大旗",},},},</v>
       </c>
       <c r="U99" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="V99" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G99&amp;"·浩气大旗"&amp;""",},"</f>
@@ -43616,19 +43646,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·恶人大旗",},</v>
       </c>
       <c r="X99" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="Y99" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="Z99" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="AA99" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="AB99" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
       <c r="AC99" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G99&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G99&amp;"·浩气大旗"""&amp;",},"</f>
@@ -43641,10 +43671,10 @@
     </row>
     <row r="100" customFormat="1" spans="1:34">
       <c r="C100" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="D100" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="K100" t="s">
         <v>1656</v>
@@ -43657,21 +43687,21 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="武王城·大旗重置",nTime=-2,nRefresh=7200,key="武王城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【武王城】大旗重置",nTime="180,【武王城】大旗重置;185,【武王城】大旗重置·结束",nRefresh=7200,key="武王城·大旗重置",},},},</v>
       </c>
       <c r="U100" t="s">
-        <v>2573</v>
+        <v>2575</v>
       </c>
       <c r="V100" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="W100" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="X100" t="s">
-        <v>2576</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="101" customFormat="1" spans="1:34">
       <c r="C101" t="s">
-        <v>2442</v>
+        <v>2444</v>
       </c>
       <c r="K101" t="s">
         <v>1656</v>
@@ -43681,18 +43711,18 @@
         <v>{szContent="本场浩气盟攻防即将结束，南屏山物资运送暂且休整，等待下一场攻防开启！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="粮草先行·活动结束",nTime=5,key="粮草先行·浩气盟",},{nClass=20,nIcon=13,szName="粮草先行·恶人谷",nTime=0,key="粮草先行·恶人谷",},{nClass=20,nIcon=589,nFrame=7,szName="赵新宇",nTime="60,赵新宇·刷新剩余;62,赵新宇·即将刷新",nRefresh=0,key="赵新宇",},},},</v>
       </c>
       <c r="U101" t="s">
-        <v>2577</v>
+        <v>2579</v>
       </c>
       <c r="V101" t="s">
-        <v>2578</v>
+        <v>2580</v>
       </c>
       <c r="W101" t="s">
-        <v>2579</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="102" customFormat="1" spans="1:34">
       <c r="C102" t="s">
-        <v>2580</v>
+        <v>2582</v>
       </c>
       <c r="K102" t="s">
         <v>2121</v>
@@ -43702,12 +43732,12 @@
         <v>{szContent="南屏山恶人谷伴江村援军已到，营地夺回，交通恢复！\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=10,nRefresh=600,key="赵新宇",},},},</v>
       </c>
       <c r="U102" t="s">
-        <v>2581</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="103" customFormat="1" spans="1:34">
       <c r="C103" t="s">
-        <v>2582</v>
+        <v>2584</v>
       </c>
       <c r="K103" t="s">
         <v>2120</v>
@@ -43717,7 +43747,7 @@
         <v>{szContent="南屏山浩气盟望北村援军已到，营地夺回，交通恢复！\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=10,nRefresh=600,key="方超",},},},</v>
       </c>
       <c r="U103" t="s">
-        <v>2583</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="104" spans="1:34">
@@ -43734,13 +43764,13 @@
     </row>
     <row r="105" customFormat="1" spans="1:34">
       <c r="C105" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="D105" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="G105" t="s">
-        <v>2584</v>
+        <v>2586</v>
       </c>
       <c r="K105" t="s">
         <v>1656</v>
@@ -43753,7 +43783,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凛风堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凛风堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·恶人大旗",},},},</v>
       </c>
       <c r="U105" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="V105" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G105&amp;"·浩气大旗"&amp;""",},"</f>
@@ -43764,19 +43794,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·恶人大旗",},</v>
       </c>
       <c r="X105" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="Y105" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="Z105" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="AA105" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="AB105" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
       <c r="AC105" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G105&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G105&amp;"·浩气大旗"""&amp;",},"</f>
@@ -43789,10 +43819,10 @@
     </row>
     <row r="106" spans="1:34">
       <c r="C106" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="D106" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="K106" t="s">
         <v>1656</v>
@@ -43805,21 +43835,21 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凛风堡·大旗重置",nTime=-2,nRefresh=7200,key="凛风堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凛风堡】大旗重置",nTime="180,【凛风堡】大旗重置;185,【凛风堡】大旗重置·结束",nRefresh=7200,key="凛风堡·大旗重置",},},},</v>
       </c>
       <c r="U106" t="s">
-        <v>2585</v>
+        <v>2587</v>
       </c>
       <c r="V106" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="W106" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="X106" t="s">
-        <v>2586</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="107" spans="1:34">
       <c r="C107" t="s">
-        <v>2438</v>
+        <v>2440</v>
       </c>
       <c r="K107" t="s">
         <v>1656</v>
@@ -43829,21 +43859,21 @@
         <v>{szContent="本场恶人谷攻防即将结束，昆仑物资运送暂且休整，等待下一场攻防开启！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="粮草先行·活动结束",nTime=5,key="粮草先行·恶人谷",},{nClass=20,nIcon=13,szName="粮草先行·浩气盟",nTime=0,key="粮草先行·浩气盟",},{nClass=20,nIcon=2864,nFrame=7,szName="霸图",nTime="60,霸图·刷新剩余;62,霸图·即将刷新",nRefresh=0,key="霸图",},{nClass=20,nIcon=845,nFrame=3,szName="孙永恒",nTime="60,孙永恒·刷新剩余;62,孙永恒·即将刷新",nRefresh=0,key="孙永恒",},},},</v>
       </c>
       <c r="U107" t="s">
-        <v>2587</v>
+        <v>2589</v>
       </c>
       <c r="V107" t="s">
-        <v>2588</v>
+        <v>2590</v>
       </c>
       <c r="W107" t="s">
-        <v>2589</v>
+        <v>2591</v>
       </c>
       <c r="X107" t="s">
-        <v>2590</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="108" spans="1:34">
       <c r="C108" t="s">
-        <v>2591</v>
+        <v>2593</v>
       </c>
       <c r="K108" t="s">
         <v>2121</v>
@@ -43853,12 +43883,12 @@
         <v>{szContent="昆仑山恶人谷西昆仑高地援军已到，营地夺回，交通恢复！\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=10,nRefresh=600,key="霸图",},},},</v>
       </c>
       <c r="U108" t="s">
-        <v>2592</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="109" spans="1:34">
       <c r="C109" t="s">
-        <v>2593</v>
+        <v>2595</v>
       </c>
       <c r="K109" t="s">
         <v>2120</v>
@@ -43868,7 +43898,7 @@
         <v>{szContent="昆仑山浩气盟东昆仑高地援军已到，营地夺回，交通恢复！\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=10,nRefresh=600,key="孙永恒",},},},</v>
       </c>
       <c r="U109" t="s">
-        <v>2594</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="110" spans="1:34">
@@ -43885,16 +43915,16 @@
     </row>
     <row r="111" customFormat="1" spans="1:34">
       <c r="C111" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="D111" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="G111" t="s">
-        <v>2595</v>
+        <v>2597</v>
       </c>
       <c r="H111" t="s">
-        <v>2596</v>
+        <v>2598</v>
       </c>
       <c r="K111" t="s">
         <v>1656</v>
@@ -43907,7 +43937,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【盘龙坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【逐鹿坪】恶人·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【盘龙坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【逐鹿坪】浩气·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·恶人大旗",},},},</v>
       </c>
       <c r="U111" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="V111" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G111&amp;"·浩气大旗"&amp;""",},"</f>
@@ -43926,19 +43956,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·恶人大旗",},</v>
       </c>
       <c r="Z111" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="AA111" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="AB111" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="AC111" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="AD111" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
       <c r="AE111" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G111&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G111&amp;"·浩气大旗"""&amp;",},"</f>
@@ -43959,10 +43989,10 @@
     </row>
     <row r="112" spans="1:34">
       <c r="C112" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="D112" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="K112" t="s">
         <v>1656</v>
@@ -43975,22 +44005,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="盘龙坞·大旗重置",nTime=-2,nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=1465,szName="逐鹿坪·大旗重置",nTime=-2,nRefresh=7200,key="逐鹿坪·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【盘龙坞】大旗重置",nTime="180,【盘龙坞】大旗重置;185,【盘龙坞】大旗重置·结束",nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【逐鹿坪】大旗重置",nTime="180,【逐鹿坪】大旗重置;185,【逐鹿坪】大旗重置·结束",nRefresh=7200,key="逐鹿坪·大旗重置",},},},</v>
       </c>
       <c r="U112" t="s">
-        <v>2597</v>
+        <v>2599</v>
       </c>
       <c r="V112" t="s">
-        <v>2598</v>
+        <v>2600</v>
       </c>
       <c r="W112" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="X112" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="Y112" t="s">
-        <v>2599</v>
+        <v>2601</v>
       </c>
       <c r="Z112" t="s">
-        <v>2600</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="113" spans="1:34">
@@ -44007,16 +44037,16 @@
     </row>
     <row r="114" customFormat="1" spans="1:34">
       <c r="C114" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="D114" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="G114" t="s">
-        <v>2601</v>
+        <v>2603</v>
       </c>
       <c r="H114" t="s">
-        <v>2602</v>
+        <v>2604</v>
       </c>
       <c r="K114" t="s">
         <v>1656</v>
@@ -44029,7 +44059,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【龙门镇】恶人·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【飞沙关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【龙门镇】浩气·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【飞沙关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·恶人大旗",},},},</v>
       </c>
       <c r="U114" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="V114" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G114&amp;"·浩气大旗"&amp;""",},"</f>
@@ -44048,19 +44078,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·恶人大旗",},</v>
       </c>
       <c r="Z114" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="AA114" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="AB114" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="AC114" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="AD114" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
       <c r="AE114" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G114&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G114&amp;"·浩气大旗"""&amp;",},"</f>
@@ -44081,10 +44111,10 @@
     </row>
     <row r="115" spans="1:34">
       <c r="C115" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="D115" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="K115" t="s">
         <v>1656</v>
@@ -44097,22 +44127,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="龙门镇·大旗重置",nTime=-2,nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=1465,szName="飞沙关·大旗重置",nTime=-2,nRefresh=7200,key="飞沙关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【龙门镇】大旗重置",nTime="180,【龙门镇】大旗重置;185,【龙门镇】大旗重置·结束",nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【飞沙关】大旗重置",nTime="180,【飞沙关】大旗重置;185,【飞沙关】大旗重置·结束",nRefresh=7200,key="飞沙关·大旗重置",},},},</v>
       </c>
       <c r="U115" t="s">
-        <v>2603</v>
+        <v>2605</v>
       </c>
       <c r="V115" t="s">
-        <v>2604</v>
+        <v>2606</v>
       </c>
       <c r="W115" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="X115" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="Y115" t="s">
-        <v>2605</v>
+        <v>2607</v>
       </c>
       <c r="Z115" t="s">
-        <v>2606</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="116" spans="1:34">
@@ -44129,16 +44159,16 @@
     </row>
     <row r="117" customFormat="1" spans="1:34">
       <c r="C117" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="D117" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="G117" t="s">
-        <v>2607</v>
+        <v>2609</v>
       </c>
       <c r="H117" t="s">
-        <v>2608</v>
+        <v>2610</v>
       </c>
       <c r="K117" t="s">
         <v>1656</v>
@@ -44151,7 +44181,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【红莲岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【秋雨堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【红莲岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【秋雨堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·恶人大旗",},},},</v>
       </c>
       <c r="U117" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="V117" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G117&amp;"·浩气大旗"&amp;""",},"</f>
@@ -44170,19 +44200,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},</v>
       </c>
       <c r="Z117" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="AA117" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="AB117" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="AC117" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="AD117" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
       <c r="AE117" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G117&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G117&amp;"·浩气大旗"""&amp;",},"</f>
@@ -44203,10 +44233,10 @@
     </row>
     <row r="118" spans="1:34">
       <c r="C118" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="D118" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="K118" t="s">
         <v>1656</v>
@@ -44219,22 +44249,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="红莲岗·大旗重置",nTime=-2,nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=1465,szName="秋雨堡·大旗重置",nTime=-2,nRefresh=7200,key="秋雨堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【红莲岗】大旗重置",nTime="180,【红莲岗】大旗重置;185,【红莲岗】大旗重置·结束",nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【秋雨堡】大旗重置",nTime="180,【秋雨堡】大旗重置;185,【秋雨堡】大旗重置·结束",nRefresh=7200,key="秋雨堡·大旗重置",},},},</v>
       </c>
       <c r="U118" t="s">
-        <v>2609</v>
+        <v>2611</v>
       </c>
       <c r="V118" t="s">
-        <v>2610</v>
+        <v>2612</v>
       </c>
       <c r="W118" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="X118" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="Y118" t="s">
-        <v>2611</v>
+        <v>2613</v>
       </c>
       <c r="Z118" t="s">
-        <v>2612</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="119" spans="1:34">
@@ -44251,16 +44281,16 @@
     </row>
     <row r="120" customFormat="1" spans="1:34">
       <c r="C120" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="D120" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="G120" t="s">
-        <v>2613</v>
+        <v>2615</v>
       </c>
       <c r="H120" t="s">
-        <v>2614</v>
+        <v>2616</v>
       </c>
       <c r="K120" t="s">
         <v>1656</v>
@@ -44273,7 +44303,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【金门关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="金门关·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【青云坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【金门关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="金门关·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【青云坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·恶人大旗",},},},</v>
       </c>
       <c r="U120" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="V120" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G120&amp;"·浩气大旗"&amp;""",},"</f>
@@ -44292,19 +44322,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·恶人大旗",},</v>
       </c>
       <c r="Z120" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="AA120" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="AB120" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="AC120" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="AD120" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
       <c r="AE120" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G120&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G120&amp;"·浩气大旗"""&amp;",},"</f>
@@ -44325,10 +44355,10 @@
     </row>
     <row r="121" spans="1:34">
       <c r="C121" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="D121" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="K121" t="s">
         <v>1656</v>
@@ -44341,22 +44371,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="金门关·大旗重置",nTime=-2,nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=1465,szName="青云坞·大旗重置",nTime=-2,nRefresh=7200,key="青云坞·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【金门关】大旗重置",nTime="180,【金门关】大旗重置;185,【金门关】大旗重置·结束",nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【青云坞】大旗重置",nTime="180,【青云坞】大旗重置;185,【青云坞】大旗重置·结束",nRefresh=7200,key="青云坞·大旗重置",},},},</v>
       </c>
       <c r="U121" t="s">
-        <v>2615</v>
+        <v>2617</v>
       </c>
       <c r="V121" t="s">
-        <v>2616</v>
+        <v>2618</v>
       </c>
       <c r="W121" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="X121" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="Y121" t="s">
-        <v>2617</v>
+        <v>2619</v>
       </c>
       <c r="Z121" t="s">
-        <v>2618</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="122" spans="1:34">
@@ -44373,16 +44403,16 @@
     </row>
     <row r="123" customFormat="1" spans="1:34">
       <c r="C123" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="D123" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="G123" t="s">
-        <v>2619</v>
+        <v>2621</v>
       </c>
       <c r="H123" t="s">
-        <v>2620</v>
+        <v>2622</v>
       </c>
       <c r="K123" t="s">
         <v>1656</v>
@@ -44395,7 +44425,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【激流坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【不空关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="不空关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【激流坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【不空关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="不空关·恶人大旗",},},},</v>
       </c>
       <c r="U123" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="V123" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G123&amp;"·浩气大旗"&amp;""",},"</f>
@@ -44414,19 +44444,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·恶人大旗",},</v>
       </c>
       <c r="Z123" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="AA123" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="AB123" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="AC123" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="AD123" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
       <c r="AE123" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G123&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G123&amp;"·浩气大旗"""&amp;",},"</f>
@@ -44447,10 +44477,10 @@
     </row>
     <row r="124" spans="1:34">
       <c r="C124" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="D124" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="K124" t="s">
         <v>1656</v>
@@ -44463,22 +44493,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="激流坞·大旗重置",nTime=-2,nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=1465,szName="不空关·大旗重置",nTime=-2,nRefresh=7200,key="不空关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【激流坞】大旗重置",nTime="180,【激流坞】大旗重置;185,【激流坞】大旗重置·结束",nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【不空关】大旗重置",nTime="180,【不空关】大旗重置;185,【不空关】大旗重置·结束",nRefresh=7200,key="不空关·大旗重置",},},},</v>
       </c>
       <c r="U124" t="s">
-        <v>2621</v>
+        <v>2623</v>
       </c>
       <c r="V124" t="s">
-        <v>2622</v>
+        <v>2624</v>
       </c>
       <c r="W124" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="X124" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="Y124" t="s">
-        <v>2623</v>
+        <v>2625</v>
       </c>
       <c r="Z124" t="s">
-        <v>2624</v>
+        <v>2626</v>
       </c>
     </row>
     <row r="125" spans="1:34">
@@ -44495,16 +44525,16 @@
     </row>
     <row r="126" customFormat="1" spans="1:34">
       <c r="C126" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="D126" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="G126" t="s">
-        <v>2625</v>
+        <v>2627</v>
       </c>
       <c r="H126" t="s">
-        <v>2626</v>
+        <v>2628</v>
       </c>
       <c r="K126" t="s">
         <v>1656</v>
@@ -44517,7 +44547,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【日月崖】恶人·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【卧龙坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【日月崖】浩气·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【卧龙坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·恶人大旗",},},},</v>
       </c>
       <c r="U126" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="V126" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G126&amp;"·浩气大旗"&amp;""",},"</f>
@@ -44536,19 +44566,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·恶人大旗",},</v>
       </c>
       <c r="Z126" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="AA126" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="AB126" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="AC126" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="AD126" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
       <c r="AE126" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G126&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G126&amp;"·浩气大旗"""&amp;",},"</f>
@@ -44569,10 +44599,10 @@
     </row>
     <row r="127" spans="1:34">
       <c r="C127" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="D127" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="K127" t="s">
         <v>1656</v>
@@ -44585,22 +44615,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="日月崖·大旗重置",nTime=-2,nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=1465,szName="卧龙坡·大旗重置",nTime=-2,nRefresh=7200,key="卧龙坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【日月崖】大旗重置",nTime="180,【日月崖】大旗重置;185,【日月崖】大旗重置·结束",nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【卧龙坡】大旗重置",nTime="180,【卧龙坡】大旗重置;185,【卧龙坡】大旗重置·结束",nRefresh=7200,key="卧龙坡·大旗重置",},},},</v>
       </c>
       <c r="U127" t="s">
-        <v>2627</v>
+        <v>2629</v>
       </c>
       <c r="V127" t="s">
-        <v>2628</v>
+        <v>2630</v>
       </c>
       <c r="W127" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="X127" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="Y127" t="s">
-        <v>2629</v>
+        <v>2631</v>
       </c>
       <c r="Z127" t="s">
-        <v>2630</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="128" spans="1:34">
@@ -44617,16 +44647,16 @@
     </row>
     <row r="129" customFormat="1" spans="1:34">
       <c r="C129" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="D129" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="G129" t="s">
-        <v>2631</v>
+        <v>2633</v>
       </c>
       <c r="H129" t="s">
-        <v>2632</v>
+        <v>2634</v>
       </c>
       <c r="K129" t="s">
         <v>1656</v>
@@ -44639,7 +44669,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【霜戈堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【澜沧城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【霜戈堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【澜沧城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·恶人大旗",},},},</v>
       </c>
       <c r="U129" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="V129" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G129&amp;"·浩气大旗"&amp;""",},"</f>
@@ -44658,19 +44688,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·恶人大旗",},</v>
       </c>
       <c r="Z129" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="AA129" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="AB129" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="AC129" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="AD129" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
       <c r="AE129" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G129&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G129&amp;"·浩气大旗"""&amp;",},"</f>
@@ -44691,10 +44721,10 @@
     </row>
     <row r="130" spans="1:34">
       <c r="C130" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="D130" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="K130" t="s">
         <v>1656</v>
@@ -44707,22 +44737,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="霜戈堡·大旗重置",nTime=-2,nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=1465,szName="澜沧城·大旗重置",nTime=-2,nRefresh=7200,key="澜沧城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【霜戈堡】大旗重置",nTime="180,【霜戈堡】大旗重置;185,【霜戈堡】大旗重置·结束",nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【澜沧城】大旗重置",nTime="180,【澜沧城】大旗重置;185,【澜沧城】大旗重置·结束",nRefresh=7200,key="澜沧城·大旗重置",},},},</v>
       </c>
       <c r="U130" t="s">
-        <v>2633</v>
+        <v>2635</v>
       </c>
       <c r="V130" t="s">
-        <v>2634</v>
+        <v>2636</v>
       </c>
       <c r="W130" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="X130" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="Y130" t="s">
-        <v>2635</v>
+        <v>2637</v>
       </c>
       <c r="Z130" t="s">
-        <v>2636</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="131" spans="1:34">
@@ -44739,16 +44769,16 @@
     </row>
     <row r="132" customFormat="1" spans="1:34">
       <c r="C132" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="D132" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="G132" t="s">
-        <v>2637</v>
+        <v>2639</v>
       </c>
       <c r="H132" t="s">
-        <v>2638</v>
+        <v>2640</v>
       </c>
       <c r="K132" t="s">
         <v>1656</v>
@@ -44761,7 +44791,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【神池岭】恶人·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【烈日岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【神池岭】浩气·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【烈日岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·恶人大旗",},},},</v>
       </c>
       <c r="U132" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="V132" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G132&amp;"·浩气大旗"&amp;""",},"</f>
@@ -44780,19 +44810,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·恶人大旗",},</v>
       </c>
       <c r="Z132" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="AA132" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="AB132" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="AC132" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="AD132" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
       <c r="AE132" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G132&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G132&amp;"·浩气大旗"""&amp;",},"</f>
@@ -44813,10 +44843,10 @@
     </row>
     <row r="133" spans="1:34">
       <c r="C133" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="D133" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="K133" t="s">
         <v>1656</v>
@@ -44829,22 +44859,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="神池岭·大旗重置",nTime=-2,nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=1465,szName="烈日岗·大旗重置",nTime=-2,nRefresh=7200,key="烈日岗·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【神池岭】大旗重置",nTime="180,【神池岭】大旗重置;185,【神池岭】大旗重置·结束",nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【烈日岗】大旗重置",nTime="180,【烈日岗】大旗重置;185,【烈日岗】大旗重置·结束",nRefresh=7200,key="烈日岗·大旗重置",},},},</v>
       </c>
       <c r="U133" t="s">
-        <v>2639</v>
+        <v>2641</v>
       </c>
       <c r="V133" t="s">
-        <v>2640</v>
+        <v>2642</v>
       </c>
       <c r="W133" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="X133" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="Y133" t="s">
-        <v>2641</v>
+        <v>2643</v>
       </c>
       <c r="Z133" t="s">
-        <v>2642</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="134" spans="1:34">
@@ -44861,16 +44891,16 @@
     </row>
     <row r="135" customFormat="1" spans="1:34">
       <c r="C135" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="D135" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="G135" t="s">
-        <v>2643</v>
+        <v>2645</v>
       </c>
       <c r="H135" t="s">
-        <v>2644</v>
+        <v>2646</v>
       </c>
       <c r="K135" t="s">
         <v>1656</v>
@@ -44883,7 +44913,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凤鸣堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【惊虬谷】恶人·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凤鸣堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【惊虬谷】浩气·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·恶人大旗",},},},</v>
       </c>
       <c r="U135" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="V135" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G135&amp;"·浩气大旗"&amp;""",},"</f>
@@ -44902,19 +44932,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},</v>
       </c>
       <c r="Z135" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="AA135" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="AB135" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="AC135" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="AD135" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
       <c r="AE135" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G135&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G135&amp;"·浩气大旗"""&amp;",},"</f>
@@ -44935,10 +44965,10 @@
     </row>
     <row r="136" spans="1:34">
       <c r="C136" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="D136" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="K136" t="s">
         <v>1656</v>
@@ -44951,22 +44981,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凤鸣堡·大旗重置",nTime=-2,nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=1465,szName="惊虬谷·大旗重置",nTime=-2,nRefresh=7200,key="惊虬谷·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凤鸣堡】大旗重置",nTime="180,【凤鸣堡】大旗重置;185,【凤鸣堡】大旗重置·结束",nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【惊虬谷】大旗重置",nTime="180,【惊虬谷】大旗重置;185,【惊虬谷】大旗重置·结束",nRefresh=7200,key="惊虬谷·大旗重置",},},},</v>
       </c>
       <c r="U136" t="s">
-        <v>2645</v>
+        <v>2647</v>
       </c>
       <c r="V136" t="s">
-        <v>2646</v>
+        <v>2648</v>
       </c>
       <c r="W136" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="X136" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="Y136" t="s">
-        <v>2647</v>
+        <v>2649</v>
       </c>
       <c r="Z136" t="s">
-        <v>2648</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="137" spans="1:34">
@@ -44983,16 +45013,16 @@
     </row>
     <row r="138" customFormat="1" spans="1:34">
       <c r="C138" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="D138" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="G138" t="s">
-        <v>2649</v>
+        <v>2651</v>
       </c>
       <c r="H138" t="s">
-        <v>2650</v>
+        <v>2652</v>
       </c>
       <c r="K138" t="s">
         <v>1656</v>
@@ -45005,7 +45035,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【大理山城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【千岩关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【大理山城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【千岩关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·恶人大旗",},},},</v>
       </c>
       <c r="U138" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="V138" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G138&amp;"·浩气大旗"&amp;""",},"</f>
@@ -45024,19 +45054,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·恶人大旗",},</v>
       </c>
       <c r="Z138" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="AA138" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="AB138" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="AC138" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="AD138" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
       <c r="AE138" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G138&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G138&amp;"·浩气大旗"""&amp;",},"</f>
@@ -45057,10 +45087,10 @@
     </row>
     <row r="139" spans="1:34">
       <c r="C139" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="D139" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="K139" t="s">
         <v>1656</v>
@@ -45073,22 +45103,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="大理山城·大旗重置",nTime=-2,nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=1465,szName="千岩关·大旗重置",nTime=-2,nRefresh=7200,key="千岩关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【大理山城】大旗重置",nTime="180,【大理山城】大旗重置;185,【大理山城】大旗重置·结束",nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【千岩关】大旗重置",nTime="180,【千岩关】大旗重置;185,【千岩关】大旗重置·结束",nRefresh=7200,key="千岩关·大旗重置",},},},</v>
       </c>
       <c r="U139" t="s">
-        <v>2651</v>
+        <v>2653</v>
       </c>
       <c r="V139" t="s">
-        <v>2652</v>
+        <v>2654</v>
       </c>
       <c r="W139" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="X139" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="Y139" t="s">
-        <v>2653</v>
+        <v>2655</v>
       </c>
       <c r="Z139" t="s">
-        <v>2654</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="140" spans="1:34">
@@ -45105,16 +45135,16 @@
     </row>
     <row r="141" customFormat="1" spans="1:34">
       <c r="C141" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="D141" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="G141" t="s">
-        <v>2655</v>
+        <v>2657</v>
       </c>
       <c r="H141" t="s">
-        <v>2656</v>
+        <v>2658</v>
       </c>
       <c r="K141" t="s">
         <v>1656</v>
@@ -45127,7 +45157,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【枫湖寨】恶人·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【啖杏林】恶人·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【枫湖寨】浩气·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【啖杏林】浩气·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·恶人大旗",},},},</v>
       </c>
       <c r="U141" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="V141" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G141&amp;"·浩气大旗"&amp;""",},"</f>
@@ -45146,19 +45176,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·恶人大旗",},</v>
       </c>
       <c r="Z141" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="AA141" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="AB141" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="AC141" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="AD141" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
       <c r="AE141" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G141&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G141&amp;"·浩气大旗"""&amp;",},"</f>
@@ -45179,10 +45209,10 @@
     </row>
     <row r="142" spans="1:34">
       <c r="C142" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="D142" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="K142" t="s">
         <v>1656</v>
@@ -45195,22 +45225,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="枫湖寨·大旗重置",nTime=-2,nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=1465,szName="啖杏林·大旗重置",nTime=-2,nRefresh=7200,key="啖杏林·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【枫湖寨】大旗重置",nTime="180,【枫湖寨】大旗重置;185,【枫湖寨】大旗重置·结束",nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【啖杏林】大旗重置",nTime="180,【啖杏林】大旗重置;185,【啖杏林】大旗重置·结束",nRefresh=7200,key="啖杏林·大旗重置",},},},</v>
       </c>
       <c r="U142" t="s">
-        <v>2657</v>
+        <v>2659</v>
       </c>
       <c r="V142" t="s">
-        <v>2658</v>
+        <v>2660</v>
       </c>
       <c r="W142" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="X142" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="Y142" t="s">
-        <v>2659</v>
+        <v>2661</v>
       </c>
       <c r="Z142" t="s">
-        <v>2660</v>
+        <v>2662</v>
       </c>
     </row>
     <row r="143" spans="1:34">
@@ -45227,16 +45257,16 @@
     </row>
     <row r="144" customFormat="1" spans="1:34">
       <c r="C144" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="D144" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="G144" t="s">
-        <v>2661</v>
+        <v>2663</v>
       </c>
       <c r="H144" t="s">
-        <v>2662</v>
+        <v>2664</v>
       </c>
       <c r="K144" t="s">
         <v>1656</v>
@@ -45249,7 +45279,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【扶风郡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【世外坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【扶风郡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【世外坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U144" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="V144" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G144&amp;"·浩气大旗"&amp;""",},"</f>
@@ -45268,19 +45298,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·恶人大旗",},</v>
       </c>
       <c r="Z144" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="AA144" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="AB144" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="AC144" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="AD144" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
       <c r="AE144" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G144&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G144&amp;"·浩气大旗"""&amp;",},"</f>
@@ -45301,10 +45331,10 @@
     </row>
     <row r="145" spans="1:26">
       <c r="C145" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="D145" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="K145" t="s">
         <v>1656</v>
@@ -45317,22 +45347,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="扶风郡·大旗重置",nTime=-2,nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=1465,szName="世外坡·大旗重置",nTime=-2,nRefresh=7200,key="世外坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【扶风郡】大旗重置",nTime="180,【扶风郡】大旗重置;185,【扶风郡】大旗重置·结束",nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【世外坡】大旗重置",nTime="180,【世外坡】大旗重置;185,【世外坡】大旗重置·结束",nRefresh=7200,key="世外坡·大旗重置",},},},</v>
       </c>
       <c r="U145" t="s">
-        <v>2663</v>
+        <v>2665</v>
       </c>
       <c r="V145" t="s">
-        <v>2664</v>
+        <v>2666</v>
       </c>
       <c r="W145" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="X145" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="Y145" t="s">
-        <v>2665</v>
+        <v>2667</v>
       </c>
       <c r="Z145" t="s">
-        <v>2666</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="146" spans="1:26">
@@ -45349,16 +45379,16 @@
     </row>
     <row r="147" spans="1:26">
       <c r="C147" t="s">
-        <v>2667</v>
+        <v>2669</v>
       </c>
       <c r="D147" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="G147" t="s">
-        <v>2668</v>
+        <v>2670</v>
       </c>
       <c r="H147" t="s">
-        <v>2669</v>
+        <v>2671</v>
       </c>
       <c r="K147" t="s">
         <v>1656</v>
@@ -45371,30 +45401,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U147" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="V147" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="W147" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="X147" t="s">
-        <v>2670</v>
+        <v>2672</v>
       </c>
       <c r="Y147" t="s">
-        <v>2509</v>
+        <v>2511</v>
       </c>
       <c r="Z147" t="s">
-        <v>2510</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="148" spans="1:26">
       <c r="C148" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="D148" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="K148" t="s">
         <v>1656</v>
@@ -45407,30 +45437,30 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime="180,【云台营】大旗重置;185,【云台营】大旗重置·结束",nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime="180,【高阳营】大旗重置;185,【高阳营】大旗重置·结束",nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U148" t="s">
-        <v>2671</v>
+        <v>2673</v>
       </c>
       <c r="V148" t="s">
-        <v>2672</v>
+        <v>2674</v>
       </c>
       <c r="W148" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="X148" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="Y148" t="s">
-        <v>2673</v>
+        <v>2675</v>
       </c>
       <c r="Z148" t="s">
-        <v>2674</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="149" customFormat="1" spans="1:26">
       <c r="C149" s="3" t="s">
-        <v>2549</v>
+        <v>2551</v>
       </c>
       <c r="D149" t="s">
-        <v>2550</v>
+        <v>2552</v>
       </c>
       <c r="K149" t="s">
         <v>1656</v>
@@ -45443,19 +45473,19 @@
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U149" t="s">
-        <v>2551</v>
+        <v>2553</v>
       </c>
       <c r="V149" t="s">
-        <v>2552</v>
+        <v>2554</v>
       </c>
       <c r="W149" t="s">
-        <v>2553</v>
+        <v>2555</v>
       </c>
       <c r="X149" t="s">
-        <v>2554</v>
+        <v>2556</v>
       </c>
       <c r="Y149" t="s">
-        <v>2555</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="150" spans="1:26">
@@ -45472,16 +45502,16 @@
     </row>
     <row r="151" spans="1:26">
       <c r="C151" t="s">
-        <v>2667</v>
+        <v>2669</v>
       </c>
       <c r="D151" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="G151" t="s">
-        <v>2668</v>
+        <v>2670</v>
       </c>
       <c r="H151" t="s">
-        <v>2669</v>
+        <v>2671</v>
       </c>
       <c r="K151" t="s">
         <v>1656</v>
@@ -45494,30 +45524,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U151" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="V151" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="W151" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="X151" t="s">
-        <v>2670</v>
+        <v>2672</v>
       </c>
       <c r="Y151" t="s">
-        <v>2509</v>
+        <v>2511</v>
       </c>
       <c r="Z151" t="s">
-        <v>2510</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="152" spans="1:26">
       <c r="C152" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="D152" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="K152" t="s">
         <v>1656</v>
@@ -45530,30 +45560,30 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime="180,【云台营】大旗重置;185,【云台营】大旗重置·结束",nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime="180,【高阳营】大旗重置;185,【高阳营】大旗重置·结束",nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U152" t="s">
-        <v>2671</v>
+        <v>2673</v>
       </c>
       <c r="V152" t="s">
-        <v>2672</v>
+        <v>2674</v>
       </c>
       <c r="W152" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="X152" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="Y152" t="s">
-        <v>2673</v>
+        <v>2675</v>
       </c>
       <c r="Z152" t="s">
-        <v>2674</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="153" customFormat="1" spans="1:26">
       <c r="C153" s="3" t="s">
-        <v>2549</v>
+        <v>2551</v>
       </c>
       <c r="D153" t="s">
-        <v>2550</v>
+        <v>2552</v>
       </c>
       <c r="K153" t="s">
         <v>1656</v>
@@ -45566,19 +45596,19 @@
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U153" t="s">
-        <v>2551</v>
+        <v>2553</v>
       </c>
       <c r="V153" t="s">
-        <v>2552</v>
+        <v>2554</v>
       </c>
       <c r="W153" t="s">
-        <v>2553</v>
+        <v>2555</v>
       </c>
       <c r="X153" t="s">
-        <v>2554</v>
+        <v>2556</v>
       </c>
       <c r="Y153" t="s">
-        <v>2555</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="154" spans="1:26">

--- a/阵营/大小攻防团队监控.xlsx
+++ b/阵营/大小攻防团队监控.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据总控" sheetId="2" r:id="rId1"/>
@@ -6703,7 +6703,7 @@
     <t>恶人谷·物资车·已运达</t>
   </si>
   <si>
-    <t>{nClass=14,nIcon=10450,nFrame=4,szName="恶人谷·营地物资·刷新",nTime="10,恶人谷·营地物资·刷新;300,恶人谷·营地物资·拾取剩余;305,恶人谷·营地物资·已消失",nRefresh=0,key="恶人·物资车·运达",},</t>
+    <t>{nClass=14,nIcon=10450,nFrame=4,szName="恶人谷·营地物资·已刷新",nTime="10,恶人谷·营地物资·已刷新;300,恶人谷·营地物资·拾取剩余;305,恶人谷·营地物资·已消失",nRefresh=0,key="恶人·物资车·运达",},</t>
   </si>
   <si>
     <t>军情速递！浩气盟物资车已运达，车内装有大量物资，望侠士们前来拾取，切莫错过。</t>
@@ -6712,7 +6712,7 @@
     <t>浩气盟·物资车·已运达</t>
   </si>
   <si>
-    <t>{nClass=14,nIcon=10449,nFrame=4,szName="浩气盟·内城物资·刷新",nTime="10,浩气盟·内城物资·刷新;300,浩气盟·内城物资·拾取剩余;305,浩气盟·内城物资·已消失",nRefresh=0,key="浩气·物资车·运达",},</t>
+    <t>{nClass=14,nIcon=10449,nFrame=4,szName="浩气盟·内城物资·已刷新",nTime="10,浩气盟·内城物资·已刷新;300,浩气盟·内城物资·拾取剩余;305,浩气盟·内城物资·已消失",nRefresh=0,key="浩气·物资车·运达",},</t>
   </si>
   <si>
     <t>平安客栈</t>
@@ -6730,10 +6730,10 @@
     <t>军情速递！恶人谷物资官传来消息，现有一批新物资运至各复活点，望恶人侠士们前来领取，以便增强战斗实力。</t>
   </si>
   <si>
-    <t>{nClass=14,nIcon=10450,nFrame=4,szName="恶人谷·内城物资·刷新",nTime="10,恶人谷·内城物资·刷新;300,恶人谷·内城物资·拾取剩余;305,恶人谷·内城物资·已消失",nRefresh=0,key="恶人·物资车·运达",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=10449,nFrame=4,szName="浩气盟·营地物资·刷新",nTime="10,浩气盟·营地物资·刷新;300,浩气盟·营地物资·拾取剩余;305,浩气盟·营地物资·已消失",nRefresh=0,key="浩气·物资车·运达",},</t>
+    <t>{nClass=14,nIcon=10450,nFrame=4,szName="恶人谷·内城物资·已刷新",nTime="10,恶人谷·内城物资·刷新;300,恶人谷·内城物资·拾取剩余;305,恶人谷·内城物资·已消失",nRefresh=0,key="恶人·物资车·运达",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=10449,nFrame=4,szName="浩气盟·营地物资·已刷新",nTime="10,浩气盟·营地物资·刷新;300,浩气盟·营地物资·拾取剩余;305,浩气盟·营地物资·已消失",nRefresh=0,key="浩气·物资车·运达",},</t>
   </si>
   <si>
     <t>门派地图</t>
@@ -9485,7 +9485,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="34" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1782396774000,</v>
+        <v>nTimeStamp = 1782648205000,</v>
       </c>
       <c r="B4" s="38" t="s">
         <v>11</v>
@@ -33337,7 +33337,7 @@
         <v>1678</v>
       </c>
       <c r="V387" t="str">
-        <f>IF(ISBLANK(B387)=FALSE,IF(ISBLANK(B386),"},["&amp;B387&amp;"]={","["&amp;B387&amp;"]={"),IF(AND(ISBLANK(B387),ISBLANK(D387),ISBLANK(C387),OR(ISBLANK(B386)=FALSE,ISBLANK(D386)=FALSE,ISBLANK(C386)=FALSE)),"},},}",IF(ISBLANK(C387),"","{dwID="&amp;C387&amp;","&amp;"nFrame="&amp;D387&amp;","&amp;IF(E387&gt;0,"nCount="&amp;E387&amp;",","")&amp;IF(F387&gt;0,"bAllLeave=true,","")&amp;IF(G387&lt;&gt;"","szName="""&amp;G387&amp;""",","")&amp;IF(H387&lt;&gt;"","tKungFu={"&amp;H387&amp;"},","")&amp;IF(I387&lt;&gt;"","szNote="""&amp;I387&amp;""",","")&amp;IF(J387&lt;&gt;"","col={"&amp;J387&amp;"},","")&amp;"[3]={"&amp;IF(K387&lt;&gt;"","tMark={"&amp;K387&amp;"},","")&amp;IF(L387&lt;&gt;"","szVoice="""&amp;L387&amp;""",","")&amp;IF(M387&gt;0,"bTeamChannel=true,","")&amp;IF(N387&gt;0,"bWhisperChannel=true,","")&amp;IF(O387&gt;0,"bCenterAlarm=true,","")&amp;IF(P387&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q387&lt;&gt;"","szVoice="""&amp;Q387&amp;""",","")&amp;IF(R387&gt;0,"bTeamChannel=true,","")&amp;IF(S387&gt;0,"bWhisperChannel=true,","")&amp;IF(T387&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U387&lt;&gt;"","aFocus={"&amp;U387&amp;"},","")&amp;IF(W387&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W387:ZZ387)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="V387:V412" si="6">IF(ISBLANK(B387)=FALSE,IF(ISBLANK(B386),"},["&amp;B387&amp;"]={","["&amp;B387&amp;"]={"),IF(AND(ISBLANK(B387),ISBLANK(D387),ISBLANK(C387),OR(ISBLANK(B386)=FALSE,ISBLANK(D386)=FALSE,ISBLANK(C386)=FALSE)),"},},}",IF(ISBLANK(C387),"","{dwID="&amp;C387&amp;","&amp;"nFrame="&amp;D387&amp;","&amp;IF(E387&gt;0,"nCount="&amp;E387&amp;",","")&amp;IF(F387&gt;0,"bAllLeave=true,","")&amp;IF(G387&lt;&gt;"","szName="""&amp;G387&amp;""",","")&amp;IF(H387&lt;&gt;"","tKungFu={"&amp;H387&amp;"},","")&amp;IF(I387&lt;&gt;"","szNote="""&amp;I387&amp;""",","")&amp;IF(J387&lt;&gt;"","col={"&amp;J387&amp;"},","")&amp;"[3]={"&amp;IF(K387&lt;&gt;"","tMark={"&amp;K387&amp;"},","")&amp;IF(L387&lt;&gt;"","szVoice="""&amp;L387&amp;""",","")&amp;IF(M387&gt;0,"bTeamChannel=true,","")&amp;IF(N387&gt;0,"bWhisperChannel=true,","")&amp;IF(O387&gt;0,"bCenterAlarm=true,","")&amp;IF(P387&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q387&lt;&gt;"","szVoice="""&amp;Q387&amp;""",","")&amp;IF(R387&gt;0,"bTeamChannel=true,","")&amp;IF(S387&gt;0,"bWhisperChannel=true,","")&amp;IF(T387&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U387&lt;&gt;"","aFocus={"&amp;U387&amp;"},","")&amp;IF(W387&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W387:ZZ387)&amp;"},","")&amp;"},")))</f>
         <v>{dwID=124270,nFrame=52,szNote="粮仓·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},},},</v>
       </c>
     </row>
@@ -33355,7 +33355,7 @@
         <v>1678</v>
       </c>
       <c r="V388" t="str">
-        <f>IF(ISBLANK(B388)=FALSE,IF(ISBLANK(B387),"},["&amp;B388&amp;"]={","["&amp;B388&amp;"]={"),IF(AND(ISBLANK(B388),ISBLANK(D388),ISBLANK(C388),OR(ISBLANK(B387)=FALSE,ISBLANK(D387)=FALSE,ISBLANK(C387)=FALSE)),"},},}",IF(ISBLANK(C388),"","{dwID="&amp;C388&amp;","&amp;"nFrame="&amp;D388&amp;","&amp;IF(E388&gt;0,"nCount="&amp;E388&amp;",","")&amp;IF(F388&gt;0,"bAllLeave=true,","")&amp;IF(G388&lt;&gt;"","szName="""&amp;G388&amp;""",","")&amp;IF(H388&lt;&gt;"","tKungFu={"&amp;H388&amp;"},","")&amp;IF(I388&lt;&gt;"","szNote="""&amp;I388&amp;""",","")&amp;IF(J388&lt;&gt;"","col={"&amp;J388&amp;"},","")&amp;"[3]={"&amp;IF(K388&lt;&gt;"","tMark={"&amp;K388&amp;"},","")&amp;IF(L388&lt;&gt;"","szVoice="""&amp;L388&amp;""",","")&amp;IF(M388&gt;0,"bTeamChannel=true,","")&amp;IF(N388&gt;0,"bWhisperChannel=true,","")&amp;IF(O388&gt;0,"bCenterAlarm=true,","")&amp;IF(P388&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q388&lt;&gt;"","szVoice="""&amp;Q388&amp;""",","")&amp;IF(R388&gt;0,"bTeamChannel=true,","")&amp;IF(S388&gt;0,"bWhisperChannel=true,","")&amp;IF(T388&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U388&lt;&gt;"","aFocus={"&amp;U388&amp;"},","")&amp;IF(W388&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W388:ZZ388)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=124271,nFrame=52,szNote="粮仓·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},},},</v>
       </c>
     </row>
@@ -33373,7 +33373,7 @@
         <v>1681</v>
       </c>
       <c r="V389" t="str">
-        <f>IF(ISBLANK(B389)=FALSE,IF(ISBLANK(B388),"},["&amp;B389&amp;"]={","["&amp;B389&amp;"]={"),IF(AND(ISBLANK(B389),ISBLANK(D389),ISBLANK(C389),OR(ISBLANK(B388)=FALSE,ISBLANK(D388)=FALSE,ISBLANK(C388)=FALSE)),"},},}",IF(ISBLANK(C389),"","{dwID="&amp;C389&amp;","&amp;"nFrame="&amp;D389&amp;","&amp;IF(E389&gt;0,"nCount="&amp;E389&amp;",","")&amp;IF(F389&gt;0,"bAllLeave=true,","")&amp;IF(G389&lt;&gt;"","szName="""&amp;G389&amp;""",","")&amp;IF(H389&lt;&gt;"","tKungFu={"&amp;H389&amp;"},","")&amp;IF(I389&lt;&gt;"","szNote="""&amp;I389&amp;""",","")&amp;IF(J389&lt;&gt;"","col={"&amp;J389&amp;"},","")&amp;"[3]={"&amp;IF(K389&lt;&gt;"","tMark={"&amp;K389&amp;"},","")&amp;IF(L389&lt;&gt;"","szVoice="""&amp;L389&amp;""",","")&amp;IF(M389&gt;0,"bTeamChannel=true,","")&amp;IF(N389&gt;0,"bWhisperChannel=true,","")&amp;IF(O389&gt;0,"bCenterAlarm=true,","")&amp;IF(P389&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q389&lt;&gt;"","szVoice="""&amp;Q389&amp;""",","")&amp;IF(R389&gt;0,"bTeamChannel=true,","")&amp;IF(S389&gt;0,"bWhisperChannel=true,","")&amp;IF(T389&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U389&lt;&gt;"","aFocus={"&amp;U389&amp;"},","")&amp;IF(W389&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W389:ZZ389)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=124109,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
@@ -33391,7 +33391,7 @@
         <v>1681</v>
       </c>
       <c r="V390" t="str">
-        <f>IF(ISBLANK(B390)=FALSE,IF(ISBLANK(B389),"},["&amp;B390&amp;"]={","["&amp;B390&amp;"]={"),IF(AND(ISBLANK(B390),ISBLANK(D390),ISBLANK(C390),OR(ISBLANK(B389)=FALSE,ISBLANK(D389)=FALSE,ISBLANK(C389)=FALSE)),"},},}",IF(ISBLANK(C390),"","{dwID="&amp;C390&amp;","&amp;"nFrame="&amp;D390&amp;","&amp;IF(E390&gt;0,"nCount="&amp;E390&amp;",","")&amp;IF(F390&gt;0,"bAllLeave=true,","")&amp;IF(G390&lt;&gt;"","szName="""&amp;G390&amp;""",","")&amp;IF(H390&lt;&gt;"","tKungFu={"&amp;H390&amp;"},","")&amp;IF(I390&lt;&gt;"","szNote="""&amp;I390&amp;""",","")&amp;IF(J390&lt;&gt;"","col={"&amp;J390&amp;"},","")&amp;"[3]={"&amp;IF(K390&lt;&gt;"","tMark={"&amp;K390&amp;"},","")&amp;IF(L390&lt;&gt;"","szVoice="""&amp;L390&amp;""",","")&amp;IF(M390&gt;0,"bTeamChannel=true,","")&amp;IF(N390&gt;0,"bWhisperChannel=true,","")&amp;IF(O390&gt;0,"bCenterAlarm=true,","")&amp;IF(P390&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q390&lt;&gt;"","szVoice="""&amp;Q390&amp;""",","")&amp;IF(R390&gt;0,"bTeamChannel=true,","")&amp;IF(S390&gt;0,"bWhisperChannel=true,","")&amp;IF(T390&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U390&lt;&gt;"","aFocus={"&amp;U390&amp;"},","")&amp;IF(W390&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W390:ZZ390)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=124110,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
@@ -33409,7 +33409,7 @@
         <v>1681</v>
       </c>
       <c r="V391" t="str">
-        <f>IF(ISBLANK(B391)=FALSE,IF(ISBLANK(B390),"},["&amp;B391&amp;"]={","["&amp;B391&amp;"]={"),IF(AND(ISBLANK(B391),ISBLANK(D391),ISBLANK(C391),OR(ISBLANK(B390)=FALSE,ISBLANK(D390)=FALSE,ISBLANK(C390)=FALSE)),"},},}",IF(ISBLANK(C391),"","{dwID="&amp;C391&amp;","&amp;"nFrame="&amp;D391&amp;","&amp;IF(E391&gt;0,"nCount="&amp;E391&amp;",","")&amp;IF(F391&gt;0,"bAllLeave=true,","")&amp;IF(G391&lt;&gt;"","szName="""&amp;G391&amp;""",","")&amp;IF(H391&lt;&gt;"","tKungFu={"&amp;H391&amp;"},","")&amp;IF(I391&lt;&gt;"","szNote="""&amp;I391&amp;""",","")&amp;IF(J391&lt;&gt;"","col={"&amp;J391&amp;"},","")&amp;"[3]={"&amp;IF(K391&lt;&gt;"","tMark={"&amp;K391&amp;"},","")&amp;IF(L391&lt;&gt;"","szVoice="""&amp;L391&amp;""",","")&amp;IF(M391&gt;0,"bTeamChannel=true,","")&amp;IF(N391&gt;0,"bWhisperChannel=true,","")&amp;IF(O391&gt;0,"bCenterAlarm=true,","")&amp;IF(P391&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q391&lt;&gt;"","szVoice="""&amp;Q391&amp;""",","")&amp;IF(R391&gt;0,"bTeamChannel=true,","")&amp;IF(S391&gt;0,"bWhisperChannel=true,","")&amp;IF(T391&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U391&lt;&gt;"","aFocus={"&amp;U391&amp;"},","")&amp;IF(W391&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W391:ZZ391)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=124111,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
@@ -33427,7 +33427,7 @@
         <v>1681</v>
       </c>
       <c r="V392" t="str">
-        <f>IF(ISBLANK(B392)=FALSE,IF(ISBLANK(B391),"},["&amp;B392&amp;"]={","["&amp;B392&amp;"]={"),IF(AND(ISBLANK(B392),ISBLANK(D392),ISBLANK(C392),OR(ISBLANK(B391)=FALSE,ISBLANK(D391)=FALSE,ISBLANK(C391)=FALSE)),"},},}",IF(ISBLANK(C392),"","{dwID="&amp;C392&amp;","&amp;"nFrame="&amp;D392&amp;","&amp;IF(E392&gt;0,"nCount="&amp;E392&amp;",","")&amp;IF(F392&gt;0,"bAllLeave=true,","")&amp;IF(G392&lt;&gt;"","szName="""&amp;G392&amp;""",","")&amp;IF(H392&lt;&gt;"","tKungFu={"&amp;H392&amp;"},","")&amp;IF(I392&lt;&gt;"","szNote="""&amp;I392&amp;""",","")&amp;IF(J392&lt;&gt;"","col={"&amp;J392&amp;"},","")&amp;"[3]={"&amp;IF(K392&lt;&gt;"","tMark={"&amp;K392&amp;"},","")&amp;IF(L392&lt;&gt;"","szVoice="""&amp;L392&amp;""",","")&amp;IF(M392&gt;0,"bTeamChannel=true,","")&amp;IF(N392&gt;0,"bWhisperChannel=true,","")&amp;IF(O392&gt;0,"bCenterAlarm=true,","")&amp;IF(P392&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q392&lt;&gt;"","szVoice="""&amp;Q392&amp;""",","")&amp;IF(R392&gt;0,"bTeamChannel=true,","")&amp;IF(S392&gt;0,"bWhisperChannel=true,","")&amp;IF(T392&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U392&lt;&gt;"","aFocus={"&amp;U392&amp;"},","")&amp;IF(W392&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W392:ZZ392)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=124112,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
@@ -33445,7 +33445,7 @@
         <v>1681</v>
       </c>
       <c r="V393" t="str">
-        <f>IF(ISBLANK(B393)=FALSE,IF(ISBLANK(B392),"},["&amp;B393&amp;"]={","["&amp;B393&amp;"]={"),IF(AND(ISBLANK(B393),ISBLANK(D393),ISBLANK(C393),OR(ISBLANK(B392)=FALSE,ISBLANK(D392)=FALSE,ISBLANK(C392)=FALSE)),"},},}",IF(ISBLANK(C393),"","{dwID="&amp;C393&amp;","&amp;"nFrame="&amp;D393&amp;","&amp;IF(E393&gt;0,"nCount="&amp;E393&amp;",","")&amp;IF(F393&gt;0,"bAllLeave=true,","")&amp;IF(G393&lt;&gt;"","szName="""&amp;G393&amp;""",","")&amp;IF(H393&lt;&gt;"","tKungFu={"&amp;H393&amp;"},","")&amp;IF(I393&lt;&gt;"","szNote="""&amp;I393&amp;""",","")&amp;IF(J393&lt;&gt;"","col={"&amp;J393&amp;"},","")&amp;"[3]={"&amp;IF(K393&lt;&gt;"","tMark={"&amp;K393&amp;"},","")&amp;IF(L393&lt;&gt;"","szVoice="""&amp;L393&amp;""",","")&amp;IF(M393&gt;0,"bTeamChannel=true,","")&amp;IF(N393&gt;0,"bWhisperChannel=true,","")&amp;IF(O393&gt;0,"bCenterAlarm=true,","")&amp;IF(P393&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q393&lt;&gt;"","szVoice="""&amp;Q393&amp;""",","")&amp;IF(R393&gt;0,"bTeamChannel=true,","")&amp;IF(S393&gt;0,"bWhisperChannel=true,","")&amp;IF(T393&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U393&lt;&gt;"","aFocus={"&amp;U393&amp;"},","")&amp;IF(W393&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W393:ZZ393)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=124113,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
@@ -33463,7 +33463,7 @@
         <v>1681</v>
       </c>
       <c r="V394" t="str">
-        <f>IF(ISBLANK(B394)=FALSE,IF(ISBLANK(B393),"},["&amp;B394&amp;"]={","["&amp;B394&amp;"]={"),IF(AND(ISBLANK(B394),ISBLANK(D394),ISBLANK(C394),OR(ISBLANK(B393)=FALSE,ISBLANK(D393)=FALSE,ISBLANK(C393)=FALSE)),"},},}",IF(ISBLANK(C394),"","{dwID="&amp;C394&amp;","&amp;"nFrame="&amp;D394&amp;","&amp;IF(E394&gt;0,"nCount="&amp;E394&amp;",","")&amp;IF(F394&gt;0,"bAllLeave=true,","")&amp;IF(G394&lt;&gt;"","szName="""&amp;G394&amp;""",","")&amp;IF(H394&lt;&gt;"","tKungFu={"&amp;H394&amp;"},","")&amp;IF(I394&lt;&gt;"","szNote="""&amp;I394&amp;""",","")&amp;IF(J394&lt;&gt;"","col={"&amp;J394&amp;"},","")&amp;"[3]={"&amp;IF(K394&lt;&gt;"","tMark={"&amp;K394&amp;"},","")&amp;IF(L394&lt;&gt;"","szVoice="""&amp;L394&amp;""",","")&amp;IF(M394&gt;0,"bTeamChannel=true,","")&amp;IF(N394&gt;0,"bWhisperChannel=true,","")&amp;IF(O394&gt;0,"bCenterAlarm=true,","")&amp;IF(P394&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q394&lt;&gt;"","szVoice="""&amp;Q394&amp;""",","")&amp;IF(R394&gt;0,"bTeamChannel=true,","")&amp;IF(S394&gt;0,"bWhisperChannel=true,","")&amp;IF(T394&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U394&lt;&gt;"","aFocus={"&amp;U394&amp;"},","")&amp;IF(W394&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W394:ZZ394)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=124114,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
@@ -33481,7 +33481,7 @@
         <v>1681</v>
       </c>
       <c r="V395" t="str">
-        <f>IF(ISBLANK(B395)=FALSE,IF(ISBLANK(B394),"},["&amp;B395&amp;"]={","["&amp;B395&amp;"]={"),IF(AND(ISBLANK(B395),ISBLANK(D395),ISBLANK(C395),OR(ISBLANK(B394)=FALSE,ISBLANK(D394)=FALSE,ISBLANK(C394)=FALSE)),"},},}",IF(ISBLANK(C395),"","{dwID="&amp;C395&amp;","&amp;"nFrame="&amp;D395&amp;","&amp;IF(E395&gt;0,"nCount="&amp;E395&amp;",","")&amp;IF(F395&gt;0,"bAllLeave=true,","")&amp;IF(G395&lt;&gt;"","szName="""&amp;G395&amp;""",","")&amp;IF(H395&lt;&gt;"","tKungFu={"&amp;H395&amp;"},","")&amp;IF(I395&lt;&gt;"","szNote="""&amp;I395&amp;""",","")&amp;IF(J395&lt;&gt;"","col={"&amp;J395&amp;"},","")&amp;"[3]={"&amp;IF(K395&lt;&gt;"","tMark={"&amp;K395&amp;"},","")&amp;IF(L395&lt;&gt;"","szVoice="""&amp;L395&amp;""",","")&amp;IF(M395&gt;0,"bTeamChannel=true,","")&amp;IF(N395&gt;0,"bWhisperChannel=true,","")&amp;IF(O395&gt;0,"bCenterAlarm=true,","")&amp;IF(P395&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q395&lt;&gt;"","szVoice="""&amp;Q395&amp;""",","")&amp;IF(R395&gt;0,"bTeamChannel=true,","")&amp;IF(S395&gt;0,"bWhisperChannel=true,","")&amp;IF(T395&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U395&lt;&gt;"","aFocus={"&amp;U395&amp;"},","")&amp;IF(W395&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W395:ZZ395)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=124115,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
@@ -33499,7 +33499,7 @@
         <v>1681</v>
       </c>
       <c r="V396" t="str">
-        <f>IF(ISBLANK(B396)=FALSE,IF(ISBLANK(B395),"},["&amp;B396&amp;"]={","["&amp;B396&amp;"]={"),IF(AND(ISBLANK(B396),ISBLANK(D396),ISBLANK(C396),OR(ISBLANK(B395)=FALSE,ISBLANK(D395)=FALSE,ISBLANK(C395)=FALSE)),"},},}",IF(ISBLANK(C396),"","{dwID="&amp;C396&amp;","&amp;"nFrame="&amp;D396&amp;","&amp;IF(E396&gt;0,"nCount="&amp;E396&amp;",","")&amp;IF(F396&gt;0,"bAllLeave=true,","")&amp;IF(G396&lt;&gt;"","szName="""&amp;G396&amp;""",","")&amp;IF(H396&lt;&gt;"","tKungFu={"&amp;H396&amp;"},","")&amp;IF(I396&lt;&gt;"","szNote="""&amp;I396&amp;""",","")&amp;IF(J396&lt;&gt;"","col={"&amp;J396&amp;"},","")&amp;"[3]={"&amp;IF(K396&lt;&gt;"","tMark={"&amp;K396&amp;"},","")&amp;IF(L396&lt;&gt;"","szVoice="""&amp;L396&amp;""",","")&amp;IF(M396&gt;0,"bTeamChannel=true,","")&amp;IF(N396&gt;0,"bWhisperChannel=true,","")&amp;IF(O396&gt;0,"bCenterAlarm=true,","")&amp;IF(P396&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q396&lt;&gt;"","szVoice="""&amp;Q396&amp;""",","")&amp;IF(R396&gt;0,"bTeamChannel=true,","")&amp;IF(S396&gt;0,"bWhisperChannel=true,","")&amp;IF(T396&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U396&lt;&gt;"","aFocus={"&amp;U396&amp;"},","")&amp;IF(W396&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W396:ZZ396)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=124116,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
@@ -33517,7 +33517,7 @@
         <v>1681</v>
       </c>
       <c r="V397" t="str">
-        <f>IF(ISBLANK(B397)=FALSE,IF(ISBLANK(B396),"},["&amp;B397&amp;"]={","["&amp;B397&amp;"]={"),IF(AND(ISBLANK(B397),ISBLANK(D397),ISBLANK(C397),OR(ISBLANK(B396)=FALSE,ISBLANK(D396)=FALSE,ISBLANK(C396)=FALSE)),"},},}",IF(ISBLANK(C397),"","{dwID="&amp;C397&amp;","&amp;"nFrame="&amp;D397&amp;","&amp;IF(E397&gt;0,"nCount="&amp;E397&amp;",","")&amp;IF(F397&gt;0,"bAllLeave=true,","")&amp;IF(G397&lt;&gt;"","szName="""&amp;G397&amp;""",","")&amp;IF(H397&lt;&gt;"","tKungFu={"&amp;H397&amp;"},","")&amp;IF(I397&lt;&gt;"","szNote="""&amp;I397&amp;""",","")&amp;IF(J397&lt;&gt;"","col={"&amp;J397&amp;"},","")&amp;"[3]={"&amp;IF(K397&lt;&gt;"","tMark={"&amp;K397&amp;"},","")&amp;IF(L397&lt;&gt;"","szVoice="""&amp;L397&amp;""",","")&amp;IF(M397&gt;0,"bTeamChannel=true,","")&amp;IF(N397&gt;0,"bWhisperChannel=true,","")&amp;IF(O397&gt;0,"bCenterAlarm=true,","")&amp;IF(P397&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q397&lt;&gt;"","szVoice="""&amp;Q397&amp;""",","")&amp;IF(R397&gt;0,"bTeamChannel=true,","")&amp;IF(S397&gt;0,"bWhisperChannel=true,","")&amp;IF(T397&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U397&lt;&gt;"","aFocus={"&amp;U397&amp;"},","")&amp;IF(W397&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W397:ZZ397)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=124117,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
@@ -33535,7 +33535,7 @@
         <v>1681</v>
       </c>
       <c r="V398" t="str">
-        <f>IF(ISBLANK(B398)=FALSE,IF(ISBLANK(B397),"},["&amp;B398&amp;"]={","["&amp;B398&amp;"]={"),IF(AND(ISBLANK(B398),ISBLANK(D398),ISBLANK(C398),OR(ISBLANK(B397)=FALSE,ISBLANK(D397)=FALSE,ISBLANK(C397)=FALSE)),"},},}",IF(ISBLANK(C398),"","{dwID="&amp;C398&amp;","&amp;"nFrame="&amp;D398&amp;","&amp;IF(E398&gt;0,"nCount="&amp;E398&amp;",","")&amp;IF(F398&gt;0,"bAllLeave=true,","")&amp;IF(G398&lt;&gt;"","szName="""&amp;G398&amp;""",","")&amp;IF(H398&lt;&gt;"","tKungFu={"&amp;H398&amp;"},","")&amp;IF(I398&lt;&gt;"","szNote="""&amp;I398&amp;""",","")&amp;IF(J398&lt;&gt;"","col={"&amp;J398&amp;"},","")&amp;"[3]={"&amp;IF(K398&lt;&gt;"","tMark={"&amp;K398&amp;"},","")&amp;IF(L398&lt;&gt;"","szVoice="""&amp;L398&amp;""",","")&amp;IF(M398&gt;0,"bTeamChannel=true,","")&amp;IF(N398&gt;0,"bWhisperChannel=true,","")&amp;IF(O398&gt;0,"bCenterAlarm=true,","")&amp;IF(P398&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q398&lt;&gt;"","szVoice="""&amp;Q398&amp;""",","")&amp;IF(R398&gt;0,"bTeamChannel=true,","")&amp;IF(S398&gt;0,"bWhisperChannel=true,","")&amp;IF(T398&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U398&lt;&gt;"","aFocus={"&amp;U398&amp;"},","")&amp;IF(W398&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W398:ZZ398)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=124118,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
@@ -33553,7 +33553,7 @@
         <v>1681</v>
       </c>
       <c r="V399" t="str">
-        <f>IF(ISBLANK(B399)=FALSE,IF(ISBLANK(B398),"},["&amp;B399&amp;"]={","["&amp;B399&amp;"]={"),IF(AND(ISBLANK(B399),ISBLANK(D399),ISBLANK(C399),OR(ISBLANK(B398)=FALSE,ISBLANK(D398)=FALSE,ISBLANK(C398)=FALSE)),"},},}",IF(ISBLANK(C399),"","{dwID="&amp;C399&amp;","&amp;"nFrame="&amp;D399&amp;","&amp;IF(E399&gt;0,"nCount="&amp;E399&amp;",","")&amp;IF(F399&gt;0,"bAllLeave=true,","")&amp;IF(G399&lt;&gt;"","szName="""&amp;G399&amp;""",","")&amp;IF(H399&lt;&gt;"","tKungFu={"&amp;H399&amp;"},","")&amp;IF(I399&lt;&gt;"","szNote="""&amp;I399&amp;""",","")&amp;IF(J399&lt;&gt;"","col={"&amp;J399&amp;"},","")&amp;"[3]={"&amp;IF(K399&lt;&gt;"","tMark={"&amp;K399&amp;"},","")&amp;IF(L399&lt;&gt;"","szVoice="""&amp;L399&amp;""",","")&amp;IF(M399&gt;0,"bTeamChannel=true,","")&amp;IF(N399&gt;0,"bWhisperChannel=true,","")&amp;IF(O399&gt;0,"bCenterAlarm=true,","")&amp;IF(P399&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q399&lt;&gt;"","szVoice="""&amp;Q399&amp;""",","")&amp;IF(R399&gt;0,"bTeamChannel=true,","")&amp;IF(S399&gt;0,"bWhisperChannel=true,","")&amp;IF(T399&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U399&lt;&gt;"","aFocus={"&amp;U399&amp;"},","")&amp;IF(W399&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W399:ZZ399)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=124119,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
@@ -33571,7 +33571,7 @@
         <v>1681</v>
       </c>
       <c r="V400" t="str">
-        <f>IF(ISBLANK(B400)=FALSE,IF(ISBLANK(B399),"},["&amp;B400&amp;"]={","["&amp;B400&amp;"]={"),IF(AND(ISBLANK(B400),ISBLANK(D400),ISBLANK(C400),OR(ISBLANK(B399)=FALSE,ISBLANK(D399)=FALSE,ISBLANK(C399)=FALSE)),"},},}",IF(ISBLANK(C400),"","{dwID="&amp;C400&amp;","&amp;"nFrame="&amp;D400&amp;","&amp;IF(E400&gt;0,"nCount="&amp;E400&amp;",","")&amp;IF(F400&gt;0,"bAllLeave=true,","")&amp;IF(G400&lt;&gt;"","szName="""&amp;G400&amp;""",","")&amp;IF(H400&lt;&gt;"","tKungFu={"&amp;H400&amp;"},","")&amp;IF(I400&lt;&gt;"","szNote="""&amp;I400&amp;""",","")&amp;IF(J400&lt;&gt;"","col={"&amp;J400&amp;"},","")&amp;"[3]={"&amp;IF(K400&lt;&gt;"","tMark={"&amp;K400&amp;"},","")&amp;IF(L400&lt;&gt;"","szVoice="""&amp;L400&amp;""",","")&amp;IF(M400&gt;0,"bTeamChannel=true,","")&amp;IF(N400&gt;0,"bWhisperChannel=true,","")&amp;IF(O400&gt;0,"bCenterAlarm=true,","")&amp;IF(P400&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q400&lt;&gt;"","szVoice="""&amp;Q400&amp;""",","")&amp;IF(R400&gt;0,"bTeamChannel=true,","")&amp;IF(S400&gt;0,"bWhisperChannel=true,","")&amp;IF(T400&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U400&lt;&gt;"","aFocus={"&amp;U400&amp;"},","")&amp;IF(W400&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W400:ZZ400)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=124120,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
@@ -33589,7 +33589,7 @@
         <v>1681</v>
       </c>
       <c r="V401" t="str">
-        <f>IF(ISBLANK(B401)=FALSE,IF(ISBLANK(B400),"},["&amp;B401&amp;"]={","["&amp;B401&amp;"]={"),IF(AND(ISBLANK(B401),ISBLANK(D401),ISBLANK(C401),OR(ISBLANK(B400)=FALSE,ISBLANK(D400)=FALSE,ISBLANK(C400)=FALSE)),"},},}",IF(ISBLANK(C401),"","{dwID="&amp;C401&amp;","&amp;"nFrame="&amp;D401&amp;","&amp;IF(E401&gt;0,"nCount="&amp;E401&amp;",","")&amp;IF(F401&gt;0,"bAllLeave=true,","")&amp;IF(G401&lt;&gt;"","szName="""&amp;G401&amp;""",","")&amp;IF(H401&lt;&gt;"","tKungFu={"&amp;H401&amp;"},","")&amp;IF(I401&lt;&gt;"","szNote="""&amp;I401&amp;""",","")&amp;IF(J401&lt;&gt;"","col={"&amp;J401&amp;"},","")&amp;"[3]={"&amp;IF(K401&lt;&gt;"","tMark={"&amp;K401&amp;"},","")&amp;IF(L401&lt;&gt;"","szVoice="""&amp;L401&amp;""",","")&amp;IF(M401&gt;0,"bTeamChannel=true,","")&amp;IF(N401&gt;0,"bWhisperChannel=true,","")&amp;IF(O401&gt;0,"bCenterAlarm=true,","")&amp;IF(P401&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q401&lt;&gt;"","szVoice="""&amp;Q401&amp;""",","")&amp;IF(R401&gt;0,"bTeamChannel=true,","")&amp;IF(S401&gt;0,"bWhisperChannel=true,","")&amp;IF(T401&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U401&lt;&gt;"","aFocus={"&amp;U401&amp;"},","")&amp;IF(W401&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W401:ZZ401)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=124121,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
@@ -33607,7 +33607,7 @@
         <v>1681</v>
       </c>
       <c r="V402" t="str">
-        <f>IF(ISBLANK(B402)=FALSE,IF(ISBLANK(B401),"},["&amp;B402&amp;"]={","["&amp;B402&amp;"]={"),IF(AND(ISBLANK(B402),ISBLANK(D402),ISBLANK(C402),OR(ISBLANK(B401)=FALSE,ISBLANK(D401)=FALSE,ISBLANK(C401)=FALSE)),"},},}",IF(ISBLANK(C402),"","{dwID="&amp;C402&amp;","&amp;"nFrame="&amp;D402&amp;","&amp;IF(E402&gt;0,"nCount="&amp;E402&amp;",","")&amp;IF(F402&gt;0,"bAllLeave=true,","")&amp;IF(G402&lt;&gt;"","szName="""&amp;G402&amp;""",","")&amp;IF(H402&lt;&gt;"","tKungFu={"&amp;H402&amp;"},","")&amp;IF(I402&lt;&gt;"","szNote="""&amp;I402&amp;""",","")&amp;IF(J402&lt;&gt;"","col={"&amp;J402&amp;"},","")&amp;"[3]={"&amp;IF(K402&lt;&gt;"","tMark={"&amp;K402&amp;"},","")&amp;IF(L402&lt;&gt;"","szVoice="""&amp;L402&amp;""",","")&amp;IF(M402&gt;0,"bTeamChannel=true,","")&amp;IF(N402&gt;0,"bWhisperChannel=true,","")&amp;IF(O402&gt;0,"bCenterAlarm=true,","")&amp;IF(P402&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q402&lt;&gt;"","szVoice="""&amp;Q402&amp;""",","")&amp;IF(R402&gt;0,"bTeamChannel=true,","")&amp;IF(S402&gt;0,"bWhisperChannel=true,","")&amp;IF(T402&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U402&lt;&gt;"","aFocus={"&amp;U402&amp;"},","")&amp;IF(W402&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W402:ZZ402)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=124122,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
@@ -33625,7 +33625,7 @@
         <v>1681</v>
       </c>
       <c r="V403" t="str">
-        <f>IF(ISBLANK(B403)=FALSE,IF(ISBLANK(B402),"},["&amp;B403&amp;"]={","["&amp;B403&amp;"]={"),IF(AND(ISBLANK(B403),ISBLANK(D403),ISBLANK(C403),OR(ISBLANK(B402)=FALSE,ISBLANK(D402)=FALSE,ISBLANK(C402)=FALSE)),"},},}",IF(ISBLANK(C403),"","{dwID="&amp;C403&amp;","&amp;"nFrame="&amp;D403&amp;","&amp;IF(E403&gt;0,"nCount="&amp;E403&amp;",","")&amp;IF(F403&gt;0,"bAllLeave=true,","")&amp;IF(G403&lt;&gt;"","szName="""&amp;G403&amp;""",","")&amp;IF(H403&lt;&gt;"","tKungFu={"&amp;H403&amp;"},","")&amp;IF(I403&lt;&gt;"","szNote="""&amp;I403&amp;""",","")&amp;IF(J403&lt;&gt;"","col={"&amp;J403&amp;"},","")&amp;"[3]={"&amp;IF(K403&lt;&gt;"","tMark={"&amp;K403&amp;"},","")&amp;IF(L403&lt;&gt;"","szVoice="""&amp;L403&amp;""",","")&amp;IF(M403&gt;0,"bTeamChannel=true,","")&amp;IF(N403&gt;0,"bWhisperChannel=true,","")&amp;IF(O403&gt;0,"bCenterAlarm=true,","")&amp;IF(P403&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q403&lt;&gt;"","szVoice="""&amp;Q403&amp;""",","")&amp;IF(R403&gt;0,"bTeamChannel=true,","")&amp;IF(S403&gt;0,"bWhisperChannel=true,","")&amp;IF(T403&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U403&lt;&gt;"","aFocus={"&amp;U403&amp;"},","")&amp;IF(W403&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W403:ZZ403)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=124123,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
@@ -33643,7 +33643,7 @@
         <v>1681</v>
       </c>
       <c r="V404" t="str">
-        <f>IF(ISBLANK(B404)=FALSE,IF(ISBLANK(B403),"},["&amp;B404&amp;"]={","["&amp;B404&amp;"]={"),IF(AND(ISBLANK(B404),ISBLANK(D404),ISBLANK(C404),OR(ISBLANK(B403)=FALSE,ISBLANK(D403)=FALSE,ISBLANK(C403)=FALSE)),"},},}",IF(ISBLANK(C404),"","{dwID="&amp;C404&amp;","&amp;"nFrame="&amp;D404&amp;","&amp;IF(E404&gt;0,"nCount="&amp;E404&amp;",","")&amp;IF(F404&gt;0,"bAllLeave=true,","")&amp;IF(G404&lt;&gt;"","szName="""&amp;G404&amp;""",","")&amp;IF(H404&lt;&gt;"","tKungFu={"&amp;H404&amp;"},","")&amp;IF(I404&lt;&gt;"","szNote="""&amp;I404&amp;""",","")&amp;IF(J404&lt;&gt;"","col={"&amp;J404&amp;"},","")&amp;"[3]={"&amp;IF(K404&lt;&gt;"","tMark={"&amp;K404&amp;"},","")&amp;IF(L404&lt;&gt;"","szVoice="""&amp;L404&amp;""",","")&amp;IF(M404&gt;0,"bTeamChannel=true,","")&amp;IF(N404&gt;0,"bWhisperChannel=true,","")&amp;IF(O404&gt;0,"bCenterAlarm=true,","")&amp;IF(P404&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q404&lt;&gt;"","szVoice="""&amp;Q404&amp;""",","")&amp;IF(R404&gt;0,"bTeamChannel=true,","")&amp;IF(S404&gt;0,"bWhisperChannel=true,","")&amp;IF(T404&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U404&lt;&gt;"","aFocus={"&amp;U404&amp;"},","")&amp;IF(W404&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W404:ZZ404)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=124124,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
@@ -33661,7 +33661,7 @@
         <v>1989</v>
       </c>
       <c r="V405" t="str">
-        <f>IF(ISBLANK(B405)=FALSE,IF(ISBLANK(B404),"},["&amp;B405&amp;"]={","["&amp;B405&amp;"]={"),IF(AND(ISBLANK(B405),ISBLANK(D405),ISBLANK(C405),OR(ISBLANK(B404)=FALSE,ISBLANK(D404)=FALSE,ISBLANK(C404)=FALSE)),"},},}",IF(ISBLANK(C405),"","{dwID="&amp;C405&amp;","&amp;"nFrame="&amp;D405&amp;","&amp;IF(E405&gt;0,"nCount="&amp;E405&amp;",","")&amp;IF(F405&gt;0,"bAllLeave=true,","")&amp;IF(G405&lt;&gt;"","szName="""&amp;G405&amp;""",","")&amp;IF(H405&lt;&gt;"","tKungFu={"&amp;H405&amp;"},","")&amp;IF(I405&lt;&gt;"","szNote="""&amp;I405&amp;""",","")&amp;IF(J405&lt;&gt;"","col={"&amp;J405&amp;"},","")&amp;"[3]={"&amp;IF(K405&lt;&gt;"","tMark={"&amp;K405&amp;"},","")&amp;IF(L405&lt;&gt;"","szVoice="""&amp;L405&amp;""",","")&amp;IF(M405&gt;0,"bTeamChannel=true,","")&amp;IF(N405&gt;0,"bWhisperChannel=true,","")&amp;IF(O405&gt;0,"bCenterAlarm=true,","")&amp;IF(P405&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q405&lt;&gt;"","szVoice="""&amp;Q405&amp;""",","")&amp;IF(R405&gt;0,"bTeamChannel=true,","")&amp;IF(S405&gt;0,"bWhisperChannel=true,","")&amp;IF(T405&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U405&lt;&gt;"","aFocus={"&amp;U405&amp;"},","")&amp;IF(W405&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W405:ZZ405)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=123871,nFrame=47,szNote="小珍",[3]={},[4]={},aFocus={{dwMapID=-1,szDisplay="分线·传送",nMaxDistance=12,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
@@ -33679,7 +33679,7 @@
         <v>1989</v>
       </c>
       <c r="V406" t="str">
-        <f>IF(ISBLANK(B406)=FALSE,IF(ISBLANK(B405),"},["&amp;B406&amp;"]={","["&amp;B406&amp;"]={"),IF(AND(ISBLANK(B406),ISBLANK(D406),ISBLANK(C406),OR(ISBLANK(B405)=FALSE,ISBLANK(D405)=FALSE,ISBLANK(C405)=FALSE)),"},},}",IF(ISBLANK(C406),"","{dwID="&amp;C406&amp;","&amp;"nFrame="&amp;D406&amp;","&amp;IF(E406&gt;0,"nCount="&amp;E406&amp;",","")&amp;IF(F406&gt;0,"bAllLeave=true,","")&amp;IF(G406&lt;&gt;"","szName="""&amp;G406&amp;""",","")&amp;IF(H406&lt;&gt;"","tKungFu={"&amp;H406&amp;"},","")&amp;IF(I406&lt;&gt;"","szNote="""&amp;I406&amp;""",","")&amp;IF(J406&lt;&gt;"","col={"&amp;J406&amp;"},","")&amp;"[3]={"&amp;IF(K406&lt;&gt;"","tMark={"&amp;K406&amp;"},","")&amp;IF(L406&lt;&gt;"","szVoice="""&amp;L406&amp;""",","")&amp;IF(M406&gt;0,"bTeamChannel=true,","")&amp;IF(N406&gt;0,"bWhisperChannel=true,","")&amp;IF(O406&gt;0,"bCenterAlarm=true,","")&amp;IF(P406&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q406&lt;&gt;"","szVoice="""&amp;Q406&amp;""",","")&amp;IF(R406&gt;0,"bTeamChannel=true,","")&amp;IF(S406&gt;0,"bWhisperChannel=true,","")&amp;IF(T406&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U406&lt;&gt;"","aFocus={"&amp;U406&amp;"},","")&amp;IF(W406&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W406:ZZ406)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=123867,nFrame=47,szNote="小曾",[3]={},[4]={},aFocus={{dwMapID=-1,szDisplay="分线·传送",nMaxDistance=12,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
@@ -33703,7 +33703,7 @@
         <v>1687</v>
       </c>
       <c r="V407" t="str">
-        <f>IF(ISBLANK(B407)=FALSE,IF(ISBLANK(B406),"},["&amp;B407&amp;"]={","["&amp;B407&amp;"]={"),IF(AND(ISBLANK(B407),ISBLANK(D407),ISBLANK(C407),OR(ISBLANK(B406)=FALSE,ISBLANK(D406)=FALSE,ISBLANK(C406)=FALSE)),"},},}",IF(ISBLANK(C407),"","{dwID="&amp;C407&amp;","&amp;"nFrame="&amp;D407&amp;","&amp;IF(E407&gt;0,"nCount="&amp;E407&amp;",","")&amp;IF(F407&gt;0,"bAllLeave=true,","")&amp;IF(G407&lt;&gt;"","szName="""&amp;G407&amp;""",","")&amp;IF(H407&lt;&gt;"","tKungFu={"&amp;H407&amp;"},","")&amp;IF(I407&lt;&gt;"","szNote="""&amp;I407&amp;""",","")&amp;IF(J407&lt;&gt;"","col={"&amp;J407&amp;"},","")&amp;"[3]={"&amp;IF(K407&lt;&gt;"","tMark={"&amp;K407&amp;"},","")&amp;IF(L407&lt;&gt;"","szVoice="""&amp;L407&amp;""",","")&amp;IF(M407&gt;0,"bTeamChannel=true,","")&amp;IF(N407&gt;0,"bWhisperChannel=true,","")&amp;IF(O407&gt;0,"bCenterAlarm=true,","")&amp;IF(P407&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q407&lt;&gt;"","szVoice="""&amp;Q407&amp;""",","")&amp;IF(R407&gt;0,"bTeamChannel=true,","")&amp;IF(S407&gt;0,"bWhisperChannel=true,","")&amp;IF(T407&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U407&lt;&gt;"","aFocus={"&amp;U407&amp;"},","")&amp;IF(W407&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W407:ZZ407)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=66809,nFrame=57,szName="火圈",szNote="减疗火圈",[3]={bCenterAlarm=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="火圈·减疗",nMaxDistance=8,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
@@ -33730,7 +33730,7 @@
         <v>1711</v>
       </c>
       <c r="V408" t="str">
-        <f>IF(ISBLANK(B408)=FALSE,IF(ISBLANK(B407),"},["&amp;B408&amp;"]={","["&amp;B408&amp;"]={"),IF(AND(ISBLANK(B408),ISBLANK(D408),ISBLANK(C408),OR(ISBLANK(B407)=FALSE,ISBLANK(D407)=FALSE,ISBLANK(C407)=FALSE)),"},},}",IF(ISBLANK(C408),"","{dwID="&amp;C408&amp;","&amp;"nFrame="&amp;D408&amp;","&amp;IF(E408&gt;0,"nCount="&amp;E408&amp;",","")&amp;IF(F408&gt;0,"bAllLeave=true,","")&amp;IF(G408&lt;&gt;"","szName="""&amp;G408&amp;""",","")&amp;IF(H408&lt;&gt;"","tKungFu={"&amp;H408&amp;"},","")&amp;IF(I408&lt;&gt;"","szNote="""&amp;I408&amp;""",","")&amp;IF(J408&lt;&gt;"","col={"&amp;J408&amp;"},","")&amp;"[3]={"&amp;IF(K408&lt;&gt;"","tMark={"&amp;K408&amp;"},","")&amp;IF(L408&lt;&gt;"","szVoice="""&amp;L408&amp;""",","")&amp;IF(M408&gt;0,"bTeamChannel=true,","")&amp;IF(N408&gt;0,"bWhisperChannel=true,","")&amp;IF(O408&gt;0,"bCenterAlarm=true,","")&amp;IF(P408&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q408&lt;&gt;"","szVoice="""&amp;Q408&amp;""",","")&amp;IF(R408&gt;0,"bTeamChannel=true,","")&amp;IF(S408&gt;0,"bWhisperChannel=true,","")&amp;IF(T408&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U408&lt;&gt;"","aFocus={"&amp;U408&amp;"},","")&amp;IF(W408&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W408:ZZ408)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=36396,nFrame=52,szName="神机台·有人",szNote="神机台·有人状态",[3]={bCenterAlarm=true,bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="神机台·敌方",nMaxDistance=60,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},{dwMapID=-1,szDisplay="神机台·有人",nMaxDistance=60,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nFrame=1,nIcon=361,nTime=10,szName="神机台·已摧毁",},},},</v>
       </c>
       <c r="W408" t="s">
@@ -33754,7 +33754,7 @@
         <v>1714</v>
       </c>
       <c r="V409" t="str">
-        <f>IF(ISBLANK(B409)=FALSE,IF(ISBLANK(B408),"},["&amp;B409&amp;"]={","["&amp;B409&amp;"]={"),IF(AND(ISBLANK(B409),ISBLANK(D409),ISBLANK(C409),OR(ISBLANK(B408)=FALSE,ISBLANK(D408)=FALSE,ISBLANK(C408)=FALSE)),"},},}",IF(ISBLANK(C409),"","{dwID="&amp;C409&amp;","&amp;"nFrame="&amp;D409&amp;","&amp;IF(E409&gt;0,"nCount="&amp;E409&amp;",","")&amp;IF(F409&gt;0,"bAllLeave=true,","")&amp;IF(G409&lt;&gt;"","szName="""&amp;G409&amp;""",","")&amp;IF(H409&lt;&gt;"","tKungFu={"&amp;H409&amp;"},","")&amp;IF(I409&lt;&gt;"","szNote="""&amp;I409&amp;""",","")&amp;IF(J409&lt;&gt;"","col={"&amp;J409&amp;"},","")&amp;"[3]={"&amp;IF(K409&lt;&gt;"","tMark={"&amp;K409&amp;"},","")&amp;IF(L409&lt;&gt;"","szVoice="""&amp;L409&amp;""",","")&amp;IF(M409&gt;0,"bTeamChannel=true,","")&amp;IF(N409&gt;0,"bWhisperChannel=true,","")&amp;IF(O409&gt;0,"bCenterAlarm=true,","")&amp;IF(P409&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q409&lt;&gt;"","szVoice="""&amp;Q409&amp;""",","")&amp;IF(R409&gt;0,"bTeamChannel=true,","")&amp;IF(S409&gt;0,"bWhisperChannel=true,","")&amp;IF(T409&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U409&lt;&gt;"","aFocus={"&amp;U409&amp;"},","")&amp;IF(W409&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W409:ZZ409)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=36005,nFrame=52,szNote="神机台·没人状态",[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},},},</v>
       </c>
     </row>
@@ -33775,7 +33775,7 @@
         <v>1716</v>
       </c>
       <c r="V410" t="str">
-        <f>IF(ISBLANK(B410)=FALSE,IF(ISBLANK(B409),"},["&amp;B410&amp;"]={","["&amp;B410&amp;"]={"),IF(AND(ISBLANK(B410),ISBLANK(D410),ISBLANK(C410),OR(ISBLANK(B409)=FALSE,ISBLANK(D409)=FALSE,ISBLANK(C409)=FALSE)),"},},}",IF(ISBLANK(C410),"","{dwID="&amp;C410&amp;","&amp;"nFrame="&amp;D410&amp;","&amp;IF(E410&gt;0,"nCount="&amp;E410&amp;",","")&amp;IF(F410&gt;0,"bAllLeave=true,","")&amp;IF(G410&lt;&gt;"","szName="""&amp;G410&amp;""",","")&amp;IF(H410&lt;&gt;"","tKungFu={"&amp;H410&amp;"},","")&amp;IF(I410&lt;&gt;"","szNote="""&amp;I410&amp;""",","")&amp;IF(J410&lt;&gt;"","col={"&amp;J410&amp;"},","")&amp;"[3]={"&amp;IF(K410&lt;&gt;"","tMark={"&amp;K410&amp;"},","")&amp;IF(L410&lt;&gt;"","szVoice="""&amp;L410&amp;""",","")&amp;IF(M410&gt;0,"bTeamChannel=true,","")&amp;IF(N410&gt;0,"bWhisperChannel=true,","")&amp;IF(O410&gt;0,"bCenterAlarm=true,","")&amp;IF(P410&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q410&lt;&gt;"","szVoice="""&amp;Q410&amp;""",","")&amp;IF(R410&gt;0,"bTeamChannel=true,","")&amp;IF(S410&gt;0,"bWhisperChannel=true,","")&amp;IF(T410&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U410&lt;&gt;"","aFocus={"&amp;U410&amp;"},","")&amp;IF(W410&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W410:ZZ410)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=100133,nFrame=57,szNote="狼牙先锋首领",[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=90,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
@@ -33799,13 +33799,13 @@
         <v>1726</v>
       </c>
       <c r="V411" t="str">
-        <f>IF(ISBLANK(B411)=FALSE,IF(ISBLANK(B410),"},["&amp;B411&amp;"]={","["&amp;B411&amp;"]={"),IF(AND(ISBLANK(B411),ISBLANK(D411),ISBLANK(C411),OR(ISBLANK(B410)=FALSE,ISBLANK(D410)=FALSE,ISBLANK(C410)=FALSE)),"},},}",IF(ISBLANK(C411),"","{dwID="&amp;C411&amp;","&amp;"nFrame="&amp;D411&amp;","&amp;IF(E411&gt;0,"nCount="&amp;E411&amp;",","")&amp;IF(F411&gt;0,"bAllLeave=true,","")&amp;IF(G411&lt;&gt;"","szName="""&amp;G411&amp;""",","")&amp;IF(H411&lt;&gt;"","tKungFu={"&amp;H411&amp;"},","")&amp;IF(I411&lt;&gt;"","szNote="""&amp;I411&amp;""",","")&amp;IF(J411&lt;&gt;"","col={"&amp;J411&amp;"},","")&amp;"[3]={"&amp;IF(K411&lt;&gt;"","tMark={"&amp;K411&amp;"},","")&amp;IF(L411&lt;&gt;"","szVoice="""&amp;L411&amp;""",","")&amp;IF(M411&gt;0,"bTeamChannel=true,","")&amp;IF(N411&gt;0,"bWhisperChannel=true,","")&amp;IF(O411&gt;0,"bCenterAlarm=true,","")&amp;IF(P411&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q411&lt;&gt;"","szVoice="""&amp;Q411&amp;""",","")&amp;IF(R411&gt;0,"bTeamChannel=true,","")&amp;IF(S411&gt;0,"bWhisperChannel=true,","")&amp;IF(T411&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U411&lt;&gt;"","aFocus={"&amp;U411&amp;"},","")&amp;IF(W411&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W411:ZZ411)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>{dwID=30537,nFrame=47,szNote="据点伙计",col={100,255,100,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=10,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},},</v>
       </c>
     </row>
     <row r="412" spans="3:23">
       <c r="V412" t="str">
-        <f>IF(ISBLANK(B412)=FALSE,IF(ISBLANK(B411),"},["&amp;B412&amp;"]={","["&amp;B412&amp;"]={"),IF(AND(ISBLANK(B412),ISBLANK(D412),ISBLANK(C412),OR(ISBLANK(B411)=FALSE,ISBLANK(D411)=FALSE,ISBLANK(C411)=FALSE)),"},},}",IF(ISBLANK(C412),"","{dwID="&amp;C412&amp;","&amp;"nFrame="&amp;D412&amp;","&amp;IF(E412&gt;0,"nCount="&amp;E412&amp;",","")&amp;IF(F412&gt;0,"bAllLeave=true,","")&amp;IF(G412&lt;&gt;"","szName="""&amp;G412&amp;""",","")&amp;IF(H412&lt;&gt;"","tKungFu={"&amp;H412&amp;"},","")&amp;IF(I412&lt;&gt;"","szNote="""&amp;I412&amp;""",","")&amp;IF(J412&lt;&gt;"","col={"&amp;J412&amp;"},","")&amp;"[3]={"&amp;IF(K412&lt;&gt;"","tMark={"&amp;K412&amp;"},","")&amp;IF(L412&lt;&gt;"","szVoice="""&amp;L412&amp;""",","")&amp;IF(M412&gt;0,"bTeamChannel=true,","")&amp;IF(N412&gt;0,"bWhisperChannel=true,","")&amp;IF(O412&gt;0,"bCenterAlarm=true,","")&amp;IF(P412&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q412&lt;&gt;"","szVoice="""&amp;Q412&amp;""",","")&amp;IF(R412&gt;0,"bTeamChannel=true,","")&amp;IF(S412&gt;0,"bWhisperChannel=true,","")&amp;IF(T412&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U412&lt;&gt;"","aFocus={"&amp;U412&amp;"},","")&amp;IF(W412&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W412:ZZ412)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="6"/>
         <v>},},}</v>
       </c>
     </row>
@@ -37874,7 +37874,7 @@
       </c>
       <c r="V69" t="str">
         <f t="shared" si="24"/>
-        <v>{szContent="军情速递！恶人谷物资车已运达，车内装有大量物资，望侠士们前来拾取，切莫错过。",szTarget="%",szNote="恶人谷·物资车·已运达",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=10450,nFrame=4,szName="恶人谷·营地物资·刷新",nTime="10,恶人谷·营地物资·刷新;300,恶人谷·营地物资·拾取剩余;305,恶人谷·营地物资·已消失",nRefresh=0,key="恶人·物资车·运达",},},},</v>
+        <v>{szContent="军情速递！恶人谷物资车已运达，车内装有大量物资，望侠士们前来拾取，切莫错过。",szTarget="%",szNote="恶人谷·物资车·已运达",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=10450,nFrame=4,szName="恶人谷·营地物资·已刷新",nTime="10,恶人谷·营地物资·已刷新;300,恶人谷·营地物资·拾取剩余;305,恶人谷·营地物资·已消失",nRefresh=0,key="恶人·物资车·运达",},},},</v>
       </c>
       <c r="W69" t="s">
         <v>2214</v>
@@ -37896,7 +37896,7 @@
       </c>
       <c r="V70" t="str">
         <f t="shared" si="24"/>
-        <v>{szContent="军情速递！浩气盟物资车已运达，车内装有大量物资，望侠士们前来拾取，切莫错过。",szTarget="%",szNote="浩气盟·物资车·已运达",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=10449,nFrame=4,szName="浩气盟·内城物资·刷新",nTime="10,浩气盟·内城物资·刷新;300,浩气盟·内城物资·拾取剩余;305,浩气盟·内城物资·已消失",nRefresh=0,key="浩气·物资车·运达",},},},</v>
+        <v>{szContent="军情速递！浩气盟物资车已运达，车内装有大量物资，望侠士们前来拾取，切莫错过。",szTarget="%",szNote="浩气盟·物资车·已运达",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=10449,nFrame=4,szName="浩气盟·内城物资·已刷新",nTime="10,浩气盟·内城物资·已刷新;300,浩气盟·内城物资·拾取剩余;305,浩气盟·内城物资·已消失",nRefresh=0,key="浩气·物资车·运达",},},},</v>
       </c>
       <c r="W70" t="s">
         <v>2217</v>
@@ -38955,7 +38955,7 @@
       </c>
       <c r="V89" t="str">
         <f t="shared" si="24"/>
-        <v>{szContent="军情速递！恶人谷物资车已运达，车内装有大量物资，望侠士们前来拾取，切莫错过。",szTarget="%",szNote="恶人谷·物资车·已运达",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=10450,nFrame=4,szName="恶人谷·内城物资·刷新",nTime="10,恶人谷·内城物资·刷新;300,恶人谷·内城物资·拾取剩余;305,恶人谷·内城物资·已消失",nRefresh=0,key="恶人·物资车·运达",},},},</v>
+        <v>{szContent="军情速递！恶人谷物资车已运达，车内装有大量物资，望侠士们前来拾取，切莫错过。",szTarget="%",szNote="恶人谷·物资车·已运达",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=10450,nFrame=4,szName="恶人谷·内城物资·已刷新",nTime="10,恶人谷·内城物资·刷新;300,恶人谷·内城物资·拾取剩余;305,恶人谷·内城物资·已消失",nRefresh=0,key="恶人·物资车·运达",},},},</v>
       </c>
       <c r="W89" t="s">
         <v>2223</v>
@@ -38977,7 +38977,7 @@
       </c>
       <c r="V90" t="str">
         <f t="shared" si="24"/>
-        <v>{szContent="军情速递！浩气盟物资车已运达，车内装有大量物资，望侠士们前来拾取，切莫错过。",szTarget="%",szNote="浩气盟·物资车·已运达",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=10449,nFrame=4,szName="浩气盟·营地物资·刷新",nTime="10,浩气盟·营地物资·刷新;300,浩气盟·营地物资·拾取剩余;305,浩气盟·营地物资·已消失",nRefresh=0,key="浩气·物资车·运达",},},},</v>
+        <v>{szContent="军情速递！浩气盟物资车已运达，车内装有大量物资，望侠士们前来拾取，切莫错过。",szTarget="%",szNote="浩气盟·物资车·已运达",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=10449,nFrame=4,szName="浩气盟·营地物资·已刷新",nTime="10,浩气盟·营地物资·刷新;300,浩气盟·营地物资·拾取剩余;305,浩气盟·营地物资·已消失",nRefresh=0,key="浩气·物资车·运达",},},},</v>
       </c>
       <c r="W90" t="s">
         <v>2224</v>
@@ -40498,7 +40498,7 @@
         <v>1</v>
       </c>
       <c r="V163" t="str">
-        <f t="shared" ref="V163:V194" si="30">IF(ISBLANK(B163)=FALSE,IF(ISBLANK(B162),"},["&amp;B163&amp;"]={","["&amp;B163&amp;"]={"),IF(AND(ISBLANK(B163),ISBLANK(D163),ISBLANK(N163),ISBLANK(O163),OR(ISBLANK(B162)=FALSE,ISBLANK(D162)=FALSE,ISBLANK(N162)=FALSE,ISBLANK(O162)=FALSE)),"},},}",IF(ISBLANK(D163),"","{szContent="""&amp;D163&amp;""","&amp;IF(C163&lt;&gt;"","szTarget="""&amp;C163&amp;""",","")&amp;IF(E163&lt;&gt;"","szNote="""&amp;E163&amp;""",","")&amp;IF(M163&lt;&gt;"","col={"&amp;M163&amp;"},","")&amp;IF(N163&gt;0,"bSearch=true,","")&amp;IF(O163&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P163&gt;0,"szVoice="""&amp;P163&amp;""",","")&amp;IF(Q163&gt;0,"bTeamChannel=true,","")&amp;IF(R163&gt;0,"bWhisperChannel=true,","")&amp;IF(S163&gt;0,"bCenterAlarm=true,","")&amp;IF(T163&gt;0,"bScreenHead=true,","")&amp;IF(U163&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W163&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W163:AAH163)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="V163:V199" si="30">IF(ISBLANK(B163)=FALSE,IF(ISBLANK(B162),"},["&amp;B163&amp;"]={","["&amp;B163&amp;"]={"),IF(AND(ISBLANK(B163),ISBLANK(D163),ISBLANK(N163),ISBLANK(O163),OR(ISBLANK(B162)=FALSE,ISBLANK(D162)=FALSE,ISBLANK(N162)=FALSE,ISBLANK(O162)=FALSE)),"},},}",IF(ISBLANK(D163),"","{szContent="""&amp;D163&amp;""","&amp;IF(C163&lt;&gt;"","szTarget="""&amp;C163&amp;""",","")&amp;IF(E163&lt;&gt;"","szNote="""&amp;E163&amp;""",","")&amp;IF(M163&lt;&gt;"","col={"&amp;M163&amp;"},","")&amp;IF(N163&gt;0,"bSearch=true,","")&amp;IF(O163&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P163&gt;0,"szVoice="""&amp;P163&amp;""",","")&amp;IF(Q163&gt;0,"bTeamChannel=true,","")&amp;IF(R163&gt;0,"bWhisperChannel=true,","")&amp;IF(S163&gt;0,"bCenterAlarm=true,","")&amp;IF(T163&gt;0,"bScreenHead=true,","")&amp;IF(U163&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W163&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W163:AAH163)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="增援已至秋雨堡，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·秋雨堡",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·秋雨堡",nTime="10,浩气·兵符增援·秋雨堡;300,浩气·秋雨堡·兵符冷却;305,浩气·秋雨堡·可用兵符",nRefresh=1,key="兵符·秋雨堡",},},},</v>
       </c>
       <c r="W163" t="s">
@@ -41258,7 +41258,7 @@
         <v>2289</v>
       </c>
       <c r="V195" t="str">
-        <f>IF(ISBLANK(B195)=FALSE,IF(ISBLANK(B194),"},["&amp;B195&amp;"]={","["&amp;B195&amp;"]={"),IF(AND(ISBLANK(B195),ISBLANK(D195),ISBLANK(N195),ISBLANK(O195),OR(ISBLANK(B194)=FALSE,ISBLANK(D194)=FALSE,ISBLANK(N194)=FALSE,ISBLANK(O194)=FALSE)),"},},}",IF(ISBLANK(D195),"","{szContent="""&amp;D195&amp;""","&amp;IF(C195&lt;&gt;"","szTarget="""&amp;C195&amp;""",","")&amp;IF(E195&lt;&gt;"","szNote="""&amp;E195&amp;""",","")&amp;IF(M195&lt;&gt;"","col={"&amp;M195&amp;"},","")&amp;IF(N195&gt;0,"bSearch=true,","")&amp;IF(O195&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P195&gt;0,"szVoice="""&amp;P195&amp;""",","")&amp;IF(Q195&gt;0,"bTeamChannel=true,","")&amp;IF(R195&gt;0,"bWhisperChannel=true,","")&amp;IF(S195&gt;0,"bCenterAlarm=true,","")&amp;IF(T195&gt;0,"bScreenHead=true,","")&amp;IF(U195&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W195&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W195:AAH195)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="30"/>
         <v>{szContent="哼，还有要事要办，今日收获甚多，来日定多来领略你们的武功！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·攻防结束",[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领·离开",nTime=0,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="W195" t="s">
@@ -41282,7 +41282,7 @@
         <v>2294</v>
       </c>
       <c r="V196" t="str">
-        <f>IF(ISBLANK(B196)=FALSE,IF(ISBLANK(B195),"},["&amp;B196&amp;"]={","["&amp;B196&amp;"]={"),IF(AND(ISBLANK(B196),ISBLANK(D196),ISBLANK(N196),ISBLANK(O196),OR(ISBLANK(B195)=FALSE,ISBLANK(D195)=FALSE,ISBLANK(N195)=FALSE,ISBLANK(O195)=FALSE)),"},},}",IF(ISBLANK(D196),"","{szContent="""&amp;D196&amp;""","&amp;IF(C196&lt;&gt;"","szTarget="""&amp;C196&amp;""",","")&amp;IF(E196&lt;&gt;"","szNote="""&amp;E196&amp;""",","")&amp;IF(M196&lt;&gt;"","col={"&amp;M196&amp;"},","")&amp;IF(N196&gt;0,"bSearch=true,","")&amp;IF(O196&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P196&gt;0,"szVoice="""&amp;P196&amp;""",","")&amp;IF(Q196&gt;0,"bTeamChannel=true,","")&amp;IF(R196&gt;0,"bWhisperChannel=true,","")&amp;IF(S196&gt;0,"bCenterAlarm=true,","")&amp;IF(T196&gt;0,"bScreenHead=true,","")&amp;IF(U196&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W196&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W196:AAH196)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="30"/>
         <v>{szContent="哼，打扰本大爷休息！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话1",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W196" t="s">
@@ -41300,7 +41300,7 @@
         <v>2297</v>
       </c>
       <c r="V197" t="str">
-        <f>IF(ISBLANK(B197)=FALSE,IF(ISBLANK(B196),"},["&amp;B197&amp;"]={","["&amp;B197&amp;"]={"),IF(AND(ISBLANK(B197),ISBLANK(D197),ISBLANK(N197),ISBLANK(O197),OR(ISBLANK(B196)=FALSE,ISBLANK(D196)=FALSE,ISBLANK(N196)=FALSE,ISBLANK(O196)=FALSE)),"},},}",IF(ISBLANK(D197),"","{szContent="""&amp;D197&amp;""","&amp;IF(C197&lt;&gt;"","szTarget="""&amp;C197&amp;""",","")&amp;IF(E197&lt;&gt;"","szNote="""&amp;E197&amp;""",","")&amp;IF(M197&lt;&gt;"","col={"&amp;M197&amp;"},","")&amp;IF(N197&gt;0,"bSearch=true,","")&amp;IF(O197&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P197&gt;0,"szVoice="""&amp;P197&amp;""",","")&amp;IF(Q197&gt;0,"bTeamChannel=true,","")&amp;IF(R197&gt;0,"bWhisperChannel=true,","")&amp;IF(S197&gt;0,"bCenterAlarm=true,","")&amp;IF(T197&gt;0,"bScreenHead=true,","")&amp;IF(U197&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W197&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W197:AAH197)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="30"/>
         <v>{szContent="你爷爷我年轻些时候，也是翻云覆雨的江湖响当当一号人物！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话2",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W197" t="s">
@@ -41324,7 +41324,7 @@
         <v>2299</v>
       </c>
       <c r="V198" t="str">
-        <f>IF(ISBLANK(B198)=FALSE,IF(ISBLANK(B197),"},["&amp;B198&amp;"]={","["&amp;B198&amp;"]={"),IF(AND(ISBLANK(B198),ISBLANK(D198),ISBLANK(N198),ISBLANK(O198),OR(ISBLANK(B197)=FALSE,ISBLANK(D197)=FALSE,ISBLANK(N197)=FALSE,ISBLANK(O197)=FALSE)),"},},}",IF(ISBLANK(D198),"","{szContent="""&amp;D198&amp;""","&amp;IF(C198&lt;&gt;"","szTarget="""&amp;C198&amp;""",","")&amp;IF(E198&lt;&gt;"","szNote="""&amp;E198&amp;""",","")&amp;IF(M198&lt;&gt;"","col={"&amp;M198&amp;"},","")&amp;IF(N198&gt;0,"bSearch=true,","")&amp;IF(O198&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P198&gt;0,"szVoice="""&amp;P198&amp;""",","")&amp;IF(Q198&gt;0,"bTeamChannel=true,","")&amp;IF(R198&gt;0,"bWhisperChannel=true,","")&amp;IF(S198&gt;0,"bCenterAlarm=true,","")&amp;IF(T198&gt;0,"bScreenHead=true,","")&amp;IF(U198&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W198&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W198:AAH198)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="30"/>
         <v>{szContent="我竟然败给你们这群小辈！",szTarget="狼牙先锋首领",szNote="防冲突禁用·击退·狼牙先锋首领",[14]={},tCountdown={{nClass=-1,nIcon=3556,nFrame=1,szName="狼牙先锋首领·拾取掉落",nTime="10,狼牙先锋首领·已击退;300,狼牙先锋首领·拾取剩余;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=2,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W198" t="s">
@@ -41339,7 +41339,7 @@
     </row>
     <row r="199" spans="3:25">
       <c r="V199" t="str">
-        <f>IF(ISBLANK(B199)=FALSE,IF(ISBLANK(B198),"},["&amp;B199&amp;"]={","["&amp;B199&amp;"]={"),IF(AND(ISBLANK(B199),ISBLANK(D199),ISBLANK(N199),ISBLANK(O199),OR(ISBLANK(B198)=FALSE,ISBLANK(D198)=FALSE,ISBLANK(N198)=FALSE,ISBLANK(O198)=FALSE)),"},},}",IF(ISBLANK(D199),"","{szContent="""&amp;D199&amp;""","&amp;IF(C199&lt;&gt;"","szTarget="""&amp;C199&amp;""",","")&amp;IF(E199&lt;&gt;"","szNote="""&amp;E199&amp;""",","")&amp;IF(M199&lt;&gt;"","col={"&amp;M199&amp;"},","")&amp;IF(N199&gt;0,"bSearch=true,","")&amp;IF(O199&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P199&gt;0,"szVoice="""&amp;P199&amp;""",","")&amp;IF(Q199&gt;0,"bTeamChannel=true,","")&amp;IF(R199&gt;0,"bWhisperChannel=true,","")&amp;IF(S199&gt;0,"bCenterAlarm=true,","")&amp;IF(T199&gt;0,"bScreenHead=true,","")&amp;IF(U199&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W199&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W199:AAH199)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="30"/>
         <v>},},}</v>
       </c>
     </row>

--- a/阵营/大小攻防团队监控.xlsx
+++ b/阵营/大小攻防团队监控.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5942" uniqueCount="2702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5942" uniqueCount="2703">
   <si>
     <t>__meta = {</t>
   </si>
@@ -6859,388 +6859,391 @@
     <t>{nClass=14,nIcon=16834,nFrame=1,szName="大旗易伤",nTime=-1,nRefresh=2,key="大旗易伤",},</t>
   </si>
   <si>
+    <t>{nClass=14,nIcon=16834,nFrame=1,szName="【{$1}】大旗·易伤{$3}层",nTime="60,【{$1}】大旗·易伤{$3}层;65,【{$1}】大旗·易伤冷却结束",nRefresh=0,key="{$1}·大旗易伤",},</t>
+  </si>
+  <si>
+    <t>您因消极怠战,扰乱阵营秩序，被阵营督查官请离当前地图，但同时给予250点贡献积分！</t>
+  </si>
+  <si>
+    <t>阵营督查官·请离据点攻防</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=1,bHold=true,nTime=30,szName="阵营督查·请离据点攻防",key="挂机检测",},</t>
+  </si>
+  <si>
+    <t>留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},</t>
+  </si>
+  <si>
+    <t>留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},</t>
+  </si>
+  <si>
+    <t>可恶！</t>
+  </si>
+  <si>
+    <t>{$sender}·退场</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},</t>
+  </si>
+  <si>
+    <t>尔等鼠辈！谁敢与我一战！</t>
+  </si>
+  <si>
+    <t>据点攻防·正式开始</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime="2,据点攻防·正式开始;10,建议关闭·江湖身份",nRefresh=2,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,szName="绣球花",nTime=-1,key="绣球花",},{nClass=14,nIcon=13,szName="郁金香",nTime=-1,key="郁金香",},{nClass=14,nIcon=13,szName="牵牛花",nTime=-1,key="牵牛花",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},</t>
+  </si>
+  <si>
+    <t>哼，还有要事要办，今日收获甚多，来日定多来领略你们的武功！</t>
+  </si>
+  <si>
+    <t>狼牙先锋首领·攻防结束</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,szName="狼牙先锋首领·离开",nTime=0,key="狼牙先锋首领",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},</t>
+  </si>
+  <si>
+    <t>哼，打扰本大爷休息！</t>
+  </si>
+  <si>
+    <t>狼牙先锋首领·刷新喊话1</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},</t>
+  </si>
+  <si>
+    <t>你爷爷我年轻些时候，也是翻云覆雨的江湖响当当一号人物！</t>
+  </si>
+  <si>
+    <t>狼牙先锋首领·刷新喊话2</t>
+  </si>
+  <si>
+    <t>我竟然败给你们这群小辈！</t>
+  </si>
+  <si>
+    <t>防冲突禁用·击退·狼牙先锋首领</t>
+  </si>
+  <si>
+    <t>{nClass=-1,nIcon=3556,nFrame=1,szName="狼牙先锋首领·拾取掉落",nTime="10,狼牙先锋首领·已击退;300,狼牙先锋首领·拾取剩余;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=2,key="狼牙先锋首领",},</t>
+  </si>
+  <si>
+    <t>浩气盟督廷卫</t>
+  </si>
+  <si>
+    <t>增援已至武王城，速速进攻！</t>
+  </si>
+  <si>
+    <t>浩气·兵符增援·武王城</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·武王城",nTime="10,浩气·兵符增援·武王城;300,浩气·武王城·兵符冷却;305,浩气·武王城·可用兵符",nRefresh=1,key="兵符·武王城",},</t>
+  </si>
+  <si>
+    <t>赵新宇死亡时，从他身上遗落一把短笛，貌似是他的随身信物。</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=589,nFrame=7,szName="赵新宇",nTime=0,key="赵新宇",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=589,nFrame=7,szName="赵新宇",nTime="60,赵新宇的信物;302,赵新宇·刷新剩余;304,赵新宇·即将刷新;310,赵新宇·延迟刷新",nRefresh=60,key="赵新宇",},</t>
+  </si>
+  <si>
+    <t>随着方超的死亡，一把短笛掉了出来，貌似是他的随身信物。</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=308,nFrame=3,szName="方超",nTime=0,key="方超",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=308,nFrame=3,szName="方超",nTime="60,方超的信物;302,方超·刷新剩余;304,方超·即将刷新;310,方超·延迟刷新",nRefresh=60,key="方超",},</t>
+  </si>
+  <si>
+    <t>赵新宇</t>
+  </si>
+  <si>
+    <t>恶人谷老友们可在我这里传送到恶人谷！</t>
+  </si>
+  <si>
+    <t>{nClass=-1,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=2,nRefresh=600,key="赵新宇",},</t>
+  </si>
+  <si>
+    <t>方超</t>
+  </si>
+  <si>
+    <t>浩气盟侠士们可在我这里传送到浩气盟！</t>
+  </si>
+  <si>
+    <t>{nClass=-1,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=2,nRefresh=600,key="方超",},</t>
+  </si>
+  <si>
+    <t>管良沧</t>
+  </si>
+  <si>
+    <t>护送不利，恶人谷的运输小队被浩气盟截下了！</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=7,szName="浩气·劫车奖励",nTime=60,key="恶人·矿车",},</t>
+  </si>
+  <si>
+    <t>恶人谷的运输小队成功到达营地！接下来由他们将物资运往更前线，大伙继续加油，收集更多物资！</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=3,szName="恶人·领取护送奖赏",nTime=60,key="恶人·矿车",},</t>
+  </si>
+  <si>
+    <t>恶人谷的运输小队出现了，大伙快前去接送到我方营地，谷主重重有赏！</t>
+  </si>
+  <si>
+    <t>粮草先行·恶人牛车</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=3,szName="恶人·护送牛车",nTime="337,恶人·护送牛车;340,恶人·延迟护送牛车",nRefresh=0,key="恶人·矿车",},</t>
+  </si>
+  <si>
+    <t>苏才寥</t>
+  </si>
+  <si>
+    <t>护送不利，浩气盟的运输小队被恶人谷截下了！</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=3,szName="恶人·劫车奖励",nTime=60,key="浩气·矿车",},</t>
+  </si>
+  <si>
+    <t>浩气盟的运输小队成功到达营地！接下来由他们将物资运往更前线，大伙继续加油，收集更多物资！</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=7,szName="浩气·领取护送奖赏",nTime=60,key="浩气·矿车",},</t>
+  </si>
+  <si>
+    <t>浩气盟的运输小队出现了，大伙快前去接送到我方营地，盟主重重有赏！</t>
+  </si>
+  <si>
+    <t>粮草先行·浩气牛车</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=7,szName="浩气·护送牛车",nTime="337,浩气·护送牛车;340,浩气·延迟护送牛车",nRefresh=0,key="浩气·矿车",},</t>
+  </si>
+  <si>
+    <t>恶人谷督廷卫</t>
+  </si>
+  <si>
+    <t>增援已至凛风堡，速速进攻！</t>
+  </si>
+  <si>
+    <t>恶人·兵符增援·凛风堡</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·凛风堡",nTime="10,恶人·兵符增援·凛风堡;300,恶人·凛风堡·兵符冷却;305,恶人·凛风堡·可用兵符",nRefresh=1,key="兵符·凛风堡",},</t>
+  </si>
+  <si>
+    <t>随着霸图的死亡，一柄钢刀从他身上滑落，似乎是他的随身信物。</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=2864,nFrame=7,szName="霸图",nTime=0,key="霸图",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=2864,nFrame=7,szName="霸图",nTime="60,霸图的信物;302,霸图·刷新剩余;304,霸图·即将刷新;310,霸图·延迟刷新",nRefresh=60,key="霸图",},</t>
+  </si>
+  <si>
+    <t>随着孙永恒的死亡，一柄短剑从他身上滑落，似乎是他的随身信物。</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=845,nFrame=3,szName="孙永恒",nTime=0,key="孙永恒",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=845,nFrame=3,szName="孙永恒",nTime="60,孙永恒的信物;302,孙永恒·刷新剩余;304,孙永恒·即将刷新;310,孙永恒·延迟刷新",nRefresh=60,key="孙永恒",},</t>
+  </si>
+  <si>
+    <t>霸图</t>
+  </si>
+  <si>
+    <t>{nClass=-1,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=2,nRefresh=600,key="霸图",},</t>
+  </si>
+  <si>
+    <t>孙永恒</t>
+  </si>
+  <si>
+    <t>{nClass=-1,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=2,nRefresh=600,key="孙永恒",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=3,szName="恶人·护送牛车",nTime="548,恶人·护送牛车;562,恶人·延迟护送牛车",nRefresh=0,key="恶人·矿车",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=7,szName="浩气·护送牛车",nTime="548,浩气·护送牛车;562,浩气·延迟护送牛车",nRefresh=0,key="浩气·矿车",},</t>
+  </si>
+  <si>
+    <t>增援已至盘龙坞，速速进攻！</t>
+  </si>
+  <si>
+    <t>浩气·兵符增援·盘龙坞</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·盘龙坞",nTime="10,浩气·兵符增援·盘龙坞;300,浩气·盘龙坞·兵符冷却;305,浩气·盘龙坞·可用兵符",nRefresh=1,key="兵符·盘龙坞",},</t>
+  </si>
+  <si>
+    <t>增援已至逐鹿坪，速速进攻！</t>
+  </si>
+  <si>
+    <t>浩气·兵符增援·逐鹿坪</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·逐鹿坪",nTime="10,浩气·兵符增援·逐鹿坪;300,浩气·逐鹿坪·兵符冷却;305,浩气·逐鹿坪·可用兵符",nRefresh=1,key="兵符·逐鹿坪",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=589,nFrame=7,szName="赵新宇",nTime="60,赵新宇的信物;302,赵新宇·刷新剩余;304,赵新宇·即将刷新",nRefresh=60,key="赵新宇",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=308,nFrame=3,szName="方超",nTime="60,方超的信物;302,方超·刷新剩余;304,方超·即将刷新",nRefresh=60,key="方超",},</t>
+  </si>
+  <si>
+    <t>增援已至龙门镇，速速进攻！</t>
+  </si>
+  <si>
+    <t>恶人·兵符增援·龙门镇</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·龙门镇",nTime="10,恶人·兵符增援·龙门镇;300,恶人·龙门镇·兵符冷却;305,恶人·龙门镇·可用兵符",nRefresh=1,key="兵符·龙门镇",},</t>
+  </si>
+  <si>
+    <t>增援已至飞沙关，速速进攻！</t>
+  </si>
+  <si>
+    <t>恶人·兵符增援·飞沙关</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·飞沙关",nTime="10,恶人·兵符增援·飞沙关;300,恶人·飞沙关·兵符冷却;305,恶人·飞沙关·可用兵符",nRefresh=1,key="兵符·飞沙关",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=2864,nFrame=7,szName="霸图",nTime="60,霸图的信物;302,霸图·刷新剩余;304,霸图·即将刷新",nRefresh=60,key="霸图",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=845,nFrame=3,szName="孙永恒",nTime="60,孙永恒的信物;302,孙永恒·刷新剩余;304,孙永恒·即将刷新",nRefresh=60,key="孙永恒",},</t>
+  </si>
+  <si>
+    <t>增援已至红莲岗，速速进攻！</t>
+  </si>
+  <si>
+    <t>浩气·兵符增援·红莲岗</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·红莲岗",nTime="10,浩气·兵符增援·红莲岗;300,浩气·红莲岗·兵符冷却;305,浩气·红莲岗·可用兵符",nRefresh=1,key="兵符·红莲岗",},</t>
+  </si>
+  <si>
+    <t>增援已至秋雨堡，速速进攻！</t>
+  </si>
+  <si>
+    <t>浩气·兵符增援·秋雨堡</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·秋雨堡",nTime="10,浩气·兵符增援·秋雨堡;300,浩气·秋雨堡·兵符冷却;305,浩气·秋雨堡·可用兵符",nRefresh=1,key="兵符·秋雨堡",},</t>
+  </si>
+  <si>
+    <t>增援已至神池岭，速速进攻！</t>
+  </si>
+  <si>
+    <t>恶人·兵符增援·神池岭</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·神池岭",nTime="10,恶人·兵符增援·神池岭;300,恶人·神池岭·兵符冷却;305,恶人·神池岭·可用兵符",nRefresh=1,key="兵符·神池岭",},</t>
+  </si>
+  <si>
+    <t>增援已至烈日岗，速速进攻！</t>
+  </si>
+  <si>
+    <t>恶人·兵符增援·烈日岗</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·烈日岗",nTime="10,恶人·兵符增援·烈日岗;300,恶人·烈日岗·兵符冷却;305,恶人·烈日岗·可用兵符",nRefresh=1,key="兵符·烈日岗",},</t>
+  </si>
+  <si>
+    <t>增援已至大理山城，速速进攻！</t>
+  </si>
+  <si>
+    <t>浩气·兵符增援·大理山城</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·大理山城",nTime="10,浩气·兵符增援·大理山城;300,浩气·大理山城·兵符冷却;305,浩气·大理山城·可用兵符",nRefresh=1,key="兵符·大理山城",},</t>
+  </si>
+  <si>
+    <t>增援已至千岩关，速速进攻！</t>
+  </si>
+  <si>
+    <t>浩气·兵符增援·千岩关</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·千岩关",nTime="10,浩气·兵符增援·千岩关;300,浩气·千岩关·兵符冷却;305,浩气·千岩关·可用兵符",nRefresh=1,key="兵符·千岩关",},</t>
+  </si>
+  <si>
+    <t>增援已至扶风郡，速速进攻！</t>
+  </si>
+  <si>
+    <t>恶人·兵符增援·扶风郡</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·扶风郡",nTime="10,恶人·兵符增援·扶风郡;300,恶人·扶风郡·兵符冷却;305,恶人·扶风郡·可用兵符",nRefresh=1,key="兵符·扶风郡",},</t>
+  </si>
+  <si>
+    <t>增援已至世外坡，速速进攻！</t>
+  </si>
+  <si>
+    <t>恶人·兵符增援·世外坡</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·世外坡",nTime="10,恶人·兵符增援·世外坡;300,恶人·世外坡·兵符冷却;305,恶人·世外坡·可用兵符",nRefresh=1,key="兵符·世外坡",},</t>
+  </si>
+  <si>
+    <t>(.-)侠士([打开关闭]+)了【(.-)据点】城门！</t>
+  </si>
+  <si>
+    <t>【{$1}】·{$2}·{$3}·城门</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},</t>
+  </si>
+  <si>
     <t>{nClass=14,nIcon=16834,nFrame=1,szName="【{$1}】大旗·易伤{$3}层",nTime="60,【{$1}】大旗·易伤{$3}层;62,【{$1}】大旗·易伤冷却结束",nRefresh=0,key="{$1}·大旗易伤",},</t>
-  </si>
-  <si>
-    <t>您因消极怠战,扰乱阵营秩序，被阵营督查官请离当前地图，但同时给予250点贡献积分！</t>
-  </si>
-  <si>
-    <t>阵营督查官·请离据点攻防</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=1,bHold=true,nTime=30,szName="阵营督查·请离据点攻防",key="挂机检测",},</t>
-  </si>
-  <si>
-    <t>留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},</t>
-  </si>
-  <si>
-    <t>留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},</t>
-  </si>
-  <si>
-    <t>可恶！</t>
-  </si>
-  <si>
-    <t>{$sender}·退场</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},</t>
-  </si>
-  <si>
-    <t>尔等鼠辈！谁敢与我一战！</t>
-  </si>
-  <si>
-    <t>据点攻防·正式开始</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime="2,据点攻防·正式开始;10,建议关闭·江湖身份",nRefresh=2,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,szName="绣球花",nTime=-1,key="绣球花",},{nClass=14,nIcon=13,szName="郁金香",nTime=-1,key="郁金香",},{nClass=14,nIcon=13,szName="牵牛花",nTime=-1,key="牵牛花",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},</t>
-  </si>
-  <si>
-    <t>哼，还有要事要办，今日收获甚多，来日定多来领略你们的武功！</t>
-  </si>
-  <si>
-    <t>狼牙先锋首领·攻防结束</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,szName="狼牙先锋首领·离开",nTime=0,key="狼牙先锋首领",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},</t>
-  </si>
-  <si>
-    <t>哼，打扰本大爷休息！</t>
-  </si>
-  <si>
-    <t>狼牙先锋首领·刷新喊话1</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},</t>
-  </si>
-  <si>
-    <t>你爷爷我年轻些时候，也是翻云覆雨的江湖响当当一号人物！</t>
-  </si>
-  <si>
-    <t>狼牙先锋首领·刷新喊话2</t>
-  </si>
-  <si>
-    <t>我竟然败给你们这群小辈！</t>
-  </si>
-  <si>
-    <t>防冲突禁用·击退·狼牙先锋首领</t>
-  </si>
-  <si>
-    <t>{nClass=-1,nIcon=3556,nFrame=1,szName="狼牙先锋首领·拾取掉落",nTime="10,狼牙先锋首领·已击退;300,狼牙先锋首领·拾取剩余;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=2,key="狼牙先锋首领",},</t>
-  </si>
-  <si>
-    <t>浩气盟督廷卫</t>
-  </si>
-  <si>
-    <t>增援已至武王城，速速进攻！</t>
-  </si>
-  <si>
-    <t>浩气·兵符增援·武王城</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·武王城",nTime="10,浩气·兵符增援·武王城;300,浩气·武王城·兵符冷却;305,浩气·武王城·可用兵符",nRefresh=1,key="兵符·武王城",},</t>
-  </si>
-  <si>
-    <t>赵新宇死亡时，从他身上遗落一把短笛，貌似是他的随身信物。</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=589,nFrame=7,szName="赵新宇",nTime=0,key="赵新宇",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=589,nFrame=7,szName="赵新宇",nTime="60,赵新宇的信物;302,赵新宇·刷新剩余;304,赵新宇·即将刷新;310,赵新宇·延迟刷新",nRefresh=60,key="赵新宇",},</t>
-  </si>
-  <si>
-    <t>随着方超的死亡，一把短笛掉了出来，貌似是他的随身信物。</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=308,nFrame=3,szName="方超",nTime=0,key="方超",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=308,nFrame=3,szName="方超",nTime="60,方超的信物;302,方超·刷新剩余;304,方超·即将刷新;310,方超·延迟刷新",nRefresh=60,key="方超",},</t>
-  </si>
-  <si>
-    <t>赵新宇</t>
-  </si>
-  <si>
-    <t>恶人谷老友们可在我这里传送到恶人谷！</t>
-  </si>
-  <si>
-    <t>{nClass=-1,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=2,nRefresh=600,key="赵新宇",},</t>
-  </si>
-  <si>
-    <t>方超</t>
-  </si>
-  <si>
-    <t>浩气盟侠士们可在我这里传送到浩气盟！</t>
-  </si>
-  <si>
-    <t>{nClass=-1,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=2,nRefresh=600,key="方超",},</t>
-  </si>
-  <si>
-    <t>管良沧</t>
-  </si>
-  <si>
-    <t>护送不利，恶人谷的运输小队被浩气盟截下了！</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=7,szName="浩气·劫车奖励",nTime=60,key="恶人·矿车",},</t>
-  </si>
-  <si>
-    <t>恶人谷的运输小队成功到达营地！接下来由他们将物资运往更前线，大伙继续加油，收集更多物资！</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=3,szName="恶人·领取护送奖赏",nTime=60,key="恶人·矿车",},</t>
-  </si>
-  <si>
-    <t>恶人谷的运输小队出现了，大伙快前去接送到我方营地，谷主重重有赏！</t>
-  </si>
-  <si>
-    <t>粮草先行·恶人牛车</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=3,szName="恶人·护送牛车",nTime="337,恶人·护送牛车;340,恶人·延迟护送牛车",nRefresh=0,key="恶人·矿车",},</t>
-  </si>
-  <si>
-    <t>苏才寥</t>
-  </si>
-  <si>
-    <t>护送不利，浩气盟的运输小队被恶人谷截下了！</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=3,szName="恶人·劫车奖励",nTime=60,key="浩气·矿车",},</t>
-  </si>
-  <si>
-    <t>浩气盟的运输小队成功到达营地！接下来由他们将物资运往更前线，大伙继续加油，收集更多物资！</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=7,szName="浩气·领取护送奖赏",nTime=60,key="浩气·矿车",},</t>
-  </si>
-  <si>
-    <t>浩气盟的运输小队出现了，大伙快前去接送到我方营地，盟主重重有赏！</t>
-  </si>
-  <si>
-    <t>粮草先行·浩气牛车</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=7,szName="浩气·护送牛车",nTime="337,浩气·护送牛车;340,浩气·延迟护送牛车",nRefresh=0,key="浩气·矿车",},</t>
-  </si>
-  <si>
-    <t>恶人谷督廷卫</t>
-  </si>
-  <si>
-    <t>增援已至凛风堡，速速进攻！</t>
-  </si>
-  <si>
-    <t>恶人·兵符增援·凛风堡</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·凛风堡",nTime="10,恶人·兵符增援·凛风堡;300,恶人·凛风堡·兵符冷却;305,恶人·凛风堡·可用兵符",nRefresh=1,key="兵符·凛风堡",},</t>
-  </si>
-  <si>
-    <t>随着霸图的死亡，一柄钢刀从他身上滑落，似乎是他的随身信物。</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=2864,nFrame=7,szName="霸图",nTime=0,key="霸图",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=2864,nFrame=7,szName="霸图",nTime="60,霸图的信物;302,霸图·刷新剩余;304,霸图·即将刷新;310,霸图·延迟刷新",nRefresh=60,key="霸图",},</t>
-  </si>
-  <si>
-    <t>随着孙永恒的死亡，一柄短剑从他身上滑落，似乎是他的随身信物。</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=845,nFrame=3,szName="孙永恒",nTime=0,key="孙永恒",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=845,nFrame=3,szName="孙永恒",nTime="60,孙永恒的信物;302,孙永恒·刷新剩余;304,孙永恒·即将刷新;310,孙永恒·延迟刷新",nRefresh=60,key="孙永恒",},</t>
-  </si>
-  <si>
-    <t>霸图</t>
-  </si>
-  <si>
-    <t>{nClass=-1,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=2,nRefresh=600,key="霸图",},</t>
-  </si>
-  <si>
-    <t>孙永恒</t>
-  </si>
-  <si>
-    <t>{nClass=-1,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=2,nRefresh=600,key="孙永恒",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=3,szName="恶人·护送牛车",nTime="548,恶人·护送牛车;562,恶人·延迟护送牛车",nRefresh=0,key="恶人·矿车",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=7,szName="浩气·护送牛车",nTime="548,浩气·护送牛车;562,浩气·延迟护送牛车",nRefresh=0,key="浩气·矿车",},</t>
-  </si>
-  <si>
-    <t>增援已至盘龙坞，速速进攻！</t>
-  </si>
-  <si>
-    <t>浩气·兵符增援·盘龙坞</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·盘龙坞",nTime="10,浩气·兵符增援·盘龙坞;300,浩气·盘龙坞·兵符冷却;305,浩气·盘龙坞·可用兵符",nRefresh=1,key="兵符·盘龙坞",},</t>
-  </si>
-  <si>
-    <t>增援已至逐鹿坪，速速进攻！</t>
-  </si>
-  <si>
-    <t>浩气·兵符增援·逐鹿坪</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·逐鹿坪",nTime="10,浩气·兵符增援·逐鹿坪;300,浩气·逐鹿坪·兵符冷却;305,浩气·逐鹿坪·可用兵符",nRefresh=1,key="兵符·逐鹿坪",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=589,nFrame=7,szName="赵新宇",nTime="60,赵新宇的信物;302,赵新宇·刷新剩余;304,赵新宇·即将刷新",nRefresh=60,key="赵新宇",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=308,nFrame=3,szName="方超",nTime="60,方超的信物;302,方超·刷新剩余;304,方超·即将刷新",nRefresh=60,key="方超",},</t>
-  </si>
-  <si>
-    <t>增援已至龙门镇，速速进攻！</t>
-  </si>
-  <si>
-    <t>恶人·兵符增援·龙门镇</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·龙门镇",nTime="10,恶人·兵符增援·龙门镇;300,恶人·龙门镇·兵符冷却;305,恶人·龙门镇·可用兵符",nRefresh=1,key="兵符·龙门镇",},</t>
-  </si>
-  <si>
-    <t>增援已至飞沙关，速速进攻！</t>
-  </si>
-  <si>
-    <t>恶人·兵符增援·飞沙关</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·飞沙关",nTime="10,恶人·兵符增援·飞沙关;300,恶人·飞沙关·兵符冷却;305,恶人·飞沙关·可用兵符",nRefresh=1,key="兵符·飞沙关",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=2864,nFrame=7,szName="霸图",nTime="60,霸图的信物;302,霸图·刷新剩余;304,霸图·即将刷新",nRefresh=60,key="霸图",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=845,nFrame=3,szName="孙永恒",nTime="60,孙永恒的信物;302,孙永恒·刷新剩余;304,孙永恒·即将刷新",nRefresh=60,key="孙永恒",},</t>
-  </si>
-  <si>
-    <t>增援已至红莲岗，速速进攻！</t>
-  </si>
-  <si>
-    <t>浩气·兵符增援·红莲岗</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·红莲岗",nTime="10,浩气·兵符增援·红莲岗;300,浩气·红莲岗·兵符冷却;305,浩气·红莲岗·可用兵符",nRefresh=1,key="兵符·红莲岗",},</t>
-  </si>
-  <si>
-    <t>增援已至秋雨堡，速速进攻！</t>
-  </si>
-  <si>
-    <t>浩气·兵符增援·秋雨堡</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·秋雨堡",nTime="10,浩气·兵符增援·秋雨堡;300,浩气·秋雨堡·兵符冷却;305,浩气·秋雨堡·可用兵符",nRefresh=1,key="兵符·秋雨堡",},</t>
-  </si>
-  <si>
-    <t>增援已至神池岭，速速进攻！</t>
-  </si>
-  <si>
-    <t>恶人·兵符增援·神池岭</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·神池岭",nTime="10,恶人·兵符增援·神池岭;300,恶人·神池岭·兵符冷却;305,恶人·神池岭·可用兵符",nRefresh=1,key="兵符·神池岭",},</t>
-  </si>
-  <si>
-    <t>增援已至烈日岗，速速进攻！</t>
-  </si>
-  <si>
-    <t>恶人·兵符增援·烈日岗</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·烈日岗",nTime="10,恶人·兵符增援·烈日岗;300,恶人·烈日岗·兵符冷却;305,恶人·烈日岗·可用兵符",nRefresh=1,key="兵符·烈日岗",},</t>
-  </si>
-  <si>
-    <t>增援已至大理山城，速速进攻！</t>
-  </si>
-  <si>
-    <t>浩气·兵符增援·大理山城</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·大理山城",nTime="10,浩气·兵符增援·大理山城;300,浩气·大理山城·兵符冷却;305,浩气·大理山城·可用兵符",nRefresh=1,key="兵符·大理山城",},</t>
-  </si>
-  <si>
-    <t>增援已至千岩关，速速进攻！</t>
-  </si>
-  <si>
-    <t>浩气·兵符增援·千岩关</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·千岩关",nTime="10,浩气·兵符增援·千岩关;300,浩气·千岩关·兵符冷却;305,浩气·千岩关·可用兵符",nRefresh=1,key="兵符·千岩关",},</t>
-  </si>
-  <si>
-    <t>增援已至扶风郡，速速进攻！</t>
-  </si>
-  <si>
-    <t>恶人·兵符增援·扶风郡</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·扶风郡",nTime="10,恶人·兵符增援·扶风郡;300,恶人·扶风郡·兵符冷却;305,恶人·扶风郡·可用兵符",nRefresh=1,key="兵符·扶风郡",},</t>
-  </si>
-  <si>
-    <t>增援已至世外坡，速速进攻！</t>
-  </si>
-  <si>
-    <t>恶人·兵符增援·世外坡</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·世外坡",nTime="10,恶人·兵符增援·世外坡;300,恶人·世外坡·兵符冷却;305,恶人·世外坡·可用兵符",nRefresh=1,key="兵符·世外坡",},</t>
-  </si>
-  <si>
-    <t>(.-)侠士([打开关闭]+)了【(.-)据点】城门！</t>
-  </si>
-  <si>
-    <t>【{$1}】·{$2}·{$3}·城门</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},</t>
   </si>
   <si>
     <t>{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="离开据点·大旗重置",},</t>
@@ -9485,7 +9488,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="34" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1782648205000,</v>
+        <v>nTimeStamp = 1782822561000,</v>
       </c>
       <c r="B4" s="38" t="s">
         <v>11</v>
@@ -11228,10 +11231,10 @@
         <v>1813</v>
       </c>
       <c r="B3" t="s">
-        <v>2566</v>
+        <v>2567</v>
       </c>
       <c r="C3" t="s">
-        <v>2674</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -11239,10 +11242,10 @@
         <v>1833</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2583</v>
+        <v>2584</v>
       </c>
       <c r="C4" t="s">
-        <v>2675</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -11250,10 +11253,10 @@
         <v>1840</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2594</v>
+        <v>2595</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>2676</v>
+        <v>2677</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -11261,10 +11264,10 @@
         <v>1844</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2595</v>
+        <v>2596</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2677</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -11272,10 +11275,10 @@
         <v>1852</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2600</v>
+        <v>2601</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>2678</v>
+        <v>2679</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -11283,10 +11286,10 @@
         <v>1856</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2601</v>
+        <v>2602</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>2679</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -11294,10 +11297,10 @@
         <v>1869</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2606</v>
+        <v>2607</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>2680</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -11305,10 +11308,10 @@
         <v>1873</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2607</v>
+        <v>2608</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>2681</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -11316,10 +11319,10 @@
         <v>1877</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2612</v>
+        <v>2613</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>2682</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -11327,10 +11330,10 @@
         <v>1881</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>2683</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -11338,10 +11341,10 @@
         <v>1885</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2618</v>
+        <v>2619</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>2684</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -11349,10 +11352,10 @@
         <v>1889</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>2619</v>
+        <v>2620</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>2685</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -11360,10 +11363,10 @@
         <v>1895</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>2624</v>
+        <v>2625</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>2686</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -11371,10 +11374,10 @@
         <v>1899</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2625</v>
+        <v>2626</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>2687</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -11382,10 +11385,10 @@
         <v>1903</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2630</v>
+        <v>2631</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>2688</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -11393,10 +11396,10 @@
         <v>1907</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>2631</v>
+        <v>2632</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>2689</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -11404,10 +11407,10 @@
         <v>1913</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>2636</v>
+        <v>2637</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>2690</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -11415,10 +11418,10 @@
         <v>1917</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2637</v>
+        <v>2638</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>2691</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -11426,10 +11429,10 @@
         <v>1921</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>2642</v>
+        <v>2643</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>2692</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -11437,10 +11440,10 @@
         <v>1925</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2643</v>
+        <v>2644</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>2693</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -11448,10 +11451,10 @@
         <v>1929</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>2648</v>
+        <v>2649</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>2694</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -11459,10 +11462,10 @@
         <v>1933</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2649</v>
+        <v>2650</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>2695</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -11470,10 +11473,10 @@
         <v>1941</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>2696</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -11481,10 +11484,10 @@
         <v>1945</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2655</v>
+        <v>2656</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>2697</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -11492,10 +11495,10 @@
         <v>1949</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2660</v>
+        <v>2661</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>2698</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -11503,10 +11506,10 @@
         <v>1953</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2661</v>
+        <v>2662</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2699</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -11514,10 +11517,10 @@
         <v>1974</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2700</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -11525,10 +11528,10 @@
         <v>1978</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>2668</v>
+        <v>2669</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>2701</v>
+        <v>2702</v>
       </c>
     </row>
   </sheetData>
@@ -39404,7 +39407,7 @@
       </c>
       <c r="V111" t="str">
         <f t="shared" si="28"/>
-        <v>{szContent="^【(.-)】据点大旗受损，获得(%d-)层易伤，当前总计【(%d-)层易伤】！",szTarget="%",szNote="【{$1}】大旗·易伤{$3}层",col={255,50,255,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=16834,nFrame=1,szName="大旗易伤",nTime=-1,nRefresh=2,key="大旗易伤",},{nClass=14,nIcon=16834,nFrame=1,szName="【{$1}】大旗·易伤{$3}层",nTime="60,【{$1}】大旗·易伤{$3}层;62,【{$1}】大旗·易伤冷却结束",nRefresh=0,key="{$1}·大旗易伤",},},},</v>
+        <v>{szContent="^【(.-)】据点大旗受损，获得(%d-)层易伤，当前总计【(%d-)层易伤】！",szTarget="%",szNote="【{$1}】大旗·易伤{$3}层",col={255,50,255,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=16834,nFrame=1,szName="大旗易伤",nTime=-1,nRefresh=2,key="大旗易伤",},{nClass=14,nIcon=16834,nFrame=1,szName="【{$1}】大旗·易伤{$3}层",nTime="60,【{$1}】大旗·易伤{$3}层;65,【{$1}】大旗·易伤冷却结束",nRefresh=0,key="{$1}·大旗易伤",},},},</v>
       </c>
       <c r="W111" t="s">
         <v>2265</v>
@@ -40868,7 +40871,7 @@
         <v>2265</v>
       </c>
       <c r="X179" t="s">
-        <v>2266</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="180" customFormat="1" spans="1:27">
@@ -40918,7 +40921,7 @@
         <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W181" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="182" customFormat="1" spans="1:27">
@@ -41194,7 +41197,7 @@
         <v>2265</v>
       </c>
       <c r="X192" t="s">
-        <v>2266</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="193" customFormat="1" spans="3:25">
@@ -41244,7 +41247,7 @@
         <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W194" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="195" customFormat="1" spans="3:25">
@@ -41398,10 +41401,10 @@
         <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="F1" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="G1" t="s">
         <v>2043</v>
@@ -41443,7 +41446,7 @@
         <v>2054</v>
       </c>
       <c r="T1" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="2" customFormat="1" spans="1:33">
@@ -41460,10 +41463,10 @@
     </row>
     <row r="3" customFormat="1" spans="1:33">
       <c r="C3" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="D3" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -41473,18 +41476,18 @@
         <v>{szContent="[团队监控]数据加载成功",szNote="关闭刷马等计时条",bSearch=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},},},</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="4" customFormat="1" spans="1:33">
       <c r="C4" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="D4" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="K4" t="s">
         <v>1656</v>
@@ -41494,15 +41497,15 @@
         <v>{szContent="驿马快报！本周浩气盟和恶人谷最终战为平手，未分胜负！\n",szNote="阵营事件·本周战平",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13354,nFrame=4,szName="阵营事件·本周战平",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U4" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:33">
       <c r="C5" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="D5" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="K5" t="s">
         <v>2117</v>
@@ -41512,15 +41515,15 @@
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U5" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:33">
       <c r="C6" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="D6" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="K6" t="s">
         <v>2116</v>
@@ -41530,15 +41533,15 @@
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U6" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="7" spans="1:33">
       <c r="C7" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="D7" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
       <c r="K7" t="s">
         <v>1656</v>
@@ -41548,39 +41551,39 @@
         <v>{szContent="本场攻防“奇袭场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手。战利品稍后开始拍卖，请留意！\n",szNote="奇袭场·平局",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2402,nFrame=4,bHold=true,szName="奇袭场·平局",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·一",key="破阵点将·一",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·二",key="破阵点将·二",},{nClass=20,nIcon=13,szName="牛车拾取间隔",nTime=-1,key="牛车拾取间隔",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,key="首领拾取间隔",},{nClass=20,nIcon=13,nFrame=4,szName="浩气·物资车·运达",nTime=-1,key="浩气·物资车·运达",},{nClass=20,nIcon=13,nFrame=4,szName="恶人·物资车·运达",nTime=-1,key="恶人·物资车·运达",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·月弄痕·减伤",nTime=-1,key="谢渊·月弄痕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·游驹·减伤",nTime=-1,key="谢渊·游驹·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·小七·减伤",nTime=-1,key="谢渊·小七·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·张桎辕·减伤",nTime=-1,key="谢渊·张桎辕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·司空仲平·减伤",nTime=-1,key="谢渊·司空仲平·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·韩非池·减伤",nTime=-1,key="谢渊·韩非池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·赵紫儿·减伤",nTime=-1,key="谢渊·赵紫儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·叶镜池·减伤",nTime=-1,key="谢渊·叶镜池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郭珠·减伤",nTime=-1,key="谢渊·郭珠·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·穆玄英·减伤",nTime=-1,key="谢渊·穆玄英·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·影·减伤",nTime=-1,key="谢渊·影·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·司徒一一·减伤",nTime=-1,key="王遗风·司徒一一·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·白某·减伤",nTime=-1,key="王遗风·白某·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·米丽古丽·减伤",nTime=-1,key="王遗风·米丽古丽·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶寒亭·减伤",nTime=-1,key="王遗风·陶寒亭·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·肖药儿·减伤",nTime=-1,key="王遗风·肖药儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·伊夜·减伤",nTime=-1,key="王遗风·伊夜·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·丁丁·减伤",nTime=-1,key="王遗风·丁丁·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·岳琅·减伤",nTime=-1,key="王遗风·岳琅·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·毕罗巴·减伤",nTime=-1,key="王遗风·毕罗巴·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·烟·减伤",nTime=-1,key="王遗风·烟·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·独孤修·减伤",nTime=-1,key="王遗风·独孤修·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·周峰·减伤",nTime=-1,key="谢渊·周峰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郑鸥·减伤",nTime=-1,key="谢渊·郑鸥·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·陶杰·减伤",nTime=-1,key="谢渊·陶杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢烟客·减伤",nTime=-1,key="谢渊·谢烟客·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·张一洋·减伤",nTime=-1,key="王遗风·张一洋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶国栋·减伤",nTime=-1,key="王遗风·陶国栋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·吕沛杰·减伤",nTime=-1,key="王遗风·吕沛杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·顾延恶·减伤",nTime=-1,key="王遗风·顾延恶·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·莫雨·减伤",nTime=-1,key="王遗风·莫雨·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·万兽王·减伤",nTime=-1,key="王遗风·万兽王·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢铃儿·减伤",nTime=-1,key="谢渊·谢铃儿·减伤",},},},</v>
       </c>
       <c r="U7" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
       <c r="V7" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="W7" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="X7" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="Y7" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="Z7" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="AA7" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="AB7" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="AC7" s="4" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="8" spans="1:33">
       <c r="C8" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="D8" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="K8" t="s">
         <v>1656</v>
@@ -41590,39 +41593,39 @@
         <v>{szContent="本场攻防“主战场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手。战利品稍后开始拍卖，请留意！\n",szNote="主战场·平局",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,bHold=true,szName="主战场·平局",nTime=57,nRefresh=5,key="大攻防·主战场",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·一",key="破阵点将·一",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·二",key="破阵点将·二",},{nClass=20,nIcon=13,szName="牛车拾取间隔",nTime=-1,key="牛车拾取间隔",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,key="首领拾取间隔",},{nClass=20,nIcon=13,nFrame=4,szName="浩气·物资车·运达",nTime=-1,key="浩气·物资车·运达",},{nClass=20,nIcon=13,nFrame=4,szName="恶人·物资车·运达",nTime=-1,key="恶人·物资车·运达",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·月弄痕·减伤",nTime=-1,key="谢渊·月弄痕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·游驹·减伤",nTime=-1,key="谢渊·游驹·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·小七·减伤",nTime=-1,key="谢渊·小七·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·张桎辕·减伤",nTime=-1,key="谢渊·张桎辕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·司空仲平·减伤",nTime=-1,key="谢渊·司空仲平·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·韩非池·减伤",nTime=-1,key="谢渊·韩非池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·赵紫儿·减伤",nTime=-1,key="谢渊·赵紫儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·叶镜池·减伤",nTime=-1,key="谢渊·叶镜池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郭珠·减伤",nTime=-1,key="谢渊·郭珠·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·穆玄英·减伤",nTime=-1,key="谢渊·穆玄英·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·影·减伤",nTime=-1,key="谢渊·影·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·司徒一一·减伤",nTime=-1,key="王遗风·司徒一一·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·白某·减伤",nTime=-1,key="王遗风·白某·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·米丽古丽·减伤",nTime=-1,key="王遗风·米丽古丽·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶寒亭·减伤",nTime=-1,key="王遗风·陶寒亭·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·肖药儿·减伤",nTime=-1,key="王遗风·肖药儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·伊夜·减伤",nTime=-1,key="王遗风·伊夜·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·丁丁·减伤",nTime=-1,key="王遗风·丁丁·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·岳琅·减伤",nTime=-1,key="王遗风·岳琅·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·毕罗巴·减伤",nTime=-1,key="王遗风·毕罗巴·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·烟·减伤",nTime=-1,key="王遗风·烟·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·独孤修·减伤",nTime=-1,key="王遗风·独孤修·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·周峰·减伤",nTime=-1,key="谢渊·周峰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郑鸥·减伤",nTime=-1,key="谢渊·郑鸥·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·陶杰·减伤",nTime=-1,key="谢渊·陶杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢烟客·减伤",nTime=-1,key="谢渊·谢烟客·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·张一洋·减伤",nTime=-1,key="王遗风·张一洋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶国栋·减伤",nTime=-1,key="王遗风·陶国栋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·吕沛杰·减伤",nTime=-1,key="王遗风·吕沛杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·顾延恶·减伤",nTime=-1,key="王遗风·顾延恶·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·莫雨·减伤",nTime=-1,key="王遗风·莫雨·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·万兽王·减伤",nTime=-1,key="王遗风·万兽王·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢铃儿·减伤",nTime=-1,key="谢渊·谢铃儿·减伤",},},},</v>
       </c>
       <c r="U8" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="V8" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="W8" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="X8" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="Y8" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="Z8" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="AA8" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="AB8" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="AC8" s="4" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="9" spans="1:33">
       <c r="C9" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="D9" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="K9" t="s">
         <v>1656</v>
@@ -41638,51 +41641,51 @@
         <v>{szContent="^本场攻防“([主战奇袭场]+)”已结束，([浩气盟恶人谷]+)[侠士们众志成城和，]-([大完险胜]+)([浩气盟恶人谷]+)[！，]+",szNote="{$1}·{$2}·{$3}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,szName="大攻防·奇袭场",nTime=-2,nRefresh=10,key="大攻防·奇袭场",},{nClass=20,nIcon=13,szName="大攻防·主战场",nTime=-2,nRefresh=10,key="大攻防·主战场",},{nClass=20,nIcon=13,szName="大攻防·{$1}",nTime=-2,key="大攻防·{$1}",},{nClass=20,nIcon=2402,nFrame=4,bHold=true,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=2400,nFrame=0,bHold=true,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·主战场",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·一",key="破阵点将·一",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·二",key="破阵点将·二",},{nClass=20,nIcon=13,szName="牛车拾取间隔",nTime=-1,key="牛车拾取间隔",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,key="首领拾取间隔",},{nClass=20,nIcon=13,nFrame=4,szName="浩气·物资车·运达",nTime=-1,key="浩气·物资车·运达",},{nClass=20,nIcon=13,nFrame=4,szName="恶人·物资车·运达",nTime=-1,key="恶人·物资车·运达",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·月弄痕·减伤",nTime=-1,key="谢渊·月弄痕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·游驹·减伤",nTime=-1,key="谢渊·游驹·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·小七·减伤",nTime=-1,key="谢渊·小七·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·张桎辕·减伤",nTime=-1,key="谢渊·张桎辕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·司空仲平·减伤",nTime=-1,key="谢渊·司空仲平·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·韩非池·减伤",nTime=-1,key="谢渊·韩非池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·赵紫儿·减伤",nTime=-1,key="谢渊·赵紫儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·叶镜池·减伤",nTime=-1,key="谢渊·叶镜池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郭珠·减伤",nTime=-1,key="谢渊·郭珠·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·穆玄英·减伤",nTime=-1,key="谢渊·穆玄英·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·影·减伤",nTime=-1,key="谢渊·影·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·司徒一一·减伤",nTime=-1,key="王遗风·司徒一一·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·白某·减伤",nTime=-1,key="王遗风·白某·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·米丽古丽·减伤",nTime=-1,key="王遗风·米丽古丽·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶寒亭·减伤",nTime=-1,key="王遗风·陶寒亭·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·肖药儿·减伤",nTime=-1,key="王遗风·肖药儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·伊夜·减伤",nTime=-1,key="王遗风·伊夜·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·丁丁·减伤",nTime=-1,key="王遗风·丁丁·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·岳琅·减伤",nTime=-1,key="王遗风·岳琅·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·毕罗巴·减伤",nTime=-1,key="王遗风·毕罗巴·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·烟·减伤",nTime=-1,key="王遗风·烟·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·独孤修·减伤",nTime=-1,key="王遗风·独孤修·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·周峰·减伤",nTime=-1,key="谢渊·周峰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郑鸥·减伤",nTime=-1,key="谢渊·郑鸥·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·陶杰·减伤",nTime=-1,key="谢渊·陶杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢烟客·减伤",nTime=-1,key="谢渊·谢烟客·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·张一洋·减伤",nTime=-1,key="王遗风·张一洋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶国栋·减伤",nTime=-1,key="王遗风·陶国栋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·吕沛杰·减伤",nTime=-1,key="王遗风·吕沛杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·顾延恶·减伤",nTime=-1,key="王遗风·顾延恶·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·莫雨·减伤",nTime=-1,key="王遗风·莫雨·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·万兽王·减伤",nTime=-1,key="王遗风·万兽王·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢铃儿·减伤",nTime=-1,key="谢渊·谢铃儿·减伤",},},},</v>
       </c>
       <c r="U9" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="V9" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
       <c r="W9" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="X9" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="Y9" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="Z9" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="AA9" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="AB9" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="AC9" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="AD9" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="AE9" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="AF9" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="AG9" s="3" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:33">
       <c r="C10" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="D10" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="K10" t="s">
         <v>1656</v>
@@ -41692,21 +41695,21 @@
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=20,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=20,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=20,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=20,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=20,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=20,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=20,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=20,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=20,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="U10" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="V10" s="5" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="W10" s="5" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="11" spans="1:33">
       <c r="C11" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="D11" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="K11" t="s">
         <v>1656</v>
@@ -41719,18 +41722,18 @@
         <v>{szContent="本场恶人谷攻防即将结束，昆仑物资运送暂且休整，等待下一场攻防开启！\n",szNote="本场攻防·即将结束",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=0,szName="本场攻防·结束剩余",nTime=60,nRefresh=5,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·肖药儿",nTime=-1,key="浩气·召请CD·肖药儿",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·司徒一一",nTime=-1,key="浩气·召请CD·司徒一一",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·陶寒亭",nTime=-1,key="浩气·召请CD·陶寒亭",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·白某",nTime=-1,key="浩气·召请CD·白某",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·米丽古丽",nTime=-1,key="浩气·召请CD·米丽古丽",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·小七",nTime=-1,key="恶人·召请CD·小七",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·游驹",nTime=-1,key="恶人·召请CD·游驹",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·张桎辕",nTime=-1,key="恶人·召请CD·张桎辕",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·月弄痕",nTime=-1,key="恶人·召请CD·月弄痕",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·司空仲平",nTime=-1,key="恶人·召请CD·司空仲平",},},},</v>
       </c>
       <c r="U11" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="V11" s="6" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="12" spans="1:33">
       <c r="C12" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="D12" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="K12" t="s">
         <v>1656</v>
@@ -41743,18 +41746,18 @@
         <v>{szContent="本场浩气盟攻防即将结束，南屏山物资运送暂且休整，等待下一场攻防开启！\n",szNote="本场攻防·即将结束",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=0,szName="本场攻防·结束剩余",nTime=60,nRefresh=5,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·肖药儿",nTime=-1,key="浩气·召请CD·肖药儿",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·司徒一一",nTime=-1,key="浩气·召请CD·司徒一一",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·陶寒亭",nTime=-1,key="浩气·召请CD·陶寒亭",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·白某",nTime=-1,key="浩气·召请CD·白某",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·米丽古丽",nTime=-1,key="浩气·召请CD·米丽古丽",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·小七",nTime=-1,key="恶人·召请CD·小七",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·游驹",nTime=-1,key="恶人·召请CD·游驹",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·张桎辕",nTime=-1,key="恶人·召请CD·张桎辕",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·月弄痕",nTime=-1,key="恶人·召请CD·月弄痕",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·司空仲平",nTime=-1,key="恶人·召请CD·司空仲平",},},},</v>
       </c>
       <c r="U12" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="V12" s="6" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="13" spans="1:33">
       <c r="C13" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="D13" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="K13" t="s">
         <v>1656</v>
@@ -41770,21 +41773,21 @@
         <v>{szContent="侠士 [{$me}] 在拾取复活点物资时意外获得了[便携装置·神机车]。",szNote="获得·便携装置·神机车",col={255,255,100,},bSearch=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=134,nFrame=0,szName="获得·[便携装置·神机车]",nTime=10,nRefresh=1,key="交互事件",},},},</v>
       </c>
       <c r="U13" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="14" spans="1:33">
       <c r="C14" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="D14" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="E14" t="s">
         <v>2113</v>
       </c>
       <c r="F14" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="G14" t="s">
         <v>2114</v>
@@ -41822,16 +41825,16 @@
     </row>
     <row r="15" spans="1:33">
       <c r="C15" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="D15" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="E15" t="s">
         <v>2112</v>
       </c>
       <c r="F15" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="G15" t="s">
         <v>2115</v>
@@ -41881,40 +41884,40 @@
     </row>
     <row r="17" spans="1:26">
       <c r="C17" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="D17" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="T17" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="你已进入地图【浩气盟】。",szNote="关闭刷马等计时条",[20]={},tCountdown={{nClass=20,nIcon=13,szName="天气事件1",nTime=-2,key="天气事件1",},{nClass=20,nIcon=13,szName="天气事件2",nTime=-2,key="天气事件2",},{nClass=20,nIcon=13,nFrame=-1,szName="阵营活动",nTime=-2,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="创意食品",nTime=-1,nRefresh=5,key="创意食品",},{nClass=20,nIcon=13,szName="速战速决",nTime=-1,nRefresh=99999,key="速战速决",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},},},</v>
       </c>
       <c r="U17" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="V17" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="W17" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="X17" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="Y17" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="Z17" s="3" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:26">
       <c r="C18" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="D18" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="K18" t="s">
         <v>1656</v>
@@ -41927,24 +41930,24 @@
         <v>{szContent="伊夜使用了一招围魏救赵的妙计，率众客将奇袭了浩气盟大本营，浩气盟侠士也请速回救援！\n",szNote="奇袭攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=0,szName="奇袭攻防·正式开始",nTime="30,奇袭攻防·正式开始;60,建议关闭·江湖身份",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=7200,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U18" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="V18" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="W18" s="3" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="X18" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="19" spans="1:26">
       <c r="C19" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="D19" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
       <c r="K19" t="s">
         <v>1656</v>
@@ -41957,19 +41960,19 @@
         <v>{szContent="王遗风已率恶人谷众首领抵达浩气盟，请各位恶人谷侠士速到浩气盟支援。浩气盟侠士也请速回浩气盟防御！\n",szNote="主场攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2710,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5405,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·正在结算;7210,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=30,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="速战速决",nTime=-2,key="速战速决",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U19" t="s">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="V19" t="s">
-        <v>2464</v>
+        <v>2465</v>
       </c>
       <c r="W19" t="s">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="X19" s="3" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="Y19" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="20" spans="1:26">
@@ -41986,40 +41989,40 @@
     </row>
     <row r="21" spans="1:26">
       <c r="C21" t="s">
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="D21" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="T21" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="你已进入地图【恶人谷】。",szNote="关闭刷马等计时条",[20]={},tCountdown={{nClass=20,nIcon=13,szName="天气事件1",nTime=-2,key="天气事件1",},{nClass=20,nIcon=13,szName="天气事件2",nTime=-2,key="天气事件2",},{nClass=20,nIcon=13,nFrame=-1,szName="阵营活动",nTime=-2,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="创意食品",nTime=-1,nRefresh=5,key="创意食品",},{nClass=20,nIcon=13,szName="速战速决",nTime=-1,nRefresh=99999,key="速战速决",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},},},</v>
       </c>
       <c r="U21" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="V21" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="W21" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="X21" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="Y21" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="Z21" s="3" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:26">
       <c r="C22" t="s">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="D22" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="K22" t="s">
         <v>1656</v>
@@ -42032,24 +42035,24 @@
         <v>{szContent="韩非池使用了一招围魏救赵的妙计，率众客将奇袭了恶人谷大本营，恶人谷侠士也请速回救援！\n",szNote="奇袭攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=0,szName="奇袭攻防·正式开始",nTime="30,奇袭攻防·正式开始;60,建议关闭·江湖身份",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=7200,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U22" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="V22" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="W22" s="3" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="X22" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="23" spans="1:26">
       <c r="C23" t="s">
-        <v>2468</v>
+        <v>2469</v>
       </c>
       <c r="D23" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
       <c r="K23" t="s">
         <v>1656</v>
@@ -42062,24 +42065,24 @@
         <v>{szContent="谢渊已率浩气盟众首领抵达恶人谷，请各位浩气盟侠士速到恶人谷支援。恶人谷侠士也请速回恶人谷防御！\n",szNote="主场攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2710,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5405,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·正在结算;7210,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=30,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="速战速决",nTime=-2,key="速战速决",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U23" t="s">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="V23" t="s">
-        <v>2464</v>
+        <v>2465</v>
       </c>
       <c r="W23" t="s">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="Y23" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="24" customFormat="1" spans="1:26">
       <c r="A24" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="B24">
         <v>-1</v>
@@ -42091,10 +42094,10 @@
     </row>
     <row r="25" customFormat="1" spans="1:26">
       <c r="C25" t="s">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="D25" t="s">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="K25" t="s">
         <v>1656</v>
@@ -42107,12 +42110,12 @@
         <v>{szContent="(.-)【(.-)】帮会的(.-)大侠成功护送祭祀物资到达(.-)据点，该据点将士备受鼓舞，战意高昂，战时必将固若金汤！",szNote="祭天·{$1}·[{$2}]·{$4}",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=8838,nFrame=1,szName="{$1}祭天·[{$2}]·{$4}",nTime=30,key="通用事件",},},},</v>
       </c>
       <c r="U25" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="26" spans="1:26">
       <c r="C26" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="K26" t="s">
         <v>1656</v>
@@ -42122,12 +42125,12 @@
         <v>{szContent="为保障各位侠士的安全，浩气盟和恶人谷重新派出了守卫，在野外地图侠士重伤后复活可回到阵营复活点！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="据点攻防·消失模式",nTime=1799.795,key="阵营活动",},},},</v>
       </c>
       <c r="U26" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="27" spans="1:26">
       <c r="C27" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="K27" t="s">
         <v>1656</v>
@@ -42137,12 +42140,12 @@
         <v>{szContent="据点争夺战即将开始，为防弄虚作假者，即将对据点活动地图进行清场操作，同时清空此前所有排队队列，请各阵营侠士做好准备。拥有据点地图优先进入权的帮众可提前进入地图以作防守准备，不会被清出地图。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=-1,szName="阵营活动",nTime="1,据点攻防·开始排队;10,据点攻防·开始排队;60,据点攻防·等待排队",nRefresh=1,key="阵营活动",},},},</v>
       </c>
       <c r="U27" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="28" spans="1:26">
       <c r="C28" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="K28" t="s">
         <v>2117</v>
@@ -42152,12 +42155,12 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“恶人谷”地图进行清场操作，并在“下午六点三十分”开始攻防排队，请勿在下午六点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·恶人谷·18:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U28" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="29" spans="1:26">
       <c r="C29" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="K29" t="s">
         <v>2117</v>
@@ -42167,12 +42170,12 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“恶人谷”地图进行清场操作，并在“中午十二点三十分”开始攻防排队，请勿在中午十二点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·恶人谷·12:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U29" t="s">
-        <v>2480</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="30" spans="1:26">
       <c r="C30" t="s">
-        <v>2481</v>
+        <v>2482</v>
       </c>
       <c r="K30" t="s">
         <v>2116</v>
@@ -42182,12 +42185,12 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“浩气盟”地图进行清场操作，并在“下午六点三十分”开始攻防排队，请勿在下午六点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·浩气盟·18:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U30" t="s">
-        <v>2482</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="31" spans="1:26">
       <c r="C31" t="s">
-        <v>2483</v>
+        <v>2484</v>
       </c>
       <c r="K31" t="s">
         <v>2116</v>
@@ -42197,12 +42200,12 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“浩气盟”地图进行清场操作，并在“中午十二点三十分”开始攻防排队，请勿在中午十二点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·浩气盟·12:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U31" t="s">
-        <v>2484</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="32" spans="1:26">
       <c r="C32" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
       <c r="K32" t="s">
         <v>2117</v>
@@ -42212,18 +42215,18 @@
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往恶人谷地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=-1,szName="阵营攻防·开始排队",nTime="1,阵营攻防·开始排队;10,阵营攻防·开始排队",nRefresh=1,key="阵营活动",},{nClass=20,nIcon=14889,nFrame=3,szName="主战场·恶人谷",nTime=60,key="大攻防·主战场",},{nClass=20,nIcon=14890,nFrame=7,szName="奇袭场·浩气盟",nTime=60,key="大攻防·奇袭场",},},},</v>
       </c>
       <c r="U32" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="V32" t="s">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="W32" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="33" spans="1:26">
       <c r="C33" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="K33" t="s">
         <v>2116</v>
@@ -42233,13 +42236,13 @@
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往浩气盟地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=-1,szName="阵营攻防·开始排队",nTime="1,阵营攻防·开始排队;10,阵营攻防·开始排队",nRefresh=1,key="阵营活动",},{nClass=20,nIcon=14890,nFrame=7,szName="主战场·浩气盟",nTime=60,key="大攻防·主战场",},{nClass=20,nIcon=14889,nFrame=3,szName="奇袭场·恶人谷",nTime=60,key="大攻防·奇袭场",},},},</v>
       </c>
       <c r="U33" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="V33" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="W33" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="34" spans="1:26">
@@ -42256,10 +42259,10 @@
     </row>
     <row r="35" customFormat="1" spans="1:26">
       <c r="C35" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="D35" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="K35" t="s">
         <v>1656</v>
@@ -42272,15 +42275,15 @@
         <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U35" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="1:26">
       <c r="C36" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="D36" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="K36" t="s">
         <v>1656</v>
@@ -42293,27 +42296,27 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U36" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="V36" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="W36" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="X36" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="Y36" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="1:26">
       <c r="C37" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="D37" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="K37" t="s">
         <v>1656</v>
@@ -42326,30 +42329,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U37" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="V37" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="W37" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="X37" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="Y37" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="Z37" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="1:26">
       <c r="C38" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="D38" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="K38" t="s">
         <v>2117</v>
@@ -42359,15 +42362,15 @@
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U38" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="39" customFormat="1" spans="1:26">
       <c r="C39" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="D39" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="K39" t="s">
         <v>2116</v>
@@ -42377,15 +42380,15 @@
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U39" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="40" customFormat="1" spans="1:26">
       <c r="C40" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="D40" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="K40" t="s">
         <v>1656</v>
@@ -42398,15 +42401,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U40" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:26">
       <c r="C41" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="D41" t="s">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="K41" t="s">
         <v>1656</v>
@@ -42416,16 +42419,16 @@
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U41" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="V41" s="7"/>
     </row>
     <row r="42" customFormat="1" spans="1:26">
       <c r="C42" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="D42" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="K42" t="s">
         <v>1656</v>
@@ -42435,16 +42438,16 @@
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U42" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="V42" s="7"/>
     </row>
     <row r="43" customFormat="1" spans="1:26">
       <c r="C43" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="D43" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="K43" t="s">
         <v>1656</v>
@@ -42454,18 +42457,18 @@
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U43" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="V43" s="6" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="44" spans="1:26">
       <c r="C44" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="D44" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="K44" t="s">
         <v>1656</v>
@@ -42475,18 +42478,18 @@
         <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",szNote="据点攻防·阴山大草原·分线·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U44" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="V44" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="45" spans="1:26">
       <c r="C45" t="s">
-        <v>2524</v>
+        <v>2525</v>
       </c>
       <c r="D45" t="s">
-        <v>2525</v>
+        <v>2526</v>
       </c>
       <c r="K45" t="s">
         <v>1656</v>
@@ -42496,15 +42499,15 @@
         <v>{szContent="前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n",szNote="据点攻防·阴山大草原",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U45" t="s">
-        <v>2526</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="46" spans="1:26">
       <c r="C46" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="D46" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
       <c r="K46" t="s">
         <v>1656</v>
@@ -42514,18 +42517,18 @@
         <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·阴山大草原·开启分线·5分钟",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U46" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="V46" t="s">
-        <v>2529</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="47" spans="1:26">
       <c r="C47" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="D47" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
       <c r="K47" t="s">
         <v>1656</v>
@@ -42535,15 +42538,15 @@
         <v>{szContent="阵营攻防首领战紧张火热，本服今日无奇袭场分线模式，请侠士速速前往主战场及奇袭场参与活动。\n",szNote="阵营攻防·奇袭场·未开分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·未开分线",nTime=30,key="分流活动",},},},</v>
       </c>
       <c r="U47" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="48" spans="1:26">
       <c r="C48" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="D48" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="K48" t="s">
         <v>1656</v>
@@ -42553,7 +42556,7 @@
         <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",szNote="阵营攻防·奇袭场·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·开启分线",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
       <c r="U48" t="s">
-        <v>2535</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" spans="1:26">
@@ -42570,10 +42573,10 @@
     </row>
     <row r="50" customFormat="1" spans="1:26">
       <c r="C50" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="D50" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="K50" t="s">
         <v>1656</v>
@@ -42589,15 +42592,15 @@
         <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U50" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="51" spans="1:26">
       <c r="C51" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="D51" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="K51" t="s">
         <v>1656</v>
@@ -42610,27 +42613,27 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,key="{$3}·恶人大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气占领",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人占领",},{nClass=20,nIcon=13,szName="{$3}·{$1}占领",nTime=-1,key="{$3}·{$1}占领",},},},</v>
       </c>
       <c r="U51" t="s">
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="V51" t="s">
-        <v>2537</v>
+        <v>2538</v>
       </c>
       <c r="W51" t="s">
-        <v>2538</v>
+        <v>2539</v>
       </c>
       <c r="X51" t="s">
-        <v>2539</v>
+        <v>2540</v>
       </c>
       <c r="Y51" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="52" customFormat="1" spans="1:26">
       <c r="C52" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="D52" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="K52" t="s">
         <v>1656</v>
@@ -42643,30 +42646,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U52" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="V52" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="W52" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="X52" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="Y52" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="Z52" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:26">
       <c r="C53" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="D53" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="K53" t="s">
         <v>2117</v>
@@ -42676,15 +42679,15 @@
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U53" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:26">
       <c r="C54" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="D54" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="K54" t="s">
         <v>2116</v>
@@ -42694,12 +42697,12 @@
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U54" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="55" spans="1:26">
       <c r="C55" t="s">
-        <v>2541</v>
+        <v>2542</v>
       </c>
       <c r="K55" t="s">
         <v>1656</v>
@@ -42709,15 +42712,15 @@
         <v>{szContent="本场贡献值进入前1200名，额外获得3000威名，可通过邮件领取\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=6,szName="攻防进入前1200名",nTime=10,key="阵营活动",},},},</v>
       </c>
       <c r="U55" t="s">
-        <v>2542</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:26">
       <c r="C56" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="D56" t="s">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="K56" t="s">
         <v>1656</v>
@@ -42727,21 +42730,21 @@
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=20,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=20,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=20,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=20,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=20,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=20,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=20,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=20,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=20,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="U56" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="V56" s="5" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="W56" s="5" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="57" customFormat="1" spans="1:26">
       <c r="C57" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="D57" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="K57" t="s">
         <v>1656</v>
@@ -42751,16 +42754,16 @@
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U57" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="V57" s="7"/>
     </row>
     <row r="58" customFormat="1" spans="1:26">
       <c r="C58" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="D58" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="K58" t="s">
         <v>1656</v>
@@ -42773,15 +42776,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U58" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="59" spans="1:26">
       <c r="C59" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="D59" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="K59" t="s">
         <v>1656</v>
@@ -42791,24 +42794,24 @@
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=13,szName="狼牙先锋首领",nTime=0,key="狼牙先锋首领",},{nClass=20,nIcon=13,szName="离开据点·大旗重置",nTime=0,key="离开据点·大旗重置",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U59" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
       <c r="V59" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="W59" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="X59" s="6" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="60" spans="1:26">
       <c r="C60" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="D60" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="K60" t="s">
         <v>1656</v>
@@ -42818,18 +42821,18 @@
         <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",szNote="据点攻防·阴山大草原·分线·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U60" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="V60" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="61" spans="1:26">
       <c r="C61" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="D61" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
       <c r="K61" t="s">
         <v>1656</v>
@@ -42839,15 +42842,15 @@
         <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·阴山大草原·开启分线·5分钟",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U61" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="V61" t="s">
-        <v>2529</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="62" spans="1:26">
       <c r="C62" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="D62" t="s">
         <v>2283</v>
@@ -42860,15 +42863,15 @@
         <v>{szContent="前线据点之争已经打响，争夺正式开始，沙盘地图（CTRL + M）绘有详细战略意图，谁将称霸中原，我们拭目以待！\n",szNote="据点攻防·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime=10,key="阵营活动",},},},</v>
       </c>
       <c r="U62" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:26">
       <c r="C63" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="D63" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
       <c r="K63" t="s">
         <v>1656</v>
@@ -42878,15 +42881,15 @@
         <v>{szContent="阵营攻防首领战紧张火热，本服今日无奇袭场分线模式，请侠士速速前往主战场及奇袭场参与活动。\n",szNote="阵营攻防·奇袭场·未开分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·未开分线",nTime=30,key="分流活动",},},},</v>
       </c>
       <c r="U63" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:26">
       <c r="C64" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="D64" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="K64" t="s">
         <v>1656</v>
@@ -42896,7 +42899,7 @@
         <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",szNote="阵营攻防·奇袭场·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·开启分线",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
       <c r="U64" t="s">
-        <v>2535</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:26">
@@ -42913,10 +42916,10 @@
     </row>
     <row r="66" customFormat="1" spans="1:26">
       <c r="C66" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="D66" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
       <c r="K66" t="s">
         <v>1656</v>
@@ -42929,19 +42932,19 @@
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U66" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
       <c r="V66" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="W66" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="X66" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
       <c r="Y66" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:26">
@@ -42958,10 +42961,10 @@
     </row>
     <row r="68" customFormat="1" spans="1:26">
       <c r="C68" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="D68" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="K68" t="s">
         <v>1656</v>
@@ -42974,15 +42977,15 @@
         <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U68" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:26">
       <c r="C69" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="D69" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="K69" t="s">
         <v>1656</v>
@@ -42995,27 +42998,27 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U69" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="V69" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="W69" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="X69" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="Y69" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="70" customFormat="1" spans="1:26">
       <c r="C70" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="D70" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="K70" t="s">
         <v>1656</v>
@@ -43028,30 +43031,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U70" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="V70" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="W70" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="X70" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="Y70" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="Z70" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="71" customFormat="1" spans="1:26">
       <c r="C71" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="D71" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="K71" t="s">
         <v>2117</v>
@@ -43061,15 +43064,15 @@
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U71" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="72" customFormat="1" spans="1:26">
       <c r="C72" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="D72" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="K72" t="s">
         <v>2116</v>
@@ -43079,15 +43082,15 @@
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U72" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="73" customFormat="1" spans="1:26">
       <c r="C73" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="D73" t="s">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="K73" t="s">
         <v>1656</v>
@@ -43097,16 +43100,16 @@
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U73" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="V73" s="7"/>
     </row>
     <row r="74" customFormat="1" spans="1:26">
       <c r="C74" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="D74" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="K74" t="s">
         <v>1656</v>
@@ -43116,16 +43119,16 @@
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U74" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="V74" s="7"/>
     </row>
     <row r="75" customFormat="1" spans="1:26">
       <c r="C75" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="D75" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="K75" t="s">
         <v>1656</v>
@@ -43138,15 +43141,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U75" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="76" customFormat="1" spans="1:26">
       <c r="C76" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="D76" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="K76" t="s">
         <v>1656</v>
@@ -43156,18 +43159,18 @@
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U76" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="V76" s="6" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="77" customFormat="1" spans="1:26">
       <c r="C77" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="D77" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="K77" t="s">
         <v>1656</v>
@@ -43177,18 +43180,18 @@
         <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",szNote="据点攻防·阴山大草原·分线·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U77" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="V77" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="78" customFormat="1" spans="1:26">
       <c r="C78" t="s">
-        <v>2524</v>
+        <v>2525</v>
       </c>
       <c r="D78" t="s">
-        <v>2525</v>
+        <v>2526</v>
       </c>
       <c r="K78" t="s">
         <v>1656</v>
@@ -43198,15 +43201,15 @@
         <v>{szContent="前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n",szNote="据点攻防·阴山大草原",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U78" t="s">
-        <v>2526</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="79" customFormat="1" spans="1:26">
       <c r="C79" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="D79" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
       <c r="K79" t="s">
         <v>1656</v>
@@ -43216,18 +43219,18 @@
         <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·阴山大草原·开启分线·5分钟",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U79" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="V79" t="s">
-        <v>2529</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="80" customFormat="1" spans="1:26">
       <c r="C80" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="D80" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
       <c r="K80" t="s">
         <v>1656</v>
@@ -43237,15 +43240,15 @@
         <v>{szContent="阵营攻防首领战紧张火热，本服今日无奇袭场分线模式，请侠士速速前往主战场及奇袭场参与活动。\n",szNote="阵营攻防·奇袭场·未开分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·未开分线",nTime=30,key="分流活动",},},},</v>
       </c>
       <c r="U80" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="81" customFormat="1" spans="1:26">
       <c r="C81" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="D81" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="K81" t="s">
         <v>1656</v>
@@ -43255,12 +43258,12 @@
         <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",szNote="阵营攻防·奇袭场·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·开启分线",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
       <c r="U81" t="s">
-        <v>2535</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="82" customFormat="1" spans="1:26">
       <c r="A82" t="s">
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="B82">
         <v>-3</v>
@@ -43272,7 +43275,7 @@
     </row>
     <row r="83" customFormat="1" spans="1:26">
       <c r="C83" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
       <c r="K83" t="s">
         <v>2117</v>
@@ -43282,12 +43285,12 @@
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往恶人谷地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=3,szName="主战场·恶人谷",nTime="1,阵营攻防·开始排队·恶人谷;10,阵营攻防·开始排队·恶人谷",nRefresh=1,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U83" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="1:26">
       <c r="C84" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="K84" t="s">
         <v>2116</v>
@@ -43297,7 +43300,7 @@
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往浩气盟地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=7,szName="主战场·浩气盟",nTime="1,阵营攻防·开始排队·浩气盟;10,阵营攻防·开始排队·浩气盟",nRefresh=1,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U84" t="s">
-        <v>2557</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="85" customFormat="1" spans="1:26">
@@ -43314,10 +43317,10 @@
     </row>
     <row r="86" customFormat="1" spans="1:26">
       <c r="C86" t="s">
-        <v>2558</v>
+        <v>2559</v>
       </c>
       <c r="D86" t="s">
-        <v>2559</v>
+        <v>2560</v>
       </c>
       <c r="K86" t="s">
         <v>1656</v>
@@ -43327,15 +43330,15 @@
         <v>{szContent="本场攻防“奇袭场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="奇袭场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2402,nFrame=4,szName="奇袭场·平手",nTime=57,nRefresh=5,key="大攻防·奇袭场",},},},</v>
       </c>
       <c r="U86" t="s">
-        <v>2560</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="87" customFormat="1" spans="1:26">
       <c r="C87" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="D87" t="s">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="K87" t="s">
         <v>1656</v>
@@ -43345,15 +43348,15 @@
         <v>{szContent="本场攻防“主战场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="主战场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="主战场·平手",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U87" t="s">
-        <v>2563</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="88" customFormat="1" spans="1:26">
       <c r="C88" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="D88" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="K88" t="s">
         <v>1656</v>
@@ -43369,27 +43372,27 @@
         <v>{szContent="^本场攻防“([主战奇袭场]+)”已结束，([浩气盟恶人谷]+)[侠士们众志成城和，]-([大完险胜]+)([浩气盟恶人谷]+)[！，]+",szNote="{$1}·{$2}·{$3}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,szName="大攻防·奇袭场",nTime=-2,nRefresh=10,key="大攻防·奇袭场",},{nClass=20,nIcon=13,szName="大攻防·主战场",nTime=-2,nRefresh=10,key="大攻防·主战场",},{nClass=20,nIcon=13,szName="大攻防·{$1}",nTime=-2,key="大攻防·{$1}",},{nClass=20,nIcon=2402,nFrame=4,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U88" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="V88" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
       <c r="W88" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="X88" t="s">
-        <v>2564</v>
+        <v>2565</v>
       </c>
       <c r="Y88" t="s">
-        <v>2565</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="89" customFormat="1" spans="1:26">
       <c r="C89" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="D89" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="K89" t="s">
         <v>1656</v>
@@ -43405,15 +43408,15 @@
         <v>{szContent="^本场战役已结束，双方战事惨烈，但终是(.-)略胜一筹，(.-)！(.-)士气大涨(%d-)分！",szNote="据点攻防·{$1}·{$2}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U89" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="90" customFormat="1" spans="1:26">
       <c r="C90" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="D90" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="K90" t="s">
         <v>1656</v>
@@ -43426,27 +43429,27 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U90" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="V90" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="W90" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="X90" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="Y90" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="91" customFormat="1" spans="1:26">
       <c r="C91" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="D91" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="K91" t="s">
         <v>1656</v>
@@ -43459,30 +43462,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U91" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="V91" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="W91" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="X91" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="Y91" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="Z91" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="92" customFormat="1" spans="1:26">
       <c r="C92" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="D92" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="K92" t="s">
         <v>2117</v>
@@ -43492,15 +43495,15 @@
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U92" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="93" customFormat="1" spans="1:26">
       <c r="C93" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="D93" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="K93" t="s">
         <v>2116</v>
@@ -43510,15 +43513,15 @@
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U93" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="1:26">
       <c r="C94" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="D94" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="K94" t="s">
         <v>1656</v>
@@ -43531,15 +43534,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U94" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="95" customFormat="1" spans="1:26">
       <c r="C95" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="D95" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="K95" t="s">
         <v>1656</v>
@@ -43549,18 +43552,18 @@
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U95" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="V95" s="6" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="96" customFormat="1" spans="1:26">
       <c r="C96" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="D96" t="s">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="K96" t="s">
         <v>1656</v>
@@ -43570,16 +43573,16 @@
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U96" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="V96" s="7"/>
     </row>
     <row r="97" customFormat="1" spans="1:34">
       <c r="C97" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="D97" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="K97" t="s">
         <v>1656</v>
@@ -43589,7 +43592,7 @@
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
       </c>
       <c r="U97" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="V97" s="7"/>
     </row>
@@ -43607,13 +43610,13 @@
     </row>
     <row r="99" customFormat="1" spans="1:34">
       <c r="C99" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="D99" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="G99" t="s">
-        <v>2566</v>
+        <v>2567</v>
       </c>
       <c r="K99" t="s">
         <v>1656</v>
@@ -43626,7 +43629,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【武王城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="武王城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【武王城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="武王城·恶人大旗",},},},</v>
       </c>
       <c r="U99" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="V99" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G99&amp;"·浩气大旗"&amp;""",},"</f>
@@ -43637,19 +43640,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·恶人大旗",},</v>
       </c>
       <c r="X99" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="Y99" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="Z99" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="AA99" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="AB99" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="AC99" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G99&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G99&amp;"·浩气大旗"""&amp;",},"</f>
@@ -43662,10 +43665,10 @@
     </row>
     <row r="100" customFormat="1" spans="1:34">
       <c r="C100" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="D100" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="K100" t="s">
         <v>1656</v>
@@ -43678,21 +43681,21 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="武王城·大旗重置",nTime=-2,nRefresh=7200,key="武王城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【武王城】大旗重置",nTime="180,【武王城】大旗重置;185,【武王城】大旗重置·结束",nRefresh=7200,key="武王城·大旗重置",},},},</v>
       </c>
       <c r="U100" t="s">
-        <v>2572</v>
+        <v>2573</v>
       </c>
       <c r="V100" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="W100" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="X100" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="101" customFormat="1" spans="1:34">
       <c r="C101" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="K101" t="s">
         <v>1656</v>
@@ -43702,18 +43705,18 @@
         <v>{szContent="本场浩气盟攻防即将结束，南屏山物资运送暂且休整，等待下一场攻防开启！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="粮草先行·活动结束",nTime=5,key="粮草先行·浩气盟",},{nClass=20,nIcon=13,szName="粮草先行·恶人谷",nTime=0,key="粮草先行·恶人谷",},{nClass=20,nIcon=589,nFrame=7,szName="赵新宇",nTime="60,赵新宇·刷新剩余;62,赵新宇·即将刷新",nRefresh=0,key="赵新宇",},},},</v>
       </c>
       <c r="U101" t="s">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="V101" t="s">
-        <v>2577</v>
+        <v>2578</v>
       </c>
       <c r="W101" t="s">
-        <v>2578</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="102" customFormat="1" spans="1:34">
       <c r="C102" t="s">
-        <v>2579</v>
+        <v>2580</v>
       </c>
       <c r="K102" t="s">
         <v>2117</v>
@@ -43723,12 +43726,12 @@
         <v>{szContent="南屏山恶人谷伴江村援军已到，营地夺回，交通恢复！\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=589,nFrame=7,szName="赵新宇·已刷新",nTime=10,nRefresh=600,key="赵新宇",},},},</v>
       </c>
       <c r="U102" t="s">
-        <v>2580</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="103" customFormat="1" spans="1:34">
       <c r="C103" t="s">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="K103" t="s">
         <v>2116</v>
@@ -43738,7 +43741,7 @@
         <v>{szContent="南屏山浩气盟望北村援军已到，营地夺回，交通恢复！\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=308,nFrame=3,szName="方超·已刷新",nTime=10,nRefresh=600,key="方超",},},},</v>
       </c>
       <c r="U103" t="s">
-        <v>2582</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="104" spans="1:34">
@@ -43755,13 +43758,13 @@
     </row>
     <row r="105" customFormat="1" spans="1:34">
       <c r="C105" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="D105" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="G105" t="s">
-        <v>2583</v>
+        <v>2584</v>
       </c>
       <c r="K105" t="s">
         <v>1656</v>
@@ -43774,7 +43777,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凛风堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凛风堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·恶人大旗",},},},</v>
       </c>
       <c r="U105" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="V105" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G105&amp;"·浩气大旗"&amp;""",},"</f>
@@ -43785,19 +43788,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·恶人大旗",},</v>
       </c>
       <c r="X105" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="Y105" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="Z105" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="AA105" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="AB105" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="AC105" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G105&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G105&amp;"·浩气大旗"""&amp;",},"</f>
@@ -43810,10 +43813,10 @@
     </row>
     <row r="106" spans="1:34">
       <c r="C106" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="D106" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="K106" t="s">
         <v>1656</v>
@@ -43826,21 +43829,21 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凛风堡·大旗重置",nTime=-2,nRefresh=7200,key="凛风堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凛风堡】大旗重置",nTime="180,【凛风堡】大旗重置;185,【凛风堡】大旗重置·结束",nRefresh=7200,key="凛风堡·大旗重置",},},},</v>
       </c>
       <c r="U106" t="s">
-        <v>2584</v>
+        <v>2585</v>
       </c>
       <c r="V106" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="W106" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="X106" t="s">
-        <v>2585</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="107" spans="1:34">
       <c r="C107" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="K107" t="s">
         <v>1656</v>
@@ -43850,21 +43853,21 @@
         <v>{szContent="本场恶人谷攻防即将结束，昆仑物资运送暂且休整，等待下一场攻防开启！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="粮草先行·活动结束",nTime=5,key="粮草先行·恶人谷",},{nClass=20,nIcon=13,szName="粮草先行·浩气盟",nTime=0,key="粮草先行·浩气盟",},{nClass=20,nIcon=2864,nFrame=7,szName="霸图",nTime="60,霸图·刷新剩余;62,霸图·即将刷新",nRefresh=0,key="霸图",},{nClass=20,nIcon=845,nFrame=3,szName="孙永恒",nTime="60,孙永恒·刷新剩余;62,孙永恒·即将刷新",nRefresh=0,key="孙永恒",},},},</v>
       </c>
       <c r="U107" t="s">
-        <v>2586</v>
+        <v>2587</v>
       </c>
       <c r="V107" t="s">
-        <v>2587</v>
+        <v>2588</v>
       </c>
       <c r="W107" t="s">
-        <v>2588</v>
+        <v>2589</v>
       </c>
       <c r="X107" t="s">
-        <v>2589</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="108" spans="1:34">
       <c r="C108" t="s">
-        <v>2590</v>
+        <v>2591</v>
       </c>
       <c r="K108" t="s">
         <v>2117</v>
@@ -43874,12 +43877,12 @@
         <v>{szContent="昆仑山恶人谷西昆仑高地援军已到，营地夺回，交通恢复！\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2864,nFrame=7,szName="霸图·已刷新",nTime=10,nRefresh=600,key="霸图",},},},</v>
       </c>
       <c r="U108" t="s">
-        <v>2591</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="109" spans="1:34">
       <c r="C109" t="s">
-        <v>2592</v>
+        <v>2593</v>
       </c>
       <c r="K109" t="s">
         <v>2116</v>
@@ -43889,7 +43892,7 @@
         <v>{szContent="昆仑山浩气盟东昆仑高地援军已到，营地夺回，交通恢复！\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=845,nFrame=3,szName="孙永恒·已刷新",nTime=10,nRefresh=600,key="孙永恒",},},},</v>
       </c>
       <c r="U109" t="s">
-        <v>2593</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="110" spans="1:34">
@@ -43906,16 +43909,16 @@
     </row>
     <row r="111" customFormat="1" spans="1:34">
       <c r="C111" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="D111" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="G111" t="s">
-        <v>2594</v>
+        <v>2595</v>
       </c>
       <c r="H111" t="s">
-        <v>2595</v>
+        <v>2596</v>
       </c>
       <c r="K111" t="s">
         <v>1656</v>
@@ -43928,7 +43931,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【盘龙坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【逐鹿坪】恶人·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【盘龙坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【逐鹿坪】浩气·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·恶人大旗",},},},</v>
       </c>
       <c r="U111" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="V111" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G111&amp;"·浩气大旗"&amp;""",},"</f>
@@ -43947,19 +43950,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·恶人大旗",},</v>
       </c>
       <c r="Z111" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="AA111" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="AB111" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="AC111" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="AD111" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="AE111" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G111&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G111&amp;"·浩气大旗"""&amp;",},"</f>
@@ -43980,10 +43983,10 @@
     </row>
     <row r="112" spans="1:34">
       <c r="C112" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="D112" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="K112" t="s">
         <v>1656</v>
@@ -43996,22 +43999,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="盘龙坞·大旗重置",nTime=-2,nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=1465,szName="逐鹿坪·大旗重置",nTime=-2,nRefresh=7200,key="逐鹿坪·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【盘龙坞】大旗重置",nTime="180,【盘龙坞】大旗重置;185,【盘龙坞】大旗重置·结束",nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【逐鹿坪】大旗重置",nTime="180,【逐鹿坪】大旗重置;185,【逐鹿坪】大旗重置·结束",nRefresh=7200,key="逐鹿坪·大旗重置",},},},</v>
       </c>
       <c r="U112" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="V112" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="W112" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="X112" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="Y112" t="s">
-        <v>2598</v>
+        <v>2599</v>
       </c>
       <c r="Z112" t="s">
-        <v>2599</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="113" spans="1:34">
@@ -44028,16 +44031,16 @@
     </row>
     <row r="114" customFormat="1" spans="1:34">
       <c r="C114" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="D114" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="G114" t="s">
-        <v>2600</v>
+        <v>2601</v>
       </c>
       <c r="H114" t="s">
-        <v>2601</v>
+        <v>2602</v>
       </c>
       <c r="K114" t="s">
         <v>1656</v>
@@ -44050,7 +44053,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【龙门镇】恶人·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【飞沙关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【龙门镇】浩气·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【飞沙关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·恶人大旗",},},},</v>
       </c>
       <c r="U114" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="V114" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G114&amp;"·浩气大旗"&amp;""",},"</f>
@@ -44069,19 +44072,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·恶人大旗",},</v>
       </c>
       <c r="Z114" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="AA114" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="AB114" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="AC114" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="AD114" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="AE114" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G114&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G114&amp;"·浩气大旗"""&amp;",},"</f>
@@ -44102,10 +44105,10 @@
     </row>
     <row r="115" spans="1:34">
       <c r="C115" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="D115" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="K115" t="s">
         <v>1656</v>
@@ -44118,22 +44121,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="龙门镇·大旗重置",nTime=-2,nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=1465,szName="飞沙关·大旗重置",nTime=-2,nRefresh=7200,key="飞沙关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【龙门镇】大旗重置",nTime="180,【龙门镇】大旗重置;185,【龙门镇】大旗重置·结束",nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【飞沙关】大旗重置",nTime="180,【飞沙关】大旗重置;185,【飞沙关】大旗重置·结束",nRefresh=7200,key="飞沙关·大旗重置",},},},</v>
       </c>
       <c r="U115" t="s">
-        <v>2602</v>
+        <v>2603</v>
       </c>
       <c r="V115" t="s">
-        <v>2603</v>
+        <v>2604</v>
       </c>
       <c r="W115" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="X115" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="Y115" t="s">
-        <v>2604</v>
+        <v>2605</v>
       </c>
       <c r="Z115" t="s">
-        <v>2605</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="116" spans="1:34">
@@ -44150,16 +44153,16 @@
     </row>
     <row r="117" customFormat="1" spans="1:34">
       <c r="C117" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="D117" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="G117" t="s">
-        <v>2606</v>
+        <v>2607</v>
       </c>
       <c r="H117" t="s">
-        <v>2607</v>
+        <v>2608</v>
       </c>
       <c r="K117" t="s">
         <v>1656</v>
@@ -44172,7 +44175,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【红莲岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【秋雨堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【红莲岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【秋雨堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·恶人大旗",},},},</v>
       </c>
       <c r="U117" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="V117" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G117&amp;"·浩气大旗"&amp;""",},"</f>
@@ -44191,19 +44194,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},</v>
       </c>
       <c r="Z117" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="AA117" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="AB117" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="AC117" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="AD117" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="AE117" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G117&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G117&amp;"·浩气大旗"""&amp;",},"</f>
@@ -44224,10 +44227,10 @@
     </row>
     <row r="118" spans="1:34">
       <c r="C118" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="D118" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="K118" t="s">
         <v>1656</v>
@@ -44240,22 +44243,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="红莲岗·大旗重置",nTime=-2,nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=1465,szName="秋雨堡·大旗重置",nTime=-2,nRefresh=7200,key="秋雨堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【红莲岗】大旗重置",nTime="180,【红莲岗】大旗重置;185,【红莲岗】大旗重置·结束",nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【秋雨堡】大旗重置",nTime="180,【秋雨堡】大旗重置;185,【秋雨堡】大旗重置·结束",nRefresh=7200,key="秋雨堡·大旗重置",},},},</v>
       </c>
       <c r="U118" t="s">
-        <v>2608</v>
+        <v>2609</v>
       </c>
       <c r="V118" t="s">
-        <v>2609</v>
+        <v>2610</v>
       </c>
       <c r="W118" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="X118" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="Y118" t="s">
-        <v>2610</v>
+        <v>2611</v>
       </c>
       <c r="Z118" t="s">
-        <v>2611</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="119" spans="1:34">
@@ -44272,16 +44275,16 @@
     </row>
     <row r="120" customFormat="1" spans="1:34">
       <c r="C120" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="D120" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="G120" t="s">
-        <v>2612</v>
+        <v>2613</v>
       </c>
       <c r="H120" t="s">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="K120" t="s">
         <v>1656</v>
@@ -44294,7 +44297,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【金门关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="金门关·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【青云坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【金门关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="金门关·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【青云坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·恶人大旗",},},},</v>
       </c>
       <c r="U120" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="V120" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G120&amp;"·浩气大旗"&amp;""",},"</f>
@@ -44313,19 +44316,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·恶人大旗",},</v>
       </c>
       <c r="Z120" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="AA120" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="AB120" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="AC120" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="AD120" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="AE120" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G120&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G120&amp;"·浩气大旗"""&amp;",},"</f>
@@ -44346,10 +44349,10 @@
     </row>
     <row r="121" spans="1:34">
       <c r="C121" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="D121" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="K121" t="s">
         <v>1656</v>
@@ -44362,22 +44365,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="金门关·大旗重置",nTime=-2,nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=1465,szName="青云坞·大旗重置",nTime=-2,nRefresh=7200,key="青云坞·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【金门关】大旗重置",nTime="180,【金门关】大旗重置;185,【金门关】大旗重置·结束",nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【青云坞】大旗重置",nTime="180,【青云坞】大旗重置;185,【青云坞】大旗重置·结束",nRefresh=7200,key="青云坞·大旗重置",},},},</v>
       </c>
       <c r="U121" t="s">
-        <v>2614</v>
+        <v>2615</v>
       </c>
       <c r="V121" t="s">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="W121" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="X121" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="Y121" t="s">
-        <v>2616</v>
+        <v>2617</v>
       </c>
       <c r="Z121" t="s">
-        <v>2617</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="122" spans="1:34">
@@ -44394,16 +44397,16 @@
     </row>
     <row r="123" customFormat="1" spans="1:34">
       <c r="C123" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="D123" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="G123" t="s">
-        <v>2618</v>
+        <v>2619</v>
       </c>
       <c r="H123" t="s">
-        <v>2619</v>
+        <v>2620</v>
       </c>
       <c r="K123" t="s">
         <v>1656</v>
@@ -44416,7 +44419,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【激流坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【不空关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="不空关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【激流坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【不空关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="不空关·恶人大旗",},},},</v>
       </c>
       <c r="U123" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="V123" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G123&amp;"·浩气大旗"&amp;""",},"</f>
@@ -44435,19 +44438,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·恶人大旗",},</v>
       </c>
       <c r="Z123" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="AA123" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="AB123" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="AC123" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="AD123" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="AE123" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G123&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G123&amp;"·浩气大旗"""&amp;",},"</f>
@@ -44468,10 +44471,10 @@
     </row>
     <row r="124" spans="1:34">
       <c r="C124" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="D124" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="K124" t="s">
         <v>1656</v>
@@ -44484,22 +44487,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="激流坞·大旗重置",nTime=-2,nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=1465,szName="不空关·大旗重置",nTime=-2,nRefresh=7200,key="不空关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【激流坞】大旗重置",nTime="180,【激流坞】大旗重置;185,【激流坞】大旗重置·结束",nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【不空关】大旗重置",nTime="180,【不空关】大旗重置;185,【不空关】大旗重置·结束",nRefresh=7200,key="不空关·大旗重置",},},},</v>
       </c>
       <c r="U124" t="s">
-        <v>2620</v>
+        <v>2621</v>
       </c>
       <c r="V124" t="s">
-        <v>2621</v>
+        <v>2622</v>
       </c>
       <c r="W124" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="X124" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="Y124" t="s">
-        <v>2622</v>
+        <v>2623</v>
       </c>
       <c r="Z124" t="s">
-        <v>2623</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="125" spans="1:34">
@@ -44516,16 +44519,16 @@
     </row>
     <row r="126" customFormat="1" spans="1:34">
       <c r="C126" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="D126" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="G126" t="s">
-        <v>2624</v>
+        <v>2625</v>
       </c>
       <c r="H126" t="s">
-        <v>2625</v>
+        <v>2626</v>
       </c>
       <c r="K126" t="s">
         <v>1656</v>
@@ -44538,7 +44541,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【日月崖】恶人·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【卧龙坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【日月崖】浩气·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【卧龙坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·恶人大旗",},},},</v>
       </c>
       <c r="U126" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="V126" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G126&amp;"·浩气大旗"&amp;""",},"</f>
@@ -44557,19 +44560,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·恶人大旗",},</v>
       </c>
       <c r="Z126" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="AA126" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="AB126" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="AC126" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="AD126" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="AE126" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G126&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G126&amp;"·浩气大旗"""&amp;",},"</f>
@@ -44590,10 +44593,10 @@
     </row>
     <row r="127" spans="1:34">
       <c r="C127" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="D127" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="K127" t="s">
         <v>1656</v>
@@ -44606,22 +44609,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="日月崖·大旗重置",nTime=-2,nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=1465,szName="卧龙坡·大旗重置",nTime=-2,nRefresh=7200,key="卧龙坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【日月崖】大旗重置",nTime="180,【日月崖】大旗重置;185,【日月崖】大旗重置·结束",nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【卧龙坡】大旗重置",nTime="180,【卧龙坡】大旗重置;185,【卧龙坡】大旗重置·结束",nRefresh=7200,key="卧龙坡·大旗重置",},},},</v>
       </c>
       <c r="U127" t="s">
-        <v>2626</v>
+        <v>2627</v>
       </c>
       <c r="V127" t="s">
-        <v>2627</v>
+        <v>2628</v>
       </c>
       <c r="W127" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="X127" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="Y127" t="s">
-        <v>2628</v>
+        <v>2629</v>
       </c>
       <c r="Z127" t="s">
-        <v>2629</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="128" spans="1:34">
@@ -44638,16 +44641,16 @@
     </row>
     <row r="129" customFormat="1" spans="1:34">
       <c r="C129" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="D129" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="G129" t="s">
-        <v>2630</v>
+        <v>2631</v>
       </c>
       <c r="H129" t="s">
-        <v>2631</v>
+        <v>2632</v>
       </c>
       <c r="K129" t="s">
         <v>1656</v>
@@ -44660,7 +44663,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【霜戈堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【澜沧城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【霜戈堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【澜沧城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·恶人大旗",},},},</v>
       </c>
       <c r="U129" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="V129" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G129&amp;"·浩气大旗"&amp;""",},"</f>
@@ -44679,19 +44682,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·恶人大旗",},</v>
       </c>
       <c r="Z129" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="AA129" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="AB129" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="AC129" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="AD129" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="AE129" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G129&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G129&amp;"·浩气大旗"""&amp;",},"</f>
@@ -44712,10 +44715,10 @@
     </row>
     <row r="130" spans="1:34">
       <c r="C130" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="D130" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="K130" t="s">
         <v>1656</v>
@@ -44728,22 +44731,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="霜戈堡·大旗重置",nTime=-2,nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=1465,szName="澜沧城·大旗重置",nTime=-2,nRefresh=7200,key="澜沧城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【霜戈堡】大旗重置",nTime="180,【霜戈堡】大旗重置;185,【霜戈堡】大旗重置·结束",nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【澜沧城】大旗重置",nTime="180,【澜沧城】大旗重置;185,【澜沧城】大旗重置·结束",nRefresh=7200,key="澜沧城·大旗重置",},},},</v>
       </c>
       <c r="U130" t="s">
-        <v>2632</v>
+        <v>2633</v>
       </c>
       <c r="V130" t="s">
-        <v>2633</v>
+        <v>2634</v>
       </c>
       <c r="W130" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="X130" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="Y130" t="s">
-        <v>2634</v>
+        <v>2635</v>
       </c>
       <c r="Z130" t="s">
-        <v>2635</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="131" spans="1:34">
@@ -44760,16 +44763,16 @@
     </row>
     <row r="132" customFormat="1" spans="1:34">
       <c r="C132" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="D132" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="G132" t="s">
-        <v>2636</v>
+        <v>2637</v>
       </c>
       <c r="H132" t="s">
-        <v>2637</v>
+        <v>2638</v>
       </c>
       <c r="K132" t="s">
         <v>1656</v>
@@ -44782,7 +44785,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【神池岭】恶人·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【烈日岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【神池岭】浩气·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【烈日岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·恶人大旗",},},},</v>
       </c>
       <c r="U132" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="V132" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G132&amp;"·浩气大旗"&amp;""",},"</f>
@@ -44801,19 +44804,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·恶人大旗",},</v>
       </c>
       <c r="Z132" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="AA132" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="AB132" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="AC132" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="AD132" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="AE132" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G132&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G132&amp;"·浩气大旗"""&amp;",},"</f>
@@ -44834,10 +44837,10 @@
     </row>
     <row r="133" spans="1:34">
       <c r="C133" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="D133" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="K133" t="s">
         <v>1656</v>
@@ -44850,22 +44853,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="神池岭·大旗重置",nTime=-2,nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=1465,szName="烈日岗·大旗重置",nTime=-2,nRefresh=7200,key="烈日岗·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【神池岭】大旗重置",nTime="180,【神池岭】大旗重置;185,【神池岭】大旗重置·结束",nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【烈日岗】大旗重置",nTime="180,【烈日岗】大旗重置;185,【烈日岗】大旗重置·结束",nRefresh=7200,key="烈日岗·大旗重置",},},},</v>
       </c>
       <c r="U133" t="s">
-        <v>2638</v>
+        <v>2639</v>
       </c>
       <c r="V133" t="s">
-        <v>2639</v>
+        <v>2640</v>
       </c>
       <c r="W133" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="X133" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="Y133" t="s">
-        <v>2640</v>
+        <v>2641</v>
       </c>
       <c r="Z133" t="s">
-        <v>2641</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="134" spans="1:34">
@@ -44882,16 +44885,16 @@
     </row>
     <row r="135" customFormat="1" spans="1:34">
       <c r="C135" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="D135" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="G135" t="s">
-        <v>2642</v>
+        <v>2643</v>
       </c>
       <c r="H135" t="s">
-        <v>2643</v>
+        <v>2644</v>
       </c>
       <c r="K135" t="s">
         <v>1656</v>
@@ -44904,7 +44907,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凤鸣堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【惊虬谷】恶人·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凤鸣堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【惊虬谷】浩气·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·恶人大旗",},},},</v>
       </c>
       <c r="U135" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="V135" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G135&amp;"·浩气大旗"&amp;""",},"</f>
@@ -44923,19 +44926,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},</v>
       </c>
       <c r="Z135" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="AA135" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="AB135" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="AC135" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="AD135" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="AE135" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G135&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G135&amp;"·浩气大旗"""&amp;",},"</f>
@@ -44956,10 +44959,10 @@
     </row>
     <row r="136" spans="1:34">
       <c r="C136" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="D136" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="K136" t="s">
         <v>1656</v>
@@ -44972,22 +44975,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凤鸣堡·大旗重置",nTime=-2,nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=1465,szName="惊虬谷·大旗重置",nTime=-2,nRefresh=7200,key="惊虬谷·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凤鸣堡】大旗重置",nTime="180,【凤鸣堡】大旗重置;185,【凤鸣堡】大旗重置·结束",nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【惊虬谷】大旗重置",nTime="180,【惊虬谷】大旗重置;185,【惊虬谷】大旗重置·结束",nRefresh=7200,key="惊虬谷·大旗重置",},},},</v>
       </c>
       <c r="U136" t="s">
-        <v>2644</v>
+        <v>2645</v>
       </c>
       <c r="V136" t="s">
-        <v>2645</v>
+        <v>2646</v>
       </c>
       <c r="W136" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="X136" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="Y136" t="s">
-        <v>2646</v>
+        <v>2647</v>
       </c>
       <c r="Z136" t="s">
-        <v>2647</v>
+        <v>2648</v>
       </c>
     </row>
     <row r="137" spans="1:34">
@@ -45004,16 +45007,16 @@
     </row>
     <row r="138" customFormat="1" spans="1:34">
       <c r="C138" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="D138" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="G138" t="s">
-        <v>2648</v>
+        <v>2649</v>
       </c>
       <c r="H138" t="s">
-        <v>2649</v>
+        <v>2650</v>
       </c>
       <c r="K138" t="s">
         <v>1656</v>
@@ -45026,7 +45029,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【大理山城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【千岩关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【大理山城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【千岩关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·恶人大旗",},},},</v>
       </c>
       <c r="U138" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="V138" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G138&amp;"·浩气大旗"&amp;""",},"</f>
@@ -45045,19 +45048,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·恶人大旗",},</v>
       </c>
       <c r="Z138" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="AA138" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="AB138" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="AC138" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="AD138" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="AE138" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G138&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G138&amp;"·浩气大旗"""&amp;",},"</f>
@@ -45078,10 +45081,10 @@
     </row>
     <row r="139" spans="1:34">
       <c r="C139" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="D139" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="K139" t="s">
         <v>1656</v>
@@ -45094,22 +45097,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="大理山城·大旗重置",nTime=-2,nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=1465,szName="千岩关·大旗重置",nTime=-2,nRefresh=7200,key="千岩关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【大理山城】大旗重置",nTime="180,【大理山城】大旗重置;185,【大理山城】大旗重置·结束",nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【千岩关】大旗重置",nTime="180,【千岩关】大旗重置;185,【千岩关】大旗重置·结束",nRefresh=7200,key="千岩关·大旗重置",},},},</v>
       </c>
       <c r="U139" t="s">
-        <v>2650</v>
+        <v>2651</v>
       </c>
       <c r="V139" t="s">
-        <v>2651</v>
+        <v>2652</v>
       </c>
       <c r="W139" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="X139" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="Y139" t="s">
-        <v>2652</v>
+        <v>2653</v>
       </c>
       <c r="Z139" t="s">
-        <v>2653</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="140" spans="1:34">
@@ -45126,16 +45129,16 @@
     </row>
     <row r="141" customFormat="1" spans="1:34">
       <c r="C141" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="D141" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="G141" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="H141" t="s">
-        <v>2655</v>
+        <v>2656</v>
       </c>
       <c r="K141" t="s">
         <v>1656</v>
@@ -45148,7 +45151,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【枫湖寨】恶人·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【啖杏林】恶人·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【枫湖寨】浩气·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【啖杏林】浩气·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·恶人大旗",},},},</v>
       </c>
       <c r="U141" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="V141" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G141&amp;"·浩气大旗"&amp;""",},"</f>
@@ -45167,19 +45170,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·恶人大旗",},</v>
       </c>
       <c r="Z141" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="AA141" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="AB141" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="AC141" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="AD141" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="AE141" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G141&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G141&amp;"·浩气大旗"""&amp;",},"</f>
@@ -45200,10 +45203,10 @@
     </row>
     <row r="142" spans="1:34">
       <c r="C142" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="D142" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="K142" t="s">
         <v>1656</v>
@@ -45216,22 +45219,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="枫湖寨·大旗重置",nTime=-2,nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=1465,szName="啖杏林·大旗重置",nTime=-2,nRefresh=7200,key="啖杏林·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【枫湖寨】大旗重置",nTime="180,【枫湖寨】大旗重置;185,【枫湖寨】大旗重置·结束",nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【啖杏林】大旗重置",nTime="180,【啖杏林】大旗重置;185,【啖杏林】大旗重置·结束",nRefresh=7200,key="啖杏林·大旗重置",},},},</v>
       </c>
       <c r="U142" t="s">
-        <v>2656</v>
+        <v>2657</v>
       </c>
       <c r="V142" t="s">
-        <v>2657</v>
+        <v>2658</v>
       </c>
       <c r="W142" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="X142" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="Y142" t="s">
-        <v>2658</v>
+        <v>2659</v>
       </c>
       <c r="Z142" t="s">
-        <v>2659</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="143" spans="1:34">
@@ -45248,16 +45251,16 @@
     </row>
     <row r="144" customFormat="1" spans="1:34">
       <c r="C144" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="D144" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="G144" t="s">
-        <v>2660</v>
+        <v>2661</v>
       </c>
       <c r="H144" t="s">
-        <v>2661</v>
+        <v>2662</v>
       </c>
       <c r="K144" t="s">
         <v>1656</v>
@@ -45270,7 +45273,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【扶风郡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【世外坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【扶风郡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【世外坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U144" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="V144" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G144&amp;"·浩气大旗"&amp;""",},"</f>
@@ -45289,19 +45292,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·恶人大旗",},</v>
       </c>
       <c r="Z144" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="AA144" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="AB144" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="AC144" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="AD144" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="AE144" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G144&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G144&amp;"·浩气大旗"""&amp;",},"</f>
@@ -45322,10 +45325,10 @@
     </row>
     <row r="145" spans="1:26">
       <c r="C145" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="D145" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="K145" t="s">
         <v>1656</v>
@@ -45338,22 +45341,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="扶风郡·大旗重置",nTime=-2,nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=1465,szName="世外坡·大旗重置",nTime=-2,nRefresh=7200,key="世外坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【扶风郡】大旗重置",nTime="180,【扶风郡】大旗重置;185,【扶风郡】大旗重置·结束",nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【世外坡】大旗重置",nTime="180,【世外坡】大旗重置;185,【世外坡】大旗重置·结束",nRefresh=7200,key="世外坡·大旗重置",},},},</v>
       </c>
       <c r="U145" t="s">
-        <v>2662</v>
+        <v>2663</v>
       </c>
       <c r="V145" t="s">
-        <v>2663</v>
+        <v>2664</v>
       </c>
       <c r="W145" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="X145" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="Y145" t="s">
-        <v>2664</v>
+        <v>2665</v>
       </c>
       <c r="Z145" t="s">
-        <v>2665</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="146" spans="1:26">
@@ -45370,16 +45373,16 @@
     </row>
     <row r="147" spans="1:26">
       <c r="C147" t="s">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="D147" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="G147" t="s">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="H147" t="s">
-        <v>2668</v>
+        <v>2669</v>
       </c>
       <c r="K147" t="s">
         <v>1656</v>
@@ -45392,30 +45395,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U147" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="V147" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="W147" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="X147" t="s">
-        <v>2669</v>
+        <v>2670</v>
       </c>
       <c r="Y147" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="Z147" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="148" spans="1:26">
       <c r="C148" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="D148" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="K148" t="s">
         <v>1656</v>
@@ -45428,30 +45431,30 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime="180,【云台营】大旗重置;185,【云台营】大旗重置·结束",nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime="180,【高阳营】大旗重置;185,【高阳营】大旗重置·结束",nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U148" t="s">
-        <v>2670</v>
+        <v>2671</v>
       </c>
       <c r="V148" t="s">
-        <v>2671</v>
+        <v>2672</v>
       </c>
       <c r="W148" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="X148" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="Y148" t="s">
-        <v>2672</v>
+        <v>2673</v>
       </c>
       <c r="Z148" t="s">
-        <v>2673</v>
+        <v>2674</v>
       </c>
     </row>
     <row r="149" customFormat="1" spans="1:26">
       <c r="C149" s="3" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="D149" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
       <c r="K149" t="s">
         <v>1656</v>
@@ -45464,19 +45467,19 @@
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U149" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
       <c r="V149" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="W149" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="X149" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
       <c r="Y149" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="150" spans="1:26">
@@ -45493,16 +45496,16 @@
     </row>
     <row r="151" spans="1:26">
       <c r="C151" t="s">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="D151" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="G151" t="s">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="H151" t="s">
-        <v>2668</v>
+        <v>2669</v>
       </c>
       <c r="K151" t="s">
         <v>1656</v>
@@ -45515,30 +45518,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U151" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="V151" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="W151" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="X151" t="s">
-        <v>2669</v>
+        <v>2670</v>
       </c>
       <c r="Y151" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="Z151" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="152" spans="1:26">
       <c r="C152" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="D152" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="K152" t="s">
         <v>1656</v>
@@ -45551,30 +45554,30 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime="180,【云台营】大旗重置;185,【云台营】大旗重置·结束",nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime="180,【高阳营】大旗重置;185,【高阳营】大旗重置·结束",nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U152" t="s">
-        <v>2670</v>
+        <v>2671</v>
       </c>
       <c r="V152" t="s">
-        <v>2671</v>
+        <v>2672</v>
       </c>
       <c r="W152" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="X152" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="Y152" t="s">
-        <v>2672</v>
+        <v>2673</v>
       </c>
       <c r="Z152" t="s">
-        <v>2673</v>
+        <v>2674</v>
       </c>
     </row>
     <row r="153" customFormat="1" spans="1:26">
       <c r="C153" s="3" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="D153" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
       <c r="K153" t="s">
         <v>1656</v>
@@ -45587,19 +45590,19 @@
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U153" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
       <c r="V153" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="W153" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="X153" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
       <c r="Y153" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="154" spans="1:26">

--- a/阵营/大小攻防团队监控.xlsx
+++ b/阵营/大小攻防团队监控.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据总控" sheetId="2" r:id="rId1"/>
@@ -5017,7 +5017,7 @@
     <t>{nClass=8,nIcon=1537,nFrame=0,nTime="1,屹立不倒·{$sender}·正在释放;9.5,屹立不倒·{$sender}·50减伤;32.5,屹立不倒·{$sender}·释放剩余;40.5,屹立不倒·{$sender}·延迟释放;50,屹立不倒·{$sender}·随时释放",szName="屹立不倒",nRefresh=0,key="屹立不倒",},</t>
   </si>
   <si>
-    <t>{nClass=9,nIcon=1537,nFrame=0,nTime="9,屹立不倒·{$sender}·50减伤;31.5,屹立不倒·{$sender}·释放剩余;40,屹立不倒·{$sender}·延迟释放;50,屹立不倒·{$sender}·随时释放",szName="屹立不倒",nRefresh=1,key="屹立不倒",},</t>
+    <t>{nClass=9,nIcon=1537,nFrame=0,nTime="9,屹立不倒·{$sender}·50减伤;31.5,屹立不倒·{$sender}·释放剩余;40,屹立不倒·{$sender}·延迟释放;50,屹立不倒·{$sender}·随时释放",szName="屹立不倒",nRefresh=5,key="屹立不倒",},</t>
   </si>
   <si>
     <t>数量</t>
@@ -7015,7 +7015,7 @@
     <t>{nClass=20,nIcon=13354,nFrame=4,szName="阵营事件·本周战平",nTime=60,key="阵营活动",},</t>
   </si>
   <si>
-    <t>[团队监控]数据加载成功</t>
+    <t>[团队监控]数据加载</t>
   </si>
   <si>
     <t>关闭刷马等计时条</t>
@@ -9111,7 +9111,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="34" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1786120373000,</v>
+        <v>nTimeStamp = 1786200569000,</v>
       </c>
       <c r="B4" s="38" t="s">
         <v>11</v>
@@ -24064,7 +24064,7 @@
       </c>
       <c r="X4" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7242,nLevel=1,szNote="屹立不倒",[9]={},[8]={bScreenHead=true,},tCountdown={{nClass=8,nIcon=1537,nFrame=0,nTime="1,屹立不倒·{$sender}·正在释放;9.5,屹立不倒·{$sender}·50减伤;32.5,屹立不倒·{$sender}·释放剩余;40.5,屹立不倒·{$sender}·延迟释放;50,屹立不倒·{$sender}·随时释放",szName="屹立不倒",nRefresh=0,key="屹立不倒",},{nClass=9,nIcon=1537,nFrame=0,nTime="9,屹立不倒·{$sender}·50减伤;31.5,屹立不倒·{$sender}·释放剩余;40,屹立不倒·{$sender}·延迟释放;50,屹立不倒·{$sender}·随时释放",szName="屹立不倒",nRefresh=1,key="屹立不倒",},},},</v>
+        <v>{dwID=7242,nLevel=1,szNote="屹立不倒",[9]={},[8]={bScreenHead=true,},tCountdown={{nClass=8,nIcon=1537,nFrame=0,nTime="1,屹立不倒·{$sender}·正在释放;9.5,屹立不倒·{$sender}·50减伤;32.5,屹立不倒·{$sender}·释放剩余;40.5,屹立不倒·{$sender}·延迟释放;50,屹立不倒·{$sender}·随时释放",szName="屹立不倒",nRefresh=0,key="屹立不倒",},{nClass=9,nIcon=1537,nFrame=0,nTime="9,屹立不倒·{$sender}·50减伤;31.5,屹立不倒·{$sender}·释放剩余;40,屹立不倒·{$sender}·延迟释放;50,屹立不倒·{$sender}·随时释放",szName="屹立不倒",nRefresh=5,key="屹立不倒",},},},</v>
       </c>
       <c r="Y4" t="s">
         <v>1651</v>
@@ -37567,7 +37567,7 @@
         <v>9</v>
       </c>
       <c r="V131" t="str">
-        <f t="shared" ref="V131:V162" si="20">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(D131),ISBLANK(N131),ISBLANK(O131),OR(ISBLANK(B130)=FALSE,ISBLANK(D130)=FALSE,ISBLANK(N130)=FALSE,ISBLANK(O130)=FALSE)),"},},}",IF(ISBLANK(D131),"","{szContent="""&amp;D131&amp;""","&amp;IF(C131&lt;&gt;"","szTarget="""&amp;C131&amp;""",","")&amp;IF(E131&lt;&gt;"","szNote="""&amp;E131&amp;""",","")&amp;IF(M131&lt;&gt;"","col={"&amp;M131&amp;"},","")&amp;IF(N131&gt;0,"bSearch=true,","")&amp;IF(O131&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P131&gt;0,"szVoice="""&amp;P131&amp;""",","")&amp;IF(Q131&gt;0,"bTeamChannel=true,","")&amp;IF(R131&gt;0,"bWhisperChannel=true,","")&amp;IF(S131&gt;0,"bCenterAlarm=true,","")&amp;IF(T131&gt;0,"bScreenHead=true,","")&amp;IF(U131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W131:AAH131)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="V131:V169" si="20">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(D131),ISBLANK(N131),ISBLANK(O131),OR(ISBLANK(B130)=FALSE,ISBLANK(D130)=FALSE,ISBLANK(N130)=FALSE,ISBLANK(O130)=FALSE)),"},},}",IF(ISBLANK(D131),"","{szContent="""&amp;D131&amp;""","&amp;IF(C131&lt;&gt;"","szTarget="""&amp;C131&amp;""",","")&amp;IF(E131&lt;&gt;"","szNote="""&amp;E131&amp;""",","")&amp;IF(M131&lt;&gt;"","col={"&amp;M131&amp;"},","")&amp;IF(N131&gt;0,"bSearch=true,","")&amp;IF(O131&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P131&gt;0,"szVoice="""&amp;P131&amp;""",","")&amp;IF(Q131&gt;0,"bTeamChannel=true,","")&amp;IF(R131&gt;0,"bWhisperChannel=true,","")&amp;IF(S131&gt;0,"bCenterAlarm=true,","")&amp;IF(T131&gt;0,"bScreenHead=true,","")&amp;IF(U131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W131:AAH131)&amp;"},","")&amp;"},")))</f>
         <v>},[9]={</v>
       </c>
     </row>
@@ -38307,7 +38307,7 @@
         <v>1</v>
       </c>
       <c r="V163" t="str">
-        <f>IF(ISBLANK(B163)=FALSE,IF(ISBLANK(B162),"},["&amp;B163&amp;"]={","["&amp;B163&amp;"]={"),IF(AND(ISBLANK(B163),ISBLANK(D163),ISBLANK(N163),ISBLANK(O163),OR(ISBLANK(B162)=FALSE,ISBLANK(D162)=FALSE,ISBLANK(N162)=FALSE,ISBLANK(O162)=FALSE)),"},},}",IF(ISBLANK(D163),"","{szContent="""&amp;D163&amp;""","&amp;IF(C163&lt;&gt;"","szTarget="""&amp;C163&amp;""",","")&amp;IF(E163&lt;&gt;"","szNote="""&amp;E163&amp;""",","")&amp;IF(M163&lt;&gt;"","col={"&amp;M163&amp;"},","")&amp;IF(N163&gt;0,"bSearch=true,","")&amp;IF(O163&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P163&gt;0,"szVoice="""&amp;P163&amp;""",","")&amp;IF(Q163&gt;0,"bTeamChannel=true,","")&amp;IF(R163&gt;0,"bWhisperChannel=true,","")&amp;IF(S163&gt;0,"bCenterAlarm=true,","")&amp;IF(T163&gt;0,"bScreenHead=true,","")&amp;IF(U163&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W163&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W163:AAH163)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="^【(.-)】据点大旗受损，获得(%d-)层易伤，当前总计【(%d-)层易伤】！",szTarget="%",szNote="【{$1}】大旗·易伤{$3}层",col={255,50,255,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=16834,nFrame=1,szName="大旗易伤",nTime=-1,nRefresh=2,key="大旗易伤",},{nClass=14,nIcon=16834,nFrame=1,szName="【{$1}】大旗·易伤{$3}层",nTime="60,【{$1}】大旗·易伤{$3}层;62,【{$1}】大旗·易伤冷却结束",nRefresh=0,key="{$1}·大旗易伤",},},},</v>
       </c>
       <c r="W163" t="s">
@@ -38337,7 +38337,7 @@
         <v>1</v>
       </c>
       <c r="V164" t="str">
-        <f>IF(ISBLANK(B164)=FALSE,IF(ISBLANK(B163),"},["&amp;B164&amp;"]={","["&amp;B164&amp;"]={"),IF(AND(ISBLANK(B164),ISBLANK(D164),ISBLANK(N164),ISBLANK(O164),OR(ISBLANK(B163)=FALSE,ISBLANK(D163)=FALSE,ISBLANK(N163)=FALSE,ISBLANK(O163)=FALSE)),"},},}",IF(ISBLANK(D164),"","{szContent="""&amp;D164&amp;""","&amp;IF(C164&lt;&gt;"","szTarget="""&amp;C164&amp;""",","")&amp;IF(E164&lt;&gt;"","szNote="""&amp;E164&amp;""",","")&amp;IF(M164&lt;&gt;"","col={"&amp;M164&amp;"},","")&amp;IF(N164&gt;0,"bSearch=true,","")&amp;IF(O164&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P164&gt;0,"szVoice="""&amp;P164&amp;""",","")&amp;IF(Q164&gt;0,"bTeamChannel=true,","")&amp;IF(R164&gt;0,"bWhisperChannel=true,","")&amp;IF(S164&gt;0,"bCenterAlarm=true,","")&amp;IF(T164&gt;0,"bScreenHead=true,","")&amp;IF(U164&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W164&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W164:AAH164)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W164" t="s">
@@ -38361,7 +38361,7 @@
         <v>1</v>
       </c>
       <c r="V165" t="str">
-        <f>IF(ISBLANK(B165)=FALSE,IF(ISBLANK(B164),"},["&amp;B165&amp;"]={","["&amp;B165&amp;"]={"),IF(AND(ISBLANK(B165),ISBLANK(D165),ISBLANK(N165),ISBLANK(O165),OR(ISBLANK(B164)=FALSE,ISBLANK(D164)=FALSE,ISBLANK(N164)=FALSE,ISBLANK(O164)=FALSE)),"},},}",IF(ISBLANK(D165),"","{szContent="""&amp;D165&amp;""","&amp;IF(C165&lt;&gt;"","szTarget="""&amp;C165&amp;""",","")&amp;IF(E165&lt;&gt;"","szNote="""&amp;E165&amp;""",","")&amp;IF(M165&lt;&gt;"","col={"&amp;M165&amp;"},","")&amp;IF(N165&gt;0,"bSearch=true,","")&amp;IF(O165&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P165&gt;0,"szVoice="""&amp;P165&amp;""",","")&amp;IF(Q165&gt;0,"bTeamChannel=true,","")&amp;IF(R165&gt;0,"bWhisperChannel=true,","")&amp;IF(S165&gt;0,"bCenterAlarm=true,","")&amp;IF(T165&gt;0,"bScreenHead=true,","")&amp;IF(U165&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W165&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W165:AAH165)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},},},</v>
       </c>
       <c r="W165" t="s">
@@ -38395,7 +38395,7 @@
         <v>1</v>
       </c>
       <c r="V166" t="str">
-        <f>IF(ISBLANK(B166)=FALSE,IF(ISBLANK(B165),"},["&amp;B166&amp;"]={","["&amp;B166&amp;"]={"),IF(AND(ISBLANK(B166),ISBLANK(D166),ISBLANK(N166),ISBLANK(O166),OR(ISBLANK(B165)=FALSE,ISBLANK(D165)=FALSE,ISBLANK(N165)=FALSE,ISBLANK(O165)=FALSE)),"},},}",IF(ISBLANK(D166),"","{szContent="""&amp;D166&amp;""","&amp;IF(C166&lt;&gt;"","szTarget="""&amp;C166&amp;""",","")&amp;IF(E166&lt;&gt;"","szNote="""&amp;E166&amp;""",","")&amp;IF(M166&lt;&gt;"","col={"&amp;M166&amp;"},","")&amp;IF(N166&gt;0,"bSearch=true,","")&amp;IF(O166&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P166&gt;0,"szVoice="""&amp;P166&amp;""",","")&amp;IF(Q166&gt;0,"bTeamChannel=true,","")&amp;IF(R166&gt;0,"bWhisperChannel=true,","")&amp;IF(S166&gt;0,"bCenterAlarm=true,","")&amp;IF(T166&gt;0,"bScreenHead=true,","")&amp;IF(U166&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W166&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W166:AAH166)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W166" t="s">
@@ -38420,7 +38420,7 @@
         <v>1</v>
       </c>
       <c r="V167" t="str">
-        <f>IF(ISBLANK(B167)=FALSE,IF(ISBLANK(B166),"},["&amp;B167&amp;"]={","["&amp;B167&amp;"]={"),IF(AND(ISBLANK(B167),ISBLANK(D167),ISBLANK(N167),ISBLANK(O167),OR(ISBLANK(B166)=FALSE,ISBLANK(D166)=FALSE,ISBLANK(N166)=FALSE,ISBLANK(O166)=FALSE)),"},},}",IF(ISBLANK(D167),"","{szContent="""&amp;D167&amp;""","&amp;IF(C167&lt;&gt;"","szTarget="""&amp;C167&amp;""",","")&amp;IF(E167&lt;&gt;"","szNote="""&amp;E167&amp;""",","")&amp;IF(M167&lt;&gt;"","col={"&amp;M167&amp;"},","")&amp;IF(N167&gt;0,"bSearch=true,","")&amp;IF(O167&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P167&gt;0,"szVoice="""&amp;P167&amp;""",","")&amp;IF(Q167&gt;0,"bTeamChannel=true,","")&amp;IF(R167&gt;0,"bWhisperChannel=true,","")&amp;IF(S167&gt;0,"bCenterAlarm=true,","")&amp;IF(T167&gt;0,"bScreenHead=true,","")&amp;IF(U167&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W167&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W167:AAH167)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W167" t="s">
@@ -38450,7 +38450,7 @@
         <v>1</v>
       </c>
       <c r="V168" t="str">
-        <f>IF(ISBLANK(B168)=FALSE,IF(ISBLANK(B167),"},["&amp;B168&amp;"]={","["&amp;B168&amp;"]={"),IF(AND(ISBLANK(B168),ISBLANK(D168),ISBLANK(N168),ISBLANK(O168),OR(ISBLANK(B167)=FALSE,ISBLANK(D167)=FALSE,ISBLANK(N167)=FALSE,ISBLANK(O167)=FALSE)),"},},}",IF(ISBLANK(D168),"","{szContent="""&amp;D168&amp;""","&amp;IF(C168&lt;&gt;"","szTarget="""&amp;C168&amp;""",","")&amp;IF(E168&lt;&gt;"","szNote="""&amp;E168&amp;""",","")&amp;IF(M168&lt;&gt;"","col={"&amp;M168&amp;"},","")&amp;IF(N168&gt;0,"bSearch=true,","")&amp;IF(O168&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P168&gt;0,"szVoice="""&amp;P168&amp;""",","")&amp;IF(Q168&gt;0,"bTeamChannel=true,","")&amp;IF(R168&gt;0,"bWhisperChannel=true,","")&amp;IF(S168&gt;0,"bCenterAlarm=true,","")&amp;IF(T168&gt;0,"bScreenHead=true,","")&amp;IF(U168&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W168&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W168:AAH168)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
       </c>
       <c r="W168" t="s">
@@ -38465,7 +38465,7 @@
     </row>
     <row r="169" spans="3:27">
       <c r="V169" t="str">
-        <f>IF(ISBLANK(B169)=FALSE,IF(ISBLANK(B168),"},["&amp;B169&amp;"]={","["&amp;B169&amp;"]={"),IF(AND(ISBLANK(B169),ISBLANK(D169),ISBLANK(N169),ISBLANK(O169),OR(ISBLANK(B168)=FALSE,ISBLANK(D168)=FALSE,ISBLANK(N168)=FALSE,ISBLANK(O168)=FALSE)),"},},}",IF(ISBLANK(D169),"","{szContent="""&amp;D169&amp;""","&amp;IF(C169&lt;&gt;"","szTarget="""&amp;C169&amp;""",","")&amp;IF(E169&lt;&gt;"","szNote="""&amp;E169&amp;""",","")&amp;IF(M169&lt;&gt;"","col={"&amp;M169&amp;"},","")&amp;IF(N169&gt;0,"bSearch=true,","")&amp;IF(O169&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P169&gt;0,"szVoice="""&amp;P169&amp;""",","")&amp;IF(Q169&gt;0,"bTeamChannel=true,","")&amp;IF(R169&gt;0,"bWhisperChannel=true,","")&amp;IF(S169&gt;0,"bCenterAlarm=true,","")&amp;IF(T169&gt;0,"bScreenHead=true,","")&amp;IF(U169&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W169&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W169:AAH169)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>},},}</v>
       </c>
     </row>
@@ -38987,7 +38987,7 @@
       </c>
       <c r="T15" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="[团队监控]数据加载成功",szNote="关闭刷马等计时条",bSearch=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},},},</v>
+        <v>{szContent="[团队监控]数据加载",szNote="关闭刷马等计时条",bSearch=true,[20]={},tCountdown={{